--- a/financial_models/opportunities/000858.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/000858.SZ_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD28B488-1CE7-4CD8-A733-1EB33A69C350}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D0DC847-FAE6-4F86-BE66-BFE334050F23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="6150" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.15414602261437696</v>
+        <v>0.10787497156703298</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5505,7 +5505,7 @@
       </c>
       <c r="C18" s="252">
         <f>C125</f>
-        <v>153.11192896882034</v>
+        <v>134.70696317865062</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>345</v>
@@ -5555,13 +5555,13 @@
       </c>
       <c r="C22" s="255">
         <f>E140</f>
-        <v>75.777412292583293</v>
+        <v>62.294573384207148</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>404</v>
       </c>
       <c r="E22" s="79">
-        <v>0.29465259038036601</v>
+        <v>0.32950289523458665</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -5570,13 +5570,13 @@
       </c>
       <c r="C23" s="256">
         <f>E141</f>
-        <v>94.440933033498069</v>
+        <v>78.83107675053482</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>405</v>
       </c>
       <c r="E23" s="443">
-        <v>0.20075184365903001</v>
+        <v>0.22621703288100403</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -5585,13 +5585,13 @@
       </c>
       <c r="C24" s="256">
         <f>E144</f>
-        <v>116.62555175843582</v>
+        <v>112.14039032279322</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>406</v>
       </c>
       <c r="E24" s="443">
-        <v>0.1174</v>
+        <v>8.6999999999999994E-2</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -5600,7 +5600,7 @@
       </c>
       <c r="C25" s="256">
         <f>E145</f>
-        <v>131.56371311308598</v>
+        <v>116.64459638273874</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>407</v>
@@ -6354,7 +6354,7 @@
     <row r="118" spans="2:6">
       <c r="B118" s="205" t="str">
         <f>DCF!B90&amp;" ("&amp;DCF!D90&amp;"yrs)"</f>
-        <v>Snowball Scenario (15yrs)</v>
+        <v>Snowball Scenario (5yrs)</v>
       </c>
       <c r="C118" s="206">
         <f>DCF!C90</f>
@@ -6362,7 +6362,7 @@
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>188.89 CNY</v>
+        <v>147.07 CNY</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6370,13 +6370,13 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>-5.1402664599581899E-2</v>
+        <v>-8.8861014087690589E-3</v>
       </c>
     </row>
     <row r="119" spans="2:6">
       <c r="B119" s="205" t="str">
         <f>DCF!B91&amp;" ("&amp;DCF!D91&amp;"yrs)"</f>
-        <v>Optimistic (15yrs)</v>
+        <v>Optimistic (5yrs)</v>
       </c>
       <c r="C119" s="198">
         <f>DCF!C91</f>
@@ -6384,7 +6384,7 @@
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>160.29 CNY</v>
+        <v>137.65 CNY</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6392,13 +6392,13 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>2.900384096051417E-3</v>
+        <v>1.3678062151602804E-2</v>
       </c>
     </row>
     <row r="120" spans="2:6">
       <c r="B120" s="205" t="str">
         <f>DCF!B92&amp;" ("&amp;DCF!D92&amp;"yrs)"</f>
-        <v>Base (15yrs)</v>
+        <v>Base (5yrs)</v>
       </c>
       <c r="C120" s="198">
         <f>DCF!C92</f>
@@ -6406,7 +6406,7 @@
       </c>
       <c r="D120" s="207" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>148.26 CNY</v>
+        <v>133.19 CNY</v>
       </c>
       <c r="E120" s="199">
         <f>DCF!F92</f>
@@ -6414,13 +6414,13 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>2.9834228701124801E-2</v>
+        <v>2.5106272015644755E-2</v>
       </c>
     </row>
     <row r="121" spans="2:6">
       <c r="B121" s="205" t="str">
         <f>DCF!B93&amp;" ("&amp;DCF!D93&amp;"yrs)"</f>
-        <v>Pessimistic (15yrs)</v>
+        <v>Pessimistic (5yrs)</v>
       </c>
       <c r="C121" s="198">
         <f>DCF!C93</f>
@@ -6428,7 +6428,7 @@
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>137.51 CNY</v>
+        <v>128.89 CNY</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6436,13 +6436,13 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>5.6500650452795217E-2</v>
+        <v>3.6626507210125503E-2</v>
       </c>
     </row>
     <row r="122" spans="2:6">
       <c r="B122" s="205" t="str">
         <f>DCF!B94&amp;" ("&amp;DCF!D94&amp;"yrs)"</f>
-        <v>Devil's advocate (15yrs)</v>
+        <v>Devil's advocate (5yrs)</v>
       </c>
       <c r="C122" s="198">
         <f>DCF!C94</f>
@@ -6450,7 +6450,7 @@
       </c>
       <c r="D122" s="207" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>127.91 CNY</v>
+        <v>124.75 CNY</v>
       </c>
       <c r="E122" s="199">
         <f>DCF!F94</f>
@@ -6458,7 +6458,7 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>8.2809577370351509E-2</v>
+        <v>4.823427764461069E-2</v>
       </c>
     </row>
     <row r="124" spans="2:6">
@@ -6476,7 +6476,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>153.11192896882034</v>
+        <v>134.70696317865062</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6579,19 +6579,19 @@
       </c>
       <c r="C140" s="333">
         <f>Scenarios!C62</f>
-        <v>5.2189196802236735</v>
+        <v>4.9724613932919821</v>
       </c>
       <c r="D140" s="333">
         <f>Scenarios!D62</f>
-        <v>70.558492612359615</v>
+        <v>57.322111990915168</v>
       </c>
       <c r="E140" s="334">
         <f>Scenarios!E62</f>
-        <v>75.777412292583293</v>
+        <v>62.294573384207148</v>
       </c>
       <c r="F140" s="335">
         <f>E22</f>
-        <v>0.29465259038036601</v>
+        <v>0.32950289523458665</v>
       </c>
     </row>
     <row r="141" spans="1:6">
@@ -6600,19 +6600,19 @@
       </c>
       <c r="C141" s="333">
         <f>Scenarios!C63</f>
-        <v>6.0008296580061398</v>
+        <v>5.7696729926225894</v>
       </c>
       <c r="D141" s="333">
         <f>Scenarios!D63</f>
-        <v>88.44010337549193</v>
+        <v>73.061403757912231</v>
       </c>
       <c r="E141" s="334">
         <f>Scenarios!E63</f>
-        <v>94.440933033498069</v>
+        <v>78.83107675053482</v>
       </c>
       <c r="F141" s="335">
         <f>Scenarios!F63</f>
-        <v>0.20075184365903001</v>
+        <v>0.22621703288100403</v>
       </c>
     </row>
     <row r="142" spans="1:6">
@@ -6647,19 +6647,19 @@
       </c>
       <c r="C144" s="333">
         <f>Scenarios!C66</f>
-        <v>6.8809853754896215</v>
+        <v>7.2582809357033913</v>
       </c>
       <c r="D144" s="333">
         <f>Scenarios!D66</f>
-        <v>109.7445663829462</v>
+        <v>104.88210938708983</v>
       </c>
       <c r="E144" s="334">
         <f>Scenarios!E66</f>
-        <v>116.62555175843582</v>
+        <v>112.14039032279322</v>
       </c>
       <c r="F144" s="335">
         <f>E24</f>
-        <v>0.1174</v>
+        <v>8.6999999999999994E-2</v>
       </c>
     </row>
     <row r="145" spans="1:6">
@@ -6672,11 +6672,11 @@
       </c>
       <c r="D145" s="333">
         <f>Scenarios!D67</f>
-        <v>124.11295772766583</v>
+        <v>109.19384099731857</v>
       </c>
       <c r="E145" s="334">
         <f>Scenarios!E67</f>
-        <v>131.56371311308598</v>
+        <v>116.64459638273874</v>
       </c>
       <c r="F145" s="335">
         <f>Scenarios!F67</f>
@@ -14819,7 +14819,7 @@
       <c r="D115" s="52"/>
       <c r="E115" s="451" t="str">
         <f>DCF!F15&amp;"yrs Projection"</f>
-        <v>8yrs Projection</v>
+        <v>3yrs Projection</v>
       </c>
       <c r="F115" s="52"/>
       <c r="G115" s="22" t="str">
@@ -16331,7 +16331,7 @@
       </c>
       <c r="C15" s="148">
         <f>Scenarios!C45</f>
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E15" s="308" t="str">
         <f>IF(F14="II","Change year","Terminal Year")</f>
@@ -16339,7 +16339,7 @@
       </c>
       <c r="F15" s="310">
         <f>IF(F14="II",_xlfn.CEILING.MATH(C15/2),C15+1)</f>
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H15" s="97" t="s">
         <v>427</v>
@@ -16405,7 +16405,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>152.73715485977306</v>
+        <v>134.89477814489302</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -16555,7 +16555,7 @@
     <row r="23" spans="1:21">
       <c r="A23" s="302" t="str">
         <f t="shared" si="0"/>
-        <v>I</v>
+        <v>II</v>
       </c>
       <c r="B23" s="117">
         <v>3</v>
@@ -16570,11 +16570,11 @@
       </c>
       <c r="E23" s="299">
         <f t="shared" si="6"/>
-        <v>0.4665778415257858</v>
+        <v>0.40406742273746776</v>
       </c>
       <c r="F23" s="277">
         <f t="shared" si="7"/>
-        <v>44656494648.866585</v>
+        <v>38673578329.929779</v>
       </c>
       <c r="G23" s="299">
         <f t="shared" si="2"/>
@@ -16582,15 +16582,15 @@
       </c>
       <c r="H23" s="277">
         <f t="shared" si="8"/>
-        <v>31986470684.304981</v>
+        <v>27499283445.102375</v>
       </c>
       <c r="I23" s="299">
         <f t="shared" si="9"/>
-        <v>2.3855917147759476E-2</v>
+        <v>-0.11977459625120046</v>
       </c>
       <c r="J23" s="299">
         <f t="shared" ref="J23:J50" si="10">IF(A23="", 0,H23/C23)</f>
-        <v>0.33419950596793269</v>
+        <v>0.28731669187669412</v>
       </c>
       <c r="K23" s="119">
         <f t="shared" si="3"/>
@@ -16598,7 +16598,7 @@
       </c>
       <c r="L23" s="277">
         <f t="shared" si="4"/>
-        <v>25928322571.827847</v>
+        <v>22290996049.420277</v>
       </c>
       <c r="N23" s="275"/>
       <c r="O23" s="275"/>
@@ -16612,7 +16612,7 @@
     <row r="24" spans="1:21">
       <c r="A24" s="302" t="str">
         <f t="shared" si="0"/>
-        <v>I</v>
+        <v>II</v>
       </c>
       <c r="B24" s="117">
         <v>4</v>
@@ -16627,11 +16627,11 @@
       </c>
       <c r="E24" s="299">
         <f t="shared" si="6"/>
-        <v>0.4665778415257858</v>
+        <v>0.40406742273746776</v>
       </c>
       <c r="F24" s="277">
         <f t="shared" si="7"/>
-        <v>45721816285.319313</v>
+        <v>39596172010.375977</v>
       </c>
       <c r="G24" s="299">
         <f t="shared" si="2"/>
@@ -16639,15 +16639,15 @@
       </c>
       <c r="H24" s="277">
         <f t="shared" si="8"/>
-        <v>32749537278.799</v>
+        <v>28155304072.591496</v>
       </c>
       <c r="I24" s="299">
         <f t="shared" si="9"/>
-        <v>2.3855917147759476E-2</v>
+        <v>2.3855917147759698E-2</v>
       </c>
       <c r="J24" s="299">
         <f t="shared" si="10"/>
-        <v>0.33419950596793269</v>
+        <v>0.28731669187669417</v>
       </c>
       <c r="K24" s="119">
         <f t="shared" si="3"/>
@@ -16655,7 +16655,7 @@
       </c>
       <c r="L24" s="277">
         <f t="shared" si="4"/>
-        <v>24752323064.691612</v>
+        <v>21279970353.674854</v>
       </c>
       <c r="N24" s="275"/>
       <c r="O24" s="275"/>
@@ -16669,7 +16669,7 @@
     <row r="25" spans="1:21">
       <c r="A25" s="302" t="str">
         <f t="shared" si="0"/>
-        <v>I</v>
+        <v>II</v>
       </c>
       <c r="B25" s="117">
         <v>5</v>
@@ -16684,11 +16684,11 @@
       </c>
       <c r="E25" s="299">
         <f t="shared" si="6"/>
-        <v>0.4665778415257858</v>
+        <v>0.40406742273746776</v>
       </c>
       <c r="F25" s="277">
         <f t="shared" si="7"/>
-        <v>46812552146.466972</v>
+        <v>40540775009.223938</v>
       </c>
       <c r="G25" s="299">
         <f t="shared" si="2"/>
@@ -16696,7 +16696,7 @@
       </c>
       <c r="H25" s="277">
         <f t="shared" si="8"/>
-        <v>33530807526.749489</v>
+        <v>28826974673.817215</v>
       </c>
       <c r="I25" s="299">
         <f t="shared" si="9"/>
@@ -16704,7 +16704,7 @@
       </c>
       <c r="J25" s="299">
         <f t="shared" si="10"/>
-        <v>0.33419950596793269</v>
+        <v>0.28731669187669417</v>
       </c>
       <c r="K25" s="119">
         <f t="shared" si="3"/>
@@ -16712,7 +16712,7 @@
       </c>
       <c r="L25" s="277">
         <f t="shared" si="4"/>
-        <v>23629661942.132843</v>
+        <v>20314800525.257717</v>
       </c>
       <c r="N25" s="275"/>
       <c r="O25" s="275"/>
@@ -16726,26 +16726,26 @@
     <row r="26" spans="1:21">
       <c r="A26" s="302" t="str">
         <f t="shared" si="0"/>
-        <v>I</v>
+        <v/>
       </c>
       <c r="B26" s="117">
         <v>6</v>
       </c>
       <c r="C26" s="277">
         <f t="shared" si="5"/>
-        <v>102725213771.85764</v>
+        <v>0</v>
       </c>
       <c r="D26" s="299">
         <f t="shared" si="1"/>
-        <v>2.38559171477595E-2</v>
+        <v>0</v>
       </c>
       <c r="E26" s="299">
         <f t="shared" si="6"/>
-        <v>0.4665778415257858</v>
+        <v>0</v>
       </c>
       <c r="F26" s="277">
         <f t="shared" si="7"/>
-        <v>47929308511.948257</v>
+        <v>0</v>
       </c>
       <c r="G26" s="299">
         <f t="shared" si="2"/>
@@ -16753,48 +16753,48 @@
       </c>
       <c r="H26" s="277">
         <f t="shared" si="8"/>
-        <v>34330715693.0051</v>
+        <v>0</v>
       </c>
       <c r="I26" s="299">
         <f t="shared" si="9"/>
-        <v>2.3855917147759698E-2</v>
+        <v>0</v>
       </c>
       <c r="J26" s="299">
         <f t="shared" si="10"/>
-        <v>0.33419950596793274</v>
+        <v>0</v>
       </c>
       <c r="K26" s="119">
         <f t="shared" si="3"/>
-        <v>0.65707689293158289</v>
+        <v>0</v>
       </c>
       <c r="L26" s="277">
         <f t="shared" si="4"/>
-        <v>22557919999.677326</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:21">
       <c r="A27" s="302" t="str">
         <f t="shared" si="0"/>
-        <v>I</v>
+        <v/>
       </c>
       <c r="B27" s="117">
         <v>7</v>
       </c>
       <c r="C27" s="277">
         <f t="shared" si="5"/>
-        <v>105175817960.58495</v>
+        <v>0</v>
       </c>
       <c r="D27" s="299">
         <f t="shared" si="1"/>
-        <v>2.38559171477595E-2</v>
+        <v>0</v>
       </c>
       <c r="E27" s="299">
         <f t="shared" si="6"/>
-        <v>0.4665778415257858</v>
+        <v>0</v>
       </c>
       <c r="F27" s="277">
         <f t="shared" si="7"/>
-        <v>49072706124.758698</v>
+        <v>0</v>
       </c>
       <c r="G27" s="299">
         <f t="shared" si="2"/>
@@ -16802,48 +16802,48 @@
       </c>
       <c r="H27" s="277">
         <f t="shared" si="8"/>
-        <v>35149706402.200706</v>
+        <v>0</v>
       </c>
       <c r="I27" s="299">
         <f t="shared" si="9"/>
-        <v>2.3855917147759254E-2</v>
+        <v>0</v>
       </c>
       <c r="J27" s="299">
         <f t="shared" si="10"/>
-        <v>0.33419950596793263</v>
+        <v>0</v>
       </c>
       <c r="K27" s="119">
         <f t="shared" si="3"/>
-        <v>0.61265910762851561</v>
+        <v>0</v>
       </c>
       <c r="L27" s="277">
         <f t="shared" si="4"/>
-        <v>21534787757.776608</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:21">
       <c r="A28" s="302" t="str">
         <f t="shared" si="0"/>
-        <v>II</v>
+        <v/>
       </c>
       <c r="B28" s="117">
         <v>8</v>
       </c>
       <c r="C28" s="277">
         <f t="shared" si="5"/>
-        <v>107684883559.80049</v>
+        <v>0</v>
       </c>
       <c r="D28" s="299">
         <f t="shared" si="1"/>
-        <v>2.38559171477595E-2</v>
+        <v>0</v>
       </c>
       <c r="E28" s="299">
         <f t="shared" si="6"/>
-        <v>0.40406742273746776</v>
+        <v>0</v>
       </c>
       <c r="F28" s="277">
         <f t="shared" si="7"/>
-        <v>43511953367.7929</v>
+        <v>0</v>
       </c>
       <c r="G28" s="299">
         <f t="shared" si="2"/>
@@ -16851,48 +16851,48 @@
       </c>
       <c r="H28" s="277">
         <f t="shared" si="8"/>
-        <v>30939664509.528885</v>
+        <v>0</v>
       </c>
       <c r="I28" s="299">
         <f t="shared" si="9"/>
-        <v>-0.11977459625120035</v>
+        <v>0</v>
       </c>
       <c r="J28" s="299">
         <f t="shared" si="10"/>
-        <v>0.28731669187669412</v>
+        <v>0</v>
       </c>
       <c r="K28" s="119">
         <f t="shared" si="3"/>
-        <v>0.5712439231967511</v>
+        <v>0</v>
       </c>
       <c r="L28" s="277">
         <f t="shared" si="4"/>
-        <v>17674095336.814564</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:21">
       <c r="A29" s="302" t="str">
         <f t="shared" si="0"/>
-        <v>II</v>
+        <v/>
       </c>
       <c r="B29" s="117">
         <v>9</v>
       </c>
       <c r="C29" s="277">
         <f t="shared" si="5"/>
-        <v>110253805220.06921</v>
+        <v>0</v>
       </c>
       <c r="D29" s="299">
         <f t="shared" si="1"/>
-        <v>2.38559171477595E-2</v>
+        <v>0</v>
       </c>
       <c r="E29" s="299">
         <f t="shared" si="6"/>
-        <v>0.40406742273746776</v>
+        <v>0</v>
       </c>
       <c r="F29" s="277">
         <f t="shared" si="7"/>
-        <v>44549970922.272141</v>
+        <v>0</v>
       </c>
       <c r="G29" s="299">
         <f t="shared" si="2"/>
@@ -16900,48 +16900,48 @@
       </c>
       <c r="H29" s="277">
         <f t="shared" si="8"/>
-        <v>31677758582.647682</v>
+        <v>0</v>
       </c>
       <c r="I29" s="299">
         <f t="shared" si="9"/>
-        <v>2.3855917147759476E-2</v>
+        <v>0</v>
       </c>
       <c r="J29" s="299">
         <f t="shared" si="10"/>
-        <v>0.28731669187669417</v>
+        <v>0</v>
       </c>
       <c r="K29" s="119">
         <f t="shared" si="3"/>
-        <v>0.53262836661701729</v>
+        <v>0</v>
       </c>
       <c r="L29" s="277">
         <f t="shared" si="4"/>
-        <v>16872472811.963835</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:21">
       <c r="A30" s="302" t="str">
         <f t="shared" si="0"/>
-        <v>II</v>
+        <v/>
       </c>
       <c r="B30" s="117">
         <v>10</v>
       </c>
       <c r="C30" s="277">
         <f t="shared" si="5"/>
-        <v>112884010862.62439</v>
+        <v>0</v>
       </c>
       <c r="D30" s="299">
         <f t="shared" si="1"/>
-        <v>2.38559171477595E-2</v>
+        <v>0</v>
       </c>
       <c r="E30" s="299">
         <f t="shared" si="6"/>
-        <v>0.40406742273746776</v>
+        <v>0</v>
       </c>
       <c r="F30" s="277">
         <f t="shared" si="7"/>
-        <v>45612751337.528954</v>
+        <v>0</v>
       </c>
       <c r="G30" s="299">
         <f t="shared" si="2"/>
@@ -16949,48 +16949,48 @@
       </c>
       <c r="H30" s="277">
         <f t="shared" si="8"/>
-        <v>32433460566.822048</v>
+        <v>0</v>
       </c>
       <c r="I30" s="299">
         <f t="shared" si="9"/>
-        <v>2.3855917147759254E-2</v>
+        <v>0</v>
       </c>
       <c r="J30" s="299">
         <f t="shared" si="10"/>
-        <v>0.28731669187669417</v>
+        <v>0</v>
       </c>
       <c r="K30" s="119">
         <f t="shared" si="3"/>
-        <v>0.49662318565689262</v>
+        <v>0</v>
       </c>
       <c r="L30" s="277">
         <f t="shared" si="4"/>
-        <v>16107208508.572372</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:21">
       <c r="A31" s="302" t="str">
         <f t="shared" si="0"/>
-        <v>II</v>
+        <v/>
       </c>
       <c r="B31" s="117">
         <v>11</v>
       </c>
       <c r="C31" s="277">
         <f t="shared" si="5"/>
-        <v>115576962473.06993</v>
+        <v>0</v>
       </c>
       <c r="D31" s="299">
         <f t="shared" si="1"/>
-        <v>2.38559171477595E-2</v>
+        <v>0</v>
       </c>
       <c r="E31" s="299">
         <f t="shared" si="6"/>
-        <v>0.40406742273746776</v>
+        <v>0</v>
       </c>
       <c r="F31" s="277">
         <f t="shared" si="7"/>
-        <v>46700885354.318398</v>
+        <v>0</v>
       </c>
       <c r="G31" s="299">
         <f t="shared" si="2"/>
@@ -16998,48 +16998,48 @@
       </c>
       <c r="H31" s="277">
         <f t="shared" si="8"/>
-        <v>33207190514.919281</v>
+        <v>0</v>
       </c>
       <c r="I31" s="299">
         <f t="shared" si="9"/>
-        <v>2.3855917147759476E-2</v>
+        <v>0</v>
       </c>
       <c r="J31" s="299">
         <f t="shared" si="10"/>
-        <v>0.28731669187669417</v>
+        <v>0</v>
       </c>
       <c r="K31" s="119">
         <f t="shared" si="3"/>
-        <v>0.46305192135840806</v>
+        <v>0</v>
       </c>
       <c r="L31" s="277">
         <f t="shared" si="4"/>
-        <v>15376653370.848078</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:21">
       <c r="A32" s="302" t="str">
         <f t="shared" si="0"/>
-        <v>II</v>
+        <v/>
       </c>
       <c r="B32" s="117">
         <v>12</v>
       </c>
       <c r="C32" s="277">
         <f t="shared" si="5"/>
-        <v>118334156914.0172</v>
+        <v>0</v>
       </c>
       <c r="D32" s="299">
         <f t="shared" si="1"/>
-        <v>2.38559171477595E-2</v>
+        <v>0</v>
       </c>
       <c r="E32" s="299">
         <f t="shared" si="6"/>
-        <v>0.40406742273746776</v>
+        <v>0</v>
       </c>
       <c r="F32" s="277">
         <f t="shared" si="7"/>
-        <v>47814977806.058029</v>
+        <v>0</v>
       </c>
       <c r="G32" s="299">
         <f t="shared" si="2"/>
@@ -17047,48 +17047,48 @@
       </c>
       <c r="H32" s="277">
         <f t="shared" si="8"/>
-        <v>33999378500.553051</v>
+        <v>0</v>
       </c>
       <c r="I32" s="299">
         <f t="shared" si="9"/>
-        <v>2.3855917147759254E-2</v>
+        <v>0</v>
       </c>
       <c r="J32" s="299">
         <f t="shared" si="10"/>
-        <v>0.28731669187669412</v>
+        <v>0</v>
       </c>
       <c r="K32" s="119">
         <f t="shared" si="3"/>
-        <v>0.43175004322462285</v>
+        <v>0</v>
       </c>
       <c r="L32" s="277">
         <f t="shared" si="4"/>
-        <v>14679233137.224092</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:21">
       <c r="A33" s="302" t="str">
         <f t="shared" si="0"/>
-        <v>II</v>
+        <v/>
       </c>
       <c r="B33" s="117">
         <v>13</v>
       </c>
       <c r="C33" s="277">
         <f t="shared" si="5"/>
-        <v>121157126757.10796</v>
+        <v>0</v>
       </c>
       <c r="D33" s="299">
         <f t="shared" si="1"/>
-        <v>2.38559171477595E-2</v>
+        <v>0</v>
       </c>
       <c r="E33" s="299">
         <f t="shared" si="6"/>
-        <v>0.40406742273746776</v>
+        <v>0</v>
       </c>
       <c r="F33" s="277">
         <f t="shared" si="7"/>
-        <v>48955647955.021309</v>
+        <v>0</v>
       </c>
       <c r="G33" s="299">
         <f t="shared" si="2"/>
@@ -17096,23 +17096,23 @@
       </c>
       <c r="H33" s="277">
         <f t="shared" si="8"/>
-        <v>34810464857.137566</v>
+        <v>0</v>
       </c>
       <c r="I33" s="299">
         <f t="shared" si="9"/>
-        <v>2.3855917147759698E-2</v>
+        <v>0</v>
       </c>
       <c r="J33" s="299">
         <f t="shared" si="10"/>
-        <v>0.28731669187669417</v>
+        <v>0</v>
       </c>
       <c r="K33" s="119">
         <f t="shared" si="3"/>
-        <v>0.40256414286678116</v>
+        <v>0</v>
       </c>
       <c r="L33" s="277">
         <f t="shared" si="4"/>
-        <v>14013444948.007792</v>
+        <v>0</v>
       </c>
       <c r="N33" s="275"/>
       <c r="O33" s="275"/>
@@ -17126,26 +17126,26 @@
     <row r="34" spans="1:21">
       <c r="A34" s="302" t="str">
         <f t="shared" si="0"/>
-        <v>II</v>
+        <v/>
       </c>
       <c r="B34" s="117">
         <v>14</v>
       </c>
       <c r="C34" s="277">
         <f t="shared" si="5"/>
-        <v>124047441134.88611</v>
+        <v>0</v>
       </c>
       <c r="D34" s="299">
         <f t="shared" si="1"/>
-        <v>2.38559171477595E-2</v>
+        <v>0</v>
       </c>
       <c r="E34" s="299">
         <f t="shared" si="6"/>
-        <v>0.40406742273746776</v>
+        <v>0</v>
       </c>
       <c r="F34" s="277">
         <f t="shared" si="7"/>
-        <v>50123529836.55117</v>
+        <v>0</v>
       </c>
       <c r="G34" s="299">
         <f t="shared" si="2"/>
@@ -17153,23 +17153,23 @@
       </c>
       <c r="H34" s="277">
         <f t="shared" si="8"/>
-        <v>35640900422.644424</v>
+        <v>0</v>
       </c>
       <c r="I34" s="299">
         <f t="shared" si="9"/>
-        <v>2.3855917147759254E-2</v>
+        <v>0</v>
       </c>
       <c r="J34" s="299">
         <f t="shared" si="10"/>
-        <v>0.28731669187669412</v>
+        <v>0</v>
       </c>
       <c r="K34" s="119">
         <f t="shared" si="3"/>
-        <v>0.37535118216016894</v>
+        <v>0</v>
       </c>
       <c r="L34" s="277">
         <f t="shared" si="4"/>
-        <v>13377854106.89245</v>
+        <v>0</v>
       </c>
       <c r="N34" s="275"/>
       <c r="O34" s="275"/>
@@ -17183,26 +17183,26 @@
     <row r="35" spans="1:21">
       <c r="A35" s="302" t="str">
         <f t="shared" si="0"/>
-        <v>II</v>
+        <v/>
       </c>
       <c r="B35" s="117">
         <v>15</v>
       </c>
       <c r="C35" s="277">
         <f t="shared" si="5"/>
-        <v>127006706612.99152</v>
+        <v>0</v>
       </c>
       <c r="D35" s="299">
         <f t="shared" si="1"/>
-        <v>2.38559171477595E-2</v>
+        <v>0</v>
       </c>
       <c r="E35" s="299">
         <f t="shared" si="6"/>
-        <v>0.40406742273746776</v>
+        <v>0</v>
       </c>
       <c r="F35" s="277">
         <f t="shared" si="7"/>
-        <v>51319272611.485184</v>
+        <v>0</v>
       </c>
       <c r="G35" s="299">
         <f t="shared" si="2"/>
@@ -17210,23 +17210,23 @@
       </c>
       <c r="H35" s="277">
         <f t="shared" si="8"/>
-        <v>36491146790.198578</v>
+        <v>0</v>
       </c>
       <c r="I35" s="299">
         <f t="shared" si="9"/>
-        <v>2.3855917147759476E-2</v>
+        <v>0</v>
       </c>
       <c r="J35" s="299">
         <f t="shared" si="10"/>
-        <v>0.28731669187669417</v>
+        <v>0</v>
       </c>
       <c r="K35" s="119">
         <f t="shared" si="3"/>
-        <v>0.34997779222393377</v>
+        <v>0</v>
       </c>
       <c r="L35" s="277">
         <f t="shared" si="4"/>
-        <v>12771090989.353186</v>
+        <v>0</v>
       </c>
       <c r="N35" s="275"/>
       <c r="O35" s="275"/>
@@ -18010,11 +18010,11 @@
       </c>
       <c r="B51" s="316">
         <f>C15+1</f>
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C51" s="277">
         <f>VLOOKUP(C15,B21:C50,2,FALSE)*(1+Terminal_Growth)</f>
-        <v>129546840745.25134</v>
+        <v>102338343015.2832</v>
       </c>
       <c r="D51" s="301">
         <f>Terminal_Growth</f>
@@ -18026,7 +18026,7 @@
       </c>
       <c r="F51" s="277">
         <f>C51*E51</f>
-        <v>52345658063.71489</v>
+        <v>41351590509.408417</v>
       </c>
       <c r="G51" s="299">
         <f>F18</f>
@@ -18034,7 +18034,7 @@
       </c>
       <c r="H51" s="277">
         <f>(F51*(1-$I$10)+C51*(G51-$I$9))/Equity_Cost</f>
-        <v>513392685875.89728</v>
+        <v>405565712652.32501</v>
       </c>
       <c r="I51" s="415">
         <f>(F51*(1-$I$10)+C51*(G51-$I$9))/VLOOKUP(C15,B21:H50,COLUMN(H20)-1,FALSE)-1</f>
@@ -18043,11 +18043,11 @@
       <c r="J51" s="454"/>
       <c r="K51" s="119">
         <f>1/(1+Equity_Cost)^C15</f>
-        <v>0.34997779222393377</v>
+        <v>0.70471496766912267</v>
       </c>
       <c r="L51" s="277">
         <f t="shared" si="4"/>
-        <v>179676038746.76208</v>
+        <v>285808228079.48792</v>
       </c>
     </row>
     <row r="52" spans="1:21" ht="13.15">
@@ -18060,7 +18060,7 @@
       <c r="K52" s="468"/>
       <c r="L52" s="317">
         <f>SUM(L21:L51)</f>
-        <v>474561895607.25757</v>
+        <v>405304783322.55359</v>
       </c>
     </row>
     <row r="53" spans="1:21">
@@ -18084,7 +18084,7 @@
     <row r="55" spans="1:21" ht="13.15">
       <c r="A55" s="125">
         <f>L52</f>
-        <v>474561895607.25757</v>
+        <v>405304783322.55359</v>
       </c>
       <c r="B55" s="123">
         <f>C94</f>
@@ -19093,11 +19093,11 @@
       </c>
       <c r="D90" s="133">
         <f>Scenarios!D29</f>
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>188.89313519662784</v>
+        <v>147.07344816810163</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19121,11 +19121,11 @@
       </c>
       <c r="D91" s="133">
         <f>Scenarios!D22</f>
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>160.29427540963457</v>
+        <v>137.65466955923245</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19149,11 +19149,11 @@
       </c>
       <c r="D92" s="133">
         <f>Scenarios!D23</f>
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>148.25683445578099</v>
+        <v>133.19389700161545</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19177,11 +19177,11 @@
       </c>
       <c r="D93" s="133">
         <f>Scenarios!D24</f>
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>137.51069985655747</v>
+        <v>128.8927415566335</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19205,11 +19205,11 @@
       </c>
       <c r="D94" s="133">
         <f>Scenarios!D30</f>
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>127.91454983859043</v>
+        <v>124.74671663841393</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19517,7 +19517,7 @@
         <v>111</v>
       </c>
       <c r="C18" s="137">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E18" s="450" t="s">
         <v>541</v>
@@ -19565,11 +19565,11 @@
       </c>
       <c r="D22" s="325">
         <f>C18</f>
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E22" s="326">
         <f>DCF!E91</f>
-        <v>160.29427540963457</v>
+        <v>137.65466955923245</v>
       </c>
       <c r="F22" s="328">
         <f>1-F23-F24</f>
@@ -19589,11 +19589,11 @@
       </c>
       <c r="D23" s="325">
         <f>C18</f>
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E23" s="326">
         <f>DCF!E92</f>
-        <v>148.25683445578099</v>
+        <v>133.19389700161545</v>
       </c>
       <c r="F23" s="327">
         <v>0.55000000000000004</v>
@@ -19612,11 +19612,11 @@
       </c>
       <c r="D24" s="325">
         <f>C18</f>
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E24" s="326">
         <f>DCF!E93</f>
-        <v>137.51069985655747</v>
+        <v>128.8927415566335</v>
       </c>
       <c r="F24" s="327">
         <v>0.25</v>
@@ -19632,7 +19632,7 @@
       </c>
       <c r="C25" s="441">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>147.97778899674583</v>
+        <v>133.01076265189337</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19675,11 +19675,11 @@
       </c>
       <c r="D29" s="325">
         <f>C18</f>
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E29" s="326">
         <f>DCF!E90</f>
-        <v>188.89313519662784</v>
+        <v>147.07344816810163</v>
       </c>
       <c r="F29" s="327">
         <v>0.15</v>
@@ -19698,11 +19698,11 @@
       </c>
       <c r="D30" s="325">
         <f>C18</f>
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E30" s="326">
         <f>DCF!E94</f>
-        <v>127.91454983859043</v>
+        <v>124.74671663841393</v>
       </c>
       <c r="F30" s="327">
         <v>0.05</v>
@@ -19758,7 +19758,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.15414602261437696</v>
+        <v>0.10787497156703298</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19778,7 +19778,7 @@
       </c>
       <c r="F35" s="330">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>-3.5130689103101562E-2</v>
+        <v>-7.3996144898412761E-2</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19787,7 +19787,7 @@
       </c>
       <c r="C36" s="321">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>153.11192896882034</v>
+        <v>134.70696317865062</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -19865,7 +19865,7 @@
       </c>
       <c r="C45" s="150">
         <f>C18</f>
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="D45" s="137"/>
       <c r="E45" s="221" t="s">
@@ -19890,7 +19890,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>152.73715485977306</v>
+        <v>134.89477814489302</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -19957,7 +19957,7 @@
       </c>
       <c r="F53" s="249">
         <f>BS!D89/C36</f>
-        <v>0.19905735965334909</v>
+        <v>0.2262544978580209</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -20031,23 +20031,23 @@
       </c>
       <c r="C62" s="119">
         <f>PV(F62, Holding_Period, -C58, 0)</f>
-        <v>5.2189196802236735</v>
+        <v>4.9724613932919821</v>
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>70.558492612359615</v>
+        <v>57.322111990915168</v>
       </c>
       <c r="E62" s="332">
         <f>C62+D62</f>
-        <v>75.777412292583293</v>
+        <v>62.294573384207148</v>
       </c>
       <c r="F62" s="301">
         <f>Thesis!E22</f>
-        <v>0.29465259038036601</v>
+        <v>0.32950289523458665</v>
       </c>
       <c r="G62" s="440">
         <f>(1-E62/C36)</f>
-        <v>0.5050848565299273</v>
+        <v>0.53755491242430398</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20056,23 +20056,23 @@
       </c>
       <c r="C63" s="119">
         <f>PV(F63, Holding_Period, -C58, 0)</f>
-        <v>6.0008296580061398</v>
+        <v>5.7696729926225894</v>
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>88.44010337549193</v>
+        <v>73.061403757912231</v>
       </c>
       <c r="E63" s="332">
         <f>C63+D63</f>
-        <v>94.440933033498069</v>
+        <v>78.83107675053482</v>
       </c>
       <c r="F63" s="301">
         <f>Thesis!E23</f>
-        <v>0.20075184365903001</v>
+        <v>0.22621703288100403</v>
       </c>
       <c r="G63" s="440">
         <f>(1-E63/C36)</f>
-        <v>0.38319023429761645</v>
+        <v>0.41479582873538823</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20102,23 +20102,23 @@
       </c>
       <c r="C66" s="119">
         <f>PV(F66, Holding_Period, -C58, 0)</f>
-        <v>6.8809853754896215</v>
+        <v>7.2582809357033913</v>
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>109.7445663829462</v>
+        <v>104.88210938708983</v>
       </c>
       <c r="E66" s="332">
         <f>C66+D66</f>
-        <v>116.62555175843582</v>
+        <v>112.14039032279322</v>
       </c>
       <c r="F66" s="301">
         <f>Thesis!E24</f>
-        <v>0.1174</v>
+        <v>8.6999999999999994E-2</v>
       </c>
       <c r="G66" s="440">
         <f>(1-E66/C36)</f>
-        <v>0.23829872339871438</v>
+        <v>0.16752343251869795</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20131,11 +20131,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>124.11295772766583</v>
+        <v>109.19384099731857</v>
       </c>
       <c r="E67" s="332">
         <f>C67+D67</f>
-        <v>131.56371311308598</v>
+        <v>116.64459638273874</v>
       </c>
       <c r="F67" s="301">
         <f>Thesis!E25</f>
@@ -20143,7 +20143,7 @@
       </c>
       <c r="G67" s="440">
         <f>(1-E67/C36)</f>
-        <v>0.14073505572594824</v>
+        <v>0.13408636324135137</v>
       </c>
     </row>
   </sheetData>
@@ -20279,7 +20279,7 @@
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.15414602261437696</v>
+        <v>0.10787497156703298</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20357,7 +20357,7 @@
       </c>
       <c r="C18" s="359">
         <f>C125</f>
-        <v>153.11192896882034</v>
+        <v>134.70696317865062</v>
       </c>
       <c r="D18" s="350" t="s">
         <v>360</v>
@@ -20409,14 +20409,14 @@
       </c>
       <c r="C22" s="364">
         <f>E140</f>
-        <v>75.777412292583293</v>
+        <v>62.294573384207148</v>
       </c>
       <c r="D22" s="365" t="s">
         <v>438</v>
       </c>
       <c r="E22" s="366">
         <f>Thesis!E22</f>
-        <v>0.29465259038036601</v>
+        <v>0.32950289523458665</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -20425,14 +20425,14 @@
       </c>
       <c r="C23" s="367">
         <f>E141</f>
-        <v>94.440933033498069</v>
+        <v>78.83107675053482</v>
       </c>
       <c r="D23" s="365" t="s">
         <v>439</v>
       </c>
       <c r="E23" s="368">
         <f>Thesis!E23</f>
-        <v>0.20075184365903001</v>
+        <v>0.22621703288100403</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -20441,14 +20441,14 @@
       </c>
       <c r="C24" s="367">
         <f>E144</f>
-        <v>116.62555175843582</v>
+        <v>112.14039032279322</v>
       </c>
       <c r="D24" s="365" t="s">
         <v>441</v>
       </c>
       <c r="E24" s="368">
         <f>Thesis!E24</f>
-        <v>0.1174</v>
+        <v>8.6999999999999994E-2</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -20457,7 +20457,7 @@
       </c>
       <c r="C25" s="367">
         <f>E145</f>
-        <v>131.56371311308598</v>
+        <v>116.64459638273874</v>
       </c>
       <c r="D25" s="365" t="s">
         <v>440</v>
@@ -21226,11 +21226,11 @@
       </c>
       <c r="D118" s="397">
         <f>DCF!D90</f>
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E118" s="398" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>188.89 CNY</v>
+        <v>147.07 CNY</v>
       </c>
       <c r="F118" s="399">
         <f>DCF!F90</f>
@@ -21249,11 +21249,11 @@
       </c>
       <c r="D119" s="402">
         <f>DCF!D91</f>
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E119" s="398" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>160.29 CNY</v>
+        <v>137.65 CNY</v>
       </c>
       <c r="F119" s="403">
         <f>DCF!F91</f>
@@ -21271,11 +21271,11 @@
       </c>
       <c r="D120" s="402">
         <f>DCF!D92</f>
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E120" s="398" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>148.26 CNY</v>
+        <v>133.19 CNY</v>
       </c>
       <c r="F120" s="403">
         <f>DCF!F92</f>
@@ -21293,11 +21293,11 @@
       </c>
       <c r="D121" s="402">
         <f>DCF!D93</f>
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E121" s="398" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>137.51 CNY</v>
+        <v>128.89 CNY</v>
       </c>
       <c r="F121" s="403">
         <f>DCF!F93</f>
@@ -21315,11 +21315,11 @@
       </c>
       <c r="D122" s="402">
         <f>DCF!D94</f>
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E122" s="398" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>127.91 CNY</v>
+        <v>124.75 CNY</v>
       </c>
       <c r="F122" s="403">
         <f>DCF!F94</f>
@@ -21341,7 +21341,7 @@
       </c>
       <c r="C125" s="404">
         <f>Scenarios!C36</f>
-        <v>153.11192896882034</v>
+        <v>134.70696317865062</v>
       </c>
       <c r="D125" s="343" t="str">
         <f>Market_currency</f>
@@ -21444,19 +21444,19 @@
       </c>
       <c r="C140" s="409">
         <f>Scenarios!C62</f>
-        <v>5.2189196802236735</v>
+        <v>4.9724613932919821</v>
       </c>
       <c r="D140" s="409">
         <f>Scenarios!D62</f>
-        <v>70.558492612359615</v>
+        <v>57.322111990915168</v>
       </c>
       <c r="E140" s="410">
         <f>Scenarios!E62</f>
-        <v>75.777412292583293</v>
+        <v>62.294573384207148</v>
       </c>
       <c r="F140" s="411">
         <f>E22</f>
-        <v>0.29465259038036601</v>
+        <v>0.32950289523458665</v>
       </c>
     </row>
     <row r="141" spans="1:6">
@@ -21465,19 +21465,19 @@
       </c>
       <c r="C141" s="409">
         <f>Scenarios!C63</f>
-        <v>6.0008296580061398</v>
+        <v>5.7696729926225894</v>
       </c>
       <c r="D141" s="409">
         <f>Scenarios!D63</f>
-        <v>88.44010337549193</v>
+        <v>73.061403757912231</v>
       </c>
       <c r="E141" s="410">
         <f>Scenarios!E63</f>
-        <v>94.440933033498069</v>
+        <v>78.83107675053482</v>
       </c>
       <c r="F141" s="411">
         <f>Scenarios!F63</f>
-        <v>0.20075184365903001</v>
+        <v>0.22621703288100403</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -21505,19 +21505,19 @@
       </c>
       <c r="C144" s="409">
         <f>Scenarios!C66</f>
-        <v>6.8809853754896215</v>
+        <v>7.2582809357033913</v>
       </c>
       <c r="D144" s="409">
         <f>Scenarios!D66</f>
-        <v>109.7445663829462</v>
+        <v>104.88210938708983</v>
       </c>
       <c r="E144" s="410">
         <f>Scenarios!E66</f>
-        <v>116.62555175843582</v>
+        <v>112.14039032279322</v>
       </c>
       <c r="F144" s="411">
         <f>E24</f>
-        <v>0.1174</v>
+        <v>8.6999999999999994E-2</v>
       </c>
     </row>
     <row r="145" spans="1:6">
@@ -21530,11 +21530,11 @@
       </c>
       <c r="D145" s="409">
         <f>Scenarios!D67</f>
-        <v>124.11295772766583</v>
+        <v>109.19384099731857</v>
       </c>
       <c r="E145" s="410">
         <f>Scenarios!E67</f>
-        <v>131.56371311308598</v>
+        <v>116.64459638273874</v>
       </c>
       <c r="F145" s="411">
         <f>Scenarios!F67</f>

--- a/financial_models/opportunities/000858.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/000858.SZ_Valuation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kamanl/PycharmProjects/Invest_Proc/financial_models/opportunities/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D0DC847-FAE6-4F86-BE66-BFE334050F23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D67B3D85-E630-2A41-BE07-4A42E9840B75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="17120" windowHeight="10760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -39,6 +39,17 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
     <ext uri="GoogleSheetsCustomDataVersion1">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId10" roundtripDataSignature="AMtx7mi73Cg0ax9bLfpeUuF69nNRn7idDQ=="/>
@@ -3269,27 +3280,27 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="19">
-    <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00;[Red]\-&quot;$&quot;#,##0.00"/>
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="165" formatCode="#,##0&quot;mm&quot;"/>
-    <numFmt numFmtId="166" formatCode="#,##0.00&quot;x&quot;"/>
-    <numFmt numFmtId="167" formatCode="0.00\x"/>
-    <numFmt numFmtId="168" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="169" formatCode="#,##0.0000"/>
-    <numFmt numFmtId="170" formatCode="#,##0_ "/>
-    <numFmt numFmtId="171" formatCode="#,##0.0000_);\(#,##0.0000\)"/>
-    <numFmt numFmtId="172" formatCode="#,##0.0000_ "/>
-    <numFmt numFmtId="173" formatCode="&quot;in &quot;#,##0&quot;s&quot;"/>
-    <numFmt numFmtId="174" formatCode="#,##0.00_ "/>
-    <numFmt numFmtId="175" formatCode="0&quot; yrs&quot;"/>
-    <numFmt numFmtId="176" formatCode="0.000_ "/>
-    <numFmt numFmtId="177" formatCode="&quot;every&quot;\ 0\ &quot;Months&quot;"/>
-    <numFmt numFmtId="178" formatCode="0.0\x"/>
-    <numFmt numFmtId="179" formatCode="0\x"/>
-    <numFmt numFmtId="180" formatCode="0.000000000000000%"/>
-    <numFmt numFmtId="181" formatCode="#,##0_);\(#,##0\);0;@"/>
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00;[Red]\-&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="166" formatCode="#,##0&quot;mm&quot;"/>
+    <numFmt numFmtId="167" formatCode="#,##0.00&quot;x&quot;"/>
+    <numFmt numFmtId="168" formatCode="0.00\x"/>
+    <numFmt numFmtId="169" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="170" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="171" formatCode="#,##0_ "/>
+    <numFmt numFmtId="172" formatCode="#,##0.0000_);\(#,##0.0000\)"/>
+    <numFmt numFmtId="173" formatCode="#,##0.0000_ "/>
+    <numFmt numFmtId="174" formatCode="&quot;in &quot;#,##0&quot;s&quot;"/>
+    <numFmt numFmtId="175" formatCode="#,##0.00_ "/>
+    <numFmt numFmtId="176" formatCode="0&quot; yrs&quot;"/>
+    <numFmt numFmtId="177" formatCode="0.000_ "/>
+    <numFmt numFmtId="178" formatCode="&quot;every&quot;\ 0\ &quot;Months&quot;"/>
+    <numFmt numFmtId="179" formatCode="0.0\x"/>
+    <numFmt numFmtId="180" formatCode="0\x"/>
+    <numFmt numFmtId="181" formatCode="0.000000000000000%"/>
+    <numFmt numFmtId="182" formatCode="#,##0_);\(#,##0\);0;@"/>
   </numFmts>
-  <fonts count="72">
+  <fonts count="72" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -4041,7 +4052,7 @@
     <xf numFmtId="3" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -4083,17 +4094,17 @@
     <xf numFmtId="3" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="169" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4102,7 +4113,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4176,10 +4187,10 @@
     </xf>
     <xf numFmtId="10" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="172" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="170" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="171" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -4190,7 +4201,7 @@
     <xf numFmtId="10" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -4228,7 +4239,7 @@
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4238,7 +4249,7 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4249,19 +4260,19 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="168" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="173" fontId="17" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="17" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="173" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="173" fontId="23" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="23" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -4269,8 +4280,8 @@
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="39" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="172" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="172" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="173" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="173" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="37" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="38" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -4293,29 +4304,29 @@
     </xf>
     <xf numFmtId="9" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="170" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="171" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="39" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="174" fontId="24" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="24" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="10" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="175" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="175" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="175" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="176" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="176" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="174" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="175" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="175" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="176" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -4332,15 +4343,15 @@
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="174" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="175" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="175" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="175" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="176" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -4351,11 +4362,11 @@
     <xf numFmtId="0" fontId="27" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="3" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="174" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4416,14 +4427,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="174" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="175" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="176" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="177" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="40" fontId="41" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -4436,7 +4447,7 @@
     </xf>
     <xf numFmtId="0" fontId="44" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="39" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="175" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="8" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -4473,7 +4484,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="175" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -4490,7 +4501,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="178" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="179" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
@@ -4536,7 +4547,7 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="179" fontId="46" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="180" fontId="46" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -4551,13 +4562,13 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="174" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="174" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="180" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="181" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -4573,53 +4584,53 @@
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="181" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="182" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="182" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="182" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="181" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="182" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="181" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="181" fontId="3" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="181" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="3" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="182" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="182" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="182" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="182" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="182" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="182" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="182" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="182" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="181" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="181" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="181" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="181" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="181" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="182" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="182" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="182" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="181" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="181" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="181" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="182" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="182" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="3" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -4636,7 +4647,7 @@
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -4649,21 +4660,21 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="181" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="182" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="175" fontId="25" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="25" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="25" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="181" fontId="32" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="182" fontId="32" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
@@ -4673,14 +4684,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="181" fontId="24" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="24" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="174" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="175" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="40" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -4689,8 +4700,8 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="10" fontId="29" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="175" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="174" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="175" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="29" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="51" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4702,7 +4713,7 @@
     </xf>
     <xf numFmtId="39" fontId="24" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="39" fontId="42" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="174" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="175" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -4710,7 +4721,7 @@
     <xf numFmtId="9" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="178" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4749,7 +4760,7 @@
     <xf numFmtId="4" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="165" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4763,39 +4774,39 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="64" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="175" fontId="64" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="64" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="174" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="174" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="10" fontId="56" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="66" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="173" fontId="67" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="67" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="181" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="182" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="37" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="181" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="10" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="180" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="181" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -4806,7 +4817,7 @@
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="10" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -4817,10 +4828,10 @@
     <xf numFmtId="9" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="178" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="181" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="182" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="10" fontId="60" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4829,7 +4840,7 @@
     <xf numFmtId="10" fontId="56" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="175" fontId="56" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="56" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="39" fontId="54" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4842,7 +4853,7 @@
     <xf numFmtId="10" fontId="56" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="175" fontId="56" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="56" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="10" fontId="54" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4851,8 +4862,8 @@
     <xf numFmtId="40" fontId="65" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="175" fontId="56" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="176" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="176" fontId="56" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="177" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -4860,10 +4871,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="39" fontId="54" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="174" fontId="65" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="175" fontId="65" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="54" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="68" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="10" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4872,10 +4883,10 @@
     <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="177" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="69" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4892,16 +4903,16 @@
     <xf numFmtId="4" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="177" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4922,7 +4933,7 @@
     <xf numFmtId="0" fontId="59" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="56" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="56" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4940,7 +4951,7 @@
     <xf numFmtId="40" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="175" fontId="70" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="70" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="10" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -4950,10 +4961,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="173" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -4968,7 +4979,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="10" fontId="71" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4982,34 +4993,34 @@
     <xf numFmtId="10" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5019,30 +5030,30 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="常规 2 2" xfId="1" xr:uid="{A35F4541-DCCE-4554-A311-39480A36979A}"/>
   </cellStyles>
   <dxfs count="7">
@@ -5324,7 +5335,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:I167"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="32.6640625" style="1" customWidth="1"/>
@@ -5333,7 +5344,7 @@
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:9" ht="13.9">
+    <row r="2" spans="1:9" ht="16" x14ac:dyDescent="0.25">
       <c r="A2" s="200" t="s">
         <v>225</v>
       </c>
@@ -5346,7 +5357,7 @@
       <c r="H2" s="21"/>
       <c r="I2" s="21"/>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.15">
       <c r="E3" s="428" t="s">
         <v>535</v>
       </c>
@@ -5354,7 +5365,7 @@
         <v>46066</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="12.4">
+    <row r="4" spans="1:9" ht="14" x14ac:dyDescent="0.2">
       <c r="B4" s="421" t="s">
         <v>530</v>
       </c>
@@ -5368,7 +5379,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B5" s="1" t="s">
         <v>347</v>
       </c>
@@ -5382,7 +5393,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B6" s="2" t="s">
         <v>53</v>
       </c>
@@ -5392,7 +5403,7 @@
       <c r="D6" s="45"/>
       <c r="E6" s="45"/>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B7" s="1" t="s">
         <v>349</v>
       </c>
@@ -5402,7 +5413,7 @@
       <c r="D7" s="45"/>
       <c r="E7" s="45"/>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B8" s="4" t="s">
         <v>348</v>
       </c>
@@ -5411,7 +5422,7 @@
       </c>
       <c r="E8" s="32"/>
     </row>
-    <row r="9" spans="1:9">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B9" s="4" t="s">
         <v>344</v>
       </c>
@@ -5419,7 +5430,7 @@
         <v>3881608005</v>
       </c>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B10" s="4" t="s">
         <v>350</v>
       </c>
@@ -5435,27 +5446,27 @@
         <v>0.10787497156703298</v>
       </c>
     </row>
-    <row r="11" spans="1:9">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.15">
       <c r="D11" s="5"/>
       <c r="E11" s="5"/>
     </row>
-    <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="460" t="s">
+    <row r="12" spans="1:9" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B12" s="462" t="s">
         <v>353</v>
       </c>
-      <c r="C12" s="460"/>
-      <c r="D12" s="460"/>
-      <c r="E12" s="460"/>
-      <c r="F12" s="460"/>
-    </row>
-    <row r="14" spans="1:9">
+      <c r="C12" s="462"/>
+      <c r="D12" s="462"/>
+      <c r="E12" s="462"/>
+      <c r="F12" s="462"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B14" s="42" t="str">
         <f>Scenarios!B39&amp;" Valuation Conclusion"</f>
         <v>2-stage DCF Valuation Conclusion</v>
       </c>
       <c r="C14" s="43"/>
     </row>
-    <row r="15" spans="1:9">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B15" s="1" t="s">
         <v>318</v>
       </c>
@@ -5470,7 +5481,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="16" spans="1:9">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B16" s="1" t="s">
         <v>319</v>
       </c>
@@ -5484,7 +5495,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B17" s="1" t="s">
         <v>529</v>
       </c>
@@ -5498,7 +5509,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B18" s="1" t="str">
         <f>"Expected Equity Value ("&amp;C7&amp;") :"</f>
         <v>Expected Equity Value (CNY) :</v>
@@ -5514,7 +5525,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B19" s="2" t="s">
         <v>275</v>
       </c>
@@ -5530,11 +5541,11 @@
         <v>46081</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.15">
       <c r="D20" s="5"/>
       <c r="E20" s="5"/>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B21" s="42" t="s">
         <v>402</v>
       </c>
@@ -5549,7 +5560,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B22" s="1" t="s">
         <v>311</v>
       </c>
@@ -5564,7 +5575,7 @@
         <v>0.32950289523458665</v>
       </c>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B23" s="1" t="s">
         <v>312</v>
       </c>
@@ -5579,7 +5590,7 @@
         <v>0.22621703288100403</v>
       </c>
     </row>
-    <row r="24" spans="1:6">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B24" s="1" t="s">
         <v>314</v>
       </c>
@@ -5594,7 +5605,7 @@
         <v>8.6999999999999994E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B25" s="1" t="s">
         <v>313</v>
       </c>
@@ -5609,11 +5620,11 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:6">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.15">
       <c r="D26" s="5"/>
       <c r="E26" s="5"/>
     </row>
-    <row r="27" spans="1:6" ht="13.9">
+    <row r="27" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A27" s="200" t="s">
         <v>280</v>
       </c>
@@ -5623,25 +5634,25 @@
       <c r="E27" s="34"/>
       <c r="F27" s="34"/>
     </row>
-    <row r="29" spans="1:6">
-      <c r="B29" s="460" t="s">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="B29" s="462" t="s">
         <v>354</v>
       </c>
-      <c r="C29" s="460"/>
-      <c r="D29" s="460"/>
-      <c r="E29" s="460"/>
-      <c r="F29" s="460"/>
-    </row>
-    <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="462" t="s">
+      <c r="C29" s="462"/>
+      <c r="D29" s="462"/>
+      <c r="E29" s="462"/>
+      <c r="F29" s="462"/>
+    </row>
+    <row r="30" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B30" s="466" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="462"/>
-      <c r="D30" s="462"/>
-      <c r="E30" s="462"/>
-      <c r="F30" s="462"/>
-    </row>
-    <row r="32" spans="1:6">
+      <c r="C30" s="466"/>
+      <c r="D30" s="466"/>
+      <c r="E30" s="466"/>
+      <c r="F30" s="466"/>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B32" s="192" t="s">
         <v>195</v>
       </c>
@@ -5650,16 +5661,16 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="461" t="s">
+    <row r="33" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B33" s="463" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="461"/>
-      <c r="D33" s="461"/>
-      <c r="E33" s="461"/>
-      <c r="F33" s="461"/>
-    </row>
-    <row r="34" spans="2:6">
+      <c r="C33" s="463"/>
+      <c r="D33" s="463"/>
+      <c r="E33" s="463"/>
+      <c r="F33" s="463"/>
+    </row>
+    <row r="34" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B34" s="44" t="s">
         <v>197</v>
       </c>
@@ -5672,20 +5683,20 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="35" spans="2:6">
+    <row r="35" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B35" s="44"/>
       <c r="C35" s="73"/>
     </row>
-    <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="461" t="s">
+    <row r="36" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B36" s="463" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="461"/>
-      <c r="D36" s="461"/>
-      <c r="E36" s="461"/>
-      <c r="F36" s="461"/>
-    </row>
-    <row r="37" spans="2:6">
+      <c r="C36" s="463"/>
+      <c r="D36" s="463"/>
+      <c r="E36" s="463"/>
+      <c r="F36" s="463"/>
+    </row>
+    <row r="37" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B37" s="44" t="s">
         <v>199</v>
       </c>
@@ -5698,7 +5709,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="38" spans="2:6">
+    <row r="38" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B38" s="49" t="s">
         <v>200</v>
       </c>
@@ -5711,16 +5722,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="40" spans="2:6">
-      <c r="B40" s="461" t="s">
+    <row r="40" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B40" s="463" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="461"/>
-      <c r="D40" s="461"/>
-      <c r="E40" s="461"/>
-      <c r="F40" s="461"/>
-    </row>
-    <row r="41" spans="2:6">
+      <c r="C40" s="463"/>
+      <c r="D40" s="463"/>
+      <c r="E40" s="463"/>
+      <c r="F40" s="463"/>
+    </row>
+    <row r="41" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B41" s="44" t="s">
         <v>202</v>
       </c>
@@ -5733,16 +5744,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="43" spans="2:6">
-      <c r="B43" s="461" t="s">
+    <row r="43" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B43" s="463" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="461"/>
-      <c r="D43" s="461"/>
-      <c r="E43" s="461"/>
-      <c r="F43" s="461"/>
-    </row>
-    <row r="44" spans="2:6">
+      <c r="C43" s="463"/>
+      <c r="D43" s="463"/>
+      <c r="E43" s="463"/>
+      <c r="F43" s="463"/>
+    </row>
+    <row r="44" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B44" s="44" t="s">
         <v>267</v>
       </c>
@@ -5757,7 +5768,7 @@
       <c r="E44" s="244"/>
       <c r="F44" s="244"/>
     </row>
-    <row r="45" spans="2:6">
+    <row r="45" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B45" s="44" t="s">
         <v>268</v>
       </c>
@@ -5772,7 +5783,7 @@
       <c r="E45" s="244"/>
       <c r="F45" s="244"/>
     </row>
-    <row r="46" spans="2:6">
+    <row r="46" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B46" s="44" t="s">
         <v>203</v>
       </c>
@@ -5785,12 +5796,12 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="48" spans="2:6">
+    <row r="48" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B48" s="1" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="49" spans="2:6">
+    <row r="49" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B49" s="44" t="s">
         <v>223</v>
       </c>
@@ -5803,16 +5814,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="51" spans="2:6">
-      <c r="B51" s="461" t="s">
+    <row r="51" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B51" s="463" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="461"/>
-      <c r="D51" s="461"/>
-      <c r="E51" s="461"/>
-      <c r="F51" s="461"/>
-    </row>
-    <row r="52" spans="2:6">
+      <c r="C51" s="463"/>
+      <c r="D51" s="463"/>
+      <c r="E51" s="463"/>
+      <c r="F51" s="463"/>
+    </row>
+    <row r="52" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B52" s="44" t="s">
         <v>204</v>
       </c>
@@ -5825,8 +5836,8 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="54" spans="2:6">
-      <c r="B54" s="461" t="s">
+    <row r="54" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B54" s="463" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="464"/>
@@ -5834,7 +5845,7 @@
       <c r="E54" s="464"/>
       <c r="F54" s="464"/>
     </row>
-    <row r="55" spans="2:6">
+    <row r="55" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B55" s="44" t="s">
         <v>207</v>
       </c>
@@ -5847,25 +5858,25 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="460" t="s">
+    <row r="57" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B57" s="462" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="460"/>
-      <c r="D57" s="460"/>
-      <c r="E57" s="460"/>
-      <c r="F57" s="460"/>
-    </row>
-    <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="460" t="s">
+      <c r="C57" s="462"/>
+      <c r="D57" s="462"/>
+      <c r="E57" s="462"/>
+      <c r="F57" s="462"/>
+    </row>
+    <row r="58" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B58" s="462" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="460"/>
-      <c r="D58" s="460"/>
-      <c r="E58" s="460"/>
-      <c r="F58" s="460"/>
-    </row>
-    <row r="60" spans="2:6">
+      <c r="C58" s="462"/>
+      <c r="D58" s="462"/>
+      <c r="E58" s="462"/>
+      <c r="F58" s="462"/>
+    </row>
+    <row r="60" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B60" s="44" t="s">
         <v>227</v>
       </c>
@@ -5878,7 +5889,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="61" spans="2:6">
+    <row r="61" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B61" s="44" t="s">
         <v>213</v>
       </c>
@@ -5891,7 +5902,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="62" spans="2:6">
+    <row r="62" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B62" s="204" t="s">
         <v>302</v>
       </c>
@@ -5901,7 +5912,7 @@
       </c>
       <c r="F62" s="257"/>
     </row>
-    <row r="63" spans="2:6">
+    <row r="63" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B63" s="204" t="s">
         <v>330</v>
       </c>
@@ -5917,7 +5928,7 @@
         <v>0.4127471888056104</v>
       </c>
     </row>
-    <row r="65" spans="1:6">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B65" s="192" t="s">
         <v>323</v>
       </c>
@@ -5928,7 +5939,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="66" spans="1:6">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B66" s="44" t="s">
         <v>324</v>
       </c>
@@ -5941,7 +5952,7 @@
         <v>0.26898198471339402</v>
       </c>
     </row>
-    <row r="67" spans="1:6">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B67" s="229" t="str">
         <f>Normalized_FCF!B116</f>
         <v>Pre-tax Profit/Sales</v>
@@ -5955,7 +5966,7 @@
         <v>0.43474742930380028</v>
       </c>
     </row>
-    <row r="68" spans="1:6">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B68" s="229" t="str">
         <f>Normalized_FCF!B117</f>
         <v>Sales/Total Assets</v>
@@ -5969,7 +5980,7 @@
         <v>0.4610552539366265</v>
       </c>
     </row>
-    <row r="69" spans="1:6">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B69" s="229" t="str">
         <f>Normalized_FCF!B118</f>
         <v>Total Assets/Equity</v>
@@ -5983,7 +5994,7 @@
         <v>1.3419403008261008</v>
       </c>
     </row>
-    <row r="71" spans="1:6" ht="13.9">
+    <row r="71" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A71" s="200" t="s">
         <v>475</v>
       </c>
@@ -5993,45 +6004,45 @@
       <c r="E71" s="34"/>
       <c r="F71" s="34"/>
     </row>
-    <row r="72" spans="1:6">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A72" s="191"/>
     </row>
-    <row r="73" spans="1:6">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A73" s="191"/>
-      <c r="B73" s="460" t="s">
+      <c r="B73" s="462" t="s">
         <v>476</v>
       </c>
-      <c r="C73" s="460"/>
-      <c r="D73" s="460"/>
-      <c r="E73" s="460"/>
-      <c r="F73" s="460"/>
-    </row>
-    <row r="74" spans="1:6">
+      <c r="C73" s="462"/>
+      <c r="D73" s="462"/>
+      <c r="E73" s="462"/>
+      <c r="F73" s="462"/>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A74" s="191"/>
       <c r="B74" s="1" t="s">
         <v>463</v>
       </c>
     </row>
-    <row r="75" spans="1:6">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A75" s="191"/>
     </row>
-    <row r="76" spans="1:6">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A76" s="191"/>
       <c r="B76" s="192" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="77" spans="1:6">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A77" s="191"/>
-      <c r="B77" s="460" t="s">
+      <c r="B77" s="462" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="460"/>
-      <c r="D77" s="460"/>
-      <c r="E77" s="460"/>
-      <c r="F77" s="460"/>
-    </row>
-    <row r="78" spans="1:6">
+      <c r="C77" s="462"/>
+      <c r="D77" s="462"/>
+      <c r="E77" s="462"/>
+      <c r="F77" s="462"/>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A78" s="191"/>
       <c r="B78" s="1" t="s">
         <v>215</v>
@@ -6045,7 +6056,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="79" spans="1:6">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A79" s="191"/>
       <c r="B79" s="44" t="s">
         <v>234</v>
@@ -6059,7 +6070,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="80" spans="1:6">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A80" s="191"/>
       <c r="B80" s="229" t="s">
         <v>308</v>
@@ -6069,7 +6080,7 @@
         <v>1.4942693904035366E-3</v>
       </c>
     </row>
-    <row r="81" spans="1:6">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A81" s="191"/>
       <c r="B81" s="229" t="s">
         <v>310</v>
@@ -6079,16 +6090,16 @@
         <v>5.1971735080735887E-3</v>
       </c>
     </row>
-    <row r="82" spans="1:6">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A82" s="191"/>
     </row>
-    <row r="83" spans="1:6">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A83" s="191"/>
       <c r="B83" s="1" t="s">
         <v>464</v>
       </c>
     </row>
-    <row r="84" spans="1:6">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A84" s="191"/>
       <c r="B84" s="1" t="s">
         <v>224</v>
@@ -6102,7 +6113,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="85" spans="1:6">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A85" s="191"/>
       <c r="B85" s="229" t="s">
         <v>222</v>
@@ -6116,7 +6127,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="86" spans="1:6">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A86" s="191"/>
       <c r="B86" s="44" t="s">
         <v>235</v>
@@ -6130,16 +6141,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="87" spans="1:6">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A87" s="191"/>
     </row>
-    <row r="88" spans="1:6">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A88" s="191"/>
       <c r="B88" s="1" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="89" spans="1:6">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A89" s="191"/>
       <c r="B89" s="1" t="s">
         <v>217</v>
@@ -6153,7 +6164,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="90" spans="1:6">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A90" s="191"/>
       <c r="B90" s="44" t="s">
         <v>236</v>
@@ -6167,10 +6178,10 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="91" spans="1:6">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A91" s="191"/>
     </row>
-    <row r="92" spans="1:6">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A92" s="191"/>
       <c r="B92" s="44" t="s">
         <v>467</v>
@@ -6184,7 +6195,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="94" spans="1:6" ht="13.9">
+    <row r="94" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A94" s="200" t="s">
         <v>468</v>
       </c>
@@ -6194,42 +6205,42 @@
       <c r="E94" s="34"/>
       <c r="F94" s="34"/>
     </row>
-    <row r="95" spans="1:6">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A95" s="191"/>
     </row>
-    <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="460" t="s">
+    <row r="96" spans="1:6" ht="11.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B96" s="462" t="s">
         <v>483</v>
       </c>
-      <c r="C96" s="460"/>
-      <c r="D96" s="460"/>
-      <c r="E96" s="460"/>
-      <c r="F96" s="460"/>
-    </row>
-    <row r="97" spans="2:6">
-      <c r="B97" s="462" t="s">
+      <c r="C96" s="462"/>
+      <c r="D96" s="462"/>
+      <c r="E96" s="462"/>
+      <c r="F96" s="462"/>
+    </row>
+    <row r="97" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B97" s="466" t="s">
         <v>482</v>
       </c>
-      <c r="C97" s="462"/>
-      <c r="D97" s="462"/>
-      <c r="E97" s="462"/>
-      <c r="F97" s="462"/>
-    </row>
-    <row r="98" spans="2:6">
-      <c r="B98" s="462" t="s">
+      <c r="C97" s="466"/>
+      <c r="D97" s="466"/>
+      <c r="E97" s="466"/>
+      <c r="F97" s="466"/>
+    </row>
+    <row r="98" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B98" s="466" t="s">
         <v>481</v>
       </c>
-      <c r="C98" s="462"/>
-      <c r="D98" s="462"/>
-      <c r="E98" s="462"/>
-      <c r="F98" s="462"/>
-    </row>
-    <row r="100" spans="2:6">
+      <c r="C98" s="466"/>
+      <c r="D98" s="466"/>
+      <c r="E98" s="466"/>
+      <c r="F98" s="466"/>
+    </row>
+    <row r="100" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B100" s="192" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="101" spans="2:6">
+    <row r="101" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B101" s="49" t="s">
         <v>465</v>
       </c>
@@ -6238,7 +6249,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="102" spans="2:6">
+    <row r="102" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B102" s="229" t="s">
         <v>317</v>
       </c>
@@ -6247,7 +6258,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="103" spans="2:6">
+    <row r="103" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B103" s="229" t="s">
         <v>316</v>
       </c>
@@ -6256,7 +6267,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="2:6">
+    <row r="104" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B104" s="44" t="s">
         <v>214</v>
       </c>
@@ -6265,36 +6276,36 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="106" spans="2:6">
+    <row r="106" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B106" s="250" t="s">
         <v>281</v>
       </c>
       <c r="C106" s="116"/>
     </row>
-    <row r="107" spans="2:6">
-      <c r="B107" s="460" t="s">
+    <row r="107" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B107" s="462" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="460"/>
-      <c r="D107" s="460"/>
-      <c r="E107" s="460"/>
-      <c r="F107" s="460"/>
-    </row>
-    <row r="108" spans="2:6">
-      <c r="B108" s="460" t="s">
+      <c r="C107" s="462"/>
+      <c r="D107" s="462"/>
+      <c r="E107" s="462"/>
+      <c r="F107" s="462"/>
+    </row>
+    <row r="108" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B108" s="462" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="460"/>
-      <c r="D108" s="460"/>
-      <c r="E108" s="460"/>
-      <c r="F108" s="460"/>
-    </row>
-    <row r="110" spans="2:6">
+      <c r="C108" s="462"/>
+      <c r="D108" s="462"/>
+      <c r="E108" s="462"/>
+      <c r="F108" s="462"/>
+    </row>
+    <row r="110" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B110" s="192" t="s">
         <v>485</v>
       </c>
     </row>
-    <row r="111" spans="2:6">
+    <row r="111" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B111" s="49" t="s">
         <v>466</v>
       </c>
@@ -6307,7 +6318,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="112" spans="2:6">
+    <row r="112" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B112" s="44" t="s">
         <v>322</v>
       </c>
@@ -6320,21 +6331,21 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="460" t="s">
+    <row r="114" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B114" s="462" t="s">
         <v>489</v>
       </c>
-      <c r="C114" s="460"/>
-      <c r="D114" s="460"/>
-      <c r="E114" s="460"/>
-      <c r="F114" s="460"/>
-    </row>
-    <row r="116" spans="2:6">
+      <c r="C114" s="462"/>
+      <c r="D114" s="462"/>
+      <c r="E114" s="462"/>
+      <c r="F114" s="462"/>
+    </row>
+    <row r="116" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B116" s="192" t="s">
         <v>486</v>
       </c>
     </row>
-    <row r="117" spans="2:6" ht="12.4">
+    <row r="117" spans="2:6" ht="14" x14ac:dyDescent="0.2">
       <c r="B117" s="342" t="s">
         <v>101</v>
       </c>
@@ -6351,7 +6362,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="118" spans="2:6">
+    <row r="118" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B118" s="205" t="str">
         <f>DCF!B90&amp;" ("&amp;DCF!D90&amp;"yrs)"</f>
         <v>Snowball Scenario (5yrs)</v>
@@ -6373,7 +6384,7 @@
         <v>-8.8861014087690589E-3</v>
       </c>
     </row>
-    <row r="119" spans="2:6">
+    <row r="119" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B119" s="205" t="str">
         <f>DCF!B91&amp;" ("&amp;DCF!D91&amp;"yrs)"</f>
         <v>Optimistic (5yrs)</v>
@@ -6395,7 +6406,7 @@
         <v>1.3678062151602804E-2</v>
       </c>
     </row>
-    <row r="120" spans="2:6">
+    <row r="120" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B120" s="205" t="str">
         <f>DCF!B92&amp;" ("&amp;DCF!D92&amp;"yrs)"</f>
         <v>Base (5yrs)</v>
@@ -6417,7 +6428,7 @@
         <v>2.5106272015644755E-2</v>
       </c>
     </row>
-    <row r="121" spans="2:6">
+    <row r="121" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B121" s="205" t="str">
         <f>DCF!B93&amp;" ("&amp;DCF!D93&amp;"yrs)"</f>
         <v>Pessimistic (5yrs)</v>
@@ -6439,7 +6450,7 @@
         <v>3.6626507210125503E-2</v>
       </c>
     </row>
-    <row r="122" spans="2:6">
+    <row r="122" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B122" s="205" t="str">
         <f>DCF!B94&amp;" ("&amp;DCF!D94&amp;"yrs)"</f>
         <v>Devil's advocate (5yrs)</v>
@@ -6461,16 +6472,16 @@
         <v>4.823427764461069E-2</v>
       </c>
     </row>
-    <row r="124" spans="2:6">
-      <c r="B124" s="461" t="s">
+    <row r="124" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B124" s="463" t="s">
         <v>355</v>
       </c>
-      <c r="C124" s="461"/>
-      <c r="D124" s="461"/>
-      <c r="E124" s="461"/>
-      <c r="F124" s="461"/>
-    </row>
-    <row r="125" spans="2:6">
+      <c r="C124" s="463"/>
+      <c r="D124" s="463"/>
+      <c r="E124" s="463"/>
+      <c r="F124" s="463"/>
+    </row>
+    <row r="125" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B125" s="193" t="s">
         <v>218</v>
       </c>
@@ -6483,7 +6494,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="127" spans="2:6" ht="24.5" customHeight="1">
+    <row r="127" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B127" s="465" t="s">
         <v>356</v>
       </c>
@@ -6492,7 +6503,7 @@
       <c r="E127" s="465"/>
       <c r="F127" s="465"/>
     </row>
-    <row r="129" spans="1:6" ht="13.9">
+    <row r="129" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A129" s="200" t="s">
         <v>472</v>
       </c>
@@ -6502,30 +6513,30 @@
       <c r="E129" s="34"/>
       <c r="F129" s="34"/>
     </row>
-    <row r="131" spans="1:6">
-      <c r="B131" s="463" t="s">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="B131" s="467" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="463"/>
-      <c r="D131" s="463"/>
-      <c r="E131" s="463"/>
-      <c r="F131" s="463"/>
-    </row>
-    <row r="132" spans="1:6">
-      <c r="B132" s="460" t="s">
+      <c r="C131" s="467"/>
+      <c r="D131" s="467"/>
+      <c r="E131" s="467"/>
+      <c r="F131" s="467"/>
+    </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="B132" s="462" t="s">
         <v>357</v>
       </c>
-      <c r="C132" s="460"/>
-      <c r="D132" s="460"/>
-      <c r="E132" s="460"/>
-      <c r="F132" s="460"/>
-    </row>
-    <row r="134" spans="1:6">
+      <c r="C132" s="462"/>
+      <c r="D132" s="462"/>
+      <c r="E132" s="462"/>
+      <c r="F132" s="462"/>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B134" s="192" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="135" spans="1:6">
+    <row r="135" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B135" s="1" t="s">
         <v>221</v>
       </c>
@@ -6534,7 +6545,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="136" spans="1:6">
+    <row r="136" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B136" s="194" t="s">
         <v>220</v>
       </c>
@@ -6547,14 +6558,14 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="138" spans="1:6">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B138" s="192" t="s">
         <v>492</v>
       </c>
       <c r="C138" s="214"/>
       <c r="D138" s="215"/>
     </row>
-    <row r="139" spans="1:6" ht="12.4">
+    <row r="139" spans="1:6" ht="14" x14ac:dyDescent="0.2">
       <c r="B139" s="340" t="s">
         <v>460</v>
       </c>
@@ -6573,7 +6584,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="140" spans="1:6">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B140" s="336" t="s">
         <v>311</v>
       </c>
@@ -6594,7 +6605,7 @@
         <v>0.32950289523458665</v>
       </c>
     </row>
-    <row r="141" spans="1:6">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B141" s="336" t="s">
         <v>312</v>
       </c>
@@ -6615,14 +6626,14 @@
         <v>0.22621703288100403</v>
       </c>
     </row>
-    <row r="142" spans="1:6">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B142" s="194"/>
       <c r="C142" s="194"/>
       <c r="D142" s="194"/>
       <c r="E142" s="194"/>
       <c r="F142" s="194"/>
     </row>
-    <row r="143" spans="1:6" ht="12.4">
+    <row r="143" spans="1:6" ht="14" x14ac:dyDescent="0.2">
       <c r="B143" s="340" t="s">
         <v>461</v>
       </c>
@@ -6641,7 +6652,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="144" spans="1:6">
+    <row r="144" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B144" s="336" t="s">
         <v>314</v>
       </c>
@@ -6662,7 +6673,7 @@
         <v>8.6999999999999994E-2</v>
       </c>
     </row>
-    <row r="145" spans="1:6">
+    <row r="145" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B145" s="336" t="s">
         <v>313</v>
       </c>
@@ -6683,7 +6694,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="147" spans="1:6" ht="13.9">
+    <row r="147" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A147" s="200" t="s">
         <v>473</v>
       </c>
@@ -6693,21 +6704,21 @@
       <c r="E147" s="34"/>
       <c r="F147" s="34"/>
     </row>
-    <row r="149" spans="1:6">
-      <c r="B149" s="467" t="s">
+    <row r="149" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="B149" s="461" t="s">
         <v>358</v>
       </c>
-      <c r="C149" s="460"/>
-      <c r="D149" s="460"/>
-      <c r="E149" s="460"/>
-      <c r="F149" s="460"/>
-    </row>
-    <row r="151" spans="1:6">
+      <c r="C149" s="462"/>
+      <c r="D149" s="462"/>
+      <c r="E149" s="462"/>
+      <c r="F149" s="462"/>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B151" s="192" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="152" spans="1:6">
+    <row r="152" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B152" s="464" t="s">
         <v>293</v>
       </c>
@@ -6716,92 +6727,80 @@
       <c r="E152" s="464"/>
       <c r="F152" s="464"/>
     </row>
-    <row r="153" spans="1:6">
+    <row r="153" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B153" s="196" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="154" spans="1:6">
+    <row r="154" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B154" s="196" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="155" spans="1:6">
+    <row r="155" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B155" s="196" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="157" spans="1:6">
+    <row r="157" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B157" s="1" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="461" t="s">
+    <row r="158" spans="1:6" ht="34.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B158" s="463" t="s">
         <v>436</v>
       </c>
-      <c r="C158" s="461"/>
-      <c r="D158" s="461"/>
-      <c r="E158" s="461"/>
-      <c r="F158" s="461"/>
-    </row>
-    <row r="160" spans="1:6">
+      <c r="C158" s="463"/>
+      <c r="D158" s="463"/>
+      <c r="E158" s="463"/>
+      <c r="F158" s="463"/>
+    </row>
+    <row r="160" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B160" s="1" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="466" t="s">
+    <row r="161" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B161" s="460" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="466"/>
-      <c r="D161" s="466"/>
-      <c r="E161" s="466"/>
-      <c r="F161" s="466"/>
-    </row>
-    <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="466" t="s">
+      <c r="C161" s="460"/>
+      <c r="D161" s="460"/>
+      <c r="E161" s="460"/>
+      <c r="F161" s="460"/>
+    </row>
+    <row r="162" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B162" s="460" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="466"/>
-      <c r="D162" s="466"/>
-      <c r="E162" s="466"/>
-      <c r="F162" s="466"/>
-    </row>
-    <row r="164" spans="2:6">
+      <c r="C162" s="460"/>
+      <c r="D162" s="460"/>
+      <c r="E162" s="460"/>
+      <c r="F162" s="460"/>
+    </row>
+    <row r="164" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B164" s="1" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="165" spans="2:6">
+    <row r="165" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B165" s="196" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="166" spans="2:6">
+    <row r="166" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B166" s="196" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="167" spans="2:6">
+    <row r="167" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B167" s="196" t="s">
         <v>300</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6818,6 +6817,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -6845,15 +6856,15 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:M80"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="11.65"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="3" style="1" customWidth="1"/>
     <col min="2" max="2" width="27.33203125" style="1" customWidth="1"/>
     <col min="3" max="13" width="20.6640625" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.796875" style="1"/>
+    <col min="14" max="16384" width="8.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:13">
+    <row r="1" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B1" s="87" t="str">
         <f>Thesis!E17</f>
         <v>CNY</v>
@@ -6902,7 +6913,7 @@
         <v>42004</v>
       </c>
     </row>
-    <row r="2" spans="2:13" ht="13.9">
+    <row r="2" spans="2:13" ht="16" x14ac:dyDescent="0.25">
       <c r="B2" s="34" t="s">
         <v>93</v>
       </c>
@@ -6918,7 +6929,7 @@
       <c r="L2" s="35"/>
       <c r="M2" s="35"/>
     </row>
-    <row r="3" spans="2:13">
+    <row r="3" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B3" s="16" t="s">
         <v>25</v>
       </c>
@@ -6926,7 +6937,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="2:13">
+    <row r="4" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B4" s="31" t="s">
         <v>0</v>
       </c>
@@ -6946,7 +6957,7 @@
       <c r="L4" s="287"/>
       <c r="M4" s="287"/>
     </row>
-    <row r="5" spans="2:13">
+    <row r="5" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B5" s="38" t="s">
         <v>40</v>
       </c>
@@ -6968,7 +6979,7 @@
       <c r="L5" s="287"/>
       <c r="M5" s="287"/>
     </row>
-    <row r="6" spans="2:13">
+    <row r="6" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B6" s="38" t="s">
         <v>51</v>
       </c>
@@ -6990,7 +7001,7 @@
       <c r="L6" s="287"/>
       <c r="M6" s="287"/>
     </row>
-    <row r="7" spans="2:13">
+    <row r="7" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B7" s="66" t="s">
         <v>58</v>
       </c>
@@ -7010,7 +7021,7 @@
       <c r="L7" s="288"/>
       <c r="M7" s="288"/>
     </row>
-    <row r="8" spans="2:13">
+    <row r="8" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B8" s="38" t="s">
         <v>46</v>
       </c>
@@ -7030,7 +7041,7 @@
       <c r="L8" s="287"/>
       <c r="M8" s="287"/>
     </row>
-    <row r="9" spans="2:13">
+    <row r="9" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B9" s="38" t="s">
         <v>134</v>
       </c>
@@ -7046,7 +7057,7 @@
       <c r="L9" s="287"/>
       <c r="M9" s="287"/>
     </row>
-    <row r="10" spans="2:13">
+    <row r="10" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B10" s="38" t="s">
         <v>138</v>
       </c>
@@ -7062,7 +7073,7 @@
       <c r="L10" s="287"/>
       <c r="M10" s="287"/>
     </row>
-    <row r="11" spans="2:13">
+    <row r="11" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B11" s="38" t="s">
         <v>133</v>
       </c>
@@ -7078,7 +7089,7 @@
       <c r="L11" s="287"/>
       <c r="M11" s="287"/>
     </row>
-    <row r="12" spans="2:13">
+    <row r="12" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B12" s="38" t="s">
         <v>37</v>
       </c>
@@ -7099,7 +7110,7 @@
       <c r="L12" s="287"/>
       <c r="M12" s="287"/>
     </row>
-    <row r="13" spans="2:13">
+    <row r="13" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B13" s="38" t="s">
         <v>64</v>
       </c>
@@ -7119,7 +7130,7 @@
       <c r="L13" s="287"/>
       <c r="M13" s="287"/>
     </row>
-    <row r="14" spans="2:13">
+    <row r="14" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B14" s="38" t="s">
         <v>47</v>
       </c>
@@ -7139,7 +7150,7 @@
       <c r="L14" s="287"/>
       <c r="M14" s="287"/>
     </row>
-    <row r="15" spans="2:13">
+    <row r="15" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B15" s="41" t="s">
         <v>39</v>
       </c>
@@ -7159,7 +7170,7 @@
       <c r="L15" s="289"/>
       <c r="M15" s="289"/>
     </row>
-    <row r="16" spans="2:13">
+    <row r="16" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B16" s="27" t="s">
         <v>41</v>
       </c>
@@ -7179,13 +7190,13 @@
       <c r="L16" s="287"/>
       <c r="M16" s="287"/>
     </row>
-    <row r="18" spans="2:13">
+    <row r="18" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B18" s="16" t="s">
         <v>48</v>
       </c>
       <c r="C18" s="9"/>
     </row>
-    <row r="19" spans="2:13">
+    <row r="19" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B19" s="26" t="s">
         <v>44</v>
       </c>
@@ -7201,7 +7212,7 @@
       <c r="L19" s="287"/>
       <c r="M19" s="287"/>
     </row>
-    <row r="20" spans="2:13">
+    <row r="20" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B20" s="26" t="s">
         <v>50</v>
       </c>
@@ -7217,7 +7228,7 @@
       <c r="L20" s="287"/>
       <c r="M20" s="287"/>
     </row>
-    <row r="21" spans="2:13">
+    <row r="21" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B21" s="26" t="s">
         <v>49</v>
       </c>
@@ -7233,7 +7244,7 @@
       <c r="L21" s="287"/>
       <c r="M21" s="287"/>
     </row>
-    <row r="22" spans="2:13">
+    <row r="22" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B22" s="26" t="s">
         <v>286</v>
       </c>
@@ -7253,7 +7264,7 @@
       <c r="L22" s="287"/>
       <c r="M22" s="287"/>
     </row>
-    <row r="23" spans="2:13">
+    <row r="23" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B23" s="26" t="s">
         <v>288</v>
       </c>
@@ -7273,7 +7284,7 @@
       <c r="L23" s="287"/>
       <c r="M23" s="287"/>
     </row>
-    <row r="24" spans="2:13">
+    <row r="24" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B24" s="26" t="s">
         <v>287</v>
       </c>
@@ -7293,7 +7304,7 @@
       <c r="L24" s="287"/>
       <c r="M24" s="287"/>
     </row>
-    <row r="25" spans="2:13">
+    <row r="25" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B25" s="23" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
         <v>Dividend per share (CNY)</v>
@@ -7316,7 +7327,7 @@
       <c r="L25" s="37"/>
       <c r="M25" s="37"/>
     </row>
-    <row r="27" spans="2:13">
+    <row r="27" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B27" s="16" t="s">
         <v>26</v>
       </c>
@@ -7324,7 +7335,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="28" spans="2:13">
+    <row r="28" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B28" s="25" t="s">
         <v>22</v>
       </c>
@@ -7346,7 +7357,7 @@
       <c r="L28" s="287"/>
       <c r="M28" s="287"/>
     </row>
-    <row r="29" spans="2:13">
+    <row r="29" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B29" s="25" t="s">
         <v>30</v>
       </c>
@@ -7367,7 +7378,7 @@
       <c r="L29" s="287"/>
       <c r="M29" s="287"/>
     </row>
-    <row r="30" spans="2:13">
+    <row r="30" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B30" s="28" t="s">
         <v>38</v>
       </c>
@@ -7388,7 +7399,7 @@
       <c r="L30" s="289"/>
       <c r="M30" s="289"/>
     </row>
-    <row r="31" spans="2:13">
+    <row r="31" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B31" s="28" t="s">
         <v>28</v>
       </c>
@@ -7409,7 +7420,7 @@
       <c r="L31" s="289"/>
       <c r="M31" s="289"/>
     </row>
-    <row r="32" spans="2:13">
+    <row r="32" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B32" s="25" t="s">
         <v>143</v>
       </c>
@@ -7430,7 +7441,7 @@
       <c r="L32" s="287"/>
       <c r="M32" s="287"/>
     </row>
-    <row r="34" spans="2:13" ht="13.9">
+    <row r="34" spans="2:13" ht="16" x14ac:dyDescent="0.25">
       <c r="B34" s="34" t="s">
         <v>78</v>
       </c>
@@ -7446,12 +7457,12 @@
       <c r="L34" s="35"/>
       <c r="M34" s="35"/>
     </row>
-    <row r="35" spans="2:13">
+    <row r="35" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B35" s="16" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="36" spans="2:13">
+    <row r="36" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B36" s="31" t="s">
         <v>0</v>
       </c>
@@ -7500,7 +7511,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="2:13">
+    <row r="37" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B37" s="38" t="s">
         <v>40</v>
       </c>
@@ -7549,7 +7560,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" spans="2:13">
+    <row r="38" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B38" s="30" t="s">
         <v>55</v>
       </c>
@@ -7598,7 +7609,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="2:13">
+    <row r="39" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B39" s="38" t="s">
         <v>51</v>
       </c>
@@ -7647,7 +7658,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="2:13">
+    <row r="40" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B40" s="66" t="s">
         <v>58</v>
       </c>
@@ -7696,7 +7707,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="2:13">
+    <row r="41" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B41" s="66" t="s">
         <v>61</v>
       </c>
@@ -7745,7 +7756,7 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="2:13">
+    <row r="42" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B42" s="38" t="s">
         <v>46</v>
       </c>
@@ -7794,7 +7805,7 @@
         <v/>
       </c>
     </row>
-    <row r="43" spans="2:13">
+    <row r="43" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B43" s="41" t="s">
         <v>127</v>
       </c>
@@ -7843,7 +7854,7 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="2:13">
+    <row r="44" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B44" s="41" t="s">
         <v>139</v>
       </c>
@@ -7892,7 +7903,7 @@
         <v/>
       </c>
     </row>
-    <row r="45" spans="2:13">
+    <row r="45" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B45" s="38" t="s">
         <v>65</v>
       </c>
@@ -7941,7 +7952,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" spans="2:13">
+    <row r="46" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B46" s="38" t="s">
         <v>47</v>
       </c>
@@ -7990,7 +8001,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" spans="2:13">
+    <row r="47" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B47" s="41" t="s">
         <v>39</v>
       </c>
@@ -8039,7 +8050,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="2:13">
+    <row r="48" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B48" s="27" t="s">
         <v>41</v>
       </c>
@@ -8088,12 +8099,12 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="2:13">
+    <row r="50" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B50" s="16" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="51" spans="2:13">
+    <row r="51" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B51" s="38" t="s">
         <v>37</v>
       </c>
@@ -8142,7 +8153,7 @@
         <v/>
       </c>
     </row>
-    <row r="52" spans="2:13">
+    <row r="52" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B52" s="38" t="s">
         <v>64</v>
       </c>
@@ -8191,12 +8202,12 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="2:13">
+    <row r="54" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B54" s="156" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="55" spans="2:13">
+    <row r="55" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B55" s="38" t="s">
         <v>134</v>
       </c>
@@ -8245,7 +8256,7 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="2:13">
+    <row r="56" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B56" s="38" t="s">
         <v>138</v>
       </c>
@@ -8294,7 +8305,7 @@
         <v/>
       </c>
     </row>
-    <row r="57" spans="2:13">
+    <row r="57" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B57" s="38" t="s">
         <v>133</v>
       </c>
@@ -8343,7 +8354,7 @@
         <v/>
       </c>
     </row>
-    <row r="58" spans="2:13">
+    <row r="58" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B58" s="38" t="s">
         <v>135</v>
       </c>
@@ -8392,13 +8403,13 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="2:13">
+    <row r="60" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B60" s="16" t="s">
         <v>48</v>
       </c>
       <c r="C60" s="9"/>
     </row>
-    <row r="61" spans="2:13">
+    <row r="61" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B61" s="26" t="s">
         <v>44</v>
       </c>
@@ -8447,7 +8458,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="2:13">
+    <row r="62" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B62" s="26" t="s">
         <v>50</v>
       </c>
@@ -8496,7 +8507,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="2:13">
+    <row r="63" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B63" s="26" t="s">
         <v>49</v>
       </c>
@@ -8545,7 +8556,7 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="2:13">
+    <row r="64" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B64" s="26" t="s">
         <v>305</v>
       </c>
@@ -8594,7 +8605,7 @@
         <v/>
       </c>
     </row>
-    <row r="65" spans="2:13">
+    <row r="65" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B65" s="23" t="s">
         <v>34</v>
       </c>
@@ -8643,12 +8654,12 @@
         <v/>
       </c>
     </row>
-    <row r="67" spans="2:13">
+    <row r="67" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B67" s="88" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="68" spans="2:13">
+    <row r="68" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B68" s="1" t="str">
         <f>B36</f>
         <v>Sales</v>
@@ -8698,7 +8709,7 @@
         <v/>
       </c>
     </row>
-    <row r="69" spans="2:13">
+    <row r="69" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B69" s="30" t="s">
         <v>55</v>
       </c>
@@ -8747,7 +8758,7 @@
         <v/>
       </c>
     </row>
-    <row r="70" spans="2:13">
+    <row r="70" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B70" s="77" t="str">
         <f>B43</f>
         <v>Operating EBIT</v>
@@ -8797,7 +8808,7 @@
         <v/>
       </c>
     </row>
-    <row r="71" spans="2:13">
+    <row r="71" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B71" s="41" t="s">
         <v>139</v>
       </c>
@@ -8846,7 +8857,7 @@
         <v/>
       </c>
     </row>
-    <row r="72" spans="2:13">
+    <row r="72" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B72" s="77" t="str">
         <f>B47</f>
         <v>Reported Net Income</v>
@@ -8896,7 +8907,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="2:13" ht="13.9">
+    <row r="74" spans="2:13" ht="16" x14ac:dyDescent="0.25">
       <c r="B74" s="34" t="s">
         <v>79</v>
       </c>
@@ -8912,13 +8923,13 @@
       <c r="L74" s="35"/>
       <c r="M74" s="35"/>
     </row>
-    <row r="75" spans="2:13">
+    <row r="75" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B75" s="16" t="s">
         <v>26</v>
       </c>
       <c r="C75" s="9"/>
     </row>
-    <row r="76" spans="2:13">
+    <row r="76" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B76" s="25" t="s">
         <v>1</v>
       </c>
@@ -8967,7 +8978,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="2:13">
+    <row r="77" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B77" s="90" t="s">
         <v>82</v>
       </c>
@@ -9001,7 +9012,7 @@
       <c r="L77" s="291"/>
       <c r="M77" s="291"/>
     </row>
-    <row r="78" spans="2:13">
+    <row r="78" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B78" s="90" t="s">
         <v>83</v>
       </c>
@@ -9035,7 +9046,7 @@
       <c r="L78" s="291"/>
       <c r="M78" s="291"/>
     </row>
-    <row r="79" spans="2:13">
+    <row r="79" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B79" s="25" t="s">
         <v>38</v>
       </c>
@@ -9084,7 +9095,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="2:13">
+    <row r="80" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B80" s="25" t="s">
         <v>28</v>
       </c>
@@ -9165,7 +9176,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:H89"/>
-  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="2.33203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="34" style="1" bestFit="1" customWidth="1"/>
@@ -9176,7 +9187,7 @@
     <col min="9" max="16384" width="12.33203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" ht="15" customHeight="1">
+    <row r="1" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B1" s="17" t="s">
         <v>35</v>
       </c>
@@ -9192,7 +9203,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="2:8" ht="15" customHeight="1">
+    <row r="2" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B2" s="76" t="s">
         <v>131</v>
       </c>
@@ -9203,7 +9214,7 @@
       <c r="G2" s="35"/>
       <c r="H2" s="35"/>
     </row>
-    <row r="3" spans="2:8" ht="15" customHeight="1">
+    <row r="3" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B3" s="16" t="s">
         <v>154</v>
       </c>
@@ -9223,7 +9234,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="2:8" ht="15" customHeight="1">
+    <row r="4" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B4" s="4" t="s">
         <v>22</v>
       </c>
@@ -9245,7 +9256,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="5" spans="2:8" ht="15" customHeight="1">
+    <row r="5" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B5" s="1" t="s">
         <v>31</v>
       </c>
@@ -9266,7 +9277,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="6" spans="2:8" ht="15" customHeight="1">
+    <row r="6" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B6" s="4" t="s">
         <v>8</v>
       </c>
@@ -9287,7 +9298,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="7" spans="2:8" ht="15" customHeight="1">
+    <row r="7" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B7" s="1" t="s">
         <v>66</v>
       </c>
@@ -9308,7 +9319,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="8" spans="2:8" ht="15" customHeight="1">
+    <row r="8" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B8" s="1" t="s">
         <v>144</v>
       </c>
@@ -9329,7 +9340,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="9" spans="2:8" ht="15" customHeight="1">
+    <row r="9" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B9" s="4" t="s">
         <v>23</v>
       </c>
@@ -9350,7 +9361,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="10" spans="2:8" ht="15" customHeight="1">
+    <row r="10" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B10" s="4" t="s">
         <v>9</v>
       </c>
@@ -9370,7 +9381,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="11" spans="2:8" ht="15" customHeight="1">
+    <row r="11" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B11" s="4" t="s">
         <v>10</v>
       </c>
@@ -9382,7 +9393,7 @@
       </c>
       <c r="H11" s="232"/>
     </row>
-    <row r="12" spans="2:8" ht="15" customHeight="1">
+    <row r="12" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B12" s="77" t="s">
         <v>69</v>
       </c>
@@ -9406,12 +9417,12 @@
         <v>133487951707.854</v>
       </c>
     </row>
-    <row r="13" spans="2:8" ht="15" customHeight="1">
+    <row r="13" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F13" s="77"/>
       <c r="G13" s="78"/>
       <c r="H13" s="19"/>
     </row>
-    <row r="14" spans="2:8" ht="15" customHeight="1">
+    <row r="14" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B14" s="16" t="s">
         <v>153</v>
       </c>
@@ -9431,7 +9442,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="15" spans="2:8" ht="15" customHeight="1">
+    <row r="15" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B15" s="4" t="s">
         <v>327</v>
       </c>
@@ -9451,7 +9462,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="16" spans="2:8" ht="15" customHeight="1">
+    <row r="16" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B16" s="1" t="s">
         <v>32</v>
       </c>
@@ -9471,7 +9482,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="17" spans="2:8" ht="15" customHeight="1">
+    <row r="17" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B17" s="1" t="s">
         <v>66</v>
       </c>
@@ -9491,7 +9502,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="18" spans="2:8" ht="15" customHeight="1">
+    <row r="18" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="4" t="s">
         <v>144</v>
       </c>
@@ -9511,7 +9522,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="19" spans="2:8" ht="15" customHeight="1">
+    <row r="19" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B19" s="4" t="s">
         <v>24</v>
       </c>
@@ -9532,7 +9543,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="20" spans="2:8" ht="15" customHeight="1">
+    <row r="20" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B20" s="4" t="s">
         <v>16</v>
       </c>
@@ -9552,7 +9563,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="21" spans="2:8" ht="15" customHeight="1">
+    <row r="21" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B21" s="4" t="s">
         <v>17</v>
       </c>
@@ -9572,7 +9583,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="22" spans="2:8" ht="15" customHeight="1">
+    <row r="22" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B22" s="4" t="s">
         <v>18</v>
       </c>
@@ -9584,7 +9595,7 @@
       </c>
       <c r="H22" s="232"/>
     </row>
-    <row r="23" spans="2:8" ht="15" customHeight="1">
+    <row r="23" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B23" s="4" t="s">
         <v>19</v>
       </c>
@@ -9597,7 +9608,7 @@
       </c>
       <c r="H23" s="232"/>
     </row>
-    <row r="24" spans="2:8" ht="15" customHeight="1">
+    <row r="24" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B24" s="77" t="s">
         <v>70</v>
       </c>
@@ -9621,7 +9632,7 @@
         <v>217300602.50500003</v>
       </c>
     </row>
-    <row r="26" spans="2:8" ht="15" customHeight="1">
+    <row r="26" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B26" s="16" t="s">
         <v>169</v>
       </c>
@@ -9638,7 +9649,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="27" spans="2:8" ht="15" customHeight="1">
+    <row r="27" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B27" s="4" t="s">
         <v>3</v>
       </c>
@@ -9657,7 +9668,7 @@
         <v>100133635249.52902</v>
       </c>
     </row>
-    <row r="28" spans="2:8" ht="15" customHeight="1">
+    <row r="28" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B28" s="4" t="s">
         <v>4</v>
       </c>
@@ -9672,7 +9683,7 @@
       </c>
       <c r="H28" s="170"/>
     </row>
-    <row r="29" spans="2:8" ht="15" customHeight="1">
+    <row r="29" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B29" s="4" t="s">
         <v>5</v>
       </c>
@@ -9691,7 +9702,7 @@
         <v>96478905988.149017</v>
       </c>
     </row>
-    <row r="30" spans="2:8" ht="15" customHeight="1">
+    <row r="30" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B30" s="2" t="s">
         <v>6</v>
       </c>
@@ -9707,7 +9718,7 @@
       </c>
       <c r="H30" s="170"/>
     </row>
-    <row r="31" spans="2:8" ht="15" customHeight="1">
+    <row r="31" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B31" s="77" t="s">
         <v>172</v>
       </c>
@@ -9724,7 +9735,7 @@
       </c>
       <c r="H31" s="170"/>
     </row>
-    <row r="32" spans="2:8" ht="15" customHeight="1">
+    <row r="32" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B32" s="4" t="s">
         <v>7</v>
       </c>
@@ -9744,7 +9755,7 @@
         <v>149417879904.20901</v>
       </c>
     </row>
-    <row r="33" spans="2:8" ht="15" customHeight="1">
+    <row r="33" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B33" s="80" t="s">
         <v>2</v>
       </c>
@@ -9755,7 +9766,7 @@
       <c r="G33" s="2"/>
       <c r="H33" s="177"/>
     </row>
-    <row r="34" spans="2:8" ht="15" customHeight="1">
+    <row r="34" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B34" s="80"/>
       <c r="C34" s="81"/>
       <c r="F34" s="178" t="s">
@@ -9768,7 +9779,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="35" spans="2:8" ht="15" customHeight="1">
+    <row r="35" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B35" s="16" t="s">
         <v>170</v>
       </c>
@@ -9787,7 +9798,7 @@
         <v>15712627593.849998</v>
       </c>
     </row>
-    <row r="36" spans="2:8" ht="15" customHeight="1">
+    <row r="36" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B36" s="4" t="s">
         <v>11</v>
       </c>
@@ -9803,7 +9814,7 @@
       </c>
       <c r="H36" s="177"/>
     </row>
-    <row r="37" spans="2:8" ht="15" customHeight="1">
+    <row r="37" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B37" s="4" t="s">
         <v>12</v>
       </c>
@@ -9819,7 +9830,7 @@
       </c>
       <c r="H37" s="177"/>
     </row>
-    <row r="38" spans="2:8" ht="15" customHeight="1">
+    <row r="38" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B38" s="4" t="s">
         <v>13</v>
       </c>
@@ -9835,7 +9846,7 @@
       </c>
       <c r="H38" s="177"/>
     </row>
-    <row r="39" spans="2:8" ht="15" customHeight="1">
+    <row r="39" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B39" s="2" t="s">
         <v>14</v>
       </c>
@@ -9854,7 +9865,7 @@
         <v>1425969106.7839999</v>
       </c>
     </row>
-    <row r="40" spans="2:8" ht="15" customHeight="1">
+    <row r="40" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B40" s="77" t="s">
         <v>173</v>
       </c>
@@ -9874,7 +9885,7 @@
         <v>133705252310.35901</v>
       </c>
     </row>
-    <row r="41" spans="2:8" ht="15" customHeight="1">
+    <row r="41" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B41" s="4" t="s">
         <v>15</v>
       </c>
@@ -9894,7 +9905,7 @@
         <v>133487951707.854</v>
       </c>
     </row>
-    <row r="42" spans="2:8" ht="15" customHeight="1">
+    <row r="42" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B42" s="80" t="s">
         <v>20</v>
       </c>
@@ -9913,7 +9924,7 @@
         <v>217300602.50500003</v>
       </c>
     </row>
-    <row r="44" spans="2:8" ht="15" customHeight="1">
+    <row r="44" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B44" s="76" t="s">
         <v>92</v>
       </c>
@@ -9924,7 +9935,7 @@
       <c r="G44" s="35"/>
       <c r="H44" s="35"/>
     </row>
-    <row r="45" spans="2:8" ht="15" customHeight="1">
+    <row r="45" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B45" s="16" t="s">
         <v>228</v>
       </c>
@@ -9938,7 +9949,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="46" spans="2:8" ht="15" customHeight="1">
+    <row r="46" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B46" s="1" t="s">
         <v>230</v>
       </c>
@@ -9952,7 +9963,7 @@
       </c>
       <c r="F46" s="223"/>
     </row>
-    <row r="47" spans="2:8" ht="15" customHeight="1">
+    <row r="47" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B47" s="1" t="str">
         <f>"Equity per share ("&amp;Market_currency&amp;")"</f>
         <v>Equity per share (CNY)</v>
@@ -9967,10 +9978,10 @@
       </c>
       <c r="F47" s="223"/>
     </row>
-    <row r="48" spans="2:8" ht="15" customHeight="1">
+    <row r="48" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F48" s="223"/>
     </row>
-    <row r="49" spans="2:8" ht="15" customHeight="1">
+    <row r="49" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B49" s="143" t="s">
         <v>120</v>
       </c>
@@ -9983,7 +9994,7 @@
       <c r="E49" s="2"/>
       <c r="F49" s="223"/>
     </row>
-    <row r="50" spans="2:8" ht="15" customHeight="1">
+    <row r="50" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B50" s="8" t="s">
         <v>90</v>
       </c>
@@ -9997,7 +10008,7 @@
       </c>
       <c r="F50" s="223"/>
     </row>
-    <row r="51" spans="2:8" ht="15" customHeight="1">
+    <row r="51" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B51" s="1" t="s">
         <v>146</v>
       </c>
@@ -10008,10 +10019,10 @@
       </c>
       <c r="F51" s="223"/>
     </row>
-    <row r="52" spans="2:8" ht="15" customHeight="1">
+    <row r="52" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F52" s="223"/>
     </row>
-    <row r="53" spans="2:8" ht="15" customHeight="1">
+    <row r="53" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B53" s="143" t="s">
         <v>119</v>
       </c>
@@ -10023,7 +10034,7 @@
       </c>
       <c r="F53" s="223"/>
     </row>
-    <row r="54" spans="2:8" ht="15" customHeight="1">
+    <row r="54" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B54" s="1" t="s">
         <v>116</v>
       </c>
@@ -10037,7 +10048,7 @@
       </c>
       <c r="F54" s="223"/>
     </row>
-    <row r="55" spans="2:8" ht="15" customHeight="1">
+    <row r="55" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B55" s="1" t="s">
         <v>118</v>
       </c>
@@ -10051,10 +10062,10 @@
       </c>
       <c r="F55" s="223"/>
     </row>
-    <row r="56" spans="2:8" ht="15" customHeight="1">
+    <row r="56" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F56" s="223"/>
     </row>
-    <row r="57" spans="2:8" ht="15" customHeight="1">
+    <row r="57" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B57" s="143" t="s">
         <v>145</v>
       </c>
@@ -10066,7 +10077,7 @@
       </c>
       <c r="F57" s="223"/>
     </row>
-    <row r="58" spans="2:8" ht="15" customHeight="1">
+    <row r="58" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B58" s="2" t="s">
         <v>86</v>
       </c>
@@ -10077,7 +10088,7 @@
       </c>
       <c r="F58" s="5"/>
     </row>
-    <row r="59" spans="2:8" ht="15" customHeight="1">
+    <row r="59" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B59" s="1" t="s">
         <v>89</v>
       </c>
@@ -10088,10 +10099,10 @@
       </c>
       <c r="F59" s="223"/>
     </row>
-    <row r="60" spans="2:8" ht="15" customHeight="1">
+    <row r="60" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F60" s="223"/>
     </row>
-    <row r="61" spans="2:8" ht="15" customHeight="1">
+    <row r="61" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B61" s="143" t="s">
         <v>231</v>
       </c>
@@ -10103,7 +10114,7 @@
       </c>
       <c r="F61" s="223"/>
     </row>
-    <row r="62" spans="2:8" ht="15" customHeight="1">
+    <row r="62" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B62" s="1" t="s">
         <v>210</v>
       </c>
@@ -10119,7 +10130,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="64" spans="2:8" ht="15" customHeight="1">
+    <row r="64" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B64" s="76" t="s">
         <v>162</v>
       </c>
@@ -10130,7 +10141,7 @@
       <c r="G64" s="35"/>
       <c r="H64" s="35"/>
     </row>
-    <row r="65" spans="2:6" ht="15" customHeight="1">
+    <row r="65" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B65" s="16" t="s">
         <v>158</v>
       </c>
@@ -10144,7 +10155,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="66" spans="2:6" ht="15" customHeight="1">
+    <row r="66" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B66" s="102" t="s">
         <v>157</v>
       </c>
@@ -10160,7 +10171,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="67" spans="2:6" ht="15" customHeight="1">
+    <row r="67" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B67" s="102" t="s">
         <v>147</v>
       </c>
@@ -10170,7 +10181,7 @@
       </c>
       <c r="F67" s="223"/>
     </row>
-    <row r="68" spans="2:6" ht="15" customHeight="1">
+    <row r="68" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B68" s="102" t="s">
         <v>151</v>
       </c>
@@ -10180,7 +10191,7 @@
       </c>
       <c r="F68" s="223"/>
     </row>
-    <row r="69" spans="2:6" ht="15" customHeight="1">
+    <row r="69" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B69" s="102" t="s">
         <v>149</v>
       </c>
@@ -10190,7 +10201,7 @@
       </c>
       <c r="F69" s="223"/>
     </row>
-    <row r="70" spans="2:6" ht="15" customHeight="1">
+    <row r="70" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B70" s="77" t="s">
         <v>158</v>
       </c>
@@ -10200,10 +10211,10 @@
       </c>
       <c r="F70" s="223"/>
     </row>
-    <row r="71" spans="2:6" ht="15" customHeight="1">
+    <row r="71" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F71" s="223"/>
     </row>
-    <row r="72" spans="2:6" ht="15" customHeight="1">
+    <row r="72" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B72" s="225" t="s">
         <v>256</v>
       </c>
@@ -10215,7 +10226,7 @@
       </c>
       <c r="F72" s="223"/>
     </row>
-    <row r="73" spans="2:6" ht="15" customHeight="1">
+    <row r="73" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B73" s="102" t="s">
         <v>255</v>
       </c>
@@ -10231,7 +10242,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="74" spans="2:6" ht="15" customHeight="1">
+    <row r="74" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B74" s="227" t="s">
         <v>259</v>
       </c>
@@ -10247,7 +10258,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="75" spans="2:6" ht="15" customHeight="1">
+    <row r="75" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B75" s="77" t="s">
         <v>258</v>
       </c>
@@ -10260,7 +10271,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="76" spans="2:6" ht="15" customHeight="1">
+    <row r="76" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B76" s="229" t="s">
         <v>260</v>
       </c>
@@ -10273,10 +10284,10 @@
         <v>261</v>
       </c>
     </row>
-    <row r="77" spans="2:6" ht="15" customHeight="1">
+    <row r="77" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F77" s="223"/>
     </row>
-    <row r="78" spans="2:6" ht="15" customHeight="1">
+    <row r="78" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B78" s="16" t="s">
         <v>159</v>
       </c>
@@ -10288,7 +10299,7 @@
       </c>
       <c r="F78" s="223"/>
     </row>
-    <row r="79" spans="2:6" ht="15" customHeight="1">
+    <row r="79" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B79" s="102" t="s">
         <v>148</v>
       </c>
@@ -10302,7 +10313,7 @@
       </c>
       <c r="F79" s="223"/>
     </row>
-    <row r="80" spans="2:6" ht="15" customHeight="1">
+    <row r="80" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B80" s="102" t="s">
         <v>152</v>
       </c>
@@ -10316,7 +10327,7 @@
       </c>
       <c r="F80" s="223"/>
     </row>
-    <row r="81" spans="2:8" ht="15" customHeight="1">
+    <row r="81" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B81" s="102" t="s">
         <v>150</v>
       </c>
@@ -10330,7 +10341,7 @@
       </c>
       <c r="F81" s="223"/>
     </row>
-    <row r="82" spans="2:8" ht="15" customHeight="1">
+    <row r="82" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B82" s="77" t="s">
         <v>159</v>
       </c>
@@ -10344,7 +10355,7 @@
       </c>
       <c r="F82" s="223"/>
     </row>
-    <row r="84" spans="2:8" ht="15" customHeight="1">
+    <row r="84" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B84" s="76" t="s">
         <v>241</v>
       </c>
@@ -10355,7 +10366,7 @@
       <c r="G84" s="35"/>
       <c r="H84" s="35"/>
     </row>
-    <row r="85" spans="2:8" ht="15" customHeight="1">
+    <row r="85" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B85" s="16" t="s">
         <v>242</v>
       </c>
@@ -10363,7 +10374,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="86" spans="2:8" ht="15" customHeight="1">
+    <row r="86" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B86" s="212" t="s">
         <v>239</v>
       </c>
@@ -10380,7 +10391,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="87" spans="2:8" ht="15" customHeight="1">
+    <row r="87" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B87" s="212" t="s">
         <v>240</v>
       </c>
@@ -10397,7 +10408,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="88" spans="2:8" ht="15" customHeight="1">
+    <row r="88" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B88" s="213" t="s">
         <v>159</v>
       </c>
@@ -10414,7 +10425,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="89" spans="2:8" ht="15" customHeight="1">
+    <row r="89" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B89" s="77" t="s">
         <v>244</v>
       </c>
@@ -10450,19 +10461,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Q807"/>
-  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="1.33203125" style="2" customWidth="1"/>
     <col min="2" max="2" width="26.33203125" style="2" customWidth="1"/>
     <col min="3" max="3" width="20.6640625" style="2" customWidth="1"/>
     <col min="4" max="4" width="2.6640625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="25.1328125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="25.1640625" style="2" customWidth="1"/>
     <col min="6" max="6" width="2.6640625" style="2" customWidth="1"/>
     <col min="7" max="17" width="20.6640625" style="2" customWidth="1"/>
     <col min="18" max="16384" width="12.33203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="15.75" customHeight="1">
+    <row r="1" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="3"/>
       <c r="B1" s="87" t="str">
         <f>Thesis!E17</f>
@@ -10519,7 +10530,7 @@
         <v>42004</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="15.75" customHeight="1">
+    <row r="2" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="51" t="s">
         <v>95</v>
@@ -10542,7 +10553,7 @@
       <c r="P2" s="35"/>
       <c r="Q2" s="35"/>
     </row>
-    <row r="3" spans="1:17" ht="15.75" customHeight="1">
+    <row r="3" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="10"/>
       <c r="B3" s="16" t="s">
         <v>391</v>
@@ -10562,7 +10573,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:17" ht="15.75" customHeight="1">
+    <row r="4" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="10"/>
       <c r="B4" s="25" t="s">
         <v>0</v>
@@ -10619,7 +10630,7 @@
         <v/>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="15.75" customHeight="1">
+    <row r="5" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="10"/>
       <c r="B5" s="2" t="s">
         <v>43</v>
@@ -10674,7 +10685,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="15.75" customHeight="1">
+    <row r="6" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="10"/>
       <c r="B6" s="30" t="s">
         <v>45</v>
@@ -10729,7 +10740,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="15.75" customHeight="1">
+    <row r="7" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="10"/>
       <c r="B7" s="8" t="s">
         <v>42</v>
@@ -10784,7 +10795,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="15.75" customHeight="1">
+    <row r="8" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="10"/>
       <c r="B8" s="28" t="s">
         <v>127</v>
@@ -10841,7 +10852,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="15.75" customHeight="1">
+    <row r="9" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="10"/>
       <c r="B9" s="26" t="s">
         <v>413</v>
@@ -10898,7 +10909,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="15.75" customHeight="1">
+    <row r="10" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="10"/>
       <c r="B10" s="2" t="s">
         <v>65</v>
@@ -10953,7 +10964,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="15.75" customHeight="1">
+    <row r="11" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="10"/>
       <c r="B11" s="67" t="s">
         <v>137</v>
@@ -11008,7 +11019,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="15.75" customHeight="1">
+    <row r="12" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="10"/>
       <c r="B12" s="2" t="s">
         <v>60</v>
@@ -11063,7 +11074,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="15.75" customHeight="1">
+    <row r="13" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="10"/>
       <c r="B13" s="38" t="s">
         <v>208</v>
@@ -11120,7 +11131,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="15.75" customHeight="1">
+    <row r="14" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="10"/>
       <c r="B14" s="39" t="s">
         <v>129</v>
@@ -11177,7 +11188,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="15.75" customHeight="1">
+    <row r="15" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="10"/>
       <c r="B15" s="2" t="s">
         <v>62</v>
@@ -11232,7 +11243,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="15.75" customHeight="1">
+    <row r="16" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="10"/>
       <c r="B16" s="2" t="s">
         <v>396</v>
@@ -11287,7 +11298,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="15.75" customHeight="1">
+    <row r="17" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="10"/>
       <c r="B17" s="26" t="s">
         <v>49</v>
@@ -11313,7 +11324,7 @@
       <c r="P17" s="272"/>
       <c r="Q17" s="272"/>
     </row>
-    <row r="18" spans="1:17" ht="15.75" customHeight="1">
+    <row r="18" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="10"/>
       <c r="B18" s="26" t="s">
         <v>94</v>
@@ -11338,7 +11349,7 @@
       <c r="P18" s="273"/>
       <c r="Q18" s="273"/>
     </row>
-    <row r="19" spans="1:17" ht="15.75" customHeight="1">
+    <row r="19" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="10"/>
       <c r="B19" s="30" t="s">
         <v>63</v>
@@ -11395,7 +11406,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="15.75" customHeight="1">
+    <row r="20" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="10"/>
       <c r="B20" s="26"/>
       <c r="C20" s="59"/>
@@ -11414,7 +11425,7 @@
       <c r="P20" s="12"/>
       <c r="Q20" s="12"/>
     </row>
-    <row r="21" spans="1:17" ht="15.75" customHeight="1">
+    <row r="21" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="10"/>
       <c r="B21" s="51" t="s">
         <v>174</v>
@@ -11437,7 +11448,7 @@
       <c r="P21" s="35"/>
       <c r="Q21" s="35"/>
     </row>
-    <row r="22" spans="1:17" ht="15.75" customHeight="1">
+    <row r="22" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="10"/>
       <c r="B22" s="61" t="s">
         <v>43</v>
@@ -11458,7 +11469,7 @@
       <c r="P22" s="12"/>
       <c r="Q22" s="12"/>
     </row>
-    <row r="23" spans="1:17" ht="15.75" customHeight="1">
+    <row r="23" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="10"/>
       <c r="B23" s="26" t="s">
         <v>40</v>
@@ -11515,7 +11526,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="15.75" customHeight="1">
+    <row r="24" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="10"/>
       <c r="B24" s="65" t="s">
         <v>59</v>
@@ -11572,7 +11583,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="15.75" customHeight="1">
+    <row r="25" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="10"/>
       <c r="B25" s="26" t="s">
         <v>46</v>
@@ -11629,7 +11640,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="15.75" customHeight="1">
+    <row r="26" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="10"/>
       <c r="B26" s="67" t="s">
         <v>43</v>
@@ -11686,18 +11697,18 @@
         <v/>
       </c>
     </row>
-    <row r="27" spans="1:17" ht="15.75" customHeight="1">
+    <row r="27" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="10"/>
       <c r="E27" s="237"/>
     </row>
-    <row r="28" spans="1:17" ht="15.75" customHeight="1">
+    <row r="28" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="10"/>
       <c r="B28" s="61" t="s">
         <v>175</v>
       </c>
       <c r="E28" s="237"/>
     </row>
-    <row r="29" spans="1:17" ht="15.75" customHeight="1">
+    <row r="29" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="10"/>
       <c r="B29" s="25" t="s">
         <v>40</v>
@@ -11754,7 +11765,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:17" ht="15.75" customHeight="1">
+    <row r="30" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="10"/>
       <c r="B30" s="65" t="str">
         <f>B24</f>
@@ -11812,7 +11823,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:17" ht="15.75" customHeight="1">
+    <row r="31" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="10"/>
       <c r="B31" s="26" t="str">
         <f>B25</f>
@@ -11870,7 +11881,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" spans="1:17" ht="15.75" customHeight="1">
+    <row r="32" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="10"/>
       <c r="B32" s="67" t="s">
         <v>43</v>
@@ -11925,18 +11936,18 @@
         <v/>
       </c>
     </row>
-    <row r="33" spans="1:17" ht="15.75" customHeight="1">
+    <row r="33" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="10"/>
       <c r="E33" s="237"/>
     </row>
-    <row r="34" spans="1:17" ht="15.75" customHeight="1">
+    <row r="34" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="10"/>
       <c r="B34" s="61" t="s">
         <v>42</v>
       </c>
       <c r="E34" s="237"/>
     </row>
-    <row r="35" spans="1:17" ht="15.75" customHeight="1">
+    <row r="35" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="10"/>
       <c r="B35" s="298" t="s">
         <v>394</v>
@@ -11993,18 +12004,18 @@
         <v/>
       </c>
     </row>
-    <row r="36" spans="1:17" ht="15.75" customHeight="1">
+    <row r="36" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="10"/>
       <c r="E36" s="237"/>
     </row>
-    <row r="37" spans="1:17" ht="15.75" customHeight="1">
+    <row r="37" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="10"/>
       <c r="B37" s="61" t="s">
         <v>176</v>
       </c>
       <c r="E37" s="237"/>
     </row>
-    <row r="38" spans="1:17" ht="15.75" customHeight="1">
+    <row r="38" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="10"/>
       <c r="B38" s="298" t="s">
         <v>394</v>
@@ -12059,18 +12070,18 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="1:17" ht="15.75" customHeight="1">
+    <row r="39" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="10"/>
       <c r="E39" s="237"/>
     </row>
-    <row r="40" spans="1:17" ht="15.75" customHeight="1">
+    <row r="40" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="10"/>
       <c r="B40" s="61" t="s">
         <v>177</v>
       </c>
       <c r="E40" s="237"/>
     </row>
-    <row r="41" spans="1:17" ht="15.75" customHeight="1">
+    <row r="41" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="10"/>
       <c r="B41" s="26" t="s">
         <v>142</v>
@@ -12128,10 +12139,10 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="1:17" ht="15.75" customHeight="1">
+    <row r="42" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="10"/>
     </row>
-    <row r="43" spans="1:17" ht="15.75" customHeight="1">
+    <row r="43" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="10"/>
       <c r="B43" s="51" t="s">
         <v>178</v>
@@ -12154,14 +12165,14 @@
       <c r="P43" s="35"/>
       <c r="Q43" s="35"/>
     </row>
-    <row r="44" spans="1:17" ht="15.75" customHeight="1">
+    <row r="44" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="10"/>
       <c r="B44" s="61" t="s">
         <v>57</v>
       </c>
       <c r="E44" s="237"/>
     </row>
-    <row r="45" spans="1:17" ht="15.75" customHeight="1">
+    <row r="45" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A45" s="10"/>
       <c r="B45" s="2" t="s">
         <v>37</v>
@@ -12216,7 +12227,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" spans="1:17" ht="15.75" customHeight="1">
+    <row r="46" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="10"/>
       <c r="B46" s="2" t="s">
         <v>272</v>
@@ -12271,7 +12282,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" spans="1:17" ht="15.75" customHeight="1">
+    <row r="47" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A47" s="10"/>
       <c r="B47" s="245" t="s">
         <v>269</v>
@@ -12328,7 +12339,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="1:17" ht="15.75" customHeight="1">
+    <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A48" s="10"/>
       <c r="B48" s="67" t="s">
         <v>65</v>
@@ -12383,11 +12394,11 @@
         <v/>
       </c>
     </row>
-    <row r="49" spans="1:17" ht="15.75" customHeight="1">
+    <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A49" s="10"/>
       <c r="E49" s="237"/>
     </row>
-    <row r="50" spans="1:17" ht="15.75" customHeight="1">
+    <row r="50" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" s="10"/>
       <c r="B50" s="69" t="s">
         <v>130</v>
@@ -12397,7 +12408,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="51" spans="1:17" ht="15.75" customHeight="1">
+    <row r="51" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A51" s="10"/>
       <c r="B51" s="8" t="s">
         <v>85</v>
@@ -12421,7 +12432,7 @@
       <c r="P51" s="151"/>
       <c r="Q51" s="151"/>
     </row>
-    <row r="52" spans="1:17" ht="15.75" customHeight="1">
+    <row r="52" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A52" s="10"/>
       <c r="B52" s="8" t="s">
         <v>84</v>
@@ -12445,7 +12456,7 @@
       <c r="P52" s="151"/>
       <c r="Q52" s="151"/>
     </row>
-    <row r="53" spans="1:17" ht="15.75" customHeight="1">
+    <row r="53" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A53" s="10"/>
       <c r="B53" s="25" t="s">
         <v>87</v>
@@ -12500,11 +12511,11 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="1:17" ht="15.75" customHeight="1">
+    <row r="54" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A54" s="10"/>
       <c r="E54" s="237"/>
     </row>
-    <row r="55" spans="1:17" ht="15.75" customHeight="1">
+    <row r="55" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A55" s="10"/>
       <c r="B55" s="61" t="s">
         <v>139</v>
@@ -12514,7 +12525,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="56" spans="1:17" ht="15.75" customHeight="1">
+    <row r="56" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A56" s="10"/>
       <c r="B56" s="38" t="s">
         <v>138</v>
@@ -12569,7 +12580,7 @@
         <v/>
       </c>
     </row>
-    <row r="57" spans="1:17" ht="15.75" customHeight="1">
+    <row r="57" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A57" s="10"/>
       <c r="B57" s="38" t="s">
         <v>134</v>
@@ -12624,7 +12635,7 @@
         <v/>
       </c>
     </row>
-    <row r="58" spans="1:17" ht="15.75" customHeight="1">
+    <row r="58" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A58" s="10"/>
       <c r="B58" s="38" t="s">
         <v>133</v>
@@ -12679,7 +12690,7 @@
         <v/>
       </c>
     </row>
-    <row r="59" spans="1:17" ht="15.75" customHeight="1">
+    <row r="59" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A59" s="10"/>
       <c r="B59" s="30" t="s">
         <v>163</v>
@@ -12734,7 +12745,7 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="1:17" ht="15.75" customHeight="1">
+    <row r="60" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" s="10"/>
       <c r="B60" s="38" t="s">
         <v>135</v>
@@ -12790,7 +12801,7 @@
         <v/>
       </c>
     </row>
-    <row r="61" spans="1:17" ht="15.75" customHeight="1">
+    <row r="61" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A61" s="10"/>
       <c r="B61" s="30" t="s">
         <v>164</v>
@@ -12845,11 +12856,11 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="1:17" ht="15.75" customHeight="1">
+    <row r="62" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A62" s="10"/>
       <c r="E62" s="237"/>
     </row>
-    <row r="63" spans="1:17" ht="15.75" customHeight="1">
+    <row r="63" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A63" s="10"/>
       <c r="B63" s="93" t="s">
         <v>140</v>
@@ -12859,7 +12870,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="64" spans="1:17" ht="15.75" customHeight="1">
+    <row r="64" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A64" s="10"/>
       <c r="B64" s="38" t="s">
         <v>138</v>
@@ -12884,7 +12895,7 @@
       <c r="P64" s="157"/>
       <c r="Q64" s="157"/>
     </row>
-    <row r="65" spans="1:17" ht="15.75" customHeight="1">
+    <row r="65" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A65" s="10"/>
       <c r="B65" s="102" t="s">
         <v>132</v>
@@ -12909,7 +12920,7 @@
       <c r="P65" s="157"/>
       <c r="Q65" s="157"/>
     </row>
-    <row r="66" spans="1:17" ht="15.75" customHeight="1">
+    <row r="66" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A66" s="10"/>
       <c r="B66" s="102" t="s">
         <v>133</v>
@@ -12934,7 +12945,7 @@
       <c r="P66" s="157"/>
       <c r="Q66" s="157"/>
     </row>
-    <row r="67" spans="1:17" ht="15.75" customHeight="1">
+    <row r="67" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A67" s="10"/>
       <c r="B67" s="30" t="s">
         <v>163</v>
@@ -12961,10 +12972,10 @@
       <c r="P67" s="157"/>
       <c r="Q67" s="157"/>
     </row>
-    <row r="68" spans="1:17" ht="15.75" customHeight="1">
+    <row r="68" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A68" s="10"/>
     </row>
-    <row r="69" spans="1:17" ht="15.75" customHeight="1">
+    <row r="69" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="10"/>
       <c r="B69" s="51" t="s">
         <v>181</v>
@@ -12987,7 +12998,7 @@
       <c r="P69" s="35"/>
       <c r="Q69" s="35"/>
     </row>
-    <row r="70" spans="1:17" ht="15.75" customHeight="1">
+    <row r="70" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A70" s="10"/>
       <c r="B70" s="69" t="s">
         <v>185</v>
@@ -13008,7 +13019,7 @@
       <c r="P70" s="12"/>
       <c r="Q70" s="12"/>
     </row>
-    <row r="71" spans="1:17" ht="15.75" customHeight="1">
+    <row r="71" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A71" s="10"/>
       <c r="B71" s="2" t="s">
         <v>43</v>
@@ -13065,7 +13076,7 @@
         <v/>
       </c>
     </row>
-    <row r="72" spans="1:17" ht="15.75" customHeight="1">
+    <row r="72" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A72" s="10"/>
       <c r="B72" s="30" t="s">
         <v>45</v>
@@ -13122,7 +13133,7 @@
         <v/>
       </c>
     </row>
-    <row r="73" spans="1:17" ht="15.75" customHeight="1">
+    <row r="73" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A73" s="10"/>
       <c r="B73" s="8" t="s">
         <v>42</v>
@@ -13179,7 +13190,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="1:17" ht="15.75" customHeight="1">
+    <row r="74" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A74" s="10"/>
       <c r="B74" s="28" t="s">
         <v>127</v>
@@ -13236,7 +13247,7 @@
         <v/>
       </c>
     </row>
-    <row r="75" spans="1:17" ht="15.75" customHeight="1">
+    <row r="75" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A75" s="10"/>
       <c r="B75" s="26" t="s">
         <v>128</v>
@@ -13293,7 +13304,7 @@
         <v/>
       </c>
     </row>
-    <row r="76" spans="1:17" ht="15.75" customHeight="1">
+    <row r="76" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A76" s="10"/>
       <c r="B76" s="2" t="s">
         <v>65</v>
@@ -13350,7 +13361,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="1:17" ht="15.75" customHeight="1">
+    <row r="77" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A77" s="10"/>
       <c r="B77" s="67" t="s">
         <v>137</v>
@@ -13407,7 +13418,7 @@
         <v/>
       </c>
     </row>
-    <row r="78" spans="1:17" ht="15.75" customHeight="1">
+    <row r="78" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A78" s="10"/>
       <c r="B78" s="2" t="s">
         <v>60</v>
@@ -13464,7 +13475,7 @@
         <v/>
       </c>
     </row>
-    <row r="79" spans="1:17" ht="15.75" customHeight="1">
+    <row r="79" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A79" s="10"/>
       <c r="B79" s="38" t="str">
         <f>B13</f>
@@ -13522,7 +13533,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="1:17" ht="15.75" customHeight="1">
+    <row r="80" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A80" s="10"/>
       <c r="B80" s="39" t="s">
         <v>129</v>
@@ -13579,7 +13590,7 @@
         <v/>
       </c>
     </row>
-    <row r="81" spans="1:17" ht="15.75" customHeight="1">
+    <row r="81" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A81" s="10"/>
       <c r="B81" s="2" t="s">
         <v>62</v>
@@ -13636,7 +13647,7 @@
         <v/>
       </c>
     </row>
-    <row r="82" spans="1:17" ht="15.75" customHeight="1">
+    <row r="82" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A82" s="10"/>
       <c r="B82" s="2" t="s">
         <v>77</v>
@@ -13695,7 +13706,7 @@
         <v/>
       </c>
     </row>
-    <row r="83" spans="1:17" ht="15.75" customHeight="1">
+    <row r="83" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A83" s="10"/>
       <c r="B83" s="26" t="s">
         <v>49</v>
@@ -13721,7 +13732,7 @@
       <c r="P83" s="203"/>
       <c r="Q83" s="203"/>
     </row>
-    <row r="84" spans="1:17" ht="15.75" customHeight="1">
+    <row r="84" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A84" s="10"/>
       <c r="B84" s="8" t="s">
         <v>94</v>
@@ -13745,7 +13756,7 @@
       <c r="P84" s="151"/>
       <c r="Q84" s="151"/>
     </row>
-    <row r="85" spans="1:17" ht="15.75" customHeight="1">
+    <row r="85" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A85" s="10"/>
       <c r="B85" s="30" t="s">
         <v>117</v>
@@ -13802,18 +13813,18 @@
         <v/>
       </c>
     </row>
-    <row r="86" spans="1:17" ht="15.75" customHeight="1">
+    <row r="86" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A86" s="10"/>
       <c r="E86" s="237"/>
     </row>
-    <row r="87" spans="1:17" ht="15.75" customHeight="1">
+    <row r="87" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A87" s="10"/>
       <c r="B87" s="61" t="s">
         <v>183</v>
       </c>
       <c r="E87" s="237"/>
     </row>
-    <row r="88" spans="1:17" ht="15.75" customHeight="1">
+    <row r="88" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A88" s="10"/>
       <c r="B88" s="2" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
@@ -13869,7 +13880,7 @@
         <v/>
       </c>
     </row>
-    <row r="89" spans="1:17" ht="15.75" customHeight="1">
+    <row r="89" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A89" s="10"/>
       <c r="B89" s="2" t="str">
         <f>"Dividend ("&amp;Market_currency&amp;")"</f>
@@ -13925,7 +13936,7 @@
         <v/>
       </c>
     </row>
-    <row r="90" spans="1:17" ht="15.75" customHeight="1">
+    <row r="90" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A90" s="10"/>
       <c r="B90" s="2" t="s">
         <v>182</v>
@@ -13980,7 +13991,7 @@
         <v/>
       </c>
     </row>
-    <row r="91" spans="1:17" ht="15.75" customHeight="1">
+    <row r="91" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A91" s="10"/>
       <c r="B91" s="2" t="s">
         <v>329</v>
@@ -14001,7 +14012,7 @@
       <c r="P91" s="293"/>
       <c r="Q91" s="293"/>
     </row>
-    <row r="92" spans="1:17" ht="15.75" customHeight="1">
+    <row r="92" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A92" s="10"/>
       <c r="B92" s="2" t="s">
         <v>328</v>
@@ -14056,11 +14067,11 @@
         <v/>
       </c>
     </row>
-    <row r="93" spans="1:17" ht="15.75" customHeight="1">
+    <row r="93" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A93" s="10"/>
       <c r="E93" s="237"/>
     </row>
-    <row r="94" spans="1:17" ht="15.75" customHeight="1">
+    <row r="94" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A94" s="10"/>
       <c r="B94" s="143" t="s">
         <v>81</v>
@@ -14081,7 +14092,7 @@
       <c r="P94" s="12"/>
       <c r="Q94" s="12"/>
     </row>
-    <row r="95" spans="1:17" ht="15.75" customHeight="1">
+    <row r="95" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A95" s="10"/>
       <c r="B95" s="26" t="s">
         <v>121</v>
@@ -14138,7 +14149,7 @@
         <v/>
       </c>
     </row>
-    <row r="96" spans="1:17" ht="15.75" customHeight="1">
+    <row r="96" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A96" s="10"/>
       <c r="B96" s="67" t="s">
         <v>137</v>
@@ -14195,10 +14206,10 @@
         <v/>
       </c>
     </row>
-    <row r="97" spans="1:17" ht="15.75" customHeight="1">
+    <row r="97" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A97" s="10"/>
     </row>
-    <row r="98" spans="1:17" ht="15.75" customHeight="1">
+    <row r="98" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="3"/>
       <c r="B98" s="51" t="s">
         <v>184</v>
@@ -14221,7 +14232,7 @@
       <c r="P98" s="35"/>
       <c r="Q98" s="35"/>
     </row>
-    <row r="99" spans="1:17" ht="15.75" customHeight="1">
+    <row r="99" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A99" s="10"/>
       <c r="B99" s="61" t="s">
         <v>26</v>
@@ -14231,7 +14242,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="100" spans="1:17" ht="15.75" customHeight="1">
+    <row r="100" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A100" s="10"/>
       <c r="B100" s="25" t="s">
         <v>1</v>
@@ -14288,7 +14299,7 @@
         <v/>
       </c>
     </row>
-    <row r="101" spans="1:17" ht="15.75" customHeight="1">
+    <row r="101" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A101" s="10"/>
       <c r="B101" s="90" t="s">
         <v>179</v>
@@ -14345,7 +14356,7 @@
         <v/>
       </c>
     </row>
-    <row r="102" spans="1:17" ht="15.75" customHeight="1">
+    <row r="102" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A102" s="10"/>
       <c r="B102" s="90" t="s">
         <v>180</v>
@@ -14402,7 +14413,7 @@
         <v/>
       </c>
     </row>
-    <row r="103" spans="1:17" ht="15.75" customHeight="1">
+    <row r="103" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A103" s="10"/>
       <c r="B103" s="25" t="s">
         <v>38</v>
@@ -14459,7 +14470,7 @@
         <v/>
       </c>
     </row>
-    <row r="104" spans="1:17" ht="15.75" customHeight="1">
+    <row r="104" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A104" s="10"/>
       <c r="B104" s="25" t="s">
         <v>28</v>
@@ -14516,11 +14527,11 @@
         <v/>
       </c>
     </row>
-    <row r="105" spans="1:17" ht="15.75" customHeight="1">
+    <row r="105" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A105" s="10"/>
       <c r="E105" s="237"/>
     </row>
-    <row r="106" spans="1:17" ht="15.75" customHeight="1">
+    <row r="106" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A106" s="10"/>
       <c r="B106" s="88" t="s">
         <v>189</v>
@@ -14543,7 +14554,7 @@
       <c r="P106" s="12"/>
       <c r="Q106" s="12"/>
     </row>
-    <row r="107" spans="1:17" ht="15.75" customHeight="1">
+    <row r="107" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A107" s="10"/>
       <c r="B107" s="25" t="s">
         <v>186</v>
@@ -14600,7 +14611,7 @@
         <v/>
       </c>
     </row>
-    <row r="108" spans="1:17" ht="15.75" customHeight="1">
+    <row r="108" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A108" s="10"/>
       <c r="B108" s="25" t="s">
         <v>187</v>
@@ -14657,7 +14668,7 @@
         <v/>
       </c>
     </row>
-    <row r="109" spans="1:17" ht="15.75" customHeight="1">
+    <row r="109" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A109" s="10"/>
       <c r="B109" s="25" t="s">
         <v>66</v>
@@ -14684,18 +14695,18 @@
       <c r="P109" s="186"/>
       <c r="Q109" s="186"/>
     </row>
-    <row r="110" spans="1:17" ht="15.75" customHeight="1">
+    <row r="110" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A110" s="10"/>
       <c r="E110" s="237"/>
     </row>
-    <row r="111" spans="1:17" ht="15.75" customHeight="1">
+    <row r="111" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A111" s="10"/>
       <c r="B111" s="61" t="s">
         <v>48</v>
       </c>
       <c r="E111" s="237"/>
     </row>
-    <row r="112" spans="1:17" ht="15.75" customHeight="1">
+    <row r="112" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A112" s="10"/>
       <c r="B112" s="2" t="s">
         <v>303</v>
@@ -14749,7 +14760,7 @@
         <v/>
       </c>
     </row>
-    <row r="113" spans="1:17" ht="15.75" customHeight="1">
+    <row r="113" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
         <v>304</v>
@@ -14804,11 +14815,11 @@
         <v/>
       </c>
     </row>
-    <row r="114" spans="1:17" ht="15.75" customHeight="1">
+    <row r="114" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A114" s="10"/>
       <c r="E114" s="237"/>
     </row>
-    <row r="115" spans="1:17" ht="15.75" customHeight="1">
+    <row r="115" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A115" s="10"/>
       <c r="B115" s="88" t="s">
         <v>36</v>
@@ -14867,7 +14878,7 @@
         <v/>
       </c>
     </row>
-    <row r="116" spans="1:17" ht="15.75" customHeight="1">
+    <row r="116" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A116" s="10"/>
       <c r="B116" s="7" t="s">
         <v>190</v>
@@ -14925,7 +14936,7 @@
         <v/>
       </c>
     </row>
-    <row r="117" spans="1:17" ht="15.75" customHeight="1">
+    <row r="117" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B117" s="7" t="s">
         <v>80</v>
       </c>
@@ -14982,7 +14993,7 @@
         <v/>
       </c>
     </row>
-    <row r="118" spans="1:17" ht="15.75" customHeight="1">
+    <row r="118" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B118" s="7" t="s">
         <v>88</v>
       </c>
@@ -15041,7 +15052,7 @@
         <v/>
       </c>
     </row>
-    <row r="119" spans="1:17" ht="15.75" customHeight="1">
+    <row r="119" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A119" s="10"/>
       <c r="B119" s="67" t="s">
         <v>191</v>
@@ -15100,7 +15111,7 @@
         <v/>
       </c>
     </row>
-    <row r="120" spans="1:17" ht="15.75" customHeight="1">
+    <row r="120" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A120" s="10"/>
       <c r="B120" s="26"/>
       <c r="C120" s="59"/>
@@ -15119,7 +15130,7 @@
       <c r="P120" s="12"/>
       <c r="Q120" s="12"/>
     </row>
-    <row r="121" spans="1:17" ht="15.75" customHeight="1">
+    <row r="121" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="10"/>
       <c r="B121" s="51" t="s">
         <v>192</v>
@@ -15142,7 +15153,7 @@
       <c r="P121" s="35"/>
       <c r="Q121" s="35"/>
     </row>
-    <row r="122" spans="1:17" ht="15.75" customHeight="1">
+    <row r="122" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A122" s="10"/>
       <c r="B122" s="160" t="s">
         <v>141</v>
@@ -15163,7 +15174,7 @@
       <c r="P122" s="12"/>
       <c r="Q122" s="12"/>
     </row>
-    <row r="123" spans="1:17" ht="15.75" customHeight="1">
+    <row r="123" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A123" s="10"/>
       <c r="B123" s="26" t="str">
         <f>"FCFE per share ("&amp;Market_currency&amp;")"</f>
@@ -15221,7 +15232,7 @@
         <v/>
       </c>
     </row>
-    <row r="124" spans="1:17" ht="15.75" customHeight="1">
+    <row r="124" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A124" s="10"/>
       <c r="B124" s="26" t="s">
         <v>226</v>
@@ -15278,7 +15289,7 @@
         <v/>
       </c>
     </row>
-    <row r="125" spans="1:17" ht="15.75" customHeight="1">
+    <row r="125" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B125" s="2" t="s">
         <v>306</v>
       </c>
@@ -15328,688 +15339,688 @@
         <v/>
       </c>
     </row>
-    <row r="126" spans="1:17" ht="15.75" customHeight="1"/>
-    <row r="127" spans="1:17" ht="15.75" customHeight="1"/>
-    <row r="128" spans="1:17" ht="15.75" customHeight="1"/>
-    <row r="129" ht="15.75" customHeight="1"/>
-    <row r="130" ht="15.75" customHeight="1"/>
-    <row r="131" ht="15.75" customHeight="1"/>
-    <row r="132" ht="15.75" customHeight="1"/>
-    <row r="133" ht="15.75" customHeight="1"/>
-    <row r="134" ht="15.75" customHeight="1"/>
-    <row r="135" ht="15.75" customHeight="1"/>
-    <row r="136" ht="15.75" customHeight="1"/>
-    <row r="137" ht="15.75" customHeight="1"/>
-    <row r="138" ht="15.75" customHeight="1"/>
-    <row r="139" ht="15.75" customHeight="1"/>
-    <row r="140" ht="15.75" customHeight="1"/>
-    <row r="141" ht="15.75" customHeight="1"/>
-    <row r="142" ht="15.75" customHeight="1"/>
-    <row r="143" ht="15.75" customHeight="1"/>
-    <row r="144" ht="15.75" customHeight="1"/>
-    <row r="145" ht="15.75" customHeight="1"/>
-    <row r="146" ht="15.75" customHeight="1"/>
-    <row r="147" ht="15.75" customHeight="1"/>
-    <row r="148" ht="15.75" customHeight="1"/>
-    <row r="149" ht="15.75" customHeight="1"/>
-    <row r="150" ht="15.75" customHeight="1"/>
-    <row r="151" ht="15.75" customHeight="1"/>
-    <row r="152" ht="15.75" customHeight="1"/>
-    <row r="153" ht="15.75" customHeight="1"/>
-    <row r="154" ht="15.75" customHeight="1"/>
-    <row r="155" ht="15.75" customHeight="1"/>
-    <row r="156" ht="15.75" customHeight="1"/>
-    <row r="157" ht="15.75" customHeight="1"/>
-    <row r="158" ht="15.75" customHeight="1"/>
-    <row r="159" ht="15.75" customHeight="1"/>
-    <row r="160" ht="15.75" customHeight="1"/>
-    <row r="161" ht="15.75" customHeight="1"/>
-    <row r="162" ht="15.75" customHeight="1"/>
-    <row r="163" ht="15.75" customHeight="1"/>
-    <row r="164" ht="15.75" customHeight="1"/>
-    <row r="165" ht="15.75" customHeight="1"/>
-    <row r="166" ht="15.75" customHeight="1"/>
-    <row r="167" ht="15.75" customHeight="1"/>
-    <row r="168" ht="15.75" customHeight="1"/>
-    <row r="169" ht="15.75" customHeight="1"/>
-    <row r="170" ht="15.75" customHeight="1"/>
-    <row r="171" ht="15.75" customHeight="1"/>
-    <row r="172" ht="15.75" customHeight="1"/>
-    <row r="173" ht="15.75" customHeight="1"/>
-    <row r="174" ht="15.75" customHeight="1"/>
-    <row r="175" ht="15.75" customHeight="1"/>
-    <row r="176" ht="15.75" customHeight="1"/>
-    <row r="177" ht="15.75" customHeight="1"/>
-    <row r="178" ht="15.75" customHeight="1"/>
-    <row r="179" ht="15.75" customHeight="1"/>
-    <row r="180" ht="15.75" customHeight="1"/>
-    <row r="181" ht="15.75" customHeight="1"/>
-    <row r="182" ht="15.75" customHeight="1"/>
-    <row r="183" ht="15.75" customHeight="1"/>
-    <row r="184" ht="15.75" customHeight="1"/>
-    <row r="185" ht="15.75" customHeight="1"/>
-    <row r="186" ht="15.75" customHeight="1"/>
-    <row r="187" ht="15.75" customHeight="1"/>
-    <row r="188" ht="15.75" customHeight="1"/>
-    <row r="189" ht="15.75" customHeight="1"/>
-    <row r="190" ht="15.75" customHeight="1"/>
-    <row r="191" ht="15.75" customHeight="1"/>
-    <row r="192" ht="15.75" customHeight="1"/>
-    <row r="193" ht="15.75" customHeight="1"/>
-    <row r="194" ht="15.75" customHeight="1"/>
-    <row r="195" ht="15.75" customHeight="1"/>
-    <row r="196" ht="15.75" customHeight="1"/>
-    <row r="197" ht="15.75" customHeight="1"/>
-    <row r="198" ht="15.75" customHeight="1"/>
-    <row r="199" ht="15.75" customHeight="1"/>
-    <row r="200" ht="15.75" customHeight="1"/>
-    <row r="201" ht="15.75" customHeight="1"/>
-    <row r="202" ht="15.75" customHeight="1"/>
-    <row r="203" ht="15.75" customHeight="1"/>
-    <row r="204" ht="15.75" customHeight="1"/>
-    <row r="205" ht="15.75" customHeight="1"/>
-    <row r="206" ht="15.75" customHeight="1"/>
-    <row r="207" ht="15.75" customHeight="1"/>
-    <row r="208" ht="15.75" customHeight="1"/>
-    <row r="209" ht="15.75" customHeight="1"/>
-    <row r="210" ht="15.75" customHeight="1"/>
-    <row r="211" ht="15.75" customHeight="1"/>
-    <row r="212" ht="15.75" customHeight="1"/>
-    <row r="213" ht="15.75" customHeight="1"/>
-    <row r="214" ht="15.75" customHeight="1"/>
-    <row r="215" ht="15.75" customHeight="1"/>
-    <row r="216" ht="15.75" customHeight="1"/>
-    <row r="217" ht="15.75" customHeight="1"/>
-    <row r="218" ht="15.75" customHeight="1"/>
-    <row r="219" ht="15.75" customHeight="1"/>
-    <row r="220" ht="15.75" customHeight="1"/>
-    <row r="221" ht="15.75" customHeight="1"/>
-    <row r="222" ht="15.75" customHeight="1"/>
-    <row r="223" ht="15.75" customHeight="1"/>
-    <row r="224" ht="15.75" customHeight="1"/>
-    <row r="225" ht="15.75" customHeight="1"/>
-    <row r="226" ht="15.75" customHeight="1"/>
-    <row r="227" ht="15.75" customHeight="1"/>
-    <row r="228" ht="15.75" customHeight="1"/>
-    <row r="229" ht="15.75" customHeight="1"/>
-    <row r="230" ht="15.75" customHeight="1"/>
-    <row r="231" ht="15.75" customHeight="1"/>
-    <row r="232" ht="15.75" customHeight="1"/>
-    <row r="233" ht="15.75" customHeight="1"/>
-    <row r="234" ht="15.75" customHeight="1"/>
-    <row r="235" ht="15.75" customHeight="1"/>
-    <row r="236" ht="15.75" customHeight="1"/>
-    <row r="237" ht="15.75" customHeight="1"/>
-    <row r="238" ht="15.75" customHeight="1"/>
-    <row r="239" ht="15.75" customHeight="1"/>
-    <row r="240" ht="15.75" customHeight="1"/>
-    <row r="241" ht="15.75" customHeight="1"/>
-    <row r="242" ht="15.75" customHeight="1"/>
-    <row r="243" ht="15.75" customHeight="1"/>
-    <row r="244" ht="15.75" customHeight="1"/>
-    <row r="245" ht="15.75" customHeight="1"/>
-    <row r="246" ht="15.75" customHeight="1"/>
-    <row r="247" ht="15.75" customHeight="1"/>
-    <row r="248" ht="15.75" customHeight="1"/>
-    <row r="249" ht="15.75" customHeight="1"/>
-    <row r="250" ht="15.75" customHeight="1"/>
-    <row r="251" ht="15.75" customHeight="1"/>
-    <row r="252" ht="15.75" customHeight="1"/>
-    <row r="253" ht="15.75" customHeight="1"/>
-    <row r="254" ht="15.75" customHeight="1"/>
-    <row r="255" ht="15.75" customHeight="1"/>
-    <row r="256" ht="15.75" customHeight="1"/>
-    <row r="257" ht="15.75" customHeight="1"/>
-    <row r="258" ht="15.75" customHeight="1"/>
-    <row r="259" ht="15.75" customHeight="1"/>
-    <row r="260" ht="15.75" customHeight="1"/>
-    <row r="261" ht="15.75" customHeight="1"/>
-    <row r="262" ht="15.75" customHeight="1"/>
-    <row r="263" ht="15.75" customHeight="1"/>
-    <row r="264" ht="15.75" customHeight="1"/>
-    <row r="265" ht="15.75" customHeight="1"/>
-    <row r="266" ht="15.75" customHeight="1"/>
-    <row r="267" ht="15.75" customHeight="1"/>
-    <row r="268" ht="15.75" customHeight="1"/>
-    <row r="269" ht="15.75" customHeight="1"/>
-    <row r="270" ht="15.75" customHeight="1"/>
-    <row r="271" ht="15.75" customHeight="1"/>
-    <row r="272" ht="15.75" customHeight="1"/>
-    <row r="273" ht="15.75" customHeight="1"/>
-    <row r="274" ht="15.75" customHeight="1"/>
-    <row r="275" ht="15.75" customHeight="1"/>
-    <row r="276" ht="15.75" customHeight="1"/>
-    <row r="277" ht="15.75" customHeight="1"/>
-    <row r="278" ht="15.75" customHeight="1"/>
-    <row r="279" ht="15.75" customHeight="1"/>
-    <row r="280" ht="15.75" customHeight="1"/>
-    <row r="281" ht="15.75" customHeight="1"/>
-    <row r="282" ht="15.75" customHeight="1"/>
-    <row r="283" ht="15.75" customHeight="1"/>
-    <row r="284" ht="15.75" customHeight="1"/>
-    <row r="285" ht="15.75" customHeight="1"/>
-    <row r="286" ht="15.75" customHeight="1"/>
-    <row r="287" ht="15.75" customHeight="1"/>
-    <row r="288" ht="15.75" customHeight="1"/>
-    <row r="289" ht="15.75" customHeight="1"/>
-    <row r="290" ht="15.75" customHeight="1"/>
-    <row r="291" ht="15.75" customHeight="1"/>
-    <row r="292" ht="15.75" customHeight="1"/>
-    <row r="293" ht="15.75" customHeight="1"/>
-    <row r="294" ht="15.75" customHeight="1"/>
-    <row r="295" ht="15.75" customHeight="1"/>
-    <row r="296" ht="15.75" customHeight="1"/>
-    <row r="297" ht="15.75" customHeight="1"/>
-    <row r="298" ht="15.75" customHeight="1"/>
-    <row r="299" ht="15.75" customHeight="1"/>
-    <row r="300" ht="15.75" customHeight="1"/>
-    <row r="301" ht="15.75" customHeight="1"/>
-    <row r="302" ht="15.75" customHeight="1"/>
-    <row r="303" ht="15.75" customHeight="1"/>
-    <row r="304" ht="15.75" customHeight="1"/>
-    <row r="305" ht="15.75" customHeight="1"/>
-    <row r="306" ht="15.75" customHeight="1"/>
-    <row r="307" ht="15.75" customHeight="1"/>
-    <row r="308" ht="15.75" customHeight="1"/>
-    <row r="309" ht="15.75" customHeight="1"/>
-    <row r="310" ht="15.75" customHeight="1"/>
-    <row r="311" ht="15.75" customHeight="1"/>
-    <row r="312" ht="15.75" customHeight="1"/>
-    <row r="313" ht="15.75" customHeight="1"/>
-    <row r="314" ht="15.75" customHeight="1"/>
-    <row r="315" ht="15.75" customHeight="1"/>
-    <row r="316" ht="15.75" customHeight="1"/>
-    <row r="317" ht="15.75" customHeight="1"/>
-    <row r="318" ht="15.75" customHeight="1"/>
-    <row r="319" ht="15.75" customHeight="1"/>
-    <row r="320" ht="15.75" customHeight="1"/>
-    <row r="321" ht="15.75" customHeight="1"/>
-    <row r="322" ht="15.75" customHeight="1"/>
-    <row r="323" ht="15.75" customHeight="1"/>
-    <row r="324" ht="15.75" customHeight="1"/>
-    <row r="325" ht="15.75" customHeight="1"/>
-    <row r="326" ht="15.75" customHeight="1"/>
-    <row r="327" ht="15.75" customHeight="1"/>
-    <row r="328" ht="15.75" customHeight="1"/>
-    <row r="329" ht="15.75" customHeight="1"/>
-    <row r="330" ht="15.75" customHeight="1"/>
-    <row r="331" ht="15.75" customHeight="1"/>
-    <row r="332" ht="15.75" customHeight="1"/>
-    <row r="333" ht="15.75" customHeight="1"/>
-    <row r="334" ht="15.75" customHeight="1"/>
-    <row r="335" ht="15.75" customHeight="1"/>
-    <row r="336" ht="15.75" customHeight="1"/>
-    <row r="337" ht="15.75" customHeight="1"/>
-    <row r="338" ht="15.75" customHeight="1"/>
-    <row r="339" ht="15.75" customHeight="1"/>
-    <row r="340" ht="15.75" customHeight="1"/>
-    <row r="341" ht="15.75" customHeight="1"/>
-    <row r="342" ht="15.75" customHeight="1"/>
-    <row r="343" ht="15.75" customHeight="1"/>
-    <row r="344" ht="15.75" customHeight="1"/>
-    <row r="345" ht="15.75" customHeight="1"/>
-    <row r="346" ht="15.75" customHeight="1"/>
-    <row r="347" ht="15.75" customHeight="1"/>
-    <row r="348" ht="15.75" customHeight="1"/>
-    <row r="349" ht="15.75" customHeight="1"/>
-    <row r="350" ht="15.75" customHeight="1"/>
-    <row r="351" ht="15.75" customHeight="1"/>
-    <row r="352" ht="15.75" customHeight="1"/>
-    <row r="353" ht="15.75" customHeight="1"/>
-    <row r="354" ht="15.75" customHeight="1"/>
-    <row r="355" ht="15.75" customHeight="1"/>
-    <row r="356" ht="15.75" customHeight="1"/>
-    <row r="357" ht="15.75" customHeight="1"/>
-    <row r="358" ht="15.75" customHeight="1"/>
-    <row r="359" ht="15.75" customHeight="1"/>
-    <row r="360" ht="15.75" customHeight="1"/>
-    <row r="361" ht="15.75" customHeight="1"/>
-    <row r="362" ht="15.75" customHeight="1"/>
-    <row r="363" ht="15.75" customHeight="1"/>
-    <row r="364" ht="15.75" customHeight="1"/>
-    <row r="365" ht="15.75" customHeight="1"/>
-    <row r="366" ht="15.75" customHeight="1"/>
-    <row r="367" ht="15.75" customHeight="1"/>
-    <row r="368" ht="15.75" customHeight="1"/>
-    <row r="369" ht="15.75" customHeight="1"/>
-    <row r="370" ht="15.75" customHeight="1"/>
-    <row r="371" ht="15.75" customHeight="1"/>
-    <row r="372" ht="15.75" customHeight="1"/>
-    <row r="373" ht="15.75" customHeight="1"/>
-    <row r="374" ht="15.75" customHeight="1"/>
-    <row r="375" ht="15.75" customHeight="1"/>
-    <row r="376" ht="15.75" customHeight="1"/>
-    <row r="377" ht="15.75" customHeight="1"/>
-    <row r="378" ht="15.75" customHeight="1"/>
-    <row r="379" ht="15.75" customHeight="1"/>
-    <row r="380" ht="15.75" customHeight="1"/>
-    <row r="381" ht="15.75" customHeight="1"/>
-    <row r="382" ht="15.75" customHeight="1"/>
-    <row r="383" ht="15.75" customHeight="1"/>
-    <row r="384" ht="15.75" customHeight="1"/>
-    <row r="385" ht="15.75" customHeight="1"/>
-    <row r="386" ht="15.75" customHeight="1"/>
-    <row r="387" ht="15.75" customHeight="1"/>
-    <row r="388" ht="15.75" customHeight="1"/>
-    <row r="389" ht="15.75" customHeight="1"/>
-    <row r="390" ht="15.75" customHeight="1"/>
-    <row r="391" ht="15.75" customHeight="1"/>
-    <row r="392" ht="15.75" customHeight="1"/>
-    <row r="393" ht="15.75" customHeight="1"/>
-    <row r="394" ht="15.75" customHeight="1"/>
-    <row r="395" ht="15.75" customHeight="1"/>
-    <row r="396" ht="15.75" customHeight="1"/>
-    <row r="397" ht="15.75" customHeight="1"/>
-    <row r="398" ht="15.75" customHeight="1"/>
-    <row r="399" ht="15.75" customHeight="1"/>
-    <row r="400" ht="15.75" customHeight="1"/>
-    <row r="401" ht="15.75" customHeight="1"/>
-    <row r="402" ht="15.75" customHeight="1"/>
-    <row r="403" ht="15.75" customHeight="1"/>
-    <row r="404" ht="15.75" customHeight="1"/>
-    <row r="405" ht="15.75" customHeight="1"/>
-    <row r="406" ht="15.75" customHeight="1"/>
-    <row r="407" ht="15.75" customHeight="1"/>
-    <row r="408" ht="15.75" customHeight="1"/>
-    <row r="409" ht="15.75" customHeight="1"/>
-    <row r="410" ht="15.75" customHeight="1"/>
-    <row r="411" ht="15.75" customHeight="1"/>
-    <row r="412" ht="15.75" customHeight="1"/>
-    <row r="413" ht="15.75" customHeight="1"/>
-    <row r="414" ht="15.75" customHeight="1"/>
-    <row r="415" ht="15.75" customHeight="1"/>
-    <row r="416" ht="15.75" customHeight="1"/>
-    <row r="417" ht="15.75" customHeight="1"/>
-    <row r="418" ht="15.75" customHeight="1"/>
-    <row r="419" ht="15.75" customHeight="1"/>
-    <row r="420" ht="15.75" customHeight="1"/>
-    <row r="421" ht="15.75" customHeight="1"/>
-    <row r="422" ht="15.75" customHeight="1"/>
-    <row r="423" ht="15.75" customHeight="1"/>
-    <row r="424" ht="15.75" customHeight="1"/>
-    <row r="425" ht="15.75" customHeight="1"/>
-    <row r="426" ht="15.75" customHeight="1"/>
-    <row r="427" ht="15.75" customHeight="1"/>
-    <row r="428" ht="15.75" customHeight="1"/>
-    <row r="429" ht="15.75" customHeight="1"/>
-    <row r="430" ht="15.75" customHeight="1"/>
-    <row r="431" ht="15.75" customHeight="1"/>
-    <row r="432" ht="15.75" customHeight="1"/>
-    <row r="433" ht="15.75" customHeight="1"/>
-    <row r="434" ht="15.75" customHeight="1"/>
-    <row r="435" ht="15.75" customHeight="1"/>
-    <row r="436" ht="15.75" customHeight="1"/>
-    <row r="437" ht="15.75" customHeight="1"/>
-    <row r="438" ht="15.75" customHeight="1"/>
-    <row r="439" ht="15.75" customHeight="1"/>
-    <row r="440" ht="15.75" customHeight="1"/>
-    <row r="441" ht="15.75" customHeight="1"/>
-    <row r="442" ht="15.75" customHeight="1"/>
-    <row r="443" ht="15.75" customHeight="1"/>
-    <row r="444" ht="15.75" customHeight="1"/>
-    <row r="445" ht="15.75" customHeight="1"/>
-    <row r="446" ht="15.75" customHeight="1"/>
-    <row r="447" ht="15.75" customHeight="1"/>
-    <row r="448" ht="15.75" customHeight="1"/>
-    <row r="449" ht="15.75" customHeight="1"/>
-    <row r="450" ht="15.75" customHeight="1"/>
-    <row r="451" ht="15.75" customHeight="1"/>
-    <row r="452" ht="15.75" customHeight="1"/>
-    <row r="453" ht="15.75" customHeight="1"/>
-    <row r="454" ht="15.75" customHeight="1"/>
-    <row r="455" ht="15.75" customHeight="1"/>
-    <row r="456" ht="15.75" customHeight="1"/>
-    <row r="457" ht="15.75" customHeight="1"/>
-    <row r="458" ht="15.75" customHeight="1"/>
-    <row r="459" ht="15.75" customHeight="1"/>
-    <row r="460" ht="15.75" customHeight="1"/>
-    <row r="461" ht="15.75" customHeight="1"/>
-    <row r="462" ht="15.75" customHeight="1"/>
-    <row r="463" ht="15.75" customHeight="1"/>
-    <row r="464" ht="15.75" customHeight="1"/>
-    <row r="465" ht="15.75" customHeight="1"/>
-    <row r="466" ht="15.75" customHeight="1"/>
-    <row r="467" ht="15.75" customHeight="1"/>
-    <row r="468" ht="15.75" customHeight="1"/>
-    <row r="469" ht="15.75" customHeight="1"/>
-    <row r="470" ht="15.75" customHeight="1"/>
-    <row r="471" ht="15.75" customHeight="1"/>
-    <row r="472" ht="15.75" customHeight="1"/>
-    <row r="473" ht="15.75" customHeight="1"/>
-    <row r="474" ht="15.75" customHeight="1"/>
-    <row r="475" ht="15.75" customHeight="1"/>
-    <row r="476" ht="15.75" customHeight="1"/>
-    <row r="477" ht="15.75" customHeight="1"/>
-    <row r="478" ht="15.75" customHeight="1"/>
-    <row r="479" ht="15.75" customHeight="1"/>
-    <row r="480" ht="15.75" customHeight="1"/>
-    <row r="481" ht="15.75" customHeight="1"/>
-    <row r="482" ht="15.75" customHeight="1"/>
-    <row r="483" ht="15.75" customHeight="1"/>
-    <row r="484" ht="15.75" customHeight="1"/>
-    <row r="485" ht="15.75" customHeight="1"/>
-    <row r="486" ht="15.75" customHeight="1"/>
-    <row r="487" ht="15.75" customHeight="1"/>
-    <row r="488" ht="15.75" customHeight="1"/>
-    <row r="489" ht="15.75" customHeight="1"/>
-    <row r="490" ht="15.75" customHeight="1"/>
-    <row r="491" ht="15.75" customHeight="1"/>
-    <row r="492" ht="15.75" customHeight="1"/>
-    <row r="493" ht="15.75" customHeight="1"/>
-    <row r="494" ht="15.75" customHeight="1"/>
-    <row r="495" ht="15.75" customHeight="1"/>
-    <row r="496" ht="15.75" customHeight="1"/>
-    <row r="497" ht="15.75" customHeight="1"/>
-    <row r="498" ht="15.75" customHeight="1"/>
-    <row r="499" ht="15.75" customHeight="1"/>
-    <row r="500" ht="15.75" customHeight="1"/>
-    <row r="501" ht="15.75" customHeight="1"/>
-    <row r="502" ht="15.75" customHeight="1"/>
-    <row r="503" ht="15.75" customHeight="1"/>
-    <row r="504" ht="15.75" customHeight="1"/>
-    <row r="505" ht="15.75" customHeight="1"/>
-    <row r="506" ht="15.75" customHeight="1"/>
-    <row r="507" ht="15.75" customHeight="1"/>
-    <row r="508" ht="15.75" customHeight="1"/>
-    <row r="509" ht="15.75" customHeight="1"/>
-    <row r="510" ht="15.75" customHeight="1"/>
-    <row r="511" ht="15.75" customHeight="1"/>
-    <row r="512" ht="15.75" customHeight="1"/>
-    <row r="513" ht="15.75" customHeight="1"/>
-    <row r="514" ht="15.75" customHeight="1"/>
-    <row r="515" ht="15.75" customHeight="1"/>
-    <row r="516" ht="15.75" customHeight="1"/>
-    <row r="517" ht="15.75" customHeight="1"/>
-    <row r="518" ht="15.75" customHeight="1"/>
-    <row r="519" ht="15.75" customHeight="1"/>
-    <row r="520" ht="15.75" customHeight="1"/>
-    <row r="521" ht="15.75" customHeight="1"/>
-    <row r="522" ht="15.75" customHeight="1"/>
-    <row r="523" ht="15.75" customHeight="1"/>
-    <row r="524" ht="15.75" customHeight="1"/>
-    <row r="525" ht="15.75" customHeight="1"/>
-    <row r="526" ht="15.75" customHeight="1"/>
-    <row r="527" ht="15.75" customHeight="1"/>
-    <row r="528" ht="15.75" customHeight="1"/>
-    <row r="529" ht="15.75" customHeight="1"/>
-    <row r="530" ht="15.75" customHeight="1"/>
-    <row r="531" ht="15.75" customHeight="1"/>
-    <row r="532" ht="15.75" customHeight="1"/>
-    <row r="533" ht="15.75" customHeight="1"/>
-    <row r="534" ht="15.75" customHeight="1"/>
-    <row r="535" ht="15.75" customHeight="1"/>
-    <row r="536" ht="15.75" customHeight="1"/>
-    <row r="537" ht="15.75" customHeight="1"/>
-    <row r="538" ht="15.75" customHeight="1"/>
-    <row r="539" ht="15.75" customHeight="1"/>
-    <row r="540" ht="15.75" customHeight="1"/>
-    <row r="541" ht="15.75" customHeight="1"/>
-    <row r="542" ht="15.75" customHeight="1"/>
-    <row r="543" ht="15.75" customHeight="1"/>
-    <row r="544" ht="15.75" customHeight="1"/>
-    <row r="545" ht="15.75" customHeight="1"/>
-    <row r="546" ht="15.75" customHeight="1"/>
-    <row r="547" ht="15.75" customHeight="1"/>
-    <row r="548" ht="15.75" customHeight="1"/>
-    <row r="549" ht="15.75" customHeight="1"/>
-    <row r="550" ht="15.75" customHeight="1"/>
-    <row r="551" ht="15.75" customHeight="1"/>
-    <row r="552" ht="15.75" customHeight="1"/>
-    <row r="553" ht="15.75" customHeight="1"/>
-    <row r="554" ht="15.75" customHeight="1"/>
-    <row r="555" ht="15.75" customHeight="1"/>
-    <row r="556" ht="15.75" customHeight="1"/>
-    <row r="557" ht="15.75" customHeight="1"/>
-    <row r="558" ht="15.75" customHeight="1"/>
-    <row r="559" ht="15.75" customHeight="1"/>
-    <row r="560" ht="15.75" customHeight="1"/>
-    <row r="561" ht="15.75" customHeight="1"/>
-    <row r="562" ht="15.75" customHeight="1"/>
-    <row r="563" ht="15.75" customHeight="1"/>
-    <row r="564" ht="15.75" customHeight="1"/>
-    <row r="565" ht="15.75" customHeight="1"/>
-    <row r="566" ht="15.75" customHeight="1"/>
-    <row r="567" ht="15.75" customHeight="1"/>
-    <row r="568" ht="15.75" customHeight="1"/>
-    <row r="569" ht="15.75" customHeight="1"/>
-    <row r="570" ht="15.75" customHeight="1"/>
-    <row r="571" ht="15.75" customHeight="1"/>
-    <row r="572" ht="15.75" customHeight="1"/>
-    <row r="573" ht="15.75" customHeight="1"/>
-    <row r="574" ht="15.75" customHeight="1"/>
-    <row r="575" ht="15.75" customHeight="1"/>
-    <row r="576" ht="15.75" customHeight="1"/>
-    <row r="577" ht="15.75" customHeight="1"/>
-    <row r="578" ht="15.75" customHeight="1"/>
-    <row r="579" ht="15.75" customHeight="1"/>
-    <row r="580" ht="15.75" customHeight="1"/>
-    <row r="581" ht="15.75" customHeight="1"/>
-    <row r="582" ht="15.75" customHeight="1"/>
-    <row r="583" ht="15.75" customHeight="1"/>
-    <row r="584" ht="15.75" customHeight="1"/>
-    <row r="585" ht="15.75" customHeight="1"/>
-    <row r="586" ht="15.75" customHeight="1"/>
-    <row r="587" ht="15.75" customHeight="1"/>
-    <row r="588" ht="15.75" customHeight="1"/>
-    <row r="589" ht="15.75" customHeight="1"/>
-    <row r="590" ht="15.75" customHeight="1"/>
-    <row r="591" ht="15.75" customHeight="1"/>
-    <row r="592" ht="15.75" customHeight="1"/>
-    <row r="593" ht="15.75" customHeight="1"/>
-    <row r="594" ht="15.75" customHeight="1"/>
-    <row r="595" ht="15.75" customHeight="1"/>
-    <row r="596" ht="15.75" customHeight="1"/>
-    <row r="597" ht="15.75" customHeight="1"/>
-    <row r="598" ht="15.75" customHeight="1"/>
-    <row r="599" ht="15.75" customHeight="1"/>
-    <row r="600" ht="15.75" customHeight="1"/>
-    <row r="601" ht="15.75" customHeight="1"/>
-    <row r="602" ht="15.75" customHeight="1"/>
-    <row r="603" ht="15.75" customHeight="1"/>
-    <row r="604" ht="15.75" customHeight="1"/>
-    <row r="605" ht="15.75" customHeight="1"/>
-    <row r="606" ht="15.75" customHeight="1"/>
-    <row r="607" ht="15.75" customHeight="1"/>
-    <row r="608" ht="15.75" customHeight="1"/>
-    <row r="609" ht="15.75" customHeight="1"/>
-    <row r="610" ht="15.75" customHeight="1"/>
-    <row r="611" ht="15.75" customHeight="1"/>
-    <row r="612" ht="15.75" customHeight="1"/>
-    <row r="613" ht="15.75" customHeight="1"/>
-    <row r="614" ht="15.75" customHeight="1"/>
-    <row r="615" ht="15.75" customHeight="1"/>
-    <row r="616" ht="15.75" customHeight="1"/>
-    <row r="617" ht="15.75" customHeight="1"/>
-    <row r="618" ht="15.75" customHeight="1"/>
-    <row r="619" ht="15.75" customHeight="1"/>
-    <row r="620" ht="15.75" customHeight="1"/>
-    <row r="621" ht="15.75" customHeight="1"/>
-    <row r="622" ht="15.75" customHeight="1"/>
-    <row r="623" ht="15.75" customHeight="1"/>
-    <row r="624" ht="15.75" customHeight="1"/>
-    <row r="625" ht="15.75" customHeight="1"/>
-    <row r="626" ht="15.75" customHeight="1"/>
-    <row r="627" ht="15.75" customHeight="1"/>
-    <row r="628" ht="15.75" customHeight="1"/>
-    <row r="629" ht="15.75" customHeight="1"/>
-    <row r="630" ht="15.75" customHeight="1"/>
-    <row r="631" ht="15.75" customHeight="1"/>
-    <row r="632" ht="15.75" customHeight="1"/>
-    <row r="633" ht="15.75" customHeight="1"/>
-    <row r="634" ht="15.75" customHeight="1"/>
-    <row r="635" ht="15.75" customHeight="1"/>
-    <row r="636" ht="15.75" customHeight="1"/>
-    <row r="637" ht="15.75" customHeight="1"/>
-    <row r="638" ht="15.75" customHeight="1"/>
-    <row r="639" ht="15.75" customHeight="1"/>
-    <row r="640" ht="15.75" customHeight="1"/>
-    <row r="641" ht="15.75" customHeight="1"/>
-    <row r="642" ht="15.75" customHeight="1"/>
-    <row r="643" ht="15.75" customHeight="1"/>
-    <row r="644" ht="15.75" customHeight="1"/>
-    <row r="645" ht="15.75" customHeight="1"/>
-    <row r="646" ht="15.75" customHeight="1"/>
-    <row r="647" ht="15.75" customHeight="1"/>
-    <row r="648" ht="15.75" customHeight="1"/>
-    <row r="649" ht="15.75" customHeight="1"/>
-    <row r="650" ht="15.75" customHeight="1"/>
-    <row r="651" ht="15.75" customHeight="1"/>
-    <row r="652" ht="15.75" customHeight="1"/>
-    <row r="653" ht="15.75" customHeight="1"/>
-    <row r="654" ht="15.75" customHeight="1"/>
-    <row r="655" ht="15.75" customHeight="1"/>
-    <row r="656" ht="15.75" customHeight="1"/>
-    <row r="657" ht="15.75" customHeight="1"/>
-    <row r="658" ht="15.75" customHeight="1"/>
-    <row r="659" ht="15.75" customHeight="1"/>
-    <row r="660" ht="15.75" customHeight="1"/>
-    <row r="661" ht="15.75" customHeight="1"/>
-    <row r="662" ht="15.75" customHeight="1"/>
-    <row r="663" ht="15.75" customHeight="1"/>
-    <row r="664" ht="15.75" customHeight="1"/>
-    <row r="665" ht="15.75" customHeight="1"/>
-    <row r="666" ht="15.75" customHeight="1"/>
-    <row r="667" ht="15.75" customHeight="1"/>
-    <row r="668" ht="15.75" customHeight="1"/>
-    <row r="669" ht="15.75" customHeight="1"/>
-    <row r="670" ht="15.75" customHeight="1"/>
-    <row r="671" ht="15.75" customHeight="1"/>
-    <row r="672" ht="15.75" customHeight="1"/>
-    <row r="673" ht="15.75" customHeight="1"/>
-    <row r="674" ht="15.75" customHeight="1"/>
-    <row r="675" ht="15.75" customHeight="1"/>
-    <row r="676" ht="15.75" customHeight="1"/>
-    <row r="677" ht="15.75" customHeight="1"/>
-    <row r="678" ht="15.75" customHeight="1"/>
-    <row r="679" ht="15.75" customHeight="1"/>
-    <row r="680" ht="15.75" customHeight="1"/>
-    <row r="681" ht="15.75" customHeight="1"/>
-    <row r="682" ht="15.75" customHeight="1"/>
-    <row r="683" ht="15.75" customHeight="1"/>
-    <row r="684" ht="15.75" customHeight="1"/>
-    <row r="685" ht="15.75" customHeight="1"/>
-    <row r="686" ht="15.75" customHeight="1"/>
-    <row r="687" ht="15.75" customHeight="1"/>
-    <row r="688" ht="15.75" customHeight="1"/>
-    <row r="689" ht="15.75" customHeight="1"/>
-    <row r="690" ht="15.75" customHeight="1"/>
-    <row r="691" ht="15.75" customHeight="1"/>
-    <row r="692" ht="15.75" customHeight="1"/>
-    <row r="693" ht="15.75" customHeight="1"/>
-    <row r="694" ht="15.75" customHeight="1"/>
-    <row r="695" ht="15.75" customHeight="1"/>
-    <row r="696" ht="15.75" customHeight="1"/>
-    <row r="697" ht="15.75" customHeight="1"/>
-    <row r="698" ht="15.75" customHeight="1"/>
-    <row r="699" ht="15.75" customHeight="1"/>
-    <row r="700" ht="15.75" customHeight="1"/>
-    <row r="701" ht="15.75" customHeight="1"/>
-    <row r="702" ht="15.75" customHeight="1"/>
-    <row r="703" ht="15.75" customHeight="1"/>
-    <row r="704" ht="15.75" customHeight="1"/>
-    <row r="705" ht="15.75" customHeight="1"/>
-    <row r="706" ht="15.75" customHeight="1"/>
-    <row r="707" ht="15.75" customHeight="1"/>
-    <row r="708" ht="15.75" customHeight="1"/>
-    <row r="709" ht="15.75" customHeight="1"/>
-    <row r="710" ht="15.75" customHeight="1"/>
-    <row r="711" ht="15.75" customHeight="1"/>
-    <row r="712" ht="15.75" customHeight="1"/>
-    <row r="713" ht="15.75" customHeight="1"/>
-    <row r="714" ht="15.75" customHeight="1"/>
-    <row r="715" ht="15.75" customHeight="1"/>
-    <row r="716" ht="15.75" customHeight="1"/>
-    <row r="717" ht="15.75" customHeight="1"/>
-    <row r="718" ht="15.75" customHeight="1"/>
-    <row r="719" ht="15.75" customHeight="1"/>
-    <row r="720" ht="15.75" customHeight="1"/>
-    <row r="721" ht="15.75" customHeight="1"/>
-    <row r="722" ht="15.75" customHeight="1"/>
-    <row r="723" ht="15.75" customHeight="1"/>
-    <row r="724" ht="15.75" customHeight="1"/>
-    <row r="725" ht="15.75" customHeight="1"/>
-    <row r="726" ht="15.75" customHeight="1"/>
-    <row r="727" ht="15.75" customHeight="1"/>
-    <row r="728" ht="15.75" customHeight="1"/>
-    <row r="729" ht="15.75" customHeight="1"/>
-    <row r="730" ht="15.75" customHeight="1"/>
-    <row r="731" ht="15.75" customHeight="1"/>
-    <row r="732" ht="15.75" customHeight="1"/>
-    <row r="733" ht="15.75" customHeight="1"/>
-    <row r="734" ht="15.75" customHeight="1"/>
-    <row r="735" ht="15.75" customHeight="1"/>
-    <row r="736" ht="15.75" customHeight="1"/>
-    <row r="737" ht="15.75" customHeight="1"/>
-    <row r="738" ht="15.75" customHeight="1"/>
-    <row r="739" ht="15.75" customHeight="1"/>
-    <row r="740" ht="15.75" customHeight="1"/>
-    <row r="741" ht="15.75" customHeight="1"/>
-    <row r="742" ht="15.75" customHeight="1"/>
-    <row r="743" ht="15.75" customHeight="1"/>
-    <row r="744" ht="15.75" customHeight="1"/>
-    <row r="745" ht="15.75" customHeight="1"/>
-    <row r="746" ht="15.75" customHeight="1"/>
-    <row r="747" ht="15.75" customHeight="1"/>
-    <row r="748" ht="15.75" customHeight="1"/>
-    <row r="749" ht="15.75" customHeight="1"/>
-    <row r="750" ht="15.75" customHeight="1"/>
-    <row r="751" ht="15.75" customHeight="1"/>
-    <row r="752" ht="15.75" customHeight="1"/>
-    <row r="753" ht="15.75" customHeight="1"/>
-    <row r="754" ht="15.75" customHeight="1"/>
-    <row r="755" ht="15.75" customHeight="1"/>
-    <row r="756" ht="15.75" customHeight="1"/>
-    <row r="757" ht="15.75" customHeight="1"/>
-    <row r="758" ht="15.75" customHeight="1"/>
-    <row r="759" ht="15.75" customHeight="1"/>
-    <row r="760" ht="15.75" customHeight="1"/>
-    <row r="761" ht="15.75" customHeight="1"/>
-    <row r="762" ht="15.75" customHeight="1"/>
-    <row r="763" ht="15.75" customHeight="1"/>
-    <row r="764" ht="15.75" customHeight="1"/>
-    <row r="765" ht="15.75" customHeight="1"/>
-    <row r="766" ht="15.75" customHeight="1"/>
-    <row r="767" ht="15.75" customHeight="1"/>
-    <row r="768" ht="15.75" customHeight="1"/>
-    <row r="769" ht="15.75" customHeight="1"/>
-    <row r="770" ht="15.75" customHeight="1"/>
-    <row r="771" ht="15.75" customHeight="1"/>
-    <row r="772" ht="15.75" customHeight="1"/>
-    <row r="773" ht="15.75" customHeight="1"/>
-    <row r="774" ht="15.75" customHeight="1"/>
-    <row r="775" ht="15.75" customHeight="1"/>
-    <row r="776" ht="15.75" customHeight="1"/>
-    <row r="777" ht="15.75" customHeight="1"/>
-    <row r="778" ht="15.75" customHeight="1"/>
-    <row r="779" ht="15.75" customHeight="1"/>
-    <row r="780" ht="15.75" customHeight="1"/>
-    <row r="781" ht="15.75" customHeight="1"/>
-    <row r="782" ht="15.75" customHeight="1"/>
-    <row r="783" ht="15.75" customHeight="1"/>
-    <row r="784" ht="15.75" customHeight="1"/>
-    <row r="785" ht="15.75" customHeight="1"/>
-    <row r="786" ht="15.75" customHeight="1"/>
-    <row r="787" ht="15.75" customHeight="1"/>
-    <row r="788" ht="15.75" customHeight="1"/>
-    <row r="789" ht="15.75" customHeight="1"/>
-    <row r="790" ht="15.75" customHeight="1"/>
-    <row r="791" ht="15.75" customHeight="1"/>
-    <row r="792" ht="15.75" customHeight="1"/>
-    <row r="793" ht="15.75" customHeight="1"/>
-    <row r="794" ht="15.75" customHeight="1"/>
-    <row r="795" ht="15.75" customHeight="1"/>
-    <row r="796" ht="15.75" customHeight="1"/>
-    <row r="797" ht="15.75" customHeight="1"/>
-    <row r="798" ht="15.75" customHeight="1"/>
-    <row r="799" ht="15.75" customHeight="1"/>
-    <row r="800" ht="15.75" customHeight="1"/>
-    <row r="801" ht="15.75" customHeight="1"/>
-    <row r="802" ht="15.75" customHeight="1"/>
-    <row r="803" ht="15.75" customHeight="1"/>
-    <row r="804" ht="15.75" customHeight="1"/>
-    <row r="805" ht="15.75" customHeight="1"/>
-    <row r="806" ht="15.75" customHeight="1"/>
-    <row r="807" ht="15.75" customHeight="1"/>
+    <row r="126" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="127" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="128" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="G4:Q11 G13:Q16 G23:Q25">
@@ -16031,16 +16042,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:U118"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="6.1328125" customWidth="1"/>
+    <col min="1" max="1" width="6.1640625" customWidth="1"/>
     <col min="2" max="9" width="20.6640625" customWidth="1"/>
-    <col min="10" max="11" width="11.1328125" customWidth="1"/>
+    <col min="10" max="11" width="11.1640625" customWidth="1"/>
     <col min="12" max="12" width="20.6640625" customWidth="1"/>
     <col min="13" max="13" width="5.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:15" ht="13.9">
+    <row r="2" spans="2:15" ht="16" x14ac:dyDescent="0.25">
       <c r="B2" s="34" t="s">
         <v>52</v>
       </c>
@@ -16055,7 +16066,7 @@
       <c r="K2" s="35"/>
       <c r="L2" s="35"/>
     </row>
-    <row r="3" spans="2:15" ht="13.15">
+    <row r="3" spans="2:15" x14ac:dyDescent="0.15">
       <c r="B3" s="106" t="s">
         <v>136</v>
       </c>
@@ -16070,7 +16081,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="4" spans="2:15">
+    <row r="4" spans="2:15" x14ac:dyDescent="0.15">
       <c r="B4" s="97" t="s">
         <v>391</v>
       </c>
@@ -16102,7 +16113,7 @@
       </c>
       <c r="J4" s="305"/>
     </row>
-    <row r="5" spans="2:15">
+    <row r="5" spans="2:15" x14ac:dyDescent="0.15">
       <c r="B5" s="187" t="s">
         <v>105</v>
       </c>
@@ -16130,7 +16141,7 @@
       </c>
       <c r="J5" s="305"/>
     </row>
-    <row r="6" spans="2:15" ht="13.25" customHeight="1">
+    <row r="6" spans="2:15" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B6" s="136" t="s">
         <v>194</v>
       </c>
@@ -16163,7 +16174,7 @@
       <c r="J6" s="305"/>
       <c r="N6" s="135"/>
     </row>
-    <row r="7" spans="2:15" ht="12.75" customHeight="1">
+    <row r="7" spans="2:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B7" s="318" t="s">
         <v>428</v>
       </c>
@@ -16193,7 +16204,7 @@
       <c r="N7" s="304"/>
       <c r="O7" s="304"/>
     </row>
-    <row r="8" spans="2:15" ht="13.15">
+    <row r="8" spans="2:15" ht="14" x14ac:dyDescent="0.15">
       <c r="B8" s="136" t="s">
         <v>424</v>
       </c>
@@ -16228,7 +16239,7 @@
       <c r="N8" s="304"/>
       <c r="O8" s="304"/>
     </row>
-    <row r="9" spans="2:15" ht="13.15" thickBot="1">
+    <row r="9" spans="2:15" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B9" s="189" t="str">
         <f>"*"&amp;Thesis!E15</f>
         <v>*CNY</v>
@@ -16254,7 +16265,7 @@
       <c r="N9" s="304"/>
       <c r="O9" s="304"/>
     </row>
-    <row r="10" spans="2:15" ht="13.5" thickTop="1">
+    <row r="10" spans="2:15" ht="14" thickTop="1" x14ac:dyDescent="0.15">
       <c r="B10" s="107" t="s">
         <v>425</v>
       </c>
@@ -16276,7 +16287,7 @@
       <c r="N10" s="304"/>
       <c r="O10" s="304"/>
     </row>
-    <row r="11" spans="2:15" ht="13.15">
+    <row r="11" spans="2:15" x14ac:dyDescent="0.15">
       <c r="B11" s="136" t="s">
         <v>423</v>
       </c>
@@ -16292,7 +16303,7 @@
       <c r="I11" s="307"/>
       <c r="J11" s="307"/>
     </row>
-    <row r="13" spans="2:15" ht="13.9">
+    <row r="13" spans="2:15" ht="16" x14ac:dyDescent="0.25">
       <c r="B13" s="34" t="s">
         <v>426</v>
       </c>
@@ -16307,7 +16318,7 @@
       <c r="K13" s="35"/>
       <c r="L13" s="35"/>
     </row>
-    <row r="14" spans="2:15" ht="13.15">
+    <row r="14" spans="2:15" x14ac:dyDescent="0.15">
       <c r="B14" s="106" t="s">
         <v>397</v>
       </c>
@@ -16325,7 +16336,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="15" spans="2:15">
+    <row r="15" spans="2:15" x14ac:dyDescent="0.15">
       <c r="B15" s="139" t="s">
         <v>419</v>
       </c>
@@ -16350,7 +16361,7 @@
       </c>
       <c r="J15" s="126"/>
     </row>
-    <row r="16" spans="2:15" ht="13.25" customHeight="1">
+    <row r="16" spans="2:15" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B16" s="114" t="s">
         <v>420</v>
       </c>
@@ -16366,7 +16377,7 @@
         <v>2.38559171477595E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:21" ht="13.25" customHeight="1">
+    <row r="17" spans="1:21" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B17" s="308" t="s">
         <v>547</v>
       </c>
@@ -16385,7 +16396,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="18" spans="1:21" ht="13.25" customHeight="1">
+    <row r="18" spans="1:21" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="308" t="s">
         <v>421</v>
       </c>
@@ -16412,10 +16423,10 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="19" spans="1:21">
+    <row r="19" spans="1:21" x14ac:dyDescent="0.15">
       <c r="L19" s="275"/>
     </row>
-    <row r="20" spans="1:21" ht="13.15">
+    <row r="20" spans="1:21" ht="14" x14ac:dyDescent="0.2">
       <c r="A20" s="121" t="s">
         <v>397</v>
       </c>
@@ -16454,7 +16465,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="21" spans="1:21">
+    <row r="21" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A21" s="302" t="str">
         <f t="shared" ref="A21:A50" si="0">IF($C$15&lt;B21,"",IF(B21&gt;=$F$15,"II","I"))</f>
         <v>I</v>
@@ -16503,7 +16514,7 @@
         <v>28450593708.666355</v>
       </c>
     </row>
-    <row r="22" spans="1:21">
+    <row r="22" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A22" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -16552,7 +16563,7 @@
         <v>27160194606.046497</v>
       </c>
     </row>
-    <row r="23" spans="1:21">
+    <row r="23" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A23" s="302" t="str">
         <f t="shared" si="0"/>
         <v>II</v>
@@ -16609,7 +16620,7 @@
       <c r="T23" s="275"/>
       <c r="U23" s="275"/>
     </row>
-    <row r="24" spans="1:21">
+    <row r="24" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A24" s="302" t="str">
         <f t="shared" si="0"/>
         <v>II</v>
@@ -16666,7 +16677,7 @@
       <c r="T24" s="275"/>
       <c r="U24" s="275"/>
     </row>
-    <row r="25" spans="1:21">
+    <row r="25" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A25" s="302" t="str">
         <f t="shared" si="0"/>
         <v>II</v>
@@ -16723,7 +16734,7 @@
       <c r="T25" s="275"/>
       <c r="U25" s="275"/>
     </row>
-    <row r="26" spans="1:21">
+    <row r="26" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A26" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -16772,7 +16783,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:21">
+    <row r="27" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A27" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -16821,7 +16832,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:21">
+    <row r="28" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A28" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -16870,7 +16881,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:21">
+    <row r="29" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A29" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -16919,7 +16930,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:21">
+    <row r="30" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A30" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -16968,7 +16979,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:21">
+    <row r="31" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A31" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17017,7 +17028,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:21">
+    <row r="32" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A32" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17066,7 +17077,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:21">
+    <row r="33" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A33" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17123,7 +17134,7 @@
       <c r="T33" s="275"/>
       <c r="U33" s="275"/>
     </row>
-    <row r="34" spans="1:21">
+    <row r="34" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A34" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17180,7 +17191,7 @@
       <c r="T34" s="275"/>
       <c r="U34" s="275"/>
     </row>
-    <row r="35" spans="1:21">
+    <row r="35" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A35" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17237,7 +17248,7 @@
       <c r="T35" s="275"/>
       <c r="U35" s="275"/>
     </row>
-    <row r="36" spans="1:21">
+    <row r="36" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A36" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17286,7 +17297,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:21">
+    <row r="37" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A37" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17335,7 +17346,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:21">
+    <row r="38" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A38" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17384,7 +17395,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:21">
+    <row r="39" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A39" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17433,7 +17444,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:21">
+    <row r="40" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A40" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17482,7 +17493,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:21">
+    <row r="41" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A41" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17531,7 +17542,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:21">
+    <row r="42" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A42" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17580,7 +17591,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:21">
+    <row r="43" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A43" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17629,7 +17640,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:21">
+    <row r="44" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A44" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17678,7 +17689,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:21">
+    <row r="45" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A45" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17727,7 +17738,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:21">
+    <row r="46" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A46" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17776,7 +17787,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:21">
+    <row r="47" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A47" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17833,7 +17844,7 @@
       <c r="T47" s="275"/>
       <c r="U47" s="275"/>
     </row>
-    <row r="48" spans="1:21">
+    <row r="48" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A48" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17890,7 +17901,7 @@
       <c r="T48" s="275"/>
       <c r="U48" s="275"/>
     </row>
-    <row r="49" spans="1:21">
+    <row r="49" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A49" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17947,7 +17958,7 @@
       <c r="T49" s="275"/>
       <c r="U49" s="275"/>
     </row>
-    <row r="50" spans="1:21">
+    <row r="50" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A50" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -18004,7 +18015,7 @@
       <c r="T50" s="275"/>
       <c r="U50" s="275"/>
     </row>
-    <row r="51" spans="1:21">
+    <row r="51" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A51" s="315" t="s">
         <v>416</v>
       </c>
@@ -18050,7 +18061,7 @@
         <v>285808228079.48792</v>
       </c>
     </row>
-    <row r="52" spans="1:21" ht="13.15">
+    <row r="52" spans="1:21" x14ac:dyDescent="0.15">
       <c r="G52" s="111"/>
       <c r="H52" s="111"/>
       <c r="I52" s="111"/>
@@ -18063,10 +18074,10 @@
         <v>405304783322.55359</v>
       </c>
     </row>
-    <row r="53" spans="1:21">
+    <row r="53" spans="1:21" x14ac:dyDescent="0.15">
       <c r="C53" s="111"/>
     </row>
-    <row r="54" spans="1:21" ht="13.15">
+    <row r="54" spans="1:21" x14ac:dyDescent="0.15">
       <c r="B54" s="115" t="s">
         <v>108</v>
       </c>
@@ -18081,7 +18092,7 @@
       <c r="K54" s="113"/>
       <c r="L54" s="113"/>
     </row>
-    <row r="55" spans="1:21" ht="13.15">
+    <row r="55" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A55" s="125">
         <f>L52</f>
         <v>405304783322.55359</v>
@@ -18113,7 +18124,7 @@
       <c r="K55" s="123"/>
       <c r="L55" s="123"/>
     </row>
-    <row r="56" spans="1:21" ht="13.15">
+    <row r="56" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A56" s="131">
         <v>1</v>
       </c>
@@ -18140,7 +18151,7 @@
       <c r="K56" s="295"/>
       <c r="L56" s="295"/>
     </row>
-    <row r="57" spans="1:21" ht="13.15">
+    <row r="57" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A57" s="131">
         <v>2</v>
       </c>
@@ -18166,7 +18177,7 @@
       <c r="K57" s="295"/>
       <c r="L57" s="295"/>
     </row>
-    <row r="58" spans="1:21" ht="13.15">
+    <row r="58" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A58" s="131">
         <v>3</v>
       </c>
@@ -18192,7 +18203,7 @@
       <c r="K58" s="295"/>
       <c r="L58" s="295"/>
     </row>
-    <row r="59" spans="1:21" ht="13.15">
+    <row r="59" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A59" s="131">
         <v>4</v>
       </c>
@@ -18218,7 +18229,7 @@
       <c r="K59" s="295"/>
       <c r="L59" s="295"/>
     </row>
-    <row r="60" spans="1:21" ht="13.15">
+    <row r="60" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A60" s="131">
         <v>5</v>
       </c>
@@ -18244,7 +18255,7 @@
       <c r="K60" s="295"/>
       <c r="L60" s="295"/>
     </row>
-    <row r="61" spans="1:21" ht="13.15">
+    <row r="61" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A61" s="131">
         <v>6</v>
       </c>
@@ -18270,7 +18281,7 @@
       <c r="K61" s="295"/>
       <c r="L61" s="295"/>
     </row>
-    <row r="62" spans="1:21" ht="13.15">
+    <row r="62" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A62" s="131">
         <v>7</v>
       </c>
@@ -18296,7 +18307,7 @@
       <c r="K62" s="295"/>
       <c r="L62" s="295"/>
     </row>
-    <row r="63" spans="1:21" ht="13.15">
+    <row r="63" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A63" s="131">
         <v>8</v>
       </c>
@@ -18322,7 +18333,7 @@
       <c r="K63" s="295"/>
       <c r="L63" s="295"/>
     </row>
-    <row r="64" spans="1:21" ht="13.15">
+    <row r="64" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A64" s="131">
         <v>9</v>
       </c>
@@ -18348,7 +18359,7 @@
       <c r="K64" s="295"/>
       <c r="L64" s="295"/>
     </row>
-    <row r="65" spans="1:21" ht="13.15">
+    <row r="65" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A65" s="131">
         <v>10</v>
       </c>
@@ -18374,7 +18385,7 @@
       <c r="K65" s="295"/>
       <c r="L65" s="295"/>
     </row>
-    <row r="66" spans="1:21" ht="13.15">
+    <row r="66" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A66" s="131">
         <v>15</v>
       </c>
@@ -18409,7 +18420,7 @@
       <c r="T66" s="275"/>
       <c r="U66" s="275"/>
     </row>
-    <row r="67" spans="1:21" ht="13.15">
+    <row r="67" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A67" s="132">
         <v>20</v>
       </c>
@@ -18444,7 +18455,7 @@
       <c r="T67" s="275"/>
       <c r="U67" s="275"/>
     </row>
-    <row r="68" spans="1:21" ht="13.15">
+    <row r="68" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A68" s="132">
         <v>25</v>
       </c>
@@ -18479,7 +18490,7 @@
       <c r="T68" s="275"/>
       <c r="U68" s="275"/>
     </row>
-    <row r="69" spans="1:21" ht="13.15">
+    <row r="69" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A69" s="132">
         <v>30</v>
       </c>
@@ -18514,7 +18525,7 @@
       <c r="T69" s="275"/>
       <c r="U69" s="275"/>
     </row>
-    <row r="70" spans="1:21">
+    <row r="70" spans="1:21" x14ac:dyDescent="0.15">
       <c r="C70" s="275"/>
       <c r="D70" s="111"/>
       <c r="E70" s="111"/>
@@ -18535,7 +18546,7 @@
       <c r="T70" s="275"/>
       <c r="U70" s="275"/>
     </row>
-    <row r="71" spans="1:21" ht="13.15">
+    <row r="71" spans="1:21" x14ac:dyDescent="0.15">
       <c r="B71" s="115" t="s">
         <v>109</v>
       </c>
@@ -18559,7 +18570,7 @@
       <c r="T71" s="275"/>
       <c r="U71" s="275"/>
     </row>
-    <row r="72" spans="1:21" ht="13.15">
+    <row r="72" spans="1:21" x14ac:dyDescent="0.15">
       <c r="B72" s="124">
         <f>B55</f>
         <v>0</v>
@@ -18587,7 +18598,7 @@
       <c r="K72" s="124"/>
       <c r="L72" s="124"/>
     </row>
-    <row r="73" spans="1:21" ht="13.15">
+    <row r="73" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A73" s="131">
         <v>0</v>
       </c>
@@ -18618,7 +18629,7 @@
       <c r="K73" s="296"/>
       <c r="L73" s="296"/>
     </row>
-    <row r="74" spans="1:21" ht="13.15">
+    <row r="74" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A74" s="131">
         <v>1</v>
       </c>
@@ -18649,7 +18660,7 @@
       <c r="K74" s="296"/>
       <c r="L74" s="296"/>
     </row>
-    <row r="75" spans="1:21" ht="13.15">
+    <row r="75" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A75" s="131">
         <v>2</v>
       </c>
@@ -18680,7 +18691,7 @@
       <c r="K75" s="296"/>
       <c r="L75" s="296"/>
     </row>
-    <row r="76" spans="1:21" ht="13.15">
+    <row r="76" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A76" s="131">
         <v>3</v>
       </c>
@@ -18711,7 +18722,7 @@
       <c r="K76" s="296"/>
       <c r="L76" s="296"/>
     </row>
-    <row r="77" spans="1:21" ht="13.15">
+    <row r="77" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A77" s="131">
         <v>4</v>
       </c>
@@ -18742,7 +18753,7 @@
       <c r="K77" s="296"/>
       <c r="L77" s="296"/>
     </row>
-    <row r="78" spans="1:21" ht="13.15">
+    <row r="78" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A78" s="131">
         <v>5</v>
       </c>
@@ -18773,7 +18784,7 @@
       <c r="K78" s="296"/>
       <c r="L78" s="296"/>
     </row>
-    <row r="79" spans="1:21" ht="13.15">
+    <row r="79" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A79" s="131">
         <v>6</v>
       </c>
@@ -18804,7 +18815,7 @@
       <c r="K79" s="296"/>
       <c r="L79" s="296"/>
     </row>
-    <row r="80" spans="1:21" ht="13.15">
+    <row r="80" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A80" s="131">
         <f t="shared" ref="A80" si="12">A62</f>
         <v>7</v>
@@ -18836,7 +18847,7 @@
       <c r="K80" s="296"/>
       <c r="L80" s="296"/>
     </row>
-    <row r="81" spans="1:12" ht="13.15">
+    <row r="81" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A81" s="131">
         <v>8</v>
       </c>
@@ -18867,7 +18878,7 @@
       <c r="K81" s="296"/>
       <c r="L81" s="296"/>
     </row>
-    <row r="82" spans="1:12" ht="13.15">
+    <row r="82" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A82" s="131">
         <f t="shared" ref="A82" si="13">A64</f>
         <v>9</v>
@@ -18899,7 +18910,7 @@
       <c r="K82" s="296"/>
       <c r="L82" s="296"/>
     </row>
-    <row r="83" spans="1:12" ht="13.15">
+    <row r="83" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A83" s="131">
         <f t="shared" ref="A83:A87" si="14">A65</f>
         <v>10</v>
@@ -18931,7 +18942,7 @@
       <c r="K83" s="296"/>
       <c r="L83" s="296"/>
     </row>
-    <row r="84" spans="1:12" ht="13.15">
+    <row r="84" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A84" s="131">
         <f t="shared" si="14"/>
         <v>15</v>
@@ -18963,7 +18974,7 @@
       <c r="K84" s="296"/>
       <c r="L84" s="296"/>
     </row>
-    <row r="85" spans="1:12" ht="13.15">
+    <row r="85" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A85" s="132">
         <f t="shared" si="14"/>
         <v>20</v>
@@ -18995,7 +19006,7 @@
       <c r="K85" s="296"/>
       <c r="L85" s="296"/>
     </row>
-    <row r="86" spans="1:12" ht="13.15">
+    <row r="86" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A86" s="132">
         <f t="shared" si="14"/>
         <v>25</v>
@@ -19027,7 +19038,7 @@
       <c r="K86" s="296"/>
       <c r="L86" s="296"/>
     </row>
-    <row r="87" spans="1:12" ht="13.15">
+    <row r="87" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A87" s="132">
         <f t="shared" si="14"/>
         <v>30</v>
@@ -19059,7 +19070,7 @@
       <c r="K87" s="296"/>
       <c r="L87" s="296"/>
     </row>
-    <row r="89" spans="1:12" ht="13.15">
+    <row r="89" spans="1:12" ht="14" x14ac:dyDescent="0.2">
       <c r="B89" s="153" t="s">
         <v>101</v>
       </c>
@@ -19082,7 +19093,7 @@
       <c r="K89" s="323"/>
       <c r="L89" s="323"/>
     </row>
-    <row r="90" spans="1:12">
+    <row r="90" spans="1:12" x14ac:dyDescent="0.15">
       <c r="B90" s="120" t="str">
         <f>Scenarios!B29</f>
         <v>Snowball Scenario</v>
@@ -19110,7 +19121,7 @@
       <c r="K90" s="297"/>
       <c r="L90" s="297"/>
     </row>
-    <row r="91" spans="1:12">
+    <row r="91" spans="1:12" x14ac:dyDescent="0.15">
       <c r="B91" s="120" t="str">
         <f>Scenarios!B22</f>
         <v>Optimistic</v>
@@ -19138,7 +19149,7 @@
       <c r="K91" s="297"/>
       <c r="L91" s="297"/>
     </row>
-    <row r="92" spans="1:12">
+    <row r="92" spans="1:12" x14ac:dyDescent="0.15">
       <c r="B92" s="120" t="str">
         <f>Scenarios!B23</f>
         <v>Base</v>
@@ -19166,7 +19177,7 @@
       <c r="K92" s="297"/>
       <c r="L92" s="297"/>
     </row>
-    <row r="93" spans="1:12">
+    <row r="93" spans="1:12" x14ac:dyDescent="0.15">
       <c r="B93" s="120" t="str">
         <f>Scenarios!B24</f>
         <v>Pessimistic</v>
@@ -19194,7 +19205,7 @@
       <c r="K93" s="297"/>
       <c r="L93" s="297"/>
     </row>
-    <row r="94" spans="1:12">
+    <row r="94" spans="1:12" x14ac:dyDescent="0.15">
       <c r="B94" s="120" t="str">
         <f>Scenarios!B30</f>
         <v>Devil's advocate</v>
@@ -19222,7 +19233,7 @@
       <c r="K94" s="297"/>
       <c r="L94" s="297"/>
     </row>
-    <row r="95" spans="1:12">
+    <row r="95" spans="1:12" x14ac:dyDescent="0.15">
       <c r="B95" s="141"/>
       <c r="C95" s="141"/>
       <c r="D95" s="141"/>
@@ -19235,16 +19246,16 @@
       <c r="K95" s="142"/>
       <c r="L95" s="142"/>
     </row>
-    <row r="105" spans="3:3">
+    <row r="105" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C105" s="112"/>
     </row>
-    <row r="106" spans="3:3">
+    <row r="106" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C106" s="112"/>
     </row>
-    <row r="107" spans="3:3">
+    <row r="107" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C107" s="112"/>
     </row>
-    <row r="114" spans="3:21">
+    <row r="114" spans="3:21" x14ac:dyDescent="0.15">
       <c r="C114" s="275"/>
       <c r="M114" s="275"/>
       <c r="N114" s="275"/>
@@ -19256,7 +19267,7 @@
       <c r="T114" s="275"/>
       <c r="U114" s="275"/>
     </row>
-    <row r="115" spans="3:21">
+    <row r="115" spans="3:21" x14ac:dyDescent="0.15">
       <c r="C115" s="275"/>
       <c r="M115" s="275"/>
       <c r="N115" s="275"/>
@@ -19268,7 +19279,7 @@
       <c r="T115" s="275"/>
       <c r="U115" s="275"/>
     </row>
-    <row r="116" spans="3:21">
+    <row r="116" spans="3:21" x14ac:dyDescent="0.15">
       <c r="C116" s="275"/>
       <c r="M116" s="275"/>
       <c r="N116" s="275"/>
@@ -19280,7 +19291,7 @@
       <c r="T116" s="275"/>
       <c r="U116" s="275"/>
     </row>
-    <row r="117" spans="3:21">
+    <row r="117" spans="3:21" x14ac:dyDescent="0.15">
       <c r="C117" s="275"/>
       <c r="M117" s="275"/>
       <c r="N117" s="275"/>
@@ -19292,7 +19303,7 @@
       <c r="T117" s="275"/>
       <c r="U117" s="275"/>
     </row>
-    <row r="118" spans="3:21">
+    <row r="118" spans="3:21" x14ac:dyDescent="0.15">
       <c r="C118" s="275"/>
       <c r="M118" s="275"/>
       <c r="N118" s="275"/>
@@ -19332,14 +19343,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
   <dimension ref="B2:G67"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="2.6640625" customWidth="1"/>
     <col min="2" max="2" width="22.6640625" customWidth="1"/>
     <col min="3" max="7" width="20.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" ht="13.9">
+    <row r="2" spans="2:7" ht="16" x14ac:dyDescent="0.25">
       <c r="B2" s="34" t="s">
         <v>122</v>
       </c>
@@ -19349,7 +19360,7 @@
       <c r="F2" s="35"/>
       <c r="G2" s="35"/>
     </row>
-    <row r="3" spans="2:7" ht="13.15">
+    <row r="3" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B3" s="145" t="s">
         <v>125</v>
       </c>
@@ -19358,7 +19369,7 @@
       </c>
       <c r="E3" s="97"/>
     </row>
-    <row r="4" spans="2:7" ht="12.75" customHeight="1">
+    <row r="4" spans="2:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B4" s="139" t="s">
         <v>123</v>
       </c>
@@ -19379,14 +19390,14 @@
       <c r="F4" s="469"/>
       <c r="G4" s="469"/>
     </row>
-    <row r="5" spans="2:7">
+    <row r="5" spans="2:7" x14ac:dyDescent="0.15">
       <c r="C5" s="445"/>
       <c r="D5" s="469"/>
       <c r="E5" s="469"/>
       <c r="F5" s="469"/>
       <c r="G5" s="469"/>
     </row>
-    <row r="6" spans="2:7" ht="13.15">
+    <row r="6" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B6" s="145" t="s">
         <v>91</v>
       </c>
@@ -19399,7 +19410,7 @@
       <c r="F6" s="469"/>
       <c r="G6" s="469"/>
     </row>
-    <row r="7" spans="2:7" ht="12.75" customHeight="1">
+    <row r="7" spans="2:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B7" s="97" t="s">
         <v>232</v>
       </c>
@@ -19412,7 +19423,7 @@
       <c r="F7" s="469"/>
       <c r="G7" s="469"/>
     </row>
-    <row r="8" spans="2:7">
+    <row r="8" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B8" s="97" t="s">
         <v>63</v>
       </c>
@@ -19425,7 +19436,7 @@
       <c r="F8" s="469"/>
       <c r="G8" s="469"/>
     </row>
-    <row r="9" spans="2:7">
+    <row r="9" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B9" s="97" t="s">
         <v>54</v>
       </c>
@@ -19438,14 +19449,14 @@
       <c r="F9" s="469"/>
       <c r="G9" s="469"/>
     </row>
-    <row r="10" spans="2:7">
+    <row r="10" spans="2:7" x14ac:dyDescent="0.15">
       <c r="C10" s="448"/>
       <c r="D10" s="469"/>
       <c r="E10" s="469"/>
       <c r="F10" s="469"/>
       <c r="G10" s="469"/>
     </row>
-    <row r="11" spans="2:7" ht="13.15">
+    <row r="11" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B11" s="145" t="s">
         <v>320</v>
       </c>
@@ -19455,7 +19466,7 @@
       <c r="F11" s="469"/>
       <c r="G11" s="469"/>
     </row>
-    <row r="12" spans="2:7">
+    <row r="12" spans="2:7" ht="14" x14ac:dyDescent="0.15">
       <c r="B12" s="114" t="s">
         <v>121</v>
       </c>
@@ -19468,7 +19479,7 @@
       <c r="F12" s="469"/>
       <c r="G12" s="469"/>
     </row>
-    <row r="13" spans="2:7">
+    <row r="13" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B13" s="135" t="s">
         <v>127</v>
       </c>
@@ -19481,7 +19492,7 @@
       <c r="F13" s="469"/>
       <c r="G13" s="469"/>
     </row>
-    <row r="14" spans="2:7">
+    <row r="14" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B14" s="97" t="s">
         <v>63</v>
       </c>
@@ -19494,7 +19505,7 @@
       <c r="F14" s="469"/>
       <c r="G14" s="469"/>
     </row>
-    <row r="16" spans="2:7" ht="13.9">
+    <row r="16" spans="2:7" ht="16" x14ac:dyDescent="0.25">
       <c r="B16" s="34" t="s">
         <v>451</v>
       </c>
@@ -19504,7 +19515,7 @@
       <c r="F16" s="35"/>
       <c r="G16" s="35"/>
     </row>
-    <row r="17" spans="2:7" ht="13.15">
+    <row r="17" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B17" s="106" t="s">
         <v>126</v>
       </c>
@@ -19512,7 +19523,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="18" spans="2:7" ht="12.75" customHeight="1">
+    <row r="18" spans="2:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="139" t="s">
         <v>111</v>
       </c>
@@ -19524,18 +19535,18 @@
       </c>
       <c r="F18" s="319"/>
     </row>
-    <row r="19" spans="2:7">
+    <row r="19" spans="2:7" x14ac:dyDescent="0.15">
       <c r="E19" s="319"/>
       <c r="F19" s="319"/>
     </row>
-    <row r="20" spans="2:7" ht="13.15">
+    <row r="20" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B20" s="106" t="s">
         <v>448</v>
       </c>
       <c r="E20" s="319"/>
       <c r="F20" s="319"/>
     </row>
-    <row r="21" spans="2:7" ht="13.15">
+    <row r="21" spans="2:7" ht="14" x14ac:dyDescent="0.2">
       <c r="B21" s="153" t="s">
         <v>434</v>
       </c>
@@ -19556,7 +19567,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="22" spans="2:7">
+    <row r="22" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B22" s="302" t="s">
         <v>443</v>
       </c>
@@ -19580,7 +19591,7 @@
         <v>0.15999999999999995</v>
       </c>
     </row>
-    <row r="23" spans="2:7">
+    <row r="23" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B23" s="302" t="s">
         <v>435</v>
       </c>
@@ -19603,7 +19614,7 @@
         <v>0.44</v>
       </c>
     </row>
-    <row r="24" spans="2:7">
+    <row r="24" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B24" s="302" t="s">
         <v>444</v>
       </c>
@@ -19626,7 +19637,7 @@
         <v>0.19999999999999998</v>
       </c>
     </row>
-    <row r="25" spans="2:7">
+    <row r="25" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B25" s="141" t="s">
         <v>449</v>
       </c>
@@ -19640,12 +19651,12 @@
       </c>
       <c r="G25" s="149"/>
     </row>
-    <row r="27" spans="2:7" ht="13.15">
+    <row r="27" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B27" s="106" t="s">
         <v>450</v>
       </c>
     </row>
-    <row r="28" spans="2:7" ht="13.15">
+    <row r="28" spans="2:7" ht="14" x14ac:dyDescent="0.2">
       <c r="B28" s="153" t="s">
         <v>434</v>
       </c>
@@ -19666,7 +19677,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="29" spans="2:7">
+    <row r="29" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B29" s="302" t="s">
         <v>442</v>
       </c>
@@ -19689,7 +19700,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="30" spans="2:7">
+    <row r="30" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B30" s="315" t="s">
         <v>445</v>
       </c>
@@ -19712,16 +19723,16 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="31" spans="2:7">
+    <row r="31" spans="2:7" x14ac:dyDescent="0.15">
       <c r="E31" s="329"/>
       <c r="F31" s="329"/>
     </row>
-    <row r="32" spans="2:7" ht="13.15">
+    <row r="32" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B32" s="145" t="s">
         <v>454</v>
       </c>
     </row>
-    <row r="33" spans="2:7">
+    <row r="33" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B33" s="97" t="s">
         <v>456</v>
       </c>
@@ -19741,7 +19752,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="34" spans="2:7">
+    <row r="34" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B34" s="97" t="s">
         <v>233</v>
       </c>
@@ -19761,7 +19772,7 @@
         <v>0.10787497156703298</v>
       </c>
     </row>
-    <row r="35" spans="2:7">
+    <row r="35" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B35" s="97" t="s">
         <v>432</v>
       </c>
@@ -19781,7 +19792,7 @@
         <v>-7.3996144898412761E-2</v>
       </c>
     </row>
-    <row r="36" spans="2:7">
+    <row r="36" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B36" s="97" t="s">
         <v>433</v>
       </c>
@@ -19800,7 +19811,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="38" spans="2:7" ht="13.9">
+    <row r="38" spans="2:7" ht="16" x14ac:dyDescent="0.25">
       <c r="B38" s="34" t="s">
         <v>409</v>
       </c>
@@ -19810,7 +19821,7 @@
       <c r="F38" s="35"/>
       <c r="G38" s="35"/>
     </row>
-    <row r="39" spans="2:7" ht="13.15">
+    <row r="39" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B39" s="414" t="str">
         <f>IF(DCF!F14="II","2","1")&amp;"-stage DCF"</f>
         <v>2-stage DCF</v>
@@ -19819,7 +19830,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="40" spans="2:7">
+    <row r="40" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B40" t="s">
         <v>548</v>
       </c>
@@ -19831,7 +19842,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="41" spans="2:7">
+    <row r="41" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B41" s="97" t="s">
         <v>398</v>
       </c>
@@ -19841,7 +19852,7 @@
       </c>
       <c r="E41" s="97"/>
     </row>
-    <row r="43" spans="2:7" ht="13.9">
+    <row r="43" spans="2:7" ht="16" x14ac:dyDescent="0.25">
       <c r="B43" s="34" t="s">
         <v>276</v>
       </c>
@@ -19851,7 +19862,7 @@
       <c r="F43" s="35"/>
       <c r="G43" s="35"/>
     </row>
-    <row r="44" spans="2:7" ht="13.15">
+    <row r="44" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B44" s="106" t="s">
         <v>249</v>
       </c>
@@ -19859,7 +19870,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="45" spans="2:7">
+    <row r="45" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B45" s="139" t="s">
         <v>111</v>
       </c>
@@ -19872,7 +19883,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="46" spans="2:7">
+    <row r="46" spans="2:7" ht="14" x14ac:dyDescent="0.15">
       <c r="B46" s="114" t="s">
         <v>112</v>
       </c>
@@ -19884,7 +19895,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="47" spans="2:7">
+    <row r="47" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B47" s="97" t="s">
         <v>96</v>
       </c>
@@ -19900,7 +19911,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="49" spans="2:7" ht="13.15">
+    <row r="49" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B49" s="106" t="s">
         <v>277</v>
       </c>
@@ -19912,7 +19923,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="50" spans="2:7">
+    <row r="50" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B50" s="97" t="s">
         <v>250</v>
       </c>
@@ -19922,7 +19933,7 @@
       </c>
       <c r="E50" s="126"/>
     </row>
-    <row r="51" spans="2:7">
+    <row r="51" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B51" s="97" t="s">
         <v>246</v>
       </c>
@@ -19934,7 +19945,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="52" spans="2:7">
+    <row r="52" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B52" s="97" t="s">
         <v>245</v>
       </c>
@@ -19944,7 +19955,7 @@
       </c>
       <c r="E52" s="221"/>
     </row>
-    <row r="53" spans="2:7">
+    <row r="53" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B53" s="97" t="s">
         <v>237</v>
       </c>
@@ -19960,7 +19971,7 @@
         <v>0.2262544978580209</v>
       </c>
     </row>
-    <row r="55" spans="2:7" ht="13.9">
+    <row r="55" spans="2:7" ht="16" x14ac:dyDescent="0.25">
       <c r="B55" s="34" t="s">
         <v>107</v>
       </c>
@@ -19970,12 +19981,12 @@
       <c r="F55" s="35"/>
       <c r="G55" s="35"/>
     </row>
-    <row r="56" spans="2:7" ht="13.15">
+    <row r="56" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B56" s="106" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="57" spans="2:7">
+    <row r="57" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B57" s="220" t="s">
         <v>248</v>
       </c>
@@ -19985,7 +19996,7 @@
       </c>
       <c r="D57" s="126"/>
     </row>
-    <row r="58" spans="2:7">
+    <row r="58" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B58" s="97" t="s">
         <v>331</v>
       </c>
@@ -19998,13 +20009,13 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="60" spans="2:7" ht="13.15">
+    <row r="60" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B60" s="106" t="s">
         <v>471</v>
       </c>
       <c r="E60" s="413"/>
     </row>
-    <row r="61" spans="2:7" ht="13.15">
+    <row r="61" spans="2:7" ht="14" x14ac:dyDescent="0.2">
       <c r="B61" s="153" t="s">
         <v>460</v>
       </c>
@@ -20025,7 +20036,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="62" spans="2:7" ht="13.15">
+    <row r="62" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B62" s="302" t="s">
         <v>311</v>
       </c>
@@ -20050,7 +20061,7 @@
         <v>0.53755491242430398</v>
       </c>
     </row>
-    <row r="63" spans="2:7" ht="13.15">
+    <row r="63" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B63" s="302" t="s">
         <v>312</v>
       </c>
@@ -20075,7 +20086,7 @@
         <v>0.41479582873538823</v>
       </c>
     </row>
-    <row r="65" spans="2:7" ht="13.15">
+    <row r="65" spans="2:7" ht="14" x14ac:dyDescent="0.2">
       <c r="B65" s="153" t="s">
         <v>461</v>
       </c>
@@ -20096,7 +20107,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="66" spans="2:7" ht="13.15">
+    <row r="66" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B66" s="302" t="s">
         <v>314</v>
       </c>
@@ -20121,7 +20132,7 @@
         <v>0.16752343251869795</v>
       </c>
     </row>
-    <row r="67" spans="2:7" ht="13.15">
+    <row r="67" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B67" s="302" t="s">
         <v>313</v>
       </c>
@@ -20162,7 +20173,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:J167"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="343" customWidth="1"/>
     <col min="2" max="2" width="32.6640625" style="343" customWidth="1"/>
@@ -20171,7 +20182,7 @@
     <col min="7" max="16384" width="9" style="343"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:10" ht="13.9">
+    <row r="2" spans="1:10" ht="16" x14ac:dyDescent="0.25">
       <c r="A2" s="345" t="s">
         <v>332</v>
       </c>
@@ -20185,7 +20196,7 @@
       <c r="I2" s="346"/>
       <c r="J2" s="346"/>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="E3" s="435" t="s">
         <v>539</v>
       </c>
@@ -20194,7 +20205,7 @@
         <v>46066</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B4" s="422" t="s">
         <v>531</v>
       </c>
@@ -20211,7 +20222,7 @@
         <v>CN</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B5" s="343" t="s">
         <v>362</v>
       </c>
@@ -20227,7 +20238,7 @@
         <v>N</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B6" s="350" t="s">
         <v>334</v>
       </c>
@@ -20237,7 +20248,7 @@
       </c>
       <c r="E6" s="354"/>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B7" s="343" t="s">
         <v>364</v>
       </c>
@@ -20248,7 +20259,7 @@
       <c r="D7" s="354"/>
       <c r="E7" s="354"/>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B8" s="351" t="s">
         <v>363</v>
       </c>
@@ -20257,7 +20268,7 @@
         <v>106.06</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B9" s="351" t="s">
         <v>359</v>
       </c>
@@ -20266,7 +20277,7 @@
         <v>3881608005</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B10" s="351" t="s">
         <v>365</v>
       </c>
@@ -20282,27 +20293,27 @@
         <v>0.10787497156703298</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="D11" s="349"/>
       <c r="E11" s="349"/>
     </row>
-    <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="471" t="s">
+    <row r="12" spans="1:10" ht="24.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B12" s="474" t="s">
         <v>495</v>
       </c>
-      <c r="C12" s="471"/>
-      <c r="D12" s="471"/>
-      <c r="E12" s="471"/>
-      <c r="F12" s="471"/>
-    </row>
-    <row r="14" spans="1:10">
+      <c r="C12" s="474"/>
+      <c r="D12" s="474"/>
+      <c r="E12" s="474"/>
+      <c r="F12" s="474"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B14" s="347" t="s">
         <v>368</v>
       </c>
       <c r="C14" s="348"/>
       <c r="D14" s="349"/>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B15" s="343" t="s">
         <v>335</v>
       </c>
@@ -20318,7 +20329,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B16" s="343" t="s">
         <v>336</v>
       </c>
@@ -20334,7 +20345,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B17" s="343" t="s">
         <v>532</v>
       </c>
@@ -20350,7 +20361,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B18" s="343" t="str">
         <f>"预期股权价值 ("&amp;C7&amp;") :"</f>
         <v>预期股权价值 (CNY) :</v>
@@ -20367,7 +20378,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B19" s="350" t="s">
         <v>333</v>
       </c>
@@ -20383,11 +20394,11 @@
         <v>46081</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="D20" s="349"/>
       <c r="E20" s="349"/>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B21" s="347" t="s">
         <v>491</v>
       </c>
@@ -20403,7 +20414,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B22" s="343" t="s">
         <v>338</v>
       </c>
@@ -20419,7 +20430,7 @@
         <v>0.32950289523458665</v>
       </c>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B23" s="343" t="s">
         <v>339</v>
       </c>
@@ -20435,7 +20446,7 @@
         <v>0.22621703288100403</v>
       </c>
     </row>
-    <row r="24" spans="1:6">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B24" s="343" t="s">
         <v>341</v>
       </c>
@@ -20451,7 +20462,7 @@
         <v>8.6999999999999994E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B25" s="343" t="s">
         <v>340</v>
       </c>
@@ -20467,7 +20478,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="13.9">
+    <row r="27" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A27" s="345" t="s">
         <v>343</v>
       </c>
@@ -20477,25 +20488,25 @@
       <c r="E27" s="345"/>
       <c r="F27" s="345"/>
     </row>
-    <row r="29" spans="1:6">
-      <c r="B29" s="471" t="s">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B29" s="474" t="s">
         <v>496</v>
       </c>
-      <c r="C29" s="471"/>
-      <c r="D29" s="471"/>
-      <c r="E29" s="471"/>
-      <c r="F29" s="471"/>
-    </row>
-    <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="472" t="s">
+      <c r="C29" s="474"/>
+      <c r="D29" s="474"/>
+      <c r="E29" s="474"/>
+      <c r="F29" s="474"/>
+    </row>
+    <row r="30" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B30" s="477" t="s">
         <v>497</v>
       </c>
-      <c r="C30" s="472"/>
-      <c r="D30" s="472"/>
-      <c r="E30" s="472"/>
-      <c r="F30" s="472"/>
-    </row>
-    <row r="32" spans="1:6">
+      <c r="C30" s="477"/>
+      <c r="D30" s="477"/>
+      <c r="E30" s="477"/>
+      <c r="F30" s="477"/>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B32" s="369" t="s">
         <v>369</v>
       </c>
@@ -20504,7 +20515,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="2:6">
+    <row r="33" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B33" s="470" t="s">
         <v>498</v>
       </c>
@@ -20513,7 +20524,7 @@
       <c r="E33" s="470"/>
       <c r="F33" s="470"/>
     </row>
-    <row r="34" spans="2:6">
+    <row r="34" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B34" s="372" t="s">
         <v>197</v>
       </c>
@@ -20526,11 +20537,11 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="35" spans="2:6">
+    <row r="35" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B35" s="372"/>
       <c r="C35" s="374"/>
     </row>
-    <row r="36" spans="2:6" ht="24.5" customHeight="1">
+    <row r="36" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B36" s="470" t="s">
         <v>499</v>
       </c>
@@ -20539,7 +20550,7 @@
       <c r="E36" s="470"/>
       <c r="F36" s="470"/>
     </row>
-    <row r="37" spans="2:6">
+    <row r="37" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B37" s="372" t="s">
         <v>199</v>
       </c>
@@ -20552,7 +20563,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="38" spans="2:6">
+    <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="375" t="s">
         <v>200</v>
       </c>
@@ -20565,7 +20576,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="40" spans="2:6">
+    <row r="40" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B40" s="470" t="s">
         <v>500</v>
       </c>
@@ -20574,7 +20585,7 @@
       <c r="E40" s="470"/>
       <c r="F40" s="470"/>
     </row>
-    <row r="41" spans="2:6">
+    <row r="41" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B41" s="372" t="s">
         <v>202</v>
       </c>
@@ -20587,7 +20598,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="43" spans="2:6">
+    <row r="43" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B43" s="470" t="s">
         <v>501</v>
       </c>
@@ -20596,7 +20607,7 @@
       <c r="E43" s="470"/>
       <c r="F43" s="470"/>
     </row>
-    <row r="44" spans="2:6">
+    <row r="44" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B44" s="372" t="s">
         <v>267</v>
       </c>
@@ -20611,7 +20622,7 @@
       <c r="E44" s="371"/>
       <c r="F44" s="371"/>
     </row>
-    <row r="45" spans="2:6">
+    <row r="45" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B45" s="372" t="s">
         <v>268</v>
       </c>
@@ -20626,7 +20637,7 @@
       <c r="E45" s="371"/>
       <c r="F45" s="371"/>
     </row>
-    <row r="46" spans="2:6">
+    <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="372" t="s">
         <v>203</v>
       </c>
@@ -20639,12 +20650,12 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="48" spans="2:6">
+    <row r="48" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B48" s="343" t="s">
         <v>502</v>
       </c>
     </row>
-    <row r="49" spans="2:6">
+    <row r="49" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B49" s="372" t="s">
         <v>223</v>
       </c>
@@ -20657,7 +20668,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="51" spans="2:6">
+    <row r="51" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B51" s="470" t="s">
         <v>503</v>
       </c>
@@ -20666,7 +20677,7 @@
       <c r="E51" s="470"/>
       <c r="F51" s="470"/>
     </row>
-    <row r="52" spans="2:6">
+    <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="372" t="s">
         <v>494</v>
       </c>
@@ -20679,16 +20690,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="54" spans="2:6">
+    <row r="54" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B54" s="470" t="s">
         <v>504</v>
       </c>
-      <c r="C54" s="473"/>
-      <c r="D54" s="473"/>
-      <c r="E54" s="473"/>
-      <c r="F54" s="473"/>
-    </row>
-    <row r="55" spans="2:6">
+      <c r="C54" s="476"/>
+      <c r="D54" s="476"/>
+      <c r="E54" s="476"/>
+      <c r="F54" s="476"/>
+    </row>
+    <row r="55" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B55" s="372" t="s">
         <v>207</v>
       </c>
@@ -20701,25 +20712,25 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="57" spans="2:6">
-      <c r="B57" s="471" t="s">
+    <row r="57" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B57" s="474" t="s">
         <v>505</v>
       </c>
-      <c r="C57" s="471"/>
-      <c r="D57" s="471"/>
-      <c r="E57" s="471"/>
-      <c r="F57" s="471"/>
-    </row>
-    <row r="58" spans="2:6">
-      <c r="B58" s="471" t="s">
+      <c r="C57" s="474"/>
+      <c r="D57" s="474"/>
+      <c r="E57" s="474"/>
+      <c r="F57" s="474"/>
+    </row>
+    <row r="58" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B58" s="474" t="s">
         <v>506</v>
       </c>
-      <c r="C58" s="471"/>
-      <c r="D58" s="471"/>
-      <c r="E58" s="471"/>
-      <c r="F58" s="471"/>
-    </row>
-    <row r="60" spans="2:6">
+      <c r="C58" s="474"/>
+      <c r="D58" s="474"/>
+      <c r="E58" s="474"/>
+      <c r="F58" s="474"/>
+    </row>
+    <row r="60" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B60" s="372" t="s">
         <v>370</v>
       </c>
@@ -20732,7 +20743,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="61" spans="2:6">
+    <row r="61" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B61" s="372" t="s">
         <v>213</v>
       </c>
@@ -20745,7 +20756,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="62" spans="2:6">
+    <row r="62" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B62" s="377" t="s">
         <v>302</v>
       </c>
@@ -20755,7 +20766,7 @@
       </c>
       <c r="F62" s="379"/>
     </row>
-    <row r="63" spans="2:6">
+    <row r="63" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B63" s="377" t="s">
         <v>330</v>
       </c>
@@ -20771,7 +20782,7 @@
         <v>0.4127471888056104</v>
       </c>
     </row>
-    <row r="65" spans="1:6">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B65" s="369" t="s">
         <v>374</v>
       </c>
@@ -20782,7 +20793,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="66" spans="1:6">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B66" s="372" t="s">
         <v>324</v>
       </c>
@@ -20795,7 +20806,7 @@
         <v>0.26898198471339402</v>
       </c>
     </row>
-    <row r="67" spans="1:6">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B67" s="382" t="str">
         <f>Normalized_FCF!B116</f>
         <v>Pre-tax Profit/Sales</v>
@@ -20809,7 +20820,7 @@
         <v>0.43474742930380028</v>
       </c>
     </row>
-    <row r="68" spans="1:6">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B68" s="382" t="str">
         <f>Normalized_FCF!B117</f>
         <v>Sales/Total Assets</v>
@@ -20823,7 +20834,7 @@
         <v>0.4610552539366265</v>
       </c>
     </row>
-    <row r="69" spans="1:6">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B69" s="382" t="str">
         <f>Normalized_FCF!B118</f>
         <v>Total Assets/Equity</v>
@@ -20837,7 +20848,7 @@
         <v>1.3419403008261008</v>
       </c>
     </row>
-    <row r="71" spans="1:6" ht="13.9">
+    <row r="71" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A71" s="345" t="s">
         <v>474</v>
       </c>
@@ -20847,43 +20858,43 @@
       <c r="E71" s="345"/>
       <c r="F71" s="345"/>
     </row>
-    <row r="72" spans="1:6">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A72" s="385"/>
     </row>
-    <row r="73" spans="1:6">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A73" s="386"/>
-      <c r="B73" s="471" t="s">
+      <c r="B73" s="474" t="s">
         <v>507</v>
       </c>
-      <c r="C73" s="471"/>
-      <c r="D73" s="471"/>
-      <c r="E73" s="471"/>
-      <c r="F73" s="471"/>
-    </row>
-    <row r="74" spans="1:6">
-      <c r="B74" s="472" t="s">
+      <c r="C73" s="474"/>
+      <c r="D73" s="474"/>
+      <c r="E73" s="474"/>
+      <c r="F73" s="474"/>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B74" s="477" t="s">
         <v>477</v>
       </c>
-      <c r="C74" s="472"/>
-      <c r="D74" s="472"/>
-      <c r="E74" s="472"/>
-      <c r="F74" s="472"/>
-    </row>
-    <row r="76" spans="1:6">
+      <c r="C74" s="477"/>
+      <c r="D74" s="477"/>
+      <c r="E74" s="477"/>
+      <c r="F74" s="477"/>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B76" s="369" t="s">
         <v>369</v>
       </c>
     </row>
-    <row r="77" spans="1:6">
-      <c r="B77" s="471" t="s">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B77" s="474" t="s">
         <v>508</v>
       </c>
-      <c r="C77" s="471"/>
-      <c r="D77" s="471"/>
-      <c r="E77" s="471"/>
-      <c r="F77" s="471"/>
-    </row>
-    <row r="78" spans="1:6">
+      <c r="C77" s="474"/>
+      <c r="D77" s="474"/>
+      <c r="E77" s="474"/>
+      <c r="F77" s="474"/>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B78" s="343" t="s">
         <v>215</v>
       </c>
@@ -20896,7 +20907,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="79" spans="1:6">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B79" s="372" t="s">
         <v>234</v>
       </c>
@@ -20909,7 +20920,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="80" spans="1:6">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B80" s="382" t="s">
         <v>308</v>
       </c>
@@ -20918,7 +20929,7 @@
         <v>1.4942693904035366E-3</v>
       </c>
     </row>
-    <row r="81" spans="1:6">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B81" s="382" t="s">
         <v>310</v>
       </c>
@@ -20927,12 +20938,12 @@
         <v>5.1971735080735887E-3</v>
       </c>
     </row>
-    <row r="83" spans="1:6">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B83" s="343" t="s">
         <v>509</v>
       </c>
     </row>
-    <row r="84" spans="1:6">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B84" s="343" t="s">
         <v>224</v>
       </c>
@@ -20945,7 +20956,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="85" spans="1:6">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B85" s="382" t="s">
         <v>479</v>
       </c>
@@ -20958,7 +20969,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="86" spans="1:6">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B86" s="372" t="s">
         <v>235</v>
       </c>
@@ -20971,12 +20982,12 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="88" spans="1:6">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B88" s="343" t="s">
         <v>510</v>
       </c>
     </row>
-    <row r="89" spans="1:6">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B89" s="343" t="s">
         <v>217</v>
       </c>
@@ -20989,7 +21000,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="90" spans="1:6">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B90" s="372" t="s">
         <v>236</v>
       </c>
@@ -21002,7 +21013,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="92" spans="1:6">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B92" s="372" t="s">
         <v>478</v>
       </c>
@@ -21015,7 +21026,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="94" spans="1:6" ht="13.9">
+    <row r="94" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A94" s="345" t="s">
         <v>480</v>
       </c>
@@ -21025,49 +21036,49 @@
       <c r="E94" s="345"/>
       <c r="F94" s="345"/>
     </row>
-    <row r="95" spans="1:6">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A95" s="385"/>
     </row>
-    <row r="96" spans="1:6">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A96" s="385"/>
-      <c r="B96" s="471" t="s">
+      <c r="B96" s="474" t="s">
         <v>511</v>
       </c>
-      <c r="C96" s="471"/>
-      <c r="D96" s="471"/>
-      <c r="E96" s="471"/>
-      <c r="F96" s="471"/>
-    </row>
-    <row r="97" spans="1:6">
+      <c r="C96" s="474"/>
+      <c r="D96" s="474"/>
+      <c r="E96" s="474"/>
+      <c r="F96" s="474"/>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A97" s="385"/>
-      <c r="B97" s="472" t="s">
+      <c r="B97" s="477" t="s">
         <v>512</v>
       </c>
-      <c r="C97" s="472"/>
-      <c r="D97" s="472"/>
-      <c r="E97" s="472"/>
-      <c r="F97" s="472"/>
-    </row>
-    <row r="98" spans="1:6">
+      <c r="C97" s="477"/>
+      <c r="D97" s="477"/>
+      <c r="E97" s="477"/>
+      <c r="F97" s="477"/>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A98" s="385"/>
-      <c r="B98" s="472" t="s">
+      <c r="B98" s="477" t="s">
         <v>513</v>
       </c>
-      <c r="C98" s="472"/>
-      <c r="D98" s="472"/>
-      <c r="E98" s="472"/>
-      <c r="F98" s="472"/>
-    </row>
-    <row r="99" spans="1:6">
+      <c r="C98" s="477"/>
+      <c r="D98" s="477"/>
+      <c r="E98" s="477"/>
+      <c r="F98" s="477"/>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A99" s="385"/>
     </row>
-    <row r="100" spans="1:6">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A100" s="385"/>
       <c r="B100" s="369" t="s">
         <v>369</v>
       </c>
     </row>
-    <row r="101" spans="1:6">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A101" s="385"/>
       <c r="B101" s="372" t="s">
         <v>212</v>
@@ -21077,7 +21088,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="102" spans="1:6">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A102" s="385"/>
       <c r="B102" s="382" t="s">
         <v>317</v>
@@ -21087,7 +21098,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="103" spans="1:6">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A103" s="385"/>
       <c r="B103" s="382" t="s">
         <v>316</v>
@@ -21097,7 +21108,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:6">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A104" s="385"/>
       <c r="B104" s="372" t="s">
         <v>532</v>
@@ -21106,47 +21117,47 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:6">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A105" s="385"/>
       <c r="C105" s="392"/>
     </row>
-    <row r="106" spans="1:6">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A106" s="385"/>
       <c r="B106" s="393" t="s">
         <v>373</v>
       </c>
       <c r="C106" s="392"/>
     </row>
-    <row r="107" spans="1:6">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A107" s="385"/>
-      <c r="B107" s="471" t="s">
+      <c r="B107" s="474" t="s">
         <v>514</v>
       </c>
-      <c r="C107" s="471"/>
-      <c r="D107" s="471"/>
-      <c r="E107" s="471"/>
-      <c r="F107" s="471"/>
-    </row>
-    <row r="108" spans="1:6">
+      <c r="C107" s="474"/>
+      <c r="D107" s="474"/>
+      <c r="E107" s="474"/>
+      <c r="F107" s="474"/>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A108" s="385"/>
-      <c r="B108" s="471" t="s">
+      <c r="B108" s="474" t="s">
         <v>533</v>
       </c>
-      <c r="C108" s="471"/>
-      <c r="D108" s="471"/>
-      <c r="E108" s="471"/>
-      <c r="F108" s="471"/>
-    </row>
-    <row r="109" spans="1:6">
+      <c r="C108" s="474"/>
+      <c r="D108" s="474"/>
+      <c r="E108" s="474"/>
+      <c r="F108" s="474"/>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A109" s="385"/>
     </row>
-    <row r="110" spans="1:6">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A110" s="385"/>
       <c r="B110" s="369" t="s">
         <v>487</v>
       </c>
     </row>
-    <row r="111" spans="1:6">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A111" s="385"/>
       <c r="B111" s="375" t="s">
         <v>484</v>
@@ -21160,7 +21171,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="112" spans="1:6">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A112" s="385"/>
       <c r="B112" s="372" t="s">
         <v>375</v>
@@ -21174,29 +21185,29 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="113" spans="1:6">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A113" s="385"/>
     </row>
-    <row r="114" spans="1:6">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A114" s="385"/>
-      <c r="B114" s="471" t="s">
+      <c r="B114" s="474" t="s">
         <v>515</v>
       </c>
-      <c r="C114" s="471"/>
-      <c r="D114" s="471"/>
-      <c r="E114" s="471"/>
-      <c r="F114" s="471"/>
-    </row>
-    <row r="115" spans="1:6">
+      <c r="C114" s="474"/>
+      <c r="D114" s="474"/>
+      <c r="E114" s="474"/>
+      <c r="F114" s="474"/>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A115" s="385"/>
     </row>
-    <row r="116" spans="1:6">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A116" s="385"/>
       <c r="B116" s="369" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="117" spans="1:6">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A117" s="385"/>
       <c r="B117" s="342" t="s">
         <v>376</v>
@@ -21214,7 +21225,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="118" spans="1:6">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A118" s="385"/>
       <c r="B118" s="395" t="str">
         <f>DCF!B90</f>
@@ -21237,7 +21248,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="119" spans="1:6">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A119" s="385"/>
       <c r="B119" s="400" t="str">
         <f>DCF!B91</f>
@@ -21260,7 +21271,7 @@
         <v>0.15999999999999995</v>
       </c>
     </row>
-    <row r="120" spans="1:6">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B120" s="400" t="str">
         <f>DCF!B92</f>
         <v>Base</v>
@@ -21282,7 +21293,7 @@
         <v>0.44</v>
       </c>
     </row>
-    <row r="121" spans="1:6">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B121" s="400" t="str">
         <f>DCF!B93</f>
         <v>Pessimistic</v>
@@ -21304,7 +21315,7 @@
         <v>0.19999999999999998</v>
       </c>
     </row>
-    <row r="122" spans="1:6">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B122" s="400" t="str">
         <f>DCF!B94</f>
         <v>Devil's advocate</v>
@@ -21326,7 +21337,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="124" spans="1:6">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B124" s="470" t="s">
         <v>516</v>
       </c>
@@ -21335,7 +21346,7 @@
       <c r="E124" s="470"/>
       <c r="F124" s="470"/>
     </row>
-    <row r="125" spans="1:6">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B125" s="372" t="s">
         <v>218</v>
       </c>
@@ -21348,16 +21359,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="127" spans="1:6">
-      <c r="B127" s="475" t="s">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B127" s="472" t="s">
         <v>517</v>
       </c>
-      <c r="C127" s="475"/>
-      <c r="D127" s="475"/>
-      <c r="E127" s="475"/>
-      <c r="F127" s="475"/>
-    </row>
-    <row r="129" spans="1:6" ht="13.9">
+      <c r="C127" s="472"/>
+      <c r="D127" s="472"/>
+      <c r="E127" s="472"/>
+      <c r="F127" s="472"/>
+    </row>
+    <row r="129" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A129" s="345" t="s">
         <v>490</v>
       </c>
@@ -21367,30 +21378,30 @@
       <c r="E129" s="345"/>
       <c r="F129" s="345"/>
     </row>
-    <row r="131" spans="1:6">
-      <c r="B131" s="476" t="s">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B131" s="473" t="s">
         <v>518</v>
       </c>
-      <c r="C131" s="476"/>
-      <c r="D131" s="476"/>
-      <c r="E131" s="476"/>
-      <c r="F131" s="476"/>
-    </row>
-    <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="471" t="s">
+      <c r="C131" s="473"/>
+      <c r="D131" s="473"/>
+      <c r="E131" s="473"/>
+      <c r="F131" s="473"/>
+    </row>
+    <row r="132" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B132" s="474" t="s">
         <v>519</v>
       </c>
-      <c r="C132" s="471"/>
-      <c r="D132" s="471"/>
-      <c r="E132" s="471"/>
-      <c r="F132" s="471"/>
-    </row>
-    <row r="134" spans="1:6">
+      <c r="C132" s="474"/>
+      <c r="D132" s="474"/>
+      <c r="E132" s="474"/>
+      <c r="F132" s="474"/>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B134" s="369" t="s">
         <v>369</v>
       </c>
     </row>
-    <row r="135" spans="1:6">
+    <row r="135" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B135" s="343" t="s">
         <v>380</v>
       </c>
@@ -21399,7 +21410,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="136" spans="1:6">
+    <row r="136" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B136" s="343" t="s">
         <v>381</v>
       </c>
@@ -21412,14 +21423,14 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="138" spans="1:6">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B138" s="369" t="s">
         <v>491</v>
       </c>
       <c r="C138" s="407"/>
       <c r="D138" s="407"/>
     </row>
-    <row r="139" spans="1:6">
+    <row r="139" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B139" s="340" t="s">
         <v>460</v>
       </c>
@@ -21438,7 +21449,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="140" spans="1:6">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B140" s="408" t="s">
         <v>311</v>
       </c>
@@ -21459,7 +21470,7 @@
         <v>0.32950289523458665</v>
       </c>
     </row>
-    <row r="141" spans="1:6">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B141" s="408" t="s">
         <v>312</v>
       </c>
@@ -21480,7 +21491,7 @@
         <v>0.22621703288100403</v>
       </c>
     </row>
-    <row r="143" spans="1:6">
+    <row r="143" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B143" s="340" t="s">
         <v>461</v>
       </c>
@@ -21499,7 +21510,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="144" spans="1:6">
+    <row r="144" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B144" s="408" t="s">
         <v>314</v>
       </c>
@@ -21520,7 +21531,7 @@
         <v>8.6999999999999994E-2</v>
       </c>
     </row>
-    <row r="145" spans="1:6">
+    <row r="145" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B145" s="408" t="s">
         <v>313</v>
       </c>
@@ -21541,7 +21552,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="147" spans="1:6" ht="13.9">
+    <row r="147" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A147" s="345" t="s">
         <v>473</v>
       </c>
@@ -21551,50 +21562,50 @@
       <c r="E147" s="345"/>
       <c r="F147" s="345"/>
     </row>
-    <row r="149" spans="1:6">
-      <c r="B149" s="477" t="s">
+    <row r="149" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B149" s="475" t="s">
         <v>520</v>
       </c>
-      <c r="C149" s="471"/>
-      <c r="D149" s="471"/>
-      <c r="E149" s="471"/>
-      <c r="F149" s="471"/>
-    </row>
-    <row r="151" spans="1:6">
+      <c r="C149" s="474"/>
+      <c r="D149" s="474"/>
+      <c r="E149" s="474"/>
+      <c r="F149" s="474"/>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B151" s="369" t="s">
         <v>382</v>
       </c>
     </row>
-    <row r="152" spans="1:6">
-      <c r="B152" s="473" t="s">
+    <row r="152" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B152" s="476" t="s">
         <v>521</v>
       </c>
-      <c r="C152" s="473"/>
-      <c r="D152" s="473"/>
-      <c r="E152" s="473"/>
-      <c r="F152" s="473"/>
-    </row>
-    <row r="153" spans="1:6">
+      <c r="C152" s="476"/>
+      <c r="D152" s="476"/>
+      <c r="E152" s="476"/>
+      <c r="F152" s="476"/>
+    </row>
+    <row r="153" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B153" s="412" t="s">
         <v>383</v>
       </c>
     </row>
-    <row r="154" spans="1:6">
+    <row r="154" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B154" s="412" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="155" spans="1:6">
+    <row r="155" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B155" s="412" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="157" spans="1:6">
+    <row r="157" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B157" s="343" t="s">
         <v>522</v>
       </c>
     </row>
-    <row r="158" spans="1:6" ht="24.5" customHeight="1">
+    <row r="158" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B158" s="470" t="s">
         <v>437</v>
       </c>
@@ -21603,60 +21614,57 @@
       <c r="E158" s="470"/>
       <c r="F158" s="470"/>
     </row>
-    <row r="160" spans="1:6">
+    <row r="160" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B160" s="343" t="s">
         <v>523</v>
       </c>
     </row>
-    <row r="161" spans="2:6">
-      <c r="B161" s="474" t="s">
+    <row r="161" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B161" s="471" t="s">
         <v>386</v>
       </c>
-      <c r="C161" s="474"/>
-      <c r="D161" s="474"/>
-      <c r="E161" s="474"/>
-      <c r="F161" s="474"/>
-    </row>
-    <row r="162" spans="2:6">
-      <c r="B162" s="474" t="s">
+      <c r="C161" s="471"/>
+      <c r="D161" s="471"/>
+      <c r="E161" s="471"/>
+      <c r="F161" s="471"/>
+    </row>
+    <row r="162" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B162" s="471" t="s">
         <v>387</v>
       </c>
-      <c r="C162" s="474"/>
-      <c r="D162" s="474"/>
-      <c r="E162" s="474"/>
-      <c r="F162" s="474"/>
-    </row>
-    <row r="164" spans="2:6">
+      <c r="C162" s="471"/>
+      <c r="D162" s="471"/>
+      <c r="E162" s="471"/>
+      <c r="F162" s="471"/>
+    </row>
+    <row r="164" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B164" s="343" t="s">
         <v>524</v>
       </c>
     </row>
-    <row r="165" spans="2:6">
+    <row r="165" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B165" s="412" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="166" spans="2:6">
+    <row r="166" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B166" s="412" t="s">
         <v>389</v>
       </c>
     </row>
-    <row r="167" spans="2:6">
+    <row r="167" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B167" s="412" t="s">
         <v>390</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21671,12 +21679,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/000858.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/000858.SZ_Valuation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kamanl/PycharmProjects/Invest_Proc/financial_models/opportunities/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D67B3D85-E630-2A41-BE07-4A42E9840B75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8439BE3B-9F9D-4255-A017-246B293F616F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="17120" windowHeight="10760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -39,17 +39,6 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
     <ext uri="GoogleSheetsCustomDataVersion1">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId10" roundtripDataSignature="AMtx7mi73Cg0ax9bLfpeUuF69nNRn7idDQ=="/>
@@ -3280,27 +3269,27 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="19">
-    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00;[Red]\-&quot;$&quot;#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="166" formatCode="#,##0&quot;mm&quot;"/>
-    <numFmt numFmtId="167" formatCode="#,##0.00&quot;x&quot;"/>
-    <numFmt numFmtId="168" formatCode="0.00\x"/>
-    <numFmt numFmtId="169" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="170" formatCode="#,##0.0000"/>
-    <numFmt numFmtId="171" formatCode="#,##0_ "/>
-    <numFmt numFmtId="172" formatCode="#,##0.0000_);\(#,##0.0000\)"/>
-    <numFmt numFmtId="173" formatCode="#,##0.0000_ "/>
-    <numFmt numFmtId="174" formatCode="&quot;in &quot;#,##0&quot;s&quot;"/>
-    <numFmt numFmtId="175" formatCode="#,##0.00_ "/>
-    <numFmt numFmtId="176" formatCode="0&quot; yrs&quot;"/>
-    <numFmt numFmtId="177" formatCode="0.000_ "/>
-    <numFmt numFmtId="178" formatCode="&quot;every&quot;\ 0\ &quot;Months&quot;"/>
-    <numFmt numFmtId="179" formatCode="0.0\x"/>
-    <numFmt numFmtId="180" formatCode="0\x"/>
-    <numFmt numFmtId="181" formatCode="0.000000000000000%"/>
-    <numFmt numFmtId="182" formatCode="#,##0_);\(#,##0\);0;@"/>
+    <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00;[Red]\-&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="165" formatCode="#,##0&quot;mm&quot;"/>
+    <numFmt numFmtId="166" formatCode="#,##0.00&quot;x&quot;"/>
+    <numFmt numFmtId="167" formatCode="0.00\x"/>
+    <numFmt numFmtId="168" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="169" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="170" formatCode="#,##0_ "/>
+    <numFmt numFmtId="171" formatCode="#,##0.0000_);\(#,##0.0000\)"/>
+    <numFmt numFmtId="172" formatCode="#,##0.0000_ "/>
+    <numFmt numFmtId="173" formatCode="&quot;in &quot;#,##0&quot;s&quot;"/>
+    <numFmt numFmtId="174" formatCode="#,##0.00_ "/>
+    <numFmt numFmtId="175" formatCode="0&quot; yrs&quot;"/>
+    <numFmt numFmtId="176" formatCode="0.000_ "/>
+    <numFmt numFmtId="177" formatCode="&quot;every&quot;\ 0\ &quot;Months&quot;"/>
+    <numFmt numFmtId="178" formatCode="0.0\x"/>
+    <numFmt numFmtId="179" formatCode="0\x"/>
+    <numFmt numFmtId="180" formatCode="0.000000000000000%"/>
+    <numFmt numFmtId="181" formatCode="#,##0_);\(#,##0\);0;@"/>
   </numFmts>
-  <fonts count="72" x14ac:knownFonts="1">
+  <fonts count="72">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -4052,7 +4041,7 @@
     <xf numFmtId="3" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -4094,17 +4083,17 @@
     <xf numFmtId="3" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="169" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="169" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="170" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4113,7 +4102,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4187,10 +4176,10 @@
     </xf>
     <xf numFmtId="10" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="172" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="171" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -4201,7 +4190,7 @@
     <xf numFmtId="10" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="169" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -4239,7 +4228,7 @@
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4249,7 +4238,7 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="169" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4260,19 +4249,19 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="169" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="174" fontId="17" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="173" fontId="17" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="174" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="173" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="174" fontId="23" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="173" fontId="23" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -4280,8 +4269,8 @@
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="39" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="173" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="173" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="172" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="172" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="37" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="38" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -4304,29 +4293,29 @@
     </xf>
     <xf numFmtId="9" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="171" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="170" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="39" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="175" fontId="24" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="24" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="10" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="176" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="176" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="175" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="175" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="175" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="174" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="176" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="175" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -4343,15 +4332,15 @@
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="175" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="174" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="176" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="175" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -4362,11 +4351,11 @@
     <xf numFmtId="0" fontId="27" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="3" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="175" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4427,14 +4416,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="175" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="174" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="177" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="176" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="40" fontId="41" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -4447,7 +4436,7 @@
     </xf>
     <xf numFmtId="0" fontId="44" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="39" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="175" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="8" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -4484,7 +4473,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="176" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -4501,7 +4490,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="179" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="178" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
@@ -4547,7 +4536,7 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="180" fontId="46" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="179" fontId="46" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -4562,13 +4551,13 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="175" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="175" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="181" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="180" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -4584,53 +4573,53 @@
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="182" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="181" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="182" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="182" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="182" fontId="3" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="182" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="3" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="181" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="182" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="182" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="182" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="182" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="182" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="181" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="182" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="182" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="182" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="182" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="182" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="3" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -4647,7 +4636,7 @@
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -4660,21 +4649,21 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="182" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="176" fontId="25" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="25" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="25" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="182" fontId="32" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="32" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
@@ -4684,14 +4673,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="182" fontId="24" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="24" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="175" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="174" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="40" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -4700,8 +4689,8 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="10" fontId="29" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="175" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="175" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="174" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="29" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="51" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4713,7 +4702,7 @@
     </xf>
     <xf numFmtId="39" fontId="24" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="39" fontId="42" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="175" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="174" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -4721,7 +4710,7 @@
     <xf numFmtId="9" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="179" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4760,7 +4749,7 @@
     <xf numFmtId="4" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="166" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4774,39 +4763,39 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="64" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="64" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="64" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="175" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="175" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="10" fontId="56" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="66" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="174" fontId="67" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="173" fontId="67" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="182" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="181" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="37" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="182" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="10" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="181" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="180" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -4817,7 +4806,7 @@
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="10" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="167" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -4828,10 +4817,10 @@
     <xf numFmtId="9" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="179" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="182" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="181" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="10" fontId="60" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4840,7 +4829,7 @@
     <xf numFmtId="10" fontId="56" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="56" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="56" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="39" fontId="54" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4853,7 +4842,7 @@
     <xf numFmtId="10" fontId="56" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="56" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="56" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="10" fontId="54" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4862,8 +4851,8 @@
     <xf numFmtId="40" fontId="65" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="176" fontId="56" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="177" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="175" fontId="56" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="176" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -4871,10 +4860,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="39" fontId="54" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="175" fontId="65" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="174" fontId="65" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="54" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="68" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="10" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4883,10 +4872,10 @@
     <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="178" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="69" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4903,16 +4892,16 @@
     <xf numFmtId="4" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="178" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4933,7 +4922,7 @@
     <xf numFmtId="0" fontId="59" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="56" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="56" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4951,7 +4940,7 @@
     <xf numFmtId="40" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="176" fontId="70" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="70" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="10" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -4961,10 +4950,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="174" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="173" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="182" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -4979,7 +4968,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="168" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="10" fontId="71" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4993,34 +4982,34 @@
     <xf numFmtId="10" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="182" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5030,6 +5019,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5039,21 +5037,12 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
     <cellStyle name="常规 2 2" xfId="1" xr:uid="{A35F4541-DCCE-4554-A311-39480A36979A}"/>
   </cellStyles>
   <dxfs count="7">
@@ -5335,7 +5324,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:I167"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="32.6640625" style="1" customWidth="1"/>
@@ -5344,7 +5333,7 @@
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:9" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" ht="13.9">
       <c r="A2" s="200" t="s">
         <v>225</v>
       </c>
@@ -5357,7 +5346,7 @@
       <c r="H2" s="21"/>
       <c r="I2" s="21"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:9">
       <c r="E3" s="428" t="s">
         <v>535</v>
       </c>
@@ -5365,7 +5354,7 @@
         <v>46066</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="14" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:9" ht="12.4">
       <c r="B4" s="421" t="s">
         <v>530</v>
       </c>
@@ -5379,7 +5368,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:9">
       <c r="B5" s="1" t="s">
         <v>347</v>
       </c>
@@ -5393,7 +5382,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:9">
       <c r="B6" s="2" t="s">
         <v>53</v>
       </c>
@@ -5403,7 +5392,7 @@
       <c r="D6" s="45"/>
       <c r="E6" s="45"/>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:9">
       <c r="B7" s="1" t="s">
         <v>349</v>
       </c>
@@ -5413,16 +5402,16 @@
       <c r="D7" s="45"/>
       <c r="E7" s="45"/>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:9">
       <c r="B8" s="4" t="s">
         <v>348</v>
       </c>
       <c r="C8" s="47">
-        <v>106.06</v>
+        <v>104.05</v>
       </c>
       <c r="E8" s="32"/>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:9">
       <c r="B9" s="4" t="s">
         <v>344</v>
       </c>
@@ -5430,43 +5419,43 @@
         <v>3881608005</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:9">
       <c r="B10" s="4" t="s">
         <v>350</v>
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>411683.34501029999</v>
+        <v>403881.31292025</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>525</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.10787497156703298</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.15">
+        <v>0.11513532579667529</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
       <c r="D11" s="5"/>
       <c r="E11" s="5"/>
     </row>
-    <row r="12" spans="1:9" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B12" s="462" t="s">
+    <row r="12" spans="1:9" ht="24.5" customHeight="1">
+      <c r="B12" s="460" t="s">
         <v>353</v>
       </c>
-      <c r="C12" s="462"/>
-      <c r="D12" s="462"/>
-      <c r="E12" s="462"/>
-      <c r="F12" s="462"/>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="C12" s="460"/>
+      <c r="D12" s="460"/>
+      <c r="E12" s="460"/>
+      <c r="F12" s="460"/>
+    </row>
+    <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
         <f>Scenarios!B39&amp;" Valuation Conclusion"</f>
         <v>2-stage DCF Valuation Conclusion</v>
       </c>
       <c r="C14" s="43"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:9">
       <c r="B15" s="1" t="s">
         <v>318</v>
       </c>
@@ -5481,7 +5470,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:9">
       <c r="B16" s="1" t="s">
         <v>319</v>
       </c>
@@ -5495,7 +5484,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:6">
       <c r="B17" s="1" t="s">
         <v>529</v>
       </c>
@@ -5509,7 +5498,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:6">
       <c r="B18" s="1" t="str">
         <f>"Expected Equity Value ("&amp;C7&amp;") :"</f>
         <v>Expected Equity Value (CNY) :</v>
@@ -5525,7 +5514,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:6">
       <c r="B19" s="2" t="s">
         <v>275</v>
       </c>
@@ -5541,11 +5530,11 @@
         <v>46081</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:6">
       <c r="D20" s="5"/>
       <c r="E20" s="5"/>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:6">
       <c r="B21" s="42" t="s">
         <v>402</v>
       </c>
@@ -5560,7 +5549,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:6">
       <c r="B22" s="1" t="s">
         <v>311</v>
       </c>
@@ -5575,7 +5564,7 @@
         <v>0.32950289523458665</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:6">
       <c r="B23" s="1" t="s">
         <v>312</v>
       </c>
@@ -5590,7 +5579,7 @@
         <v>0.22621703288100403</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:6">
       <c r="B24" s="1" t="s">
         <v>314</v>
       </c>
@@ -5605,7 +5594,7 @@
         <v>8.6999999999999994E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:6">
       <c r="B25" s="1" t="s">
         <v>313</v>
       </c>
@@ -5620,11 +5609,11 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:6">
       <c r="D26" s="5"/>
       <c r="E26" s="5"/>
     </row>
-    <row r="27" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" ht="13.9">
       <c r="A27" s="200" t="s">
         <v>280</v>
       </c>
@@ -5634,25 +5623,25 @@
       <c r="E27" s="34"/>
       <c r="F27" s="34"/>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B29" s="462" t="s">
+    <row r="29" spans="1:6">
+      <c r="B29" s="460" t="s">
         <v>354</v>
       </c>
-      <c r="C29" s="462"/>
-      <c r="D29" s="462"/>
-      <c r="E29" s="462"/>
-      <c r="F29" s="462"/>
-    </row>
-    <row r="30" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B30" s="466" t="s">
+      <c r="C29" s="460"/>
+      <c r="D29" s="460"/>
+      <c r="E29" s="460"/>
+      <c r="F29" s="460"/>
+    </row>
+    <row r="30" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B30" s="462" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="466"/>
-      <c r="D30" s="466"/>
-      <c r="E30" s="466"/>
-      <c r="F30" s="466"/>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C30" s="462"/>
+      <c r="D30" s="462"/>
+      <c r="E30" s="462"/>
+      <c r="F30" s="462"/>
+    </row>
+    <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
         <v>195</v>
       </c>
@@ -5661,16 +5650,16 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B33" s="463" t="s">
+    <row r="33" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B33" s="461" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="463"/>
-      <c r="D33" s="463"/>
-      <c r="E33" s="463"/>
-      <c r="F33" s="463"/>
-    </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C33" s="461"/>
+      <c r="D33" s="461"/>
+      <c r="E33" s="461"/>
+      <c r="F33" s="461"/>
+    </row>
+    <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
         <v>197</v>
       </c>
@@ -5683,20 +5672,20 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="35" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:6">
       <c r="B35" s="44"/>
       <c r="C35" s="73"/>
     </row>
-    <row r="36" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B36" s="463" t="s">
+    <row r="36" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B36" s="461" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="463"/>
-      <c r="D36" s="463"/>
-      <c r="E36" s="463"/>
-      <c r="F36" s="463"/>
-    </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C36" s="461"/>
+      <c r="D36" s="461"/>
+      <c r="E36" s="461"/>
+      <c r="F36" s="461"/>
+    </row>
+    <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
         <v>199</v>
       </c>
@@ -5709,7 +5698,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="38" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:6">
       <c r="B38" s="49" t="s">
         <v>200</v>
       </c>
@@ -5722,16 +5711,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="40" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B40" s="463" t="s">
+    <row r="40" spans="2:6">
+      <c r="B40" s="461" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="463"/>
-      <c r="D40" s="463"/>
-      <c r="E40" s="463"/>
-      <c r="F40" s="463"/>
-    </row>
-    <row r="41" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C40" s="461"/>
+      <c r="D40" s="461"/>
+      <c r="E40" s="461"/>
+      <c r="F40" s="461"/>
+    </row>
+    <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
         <v>202</v>
       </c>
@@ -5744,16 +5733,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="43" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B43" s="463" t="s">
+    <row r="43" spans="2:6">
+      <c r="B43" s="461" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="463"/>
-      <c r="D43" s="463"/>
-      <c r="E43" s="463"/>
-      <c r="F43" s="463"/>
-    </row>
-    <row r="44" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C43" s="461"/>
+      <c r="D43" s="461"/>
+      <c r="E43" s="461"/>
+      <c r="F43" s="461"/>
+    </row>
+    <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
         <v>267</v>
       </c>
@@ -5768,7 +5757,7 @@
       <c r="E44" s="244"/>
       <c r="F44" s="244"/>
     </row>
-    <row r="45" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:6">
       <c r="B45" s="44" t="s">
         <v>268</v>
       </c>
@@ -5783,7 +5772,7 @@
       <c r="E45" s="244"/>
       <c r="F45" s="244"/>
     </row>
-    <row r="46" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:6">
       <c r="B46" s="44" t="s">
         <v>203</v>
       </c>
@@ -5796,12 +5785,12 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="48" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:6">
       <c r="B48" s="1" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="49" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="49" spans="2:6">
       <c r="B49" s="44" t="s">
         <v>223</v>
       </c>
@@ -5814,16 +5803,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="51" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B51" s="463" t="s">
+    <row r="51" spans="2:6">
+      <c r="B51" s="461" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="463"/>
-      <c r="D51" s="463"/>
-      <c r="E51" s="463"/>
-      <c r="F51" s="463"/>
-    </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C51" s="461"/>
+      <c r="D51" s="461"/>
+      <c r="E51" s="461"/>
+      <c r="F51" s="461"/>
+    </row>
+    <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
         <v>204</v>
       </c>
@@ -5836,8 +5825,8 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="54" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B54" s="463" t="s">
+    <row r="54" spans="2:6">
+      <c r="B54" s="461" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="464"/>
@@ -5845,7 +5834,7 @@
       <c r="E54" s="464"/>
       <c r="F54" s="464"/>
     </row>
-    <row r="55" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:6">
       <c r="B55" s="44" t="s">
         <v>207</v>
       </c>
@@ -5858,25 +5847,25 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="57" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B57" s="462" t="s">
+    <row r="57" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B57" s="460" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="462"/>
-      <c r="D57" s="462"/>
-      <c r="E57" s="462"/>
-      <c r="F57" s="462"/>
-    </row>
-    <row r="58" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B58" s="462" t="s">
+      <c r="C57" s="460"/>
+      <c r="D57" s="460"/>
+      <c r="E57" s="460"/>
+      <c r="F57" s="460"/>
+    </row>
+    <row r="58" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B58" s="460" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="462"/>
-      <c r="D58" s="462"/>
-      <c r="E58" s="462"/>
-      <c r="F58" s="462"/>
-    </row>
-    <row r="60" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C58" s="460"/>
+      <c r="D58" s="460"/>
+      <c r="E58" s="460"/>
+      <c r="F58" s="460"/>
+    </row>
+    <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
         <v>227</v>
       </c>
@@ -5889,7 +5878,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="61" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="61" spans="2:6">
       <c r="B61" s="44" t="s">
         <v>213</v>
       </c>
@@ -5902,23 +5891,23 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="62" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:6">
       <c r="B62" s="204" t="s">
         <v>302</v>
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>7.2391319447967964E-2</v>
+        <v>7.3789748588673543E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
-    <row r="63" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="63" spans="2:6">
       <c r="B63" s="204" t="s">
         <v>330</v>
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>2.6891382236469922E-2</v>
+        <v>2.741086016338299E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>321</v>
@@ -5928,7 +5917,7 @@
         <v>0.4127471888056104</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:6">
       <c r="B65" s="192" t="s">
         <v>323</v>
       </c>
@@ -5939,7 +5928,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:6">
       <c r="B66" s="44" t="s">
         <v>324</v>
       </c>
@@ -5952,7 +5941,7 @@
         <v>0.26898198471339402</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:6">
       <c r="B67" s="229" t="str">
         <f>Normalized_FCF!B116</f>
         <v>Pre-tax Profit/Sales</v>
@@ -5966,7 +5955,7 @@
         <v>0.43474742930380028</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:6">
       <c r="B68" s="229" t="str">
         <f>Normalized_FCF!B117</f>
         <v>Sales/Total Assets</v>
@@ -5980,7 +5969,7 @@
         <v>0.4610552539366265</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:6">
       <c r="B69" s="229" t="str">
         <f>Normalized_FCF!B118</f>
         <v>Total Assets/Equity</v>
@@ -5994,7 +5983,7 @@
         <v>1.3419403008261008</v>
       </c>
     </row>
-    <row r="71" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:6" ht="13.9">
       <c r="A71" s="200" t="s">
         <v>475</v>
       </c>
@@ -6004,45 +5993,45 @@
       <c r="E71" s="34"/>
       <c r="F71" s="34"/>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:6">
       <c r="A72" s="191"/>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="462" t="s">
+      <c r="B73" s="460" t="s">
         <v>476</v>
       </c>
-      <c r="C73" s="462"/>
-      <c r="D73" s="462"/>
-      <c r="E73" s="462"/>
-      <c r="F73" s="462"/>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C73" s="460"/>
+      <c r="D73" s="460"/>
+      <c r="E73" s="460"/>
+      <c r="F73" s="460"/>
+    </row>
+    <row r="74" spans="1:6">
       <c r="A74" s="191"/>
       <c r="B74" s="1" t="s">
         <v>463</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:6">
       <c r="A75" s="191"/>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:6">
       <c r="A76" s="191"/>
       <c r="B76" s="192" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="462" t="s">
+      <c r="B77" s="460" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="462"/>
-      <c r="D77" s="462"/>
-      <c r="E77" s="462"/>
-      <c r="F77" s="462"/>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C77" s="460"/>
+      <c r="D77" s="460"/>
+      <c r="E77" s="460"/>
+      <c r="F77" s="460"/>
+    </row>
+    <row r="78" spans="1:6">
       <c r="A78" s="191"/>
       <c r="B78" s="1" t="s">
         <v>215</v>
@@ -6056,7 +6045,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:6">
       <c r="A79" s="191"/>
       <c r="B79" s="44" t="s">
         <v>234</v>
@@ -6070,7 +6059,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:6">
       <c r="A80" s="191"/>
       <c r="B80" s="229" t="s">
         <v>308</v>
@@ -6080,7 +6069,7 @@
         <v>1.4942693904035366E-3</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:6">
       <c r="A81" s="191"/>
       <c r="B81" s="229" t="s">
         <v>310</v>
@@ -6090,16 +6079,16 @@
         <v>5.1971735080735887E-3</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:6">
       <c r="A82" s="191"/>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:6">
       <c r="A83" s="191"/>
       <c r="B83" s="1" t="s">
         <v>464</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:6">
       <c r="A84" s="191"/>
       <c r="B84" s="1" t="s">
         <v>224</v>
@@ -6113,7 +6102,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:6">
       <c r="A85" s="191"/>
       <c r="B85" s="229" t="s">
         <v>222</v>
@@ -6127,7 +6116,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:6">
       <c r="A86" s="191"/>
       <c r="B86" s="44" t="s">
         <v>235</v>
@@ -6141,16 +6130,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:6">
       <c r="A87" s="191"/>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:6">
       <c r="A88" s="191"/>
       <c r="B88" s="1" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:6">
       <c r="A89" s="191"/>
       <c r="B89" s="1" t="s">
         <v>217</v>
@@ -6164,7 +6153,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:6">
       <c r="A90" s="191"/>
       <c r="B90" s="44" t="s">
         <v>236</v>
@@ -6178,10 +6167,10 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:6">
       <c r="A91" s="191"/>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:6">
       <c r="A92" s="191"/>
       <c r="B92" s="44" t="s">
         <v>467</v>
@@ -6195,7 +6184,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="94" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:6" ht="13.9">
       <c r="A94" s="200" t="s">
         <v>468</v>
       </c>
@@ -6205,42 +6194,42 @@
       <c r="E94" s="34"/>
       <c r="F94" s="34"/>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:6">
       <c r="A95" s="191"/>
     </row>
-    <row r="96" spans="1:6" ht="11.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B96" s="462" t="s">
+    <row r="96" spans="1:6" ht="11.75" customHeight="1">
+      <c r="B96" s="460" t="s">
         <v>483</v>
       </c>
-      <c r="C96" s="462"/>
-      <c r="D96" s="462"/>
-      <c r="E96" s="462"/>
-      <c r="F96" s="462"/>
-    </row>
-    <row r="97" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B97" s="466" t="s">
+      <c r="C96" s="460"/>
+      <c r="D96" s="460"/>
+      <c r="E96" s="460"/>
+      <c r="F96" s="460"/>
+    </row>
+    <row r="97" spans="2:6">
+      <c r="B97" s="462" t="s">
         <v>482</v>
       </c>
-      <c r="C97" s="466"/>
-      <c r="D97" s="466"/>
-      <c r="E97" s="466"/>
-      <c r="F97" s="466"/>
-    </row>
-    <row r="98" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B98" s="466" t="s">
+      <c r="C97" s="462"/>
+      <c r="D97" s="462"/>
+      <c r="E97" s="462"/>
+      <c r="F97" s="462"/>
+    </row>
+    <row r="98" spans="2:6">
+      <c r="B98" s="462" t="s">
         <v>481</v>
       </c>
-      <c r="C98" s="466"/>
-      <c r="D98" s="466"/>
-      <c r="E98" s="466"/>
-      <c r="F98" s="466"/>
-    </row>
-    <row r="100" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C98" s="462"/>
+      <c r="D98" s="462"/>
+      <c r="E98" s="462"/>
+      <c r="F98" s="462"/>
+    </row>
+    <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="101" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="101" spans="2:6">
       <c r="B101" s="49" t="s">
         <v>465</v>
       </c>
@@ -6249,7 +6238,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="102" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="102" spans="2:6">
       <c r="B102" s="229" t="s">
         <v>317</v>
       </c>
@@ -6258,7 +6247,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="103" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="103" spans="2:6">
       <c r="B103" s="229" t="s">
         <v>316</v>
       </c>
@@ -6267,7 +6256,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="104" spans="2:6">
       <c r="B104" s="44" t="s">
         <v>214</v>
       </c>
@@ -6276,36 +6265,36 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="106" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="106" spans="2:6">
       <c r="B106" s="250" t="s">
         <v>281</v>
       </c>
       <c r="C106" s="116"/>
     </row>
-    <row r="107" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B107" s="462" t="s">
+    <row r="107" spans="2:6">
+      <c r="B107" s="460" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="462"/>
-      <c r="D107" s="462"/>
-      <c r="E107" s="462"/>
-      <c r="F107" s="462"/>
-    </row>
-    <row r="108" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B108" s="462" t="s">
+      <c r="C107" s="460"/>
+      <c r="D107" s="460"/>
+      <c r="E107" s="460"/>
+      <c r="F107" s="460"/>
+    </row>
+    <row r="108" spans="2:6">
+      <c r="B108" s="460" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="462"/>
-      <c r="D108" s="462"/>
-      <c r="E108" s="462"/>
-      <c r="F108" s="462"/>
-    </row>
-    <row r="110" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C108" s="460"/>
+      <c r="D108" s="460"/>
+      <c r="E108" s="460"/>
+      <c r="F108" s="460"/>
+    </row>
+    <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
         <v>485</v>
       </c>
     </row>
-    <row r="111" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="111" spans="2:6">
       <c r="B111" s="49" t="s">
         <v>466</v>
       </c>
@@ -6318,7 +6307,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="112" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="112" spans="2:6">
       <c r="B112" s="44" t="s">
         <v>322</v>
       </c>
@@ -6331,21 +6320,21 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="114" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B114" s="462" t="s">
+    <row r="114" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B114" s="460" t="s">
         <v>489</v>
       </c>
-      <c r="C114" s="462"/>
-      <c r="D114" s="462"/>
-      <c r="E114" s="462"/>
-      <c r="F114" s="462"/>
-    </row>
-    <row r="116" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C114" s="460"/>
+      <c r="D114" s="460"/>
+      <c r="E114" s="460"/>
+      <c r="F114" s="460"/>
+    </row>
+    <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
         <v>486</v>
       </c>
     </row>
-    <row r="117" spans="2:6" ht="14" x14ac:dyDescent="0.2">
+    <row r="117" spans="2:6" ht="12.4">
       <c r="B117" s="342" t="s">
         <v>101</v>
       </c>
@@ -6362,7 +6351,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="118" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="118" spans="2:6">
       <c r="B118" s="205" t="str">
         <f>DCF!B90&amp;" ("&amp;DCF!D90&amp;"yrs)"</f>
         <v>Snowball Scenario (5yrs)</v>
@@ -6384,7 +6373,7 @@
         <v>-8.8861014087690589E-3</v>
       </c>
     </row>
-    <row r="119" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="119" spans="2:6">
       <c r="B119" s="205" t="str">
         <f>DCF!B91&amp;" ("&amp;DCF!D91&amp;"yrs)"</f>
         <v>Optimistic (5yrs)</v>
@@ -6406,7 +6395,7 @@
         <v>1.3678062151602804E-2</v>
       </c>
     </row>
-    <row r="120" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="120" spans="2:6">
       <c r="B120" s="205" t="str">
         <f>DCF!B92&amp;" ("&amp;DCF!D92&amp;"yrs)"</f>
         <v>Base (5yrs)</v>
@@ -6428,7 +6417,7 @@
         <v>2.5106272015644755E-2</v>
       </c>
     </row>
-    <row r="121" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="121" spans="2:6">
       <c r="B121" s="205" t="str">
         <f>DCF!B93&amp;" ("&amp;DCF!D93&amp;"yrs)"</f>
         <v>Pessimistic (5yrs)</v>
@@ -6450,7 +6439,7 @@
         <v>3.6626507210125503E-2</v>
       </c>
     </row>
-    <row r="122" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="122" spans="2:6">
       <c r="B122" s="205" t="str">
         <f>DCF!B94&amp;" ("&amp;DCF!D94&amp;"yrs)"</f>
         <v>Devil's advocate (5yrs)</v>
@@ -6472,16 +6461,16 @@
         <v>4.823427764461069E-2</v>
       </c>
     </row>
-    <row r="124" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B124" s="463" t="s">
+    <row r="124" spans="2:6">
+      <c r="B124" s="461" t="s">
         <v>355</v>
       </c>
-      <c r="C124" s="463"/>
-      <c r="D124" s="463"/>
-      <c r="E124" s="463"/>
-      <c r="F124" s="463"/>
-    </row>
-    <row r="125" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C124" s="461"/>
+      <c r="D124" s="461"/>
+      <c r="E124" s="461"/>
+      <c r="F124" s="461"/>
+    </row>
+    <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
         <v>218</v>
       </c>
@@ -6494,7 +6483,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="127" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="127" spans="2:6" ht="24.5" customHeight="1">
       <c r="B127" s="465" t="s">
         <v>356</v>
       </c>
@@ -6503,7 +6492,7 @@
       <c r="E127" s="465"/>
       <c r="F127" s="465"/>
     </row>
-    <row r="129" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="200" t="s">
         <v>472</v>
       </c>
@@ -6513,30 +6502,30 @@
       <c r="E129" s="34"/>
       <c r="F129" s="34"/>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B131" s="467" t="s">
+    <row r="131" spans="1:6">
+      <c r="B131" s="463" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="467"/>
-      <c r="D131" s="467"/>
-      <c r="E131" s="467"/>
-      <c r="F131" s="467"/>
-    </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B132" s="462" t="s">
+      <c r="C131" s="463"/>
+      <c r="D131" s="463"/>
+      <c r="E131" s="463"/>
+      <c r="F131" s="463"/>
+    </row>
+    <row r="132" spans="1:6">
+      <c r="B132" s="460" t="s">
         <v>357</v>
       </c>
-      <c r="C132" s="462"/>
-      <c r="D132" s="462"/>
-      <c r="E132" s="462"/>
-      <c r="F132" s="462"/>
-    </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C132" s="460"/>
+      <c r="D132" s="460"/>
+      <c r="E132" s="460"/>
+      <c r="F132" s="460"/>
+    </row>
+    <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="135" spans="1:6">
       <c r="B135" s="1" t="s">
         <v>221</v>
       </c>
@@ -6545,7 +6534,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="136" spans="1:6">
       <c r="B136" s="194" t="s">
         <v>220</v>
       </c>
@@ -6558,14 +6547,14 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="138" spans="1:6">
       <c r="B138" s="192" t="s">
         <v>492</v>
       </c>
       <c r="C138" s="214"/>
       <c r="D138" s="215"/>
     </row>
-    <row r="139" spans="1:6" ht="14" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:6" ht="12.4">
       <c r="B139" s="340" t="s">
         <v>460</v>
       </c>
@@ -6584,7 +6573,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="140" spans="1:6">
       <c r="B140" s="336" t="s">
         <v>311</v>
       </c>
@@ -6605,7 +6594,7 @@
         <v>0.32950289523458665</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="141" spans="1:6">
       <c r="B141" s="336" t="s">
         <v>312</v>
       </c>
@@ -6626,14 +6615,14 @@
         <v>0.22621703288100403</v>
       </c>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="142" spans="1:6">
       <c r="B142" s="194"/>
       <c r="C142" s="194"/>
       <c r="D142" s="194"/>
       <c r="E142" s="194"/>
       <c r="F142" s="194"/>
     </row>
-    <row r="143" spans="1:6" ht="14" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:6" ht="12.4">
       <c r="B143" s="340" t="s">
         <v>461</v>
       </c>
@@ -6652,7 +6641,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="144" spans="1:6">
       <c r="B144" s="336" t="s">
         <v>314</v>
       </c>
@@ -6673,7 +6662,7 @@
         <v>8.6999999999999994E-2</v>
       </c>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="145" spans="1:6">
       <c r="B145" s="336" t="s">
         <v>313</v>
       </c>
@@ -6694,7 +6683,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="147" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:6" ht="13.9">
       <c r="A147" s="200" t="s">
         <v>473</v>
       </c>
@@ -6704,21 +6693,21 @@
       <c r="E147" s="34"/>
       <c r="F147" s="34"/>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B149" s="461" t="s">
+    <row r="149" spans="1:6">
+      <c r="B149" s="467" t="s">
         <v>358</v>
       </c>
-      <c r="C149" s="462"/>
-      <c r="D149" s="462"/>
-      <c r="E149" s="462"/>
-      <c r="F149" s="462"/>
-    </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C149" s="460"/>
+      <c r="D149" s="460"/>
+      <c r="E149" s="460"/>
+      <c r="F149" s="460"/>
+    </row>
+    <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="152" spans="1:6">
       <c r="B152" s="464" t="s">
         <v>293</v>
       </c>
@@ -6727,80 +6716,92 @@
       <c r="E152" s="464"/>
       <c r="F152" s="464"/>
     </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="153" spans="1:6">
       <c r="B153" s="196" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="154" spans="1:6">
       <c r="B154" s="196" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="155" spans="1:6">
       <c r="B155" s="196" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="157" spans="1:6">
       <c r="B157" s="1" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="158" spans="1:6" ht="34.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B158" s="463" t="s">
+    <row r="158" spans="1:6" ht="34.25" customHeight="1">
+      <c r="B158" s="461" t="s">
         <v>436</v>
       </c>
-      <c r="C158" s="463"/>
-      <c r="D158" s="463"/>
-      <c r="E158" s="463"/>
-      <c r="F158" s="463"/>
-    </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C158" s="461"/>
+      <c r="D158" s="461"/>
+      <c r="E158" s="461"/>
+      <c r="F158" s="461"/>
+    </row>
+    <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="161" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B161" s="460" t="s">
+    <row r="161" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B161" s="466" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="460"/>
-      <c r="D161" s="460"/>
-      <c r="E161" s="460"/>
-      <c r="F161" s="460"/>
-    </row>
-    <row r="162" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B162" s="460" t="s">
+      <c r="C161" s="466"/>
+      <c r="D161" s="466"/>
+      <c r="E161" s="466"/>
+      <c r="F161" s="466"/>
+    </row>
+    <row r="162" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B162" s="466" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="460"/>
-      <c r="D162" s="460"/>
-      <c r="E162" s="460"/>
-      <c r="F162" s="460"/>
-    </row>
-    <row r="164" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C162" s="466"/>
+      <c r="D162" s="466"/>
+      <c r="E162" s="466"/>
+      <c r="F162" s="466"/>
+    </row>
+    <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="165" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="165" spans="2:6">
       <c r="B165" s="196" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="166" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="166" spans="2:6">
       <c r="B166" s="196" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="167" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="167" spans="2:6">
       <c r="B167" s="196" t="s">
         <v>300</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6817,18 +6818,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -6856,15 +6845,15 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:M80"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="3" style="1" customWidth="1"/>
     <col min="2" max="2" width="27.33203125" style="1" customWidth="1"/>
     <col min="3" max="13" width="20.6640625" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.83203125" style="1"/>
+    <col min="14" max="16384" width="8.796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="1" spans="2:13">
       <c r="B1" s="87" t="str">
         <f>Thesis!E17</f>
         <v>CNY</v>
@@ -6913,7 +6902,7 @@
         <v>42004</v>
       </c>
     </row>
-    <row r="2" spans="2:13" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:13" ht="13.9">
       <c r="B2" s="34" t="s">
         <v>93</v>
       </c>
@@ -6929,7 +6918,7 @@
       <c r="L2" s="35"/>
       <c r="M2" s="35"/>
     </row>
-    <row r="3" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:13">
       <c r="B3" s="16" t="s">
         <v>25</v>
       </c>
@@ -6937,7 +6926,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:13">
       <c r="B4" s="31" t="s">
         <v>0</v>
       </c>
@@ -6957,7 +6946,7 @@
       <c r="L4" s="287"/>
       <c r="M4" s="287"/>
     </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:13">
       <c r="B5" s="38" t="s">
         <v>40</v>
       </c>
@@ -6979,7 +6968,7 @@
       <c r="L5" s="287"/>
       <c r="M5" s="287"/>
     </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:13">
       <c r="B6" s="38" t="s">
         <v>51</v>
       </c>
@@ -7001,7 +6990,7 @@
       <c r="L6" s="287"/>
       <c r="M6" s="287"/>
     </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:13">
       <c r="B7" s="66" t="s">
         <v>58</v>
       </c>
@@ -7021,7 +7010,7 @@
       <c r="L7" s="288"/>
       <c r="M7" s="288"/>
     </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:13">
       <c r="B8" s="38" t="s">
         <v>46</v>
       </c>
@@ -7041,7 +7030,7 @@
       <c r="L8" s="287"/>
       <c r="M8" s="287"/>
     </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:13">
       <c r="B9" s="38" t="s">
         <v>134</v>
       </c>
@@ -7057,7 +7046,7 @@
       <c r="L9" s="287"/>
       <c r="M9" s="287"/>
     </row>
-    <row r="10" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:13">
       <c r="B10" s="38" t="s">
         <v>138</v>
       </c>
@@ -7073,7 +7062,7 @@
       <c r="L10" s="287"/>
       <c r="M10" s="287"/>
     </row>
-    <row r="11" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:13">
       <c r="B11" s="38" t="s">
         <v>133</v>
       </c>
@@ -7089,7 +7078,7 @@
       <c r="L11" s="287"/>
       <c r="M11" s="287"/>
     </row>
-    <row r="12" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:13">
       <c r="B12" s="38" t="s">
         <v>37</v>
       </c>
@@ -7110,7 +7099,7 @@
       <c r="L12" s="287"/>
       <c r="M12" s="287"/>
     </row>
-    <row r="13" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:13">
       <c r="B13" s="38" t="s">
         <v>64</v>
       </c>
@@ -7130,7 +7119,7 @@
       <c r="L13" s="287"/>
       <c r="M13" s="287"/>
     </row>
-    <row r="14" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:13">
       <c r="B14" s="38" t="s">
         <v>47</v>
       </c>
@@ -7150,7 +7139,7 @@
       <c r="L14" s="287"/>
       <c r="M14" s="287"/>
     </row>
-    <row r="15" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="15" spans="2:13">
       <c r="B15" s="41" t="s">
         <v>39</v>
       </c>
@@ -7170,7 +7159,7 @@
       <c r="L15" s="289"/>
       <c r="M15" s="289"/>
     </row>
-    <row r="16" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:13">
       <c r="B16" s="27" t="s">
         <v>41</v>
       </c>
@@ -7190,13 +7179,13 @@
       <c r="L16" s="287"/>
       <c r="M16" s="287"/>
     </row>
-    <row r="18" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:13">
       <c r="B18" s="16" t="s">
         <v>48</v>
       </c>
       <c r="C18" s="9"/>
     </row>
-    <row r="19" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:13">
       <c r="B19" s="26" t="s">
         <v>44</v>
       </c>
@@ -7212,7 +7201,7 @@
       <c r="L19" s="287"/>
       <c r="M19" s="287"/>
     </row>
-    <row r="20" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:13">
       <c r="B20" s="26" t="s">
         <v>50</v>
       </c>
@@ -7228,7 +7217,7 @@
       <c r="L20" s="287"/>
       <c r="M20" s="287"/>
     </row>
-    <row r="21" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:13">
       <c r="B21" s="26" t="s">
         <v>49</v>
       </c>
@@ -7244,7 +7233,7 @@
       <c r="L21" s="287"/>
       <c r="M21" s="287"/>
     </row>
-    <row r="22" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:13">
       <c r="B22" s="26" t="s">
         <v>286</v>
       </c>
@@ -7264,7 +7253,7 @@
       <c r="L22" s="287"/>
       <c r="M22" s="287"/>
     </row>
-    <row r="23" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:13">
       <c r="B23" s="26" t="s">
         <v>288</v>
       </c>
@@ -7284,7 +7273,7 @@
       <c r="L23" s="287"/>
       <c r="M23" s="287"/>
     </row>
-    <row r="24" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:13">
       <c r="B24" s="26" t="s">
         <v>287</v>
       </c>
@@ -7304,7 +7293,7 @@
       <c r="L24" s="287"/>
       <c r="M24" s="287"/>
     </row>
-    <row r="25" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:13">
       <c r="B25" s="23" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
         <v>Dividend per share (CNY)</v>
@@ -7327,7 +7316,7 @@
       <c r="L25" s="37"/>
       <c r="M25" s="37"/>
     </row>
-    <row r="27" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:13">
       <c r="B27" s="16" t="s">
         <v>26</v>
       </c>
@@ -7335,7 +7324,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="28" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:13">
       <c r="B28" s="25" t="s">
         <v>22</v>
       </c>
@@ -7357,7 +7346,7 @@
       <c r="L28" s="287"/>
       <c r="M28" s="287"/>
     </row>
-    <row r="29" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:13">
       <c r="B29" s="25" t="s">
         <v>30</v>
       </c>
@@ -7378,7 +7367,7 @@
       <c r="L29" s="287"/>
       <c r="M29" s="287"/>
     </row>
-    <row r="30" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:13">
       <c r="B30" s="28" t="s">
         <v>38</v>
       </c>
@@ -7399,7 +7388,7 @@
       <c r="L30" s="289"/>
       <c r="M30" s="289"/>
     </row>
-    <row r="31" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:13">
       <c r="B31" s="28" t="s">
         <v>28</v>
       </c>
@@ -7420,7 +7409,7 @@
       <c r="L31" s="289"/>
       <c r="M31" s="289"/>
     </row>
-    <row r="32" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:13">
       <c r="B32" s="25" t="s">
         <v>143</v>
       </c>
@@ -7441,7 +7430,7 @@
       <c r="L32" s="287"/>
       <c r="M32" s="287"/>
     </row>
-    <row r="34" spans="2:13" ht="16" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:13" ht="13.9">
       <c r="B34" s="34" t="s">
         <v>78</v>
       </c>
@@ -7457,12 +7446,12 @@
       <c r="L34" s="35"/>
       <c r="M34" s="35"/>
     </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:13">
       <c r="B35" s="16" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="36" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:13">
       <c r="B36" s="31" t="s">
         <v>0</v>
       </c>
@@ -7511,7 +7500,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:13">
       <c r="B37" s="38" t="s">
         <v>40</v>
       </c>
@@ -7560,7 +7549,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:13">
       <c r="B38" s="30" t="s">
         <v>55</v>
       </c>
@@ -7609,7 +7598,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:13">
       <c r="B39" s="38" t="s">
         <v>51</v>
       </c>
@@ -7658,7 +7647,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:13">
       <c r="B40" s="66" t="s">
         <v>58</v>
       </c>
@@ -7707,7 +7696,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:13">
       <c r="B41" s="66" t="s">
         <v>61</v>
       </c>
@@ -7756,7 +7745,7 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:13">
       <c r="B42" s="38" t="s">
         <v>46</v>
       </c>
@@ -7805,7 +7794,7 @@
         <v/>
       </c>
     </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="43" spans="2:13">
       <c r="B43" s="41" t="s">
         <v>127</v>
       </c>
@@ -7854,7 +7843,7 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:13">
       <c r="B44" s="41" t="s">
         <v>139</v>
       </c>
@@ -7903,7 +7892,7 @@
         <v/>
       </c>
     </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:13">
       <c r="B45" s="38" t="s">
         <v>65</v>
       </c>
@@ -7952,7 +7941,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:13">
       <c r="B46" s="38" t="s">
         <v>47</v>
       </c>
@@ -8001,7 +7990,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:13">
       <c r="B47" s="41" t="s">
         <v>39</v>
       </c>
@@ -8050,7 +8039,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:13">
       <c r="B48" s="27" t="s">
         <v>41</v>
       </c>
@@ -8099,12 +8088,12 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:13">
       <c r="B50" s="16" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="51" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:13">
       <c r="B51" s="38" t="s">
         <v>37</v>
       </c>
@@ -8153,7 +8142,7 @@
         <v/>
       </c>
     </row>
-    <row r="52" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:13">
       <c r="B52" s="38" t="s">
         <v>64</v>
       </c>
@@ -8202,12 +8191,12 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="54" spans="2:13">
       <c r="B54" s="156" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="55" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:13">
       <c r="B55" s="38" t="s">
         <v>134</v>
       </c>
@@ -8256,7 +8245,7 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:13">
       <c r="B56" s="38" t="s">
         <v>138</v>
       </c>
@@ -8305,7 +8294,7 @@
         <v/>
       </c>
     </row>
-    <row r="57" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="57" spans="2:13">
       <c r="B57" s="38" t="s">
         <v>133</v>
       </c>
@@ -8354,7 +8343,7 @@
         <v/>
       </c>
     </row>
-    <row r="58" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:13">
       <c r="B58" s="38" t="s">
         <v>135</v>
       </c>
@@ -8403,13 +8392,13 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="60" spans="2:13">
       <c r="B60" s="16" t="s">
         <v>48</v>
       </c>
       <c r="C60" s="9"/>
     </row>
-    <row r="61" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="61" spans="2:13">
       <c r="B61" s="26" t="s">
         <v>44</v>
       </c>
@@ -8458,7 +8447,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:13">
       <c r="B62" s="26" t="s">
         <v>50</v>
       </c>
@@ -8507,7 +8496,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="63" spans="2:13">
       <c r="B63" s="26" t="s">
         <v>49</v>
       </c>
@@ -8556,7 +8545,7 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="64" spans="2:13">
       <c r="B64" s="26" t="s">
         <v>305</v>
       </c>
@@ -8605,7 +8594,7 @@
         <v/>
       </c>
     </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="65" spans="2:13">
       <c r="B65" s="23" t="s">
         <v>34</v>
       </c>
@@ -8654,12 +8643,12 @@
         <v/>
       </c>
     </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="67" spans="2:13">
       <c r="B67" s="88" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="68" spans="2:13">
       <c r="B68" s="1" t="str">
         <f>B36</f>
         <v>Sales</v>
@@ -8709,7 +8698,7 @@
         <v/>
       </c>
     </row>
-    <row r="69" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="69" spans="2:13">
       <c r="B69" s="30" t="s">
         <v>55</v>
       </c>
@@ -8758,7 +8747,7 @@
         <v/>
       </c>
     </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="70" spans="2:13">
       <c r="B70" s="77" t="str">
         <f>B43</f>
         <v>Operating EBIT</v>
@@ -8808,7 +8797,7 @@
         <v/>
       </c>
     </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="71" spans="2:13">
       <c r="B71" s="41" t="s">
         <v>139</v>
       </c>
@@ -8857,7 +8846,7 @@
         <v/>
       </c>
     </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="72" spans="2:13">
       <c r="B72" s="77" t="str">
         <f>B47</f>
         <v>Reported Net Income</v>
@@ -8907,7 +8896,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="2:13" ht="16" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:13" ht="13.9">
       <c r="B74" s="34" t="s">
         <v>79</v>
       </c>
@@ -8923,13 +8912,13 @@
       <c r="L74" s="35"/>
       <c r="M74" s="35"/>
     </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="75" spans="2:13">
       <c r="B75" s="16" t="s">
         <v>26</v>
       </c>
       <c r="C75" s="9"/>
     </row>
-    <row r="76" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="76" spans="2:13">
       <c r="B76" s="25" t="s">
         <v>1</v>
       </c>
@@ -8978,7 +8967,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="77" spans="2:13">
       <c r="B77" s="90" t="s">
         <v>82</v>
       </c>
@@ -9012,7 +9001,7 @@
       <c r="L77" s="291"/>
       <c r="M77" s="291"/>
     </row>
-    <row r="78" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="78" spans="2:13">
       <c r="B78" s="90" t="s">
         <v>83</v>
       </c>
@@ -9046,7 +9035,7 @@
       <c r="L78" s="291"/>
       <c r="M78" s="291"/>
     </row>
-    <row r="79" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="79" spans="2:13">
       <c r="B79" s="25" t="s">
         <v>38</v>
       </c>
@@ -9095,7 +9084,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="80" spans="2:13">
       <c r="B80" s="25" t="s">
         <v>28</v>
       </c>
@@ -9176,7 +9165,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:H89"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="2.33203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="34" style="1" bestFit="1" customWidth="1"/>
@@ -9187,7 +9176,7 @@
     <col min="9" max="16384" width="12.33203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="2:8" ht="15" customHeight="1">
       <c r="B1" s="17" t="s">
         <v>35</v>
       </c>
@@ -9203,7 +9192,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="2:8" ht="15" customHeight="1">
       <c r="B2" s="76" t="s">
         <v>131</v>
       </c>
@@ -9214,7 +9203,7 @@
       <c r="G2" s="35"/>
       <c r="H2" s="35"/>
     </row>
-    <row r="3" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:8" ht="15" customHeight="1">
       <c r="B3" s="16" t="s">
         <v>154</v>
       </c>
@@ -9234,7 +9223,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:8" ht="15" customHeight="1">
       <c r="B4" s="4" t="s">
         <v>22</v>
       </c>
@@ -9256,7 +9245,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="5" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:8" ht="15" customHeight="1">
       <c r="B5" s="1" t="s">
         <v>31</v>
       </c>
@@ -9277,7 +9266,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="6" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:8" ht="15" customHeight="1">
       <c r="B6" s="4" t="s">
         <v>8</v>
       </c>
@@ -9298,7 +9287,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="7" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:8" ht="15" customHeight="1">
       <c r="B7" s="1" t="s">
         <v>66</v>
       </c>
@@ -9319,7 +9308,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="8" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:8" ht="15" customHeight="1">
       <c r="B8" s="1" t="s">
         <v>144</v>
       </c>
@@ -9340,7 +9329,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="9" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:8" ht="15" customHeight="1">
       <c r="B9" s="4" t="s">
         <v>23</v>
       </c>
@@ -9361,7 +9350,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="10" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:8" ht="15" customHeight="1">
       <c r="B10" s="4" t="s">
         <v>9</v>
       </c>
@@ -9381,7 +9370,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="11" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:8" ht="15" customHeight="1">
       <c r="B11" s="4" t="s">
         <v>10</v>
       </c>
@@ -9393,7 +9382,7 @@
       </c>
       <c r="H11" s="232"/>
     </row>
-    <row r="12" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:8" ht="15" customHeight="1">
       <c r="B12" s="77" t="s">
         <v>69</v>
       </c>
@@ -9417,12 +9406,12 @@
         <v>133487951707.854</v>
       </c>
     </row>
-    <row r="13" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:8" ht="15" customHeight="1">
       <c r="F13" s="77"/>
       <c r="G13" s="78"/>
       <c r="H13" s="19"/>
     </row>
-    <row r="14" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:8" ht="15" customHeight="1">
       <c r="B14" s="16" t="s">
         <v>153</v>
       </c>
@@ -9442,7 +9431,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="15" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="2:8" ht="15" customHeight="1">
       <c r="B15" s="4" t="s">
         <v>327</v>
       </c>
@@ -9462,7 +9451,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="16" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:8" ht="15" customHeight="1">
       <c r="B16" s="1" t="s">
         <v>32</v>
       </c>
@@ -9482,7 +9471,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="17" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:8" ht="15" customHeight="1">
       <c r="B17" s="1" t="s">
         <v>66</v>
       </c>
@@ -9502,7 +9491,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="18" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:8" ht="15" customHeight="1">
       <c r="B18" s="4" t="s">
         <v>144</v>
       </c>
@@ -9522,7 +9511,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="19" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:8" ht="15" customHeight="1">
       <c r="B19" s="4" t="s">
         <v>24</v>
       </c>
@@ -9543,7 +9532,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="20" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:8" ht="15" customHeight="1">
       <c r="B20" s="4" t="s">
         <v>16</v>
       </c>
@@ -9563,7 +9552,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="21" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:8" ht="15" customHeight="1">
       <c r="B21" s="4" t="s">
         <v>17</v>
       </c>
@@ -9583,7 +9572,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="22" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:8" ht="15" customHeight="1">
       <c r="B22" s="4" t="s">
         <v>18</v>
       </c>
@@ -9595,7 +9584,7 @@
       </c>
       <c r="H22" s="232"/>
     </row>
-    <row r="23" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:8" ht="15" customHeight="1">
       <c r="B23" s="4" t="s">
         <v>19</v>
       </c>
@@ -9608,7 +9597,7 @@
       </c>
       <c r="H23" s="232"/>
     </row>
-    <row r="24" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:8" ht="15" customHeight="1">
       <c r="B24" s="77" t="s">
         <v>70</v>
       </c>
@@ -9632,7 +9621,7 @@
         <v>217300602.50500003</v>
       </c>
     </row>
-    <row r="26" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:8" ht="15" customHeight="1">
       <c r="B26" s="16" t="s">
         <v>169</v>
       </c>
@@ -9649,7 +9638,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="27" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:8" ht="15" customHeight="1">
       <c r="B27" s="4" t="s">
         <v>3</v>
       </c>
@@ -9668,7 +9657,7 @@
         <v>100133635249.52902</v>
       </c>
     </row>
-    <row r="28" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:8" ht="15" customHeight="1">
       <c r="B28" s="4" t="s">
         <v>4</v>
       </c>
@@ -9683,7 +9672,7 @@
       </c>
       <c r="H28" s="170"/>
     </row>
-    <row r="29" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:8" ht="15" customHeight="1">
       <c r="B29" s="4" t="s">
         <v>5</v>
       </c>
@@ -9702,7 +9691,7 @@
         <v>96478905988.149017</v>
       </c>
     </row>
-    <row r="30" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:8" ht="15" customHeight="1">
       <c r="B30" s="2" t="s">
         <v>6</v>
       </c>
@@ -9718,7 +9707,7 @@
       </c>
       <c r="H30" s="170"/>
     </row>
-    <row r="31" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:8" ht="15" customHeight="1">
       <c r="B31" s="77" t="s">
         <v>172</v>
       </c>
@@ -9735,7 +9724,7 @@
       </c>
       <c r="H31" s="170"/>
     </row>
-    <row r="32" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:8" ht="15" customHeight="1">
       <c r="B32" s="4" t="s">
         <v>7</v>
       </c>
@@ -9755,7 +9744,7 @@
         <v>149417879904.20901</v>
       </c>
     </row>
-    <row r="33" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:8" ht="15" customHeight="1">
       <c r="B33" s="80" t="s">
         <v>2</v>
       </c>
@@ -9766,7 +9755,7 @@
       <c r="G33" s="2"/>
       <c r="H33" s="177"/>
     </row>
-    <row r="34" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:8" ht="15" customHeight="1">
       <c r="B34" s="80"/>
       <c r="C34" s="81"/>
       <c r="F34" s="178" t="s">
@@ -9779,7 +9768,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="35" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:8" ht="15" customHeight="1">
       <c r="B35" s="16" t="s">
         <v>170</v>
       </c>
@@ -9798,7 +9787,7 @@
         <v>15712627593.849998</v>
       </c>
     </row>
-    <row r="36" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:8" ht="15" customHeight="1">
       <c r="B36" s="4" t="s">
         <v>11</v>
       </c>
@@ -9814,7 +9803,7 @@
       </c>
       <c r="H36" s="177"/>
     </row>
-    <row r="37" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:8" ht="15" customHeight="1">
       <c r="B37" s="4" t="s">
         <v>12</v>
       </c>
@@ -9830,7 +9819,7 @@
       </c>
       <c r="H37" s="177"/>
     </row>
-    <row r="38" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:8" ht="15" customHeight="1">
       <c r="B38" s="4" t="s">
         <v>13</v>
       </c>
@@ -9846,7 +9835,7 @@
       </c>
       <c r="H38" s="177"/>
     </row>
-    <row r="39" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:8" ht="15" customHeight="1">
       <c r="B39" s="2" t="s">
         <v>14</v>
       </c>
@@ -9865,7 +9854,7 @@
         <v>1425969106.7839999</v>
       </c>
     </row>
-    <row r="40" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:8" ht="15" customHeight="1">
       <c r="B40" s="77" t="s">
         <v>173</v>
       </c>
@@ -9885,7 +9874,7 @@
         <v>133705252310.35901</v>
       </c>
     </row>
-    <row r="41" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:8" ht="15" customHeight="1">
       <c r="B41" s="4" t="s">
         <v>15</v>
       </c>
@@ -9905,7 +9894,7 @@
         <v>133487951707.854</v>
       </c>
     </row>
-    <row r="42" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:8" ht="15" customHeight="1">
       <c r="B42" s="80" t="s">
         <v>20</v>
       </c>
@@ -9924,7 +9913,7 @@
         <v>217300602.50500003</v>
       </c>
     </row>
-    <row r="44" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:8" ht="15" customHeight="1">
       <c r="B44" s="76" t="s">
         <v>92</v>
       </c>
@@ -9935,7 +9924,7 @@
       <c r="G44" s="35"/>
       <c r="H44" s="35"/>
     </row>
-    <row r="45" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:8" ht="15" customHeight="1">
       <c r="B45" s="16" t="s">
         <v>228</v>
       </c>
@@ -9949,7 +9938,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="46" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:8" ht="15" customHeight="1">
       <c r="B46" s="1" t="s">
         <v>230</v>
       </c>
@@ -9963,7 +9952,7 @@
       </c>
       <c r="F46" s="223"/>
     </row>
-    <row r="47" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:8" ht="15" customHeight="1">
       <c r="B47" s="1" t="str">
         <f>"Equity per share ("&amp;Market_currency&amp;")"</f>
         <v>Equity per share (CNY)</v>
@@ -9978,10 +9967,10 @@
       </c>
       <c r="F47" s="223"/>
     </row>
-    <row r="48" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:8" ht="15" customHeight="1">
       <c r="F48" s="223"/>
     </row>
-    <row r="49" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="2:8" ht="15" customHeight="1">
       <c r="B49" s="143" t="s">
         <v>120</v>
       </c>
@@ -9994,7 +9983,7 @@
       <c r="E49" s="2"/>
       <c r="F49" s="223"/>
     </row>
-    <row r="50" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:8" ht="15" customHeight="1">
       <c r="B50" s="8" t="s">
         <v>90</v>
       </c>
@@ -10008,7 +9997,7 @@
       </c>
       <c r="F50" s="223"/>
     </row>
-    <row r="51" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:8" ht="15" customHeight="1">
       <c r="B51" s="1" t="s">
         <v>146</v>
       </c>
@@ -10019,10 +10008,10 @@
       </c>
       <c r="F51" s="223"/>
     </row>
-    <row r="52" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:8" ht="15" customHeight="1">
       <c r="F52" s="223"/>
     </row>
-    <row r="53" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="53" spans="2:8" ht="15" customHeight="1">
       <c r="B53" s="143" t="s">
         <v>119</v>
       </c>
@@ -10034,7 +10023,7 @@
       </c>
       <c r="F53" s="223"/>
     </row>
-    <row r="54" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="54" spans="2:8" ht="15" customHeight="1">
       <c r="B54" s="1" t="s">
         <v>116</v>
       </c>
@@ -10048,7 +10037,7 @@
       </c>
       <c r="F54" s="223"/>
     </row>
-    <row r="55" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:8" ht="15" customHeight="1">
       <c r="B55" s="1" t="s">
         <v>118</v>
       </c>
@@ -10062,10 +10051,10 @@
       </c>
       <c r="F55" s="223"/>
     </row>
-    <row r="56" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:8" ht="15" customHeight="1">
       <c r="F56" s="223"/>
     </row>
-    <row r="57" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="57" spans="2:8" ht="15" customHeight="1">
       <c r="B57" s="143" t="s">
         <v>145</v>
       </c>
@@ -10077,7 +10066,7 @@
       </c>
       <c r="F57" s="223"/>
     </row>
-    <row r="58" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:8" ht="15" customHeight="1">
       <c r="B58" s="2" t="s">
         <v>86</v>
       </c>
@@ -10088,7 +10077,7 @@
       </c>
       <c r="F58" s="5"/>
     </row>
-    <row r="59" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="59" spans="2:8" ht="15" customHeight="1">
       <c r="B59" s="1" t="s">
         <v>89</v>
       </c>
@@ -10099,10 +10088,10 @@
       </c>
       <c r="F59" s="223"/>
     </row>
-    <row r="60" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="2:8" ht="15" customHeight="1">
       <c r="F60" s="223"/>
     </row>
-    <row r="61" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="61" spans="2:8" ht="15" customHeight="1">
       <c r="B61" s="143" t="s">
         <v>231</v>
       </c>
@@ -10114,7 +10103,7 @@
       </c>
       <c r="F61" s="223"/>
     </row>
-    <row r="62" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:8" ht="15" customHeight="1">
       <c r="B62" s="1" t="s">
         <v>210</v>
       </c>
@@ -10130,7 +10119,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="64" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="2:8" ht="15" customHeight="1">
       <c r="B64" s="76" t="s">
         <v>162</v>
       </c>
@@ -10141,7 +10130,7 @@
       <c r="G64" s="35"/>
       <c r="H64" s="35"/>
     </row>
-    <row r="65" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="65" spans="2:6" ht="15" customHeight="1">
       <c r="B65" s="16" t="s">
         <v>158</v>
       </c>
@@ -10155,7 +10144,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="66" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="66" spans="2:6" ht="15" customHeight="1">
       <c r="B66" s="102" t="s">
         <v>157</v>
       </c>
@@ -10171,7 +10160,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="67" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="67" spans="2:6" ht="15" customHeight="1">
       <c r="B67" s="102" t="s">
         <v>147</v>
       </c>
@@ -10181,7 +10170,7 @@
       </c>
       <c r="F67" s="223"/>
     </row>
-    <row r="68" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="68" spans="2:6" ht="15" customHeight="1">
       <c r="B68" s="102" t="s">
         <v>151</v>
       </c>
@@ -10191,7 +10180,7 @@
       </c>
       <c r="F68" s="223"/>
     </row>
-    <row r="69" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="69" spans="2:6" ht="15" customHeight="1">
       <c r="B69" s="102" t="s">
         <v>149</v>
       </c>
@@ -10201,7 +10190,7 @@
       </c>
       <c r="F69" s="223"/>
     </row>
-    <row r="70" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="70" spans="2:6" ht="15" customHeight="1">
       <c r="B70" s="77" t="s">
         <v>158</v>
       </c>
@@ -10211,10 +10200,10 @@
       </c>
       <c r="F70" s="223"/>
     </row>
-    <row r="71" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="71" spans="2:6" ht="15" customHeight="1">
       <c r="F71" s="223"/>
     </row>
-    <row r="72" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="72" spans="2:6" ht="15" customHeight="1">
       <c r="B72" s="225" t="s">
         <v>256</v>
       </c>
@@ -10226,7 +10215,7 @@
       </c>
       <c r="F72" s="223"/>
     </row>
-    <row r="73" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="73" spans="2:6" ht="15" customHeight="1">
       <c r="B73" s="102" t="s">
         <v>255</v>
       </c>
@@ -10242,7 +10231,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="74" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="74" spans="2:6" ht="15" customHeight="1">
       <c r="B74" s="227" t="s">
         <v>259</v>
       </c>
@@ -10258,7 +10247,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="75" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="75" spans="2:6" ht="15" customHeight="1">
       <c r="B75" s="77" t="s">
         <v>258</v>
       </c>
@@ -10271,7 +10260,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="76" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="76" spans="2:6" ht="15" customHeight="1">
       <c r="B76" s="229" t="s">
         <v>260</v>
       </c>
@@ -10284,10 +10273,10 @@
         <v>261</v>
       </c>
     </row>
-    <row r="77" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="77" spans="2:6" ht="15" customHeight="1">
       <c r="F77" s="223"/>
     </row>
-    <row r="78" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="78" spans="2:6" ht="15" customHeight="1">
       <c r="B78" s="16" t="s">
         <v>159</v>
       </c>
@@ -10299,7 +10288,7 @@
       </c>
       <c r="F78" s="223"/>
     </row>
-    <row r="79" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="79" spans="2:6" ht="15" customHeight="1">
       <c r="B79" s="102" t="s">
         <v>148</v>
       </c>
@@ -10313,7 +10302,7 @@
       </c>
       <c r="F79" s="223"/>
     </row>
-    <row r="80" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="80" spans="2:6" ht="15" customHeight="1">
       <c r="B80" s="102" t="s">
         <v>152</v>
       </c>
@@ -10327,7 +10316,7 @@
       </c>
       <c r="F80" s="223"/>
     </row>
-    <row r="81" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="81" spans="2:8" ht="15" customHeight="1">
       <c r="B81" s="102" t="s">
         <v>150</v>
       </c>
@@ -10341,7 +10330,7 @@
       </c>
       <c r="F81" s="223"/>
     </row>
-    <row r="82" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="82" spans="2:8" ht="15" customHeight="1">
       <c r="B82" s="77" t="s">
         <v>159</v>
       </c>
@@ -10355,7 +10344,7 @@
       </c>
       <c r="F82" s="223"/>
     </row>
-    <row r="84" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="84" spans="2:8" ht="15" customHeight="1">
       <c r="B84" s="76" t="s">
         <v>241</v>
       </c>
@@ -10366,7 +10355,7 @@
       <c r="G84" s="35"/>
       <c r="H84" s="35"/>
     </row>
-    <row r="85" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="85" spans="2:8" ht="15" customHeight="1">
       <c r="B85" s="16" t="s">
         <v>242</v>
       </c>
@@ -10374,7 +10363,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="86" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="86" spans="2:8" ht="15" customHeight="1">
       <c r="B86" s="212" t="s">
         <v>239</v>
       </c>
@@ -10391,7 +10380,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="87" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="87" spans="2:8" ht="15" customHeight="1">
       <c r="B87" s="212" t="s">
         <v>240</v>
       </c>
@@ -10408,7 +10397,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="88" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="88" spans="2:8" ht="15" customHeight="1">
       <c r="B88" s="213" t="s">
         <v>159</v>
       </c>
@@ -10425,7 +10414,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="89" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="89" spans="2:8" ht="15" customHeight="1">
       <c r="B89" s="77" t="s">
         <v>244</v>
       </c>
@@ -10461,19 +10450,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Q807"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="1.33203125" style="2" customWidth="1"/>
     <col min="2" max="2" width="26.33203125" style="2" customWidth="1"/>
     <col min="3" max="3" width="20.6640625" style="2" customWidth="1"/>
     <col min="4" max="4" width="2.6640625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="25.1640625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="25.1328125" style="2" customWidth="1"/>
     <col min="6" max="6" width="2.6640625" style="2" customWidth="1"/>
     <col min="7" max="17" width="20.6640625" style="2" customWidth="1"/>
     <col min="18" max="16384" width="12.33203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:17" ht="15.75" customHeight="1">
       <c r="A1" s="3"/>
       <c r="B1" s="87" t="str">
         <f>Thesis!E17</f>
@@ -10530,7 +10519,7 @@
         <v>42004</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" ht="15.75" customHeight="1">
       <c r="A2" s="3"/>
       <c r="B2" s="51" t="s">
         <v>95</v>
@@ -10553,7 +10542,7 @@
       <c r="P2" s="35"/>
       <c r="Q2" s="35"/>
     </row>
-    <row r="3" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:17" ht="15.75" customHeight="1">
       <c r="A3" s="10"/>
       <c r="B3" s="16" t="s">
         <v>391</v>
@@ -10573,7 +10562,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:17" ht="15.75" customHeight="1">
       <c r="A4" s="10"/>
       <c r="B4" s="25" t="s">
         <v>0</v>
@@ -10630,7 +10619,7 @@
         <v/>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:17" ht="15.75" customHeight="1">
       <c r="A5" s="10"/>
       <c r="B5" s="2" t="s">
         <v>43</v>
@@ -10685,7 +10674,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:17" ht="15.75" customHeight="1">
       <c r="A6" s="10"/>
       <c r="B6" s="30" t="s">
         <v>45</v>
@@ -10740,7 +10729,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:17" ht="15.75" customHeight="1">
       <c r="A7" s="10"/>
       <c r="B7" s="8" t="s">
         <v>42</v>
@@ -10795,7 +10784,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:17" ht="15.75" customHeight="1">
       <c r="A8" s="10"/>
       <c r="B8" s="28" t="s">
         <v>127</v>
@@ -10852,7 +10841,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:17" ht="15.75" customHeight="1">
       <c r="A9" s="10"/>
       <c r="B9" s="26" t="s">
         <v>413</v>
@@ -10909,7 +10898,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:17" ht="15.75" customHeight="1">
       <c r="A10" s="10"/>
       <c r="B10" s="2" t="s">
         <v>65</v>
@@ -10964,7 +10953,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:17" ht="15.75" customHeight="1">
       <c r="A11" s="10"/>
       <c r="B11" s="67" t="s">
         <v>137</v>
@@ -11019,7 +11008,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:17" ht="15.75" customHeight="1">
       <c r="A12" s="10"/>
       <c r="B12" s="2" t="s">
         <v>60</v>
@@ -11074,7 +11063,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:17" ht="15.75" customHeight="1">
       <c r="A13" s="10"/>
       <c r="B13" s="38" t="s">
         <v>208</v>
@@ -11131,7 +11120,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:17" ht="15.75" customHeight="1">
       <c r="A14" s="10"/>
       <c r="B14" s="39" t="s">
         <v>129</v>
@@ -11188,7 +11177,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:17" ht="15.75" customHeight="1">
       <c r="A15" s="10"/>
       <c r="B15" s="2" t="s">
         <v>62</v>
@@ -11243,7 +11232,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:17" ht="15.75" customHeight="1">
       <c r="A16" s="10"/>
       <c r="B16" s="2" t="s">
         <v>396</v>
@@ -11298,7 +11287,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:17" ht="15.75" customHeight="1">
       <c r="A17" s="10"/>
       <c r="B17" s="26" t="s">
         <v>49</v>
@@ -11324,7 +11313,7 @@
       <c r="P17" s="272"/>
       <c r="Q17" s="272"/>
     </row>
-    <row r="18" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:17" ht="15.75" customHeight="1">
       <c r="A18" s="10"/>
       <c r="B18" s="26" t="s">
         <v>94</v>
@@ -11349,7 +11338,7 @@
       <c r="P18" s="273"/>
       <c r="Q18" s="273"/>
     </row>
-    <row r="19" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:17" ht="15.75" customHeight="1">
       <c r="A19" s="10"/>
       <c r="B19" s="30" t="s">
         <v>63</v>
@@ -11406,7 +11395,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:17" ht="15.75" customHeight="1">
       <c r="A20" s="10"/>
       <c r="B20" s="26"/>
       <c r="C20" s="59"/>
@@ -11425,7 +11414,7 @@
       <c r="P20" s="12"/>
       <c r="Q20" s="12"/>
     </row>
-    <row r="21" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:17" ht="15.75" customHeight="1">
       <c r="A21" s="10"/>
       <c r="B21" s="51" t="s">
         <v>174</v>
@@ -11448,7 +11437,7 @@
       <c r="P21" s="35"/>
       <c r="Q21" s="35"/>
     </row>
-    <row r="22" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:17" ht="15.75" customHeight="1">
       <c r="A22" s="10"/>
       <c r="B22" s="61" t="s">
         <v>43</v>
@@ -11469,7 +11458,7 @@
       <c r="P22" s="12"/>
       <c r="Q22" s="12"/>
     </row>
-    <row r="23" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:17" ht="15.75" customHeight="1">
       <c r="A23" s="10"/>
       <c r="B23" s="26" t="s">
         <v>40</v>
@@ -11526,7 +11515,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:17" ht="15.75" customHeight="1">
       <c r="A24" s="10"/>
       <c r="B24" s="65" t="s">
         <v>59</v>
@@ -11583,7 +11572,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:17" ht="15.75" customHeight="1">
       <c r="A25" s="10"/>
       <c r="B25" s="26" t="s">
         <v>46</v>
@@ -11640,7 +11629,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:17" ht="15.75" customHeight="1">
       <c r="A26" s="10"/>
       <c r="B26" s="67" t="s">
         <v>43</v>
@@ -11697,18 +11686,18 @@
         <v/>
       </c>
     </row>
-    <row r="27" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:17" ht="15.75" customHeight="1">
       <c r="A27" s="10"/>
       <c r="E27" s="237"/>
     </row>
-    <row r="28" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:17" ht="15.75" customHeight="1">
       <c r="A28" s="10"/>
       <c r="B28" s="61" t="s">
         <v>175</v>
       </c>
       <c r="E28" s="237"/>
     </row>
-    <row r="29" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:17" ht="15.75" customHeight="1">
       <c r="A29" s="10"/>
       <c r="B29" s="25" t="s">
         <v>40</v>
@@ -11765,7 +11754,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:17" ht="15.75" customHeight="1">
       <c r="A30" s="10"/>
       <c r="B30" s="65" t="str">
         <f>B24</f>
@@ -11823,7 +11812,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:17" ht="15.75" customHeight="1">
       <c r="A31" s="10"/>
       <c r="B31" s="26" t="str">
         <f>B25</f>
@@ -11881,7 +11870,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:17" ht="15.75" customHeight="1">
       <c r="A32" s="10"/>
       <c r="B32" s="67" t="s">
         <v>43</v>
@@ -11936,18 +11925,18 @@
         <v/>
       </c>
     </row>
-    <row r="33" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:17" ht="15.75" customHeight="1">
       <c r="A33" s="10"/>
       <c r="E33" s="237"/>
     </row>
-    <row r="34" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:17" ht="15.75" customHeight="1">
       <c r="A34" s="10"/>
       <c r="B34" s="61" t="s">
         <v>42</v>
       </c>
       <c r="E34" s="237"/>
     </row>
-    <row r="35" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:17" ht="15.75" customHeight="1">
       <c r="A35" s="10"/>
       <c r="B35" s="298" t="s">
         <v>394</v>
@@ -12004,18 +11993,18 @@
         <v/>
       </c>
     </row>
-    <row r="36" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:17" ht="15.75" customHeight="1">
       <c r="A36" s="10"/>
       <c r="E36" s="237"/>
     </row>
-    <row r="37" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:17" ht="15.75" customHeight="1">
       <c r="A37" s="10"/>
       <c r="B37" s="61" t="s">
         <v>176</v>
       </c>
       <c r="E37" s="237"/>
     </row>
-    <row r="38" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:17" ht="15.75" customHeight="1">
       <c r="A38" s="10"/>
       <c r="B38" s="298" t="s">
         <v>394</v>
@@ -12070,18 +12059,18 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:17" ht="15.75" customHeight="1">
       <c r="A39" s="10"/>
       <c r="E39" s="237"/>
     </row>
-    <row r="40" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:17" ht="15.75" customHeight="1">
       <c r="A40" s="10"/>
       <c r="B40" s="61" t="s">
         <v>177</v>
       </c>
       <c r="E40" s="237"/>
     </row>
-    <row r="41" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:17" ht="15.75" customHeight="1">
       <c r="A41" s="10"/>
       <c r="B41" s="26" t="s">
         <v>142</v>
@@ -12139,10 +12128,10 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:17" ht="15.75" customHeight="1">
       <c r="A42" s="10"/>
     </row>
-    <row r="43" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:17" ht="15.75" customHeight="1">
       <c r="A43" s="10"/>
       <c r="B43" s="51" t="s">
         <v>178</v>
@@ -12165,14 +12154,14 @@
       <c r="P43" s="35"/>
       <c r="Q43" s="35"/>
     </row>
-    <row r="44" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:17" ht="15.75" customHeight="1">
       <c r="A44" s="10"/>
       <c r="B44" s="61" t="s">
         <v>57</v>
       </c>
       <c r="E44" s="237"/>
     </row>
-    <row r="45" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:17" ht="15.75" customHeight="1">
       <c r="A45" s="10"/>
       <c r="B45" s="2" t="s">
         <v>37</v>
@@ -12227,7 +12216,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:17" ht="15.75" customHeight="1">
       <c r="A46" s="10"/>
       <c r="B46" s="2" t="s">
         <v>272</v>
@@ -12282,7 +12271,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:17" ht="15.75" customHeight="1">
       <c r="A47" s="10"/>
       <c r="B47" s="245" t="s">
         <v>269</v>
@@ -12339,7 +12328,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:17" ht="15.75" customHeight="1">
       <c r="A48" s="10"/>
       <c r="B48" s="67" t="s">
         <v>65</v>
@@ -12394,11 +12383,11 @@
         <v/>
       </c>
     </row>
-    <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:17" ht="15.75" customHeight="1">
       <c r="A49" s="10"/>
       <c r="E49" s="237"/>
     </row>
-    <row r="50" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:17" ht="15.75" customHeight="1">
       <c r="A50" s="10"/>
       <c r="B50" s="69" t="s">
         <v>130</v>
@@ -12408,7 +12397,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="51" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:17" ht="15.75" customHeight="1">
       <c r="A51" s="10"/>
       <c r="B51" s="8" t="s">
         <v>85</v>
@@ -12432,7 +12421,7 @@
       <c r="P51" s="151"/>
       <c r="Q51" s="151"/>
     </row>
-    <row r="52" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:17" ht="15.75" customHeight="1">
       <c r="A52" s="10"/>
       <c r="B52" s="8" t="s">
         <v>84</v>
@@ -12456,7 +12445,7 @@
       <c r="P52" s="151"/>
       <c r="Q52" s="151"/>
     </row>
-    <row r="53" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:17" ht="15.75" customHeight="1">
       <c r="A53" s="10"/>
       <c r="B53" s="25" t="s">
         <v>87</v>
@@ -12511,11 +12500,11 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:17" ht="15.75" customHeight="1">
       <c r="A54" s="10"/>
       <c r="E54" s="237"/>
     </row>
-    <row r="55" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:17" ht="15.75" customHeight="1">
       <c r="A55" s="10"/>
       <c r="B55" s="61" t="s">
         <v>139</v>
@@ -12525,7 +12514,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="56" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:17" ht="15.75" customHeight="1">
       <c r="A56" s="10"/>
       <c r="B56" s="38" t="s">
         <v>138</v>
@@ -12580,7 +12569,7 @@
         <v/>
       </c>
     </row>
-    <row r="57" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:17" ht="15.75" customHeight="1">
       <c r="A57" s="10"/>
       <c r="B57" s="38" t="s">
         <v>134</v>
@@ -12635,7 +12624,7 @@
         <v/>
       </c>
     </row>
-    <row r="58" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:17" ht="15.75" customHeight="1">
       <c r="A58" s="10"/>
       <c r="B58" s="38" t="s">
         <v>133</v>
@@ -12690,7 +12679,7 @@
         <v/>
       </c>
     </row>
-    <row r="59" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:17" ht="15.75" customHeight="1">
       <c r="A59" s="10"/>
       <c r="B59" s="30" t="s">
         <v>163</v>
@@ -12745,7 +12734,7 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:17" ht="15.75" customHeight="1">
       <c r="A60" s="10"/>
       <c r="B60" s="38" t="s">
         <v>135</v>
@@ -12801,7 +12790,7 @@
         <v/>
       </c>
     </row>
-    <row r="61" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:17" ht="15.75" customHeight="1">
       <c r="A61" s="10"/>
       <c r="B61" s="30" t="s">
         <v>164</v>
@@ -12856,11 +12845,11 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:17" ht="15.75" customHeight="1">
       <c r="A62" s="10"/>
       <c r="E62" s="237"/>
     </row>
-    <row r="63" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:17" ht="15.75" customHeight="1">
       <c r="A63" s="10"/>
       <c r="B63" s="93" t="s">
         <v>140</v>
@@ -12870,7 +12859,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="64" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:17" ht="15.75" customHeight="1">
       <c r="A64" s="10"/>
       <c r="B64" s="38" t="s">
         <v>138</v>
@@ -12895,7 +12884,7 @@
       <c r="P64" s="157"/>
       <c r="Q64" s="157"/>
     </row>
-    <row r="65" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:17" ht="15.75" customHeight="1">
       <c r="A65" s="10"/>
       <c r="B65" s="102" t="s">
         <v>132</v>
@@ -12920,7 +12909,7 @@
       <c r="P65" s="157"/>
       <c r="Q65" s="157"/>
     </row>
-    <row r="66" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:17" ht="15.75" customHeight="1">
       <c r="A66" s="10"/>
       <c r="B66" s="102" t="s">
         <v>133</v>
@@ -12945,7 +12934,7 @@
       <c r="P66" s="157"/>
       <c r="Q66" s="157"/>
     </row>
-    <row r="67" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:17" ht="15.75" customHeight="1">
       <c r="A67" s="10"/>
       <c r="B67" s="30" t="s">
         <v>163</v>
@@ -12972,10 +12961,10 @@
       <c r="P67" s="157"/>
       <c r="Q67" s="157"/>
     </row>
-    <row r="68" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:17" ht="15.75" customHeight="1">
       <c r="A68" s="10"/>
     </row>
-    <row r="69" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:17" ht="15.75" customHeight="1">
       <c r="A69" s="10"/>
       <c r="B69" s="51" t="s">
         <v>181</v>
@@ -12998,7 +12987,7 @@
       <c r="P69" s="35"/>
       <c r="Q69" s="35"/>
     </row>
-    <row r="70" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:17" ht="15.75" customHeight="1">
       <c r="A70" s="10"/>
       <c r="B70" s="69" t="s">
         <v>185</v>
@@ -13019,7 +13008,7 @@
       <c r="P70" s="12"/>
       <c r="Q70" s="12"/>
     </row>
-    <row r="71" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:17" ht="15.75" customHeight="1">
       <c r="A71" s="10"/>
       <c r="B71" s="2" t="s">
         <v>43</v>
@@ -13076,7 +13065,7 @@
         <v/>
       </c>
     </row>
-    <row r="72" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:17" ht="15.75" customHeight="1">
       <c r="A72" s="10"/>
       <c r="B72" s="30" t="s">
         <v>45</v>
@@ -13133,7 +13122,7 @@
         <v/>
       </c>
     </row>
-    <row r="73" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:17" ht="15.75" customHeight="1">
       <c r="A73" s="10"/>
       <c r="B73" s="8" t="s">
         <v>42</v>
@@ -13190,7 +13179,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:17" ht="15.75" customHeight="1">
       <c r="A74" s="10"/>
       <c r="B74" s="28" t="s">
         <v>127</v>
@@ -13247,7 +13236,7 @@
         <v/>
       </c>
     </row>
-    <row r="75" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:17" ht="15.75" customHeight="1">
       <c r="A75" s="10"/>
       <c r="B75" s="26" t="s">
         <v>128</v>
@@ -13304,7 +13293,7 @@
         <v/>
       </c>
     </row>
-    <row r="76" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:17" ht="15.75" customHeight="1">
       <c r="A76" s="10"/>
       <c r="B76" s="2" t="s">
         <v>65</v>
@@ -13361,7 +13350,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:17" ht="15.75" customHeight="1">
       <c r="A77" s="10"/>
       <c r="B77" s="67" t="s">
         <v>137</v>
@@ -13418,7 +13407,7 @@
         <v/>
       </c>
     </row>
-    <row r="78" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:17" ht="15.75" customHeight="1">
       <c r="A78" s="10"/>
       <c r="B78" s="2" t="s">
         <v>60</v>
@@ -13475,7 +13464,7 @@
         <v/>
       </c>
     </row>
-    <row r="79" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:17" ht="15.75" customHeight="1">
       <c r="A79" s="10"/>
       <c r="B79" s="38" t="str">
         <f>B13</f>
@@ -13533,7 +13522,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:17" ht="15.75" customHeight="1">
       <c r="A80" s="10"/>
       <c r="B80" s="39" t="s">
         <v>129</v>
@@ -13590,7 +13579,7 @@
         <v/>
       </c>
     </row>
-    <row r="81" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:17" ht="15.75" customHeight="1">
       <c r="A81" s="10"/>
       <c r="B81" s="2" t="s">
         <v>62</v>
@@ -13647,7 +13636,7 @@
         <v/>
       </c>
     </row>
-    <row r="82" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:17" ht="15.75" customHeight="1">
       <c r="A82" s="10"/>
       <c r="B82" s="2" t="s">
         <v>77</v>
@@ -13706,7 +13695,7 @@
         <v/>
       </c>
     </row>
-    <row r="83" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:17" ht="15.75" customHeight="1">
       <c r="A83" s="10"/>
       <c r="B83" s="26" t="s">
         <v>49</v>
@@ -13732,7 +13721,7 @@
       <c r="P83" s="203"/>
       <c r="Q83" s="203"/>
     </row>
-    <row r="84" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:17" ht="15.75" customHeight="1">
       <c r="A84" s="10"/>
       <c r="B84" s="8" t="s">
         <v>94</v>
@@ -13756,7 +13745,7 @@
       <c r="P84" s="151"/>
       <c r="Q84" s="151"/>
     </row>
-    <row r="85" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:17" ht="15.75" customHeight="1">
       <c r="A85" s="10"/>
       <c r="B85" s="30" t="s">
         <v>117</v>
@@ -13813,18 +13802,18 @@
         <v/>
       </c>
     </row>
-    <row r="86" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:17" ht="15.75" customHeight="1">
       <c r="A86" s="10"/>
       <c r="E86" s="237"/>
     </row>
-    <row r="87" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:17" ht="15.75" customHeight="1">
       <c r="A87" s="10"/>
       <c r="B87" s="61" t="s">
         <v>183</v>
       </c>
       <c r="E87" s="237"/>
     </row>
-    <row r="88" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:17" ht="15.75" customHeight="1">
       <c r="A88" s="10"/>
       <c r="B88" s="2" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
@@ -13880,7 +13869,7 @@
         <v/>
       </c>
     </row>
-    <row r="89" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:17" ht="15.75" customHeight="1">
       <c r="A89" s="10"/>
       <c r="B89" s="2" t="str">
         <f>"Dividend ("&amp;Market_currency&amp;")"</f>
@@ -13936,7 +13925,7 @@
         <v/>
       </c>
     </row>
-    <row r="90" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:17" ht="15.75" customHeight="1">
       <c r="A90" s="10"/>
       <c r="B90" s="2" t="s">
         <v>182</v>
@@ -13991,7 +13980,7 @@
         <v/>
       </c>
     </row>
-    <row r="91" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:17" ht="15.75" customHeight="1">
       <c r="A91" s="10"/>
       <c r="B91" s="2" t="s">
         <v>329</v>
@@ -14012,23 +14001,23 @@
       <c r="P91" s="293"/>
       <c r="Q91" s="293"/>
     </row>
-    <row r="92" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:17" ht="15.75" customHeight="1">
       <c r="A92" s="10"/>
       <c r="B92" s="2" t="s">
         <v>328</v>
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>2.6891382236469922E-2</v>
+        <v>2.741086016338299E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>2.6891382236469922E-2</v>
+        <v>2.741086016338299E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>3.9628512162926649E-2</v>
+        <v>4.0394041326285442E-2</v>
       </c>
       <c r="I92" s="22" t="str">
         <f t="shared" si="38"/>
@@ -14067,11 +14056,11 @@
         <v/>
       </c>
     </row>
-    <row r="93" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:17" ht="15.75" customHeight="1">
       <c r="A93" s="10"/>
       <c r="E93" s="237"/>
     </row>
-    <row r="94" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:17" ht="15.75" customHeight="1">
       <c r="A94" s="10"/>
       <c r="B94" s="143" t="s">
         <v>81</v>
@@ -14092,7 +14081,7 @@
       <c r="P94" s="12"/>
       <c r="Q94" s="12"/>
     </row>
-    <row r="95" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:17" ht="15.75" customHeight="1">
       <c r="A95" s="10"/>
       <c r="B95" s="26" t="s">
         <v>121</v>
@@ -14149,7 +14138,7 @@
         <v/>
       </c>
     </row>
-    <row r="96" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:17" ht="15.75" customHeight="1">
       <c r="A96" s="10"/>
       <c r="B96" s="67" t="s">
         <v>137</v>
@@ -14206,10 +14195,10 @@
         <v/>
       </c>
     </row>
-    <row r="97" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="97" spans="1:17" ht="15.75" customHeight="1">
       <c r="A97" s="10"/>
     </row>
-    <row r="98" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:17" ht="15.75" customHeight="1">
       <c r="A98" s="3"/>
       <c r="B98" s="51" t="s">
         <v>184</v>
@@ -14232,7 +14221,7 @@
       <c r="P98" s="35"/>
       <c r="Q98" s="35"/>
     </row>
-    <row r="99" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="99" spans="1:17" ht="15.75" customHeight="1">
       <c r="A99" s="10"/>
       <c r="B99" s="61" t="s">
         <v>26</v>
@@ -14242,7 +14231,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="100" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="100" spans="1:17" ht="15.75" customHeight="1">
       <c r="A100" s="10"/>
       <c r="B100" s="25" t="s">
         <v>1</v>
@@ -14299,7 +14288,7 @@
         <v/>
       </c>
     </row>
-    <row r="101" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="101" spans="1:17" ht="15.75" customHeight="1">
       <c r="A101" s="10"/>
       <c r="B101" s="90" t="s">
         <v>179</v>
@@ -14356,7 +14345,7 @@
         <v/>
       </c>
     </row>
-    <row r="102" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="102" spans="1:17" ht="15.75" customHeight="1">
       <c r="A102" s="10"/>
       <c r="B102" s="90" t="s">
         <v>180</v>
@@ -14413,7 +14402,7 @@
         <v/>
       </c>
     </row>
-    <row r="103" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="103" spans="1:17" ht="15.75" customHeight="1">
       <c r="A103" s="10"/>
       <c r="B103" s="25" t="s">
         <v>38</v>
@@ -14470,7 +14459,7 @@
         <v/>
       </c>
     </row>
-    <row r="104" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="104" spans="1:17" ht="15.75" customHeight="1">
       <c r="A104" s="10"/>
       <c r="B104" s="25" t="s">
         <v>28</v>
@@ -14527,11 +14516,11 @@
         <v/>
       </c>
     </row>
-    <row r="105" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="105" spans="1:17" ht="15.75" customHeight="1">
       <c r="A105" s="10"/>
       <c r="E105" s="237"/>
     </row>
-    <row r="106" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="106" spans="1:17" ht="15.75" customHeight="1">
       <c r="A106" s="10"/>
       <c r="B106" s="88" t="s">
         <v>189</v>
@@ -14554,7 +14543,7 @@
       <c r="P106" s="12"/>
       <c r="Q106" s="12"/>
     </row>
-    <row r="107" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="107" spans="1:17" ht="15.75" customHeight="1">
       <c r="A107" s="10"/>
       <c r="B107" s="25" t="s">
         <v>186</v>
@@ -14611,7 +14600,7 @@
         <v/>
       </c>
     </row>
-    <row r="108" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="108" spans="1:17" ht="15.75" customHeight="1">
       <c r="A108" s="10"/>
       <c r="B108" s="25" t="s">
         <v>187</v>
@@ -14668,7 +14657,7 @@
         <v/>
       </c>
     </row>
-    <row r="109" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="109" spans="1:17" ht="15.75" customHeight="1">
       <c r="A109" s="10"/>
       <c r="B109" s="25" t="s">
         <v>66</v>
@@ -14695,18 +14684,18 @@
       <c r="P109" s="186"/>
       <c r="Q109" s="186"/>
     </row>
-    <row r="110" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="110" spans="1:17" ht="15.75" customHeight="1">
       <c r="A110" s="10"/>
       <c r="E110" s="237"/>
     </row>
-    <row r="111" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="111" spans="1:17" ht="15.75" customHeight="1">
       <c r="A111" s="10"/>
       <c r="B111" s="61" t="s">
         <v>48</v>
       </c>
       <c r="E111" s="237"/>
     </row>
-    <row r="112" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="112" spans="1:17" ht="15.75" customHeight="1">
       <c r="A112" s="10"/>
       <c r="B112" s="2" t="s">
         <v>303</v>
@@ -14760,7 +14749,7 @@
         <v/>
       </c>
     </row>
-    <row r="113" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="113" spans="1:17" ht="15.75" customHeight="1">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
         <v>304</v>
@@ -14815,11 +14804,11 @@
         <v/>
       </c>
     </row>
-    <row r="114" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="114" spans="1:17" ht="15.75" customHeight="1">
       <c r="A114" s="10"/>
       <c r="E114" s="237"/>
     </row>
-    <row r="115" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="115" spans="1:17" ht="15.75" customHeight="1">
       <c r="A115" s="10"/>
       <c r="B115" s="88" t="s">
         <v>36</v>
@@ -14878,7 +14867,7 @@
         <v/>
       </c>
     </row>
-    <row r="116" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="116" spans="1:17" ht="15.75" customHeight="1">
       <c r="A116" s="10"/>
       <c r="B116" s="7" t="s">
         <v>190</v>
@@ -14936,7 +14925,7 @@
         <v/>
       </c>
     </row>
-    <row r="117" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="117" spans="1:17" ht="15.75" customHeight="1">
       <c r="B117" s="7" t="s">
         <v>80</v>
       </c>
@@ -14993,7 +14982,7 @@
         <v/>
       </c>
     </row>
-    <row r="118" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="118" spans="1:17" ht="15.75" customHeight="1">
       <c r="B118" s="7" t="s">
         <v>88</v>
       </c>
@@ -15052,7 +15041,7 @@
         <v/>
       </c>
     </row>
-    <row r="119" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="119" spans="1:17" ht="15.75" customHeight="1">
       <c r="A119" s="10"/>
       <c r="B119" s="67" t="s">
         <v>191</v>
@@ -15111,7 +15100,7 @@
         <v/>
       </c>
     </row>
-    <row r="120" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="120" spans="1:17" ht="15.75" customHeight="1">
       <c r="A120" s="10"/>
       <c r="B120" s="26"/>
       <c r="C120" s="59"/>
@@ -15130,7 +15119,7 @@
       <c r="P120" s="12"/>
       <c r="Q120" s="12"/>
     </row>
-    <row r="121" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:17" ht="15.75" customHeight="1">
       <c r="A121" s="10"/>
       <c r="B121" s="51" t="s">
         <v>192</v>
@@ -15153,7 +15142,7 @@
       <c r="P121" s="35"/>
       <c r="Q121" s="35"/>
     </row>
-    <row r="122" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="122" spans="1:17" ht="15.75" customHeight="1">
       <c r="A122" s="10"/>
       <c r="B122" s="160" t="s">
         <v>141</v>
@@ -15174,7 +15163,7 @@
       <c r="P122" s="12"/>
       <c r="Q122" s="12"/>
     </row>
-    <row r="123" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="123" spans="1:17" ht="15.75" customHeight="1">
       <c r="A123" s="10"/>
       <c r="B123" s="26" t="str">
         <f>"FCFE per share ("&amp;Market_currency&amp;")"</f>
@@ -15232,25 +15221,25 @@
         <v/>
       </c>
     </row>
-    <row r="124" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="124" spans="1:17" ht="15.75" customHeight="1">
       <c r="A124" s="10"/>
       <c r="B124" s="26" t="s">
         <v>226</v>
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>7.2391319447967964E-2</v>
+        <v>7.3789748588673543E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>6.4269121270402199E-2</v>
+        <v>6.5510648745207664E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>6.1877413569646211E-2</v>
+        <v>6.3072738906263123E-2</v>
       </c>
       <c r="I124" s="74" t="str">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
@@ -15289,18 +15278,18 @@
         <v/>
       </c>
     </row>
-    <row r="125" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="125" spans="1:17" ht="15.75" customHeight="1">
       <c r="B125" s="2" t="s">
         <v>306</v>
       </c>
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.062862121247466E-2</v>
+        <v>8.2186175548246643E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.6565588489768452E-2</v>
+        <v>7.804465463935456E-2</v>
       </c>
       <c r="I125" s="22" t="str">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -15339,688 +15328,688 @@
         <v/>
       </c>
     </row>
-    <row r="126" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="127" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="128" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="126" spans="1:17" ht="15.75" customHeight="1"/>
+    <row r="127" spans="1:17" ht="15.75" customHeight="1"/>
+    <row r="128" spans="1:17" ht="15.75" customHeight="1"/>
+    <row r="129" ht="15.75" customHeight="1"/>
+    <row r="130" ht="15.75" customHeight="1"/>
+    <row r="131" ht="15.75" customHeight="1"/>
+    <row r="132" ht="15.75" customHeight="1"/>
+    <row r="133" ht="15.75" customHeight="1"/>
+    <row r="134" ht="15.75" customHeight="1"/>
+    <row r="135" ht="15.75" customHeight="1"/>
+    <row r="136" ht="15.75" customHeight="1"/>
+    <row r="137" ht="15.75" customHeight="1"/>
+    <row r="138" ht="15.75" customHeight="1"/>
+    <row r="139" ht="15.75" customHeight="1"/>
+    <row r="140" ht="15.75" customHeight="1"/>
+    <row r="141" ht="15.75" customHeight="1"/>
+    <row r="142" ht="15.75" customHeight="1"/>
+    <row r="143" ht="15.75" customHeight="1"/>
+    <row r="144" ht="15.75" customHeight="1"/>
+    <row r="145" ht="15.75" customHeight="1"/>
+    <row r="146" ht="15.75" customHeight="1"/>
+    <row r="147" ht="15.75" customHeight="1"/>
+    <row r="148" ht="15.75" customHeight="1"/>
+    <row r="149" ht="15.75" customHeight="1"/>
+    <row r="150" ht="15.75" customHeight="1"/>
+    <row r="151" ht="15.75" customHeight="1"/>
+    <row r="152" ht="15.75" customHeight="1"/>
+    <row r="153" ht="15.75" customHeight="1"/>
+    <row r="154" ht="15.75" customHeight="1"/>
+    <row r="155" ht="15.75" customHeight="1"/>
+    <row r="156" ht="15.75" customHeight="1"/>
+    <row r="157" ht="15.75" customHeight="1"/>
+    <row r="158" ht="15.75" customHeight="1"/>
+    <row r="159" ht="15.75" customHeight="1"/>
+    <row r="160" ht="15.75" customHeight="1"/>
+    <row r="161" ht="15.75" customHeight="1"/>
+    <row r="162" ht="15.75" customHeight="1"/>
+    <row r="163" ht="15.75" customHeight="1"/>
+    <row r="164" ht="15.75" customHeight="1"/>
+    <row r="165" ht="15.75" customHeight="1"/>
+    <row r="166" ht="15.75" customHeight="1"/>
+    <row r="167" ht="15.75" customHeight="1"/>
+    <row r="168" ht="15.75" customHeight="1"/>
+    <row r="169" ht="15.75" customHeight="1"/>
+    <row r="170" ht="15.75" customHeight="1"/>
+    <row r="171" ht="15.75" customHeight="1"/>
+    <row r="172" ht="15.75" customHeight="1"/>
+    <row r="173" ht="15.75" customHeight="1"/>
+    <row r="174" ht="15.75" customHeight="1"/>
+    <row r="175" ht="15.75" customHeight="1"/>
+    <row r="176" ht="15.75" customHeight="1"/>
+    <row r="177" ht="15.75" customHeight="1"/>
+    <row r="178" ht="15.75" customHeight="1"/>
+    <row r="179" ht="15.75" customHeight="1"/>
+    <row r="180" ht="15.75" customHeight="1"/>
+    <row r="181" ht="15.75" customHeight="1"/>
+    <row r="182" ht="15.75" customHeight="1"/>
+    <row r="183" ht="15.75" customHeight="1"/>
+    <row r="184" ht="15.75" customHeight="1"/>
+    <row r="185" ht="15.75" customHeight="1"/>
+    <row r="186" ht="15.75" customHeight="1"/>
+    <row r="187" ht="15.75" customHeight="1"/>
+    <row r="188" ht="15.75" customHeight="1"/>
+    <row r="189" ht="15.75" customHeight="1"/>
+    <row r="190" ht="15.75" customHeight="1"/>
+    <row r="191" ht="15.75" customHeight="1"/>
+    <row r="192" ht="15.75" customHeight="1"/>
+    <row r="193" ht="15.75" customHeight="1"/>
+    <row r="194" ht="15.75" customHeight="1"/>
+    <row r="195" ht="15.75" customHeight="1"/>
+    <row r="196" ht="15.75" customHeight="1"/>
+    <row r="197" ht="15.75" customHeight="1"/>
+    <row r="198" ht="15.75" customHeight="1"/>
+    <row r="199" ht="15.75" customHeight="1"/>
+    <row r="200" ht="15.75" customHeight="1"/>
+    <row r="201" ht="15.75" customHeight="1"/>
+    <row r="202" ht="15.75" customHeight="1"/>
+    <row r="203" ht="15.75" customHeight="1"/>
+    <row r="204" ht="15.75" customHeight="1"/>
+    <row r="205" ht="15.75" customHeight="1"/>
+    <row r="206" ht="15.75" customHeight="1"/>
+    <row r="207" ht="15.75" customHeight="1"/>
+    <row r="208" ht="15.75" customHeight="1"/>
+    <row r="209" ht="15.75" customHeight="1"/>
+    <row r="210" ht="15.75" customHeight="1"/>
+    <row r="211" ht="15.75" customHeight="1"/>
+    <row r="212" ht="15.75" customHeight="1"/>
+    <row r="213" ht="15.75" customHeight="1"/>
+    <row r="214" ht="15.75" customHeight="1"/>
+    <row r="215" ht="15.75" customHeight="1"/>
+    <row r="216" ht="15.75" customHeight="1"/>
+    <row r="217" ht="15.75" customHeight="1"/>
+    <row r="218" ht="15.75" customHeight="1"/>
+    <row r="219" ht="15.75" customHeight="1"/>
+    <row r="220" ht="15.75" customHeight="1"/>
+    <row r="221" ht="15.75" customHeight="1"/>
+    <row r="222" ht="15.75" customHeight="1"/>
+    <row r="223" ht="15.75" customHeight="1"/>
+    <row r="224" ht="15.75" customHeight="1"/>
+    <row r="225" ht="15.75" customHeight="1"/>
+    <row r="226" ht="15.75" customHeight="1"/>
+    <row r="227" ht="15.75" customHeight="1"/>
+    <row r="228" ht="15.75" customHeight="1"/>
+    <row r="229" ht="15.75" customHeight="1"/>
+    <row r="230" ht="15.75" customHeight="1"/>
+    <row r="231" ht="15.75" customHeight="1"/>
+    <row r="232" ht="15.75" customHeight="1"/>
+    <row r="233" ht="15.75" customHeight="1"/>
+    <row r="234" ht="15.75" customHeight="1"/>
+    <row r="235" ht="15.75" customHeight="1"/>
+    <row r="236" ht="15.75" customHeight="1"/>
+    <row r="237" ht="15.75" customHeight="1"/>
+    <row r="238" ht="15.75" customHeight="1"/>
+    <row r="239" ht="15.75" customHeight="1"/>
+    <row r="240" ht="15.75" customHeight="1"/>
+    <row r="241" ht="15.75" customHeight="1"/>
+    <row r="242" ht="15.75" customHeight="1"/>
+    <row r="243" ht="15.75" customHeight="1"/>
+    <row r="244" ht="15.75" customHeight="1"/>
+    <row r="245" ht="15.75" customHeight="1"/>
+    <row r="246" ht="15.75" customHeight="1"/>
+    <row r="247" ht="15.75" customHeight="1"/>
+    <row r="248" ht="15.75" customHeight="1"/>
+    <row r="249" ht="15.75" customHeight="1"/>
+    <row r="250" ht="15.75" customHeight="1"/>
+    <row r="251" ht="15.75" customHeight="1"/>
+    <row r="252" ht="15.75" customHeight="1"/>
+    <row r="253" ht="15.75" customHeight="1"/>
+    <row r="254" ht="15.75" customHeight="1"/>
+    <row r="255" ht="15.75" customHeight="1"/>
+    <row r="256" ht="15.75" customHeight="1"/>
+    <row r="257" ht="15.75" customHeight="1"/>
+    <row r="258" ht="15.75" customHeight="1"/>
+    <row r="259" ht="15.75" customHeight="1"/>
+    <row r="260" ht="15.75" customHeight="1"/>
+    <row r="261" ht="15.75" customHeight="1"/>
+    <row r="262" ht="15.75" customHeight="1"/>
+    <row r="263" ht="15.75" customHeight="1"/>
+    <row r="264" ht="15.75" customHeight="1"/>
+    <row r="265" ht="15.75" customHeight="1"/>
+    <row r="266" ht="15.75" customHeight="1"/>
+    <row r="267" ht="15.75" customHeight="1"/>
+    <row r="268" ht="15.75" customHeight="1"/>
+    <row r="269" ht="15.75" customHeight="1"/>
+    <row r="270" ht="15.75" customHeight="1"/>
+    <row r="271" ht="15.75" customHeight="1"/>
+    <row r="272" ht="15.75" customHeight="1"/>
+    <row r="273" ht="15.75" customHeight="1"/>
+    <row r="274" ht="15.75" customHeight="1"/>
+    <row r="275" ht="15.75" customHeight="1"/>
+    <row r="276" ht="15.75" customHeight="1"/>
+    <row r="277" ht="15.75" customHeight="1"/>
+    <row r="278" ht="15.75" customHeight="1"/>
+    <row r="279" ht="15.75" customHeight="1"/>
+    <row r="280" ht="15.75" customHeight="1"/>
+    <row r="281" ht="15.75" customHeight="1"/>
+    <row r="282" ht="15.75" customHeight="1"/>
+    <row r="283" ht="15.75" customHeight="1"/>
+    <row r="284" ht="15.75" customHeight="1"/>
+    <row r="285" ht="15.75" customHeight="1"/>
+    <row r="286" ht="15.75" customHeight="1"/>
+    <row r="287" ht="15.75" customHeight="1"/>
+    <row r="288" ht="15.75" customHeight="1"/>
+    <row r="289" ht="15.75" customHeight="1"/>
+    <row r="290" ht="15.75" customHeight="1"/>
+    <row r="291" ht="15.75" customHeight="1"/>
+    <row r="292" ht="15.75" customHeight="1"/>
+    <row r="293" ht="15.75" customHeight="1"/>
+    <row r="294" ht="15.75" customHeight="1"/>
+    <row r="295" ht="15.75" customHeight="1"/>
+    <row r="296" ht="15.75" customHeight="1"/>
+    <row r="297" ht="15.75" customHeight="1"/>
+    <row r="298" ht="15.75" customHeight="1"/>
+    <row r="299" ht="15.75" customHeight="1"/>
+    <row r="300" ht="15.75" customHeight="1"/>
+    <row r="301" ht="15.75" customHeight="1"/>
+    <row r="302" ht="15.75" customHeight="1"/>
+    <row r="303" ht="15.75" customHeight="1"/>
+    <row r="304" ht="15.75" customHeight="1"/>
+    <row r="305" ht="15.75" customHeight="1"/>
+    <row r="306" ht="15.75" customHeight="1"/>
+    <row r="307" ht="15.75" customHeight="1"/>
+    <row r="308" ht="15.75" customHeight="1"/>
+    <row r="309" ht="15.75" customHeight="1"/>
+    <row r="310" ht="15.75" customHeight="1"/>
+    <row r="311" ht="15.75" customHeight="1"/>
+    <row r="312" ht="15.75" customHeight="1"/>
+    <row r="313" ht="15.75" customHeight="1"/>
+    <row r="314" ht="15.75" customHeight="1"/>
+    <row r="315" ht="15.75" customHeight="1"/>
+    <row r="316" ht="15.75" customHeight="1"/>
+    <row r="317" ht="15.75" customHeight="1"/>
+    <row r="318" ht="15.75" customHeight="1"/>
+    <row r="319" ht="15.75" customHeight="1"/>
+    <row r="320" ht="15.75" customHeight="1"/>
+    <row r="321" ht="15.75" customHeight="1"/>
+    <row r="322" ht="15.75" customHeight="1"/>
+    <row r="323" ht="15.75" customHeight="1"/>
+    <row r="324" ht="15.75" customHeight="1"/>
+    <row r="325" ht="15.75" customHeight="1"/>
+    <row r="326" ht="15.75" customHeight="1"/>
+    <row r="327" ht="15.75" customHeight="1"/>
+    <row r="328" ht="15.75" customHeight="1"/>
+    <row r="329" ht="15.75" customHeight="1"/>
+    <row r="330" ht="15.75" customHeight="1"/>
+    <row r="331" ht="15.75" customHeight="1"/>
+    <row r="332" ht="15.75" customHeight="1"/>
+    <row r="333" ht="15.75" customHeight="1"/>
+    <row r="334" ht="15.75" customHeight="1"/>
+    <row r="335" ht="15.75" customHeight="1"/>
+    <row r="336" ht="15.75" customHeight="1"/>
+    <row r="337" ht="15.75" customHeight="1"/>
+    <row r="338" ht="15.75" customHeight="1"/>
+    <row r="339" ht="15.75" customHeight="1"/>
+    <row r="340" ht="15.75" customHeight="1"/>
+    <row r="341" ht="15.75" customHeight="1"/>
+    <row r="342" ht="15.75" customHeight="1"/>
+    <row r="343" ht="15.75" customHeight="1"/>
+    <row r="344" ht="15.75" customHeight="1"/>
+    <row r="345" ht="15.75" customHeight="1"/>
+    <row r="346" ht="15.75" customHeight="1"/>
+    <row r="347" ht="15.75" customHeight="1"/>
+    <row r="348" ht="15.75" customHeight="1"/>
+    <row r="349" ht="15.75" customHeight="1"/>
+    <row r="350" ht="15.75" customHeight="1"/>
+    <row r="351" ht="15.75" customHeight="1"/>
+    <row r="352" ht="15.75" customHeight="1"/>
+    <row r="353" ht="15.75" customHeight="1"/>
+    <row r="354" ht="15.75" customHeight="1"/>
+    <row r="355" ht="15.75" customHeight="1"/>
+    <row r="356" ht="15.75" customHeight="1"/>
+    <row r="357" ht="15.75" customHeight="1"/>
+    <row r="358" ht="15.75" customHeight="1"/>
+    <row r="359" ht="15.75" customHeight="1"/>
+    <row r="360" ht="15.75" customHeight="1"/>
+    <row r="361" ht="15.75" customHeight="1"/>
+    <row r="362" ht="15.75" customHeight="1"/>
+    <row r="363" ht="15.75" customHeight="1"/>
+    <row r="364" ht="15.75" customHeight="1"/>
+    <row r="365" ht="15.75" customHeight="1"/>
+    <row r="366" ht="15.75" customHeight="1"/>
+    <row r="367" ht="15.75" customHeight="1"/>
+    <row r="368" ht="15.75" customHeight="1"/>
+    <row r="369" ht="15.75" customHeight="1"/>
+    <row r="370" ht="15.75" customHeight="1"/>
+    <row r="371" ht="15.75" customHeight="1"/>
+    <row r="372" ht="15.75" customHeight="1"/>
+    <row r="373" ht="15.75" customHeight="1"/>
+    <row r="374" ht="15.75" customHeight="1"/>
+    <row r="375" ht="15.75" customHeight="1"/>
+    <row r="376" ht="15.75" customHeight="1"/>
+    <row r="377" ht="15.75" customHeight="1"/>
+    <row r="378" ht="15.75" customHeight="1"/>
+    <row r="379" ht="15.75" customHeight="1"/>
+    <row r="380" ht="15.75" customHeight="1"/>
+    <row r="381" ht="15.75" customHeight="1"/>
+    <row r="382" ht="15.75" customHeight="1"/>
+    <row r="383" ht="15.75" customHeight="1"/>
+    <row r="384" ht="15.75" customHeight="1"/>
+    <row r="385" ht="15.75" customHeight="1"/>
+    <row r="386" ht="15.75" customHeight="1"/>
+    <row r="387" ht="15.75" customHeight="1"/>
+    <row r="388" ht="15.75" customHeight="1"/>
+    <row r="389" ht="15.75" customHeight="1"/>
+    <row r="390" ht="15.75" customHeight="1"/>
+    <row r="391" ht="15.75" customHeight="1"/>
+    <row r="392" ht="15.75" customHeight="1"/>
+    <row r="393" ht="15.75" customHeight="1"/>
+    <row r="394" ht="15.75" customHeight="1"/>
+    <row r="395" ht="15.75" customHeight="1"/>
+    <row r="396" ht="15.75" customHeight="1"/>
+    <row r="397" ht="15.75" customHeight="1"/>
+    <row r="398" ht="15.75" customHeight="1"/>
+    <row r="399" ht="15.75" customHeight="1"/>
+    <row r="400" ht="15.75" customHeight="1"/>
+    <row r="401" ht="15.75" customHeight="1"/>
+    <row r="402" ht="15.75" customHeight="1"/>
+    <row r="403" ht="15.75" customHeight="1"/>
+    <row r="404" ht="15.75" customHeight="1"/>
+    <row r="405" ht="15.75" customHeight="1"/>
+    <row r="406" ht="15.75" customHeight="1"/>
+    <row r="407" ht="15.75" customHeight="1"/>
+    <row r="408" ht="15.75" customHeight="1"/>
+    <row r="409" ht="15.75" customHeight="1"/>
+    <row r="410" ht="15.75" customHeight="1"/>
+    <row r="411" ht="15.75" customHeight="1"/>
+    <row r="412" ht="15.75" customHeight="1"/>
+    <row r="413" ht="15.75" customHeight="1"/>
+    <row r="414" ht="15.75" customHeight="1"/>
+    <row r="415" ht="15.75" customHeight="1"/>
+    <row r="416" ht="15.75" customHeight="1"/>
+    <row r="417" ht="15.75" customHeight="1"/>
+    <row r="418" ht="15.75" customHeight="1"/>
+    <row r="419" ht="15.75" customHeight="1"/>
+    <row r="420" ht="15.75" customHeight="1"/>
+    <row r="421" ht="15.75" customHeight="1"/>
+    <row r="422" ht="15.75" customHeight="1"/>
+    <row r="423" ht="15.75" customHeight="1"/>
+    <row r="424" ht="15.75" customHeight="1"/>
+    <row r="425" ht="15.75" customHeight="1"/>
+    <row r="426" ht="15.75" customHeight="1"/>
+    <row r="427" ht="15.75" customHeight="1"/>
+    <row r="428" ht="15.75" customHeight="1"/>
+    <row r="429" ht="15.75" customHeight="1"/>
+    <row r="430" ht="15.75" customHeight="1"/>
+    <row r="431" ht="15.75" customHeight="1"/>
+    <row r="432" ht="15.75" customHeight="1"/>
+    <row r="433" ht="15.75" customHeight="1"/>
+    <row r="434" ht="15.75" customHeight="1"/>
+    <row r="435" ht="15.75" customHeight="1"/>
+    <row r="436" ht="15.75" customHeight="1"/>
+    <row r="437" ht="15.75" customHeight="1"/>
+    <row r="438" ht="15.75" customHeight="1"/>
+    <row r="439" ht="15.75" customHeight="1"/>
+    <row r="440" ht="15.75" customHeight="1"/>
+    <row r="441" ht="15.75" customHeight="1"/>
+    <row r="442" ht="15.75" customHeight="1"/>
+    <row r="443" ht="15.75" customHeight="1"/>
+    <row r="444" ht="15.75" customHeight="1"/>
+    <row r="445" ht="15.75" customHeight="1"/>
+    <row r="446" ht="15.75" customHeight="1"/>
+    <row r="447" ht="15.75" customHeight="1"/>
+    <row r="448" ht="15.75" customHeight="1"/>
+    <row r="449" ht="15.75" customHeight="1"/>
+    <row r="450" ht="15.75" customHeight="1"/>
+    <row r="451" ht="15.75" customHeight="1"/>
+    <row r="452" ht="15.75" customHeight="1"/>
+    <row r="453" ht="15.75" customHeight="1"/>
+    <row r="454" ht="15.75" customHeight="1"/>
+    <row r="455" ht="15.75" customHeight="1"/>
+    <row r="456" ht="15.75" customHeight="1"/>
+    <row r="457" ht="15.75" customHeight="1"/>
+    <row r="458" ht="15.75" customHeight="1"/>
+    <row r="459" ht="15.75" customHeight="1"/>
+    <row r="460" ht="15.75" customHeight="1"/>
+    <row r="461" ht="15.75" customHeight="1"/>
+    <row r="462" ht="15.75" customHeight="1"/>
+    <row r="463" ht="15.75" customHeight="1"/>
+    <row r="464" ht="15.75" customHeight="1"/>
+    <row r="465" ht="15.75" customHeight="1"/>
+    <row r="466" ht="15.75" customHeight="1"/>
+    <row r="467" ht="15.75" customHeight="1"/>
+    <row r="468" ht="15.75" customHeight="1"/>
+    <row r="469" ht="15.75" customHeight="1"/>
+    <row r="470" ht="15.75" customHeight="1"/>
+    <row r="471" ht="15.75" customHeight="1"/>
+    <row r="472" ht="15.75" customHeight="1"/>
+    <row r="473" ht="15.75" customHeight="1"/>
+    <row r="474" ht="15.75" customHeight="1"/>
+    <row r="475" ht="15.75" customHeight="1"/>
+    <row r="476" ht="15.75" customHeight="1"/>
+    <row r="477" ht="15.75" customHeight="1"/>
+    <row r="478" ht="15.75" customHeight="1"/>
+    <row r="479" ht="15.75" customHeight="1"/>
+    <row r="480" ht="15.75" customHeight="1"/>
+    <row r="481" ht="15.75" customHeight="1"/>
+    <row r="482" ht="15.75" customHeight="1"/>
+    <row r="483" ht="15.75" customHeight="1"/>
+    <row r="484" ht="15.75" customHeight="1"/>
+    <row r="485" ht="15.75" customHeight="1"/>
+    <row r="486" ht="15.75" customHeight="1"/>
+    <row r="487" ht="15.75" customHeight="1"/>
+    <row r="488" ht="15.75" customHeight="1"/>
+    <row r="489" ht="15.75" customHeight="1"/>
+    <row r="490" ht="15.75" customHeight="1"/>
+    <row r="491" ht="15.75" customHeight="1"/>
+    <row r="492" ht="15.75" customHeight="1"/>
+    <row r="493" ht="15.75" customHeight="1"/>
+    <row r="494" ht="15.75" customHeight="1"/>
+    <row r="495" ht="15.75" customHeight="1"/>
+    <row r="496" ht="15.75" customHeight="1"/>
+    <row r="497" ht="15.75" customHeight="1"/>
+    <row r="498" ht="15.75" customHeight="1"/>
+    <row r="499" ht="15.75" customHeight="1"/>
+    <row r="500" ht="15.75" customHeight="1"/>
+    <row r="501" ht="15.75" customHeight="1"/>
+    <row r="502" ht="15.75" customHeight="1"/>
+    <row r="503" ht="15.75" customHeight="1"/>
+    <row r="504" ht="15.75" customHeight="1"/>
+    <row r="505" ht="15.75" customHeight="1"/>
+    <row r="506" ht="15.75" customHeight="1"/>
+    <row r="507" ht="15.75" customHeight="1"/>
+    <row r="508" ht="15.75" customHeight="1"/>
+    <row r="509" ht="15.75" customHeight="1"/>
+    <row r="510" ht="15.75" customHeight="1"/>
+    <row r="511" ht="15.75" customHeight="1"/>
+    <row r="512" ht="15.75" customHeight="1"/>
+    <row r="513" ht="15.75" customHeight="1"/>
+    <row r="514" ht="15.75" customHeight="1"/>
+    <row r="515" ht="15.75" customHeight="1"/>
+    <row r="516" ht="15.75" customHeight="1"/>
+    <row r="517" ht="15.75" customHeight="1"/>
+    <row r="518" ht="15.75" customHeight="1"/>
+    <row r="519" ht="15.75" customHeight="1"/>
+    <row r="520" ht="15.75" customHeight="1"/>
+    <row r="521" ht="15.75" customHeight="1"/>
+    <row r="522" ht="15.75" customHeight="1"/>
+    <row r="523" ht="15.75" customHeight="1"/>
+    <row r="524" ht="15.75" customHeight="1"/>
+    <row r="525" ht="15.75" customHeight="1"/>
+    <row r="526" ht="15.75" customHeight="1"/>
+    <row r="527" ht="15.75" customHeight="1"/>
+    <row r="528" ht="15.75" customHeight="1"/>
+    <row r="529" ht="15.75" customHeight="1"/>
+    <row r="530" ht="15.75" customHeight="1"/>
+    <row r="531" ht="15.75" customHeight="1"/>
+    <row r="532" ht="15.75" customHeight="1"/>
+    <row r="533" ht="15.75" customHeight="1"/>
+    <row r="534" ht="15.75" customHeight="1"/>
+    <row r="535" ht="15.75" customHeight="1"/>
+    <row r="536" ht="15.75" customHeight="1"/>
+    <row r="537" ht="15.75" customHeight="1"/>
+    <row r="538" ht="15.75" customHeight="1"/>
+    <row r="539" ht="15.75" customHeight="1"/>
+    <row r="540" ht="15.75" customHeight="1"/>
+    <row r="541" ht="15.75" customHeight="1"/>
+    <row r="542" ht="15.75" customHeight="1"/>
+    <row r="543" ht="15.75" customHeight="1"/>
+    <row r="544" ht="15.75" customHeight="1"/>
+    <row r="545" ht="15.75" customHeight="1"/>
+    <row r="546" ht="15.75" customHeight="1"/>
+    <row r="547" ht="15.75" customHeight="1"/>
+    <row r="548" ht="15.75" customHeight="1"/>
+    <row r="549" ht="15.75" customHeight="1"/>
+    <row r="550" ht="15.75" customHeight="1"/>
+    <row r="551" ht="15.75" customHeight="1"/>
+    <row r="552" ht="15.75" customHeight="1"/>
+    <row r="553" ht="15.75" customHeight="1"/>
+    <row r="554" ht="15.75" customHeight="1"/>
+    <row r="555" ht="15.75" customHeight="1"/>
+    <row r="556" ht="15.75" customHeight="1"/>
+    <row r="557" ht="15.75" customHeight="1"/>
+    <row r="558" ht="15.75" customHeight="1"/>
+    <row r="559" ht="15.75" customHeight="1"/>
+    <row r="560" ht="15.75" customHeight="1"/>
+    <row r="561" ht="15.75" customHeight="1"/>
+    <row r="562" ht="15.75" customHeight="1"/>
+    <row r="563" ht="15.75" customHeight="1"/>
+    <row r="564" ht="15.75" customHeight="1"/>
+    <row r="565" ht="15.75" customHeight="1"/>
+    <row r="566" ht="15.75" customHeight="1"/>
+    <row r="567" ht="15.75" customHeight="1"/>
+    <row r="568" ht="15.75" customHeight="1"/>
+    <row r="569" ht="15.75" customHeight="1"/>
+    <row r="570" ht="15.75" customHeight="1"/>
+    <row r="571" ht="15.75" customHeight="1"/>
+    <row r="572" ht="15.75" customHeight="1"/>
+    <row r="573" ht="15.75" customHeight="1"/>
+    <row r="574" ht="15.75" customHeight="1"/>
+    <row r="575" ht="15.75" customHeight="1"/>
+    <row r="576" ht="15.75" customHeight="1"/>
+    <row r="577" ht="15.75" customHeight="1"/>
+    <row r="578" ht="15.75" customHeight="1"/>
+    <row r="579" ht="15.75" customHeight="1"/>
+    <row r="580" ht="15.75" customHeight="1"/>
+    <row r="581" ht="15.75" customHeight="1"/>
+    <row r="582" ht="15.75" customHeight="1"/>
+    <row r="583" ht="15.75" customHeight="1"/>
+    <row r="584" ht="15.75" customHeight="1"/>
+    <row r="585" ht="15.75" customHeight="1"/>
+    <row r="586" ht="15.75" customHeight="1"/>
+    <row r="587" ht="15.75" customHeight="1"/>
+    <row r="588" ht="15.75" customHeight="1"/>
+    <row r="589" ht="15.75" customHeight="1"/>
+    <row r="590" ht="15.75" customHeight="1"/>
+    <row r="591" ht="15.75" customHeight="1"/>
+    <row r="592" ht="15.75" customHeight="1"/>
+    <row r="593" ht="15.75" customHeight="1"/>
+    <row r="594" ht="15.75" customHeight="1"/>
+    <row r="595" ht="15.75" customHeight="1"/>
+    <row r="596" ht="15.75" customHeight="1"/>
+    <row r="597" ht="15.75" customHeight="1"/>
+    <row r="598" ht="15.75" customHeight="1"/>
+    <row r="599" ht="15.75" customHeight="1"/>
+    <row r="600" ht="15.75" customHeight="1"/>
+    <row r="601" ht="15.75" customHeight="1"/>
+    <row r="602" ht="15.75" customHeight="1"/>
+    <row r="603" ht="15.75" customHeight="1"/>
+    <row r="604" ht="15.75" customHeight="1"/>
+    <row r="605" ht="15.75" customHeight="1"/>
+    <row r="606" ht="15.75" customHeight="1"/>
+    <row r="607" ht="15.75" customHeight="1"/>
+    <row r="608" ht="15.75" customHeight="1"/>
+    <row r="609" ht="15.75" customHeight="1"/>
+    <row r="610" ht="15.75" customHeight="1"/>
+    <row r="611" ht="15.75" customHeight="1"/>
+    <row r="612" ht="15.75" customHeight="1"/>
+    <row r="613" ht="15.75" customHeight="1"/>
+    <row r="614" ht="15.75" customHeight="1"/>
+    <row r="615" ht="15.75" customHeight="1"/>
+    <row r="616" ht="15.75" customHeight="1"/>
+    <row r="617" ht="15.75" customHeight="1"/>
+    <row r="618" ht="15.75" customHeight="1"/>
+    <row r="619" ht="15.75" customHeight="1"/>
+    <row r="620" ht="15.75" customHeight="1"/>
+    <row r="621" ht="15.75" customHeight="1"/>
+    <row r="622" ht="15.75" customHeight="1"/>
+    <row r="623" ht="15.75" customHeight="1"/>
+    <row r="624" ht="15.75" customHeight="1"/>
+    <row r="625" ht="15.75" customHeight="1"/>
+    <row r="626" ht="15.75" customHeight="1"/>
+    <row r="627" ht="15.75" customHeight="1"/>
+    <row r="628" ht="15.75" customHeight="1"/>
+    <row r="629" ht="15.75" customHeight="1"/>
+    <row r="630" ht="15.75" customHeight="1"/>
+    <row r="631" ht="15.75" customHeight="1"/>
+    <row r="632" ht="15.75" customHeight="1"/>
+    <row r="633" ht="15.75" customHeight="1"/>
+    <row r="634" ht="15.75" customHeight="1"/>
+    <row r="635" ht="15.75" customHeight="1"/>
+    <row r="636" ht="15.75" customHeight="1"/>
+    <row r="637" ht="15.75" customHeight="1"/>
+    <row r="638" ht="15.75" customHeight="1"/>
+    <row r="639" ht="15.75" customHeight="1"/>
+    <row r="640" ht="15.75" customHeight="1"/>
+    <row r="641" ht="15.75" customHeight="1"/>
+    <row r="642" ht="15.75" customHeight="1"/>
+    <row r="643" ht="15.75" customHeight="1"/>
+    <row r="644" ht="15.75" customHeight="1"/>
+    <row r="645" ht="15.75" customHeight="1"/>
+    <row r="646" ht="15.75" customHeight="1"/>
+    <row r="647" ht="15.75" customHeight="1"/>
+    <row r="648" ht="15.75" customHeight="1"/>
+    <row r="649" ht="15.75" customHeight="1"/>
+    <row r="650" ht="15.75" customHeight="1"/>
+    <row r="651" ht="15.75" customHeight="1"/>
+    <row r="652" ht="15.75" customHeight="1"/>
+    <row r="653" ht="15.75" customHeight="1"/>
+    <row r="654" ht="15.75" customHeight="1"/>
+    <row r="655" ht="15.75" customHeight="1"/>
+    <row r="656" ht="15.75" customHeight="1"/>
+    <row r="657" ht="15.75" customHeight="1"/>
+    <row r="658" ht="15.75" customHeight="1"/>
+    <row r="659" ht="15.75" customHeight="1"/>
+    <row r="660" ht="15.75" customHeight="1"/>
+    <row r="661" ht="15.75" customHeight="1"/>
+    <row r="662" ht="15.75" customHeight="1"/>
+    <row r="663" ht="15.75" customHeight="1"/>
+    <row r="664" ht="15.75" customHeight="1"/>
+    <row r="665" ht="15.75" customHeight="1"/>
+    <row r="666" ht="15.75" customHeight="1"/>
+    <row r="667" ht="15.75" customHeight="1"/>
+    <row r="668" ht="15.75" customHeight="1"/>
+    <row r="669" ht="15.75" customHeight="1"/>
+    <row r="670" ht="15.75" customHeight="1"/>
+    <row r="671" ht="15.75" customHeight="1"/>
+    <row r="672" ht="15.75" customHeight="1"/>
+    <row r="673" ht="15.75" customHeight="1"/>
+    <row r="674" ht="15.75" customHeight="1"/>
+    <row r="675" ht="15.75" customHeight="1"/>
+    <row r="676" ht="15.75" customHeight="1"/>
+    <row r="677" ht="15.75" customHeight="1"/>
+    <row r="678" ht="15.75" customHeight="1"/>
+    <row r="679" ht="15.75" customHeight="1"/>
+    <row r="680" ht="15.75" customHeight="1"/>
+    <row r="681" ht="15.75" customHeight="1"/>
+    <row r="682" ht="15.75" customHeight="1"/>
+    <row r="683" ht="15.75" customHeight="1"/>
+    <row r="684" ht="15.75" customHeight="1"/>
+    <row r="685" ht="15.75" customHeight="1"/>
+    <row r="686" ht="15.75" customHeight="1"/>
+    <row r="687" ht="15.75" customHeight="1"/>
+    <row r="688" ht="15.75" customHeight="1"/>
+    <row r="689" ht="15.75" customHeight="1"/>
+    <row r="690" ht="15.75" customHeight="1"/>
+    <row r="691" ht="15.75" customHeight="1"/>
+    <row r="692" ht="15.75" customHeight="1"/>
+    <row r="693" ht="15.75" customHeight="1"/>
+    <row r="694" ht="15.75" customHeight="1"/>
+    <row r="695" ht="15.75" customHeight="1"/>
+    <row r="696" ht="15.75" customHeight="1"/>
+    <row r="697" ht="15.75" customHeight="1"/>
+    <row r="698" ht="15.75" customHeight="1"/>
+    <row r="699" ht="15.75" customHeight="1"/>
+    <row r="700" ht="15.75" customHeight="1"/>
+    <row r="701" ht="15.75" customHeight="1"/>
+    <row r="702" ht="15.75" customHeight="1"/>
+    <row r="703" ht="15.75" customHeight="1"/>
+    <row r="704" ht="15.75" customHeight="1"/>
+    <row r="705" ht="15.75" customHeight="1"/>
+    <row r="706" ht="15.75" customHeight="1"/>
+    <row r="707" ht="15.75" customHeight="1"/>
+    <row r="708" ht="15.75" customHeight="1"/>
+    <row r="709" ht="15.75" customHeight="1"/>
+    <row r="710" ht="15.75" customHeight="1"/>
+    <row r="711" ht="15.75" customHeight="1"/>
+    <row r="712" ht="15.75" customHeight="1"/>
+    <row r="713" ht="15.75" customHeight="1"/>
+    <row r="714" ht="15.75" customHeight="1"/>
+    <row r="715" ht="15.75" customHeight="1"/>
+    <row r="716" ht="15.75" customHeight="1"/>
+    <row r="717" ht="15.75" customHeight="1"/>
+    <row r="718" ht="15.75" customHeight="1"/>
+    <row r="719" ht="15.75" customHeight="1"/>
+    <row r="720" ht="15.75" customHeight="1"/>
+    <row r="721" ht="15.75" customHeight="1"/>
+    <row r="722" ht="15.75" customHeight="1"/>
+    <row r="723" ht="15.75" customHeight="1"/>
+    <row r="724" ht="15.75" customHeight="1"/>
+    <row r="725" ht="15.75" customHeight="1"/>
+    <row r="726" ht="15.75" customHeight="1"/>
+    <row r="727" ht="15.75" customHeight="1"/>
+    <row r="728" ht="15.75" customHeight="1"/>
+    <row r="729" ht="15.75" customHeight="1"/>
+    <row r="730" ht="15.75" customHeight="1"/>
+    <row r="731" ht="15.75" customHeight="1"/>
+    <row r="732" ht="15.75" customHeight="1"/>
+    <row r="733" ht="15.75" customHeight="1"/>
+    <row r="734" ht="15.75" customHeight="1"/>
+    <row r="735" ht="15.75" customHeight="1"/>
+    <row r="736" ht="15.75" customHeight="1"/>
+    <row r="737" ht="15.75" customHeight="1"/>
+    <row r="738" ht="15.75" customHeight="1"/>
+    <row r="739" ht="15.75" customHeight="1"/>
+    <row r="740" ht="15.75" customHeight="1"/>
+    <row r="741" ht="15.75" customHeight="1"/>
+    <row r="742" ht="15.75" customHeight="1"/>
+    <row r="743" ht="15.75" customHeight="1"/>
+    <row r="744" ht="15.75" customHeight="1"/>
+    <row r="745" ht="15.75" customHeight="1"/>
+    <row r="746" ht="15.75" customHeight="1"/>
+    <row r="747" ht="15.75" customHeight="1"/>
+    <row r="748" ht="15.75" customHeight="1"/>
+    <row r="749" ht="15.75" customHeight="1"/>
+    <row r="750" ht="15.75" customHeight="1"/>
+    <row r="751" ht="15.75" customHeight="1"/>
+    <row r="752" ht="15.75" customHeight="1"/>
+    <row r="753" ht="15.75" customHeight="1"/>
+    <row r="754" ht="15.75" customHeight="1"/>
+    <row r="755" ht="15.75" customHeight="1"/>
+    <row r="756" ht="15.75" customHeight="1"/>
+    <row r="757" ht="15.75" customHeight="1"/>
+    <row r="758" ht="15.75" customHeight="1"/>
+    <row r="759" ht="15.75" customHeight="1"/>
+    <row r="760" ht="15.75" customHeight="1"/>
+    <row r="761" ht="15.75" customHeight="1"/>
+    <row r="762" ht="15.75" customHeight="1"/>
+    <row r="763" ht="15.75" customHeight="1"/>
+    <row r="764" ht="15.75" customHeight="1"/>
+    <row r="765" ht="15.75" customHeight="1"/>
+    <row r="766" ht="15.75" customHeight="1"/>
+    <row r="767" ht="15.75" customHeight="1"/>
+    <row r="768" ht="15.75" customHeight="1"/>
+    <row r="769" ht="15.75" customHeight="1"/>
+    <row r="770" ht="15.75" customHeight="1"/>
+    <row r="771" ht="15.75" customHeight="1"/>
+    <row r="772" ht="15.75" customHeight="1"/>
+    <row r="773" ht="15.75" customHeight="1"/>
+    <row r="774" ht="15.75" customHeight="1"/>
+    <row r="775" ht="15.75" customHeight="1"/>
+    <row r="776" ht="15.75" customHeight="1"/>
+    <row r="777" ht="15.75" customHeight="1"/>
+    <row r="778" ht="15.75" customHeight="1"/>
+    <row r="779" ht="15.75" customHeight="1"/>
+    <row r="780" ht="15.75" customHeight="1"/>
+    <row r="781" ht="15.75" customHeight="1"/>
+    <row r="782" ht="15.75" customHeight="1"/>
+    <row r="783" ht="15.75" customHeight="1"/>
+    <row r="784" ht="15.75" customHeight="1"/>
+    <row r="785" ht="15.75" customHeight="1"/>
+    <row r="786" ht="15.75" customHeight="1"/>
+    <row r="787" ht="15.75" customHeight="1"/>
+    <row r="788" ht="15.75" customHeight="1"/>
+    <row r="789" ht="15.75" customHeight="1"/>
+    <row r="790" ht="15.75" customHeight="1"/>
+    <row r="791" ht="15.75" customHeight="1"/>
+    <row r="792" ht="15.75" customHeight="1"/>
+    <row r="793" ht="15.75" customHeight="1"/>
+    <row r="794" ht="15.75" customHeight="1"/>
+    <row r="795" ht="15.75" customHeight="1"/>
+    <row r="796" ht="15.75" customHeight="1"/>
+    <row r="797" ht="15.75" customHeight="1"/>
+    <row r="798" ht="15.75" customHeight="1"/>
+    <row r="799" ht="15.75" customHeight="1"/>
+    <row r="800" ht="15.75" customHeight="1"/>
+    <row r="801" ht="15.75" customHeight="1"/>
+    <row r="802" ht="15.75" customHeight="1"/>
+    <row r="803" ht="15.75" customHeight="1"/>
+    <row r="804" ht="15.75" customHeight="1"/>
+    <row r="805" ht="15.75" customHeight="1"/>
+    <row r="806" ht="15.75" customHeight="1"/>
+    <row r="807" ht="15.75" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="G4:Q11 G13:Q16 G23:Q25">
@@ -16042,16 +16031,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:U118"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="6.1640625" customWidth="1"/>
+    <col min="1" max="1" width="6.1328125" customWidth="1"/>
     <col min="2" max="9" width="20.6640625" customWidth="1"/>
-    <col min="10" max="11" width="11.1640625" customWidth="1"/>
+    <col min="10" max="11" width="11.1328125" customWidth="1"/>
     <col min="12" max="12" width="20.6640625" customWidth="1"/>
     <col min="13" max="13" width="5.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:15" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:15" ht="13.9">
       <c r="B2" s="34" t="s">
         <v>52</v>
       </c>
@@ -16066,7 +16055,7 @@
       <c r="K2" s="35"/>
       <c r="L2" s="35"/>
     </row>
-    <row r="3" spans="2:15" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:15" ht="13.15">
       <c r="B3" s="106" t="s">
         <v>136</v>
       </c>
@@ -16081,7 +16070,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="4" spans="2:15" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:15">
       <c r="B4" s="97" t="s">
         <v>391</v>
       </c>
@@ -16113,7 +16102,7 @@
       </c>
       <c r="J4" s="305"/>
     </row>
-    <row r="5" spans="2:15" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:15">
       <c r="B5" s="187" t="s">
         <v>105</v>
       </c>
@@ -16141,7 +16130,7 @@
       </c>
       <c r="J5" s="305"/>
     </row>
-    <row r="6" spans="2:15" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:15" ht="13.25" customHeight="1">
       <c r="B6" s="136" t="s">
         <v>194</v>
       </c>
@@ -16174,7 +16163,7 @@
       <c r="J6" s="305"/>
       <c r="N6" s="135"/>
     </row>
-    <row r="7" spans="2:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:15" ht="12.75" customHeight="1">
       <c r="B7" s="318" t="s">
         <v>428</v>
       </c>
@@ -16204,7 +16193,7 @@
       <c r="N7" s="304"/>
       <c r="O7" s="304"/>
     </row>
-    <row r="8" spans="2:15" ht="14" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:15" ht="13.15">
       <c r="B8" s="136" t="s">
         <v>424</v>
       </c>
@@ -16239,7 +16228,7 @@
       <c r="N8" s="304"/>
       <c r="O8" s="304"/>
     </row>
-    <row r="9" spans="2:15" ht="14" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:15" ht="13.15" thickBot="1">
       <c r="B9" s="189" t="str">
         <f>"*"&amp;Thesis!E15</f>
         <v>*CNY</v>
@@ -16265,7 +16254,7 @@
       <c r="N9" s="304"/>
       <c r="O9" s="304"/>
     </row>
-    <row r="10" spans="2:15" ht="14" thickTop="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:15" ht="13.5" thickTop="1">
       <c r="B10" s="107" t="s">
         <v>425</v>
       </c>
@@ -16287,7 +16276,7 @@
       <c r="N10" s="304"/>
       <c r="O10" s="304"/>
     </row>
-    <row r="11" spans="2:15" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:15" ht="13.15">
       <c r="B11" s="136" t="s">
         <v>423</v>
       </c>
@@ -16303,7 +16292,7 @@
       <c r="I11" s="307"/>
       <c r="J11" s="307"/>
     </row>
-    <row r="13" spans="2:15" ht="16" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:15" ht="13.9">
       <c r="B13" s="34" t="s">
         <v>426</v>
       </c>
@@ -16318,7 +16307,7 @@
       <c r="K13" s="35"/>
       <c r="L13" s="35"/>
     </row>
-    <row r="14" spans="2:15" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:15" ht="13.15">
       <c r="B14" s="106" t="s">
         <v>397</v>
       </c>
@@ -16336,7 +16325,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="15" spans="2:15" x14ac:dyDescent="0.15">
+    <row r="15" spans="2:15">
       <c r="B15" s="139" t="s">
         <v>419</v>
       </c>
@@ -16361,7 +16350,7 @@
       </c>
       <c r="J15" s="126"/>
     </row>
-    <row r="16" spans="2:15" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:15" ht="13.25" customHeight="1">
       <c r="B16" s="114" t="s">
         <v>420</v>
       </c>
@@ -16377,7 +16366,7 @@
         <v>2.38559171477595E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:21" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:21" ht="13.25" customHeight="1">
       <c r="B17" s="308" t="s">
         <v>547</v>
       </c>
@@ -16396,7 +16385,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="18" spans="1:21" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:21" ht="13.25" customHeight="1">
       <c r="B18" s="308" t="s">
         <v>421</v>
       </c>
@@ -16423,10 +16412,10 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:21">
       <c r="L19" s="275"/>
     </row>
-    <row r="20" spans="1:21" ht="14" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:21" ht="13.15">
       <c r="A20" s="121" t="s">
         <v>397</v>
       </c>
@@ -16465,7 +16454,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:21">
       <c r="A21" s="302" t="str">
         <f t="shared" ref="A21:A50" si="0">IF($C$15&lt;B21,"",IF(B21&gt;=$F$15,"II","I"))</f>
         <v>I</v>
@@ -16514,7 +16503,7 @@
         <v>28450593708.666355</v>
       </c>
     </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:21">
       <c r="A22" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -16563,7 +16552,7 @@
         <v>27160194606.046497</v>
       </c>
     </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:21">
       <c r="A23" s="302" t="str">
         <f t="shared" si="0"/>
         <v>II</v>
@@ -16620,7 +16609,7 @@
       <c r="T23" s="275"/>
       <c r="U23" s="275"/>
     </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:21">
       <c r="A24" s="302" t="str">
         <f t="shared" si="0"/>
         <v>II</v>
@@ -16677,7 +16666,7 @@
       <c r="T24" s="275"/>
       <c r="U24" s="275"/>
     </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:21">
       <c r="A25" s="302" t="str">
         <f t="shared" si="0"/>
         <v>II</v>
@@ -16734,7 +16723,7 @@
       <c r="T25" s="275"/>
       <c r="U25" s="275"/>
     </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:21">
       <c r="A26" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -16783,7 +16772,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:21">
       <c r="A27" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -16832,7 +16821,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:21">
       <c r="A28" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -16881,7 +16870,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:21">
       <c r="A29" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -16930,7 +16919,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:21">
       <c r="A30" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -16979,7 +16968,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:21">
       <c r="A31" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17028,7 +17017,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:21">
       <c r="A32" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17077,7 +17066,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:21">
       <c r="A33" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17134,7 +17123,7 @@
       <c r="T33" s="275"/>
       <c r="U33" s="275"/>
     </row>
-    <row r="34" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:21">
       <c r="A34" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17191,7 +17180,7 @@
       <c r="T34" s="275"/>
       <c r="U34" s="275"/>
     </row>
-    <row r="35" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:21">
       <c r="A35" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17248,7 +17237,7 @@
       <c r="T35" s="275"/>
       <c r="U35" s="275"/>
     </row>
-    <row r="36" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:21">
       <c r="A36" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17297,7 +17286,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:21">
       <c r="A37" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17346,7 +17335,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:21">
       <c r="A38" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17395,7 +17384,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:21">
       <c r="A39" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17444,7 +17433,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:21">
       <c r="A40" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17493,7 +17482,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:21">
       <c r="A41" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17542,7 +17531,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:21">
       <c r="A42" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17591,7 +17580,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:21">
       <c r="A43" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17640,7 +17629,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:21">
       <c r="A44" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17689,7 +17678,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:21">
       <c r="A45" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17738,7 +17727,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:21">
       <c r="A46" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17787,7 +17776,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:21">
       <c r="A47" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17844,7 +17833,7 @@
       <c r="T47" s="275"/>
       <c r="U47" s="275"/>
     </row>
-    <row r="48" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:21">
       <c r="A48" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17901,7 +17890,7 @@
       <c r="T48" s="275"/>
       <c r="U48" s="275"/>
     </row>
-    <row r="49" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:21">
       <c r="A49" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17958,7 +17947,7 @@
       <c r="T49" s="275"/>
       <c r="U49" s="275"/>
     </row>
-    <row r="50" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:21">
       <c r="A50" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -18015,7 +18004,7 @@
       <c r="T50" s="275"/>
       <c r="U50" s="275"/>
     </row>
-    <row r="51" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:21">
       <c r="A51" s="315" t="s">
         <v>416</v>
       </c>
@@ -18061,7 +18050,7 @@
         <v>285808228079.48792</v>
       </c>
     </row>
-    <row r="52" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:21" ht="13.15">
       <c r="G52" s="111"/>
       <c r="H52" s="111"/>
       <c r="I52" s="111"/>
@@ -18074,10 +18063,10 @@
         <v>405304783322.55359</v>
       </c>
     </row>
-    <row r="53" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:21">
       <c r="C53" s="111"/>
     </row>
-    <row r="54" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:21" ht="13.15">
       <c r="B54" s="115" t="s">
         <v>108</v>
       </c>
@@ -18092,7 +18081,7 @@
       <c r="K54" s="113"/>
       <c r="L54" s="113"/>
     </row>
-    <row r="55" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:21" ht="13.15">
       <c r="A55" s="125">
         <f>L52</f>
         <v>405304783322.55359</v>
@@ -18124,7 +18113,7 @@
       <c r="K55" s="123"/>
       <c r="L55" s="123"/>
     </row>
-    <row r="56" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:21" ht="13.15">
       <c r="A56" s="131">
         <v>1</v>
       </c>
@@ -18151,7 +18140,7 @@
       <c r="K56" s="295"/>
       <c r="L56" s="295"/>
     </row>
-    <row r="57" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:21" ht="13.15">
       <c r="A57" s="131">
         <v>2</v>
       </c>
@@ -18177,7 +18166,7 @@
       <c r="K57" s="295"/>
       <c r="L57" s="295"/>
     </row>
-    <row r="58" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:21" ht="13.15">
       <c r="A58" s="131">
         <v>3</v>
       </c>
@@ -18203,7 +18192,7 @@
       <c r="K58" s="295"/>
       <c r="L58" s="295"/>
     </row>
-    <row r="59" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:21" ht="13.15">
       <c r="A59" s="131">
         <v>4</v>
       </c>
@@ -18229,7 +18218,7 @@
       <c r="K59" s="295"/>
       <c r="L59" s="295"/>
     </row>
-    <row r="60" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:21" ht="13.15">
       <c r="A60" s="131">
         <v>5</v>
       </c>
@@ -18255,7 +18244,7 @@
       <c r="K60" s="295"/>
       <c r="L60" s="295"/>
     </row>
-    <row r="61" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:21" ht="13.15">
       <c r="A61" s="131">
         <v>6</v>
       </c>
@@ -18281,7 +18270,7 @@
       <c r="K61" s="295"/>
       <c r="L61" s="295"/>
     </row>
-    <row r="62" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:21" ht="13.15">
       <c r="A62" s="131">
         <v>7</v>
       </c>
@@ -18307,7 +18296,7 @@
       <c r="K62" s="295"/>
       <c r="L62" s="295"/>
     </row>
-    <row r="63" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:21" ht="13.15">
       <c r="A63" s="131">
         <v>8</v>
       </c>
@@ -18333,7 +18322,7 @@
       <c r="K63" s="295"/>
       <c r="L63" s="295"/>
     </row>
-    <row r="64" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:21" ht="13.15">
       <c r="A64" s="131">
         <v>9</v>
       </c>
@@ -18359,7 +18348,7 @@
       <c r="K64" s="295"/>
       <c r="L64" s="295"/>
     </row>
-    <row r="65" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:21" ht="13.15">
       <c r="A65" s="131">
         <v>10</v>
       </c>
@@ -18385,7 +18374,7 @@
       <c r="K65" s="295"/>
       <c r="L65" s="295"/>
     </row>
-    <row r="66" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:21" ht="13.15">
       <c r="A66" s="131">
         <v>15</v>
       </c>
@@ -18420,7 +18409,7 @@
       <c r="T66" s="275"/>
       <c r="U66" s="275"/>
     </row>
-    <row r="67" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:21" ht="13.15">
       <c r="A67" s="132">
         <v>20</v>
       </c>
@@ -18455,7 +18444,7 @@
       <c r="T67" s="275"/>
       <c r="U67" s="275"/>
     </row>
-    <row r="68" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:21" ht="13.15">
       <c r="A68" s="132">
         <v>25</v>
       </c>
@@ -18490,7 +18479,7 @@
       <c r="T68" s="275"/>
       <c r="U68" s="275"/>
     </row>
-    <row r="69" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:21" ht="13.15">
       <c r="A69" s="132">
         <v>30</v>
       </c>
@@ -18525,7 +18514,7 @@
       <c r="T69" s="275"/>
       <c r="U69" s="275"/>
     </row>
-    <row r="70" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:21">
       <c r="C70" s="275"/>
       <c r="D70" s="111"/>
       <c r="E70" s="111"/>
@@ -18546,7 +18535,7 @@
       <c r="T70" s="275"/>
       <c r="U70" s="275"/>
     </row>
-    <row r="71" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:21" ht="13.15">
       <c r="B71" s="115" t="s">
         <v>109</v>
       </c>
@@ -18570,7 +18559,7 @@
       <c r="T71" s="275"/>
       <c r="U71" s="275"/>
     </row>
-    <row r="72" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:21" ht="13.15">
       <c r="B72" s="124">
         <f>B55</f>
         <v>0</v>
@@ -18598,7 +18587,7 @@
       <c r="K72" s="124"/>
       <c r="L72" s="124"/>
     </row>
-    <row r="73" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:21" ht="13.15">
       <c r="A73" s="131">
         <v>0</v>
       </c>
@@ -18629,7 +18618,7 @@
       <c r="K73" s="296"/>
       <c r="L73" s="296"/>
     </row>
-    <row r="74" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:21" ht="13.15">
       <c r="A74" s="131">
         <v>1</v>
       </c>
@@ -18660,7 +18649,7 @@
       <c r="K74" s="296"/>
       <c r="L74" s="296"/>
     </row>
-    <row r="75" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:21" ht="13.15">
       <c r="A75" s="131">
         <v>2</v>
       </c>
@@ -18691,7 +18680,7 @@
       <c r="K75" s="296"/>
       <c r="L75" s="296"/>
     </row>
-    <row r="76" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:21" ht="13.15">
       <c r="A76" s="131">
         <v>3</v>
       </c>
@@ -18722,7 +18711,7 @@
       <c r="K76" s="296"/>
       <c r="L76" s="296"/>
     </row>
-    <row r="77" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:21" ht="13.15">
       <c r="A77" s="131">
         <v>4</v>
       </c>
@@ -18753,7 +18742,7 @@
       <c r="K77" s="296"/>
       <c r="L77" s="296"/>
     </row>
-    <row r="78" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:21" ht="13.15">
       <c r="A78" s="131">
         <v>5</v>
       </c>
@@ -18784,7 +18773,7 @@
       <c r="K78" s="296"/>
       <c r="L78" s="296"/>
     </row>
-    <row r="79" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:21" ht="13.15">
       <c r="A79" s="131">
         <v>6</v>
       </c>
@@ -18815,7 +18804,7 @@
       <c r="K79" s="296"/>
       <c r="L79" s="296"/>
     </row>
-    <row r="80" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:21" ht="13.15">
       <c r="A80" s="131">
         <f t="shared" ref="A80" si="12">A62</f>
         <v>7</v>
@@ -18847,7 +18836,7 @@
       <c r="K80" s="296"/>
       <c r="L80" s="296"/>
     </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:12" ht="13.15">
       <c r="A81" s="131">
         <v>8</v>
       </c>
@@ -18878,7 +18867,7 @@
       <c r="K81" s="296"/>
       <c r="L81" s="296"/>
     </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:12" ht="13.15">
       <c r="A82" s="131">
         <f t="shared" ref="A82" si="13">A64</f>
         <v>9</v>
@@ -18910,7 +18899,7 @@
       <c r="K82" s="296"/>
       <c r="L82" s="296"/>
     </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:12" ht="13.15">
       <c r="A83" s="131">
         <f t="shared" ref="A83:A87" si="14">A65</f>
         <v>10</v>
@@ -18942,7 +18931,7 @@
       <c r="K83" s="296"/>
       <c r="L83" s="296"/>
     </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:12" ht="13.15">
       <c r="A84" s="131">
         <f t="shared" si="14"/>
         <v>15</v>
@@ -18974,7 +18963,7 @@
       <c r="K84" s="296"/>
       <c r="L84" s="296"/>
     </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:12" ht="13.15">
       <c r="A85" s="132">
         <f t="shared" si="14"/>
         <v>20</v>
@@ -19006,7 +18995,7 @@
       <c r="K85" s="296"/>
       <c r="L85" s="296"/>
     </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:12" ht="13.15">
       <c r="A86" s="132">
         <f t="shared" si="14"/>
         <v>25</v>
@@ -19038,7 +19027,7 @@
       <c r="K86" s="296"/>
       <c r="L86" s="296"/>
     </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:12" ht="13.15">
       <c r="A87" s="132">
         <f t="shared" si="14"/>
         <v>30</v>
@@ -19070,7 +19059,7 @@
       <c r="K87" s="296"/>
       <c r="L87" s="296"/>
     </row>
-    <row r="89" spans="1:12" ht="14" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:12" ht="13.15">
       <c r="B89" s="153" t="s">
         <v>101</v>
       </c>
@@ -19093,7 +19082,7 @@
       <c r="K89" s="323"/>
       <c r="L89" s="323"/>
     </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:12">
       <c r="B90" s="120" t="str">
         <f>Scenarios!B29</f>
         <v>Snowball Scenario</v>
@@ -19121,7 +19110,7 @@
       <c r="K90" s="297"/>
       <c r="L90" s="297"/>
     </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:12">
       <c r="B91" s="120" t="str">
         <f>Scenarios!B22</f>
         <v>Optimistic</v>
@@ -19149,7 +19138,7 @@
       <c r="K91" s="297"/>
       <c r="L91" s="297"/>
     </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:12">
       <c r="B92" s="120" t="str">
         <f>Scenarios!B23</f>
         <v>Base</v>
@@ -19177,7 +19166,7 @@
       <c r="K92" s="297"/>
       <c r="L92" s="297"/>
     </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:12">
       <c r="B93" s="120" t="str">
         <f>Scenarios!B24</f>
         <v>Pessimistic</v>
@@ -19205,7 +19194,7 @@
       <c r="K93" s="297"/>
       <c r="L93" s="297"/>
     </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:12">
       <c r="B94" s="120" t="str">
         <f>Scenarios!B30</f>
         <v>Devil's advocate</v>
@@ -19233,7 +19222,7 @@
       <c r="K94" s="297"/>
       <c r="L94" s="297"/>
     </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:12">
       <c r="B95" s="141"/>
       <c r="C95" s="141"/>
       <c r="D95" s="141"/>
@@ -19246,16 +19235,16 @@
       <c r="K95" s="142"/>
       <c r="L95" s="142"/>
     </row>
-    <row r="105" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="105" spans="3:3">
       <c r="C105" s="112"/>
     </row>
-    <row r="106" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="106" spans="3:3">
       <c r="C106" s="112"/>
     </row>
-    <row r="107" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="107" spans="3:3">
       <c r="C107" s="112"/>
     </row>
-    <row r="114" spans="3:21" x14ac:dyDescent="0.15">
+    <row r="114" spans="3:21">
       <c r="C114" s="275"/>
       <c r="M114" s="275"/>
       <c r="N114" s="275"/>
@@ -19267,7 +19256,7 @@
       <c r="T114" s="275"/>
       <c r="U114" s="275"/>
     </row>
-    <row r="115" spans="3:21" x14ac:dyDescent="0.15">
+    <row r="115" spans="3:21">
       <c r="C115" s="275"/>
       <c r="M115" s="275"/>
       <c r="N115" s="275"/>
@@ -19279,7 +19268,7 @@
       <c r="T115" s="275"/>
       <c r="U115" s="275"/>
     </row>
-    <row r="116" spans="3:21" x14ac:dyDescent="0.15">
+    <row r="116" spans="3:21">
       <c r="C116" s="275"/>
       <c r="M116" s="275"/>
       <c r="N116" s="275"/>
@@ -19291,7 +19280,7 @@
       <c r="T116" s="275"/>
       <c r="U116" s="275"/>
     </row>
-    <row r="117" spans="3:21" x14ac:dyDescent="0.15">
+    <row r="117" spans="3:21">
       <c r="C117" s="275"/>
       <c r="M117" s="275"/>
       <c r="N117" s="275"/>
@@ -19303,7 +19292,7 @@
       <c r="T117" s="275"/>
       <c r="U117" s="275"/>
     </row>
-    <row r="118" spans="3:21" x14ac:dyDescent="0.15">
+    <row r="118" spans="3:21">
       <c r="C118" s="275"/>
       <c r="M118" s="275"/>
       <c r="N118" s="275"/>
@@ -19343,14 +19332,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
   <dimension ref="B2:G67"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="2.6640625" customWidth="1"/>
     <col min="2" max="2" width="22.6640625" customWidth="1"/>
     <col min="3" max="7" width="20.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:7" ht="13.9">
       <c r="B2" s="34" t="s">
         <v>122</v>
       </c>
@@ -19360,7 +19349,7 @@
       <c r="F2" s="35"/>
       <c r="G2" s="35"/>
     </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:7" ht="13.15">
       <c r="B3" s="145" t="s">
         <v>125</v>
       </c>
@@ -19369,7 +19358,7 @@
       </c>
       <c r="E3" s="97"/>
     </row>
-    <row r="4" spans="2:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:7" ht="12.75" customHeight="1">
       <c r="B4" s="139" t="s">
         <v>123</v>
       </c>
@@ -19390,14 +19379,14 @@
       <c r="F4" s="469"/>
       <c r="G4" s="469"/>
     </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:7">
       <c r="C5" s="445"/>
       <c r="D5" s="469"/>
       <c r="E5" s="469"/>
       <c r="F5" s="469"/>
       <c r="G5" s="469"/>
     </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:7" ht="13.15">
       <c r="B6" s="145" t="s">
         <v>91</v>
       </c>
@@ -19410,7 +19399,7 @@
       <c r="F6" s="469"/>
       <c r="G6" s="469"/>
     </row>
-    <row r="7" spans="2:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:7" ht="12.75" customHeight="1">
       <c r="B7" s="97" t="s">
         <v>232</v>
       </c>
@@ -19423,7 +19412,7 @@
       <c r="F7" s="469"/>
       <c r="G7" s="469"/>
     </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:7">
       <c r="B8" s="97" t="s">
         <v>63</v>
       </c>
@@ -19436,7 +19425,7 @@
       <c r="F8" s="469"/>
       <c r="G8" s="469"/>
     </row>
-    <row r="9" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:7">
       <c r="B9" s="97" t="s">
         <v>54</v>
       </c>
@@ -19449,14 +19438,14 @@
       <c r="F9" s="469"/>
       <c r="G9" s="469"/>
     </row>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:7">
       <c r="C10" s="448"/>
       <c r="D10" s="469"/>
       <c r="E10" s="469"/>
       <c r="F10" s="469"/>
       <c r="G10" s="469"/>
     </row>
-    <row r="11" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:7" ht="13.15">
       <c r="B11" s="145" t="s">
         <v>320</v>
       </c>
@@ -19466,7 +19455,7 @@
       <c r="F11" s="469"/>
       <c r="G11" s="469"/>
     </row>
-    <row r="12" spans="2:7" ht="14" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:7">
       <c r="B12" s="114" t="s">
         <v>121</v>
       </c>
@@ -19479,7 +19468,7 @@
       <c r="F12" s="469"/>
       <c r="G12" s="469"/>
     </row>
-    <row r="13" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:7">
       <c r="B13" s="135" t="s">
         <v>127</v>
       </c>
@@ -19492,7 +19481,7 @@
       <c r="F13" s="469"/>
       <c r="G13" s="469"/>
     </row>
-    <row r="14" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:7">
       <c r="B14" s="97" t="s">
         <v>63</v>
       </c>
@@ -19505,7 +19494,7 @@
       <c r="F14" s="469"/>
       <c r="G14" s="469"/>
     </row>
-    <row r="16" spans="2:7" ht="16" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:7" ht="13.9">
       <c r="B16" s="34" t="s">
         <v>451</v>
       </c>
@@ -19515,7 +19504,7 @@
       <c r="F16" s="35"/>
       <c r="G16" s="35"/>
     </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:7" ht="13.15">
       <c r="B17" s="106" t="s">
         <v>126</v>
       </c>
@@ -19523,7 +19512,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="18" spans="2:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:7" ht="12.75" customHeight="1">
       <c r="B18" s="139" t="s">
         <v>111</v>
       </c>
@@ -19535,18 +19524,18 @@
       </c>
       <c r="F18" s="319"/>
     </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:7">
       <c r="E19" s="319"/>
       <c r="F19" s="319"/>
     </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:7" ht="13.15">
       <c r="B20" s="106" t="s">
         <v>448</v>
       </c>
       <c r="E20" s="319"/>
       <c r="F20" s="319"/>
     </row>
-    <row r="21" spans="2:7" ht="14" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:7" ht="13.15">
       <c r="B21" s="153" t="s">
         <v>434</v>
       </c>
@@ -19567,7 +19556,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="22" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:7">
       <c r="B22" s="302" t="s">
         <v>443</v>
       </c>
@@ -19591,7 +19580,7 @@
         <v>0.15999999999999995</v>
       </c>
     </row>
-    <row r="23" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:7">
       <c r="B23" s="302" t="s">
         <v>435</v>
       </c>
@@ -19614,7 +19603,7 @@
         <v>0.44</v>
       </c>
     </row>
-    <row r="24" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:7">
       <c r="B24" s="302" t="s">
         <v>444</v>
       </c>
@@ -19637,7 +19626,7 @@
         <v>0.19999999999999998</v>
       </c>
     </row>
-    <row r="25" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:7">
       <c r="B25" s="141" t="s">
         <v>449</v>
       </c>
@@ -19651,12 +19640,12 @@
       </c>
       <c r="G25" s="149"/>
     </row>
-    <row r="27" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:7" ht="13.15">
       <c r="B27" s="106" t="s">
         <v>450</v>
       </c>
     </row>
-    <row r="28" spans="2:7" ht="14" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:7" ht="13.15">
       <c r="B28" s="153" t="s">
         <v>434</v>
       </c>
@@ -19677,7 +19666,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="29" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:7">
       <c r="B29" s="302" t="s">
         <v>442</v>
       </c>
@@ -19700,7 +19689,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="30" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:7">
       <c r="B30" s="315" t="s">
         <v>445</v>
       </c>
@@ -19723,16 +19712,16 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="31" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:7">
       <c r="E31" s="329"/>
       <c r="F31" s="329"/>
     </row>
-    <row r="32" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:7" ht="13.15">
       <c r="B32" s="145" t="s">
         <v>454</v>
       </c>
     </row>
-    <row r="33" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:7">
       <c r="B33" s="97" t="s">
         <v>456</v>
       </c>
@@ -19752,13 +19741,13 @@
         <v>3</v>
       </c>
     </row>
-    <row r="34" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:7">
       <c r="B34" s="97" t="s">
         <v>233</v>
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>106.06</v>
+        <v>104.05</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19769,10 +19758,10 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.10787497156703298</v>
-      </c>
-    </row>
-    <row r="35" spans="2:7" x14ac:dyDescent="0.15">
+        <v>0.11513532579667529</v>
+      </c>
+    </row>
+    <row r="35" spans="2:7">
       <c r="B35" s="97" t="s">
         <v>432</v>
       </c>
@@ -19792,7 +19781,7 @@
         <v>-7.3996144898412761E-2</v>
       </c>
     </row>
-    <row r="36" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:7">
       <c r="B36" s="97" t="s">
         <v>433</v>
       </c>
@@ -19811,7 +19800,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="38" spans="2:7" ht="16" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:7" ht="13.9">
       <c r="B38" s="34" t="s">
         <v>409</v>
       </c>
@@ -19821,7 +19810,7 @@
       <c r="F38" s="35"/>
       <c r="G38" s="35"/>
     </row>
-    <row r="39" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:7" ht="13.15">
       <c r="B39" s="414" t="str">
         <f>IF(DCF!F14="II","2","1")&amp;"-stage DCF"</f>
         <v>2-stage DCF</v>
@@ -19830,7 +19819,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="40" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:7">
       <c r="B40" t="s">
         <v>548</v>
       </c>
@@ -19842,7 +19831,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="41" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:7">
       <c r="B41" s="97" t="s">
         <v>398</v>
       </c>
@@ -19852,7 +19841,7 @@
       </c>
       <c r="E41" s="97"/>
     </row>
-    <row r="43" spans="2:7" ht="16" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:7" ht="13.9">
       <c r="B43" s="34" t="s">
         <v>276</v>
       </c>
@@ -19862,7 +19851,7 @@
       <c r="F43" s="35"/>
       <c r="G43" s="35"/>
     </row>
-    <row r="44" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:7" ht="13.15">
       <c r="B44" s="106" t="s">
         <v>249</v>
       </c>
@@ -19870,7 +19859,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="45" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:7">
       <c r="B45" s="139" t="s">
         <v>111</v>
       </c>
@@ -19883,7 +19872,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="46" spans="2:7" ht="14" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:7">
       <c r="B46" s="114" t="s">
         <v>112</v>
       </c>
@@ -19895,7 +19884,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="47" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:7">
       <c r="B47" s="97" t="s">
         <v>96</v>
       </c>
@@ -19911,7 +19900,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="49" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="49" spans="2:7" ht="13.15">
       <c r="B49" s="106" t="s">
         <v>277</v>
       </c>
@@ -19923,7 +19912,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="50" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:7">
       <c r="B50" s="97" t="s">
         <v>250</v>
       </c>
@@ -19933,7 +19922,7 @@
       </c>
       <c r="E50" s="126"/>
     </row>
-    <row r="51" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:7">
       <c r="B51" s="97" t="s">
         <v>246</v>
       </c>
@@ -19945,7 +19934,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="52" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:7">
       <c r="B52" s="97" t="s">
         <v>245</v>
       </c>
@@ -19955,7 +19944,7 @@
       </c>
       <c r="E52" s="221"/>
     </row>
-    <row r="53" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="53" spans="2:7">
       <c r="B53" s="97" t="s">
         <v>237</v>
       </c>
@@ -19971,7 +19960,7 @@
         <v>0.2262544978580209</v>
       </c>
     </row>
-    <row r="55" spans="2:7" ht="16" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:7" ht="13.9">
       <c r="B55" s="34" t="s">
         <v>107</v>
       </c>
@@ -19981,12 +19970,12 @@
       <c r="F55" s="35"/>
       <c r="G55" s="35"/>
     </row>
-    <row r="56" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:7" ht="13.15">
       <c r="B56" s="106" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="57" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="57" spans="2:7">
       <c r="B57" s="220" t="s">
         <v>248</v>
       </c>
@@ -19996,7 +19985,7 @@
       </c>
       <c r="D57" s="126"/>
     </row>
-    <row r="58" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:7">
       <c r="B58" s="97" t="s">
         <v>331</v>
       </c>
@@ -20009,13 +19998,13 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="60" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="60" spans="2:7" ht="13.15">
       <c r="B60" s="106" t="s">
         <v>471</v>
       </c>
       <c r="E60" s="413"/>
     </row>
-    <row r="61" spans="2:7" ht="14" x14ac:dyDescent="0.2">
+    <row r="61" spans="2:7" ht="13.15">
       <c r="B61" s="153" t="s">
         <v>460</v>
       </c>
@@ -20036,7 +20025,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="62" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:7" ht="13.15">
       <c r="B62" s="302" t="s">
         <v>311</v>
       </c>
@@ -20061,7 +20050,7 @@
         <v>0.53755491242430398</v>
       </c>
     </row>
-    <row r="63" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="63" spans="2:7" ht="13.15">
       <c r="B63" s="302" t="s">
         <v>312</v>
       </c>
@@ -20086,7 +20075,7 @@
         <v>0.41479582873538823</v>
       </c>
     </row>
-    <row r="65" spans="2:7" ht="14" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:7" ht="13.15">
       <c r="B65" s="153" t="s">
         <v>461</v>
       </c>
@@ -20107,7 +20096,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="66" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="66" spans="2:7" ht="13.15">
       <c r="B66" s="302" t="s">
         <v>314</v>
       </c>
@@ -20132,7 +20121,7 @@
         <v>0.16752343251869795</v>
       </c>
     </row>
-    <row r="67" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="67" spans="2:7" ht="13.15">
       <c r="B67" s="302" t="s">
         <v>313</v>
       </c>
@@ -20173,7 +20162,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:J167"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.4"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="343" customWidth="1"/>
     <col min="2" max="2" width="32.6640625" style="343" customWidth="1"/>
@@ -20182,7 +20171,7 @@
     <col min="7" max="16384" width="9" style="343"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:10" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" ht="13.9">
       <c r="A2" s="345" t="s">
         <v>332</v>
       </c>
@@ -20196,7 +20185,7 @@
       <c r="I2" s="346"/>
       <c r="J2" s="346"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10">
       <c r="E3" s="435" t="s">
         <v>539</v>
       </c>
@@ -20205,7 +20194,7 @@
         <v>46066</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10">
       <c r="B4" s="422" t="s">
         <v>531</v>
       </c>
@@ -20222,7 +20211,7 @@
         <v>CN</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10">
       <c r="B5" s="343" t="s">
         <v>362</v>
       </c>
@@ -20238,7 +20227,7 @@
         <v>N</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10">
       <c r="B6" s="350" t="s">
         <v>334</v>
       </c>
@@ -20248,7 +20237,7 @@
       </c>
       <c r="E6" s="354"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10">
       <c r="B7" s="343" t="s">
         <v>364</v>
       </c>
@@ -20259,16 +20248,16 @@
       <c r="D7" s="354"/>
       <c r="E7" s="354"/>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10">
       <c r="B8" s="351" t="s">
         <v>363</v>
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>106.06</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+        <v>104.05</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
       <c r="B9" s="351" t="s">
         <v>359</v>
       </c>
@@ -20277,43 +20266,43 @@
         <v>3881608005</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10">
       <c r="B10" s="351" t="s">
         <v>365</v>
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>411683.34501029999</v>
+        <v>403881.31292025</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>526</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.10787497156703298</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+        <v>0.11513532579667529</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
       <c r="D11" s="349"/>
       <c r="E11" s="349"/>
     </row>
-    <row r="12" spans="1:10" ht="24.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="474" t="s">
+    <row r="12" spans="1:10" ht="24.5" customHeight="1">
+      <c r="B12" s="471" t="s">
         <v>495</v>
       </c>
-      <c r="C12" s="474"/>
-      <c r="D12" s="474"/>
-      <c r="E12" s="474"/>
-      <c r="F12" s="474"/>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="C12" s="471"/>
+      <c r="D12" s="471"/>
+      <c r="E12" s="471"/>
+      <c r="F12" s="471"/>
+    </row>
+    <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
         <v>368</v>
       </c>
       <c r="C14" s="348"/>
       <c r="D14" s="349"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10">
       <c r="B15" s="343" t="s">
         <v>335</v>
       </c>
@@ -20329,7 +20318,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10">
       <c r="B16" s="343" t="s">
         <v>336</v>
       </c>
@@ -20345,7 +20334,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:6">
       <c r="B17" s="343" t="s">
         <v>532</v>
       </c>
@@ -20361,7 +20350,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:6">
       <c r="B18" s="343" t="str">
         <f>"预期股权价值 ("&amp;C7&amp;") :"</f>
         <v>预期股权价值 (CNY) :</v>
@@ -20378,7 +20367,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:6">
       <c r="B19" s="350" t="s">
         <v>333</v>
       </c>
@@ -20394,11 +20383,11 @@
         <v>46081</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:6">
       <c r="D20" s="349"/>
       <c r="E20" s="349"/>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:6">
       <c r="B21" s="347" t="s">
         <v>491</v>
       </c>
@@ -20414,7 +20403,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:6">
       <c r="B22" s="343" t="s">
         <v>338</v>
       </c>
@@ -20430,7 +20419,7 @@
         <v>0.32950289523458665</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:6">
       <c r="B23" s="343" t="s">
         <v>339</v>
       </c>
@@ -20446,7 +20435,7 @@
         <v>0.22621703288100403</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:6">
       <c r="B24" s="343" t="s">
         <v>341</v>
       </c>
@@ -20462,7 +20451,7 @@
         <v>8.6999999999999994E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:6">
       <c r="B25" s="343" t="s">
         <v>340</v>
       </c>
@@ -20478,7 +20467,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" ht="13.9">
       <c r="A27" s="345" t="s">
         <v>343</v>
       </c>
@@ -20488,25 +20477,25 @@
       <c r="E27" s="345"/>
       <c r="F27" s="345"/>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="474" t="s">
+    <row r="29" spans="1:6">
+      <c r="B29" s="471" t="s">
         <v>496</v>
       </c>
-      <c r="C29" s="474"/>
-      <c r="D29" s="474"/>
-      <c r="E29" s="474"/>
-      <c r="F29" s="474"/>
-    </row>
-    <row r="30" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B30" s="477" t="s">
+      <c r="C29" s="471"/>
+      <c r="D29" s="471"/>
+      <c r="E29" s="471"/>
+      <c r="F29" s="471"/>
+    </row>
+    <row r="30" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B30" s="472" t="s">
         <v>497</v>
       </c>
-      <c r="C30" s="477"/>
-      <c r="D30" s="477"/>
-      <c r="E30" s="477"/>
-      <c r="F30" s="477"/>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C30" s="472"/>
+      <c r="D30" s="472"/>
+      <c r="E30" s="472"/>
+      <c r="F30" s="472"/>
+    </row>
+    <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
         <v>369</v>
       </c>
@@ -20515,7 +20504,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:6">
       <c r="B33" s="470" t="s">
         <v>498</v>
       </c>
@@ -20524,7 +20513,7 @@
       <c r="E33" s="470"/>
       <c r="F33" s="470"/>
     </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:6">
       <c r="B34" s="372" t="s">
         <v>197</v>
       </c>
@@ -20537,11 +20526,11 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="35" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:6">
       <c r="B35" s="372"/>
       <c r="C35" s="374"/>
     </row>
-    <row r="36" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:6" ht="24.5" customHeight="1">
       <c r="B36" s="470" t="s">
         <v>499</v>
       </c>
@@ -20550,7 +20539,7 @@
       <c r="E36" s="470"/>
       <c r="F36" s="470"/>
     </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:6">
       <c r="B37" s="372" t="s">
         <v>199</v>
       </c>
@@ -20563,7 +20552,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="38" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:6">
       <c r="B38" s="375" t="s">
         <v>200</v>
       </c>
@@ -20576,7 +20565,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="40" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:6">
       <c r="B40" s="470" t="s">
         <v>500</v>
       </c>
@@ -20585,7 +20574,7 @@
       <c r="E40" s="470"/>
       <c r="F40" s="470"/>
     </row>
-    <row r="41" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:6">
       <c r="B41" s="372" t="s">
         <v>202</v>
       </c>
@@ -20598,7 +20587,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="43" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:6">
       <c r="B43" s="470" t="s">
         <v>501</v>
       </c>
@@ -20607,7 +20596,7 @@
       <c r="E43" s="470"/>
       <c r="F43" s="470"/>
     </row>
-    <row r="44" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:6">
       <c r="B44" s="372" t="s">
         <v>267</v>
       </c>
@@ -20622,7 +20611,7 @@
       <c r="E44" s="371"/>
       <c r="F44" s="371"/>
     </row>
-    <row r="45" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:6">
       <c r="B45" s="372" t="s">
         <v>268</v>
       </c>
@@ -20637,7 +20626,7 @@
       <c r="E45" s="371"/>
       <c r="F45" s="371"/>
     </row>
-    <row r="46" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:6">
       <c r="B46" s="372" t="s">
         <v>203</v>
       </c>
@@ -20650,12 +20639,12 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="48" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:6">
       <c r="B48" s="343" t="s">
         <v>502</v>
       </c>
     </row>
-    <row r="49" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="49" spans="2:6">
       <c r="B49" s="372" t="s">
         <v>223</v>
       </c>
@@ -20668,7 +20657,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="51" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="51" spans="2:6">
       <c r="B51" s="470" t="s">
         <v>503</v>
       </c>
@@ -20677,7 +20666,7 @@
       <c r="E51" s="470"/>
       <c r="F51" s="470"/>
     </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="52" spans="2:6">
       <c r="B52" s="372" t="s">
         <v>494</v>
       </c>
@@ -20690,16 +20679,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="54" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="54" spans="2:6">
       <c r="B54" s="470" t="s">
         <v>504</v>
       </c>
-      <c r="C54" s="476"/>
-      <c r="D54" s="476"/>
-      <c r="E54" s="476"/>
-      <c r="F54" s="476"/>
-    </row>
-    <row r="55" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="C54" s="473"/>
+      <c r="D54" s="473"/>
+      <c r="E54" s="473"/>
+      <c r="F54" s="473"/>
+    </row>
+    <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
         <v>207</v>
       </c>
@@ -20712,25 +20701,25 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="57" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B57" s="474" t="s">
+    <row r="57" spans="2:6">
+      <c r="B57" s="471" t="s">
         <v>505</v>
       </c>
-      <c r="C57" s="474"/>
-      <c r="D57" s="474"/>
-      <c r="E57" s="474"/>
-      <c r="F57" s="474"/>
-    </row>
-    <row r="58" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B58" s="474" t="s">
+      <c r="C57" s="471"/>
+      <c r="D57" s="471"/>
+      <c r="E57" s="471"/>
+      <c r="F57" s="471"/>
+    </row>
+    <row r="58" spans="2:6">
+      <c r="B58" s="471" t="s">
         <v>506</v>
       </c>
-      <c r="C58" s="474"/>
-      <c r="D58" s="474"/>
-      <c r="E58" s="474"/>
-      <c r="F58" s="474"/>
-    </row>
-    <row r="60" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="C58" s="471"/>
+      <c r="D58" s="471"/>
+      <c r="E58" s="471"/>
+      <c r="F58" s="471"/>
+    </row>
+    <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
         <v>370</v>
       </c>
@@ -20743,7 +20732,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="61" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="61" spans="2:6">
       <c r="B61" s="372" t="s">
         <v>213</v>
       </c>
@@ -20756,23 +20745,23 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="62" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="62" spans="2:6">
       <c r="B62" s="377" t="s">
         <v>302</v>
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>7.2391319447967964E-2</v>
+        <v>7.3789748588673543E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
-    <row r="63" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="63" spans="2:6">
       <c r="B63" s="377" t="s">
         <v>330</v>
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>2.6891382236469922E-2</v>
+        <v>2.741086016338299E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>371</v>
@@ -20782,7 +20771,7 @@
         <v>0.4127471888056104</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:6">
       <c r="B65" s="369" t="s">
         <v>374</v>
       </c>
@@ -20793,7 +20782,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:6">
       <c r="B66" s="372" t="s">
         <v>324</v>
       </c>
@@ -20806,7 +20795,7 @@
         <v>0.26898198471339402</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:6">
       <c r="B67" s="382" t="str">
         <f>Normalized_FCF!B116</f>
         <v>Pre-tax Profit/Sales</v>
@@ -20820,7 +20809,7 @@
         <v>0.43474742930380028</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:6">
       <c r="B68" s="382" t="str">
         <f>Normalized_FCF!B117</f>
         <v>Sales/Total Assets</v>
@@ -20834,7 +20823,7 @@
         <v>0.4610552539366265</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:6">
       <c r="B69" s="382" t="str">
         <f>Normalized_FCF!B118</f>
         <v>Total Assets/Equity</v>
@@ -20848,7 +20837,7 @@
         <v>1.3419403008261008</v>
       </c>
     </row>
-    <row r="71" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:6" ht="13.9">
       <c r="A71" s="345" t="s">
         <v>474</v>
       </c>
@@ -20858,43 +20847,43 @@
       <c r="E71" s="345"/>
       <c r="F71" s="345"/>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:6">
       <c r="A72" s="385"/>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="474" t="s">
+      <c r="B73" s="471" t="s">
         <v>507</v>
       </c>
-      <c r="C73" s="474"/>
-      <c r="D73" s="474"/>
-      <c r="E73" s="474"/>
-      <c r="F73" s="474"/>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B74" s="477" t="s">
+      <c r="C73" s="471"/>
+      <c r="D73" s="471"/>
+      <c r="E73" s="471"/>
+      <c r="F73" s="471"/>
+    </row>
+    <row r="74" spans="1:6">
+      <c r="B74" s="472" t="s">
         <v>477</v>
       </c>
-      <c r="C74" s="477"/>
-      <c r="D74" s="477"/>
-      <c r="E74" s="477"/>
-      <c r="F74" s="477"/>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C74" s="472"/>
+      <c r="D74" s="472"/>
+      <c r="E74" s="472"/>
+      <c r="F74" s="472"/>
+    </row>
+    <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
         <v>369</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B77" s="474" t="s">
+    <row r="77" spans="1:6">
+      <c r="B77" s="471" t="s">
         <v>508</v>
       </c>
-      <c r="C77" s="474"/>
-      <c r="D77" s="474"/>
-      <c r="E77" s="474"/>
-      <c r="F77" s="474"/>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C77" s="471"/>
+      <c r="D77" s="471"/>
+      <c r="E77" s="471"/>
+      <c r="F77" s="471"/>
+    </row>
+    <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
         <v>215</v>
       </c>
@@ -20907,7 +20896,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:6">
       <c r="B79" s="372" t="s">
         <v>234</v>
       </c>
@@ -20920,7 +20909,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:6">
       <c r="B80" s="382" t="s">
         <v>308</v>
       </c>
@@ -20929,7 +20918,7 @@
         <v>1.4942693904035366E-3</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:6">
       <c r="B81" s="382" t="s">
         <v>310</v>
       </c>
@@ -20938,12 +20927,12 @@
         <v>5.1971735080735887E-3</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:6">
       <c r="B83" s="343" t="s">
         <v>509</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:6">
       <c r="B84" s="343" t="s">
         <v>224</v>
       </c>
@@ -20956,7 +20945,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:6">
       <c r="B85" s="382" t="s">
         <v>479</v>
       </c>
@@ -20969,7 +20958,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:6">
       <c r="B86" s="372" t="s">
         <v>235</v>
       </c>
@@ -20982,12 +20971,12 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:6">
       <c r="B88" s="343" t="s">
         <v>510</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:6">
       <c r="B89" s="343" t="s">
         <v>217</v>
       </c>
@@ -21000,7 +20989,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:6">
       <c r="B90" s="372" t="s">
         <v>236</v>
       </c>
@@ -21013,7 +21002,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:6">
       <c r="B92" s="372" t="s">
         <v>478</v>
       </c>
@@ -21026,7 +21015,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="94" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:6" ht="13.9">
       <c r="A94" s="345" t="s">
         <v>480</v>
       </c>
@@ -21036,49 +21025,49 @@
       <c r="E94" s="345"/>
       <c r="F94" s="345"/>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:6">
       <c r="A95" s="385"/>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="474" t="s">
+      <c r="B96" s="471" t="s">
         <v>511</v>
       </c>
-      <c r="C96" s="474"/>
-      <c r="D96" s="474"/>
-      <c r="E96" s="474"/>
-      <c r="F96" s="474"/>
-    </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C96" s="471"/>
+      <c r="D96" s="471"/>
+      <c r="E96" s="471"/>
+      <c r="F96" s="471"/>
+    </row>
+    <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="477" t="s">
+      <c r="B97" s="472" t="s">
         <v>512</v>
       </c>
-      <c r="C97" s="477"/>
-      <c r="D97" s="477"/>
-      <c r="E97" s="477"/>
-      <c r="F97" s="477"/>
-    </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C97" s="472"/>
+      <c r="D97" s="472"/>
+      <c r="E97" s="472"/>
+      <c r="F97" s="472"/>
+    </row>
+    <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="477" t="s">
+      <c r="B98" s="472" t="s">
         <v>513</v>
       </c>
-      <c r="C98" s="477"/>
-      <c r="D98" s="477"/>
-      <c r="E98" s="477"/>
-      <c r="F98" s="477"/>
-    </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C98" s="472"/>
+      <c r="D98" s="472"/>
+      <c r="E98" s="472"/>
+      <c r="F98" s="472"/>
+    </row>
+    <row r="99" spans="1:6">
       <c r="A99" s="385"/>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:6">
       <c r="A100" s="385"/>
       <c r="B100" s="369" t="s">
         <v>369</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:6">
       <c r="A101" s="385"/>
       <c r="B101" s="372" t="s">
         <v>212</v>
@@ -21088,7 +21077,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:6">
       <c r="A102" s="385"/>
       <c r="B102" s="382" t="s">
         <v>317</v>
@@ -21098,7 +21087,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:6">
       <c r="A103" s="385"/>
       <c r="B103" s="382" t="s">
         <v>316</v>
@@ -21108,7 +21097,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:6">
       <c r="A104" s="385"/>
       <c r="B104" s="372" t="s">
         <v>532</v>
@@ -21117,47 +21106,47 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:6">
       <c r="A105" s="385"/>
       <c r="C105" s="392"/>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:6">
       <c r="A106" s="385"/>
       <c r="B106" s="393" t="s">
         <v>373</v>
       </c>
       <c r="C106" s="392"/>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="474" t="s">
+      <c r="B107" s="471" t="s">
         <v>514</v>
       </c>
-      <c r="C107" s="474"/>
-      <c r="D107" s="474"/>
-      <c r="E107" s="474"/>
-      <c r="F107" s="474"/>
-    </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C107" s="471"/>
+      <c r="D107" s="471"/>
+      <c r="E107" s="471"/>
+      <c r="F107" s="471"/>
+    </row>
+    <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="474" t="s">
+      <c r="B108" s="471" t="s">
         <v>533</v>
       </c>
-      <c r="C108" s="474"/>
-      <c r="D108" s="474"/>
-      <c r="E108" s="474"/>
-      <c r="F108" s="474"/>
-    </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C108" s="471"/>
+      <c r="D108" s="471"/>
+      <c r="E108" s="471"/>
+      <c r="F108" s="471"/>
+    </row>
+    <row r="109" spans="1:6">
       <c r="A109" s="385"/>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:6">
       <c r="A110" s="385"/>
       <c r="B110" s="369" t="s">
         <v>487</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:6">
       <c r="A111" s="385"/>
       <c r="B111" s="375" t="s">
         <v>484</v>
@@ -21171,7 +21160,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:6">
       <c r="A112" s="385"/>
       <c r="B112" s="372" t="s">
         <v>375</v>
@@ -21185,29 +21174,29 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:6">
       <c r="A113" s="385"/>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="474" t="s">
+      <c r="B114" s="471" t="s">
         <v>515</v>
       </c>
-      <c r="C114" s="474"/>
-      <c r="D114" s="474"/>
-      <c r="E114" s="474"/>
-      <c r="F114" s="474"/>
-    </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C114" s="471"/>
+      <c r="D114" s="471"/>
+      <c r="E114" s="471"/>
+      <c r="F114" s="471"/>
+    </row>
+    <row r="115" spans="1:6">
       <c r="A115" s="385"/>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:6">
       <c r="A116" s="385"/>
       <c r="B116" s="369" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:6">
       <c r="A117" s="385"/>
       <c r="B117" s="342" t="s">
         <v>376</v>
@@ -21225,7 +21214,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:6">
       <c r="A118" s="385"/>
       <c r="B118" s="395" t="str">
         <f>DCF!B90</f>
@@ -21248,7 +21237,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:6">
       <c r="A119" s="385"/>
       <c r="B119" s="400" t="str">
         <f>DCF!B91</f>
@@ -21271,7 +21260,7 @@
         <v>0.15999999999999995</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:6">
       <c r="B120" s="400" t="str">
         <f>DCF!B92</f>
         <v>Base</v>
@@ -21293,7 +21282,7 @@
         <v>0.44</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:6">
       <c r="B121" s="400" t="str">
         <f>DCF!B93</f>
         <v>Pessimistic</v>
@@ -21315,7 +21304,7 @@
         <v>0.19999999999999998</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:6">
       <c r="B122" s="400" t="str">
         <f>DCF!B94</f>
         <v>Devil's advocate</v>
@@ -21337,7 +21326,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:6">
       <c r="B124" s="470" t="s">
         <v>516</v>
       </c>
@@ -21346,7 +21335,7 @@
       <c r="E124" s="470"/>
       <c r="F124" s="470"/>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:6">
       <c r="B125" s="372" t="s">
         <v>218</v>
       </c>
@@ -21359,16 +21348,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B127" s="472" t="s">
+    <row r="127" spans="1:6">
+      <c r="B127" s="475" t="s">
         <v>517</v>
       </c>
-      <c r="C127" s="472"/>
-      <c r="D127" s="472"/>
-      <c r="E127" s="472"/>
-      <c r="F127" s="472"/>
-    </row>
-    <row r="129" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+      <c r="C127" s="475"/>
+      <c r="D127" s="475"/>
+      <c r="E127" s="475"/>
+      <c r="F127" s="475"/>
+    </row>
+    <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
         <v>490</v>
       </c>
@@ -21378,30 +21367,30 @@
       <c r="E129" s="345"/>
       <c r="F129" s="345"/>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B131" s="473" t="s">
+    <row r="131" spans="1:6">
+      <c r="B131" s="476" t="s">
         <v>518</v>
       </c>
-      <c r="C131" s="473"/>
-      <c r="D131" s="473"/>
-      <c r="E131" s="473"/>
-      <c r="F131" s="473"/>
-    </row>
-    <row r="132" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B132" s="474" t="s">
+      <c r="C131" s="476"/>
+      <c r="D131" s="476"/>
+      <c r="E131" s="476"/>
+      <c r="F131" s="476"/>
+    </row>
+    <row r="132" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B132" s="471" t="s">
         <v>519</v>
       </c>
-      <c r="C132" s="474"/>
-      <c r="D132" s="474"/>
-      <c r="E132" s="474"/>
-      <c r="F132" s="474"/>
-    </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C132" s="471"/>
+      <c r="D132" s="471"/>
+      <c r="E132" s="471"/>
+      <c r="F132" s="471"/>
+    </row>
+    <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
         <v>369</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:6">
       <c r="B135" s="343" t="s">
         <v>380</v>
       </c>
@@ -21410,7 +21399,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:6">
       <c r="B136" s="343" t="s">
         <v>381</v>
       </c>
@@ -21423,14 +21412,14 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:6">
       <c r="B138" s="369" t="s">
         <v>491</v>
       </c>
       <c r="C138" s="407"/>
       <c r="D138" s="407"/>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:6">
       <c r="B139" s="340" t="s">
         <v>460</v>
       </c>
@@ -21449,7 +21438,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:6">
       <c r="B140" s="408" t="s">
         <v>311</v>
       </c>
@@ -21470,7 +21459,7 @@
         <v>0.32950289523458665</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:6">
       <c r="B141" s="408" t="s">
         <v>312</v>
       </c>
@@ -21491,7 +21480,7 @@
         <v>0.22621703288100403</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:6">
       <c r="B143" s="340" t="s">
         <v>461</v>
       </c>
@@ -21510,7 +21499,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:6">
       <c r="B144" s="408" t="s">
         <v>314</v>
       </c>
@@ -21531,7 +21520,7 @@
         <v>8.6999999999999994E-2</v>
       </c>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:6">
       <c r="B145" s="408" t="s">
         <v>313</v>
       </c>
@@ -21552,7 +21541,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="147" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:6" ht="13.9">
       <c r="A147" s="345" t="s">
         <v>473</v>
       </c>
@@ -21562,50 +21551,50 @@
       <c r="E147" s="345"/>
       <c r="F147" s="345"/>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B149" s="475" t="s">
+    <row r="149" spans="1:6">
+      <c r="B149" s="477" t="s">
         <v>520</v>
       </c>
-      <c r="C149" s="474"/>
-      <c r="D149" s="474"/>
-      <c r="E149" s="474"/>
-      <c r="F149" s="474"/>
-    </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C149" s="471"/>
+      <c r="D149" s="471"/>
+      <c r="E149" s="471"/>
+      <c r="F149" s="471"/>
+    </row>
+    <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
         <v>382</v>
       </c>
     </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B152" s="476" t="s">
+    <row r="152" spans="1:6">
+      <c r="B152" s="473" t="s">
         <v>521</v>
       </c>
-      <c r="C152" s="476"/>
-      <c r="D152" s="476"/>
-      <c r="E152" s="476"/>
-      <c r="F152" s="476"/>
-    </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C152" s="473"/>
+      <c r="D152" s="473"/>
+      <c r="E152" s="473"/>
+      <c r="F152" s="473"/>
+    </row>
+    <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
         <v>383</v>
       </c>
     </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:6">
       <c r="B154" s="412" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:6">
       <c r="B155" s="412" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:6">
       <c r="B157" s="343" t="s">
         <v>522</v>
       </c>
     </row>
-    <row r="158" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:6" ht="24.5" customHeight="1">
       <c r="B158" s="470" t="s">
         <v>437</v>
       </c>
@@ -21614,57 +21603,60 @@
       <c r="E158" s="470"/>
       <c r="F158" s="470"/>
     </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:6">
       <c r="B160" s="343" t="s">
         <v>523</v>
       </c>
     </row>
-    <row r="161" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B161" s="471" t="s">
+    <row r="161" spans="2:6">
+      <c r="B161" s="474" t="s">
         <v>386</v>
       </c>
-      <c r="C161" s="471"/>
-      <c r="D161" s="471"/>
-      <c r="E161" s="471"/>
-      <c r="F161" s="471"/>
-    </row>
-    <row r="162" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B162" s="471" t="s">
+      <c r="C161" s="474"/>
+      <c r="D161" s="474"/>
+      <c r="E161" s="474"/>
+      <c r="F161" s="474"/>
+    </row>
+    <row r="162" spans="2:6">
+      <c r="B162" s="474" t="s">
         <v>387</v>
       </c>
-      <c r="C162" s="471"/>
-      <c r="D162" s="471"/>
-      <c r="E162" s="471"/>
-      <c r="F162" s="471"/>
-    </row>
-    <row r="164" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="C162" s="474"/>
+      <c r="D162" s="474"/>
+      <c r="E162" s="474"/>
+      <c r="F162" s="474"/>
+    </row>
+    <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
         <v>524</v>
       </c>
     </row>
-    <row r="165" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="165" spans="2:6">
       <c r="B165" s="412" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="166" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="166" spans="2:6">
       <c r="B166" s="412" t="s">
         <v>389</v>
       </c>
     </row>
-    <row r="167" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="167" spans="2:6">
       <c r="B167" s="412" t="s">
         <v>390</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21679,15 +21671,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/000858.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/000858.SZ_Valuation.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8439BE3B-9F9D-4255-A017-246B293F616F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72FE379C-0D44-4857-9D0B-3E7A901CFB13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4986,30 +4986,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5019,25 +5019,25 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5407,7 +5407,7 @@
         <v>348</v>
       </c>
       <c r="C8" s="47">
-        <v>104.05</v>
+        <v>102.4</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5425,14 +5425,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>403881.31292025</v>
+        <v>397476.65971199999</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>525</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.11513532579667529</v>
+        <v>0.12123883246616156</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5440,13 +5440,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="460" t="s">
+      <c r="B12" s="462" t="s">
         <v>353</v>
       </c>
-      <c r="C12" s="460"/>
-      <c r="D12" s="460"/>
-      <c r="E12" s="460"/>
-      <c r="F12" s="460"/>
+      <c r="C12" s="462"/>
+      <c r="D12" s="462"/>
+      <c r="E12" s="462"/>
+      <c r="F12" s="462"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5624,22 +5624,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="460" t="s">
+      <c r="B29" s="462" t="s">
         <v>354</v>
       </c>
-      <c r="C29" s="460"/>
-      <c r="D29" s="460"/>
-      <c r="E29" s="460"/>
-      <c r="F29" s="460"/>
+      <c r="C29" s="462"/>
+      <c r="D29" s="462"/>
+      <c r="E29" s="462"/>
+      <c r="F29" s="462"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="462" t="s">
+      <c r="B30" s="466" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="462"/>
-      <c r="D30" s="462"/>
-      <c r="E30" s="462"/>
-      <c r="F30" s="462"/>
+      <c r="C30" s="466"/>
+      <c r="D30" s="466"/>
+      <c r="E30" s="466"/>
+      <c r="F30" s="466"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5651,13 +5651,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="461" t="s">
+      <c r="B33" s="463" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="461"/>
-      <c r="D33" s="461"/>
-      <c r="E33" s="461"/>
-      <c r="F33" s="461"/>
+      <c r="C33" s="463"/>
+      <c r="D33" s="463"/>
+      <c r="E33" s="463"/>
+      <c r="F33" s="463"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5677,13 +5677,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="461" t="s">
+      <c r="B36" s="463" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="461"/>
-      <c r="D36" s="461"/>
-      <c r="E36" s="461"/>
-      <c r="F36" s="461"/>
+      <c r="C36" s="463"/>
+      <c r="D36" s="463"/>
+      <c r="E36" s="463"/>
+      <c r="F36" s="463"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5712,13 +5712,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="461" t="s">
+      <c r="B40" s="463" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="461"/>
-      <c r="D40" s="461"/>
-      <c r="E40" s="461"/>
-      <c r="F40" s="461"/>
+      <c r="C40" s="463"/>
+      <c r="D40" s="463"/>
+      <c r="E40" s="463"/>
+      <c r="F40" s="463"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5734,13 +5734,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="461" t="s">
+      <c r="B43" s="463" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="461"/>
-      <c r="D43" s="461"/>
-      <c r="E43" s="461"/>
-      <c r="F43" s="461"/>
+      <c r="C43" s="463"/>
+      <c r="D43" s="463"/>
+      <c r="E43" s="463"/>
+      <c r="F43" s="463"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5804,13 +5804,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="461" t="s">
+      <c r="B51" s="463" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="461"/>
-      <c r="D51" s="461"/>
-      <c r="E51" s="461"/>
-      <c r="F51" s="461"/>
+      <c r="C51" s="463"/>
+      <c r="D51" s="463"/>
+      <c r="E51" s="463"/>
+      <c r="F51" s="463"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5826,7 +5826,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="461" t="s">
+      <c r="B54" s="463" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="464"/>
@@ -5848,22 +5848,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="460" t="s">
+      <c r="B57" s="462" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="460"/>
-      <c r="D57" s="460"/>
-      <c r="E57" s="460"/>
-      <c r="F57" s="460"/>
+      <c r="C57" s="462"/>
+      <c r="D57" s="462"/>
+      <c r="E57" s="462"/>
+      <c r="F57" s="462"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="460" t="s">
+      <c r="B58" s="462" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="460"/>
-      <c r="D58" s="460"/>
-      <c r="E58" s="460"/>
-      <c r="F58" s="460"/>
+      <c r="C58" s="462"/>
+      <c r="D58" s="462"/>
+      <c r="E58" s="462"/>
+      <c r="F58" s="462"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>7.3789748588673543E-2</v>
+        <v>7.4978743561049638E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5907,7 +5907,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>2.741086016338299E-2</v>
+        <v>2.7852539062500001E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>321</v>
@@ -5998,13 +5998,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="460" t="s">
+      <c r="B73" s="462" t="s">
         <v>476</v>
       </c>
-      <c r="C73" s="460"/>
-      <c r="D73" s="460"/>
-      <c r="E73" s="460"/>
-      <c r="F73" s="460"/>
+      <c r="C73" s="462"/>
+      <c r="D73" s="462"/>
+      <c r="E73" s="462"/>
+      <c r="F73" s="462"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6023,13 +6023,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="460" t="s">
+      <c r="B77" s="462" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="460"/>
-      <c r="D77" s="460"/>
-      <c r="E77" s="460"/>
-      <c r="F77" s="460"/>
+      <c r="C77" s="462"/>
+      <c r="D77" s="462"/>
+      <c r="E77" s="462"/>
+      <c r="F77" s="462"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6198,31 +6198,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="460" t="s">
+      <c r="B96" s="462" t="s">
         <v>483</v>
       </c>
-      <c r="C96" s="460"/>
-      <c r="D96" s="460"/>
-      <c r="E96" s="460"/>
-      <c r="F96" s="460"/>
+      <c r="C96" s="462"/>
+      <c r="D96" s="462"/>
+      <c r="E96" s="462"/>
+      <c r="F96" s="462"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="462" t="s">
+      <c r="B97" s="466" t="s">
         <v>482</v>
       </c>
-      <c r="C97" s="462"/>
-      <c r="D97" s="462"/>
-      <c r="E97" s="462"/>
-      <c r="F97" s="462"/>
+      <c r="C97" s="466"/>
+      <c r="D97" s="466"/>
+      <c r="E97" s="466"/>
+      <c r="F97" s="466"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="462" t="s">
+      <c r="B98" s="466" t="s">
         <v>481</v>
       </c>
-      <c r="C98" s="462"/>
-      <c r="D98" s="462"/>
-      <c r="E98" s="462"/>
-      <c r="F98" s="462"/>
+      <c r="C98" s="466"/>
+      <c r="D98" s="466"/>
+      <c r="E98" s="466"/>
+      <c r="F98" s="466"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6272,22 +6272,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="460" t="s">
+      <c r="B107" s="462" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="460"/>
-      <c r="D107" s="460"/>
-      <c r="E107" s="460"/>
-      <c r="F107" s="460"/>
+      <c r="C107" s="462"/>
+      <c r="D107" s="462"/>
+      <c r="E107" s="462"/>
+      <c r="F107" s="462"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="460" t="s">
+      <c r="B108" s="462" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="460"/>
-      <c r="D108" s="460"/>
-      <c r="E108" s="460"/>
-      <c r="F108" s="460"/>
+      <c r="C108" s="462"/>
+      <c r="D108" s="462"/>
+      <c r="E108" s="462"/>
+      <c r="F108" s="462"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6321,13 +6321,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="460" t="s">
+      <c r="B114" s="462" t="s">
         <v>489</v>
       </c>
-      <c r="C114" s="460"/>
-      <c r="D114" s="460"/>
-      <c r="E114" s="460"/>
-      <c r="F114" s="460"/>
+      <c r="C114" s="462"/>
+      <c r="D114" s="462"/>
+      <c r="E114" s="462"/>
+      <c r="F114" s="462"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6462,13 +6462,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="461" t="s">
+      <c r="B124" s="463" t="s">
         <v>355</v>
       </c>
-      <c r="C124" s="461"/>
-      <c r="D124" s="461"/>
-      <c r="E124" s="461"/>
-      <c r="F124" s="461"/>
+      <c r="C124" s="463"/>
+      <c r="D124" s="463"/>
+      <c r="E124" s="463"/>
+      <c r="F124" s="463"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6503,22 +6503,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="463" t="s">
+      <c r="B131" s="467" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="463"/>
-      <c r="D131" s="463"/>
-      <c r="E131" s="463"/>
-      <c r="F131" s="463"/>
+      <c r="C131" s="467"/>
+      <c r="D131" s="467"/>
+      <c r="E131" s="467"/>
+      <c r="F131" s="467"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="460" t="s">
+      <c r="B132" s="462" t="s">
         <v>357</v>
       </c>
-      <c r="C132" s="460"/>
-      <c r="D132" s="460"/>
-      <c r="E132" s="460"/>
-      <c r="F132" s="460"/>
+      <c r="C132" s="462"/>
+      <c r="D132" s="462"/>
+      <c r="E132" s="462"/>
+      <c r="F132" s="462"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6694,13 +6694,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="467" t="s">
+      <c r="B149" s="461" t="s">
         <v>358</v>
       </c>
-      <c r="C149" s="460"/>
-      <c r="D149" s="460"/>
-      <c r="E149" s="460"/>
-      <c r="F149" s="460"/>
+      <c r="C149" s="462"/>
+      <c r="D149" s="462"/>
+      <c r="E149" s="462"/>
+      <c r="F149" s="462"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6737,13 +6737,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="461" t="s">
+      <c r="B158" s="463" t="s">
         <v>436</v>
       </c>
-      <c r="C158" s="461"/>
-      <c r="D158" s="461"/>
-      <c r="E158" s="461"/>
-      <c r="F158" s="461"/>
+      <c r="C158" s="463"/>
+      <c r="D158" s="463"/>
+      <c r="E158" s="463"/>
+      <c r="F158" s="463"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6751,22 +6751,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="466" t="s">
+      <c r="B161" s="460" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="466"/>
-      <c r="D161" s="466"/>
-      <c r="E161" s="466"/>
-      <c r="F161" s="466"/>
+      <c r="C161" s="460"/>
+      <c r="D161" s="460"/>
+      <c r="E161" s="460"/>
+      <c r="F161" s="460"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="466" t="s">
+      <c r="B162" s="460" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="466"/>
-      <c r="D162" s="466"/>
-      <c r="E162" s="466"/>
-      <c r="F162" s="466"/>
+      <c r="C162" s="460"/>
+      <c r="D162" s="460"/>
+      <c r="E162" s="460"/>
+      <c r="F162" s="460"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6790,18 +6790,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6818,6 +6806,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -14008,16 +14008,16 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>2.741086016338299E-2</v>
+        <v>2.7852539062500001E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>2.741086016338299E-2</v>
+        <v>2.7852539062500001E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>4.0394041326285442E-2</v>
+        <v>4.1044921875000001E-2</v>
       </c>
       <c r="I92" s="22" t="str">
         <f t="shared" si="38"/>
@@ -15228,18 +15228,18 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>7.3789748588673543E-2</v>
+        <v>7.4978743561049638E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>6.5510648745207664E-2</v>
+        <v>6.656624025330915E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>6.3072738906263123E-2</v>
+        <v>6.4089047687467551E-2</v>
       </c>
       <c r="I124" s="74" t="str">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
@@ -15285,11 +15285,11 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.2186175548246643E-2</v>
+        <v>8.3510464509717414E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.804465463935456E-2</v>
+        <v>7.9302210109617605E-2</v>
       </c>
       <c r="I125" s="22" t="str">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -19747,7 +19747,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>104.05</v>
+        <v>102.4</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19758,7 +19758,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.11513532579667529</v>
+        <v>0.12123883246616156</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -20254,7 +20254,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>104.05</v>
+        <v>102.4</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20272,14 +20272,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>403881.31292025</v>
+        <v>397476.65971199999</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>526</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.11513532579667529</v>
+        <v>0.12123883246616156</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20287,13 +20287,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="471" t="s">
+      <c r="B12" s="474" t="s">
         <v>495</v>
       </c>
-      <c r="C12" s="471"/>
-      <c r="D12" s="471"/>
-      <c r="E12" s="471"/>
-      <c r="F12" s="471"/>
+      <c r="C12" s="474"/>
+      <c r="D12" s="474"/>
+      <c r="E12" s="474"/>
+      <c r="F12" s="474"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20478,22 +20478,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="471" t="s">
+      <c r="B29" s="474" t="s">
         <v>496</v>
       </c>
-      <c r="C29" s="471"/>
-      <c r="D29" s="471"/>
-      <c r="E29" s="471"/>
-      <c r="F29" s="471"/>
+      <c r="C29" s="474"/>
+      <c r="D29" s="474"/>
+      <c r="E29" s="474"/>
+      <c r="F29" s="474"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="472" t="s">
+      <c r="B30" s="477" t="s">
         <v>497</v>
       </c>
-      <c r="C30" s="472"/>
-      <c r="D30" s="472"/>
-      <c r="E30" s="472"/>
-      <c r="F30" s="472"/>
+      <c r="C30" s="477"/>
+      <c r="D30" s="477"/>
+      <c r="E30" s="477"/>
+      <c r="F30" s="477"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20683,10 +20683,10 @@
       <c r="B54" s="470" t="s">
         <v>504</v>
       </c>
-      <c r="C54" s="473"/>
-      <c r="D54" s="473"/>
-      <c r="E54" s="473"/>
-      <c r="F54" s="473"/>
+      <c r="C54" s="476"/>
+      <c r="D54" s="476"/>
+      <c r="E54" s="476"/>
+      <c r="F54" s="476"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20702,22 +20702,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="471" t="s">
+      <c r="B57" s="474" t="s">
         <v>505</v>
       </c>
-      <c r="C57" s="471"/>
-      <c r="D57" s="471"/>
-      <c r="E57" s="471"/>
-      <c r="F57" s="471"/>
+      <c r="C57" s="474"/>
+      <c r="D57" s="474"/>
+      <c r="E57" s="474"/>
+      <c r="F57" s="474"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="471" t="s">
+      <c r="B58" s="474" t="s">
         <v>506</v>
       </c>
-      <c r="C58" s="471"/>
-      <c r="D58" s="471"/>
-      <c r="E58" s="471"/>
-      <c r="F58" s="471"/>
+      <c r="C58" s="474"/>
+      <c r="D58" s="474"/>
+      <c r="E58" s="474"/>
+      <c r="F58" s="474"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20751,7 +20751,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>7.3789748588673543E-2</v>
+        <v>7.4978743561049638E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20761,7 +20761,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>2.741086016338299E-2</v>
+        <v>2.7852539062500001E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>371</v>
@@ -20852,22 +20852,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="471" t="s">
+      <c r="B73" s="474" t="s">
         <v>507</v>
       </c>
-      <c r="C73" s="471"/>
-      <c r="D73" s="471"/>
-      <c r="E73" s="471"/>
-      <c r="F73" s="471"/>
+      <c r="C73" s="474"/>
+      <c r="D73" s="474"/>
+      <c r="E73" s="474"/>
+      <c r="F73" s="474"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="472" t="s">
+      <c r="B74" s="477" t="s">
         <v>477</v>
       </c>
-      <c r="C74" s="472"/>
-      <c r="D74" s="472"/>
-      <c r="E74" s="472"/>
-      <c r="F74" s="472"/>
+      <c r="C74" s="477"/>
+      <c r="D74" s="477"/>
+      <c r="E74" s="477"/>
+      <c r="F74" s="477"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -20875,13 +20875,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="471" t="s">
+      <c r="B77" s="474" t="s">
         <v>508</v>
       </c>
-      <c r="C77" s="471"/>
-      <c r="D77" s="471"/>
-      <c r="E77" s="471"/>
-      <c r="F77" s="471"/>
+      <c r="C77" s="474"/>
+      <c r="D77" s="474"/>
+      <c r="E77" s="474"/>
+      <c r="F77" s="474"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21030,33 +21030,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="471" t="s">
+      <c r="B96" s="474" t="s">
         <v>511</v>
       </c>
-      <c r="C96" s="471"/>
-      <c r="D96" s="471"/>
-      <c r="E96" s="471"/>
-      <c r="F96" s="471"/>
+      <c r="C96" s="474"/>
+      <c r="D96" s="474"/>
+      <c r="E96" s="474"/>
+      <c r="F96" s="474"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="472" t="s">
+      <c r="B97" s="477" t="s">
         <v>512</v>
       </c>
-      <c r="C97" s="472"/>
-      <c r="D97" s="472"/>
-      <c r="E97" s="472"/>
-      <c r="F97" s="472"/>
+      <c r="C97" s="477"/>
+      <c r="D97" s="477"/>
+      <c r="E97" s="477"/>
+      <c r="F97" s="477"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="472" t="s">
+      <c r="B98" s="477" t="s">
         <v>513</v>
       </c>
-      <c r="C98" s="472"/>
-      <c r="D98" s="472"/>
-      <c r="E98" s="472"/>
-      <c r="F98" s="472"/>
+      <c r="C98" s="477"/>
+      <c r="D98" s="477"/>
+      <c r="E98" s="477"/>
+      <c r="F98" s="477"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21119,23 +21119,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="471" t="s">
+      <c r="B107" s="474" t="s">
         <v>514</v>
       </c>
-      <c r="C107" s="471"/>
-      <c r="D107" s="471"/>
-      <c r="E107" s="471"/>
-      <c r="F107" s="471"/>
+      <c r="C107" s="474"/>
+      <c r="D107" s="474"/>
+      <c r="E107" s="474"/>
+      <c r="F107" s="474"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="471" t="s">
+      <c r="B108" s="474" t="s">
         <v>533</v>
       </c>
-      <c r="C108" s="471"/>
-      <c r="D108" s="471"/>
-      <c r="E108" s="471"/>
-      <c r="F108" s="471"/>
+      <c r="C108" s="474"/>
+      <c r="D108" s="474"/>
+      <c r="E108" s="474"/>
+      <c r="F108" s="474"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21179,13 +21179,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="471" t="s">
+      <c r="B114" s="474" t="s">
         <v>515</v>
       </c>
-      <c r="C114" s="471"/>
-      <c r="D114" s="471"/>
-      <c r="E114" s="471"/>
-      <c r="F114" s="471"/>
+      <c r="C114" s="474"/>
+      <c r="D114" s="474"/>
+      <c r="E114" s="474"/>
+      <c r="F114" s="474"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21349,13 +21349,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="475" t="s">
+      <c r="B127" s="472" t="s">
         <v>517</v>
       </c>
-      <c r="C127" s="475"/>
-      <c r="D127" s="475"/>
-      <c r="E127" s="475"/>
-      <c r="F127" s="475"/>
+      <c r="C127" s="472"/>
+      <c r="D127" s="472"/>
+      <c r="E127" s="472"/>
+      <c r="F127" s="472"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21368,22 +21368,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="476" t="s">
+      <c r="B131" s="473" t="s">
         <v>518</v>
       </c>
-      <c r="C131" s="476"/>
-      <c r="D131" s="476"/>
-      <c r="E131" s="476"/>
-      <c r="F131" s="476"/>
+      <c r="C131" s="473"/>
+      <c r="D131" s="473"/>
+      <c r="E131" s="473"/>
+      <c r="F131" s="473"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="471" t="s">
+      <c r="B132" s="474" t="s">
         <v>519</v>
       </c>
-      <c r="C132" s="471"/>
-      <c r="D132" s="471"/>
-      <c r="E132" s="471"/>
-      <c r="F132" s="471"/>
+      <c r="C132" s="474"/>
+      <c r="D132" s="474"/>
+      <c r="E132" s="474"/>
+      <c r="F132" s="474"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21552,13 +21552,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="477" t="s">
+      <c r="B149" s="475" t="s">
         <v>520</v>
       </c>
-      <c r="C149" s="471"/>
-      <c r="D149" s="471"/>
-      <c r="E149" s="471"/>
-      <c r="F149" s="471"/>
+      <c r="C149" s="474"/>
+      <c r="D149" s="474"/>
+      <c r="E149" s="474"/>
+      <c r="F149" s="474"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21566,13 +21566,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="473" t="s">
+      <c r="B152" s="476" t="s">
         <v>521</v>
       </c>
-      <c r="C152" s="473"/>
-      <c r="D152" s="473"/>
-      <c r="E152" s="473"/>
-      <c r="F152" s="473"/>
+      <c r="C152" s="476"/>
+      <c r="D152" s="476"/>
+      <c r="E152" s="476"/>
+      <c r="F152" s="476"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21609,22 +21609,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="474" t="s">
+      <c r="B161" s="471" t="s">
         <v>386</v>
       </c>
-      <c r="C161" s="474"/>
-      <c r="D161" s="474"/>
-      <c r="E161" s="474"/>
-      <c r="F161" s="474"/>
+      <c r="C161" s="471"/>
+      <c r="D161" s="471"/>
+      <c r="E161" s="471"/>
+      <c r="F161" s="471"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="474" t="s">
+      <c r="B162" s="471" t="s">
         <v>387</v>
       </c>
-      <c r="C162" s="474"/>
-      <c r="D162" s="474"/>
-      <c r="E162" s="474"/>
-      <c r="F162" s="474"/>
+      <c r="C162" s="471"/>
+      <c r="D162" s="471"/>
+      <c r="E162" s="471"/>
+      <c r="F162" s="471"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21648,15 +21648,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21671,12 +21668,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/000858.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/000858.SZ_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72FE379C-0D44-4857-9D0B-3E7A901CFB13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DEC2F9F-A83F-4739-BD9E-2D57AD4FF104}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4986,30 +4986,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5019,6 +5019,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5028,16 +5037,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5407,7 +5407,7 @@
         <v>348</v>
       </c>
       <c r="C8" s="47">
-        <v>102.4</v>
+        <v>102.26</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5425,14 +5425,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>397476.65971199999</v>
+        <v>396933.23459130008</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>525</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.12123883246616156</v>
+        <v>0.12176283506510555</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5440,13 +5440,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="462" t="s">
+      <c r="B12" s="460" t="s">
         <v>353</v>
       </c>
-      <c r="C12" s="462"/>
-      <c r="D12" s="462"/>
-      <c r="E12" s="462"/>
-      <c r="F12" s="462"/>
+      <c r="C12" s="460"/>
+      <c r="D12" s="460"/>
+      <c r="E12" s="460"/>
+      <c r="F12" s="460"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5624,22 +5624,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="462" t="s">
+      <c r="B29" s="460" t="s">
         <v>354</v>
       </c>
-      <c r="C29" s="462"/>
-      <c r="D29" s="462"/>
-      <c r="E29" s="462"/>
-      <c r="F29" s="462"/>
+      <c r="C29" s="460"/>
+      <c r="D29" s="460"/>
+      <c r="E29" s="460"/>
+      <c r="F29" s="460"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="466" t="s">
+      <c r="B30" s="462" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="466"/>
-      <c r="D30" s="466"/>
-      <c r="E30" s="466"/>
-      <c r="F30" s="466"/>
+      <c r="C30" s="462"/>
+      <c r="D30" s="462"/>
+      <c r="E30" s="462"/>
+      <c r="F30" s="462"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5651,13 +5651,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="463" t="s">
+      <c r="B33" s="461" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="463"/>
-      <c r="D33" s="463"/>
-      <c r="E33" s="463"/>
-      <c r="F33" s="463"/>
+      <c r="C33" s="461"/>
+      <c r="D33" s="461"/>
+      <c r="E33" s="461"/>
+      <c r="F33" s="461"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5677,13 +5677,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="463" t="s">
+      <c r="B36" s="461" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="463"/>
-      <c r="D36" s="463"/>
-      <c r="E36" s="463"/>
-      <c r="F36" s="463"/>
+      <c r="C36" s="461"/>
+      <c r="D36" s="461"/>
+      <c r="E36" s="461"/>
+      <c r="F36" s="461"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5712,13 +5712,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="463" t="s">
+      <c r="B40" s="461" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="463"/>
-      <c r="D40" s="463"/>
-      <c r="E40" s="463"/>
-      <c r="F40" s="463"/>
+      <c r="C40" s="461"/>
+      <c r="D40" s="461"/>
+      <c r="E40" s="461"/>
+      <c r="F40" s="461"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5734,13 +5734,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="463" t="s">
+      <c r="B43" s="461" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="463"/>
-      <c r="D43" s="463"/>
-      <c r="E43" s="463"/>
-      <c r="F43" s="463"/>
+      <c r="C43" s="461"/>
+      <c r="D43" s="461"/>
+      <c r="E43" s="461"/>
+      <c r="F43" s="461"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5804,13 +5804,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="463" t="s">
+      <c r="B51" s="461" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="463"/>
-      <c r="D51" s="463"/>
-      <c r="E51" s="463"/>
-      <c r="F51" s="463"/>
+      <c r="C51" s="461"/>
+      <c r="D51" s="461"/>
+      <c r="E51" s="461"/>
+      <c r="F51" s="461"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5826,7 +5826,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="463" t="s">
+      <c r="B54" s="461" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="464"/>
@@ -5848,22 +5848,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="462" t="s">
+      <c r="B57" s="460" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="462"/>
-      <c r="D57" s="462"/>
-      <c r="E57" s="462"/>
-      <c r="F57" s="462"/>
+      <c r="C57" s="460"/>
+      <c r="D57" s="460"/>
+      <c r="E57" s="460"/>
+      <c r="F57" s="460"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="462" t="s">
+      <c r="B58" s="460" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="462"/>
-      <c r="D58" s="462"/>
-      <c r="E58" s="462"/>
-      <c r="F58" s="462"/>
+      <c r="C58" s="460"/>
+      <c r="D58" s="460"/>
+      <c r="E58" s="460"/>
+      <c r="F58" s="460"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>7.4978743561049638E-2</v>
+        <v>7.5081393904278135E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5907,7 +5907,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>2.7852539062500001E-2</v>
+        <v>2.7890670839037745E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>321</v>
@@ -5998,13 +5998,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="462" t="s">
+      <c r="B73" s="460" t="s">
         <v>476</v>
       </c>
-      <c r="C73" s="462"/>
-      <c r="D73" s="462"/>
-      <c r="E73" s="462"/>
-      <c r="F73" s="462"/>
+      <c r="C73" s="460"/>
+      <c r="D73" s="460"/>
+      <c r="E73" s="460"/>
+      <c r="F73" s="460"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6023,13 +6023,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="462" t="s">
+      <c r="B77" s="460" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="462"/>
-      <c r="D77" s="462"/>
-      <c r="E77" s="462"/>
-      <c r="F77" s="462"/>
+      <c r="C77" s="460"/>
+      <c r="D77" s="460"/>
+      <c r="E77" s="460"/>
+      <c r="F77" s="460"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6198,31 +6198,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="462" t="s">
+      <c r="B96" s="460" t="s">
         <v>483</v>
       </c>
-      <c r="C96" s="462"/>
-      <c r="D96" s="462"/>
-      <c r="E96" s="462"/>
-      <c r="F96" s="462"/>
+      <c r="C96" s="460"/>
+      <c r="D96" s="460"/>
+      <c r="E96" s="460"/>
+      <c r="F96" s="460"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="466" t="s">
+      <c r="B97" s="462" t="s">
         <v>482</v>
       </c>
-      <c r="C97" s="466"/>
-      <c r="D97" s="466"/>
-      <c r="E97" s="466"/>
-      <c r="F97" s="466"/>
+      <c r="C97" s="462"/>
+      <c r="D97" s="462"/>
+      <c r="E97" s="462"/>
+      <c r="F97" s="462"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="466" t="s">
+      <c r="B98" s="462" t="s">
         <v>481</v>
       </c>
-      <c r="C98" s="466"/>
-      <c r="D98" s="466"/>
-      <c r="E98" s="466"/>
-      <c r="F98" s="466"/>
+      <c r="C98" s="462"/>
+      <c r="D98" s="462"/>
+      <c r="E98" s="462"/>
+      <c r="F98" s="462"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6272,22 +6272,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="462" t="s">
+      <c r="B107" s="460" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="462"/>
-      <c r="D107" s="462"/>
-      <c r="E107" s="462"/>
-      <c r="F107" s="462"/>
+      <c r="C107" s="460"/>
+      <c r="D107" s="460"/>
+      <c r="E107" s="460"/>
+      <c r="F107" s="460"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="462" t="s">
+      <c r="B108" s="460" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="462"/>
-      <c r="D108" s="462"/>
-      <c r="E108" s="462"/>
-      <c r="F108" s="462"/>
+      <c r="C108" s="460"/>
+      <c r="D108" s="460"/>
+      <c r="E108" s="460"/>
+      <c r="F108" s="460"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6321,13 +6321,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="462" t="s">
+      <c r="B114" s="460" t="s">
         <v>489</v>
       </c>
-      <c r="C114" s="462"/>
-      <c r="D114" s="462"/>
-      <c r="E114" s="462"/>
-      <c r="F114" s="462"/>
+      <c r="C114" s="460"/>
+      <c r="D114" s="460"/>
+      <c r="E114" s="460"/>
+      <c r="F114" s="460"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6462,13 +6462,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="463" t="s">
+      <c r="B124" s="461" t="s">
         <v>355</v>
       </c>
-      <c r="C124" s="463"/>
-      <c r="D124" s="463"/>
-      <c r="E124" s="463"/>
-      <c r="F124" s="463"/>
+      <c r="C124" s="461"/>
+      <c r="D124" s="461"/>
+      <c r="E124" s="461"/>
+      <c r="F124" s="461"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6503,22 +6503,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="467" t="s">
+      <c r="B131" s="463" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="467"/>
-      <c r="D131" s="467"/>
-      <c r="E131" s="467"/>
-      <c r="F131" s="467"/>
+      <c r="C131" s="463"/>
+      <c r="D131" s="463"/>
+      <c r="E131" s="463"/>
+      <c r="F131" s="463"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="462" t="s">
+      <c r="B132" s="460" t="s">
         <v>357</v>
       </c>
-      <c r="C132" s="462"/>
-      <c r="D132" s="462"/>
-      <c r="E132" s="462"/>
-      <c r="F132" s="462"/>
+      <c r="C132" s="460"/>
+      <c r="D132" s="460"/>
+      <c r="E132" s="460"/>
+      <c r="F132" s="460"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6694,13 +6694,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="461" t="s">
+      <c r="B149" s="467" t="s">
         <v>358</v>
       </c>
-      <c r="C149" s="462"/>
-      <c r="D149" s="462"/>
-      <c r="E149" s="462"/>
-      <c r="F149" s="462"/>
+      <c r="C149" s="460"/>
+      <c r="D149" s="460"/>
+      <c r="E149" s="460"/>
+      <c r="F149" s="460"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6737,13 +6737,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="463" t="s">
+      <c r="B158" s="461" t="s">
         <v>436</v>
       </c>
-      <c r="C158" s="463"/>
-      <c r="D158" s="463"/>
-      <c r="E158" s="463"/>
-      <c r="F158" s="463"/>
+      <c r="C158" s="461"/>
+      <c r="D158" s="461"/>
+      <c r="E158" s="461"/>
+      <c r="F158" s="461"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6751,22 +6751,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="460" t="s">
+      <c r="B161" s="466" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="460"/>
-      <c r="D161" s="460"/>
-      <c r="E161" s="460"/>
-      <c r="F161" s="460"/>
+      <c r="C161" s="466"/>
+      <c r="D161" s="466"/>
+      <c r="E161" s="466"/>
+      <c r="F161" s="466"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="460" t="s">
+      <c r="B162" s="466" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="460"/>
-      <c r="D162" s="460"/>
-      <c r="E162" s="460"/>
-      <c r="F162" s="460"/>
+      <c r="C162" s="466"/>
+      <c r="D162" s="466"/>
+      <c r="E162" s="466"/>
+      <c r="F162" s="466"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6790,6 +6790,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6806,18 +6818,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -14008,16 +14008,16 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>2.7852539062500001E-2</v>
+        <v>2.7890670839037745E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>2.7852539062500001E-2</v>
+        <v>2.7890670839037745E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>4.1044921875000001E-2</v>
+        <v>4.1101114805398006E-2</v>
       </c>
       <c r="I92" s="22" t="str">
         <f t="shared" si="38"/>
@@ -15228,18 +15228,18 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>7.4978743561049638E-2</v>
+        <v>7.5081393904278135E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>6.656624025330915E-2</v>
+        <v>6.6657373380978449E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>6.4089047687467551E-2</v>
+        <v>6.4176789391714034E-2</v>
       </c>
       <c r="I124" s="74" t="str">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
@@ -15285,11 +15285,11 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.3510464509717414E-2</v>
+        <v>8.3624795284520451E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.9302210109617605E-2</v>
+        <v>7.9410779534762777E-2</v>
       </c>
       <c r="I125" s="22" t="str">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -19747,7 +19747,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>102.4</v>
+        <v>102.26</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19758,7 +19758,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.12123883246616156</v>
+        <v>0.12176283506510555</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -20254,7 +20254,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>102.4</v>
+        <v>102.26</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20272,14 +20272,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>397476.65971199999</v>
+        <v>396933.23459130008</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>526</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.12123883246616156</v>
+        <v>0.12176283506510555</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20287,13 +20287,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="474" t="s">
+      <c r="B12" s="471" t="s">
         <v>495</v>
       </c>
-      <c r="C12" s="474"/>
-      <c r="D12" s="474"/>
-      <c r="E12" s="474"/>
-      <c r="F12" s="474"/>
+      <c r="C12" s="471"/>
+      <c r="D12" s="471"/>
+      <c r="E12" s="471"/>
+      <c r="F12" s="471"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20478,22 +20478,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="474" t="s">
+      <c r="B29" s="471" t="s">
         <v>496</v>
       </c>
-      <c r="C29" s="474"/>
-      <c r="D29" s="474"/>
-      <c r="E29" s="474"/>
-      <c r="F29" s="474"/>
+      <c r="C29" s="471"/>
+      <c r="D29" s="471"/>
+      <c r="E29" s="471"/>
+      <c r="F29" s="471"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="477" t="s">
+      <c r="B30" s="472" t="s">
         <v>497</v>
       </c>
-      <c r="C30" s="477"/>
-      <c r="D30" s="477"/>
-      <c r="E30" s="477"/>
-      <c r="F30" s="477"/>
+      <c r="C30" s="472"/>
+      <c r="D30" s="472"/>
+      <c r="E30" s="472"/>
+      <c r="F30" s="472"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20683,10 +20683,10 @@
       <c r="B54" s="470" t="s">
         <v>504</v>
       </c>
-      <c r="C54" s="476"/>
-      <c r="D54" s="476"/>
-      <c r="E54" s="476"/>
-      <c r="F54" s="476"/>
+      <c r="C54" s="473"/>
+      <c r="D54" s="473"/>
+      <c r="E54" s="473"/>
+      <c r="F54" s="473"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20702,22 +20702,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="474" t="s">
+      <c r="B57" s="471" t="s">
         <v>505</v>
       </c>
-      <c r="C57" s="474"/>
-      <c r="D57" s="474"/>
-      <c r="E57" s="474"/>
-      <c r="F57" s="474"/>
+      <c r="C57" s="471"/>
+      <c r="D57" s="471"/>
+      <c r="E57" s="471"/>
+      <c r="F57" s="471"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="474" t="s">
+      <c r="B58" s="471" t="s">
         <v>506</v>
       </c>
-      <c r="C58" s="474"/>
-      <c r="D58" s="474"/>
-      <c r="E58" s="474"/>
-      <c r="F58" s="474"/>
+      <c r="C58" s="471"/>
+      <c r="D58" s="471"/>
+      <c r="E58" s="471"/>
+      <c r="F58" s="471"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20751,7 +20751,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>7.4978743561049638E-2</v>
+        <v>7.5081393904278135E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20761,7 +20761,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>2.7852539062500001E-2</v>
+        <v>2.7890670839037745E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>371</v>
@@ -20852,22 +20852,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="474" t="s">
+      <c r="B73" s="471" t="s">
         <v>507</v>
       </c>
-      <c r="C73" s="474"/>
-      <c r="D73" s="474"/>
-      <c r="E73" s="474"/>
-      <c r="F73" s="474"/>
+      <c r="C73" s="471"/>
+      <c r="D73" s="471"/>
+      <c r="E73" s="471"/>
+      <c r="F73" s="471"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="477" t="s">
+      <c r="B74" s="472" t="s">
         <v>477</v>
       </c>
-      <c r="C74" s="477"/>
-      <c r="D74" s="477"/>
-      <c r="E74" s="477"/>
-      <c r="F74" s="477"/>
+      <c r="C74" s="472"/>
+      <c r="D74" s="472"/>
+      <c r="E74" s="472"/>
+      <c r="F74" s="472"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -20875,13 +20875,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="474" t="s">
+      <c r="B77" s="471" t="s">
         <v>508</v>
       </c>
-      <c r="C77" s="474"/>
-      <c r="D77" s="474"/>
-      <c r="E77" s="474"/>
-      <c r="F77" s="474"/>
+      <c r="C77" s="471"/>
+      <c r="D77" s="471"/>
+      <c r="E77" s="471"/>
+      <c r="F77" s="471"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21030,33 +21030,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="474" t="s">
+      <c r="B96" s="471" t="s">
         <v>511</v>
       </c>
-      <c r="C96" s="474"/>
-      <c r="D96" s="474"/>
-      <c r="E96" s="474"/>
-      <c r="F96" s="474"/>
+      <c r="C96" s="471"/>
+      <c r="D96" s="471"/>
+      <c r="E96" s="471"/>
+      <c r="F96" s="471"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="477" t="s">
+      <c r="B97" s="472" t="s">
         <v>512</v>
       </c>
-      <c r="C97" s="477"/>
-      <c r="D97" s="477"/>
-      <c r="E97" s="477"/>
-      <c r="F97" s="477"/>
+      <c r="C97" s="472"/>
+      <c r="D97" s="472"/>
+      <c r="E97" s="472"/>
+      <c r="F97" s="472"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="477" t="s">
+      <c r="B98" s="472" t="s">
         <v>513</v>
       </c>
-      <c r="C98" s="477"/>
-      <c r="D98" s="477"/>
-      <c r="E98" s="477"/>
-      <c r="F98" s="477"/>
+      <c r="C98" s="472"/>
+      <c r="D98" s="472"/>
+      <c r="E98" s="472"/>
+      <c r="F98" s="472"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21119,23 +21119,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="474" t="s">
+      <c r="B107" s="471" t="s">
         <v>514</v>
       </c>
-      <c r="C107" s="474"/>
-      <c r="D107" s="474"/>
-      <c r="E107" s="474"/>
-      <c r="F107" s="474"/>
+      <c r="C107" s="471"/>
+      <c r="D107" s="471"/>
+      <c r="E107" s="471"/>
+      <c r="F107" s="471"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="474" t="s">
+      <c r="B108" s="471" t="s">
         <v>533</v>
       </c>
-      <c r="C108" s="474"/>
-      <c r="D108" s="474"/>
-      <c r="E108" s="474"/>
-      <c r="F108" s="474"/>
+      <c r="C108" s="471"/>
+      <c r="D108" s="471"/>
+      <c r="E108" s="471"/>
+      <c r="F108" s="471"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21179,13 +21179,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="474" t="s">
+      <c r="B114" s="471" t="s">
         <v>515</v>
       </c>
-      <c r="C114" s="474"/>
-      <c r="D114" s="474"/>
-      <c r="E114" s="474"/>
-      <c r="F114" s="474"/>
+      <c r="C114" s="471"/>
+      <c r="D114" s="471"/>
+      <c r="E114" s="471"/>
+      <c r="F114" s="471"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21349,13 +21349,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="472" t="s">
+      <c r="B127" s="475" t="s">
         <v>517</v>
       </c>
-      <c r="C127" s="472"/>
-      <c r="D127" s="472"/>
-      <c r="E127" s="472"/>
-      <c r="F127" s="472"/>
+      <c r="C127" s="475"/>
+      <c r="D127" s="475"/>
+      <c r="E127" s="475"/>
+      <c r="F127" s="475"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21368,22 +21368,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="473" t="s">
+      <c r="B131" s="476" t="s">
         <v>518</v>
       </c>
-      <c r="C131" s="473"/>
-      <c r="D131" s="473"/>
-      <c r="E131" s="473"/>
-      <c r="F131" s="473"/>
+      <c r="C131" s="476"/>
+      <c r="D131" s="476"/>
+      <c r="E131" s="476"/>
+      <c r="F131" s="476"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="474" t="s">
+      <c r="B132" s="471" t="s">
         <v>519</v>
       </c>
-      <c r="C132" s="474"/>
-      <c r="D132" s="474"/>
-      <c r="E132" s="474"/>
-      <c r="F132" s="474"/>
+      <c r="C132" s="471"/>
+      <c r="D132" s="471"/>
+      <c r="E132" s="471"/>
+      <c r="F132" s="471"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21552,13 +21552,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="475" t="s">
+      <c r="B149" s="477" t="s">
         <v>520</v>
       </c>
-      <c r="C149" s="474"/>
-      <c r="D149" s="474"/>
-      <c r="E149" s="474"/>
-      <c r="F149" s="474"/>
+      <c r="C149" s="471"/>
+      <c r="D149" s="471"/>
+      <c r="E149" s="471"/>
+      <c r="F149" s="471"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21566,13 +21566,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="476" t="s">
+      <c r="B152" s="473" t="s">
         <v>521</v>
       </c>
-      <c r="C152" s="476"/>
-      <c r="D152" s="476"/>
-      <c r="E152" s="476"/>
-      <c r="F152" s="476"/>
+      <c r="C152" s="473"/>
+      <c r="D152" s="473"/>
+      <c r="E152" s="473"/>
+      <c r="F152" s="473"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21609,22 +21609,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="471" t="s">
+      <c r="B161" s="474" t="s">
         <v>386</v>
       </c>
-      <c r="C161" s="471"/>
-      <c r="D161" s="471"/>
-      <c r="E161" s="471"/>
-      <c r="F161" s="471"/>
+      <c r="C161" s="474"/>
+      <c r="D161" s="474"/>
+      <c r="E161" s="474"/>
+      <c r="F161" s="474"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="471" t="s">
+      <c r="B162" s="474" t="s">
         <v>387</v>
       </c>
-      <c r="C162" s="471"/>
-      <c r="D162" s="471"/>
-      <c r="E162" s="471"/>
-      <c r="F162" s="471"/>
+      <c r="C162" s="474"/>
+      <c r="D162" s="474"/>
+      <c r="E162" s="474"/>
+      <c r="F162" s="474"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21648,12 +21648,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21668,15 +21671,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/000858.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/000858.SZ_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DEC2F9F-A83F-4739-BD9E-2D57AD4FF104}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF4CD423-9340-44A9-BCB4-C09BA4E84EC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1837" yWindow="1837" windowWidth="12691" windowHeight="7643" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4986,30 +4986,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5019,25 +5019,25 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5407,7 +5407,7 @@
         <v>348</v>
       </c>
       <c r="C8" s="47">
-        <v>102.26</v>
+        <v>102.18</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5425,14 +5425,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>396933.23459130008</v>
+        <v>396622.70595090004</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>525</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.12176283506510555</v>
+        <v>0.12206270179382848</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5440,13 +5440,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="460" t="s">
+      <c r="B12" s="462" t="s">
         <v>353</v>
       </c>
-      <c r="C12" s="460"/>
-      <c r="D12" s="460"/>
-      <c r="E12" s="460"/>
-      <c r="F12" s="460"/>
+      <c r="C12" s="462"/>
+      <c r="D12" s="462"/>
+      <c r="E12" s="462"/>
+      <c r="F12" s="462"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5624,22 +5624,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="460" t="s">
+      <c r="B29" s="462" t="s">
         <v>354</v>
       </c>
-      <c r="C29" s="460"/>
-      <c r="D29" s="460"/>
-      <c r="E29" s="460"/>
-      <c r="F29" s="460"/>
+      <c r="C29" s="462"/>
+      <c r="D29" s="462"/>
+      <c r="E29" s="462"/>
+      <c r="F29" s="462"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="462" t="s">
+      <c r="B30" s="466" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="462"/>
-      <c r="D30" s="462"/>
-      <c r="E30" s="462"/>
-      <c r="F30" s="462"/>
+      <c r="C30" s="466"/>
+      <c r="D30" s="466"/>
+      <c r="E30" s="466"/>
+      <c r="F30" s="466"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5651,13 +5651,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="461" t="s">
+      <c r="B33" s="463" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="461"/>
-      <c r="D33" s="461"/>
-      <c r="E33" s="461"/>
-      <c r="F33" s="461"/>
+      <c r="C33" s="463"/>
+      <c r="D33" s="463"/>
+      <c r="E33" s="463"/>
+      <c r="F33" s="463"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5677,13 +5677,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="461" t="s">
+      <c r="B36" s="463" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="461"/>
-      <c r="D36" s="461"/>
-      <c r="E36" s="461"/>
-      <c r="F36" s="461"/>
+      <c r="C36" s="463"/>
+      <c r="D36" s="463"/>
+      <c r="E36" s="463"/>
+      <c r="F36" s="463"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5712,13 +5712,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="461" t="s">
+      <c r="B40" s="463" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="461"/>
-      <c r="D40" s="461"/>
-      <c r="E40" s="461"/>
-      <c r="F40" s="461"/>
+      <c r="C40" s="463"/>
+      <c r="D40" s="463"/>
+      <c r="E40" s="463"/>
+      <c r="F40" s="463"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5734,13 +5734,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="461" t="s">
+      <c r="B43" s="463" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="461"/>
-      <c r="D43" s="461"/>
-      <c r="E43" s="461"/>
-      <c r="F43" s="461"/>
+      <c r="C43" s="463"/>
+      <c r="D43" s="463"/>
+      <c r="E43" s="463"/>
+      <c r="F43" s="463"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5804,13 +5804,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="461" t="s">
+      <c r="B51" s="463" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="461"/>
-      <c r="D51" s="461"/>
-      <c r="E51" s="461"/>
-      <c r="F51" s="461"/>
+      <c r="C51" s="463"/>
+      <c r="D51" s="463"/>
+      <c r="E51" s="463"/>
+      <c r="F51" s="463"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5826,7 +5826,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="461" t="s">
+      <c r="B54" s="463" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="464"/>
@@ -5848,22 +5848,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="460" t="s">
+      <c r="B57" s="462" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="460"/>
-      <c r="D57" s="460"/>
-      <c r="E57" s="460"/>
-      <c r="F57" s="460"/>
+      <c r="C57" s="462"/>
+      <c r="D57" s="462"/>
+      <c r="E57" s="462"/>
+      <c r="F57" s="462"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="460" t="s">
+      <c r="B58" s="462" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="460"/>
-      <c r="D58" s="460"/>
-      <c r="E58" s="460"/>
-      <c r="F58" s="460"/>
+      <c r="C58" s="462"/>
+      <c r="D58" s="462"/>
+      <c r="E58" s="462"/>
+      <c r="F58" s="462"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>7.5081393904278135E-2</v>
+        <v>7.5140177536225108E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5907,7 +5907,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>2.7890670839037745E-2</v>
+        <v>2.7912507339988256E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>321</v>
@@ -5998,13 +5998,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="460" t="s">
+      <c r="B73" s="462" t="s">
         <v>476</v>
       </c>
-      <c r="C73" s="460"/>
-      <c r="D73" s="460"/>
-      <c r="E73" s="460"/>
-      <c r="F73" s="460"/>
+      <c r="C73" s="462"/>
+      <c r="D73" s="462"/>
+      <c r="E73" s="462"/>
+      <c r="F73" s="462"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6023,13 +6023,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="460" t="s">
+      <c r="B77" s="462" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="460"/>
-      <c r="D77" s="460"/>
-      <c r="E77" s="460"/>
-      <c r="F77" s="460"/>
+      <c r="C77" s="462"/>
+      <c r="D77" s="462"/>
+      <c r="E77" s="462"/>
+      <c r="F77" s="462"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6198,31 +6198,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="460" t="s">
+      <c r="B96" s="462" t="s">
         <v>483</v>
       </c>
-      <c r="C96" s="460"/>
-      <c r="D96" s="460"/>
-      <c r="E96" s="460"/>
-      <c r="F96" s="460"/>
+      <c r="C96" s="462"/>
+      <c r="D96" s="462"/>
+      <c r="E96" s="462"/>
+      <c r="F96" s="462"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="462" t="s">
+      <c r="B97" s="466" t="s">
         <v>482</v>
       </c>
-      <c r="C97" s="462"/>
-      <c r="D97" s="462"/>
-      <c r="E97" s="462"/>
-      <c r="F97" s="462"/>
+      <c r="C97" s="466"/>
+      <c r="D97" s="466"/>
+      <c r="E97" s="466"/>
+      <c r="F97" s="466"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="462" t="s">
+      <c r="B98" s="466" t="s">
         <v>481</v>
       </c>
-      <c r="C98" s="462"/>
-      <c r="D98" s="462"/>
-      <c r="E98" s="462"/>
-      <c r="F98" s="462"/>
+      <c r="C98" s="466"/>
+      <c r="D98" s="466"/>
+      <c r="E98" s="466"/>
+      <c r="F98" s="466"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6272,22 +6272,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="460" t="s">
+      <c r="B107" s="462" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="460"/>
-      <c r="D107" s="460"/>
-      <c r="E107" s="460"/>
-      <c r="F107" s="460"/>
+      <c r="C107" s="462"/>
+      <c r="D107" s="462"/>
+      <c r="E107" s="462"/>
+      <c r="F107" s="462"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="460" t="s">
+      <c r="B108" s="462" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="460"/>
-      <c r="D108" s="460"/>
-      <c r="E108" s="460"/>
-      <c r="F108" s="460"/>
+      <c r="C108" s="462"/>
+      <c r="D108" s="462"/>
+      <c r="E108" s="462"/>
+      <c r="F108" s="462"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6321,13 +6321,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="460" t="s">
+      <c r="B114" s="462" t="s">
         <v>489</v>
       </c>
-      <c r="C114" s="460"/>
-      <c r="D114" s="460"/>
-      <c r="E114" s="460"/>
-      <c r="F114" s="460"/>
+      <c r="C114" s="462"/>
+      <c r="D114" s="462"/>
+      <c r="E114" s="462"/>
+      <c r="F114" s="462"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6462,13 +6462,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="461" t="s">
+      <c r="B124" s="463" t="s">
         <v>355</v>
       </c>
-      <c r="C124" s="461"/>
-      <c r="D124" s="461"/>
-      <c r="E124" s="461"/>
-      <c r="F124" s="461"/>
+      <c r="C124" s="463"/>
+      <c r="D124" s="463"/>
+      <c r="E124" s="463"/>
+      <c r="F124" s="463"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6503,22 +6503,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="463" t="s">
+      <c r="B131" s="467" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="463"/>
-      <c r="D131" s="463"/>
-      <c r="E131" s="463"/>
-      <c r="F131" s="463"/>
+      <c r="C131" s="467"/>
+      <c r="D131" s="467"/>
+      <c r="E131" s="467"/>
+      <c r="F131" s="467"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="460" t="s">
+      <c r="B132" s="462" t="s">
         <v>357</v>
       </c>
-      <c r="C132" s="460"/>
-      <c r="D132" s="460"/>
-      <c r="E132" s="460"/>
-      <c r="F132" s="460"/>
+      <c r="C132" s="462"/>
+      <c r="D132" s="462"/>
+      <c r="E132" s="462"/>
+      <c r="F132" s="462"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6694,13 +6694,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="467" t="s">
+      <c r="B149" s="461" t="s">
         <v>358</v>
       </c>
-      <c r="C149" s="460"/>
-      <c r="D149" s="460"/>
-      <c r="E149" s="460"/>
-      <c r="F149" s="460"/>
+      <c r="C149" s="462"/>
+      <c r="D149" s="462"/>
+      <c r="E149" s="462"/>
+      <c r="F149" s="462"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6737,13 +6737,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="461" t="s">
+      <c r="B158" s="463" t="s">
         <v>436</v>
       </c>
-      <c r="C158" s="461"/>
-      <c r="D158" s="461"/>
-      <c r="E158" s="461"/>
-      <c r="F158" s="461"/>
+      <c r="C158" s="463"/>
+      <c r="D158" s="463"/>
+      <c r="E158" s="463"/>
+      <c r="F158" s="463"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6751,22 +6751,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="466" t="s">
+      <c r="B161" s="460" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="466"/>
-      <c r="D161" s="466"/>
-      <c r="E161" s="466"/>
-      <c r="F161" s="466"/>
+      <c r="C161" s="460"/>
+      <c r="D161" s="460"/>
+      <c r="E161" s="460"/>
+      <c r="F161" s="460"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="466" t="s">
+      <c r="B162" s="460" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="466"/>
-      <c r="D162" s="466"/>
-      <c r="E162" s="466"/>
-      <c r="F162" s="466"/>
+      <c r="C162" s="460"/>
+      <c r="D162" s="460"/>
+      <c r="E162" s="460"/>
+      <c r="F162" s="460"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6790,18 +6790,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6818,6 +6806,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -14008,16 +14008,16 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>2.7890670839037745E-2</v>
+        <v>2.7912507339988256E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>2.7890670839037745E-2</v>
+        <v>2.7912507339988256E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>4.1101114805398006E-2</v>
+        <v>4.1133294186729299E-2</v>
       </c>
       <c r="I92" s="22" t="str">
         <f t="shared" si="38"/>
@@ -15228,18 +15228,18 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>7.5081393904278135E-2</v>
+        <v>7.5140177536225108E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>6.6657373380978449E-2</v>
+        <v>6.670956157700976E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>6.4176789391714034E-2</v>
+        <v>6.4227035458961412E-2</v>
       </c>
       <c r="I124" s="74" t="str">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
@@ -15285,11 +15285,11 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.3624795284520451E-2</v>
+        <v>8.3690267819485825E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.9410779534762777E-2</v>
+        <v>7.9472952781609332E-2</v>
       </c>
       <c r="I125" s="22" t="str">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -19747,7 +19747,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>102.26</v>
+        <v>102.18</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19758,7 +19758,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.12176283506510555</v>
+        <v>0.12206270179382848</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -20254,7 +20254,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>102.26</v>
+        <v>102.18</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20272,14 +20272,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>396933.23459130008</v>
+        <v>396622.70595090004</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>526</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.12176283506510555</v>
+        <v>0.12206270179382848</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20287,13 +20287,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="471" t="s">
+      <c r="B12" s="474" t="s">
         <v>495</v>
       </c>
-      <c r="C12" s="471"/>
-      <c r="D12" s="471"/>
-      <c r="E12" s="471"/>
-      <c r="F12" s="471"/>
+      <c r="C12" s="474"/>
+      <c r="D12" s="474"/>
+      <c r="E12" s="474"/>
+      <c r="F12" s="474"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20478,22 +20478,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="471" t="s">
+      <c r="B29" s="474" t="s">
         <v>496</v>
       </c>
-      <c r="C29" s="471"/>
-      <c r="D29" s="471"/>
-      <c r="E29" s="471"/>
-      <c r="F29" s="471"/>
+      <c r="C29" s="474"/>
+      <c r="D29" s="474"/>
+      <c r="E29" s="474"/>
+      <c r="F29" s="474"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="472" t="s">
+      <c r="B30" s="477" t="s">
         <v>497</v>
       </c>
-      <c r="C30" s="472"/>
-      <c r="D30" s="472"/>
-      <c r="E30" s="472"/>
-      <c r="F30" s="472"/>
+      <c r="C30" s="477"/>
+      <c r="D30" s="477"/>
+      <c r="E30" s="477"/>
+      <c r="F30" s="477"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20683,10 +20683,10 @@
       <c r="B54" s="470" t="s">
         <v>504</v>
       </c>
-      <c r="C54" s="473"/>
-      <c r="D54" s="473"/>
-      <c r="E54" s="473"/>
-      <c r="F54" s="473"/>
+      <c r="C54" s="476"/>
+      <c r="D54" s="476"/>
+      <c r="E54" s="476"/>
+      <c r="F54" s="476"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20702,22 +20702,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="471" t="s">
+      <c r="B57" s="474" t="s">
         <v>505</v>
       </c>
-      <c r="C57" s="471"/>
-      <c r="D57" s="471"/>
-      <c r="E57" s="471"/>
-      <c r="F57" s="471"/>
+      <c r="C57" s="474"/>
+      <c r="D57" s="474"/>
+      <c r="E57" s="474"/>
+      <c r="F57" s="474"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="471" t="s">
+      <c r="B58" s="474" t="s">
         <v>506</v>
       </c>
-      <c r="C58" s="471"/>
-      <c r="D58" s="471"/>
-      <c r="E58" s="471"/>
-      <c r="F58" s="471"/>
+      <c r="C58" s="474"/>
+      <c r="D58" s="474"/>
+      <c r="E58" s="474"/>
+      <c r="F58" s="474"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20751,7 +20751,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>7.5081393904278135E-2</v>
+        <v>7.5140177536225108E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20761,7 +20761,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>2.7890670839037745E-2</v>
+        <v>2.7912507339988256E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>371</v>
@@ -20852,22 +20852,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="471" t="s">
+      <c r="B73" s="474" t="s">
         <v>507</v>
       </c>
-      <c r="C73" s="471"/>
-      <c r="D73" s="471"/>
-      <c r="E73" s="471"/>
-      <c r="F73" s="471"/>
+      <c r="C73" s="474"/>
+      <c r="D73" s="474"/>
+      <c r="E73" s="474"/>
+      <c r="F73" s="474"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="472" t="s">
+      <c r="B74" s="477" t="s">
         <v>477</v>
       </c>
-      <c r="C74" s="472"/>
-      <c r="D74" s="472"/>
-      <c r="E74" s="472"/>
-      <c r="F74" s="472"/>
+      <c r="C74" s="477"/>
+      <c r="D74" s="477"/>
+      <c r="E74" s="477"/>
+      <c r="F74" s="477"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -20875,13 +20875,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="471" t="s">
+      <c r="B77" s="474" t="s">
         <v>508</v>
       </c>
-      <c r="C77" s="471"/>
-      <c r="D77" s="471"/>
-      <c r="E77" s="471"/>
-      <c r="F77" s="471"/>
+      <c r="C77" s="474"/>
+      <c r="D77" s="474"/>
+      <c r="E77" s="474"/>
+      <c r="F77" s="474"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21030,33 +21030,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="471" t="s">
+      <c r="B96" s="474" t="s">
         <v>511</v>
       </c>
-      <c r="C96" s="471"/>
-      <c r="D96" s="471"/>
-      <c r="E96" s="471"/>
-      <c r="F96" s="471"/>
+      <c r="C96" s="474"/>
+      <c r="D96" s="474"/>
+      <c r="E96" s="474"/>
+      <c r="F96" s="474"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="472" t="s">
+      <c r="B97" s="477" t="s">
         <v>512</v>
       </c>
-      <c r="C97" s="472"/>
-      <c r="D97" s="472"/>
-      <c r="E97" s="472"/>
-      <c r="F97" s="472"/>
+      <c r="C97" s="477"/>
+      <c r="D97" s="477"/>
+      <c r="E97" s="477"/>
+      <c r="F97" s="477"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="472" t="s">
+      <c r="B98" s="477" t="s">
         <v>513</v>
       </c>
-      <c r="C98" s="472"/>
-      <c r="D98" s="472"/>
-      <c r="E98" s="472"/>
-      <c r="F98" s="472"/>
+      <c r="C98" s="477"/>
+      <c r="D98" s="477"/>
+      <c r="E98" s="477"/>
+      <c r="F98" s="477"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21119,23 +21119,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="471" t="s">
+      <c r="B107" s="474" t="s">
         <v>514</v>
       </c>
-      <c r="C107" s="471"/>
-      <c r="D107" s="471"/>
-      <c r="E107" s="471"/>
-      <c r="F107" s="471"/>
+      <c r="C107" s="474"/>
+      <c r="D107" s="474"/>
+      <c r="E107" s="474"/>
+      <c r="F107" s="474"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="471" t="s">
+      <c r="B108" s="474" t="s">
         <v>533</v>
       </c>
-      <c r="C108" s="471"/>
-      <c r="D108" s="471"/>
-      <c r="E108" s="471"/>
-      <c r="F108" s="471"/>
+      <c r="C108" s="474"/>
+      <c r="D108" s="474"/>
+      <c r="E108" s="474"/>
+      <c r="F108" s="474"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21179,13 +21179,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="471" t="s">
+      <c r="B114" s="474" t="s">
         <v>515</v>
       </c>
-      <c r="C114" s="471"/>
-      <c r="D114" s="471"/>
-      <c r="E114" s="471"/>
-      <c r="F114" s="471"/>
+      <c r="C114" s="474"/>
+      <c r="D114" s="474"/>
+      <c r="E114" s="474"/>
+      <c r="F114" s="474"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21349,13 +21349,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="475" t="s">
+      <c r="B127" s="472" t="s">
         <v>517</v>
       </c>
-      <c r="C127" s="475"/>
-      <c r="D127" s="475"/>
-      <c r="E127" s="475"/>
-      <c r="F127" s="475"/>
+      <c r="C127" s="472"/>
+      <c r="D127" s="472"/>
+      <c r="E127" s="472"/>
+      <c r="F127" s="472"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21368,22 +21368,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="476" t="s">
+      <c r="B131" s="473" t="s">
         <v>518</v>
       </c>
-      <c r="C131" s="476"/>
-      <c r="D131" s="476"/>
-      <c r="E131" s="476"/>
-      <c r="F131" s="476"/>
+      <c r="C131" s="473"/>
+      <c r="D131" s="473"/>
+      <c r="E131" s="473"/>
+      <c r="F131" s="473"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="471" t="s">
+      <c r="B132" s="474" t="s">
         <v>519</v>
       </c>
-      <c r="C132" s="471"/>
-      <c r="D132" s="471"/>
-      <c r="E132" s="471"/>
-      <c r="F132" s="471"/>
+      <c r="C132" s="474"/>
+      <c r="D132" s="474"/>
+      <c r="E132" s="474"/>
+      <c r="F132" s="474"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21552,13 +21552,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="477" t="s">
+      <c r="B149" s="475" t="s">
         <v>520</v>
       </c>
-      <c r="C149" s="471"/>
-      <c r="D149" s="471"/>
-      <c r="E149" s="471"/>
-      <c r="F149" s="471"/>
+      <c r="C149" s="474"/>
+      <c r="D149" s="474"/>
+      <c r="E149" s="474"/>
+      <c r="F149" s="474"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21566,13 +21566,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="473" t="s">
+      <c r="B152" s="476" t="s">
         <v>521</v>
       </c>
-      <c r="C152" s="473"/>
-      <c r="D152" s="473"/>
-      <c r="E152" s="473"/>
-      <c r="F152" s="473"/>
+      <c r="C152" s="476"/>
+      <c r="D152" s="476"/>
+      <c r="E152" s="476"/>
+      <c r="F152" s="476"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21609,22 +21609,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="474" t="s">
+      <c r="B161" s="471" t="s">
         <v>386</v>
       </c>
-      <c r="C161" s="474"/>
-      <c r="D161" s="474"/>
-      <c r="E161" s="474"/>
-      <c r="F161" s="474"/>
+      <c r="C161" s="471"/>
+      <c r="D161" s="471"/>
+      <c r="E161" s="471"/>
+      <c r="F161" s="471"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="474" t="s">
+      <c r="B162" s="471" t="s">
         <v>387</v>
       </c>
-      <c r="C162" s="474"/>
-      <c r="D162" s="474"/>
-      <c r="E162" s="474"/>
-      <c r="F162" s="474"/>
+      <c r="C162" s="471"/>
+      <c r="D162" s="471"/>
+      <c r="E162" s="471"/>
+      <c r="F162" s="471"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21648,15 +21648,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21671,12 +21668,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/000858.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/000858.SZ_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF4CD423-9340-44A9-BCB4-C09BA4E84EC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4FA0417-B5F0-4188-81E0-66E06FC8D0BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1837" yWindow="1837" windowWidth="12691" windowHeight="7643" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4986,30 +4986,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5019,6 +5019,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5028,16 +5037,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5407,7 +5407,7 @@
         <v>348</v>
       </c>
       <c r="C8" s="47">
-        <v>102.18</v>
+        <v>102.95</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5425,14 +5425,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>396622.70595090004</v>
+        <v>399611.54411475</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>525</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.12206270179382848</v>
+        <v>0.11918961100802902</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5440,13 +5440,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="462" t="s">
+      <c r="B12" s="460" t="s">
         <v>353</v>
       </c>
-      <c r="C12" s="462"/>
-      <c r="D12" s="462"/>
-      <c r="E12" s="462"/>
-      <c r="F12" s="462"/>
+      <c r="C12" s="460"/>
+      <c r="D12" s="460"/>
+      <c r="E12" s="460"/>
+      <c r="F12" s="460"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5624,22 +5624,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="462" t="s">
+      <c r="B29" s="460" t="s">
         <v>354</v>
       </c>
-      <c r="C29" s="462"/>
-      <c r="D29" s="462"/>
-      <c r="E29" s="462"/>
-      <c r="F29" s="462"/>
+      <c r="C29" s="460"/>
+      <c r="D29" s="460"/>
+      <c r="E29" s="460"/>
+      <c r="F29" s="460"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="466" t="s">
+      <c r="B30" s="462" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="466"/>
-      <c r="D30" s="466"/>
-      <c r="E30" s="466"/>
-      <c r="F30" s="466"/>
+      <c r="C30" s="462"/>
+      <c r="D30" s="462"/>
+      <c r="E30" s="462"/>
+      <c r="F30" s="462"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5651,13 +5651,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="463" t="s">
+      <c r="B33" s="461" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="463"/>
-      <c r="D33" s="463"/>
-      <c r="E33" s="463"/>
-      <c r="F33" s="463"/>
+      <c r="C33" s="461"/>
+      <c r="D33" s="461"/>
+      <c r="E33" s="461"/>
+      <c r="F33" s="461"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5677,13 +5677,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="463" t="s">
+      <c r="B36" s="461" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="463"/>
-      <c r="D36" s="463"/>
-      <c r="E36" s="463"/>
-      <c r="F36" s="463"/>
+      <c r="C36" s="461"/>
+      <c r="D36" s="461"/>
+      <c r="E36" s="461"/>
+      <c r="F36" s="461"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5712,13 +5712,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="463" t="s">
+      <c r="B40" s="461" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="463"/>
-      <c r="D40" s="463"/>
-      <c r="E40" s="463"/>
-      <c r="F40" s="463"/>
+      <c r="C40" s="461"/>
+      <c r="D40" s="461"/>
+      <c r="E40" s="461"/>
+      <c r="F40" s="461"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5734,13 +5734,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="463" t="s">
+      <c r="B43" s="461" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="463"/>
-      <c r="D43" s="463"/>
-      <c r="E43" s="463"/>
-      <c r="F43" s="463"/>
+      <c r="C43" s="461"/>
+      <c r="D43" s="461"/>
+      <c r="E43" s="461"/>
+      <c r="F43" s="461"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5804,13 +5804,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="463" t="s">
+      <c r="B51" s="461" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="463"/>
-      <c r="D51" s="463"/>
-      <c r="E51" s="463"/>
-      <c r="F51" s="463"/>
+      <c r="C51" s="461"/>
+      <c r="D51" s="461"/>
+      <c r="E51" s="461"/>
+      <c r="F51" s="461"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5826,7 +5826,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="463" t="s">
+      <c r="B54" s="461" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="464"/>
@@ -5848,22 +5848,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="462" t="s">
+      <c r="B57" s="460" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="462"/>
-      <c r="D57" s="462"/>
-      <c r="E57" s="462"/>
-      <c r="F57" s="462"/>
+      <c r="C57" s="460"/>
+      <c r="D57" s="460"/>
+      <c r="E57" s="460"/>
+      <c r="F57" s="460"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="462" t="s">
+      <c r="B58" s="460" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="462"/>
-      <c r="D58" s="462"/>
-      <c r="E58" s="462"/>
-      <c r="F58" s="462"/>
+      <c r="C58" s="460"/>
+      <c r="D58" s="460"/>
+      <c r="E58" s="460"/>
+      <c r="F58" s="460"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>7.5140177536225108E-2</v>
+        <v>7.4578177179713281E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5907,7 +5907,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>2.7912507339988256E-2</v>
+        <v>2.7703739679456045E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>321</v>
@@ -5998,13 +5998,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="462" t="s">
+      <c r="B73" s="460" t="s">
         <v>476</v>
       </c>
-      <c r="C73" s="462"/>
-      <c r="D73" s="462"/>
-      <c r="E73" s="462"/>
-      <c r="F73" s="462"/>
+      <c r="C73" s="460"/>
+      <c r="D73" s="460"/>
+      <c r="E73" s="460"/>
+      <c r="F73" s="460"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6023,13 +6023,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="462" t="s">
+      <c r="B77" s="460" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="462"/>
-      <c r="D77" s="462"/>
-      <c r="E77" s="462"/>
-      <c r="F77" s="462"/>
+      <c r="C77" s="460"/>
+      <c r="D77" s="460"/>
+      <c r="E77" s="460"/>
+      <c r="F77" s="460"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6198,31 +6198,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="462" t="s">
+      <c r="B96" s="460" t="s">
         <v>483</v>
       </c>
-      <c r="C96" s="462"/>
-      <c r="D96" s="462"/>
-      <c r="E96" s="462"/>
-      <c r="F96" s="462"/>
+      <c r="C96" s="460"/>
+      <c r="D96" s="460"/>
+      <c r="E96" s="460"/>
+      <c r="F96" s="460"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="466" t="s">
+      <c r="B97" s="462" t="s">
         <v>482</v>
       </c>
-      <c r="C97" s="466"/>
-      <c r="D97" s="466"/>
-      <c r="E97" s="466"/>
-      <c r="F97" s="466"/>
+      <c r="C97" s="462"/>
+      <c r="D97" s="462"/>
+      <c r="E97" s="462"/>
+      <c r="F97" s="462"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="466" t="s">
+      <c r="B98" s="462" t="s">
         <v>481</v>
       </c>
-      <c r="C98" s="466"/>
-      <c r="D98" s="466"/>
-      <c r="E98" s="466"/>
-      <c r="F98" s="466"/>
+      <c r="C98" s="462"/>
+      <c r="D98" s="462"/>
+      <c r="E98" s="462"/>
+      <c r="F98" s="462"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6272,22 +6272,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="462" t="s">
+      <c r="B107" s="460" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="462"/>
-      <c r="D107" s="462"/>
-      <c r="E107" s="462"/>
-      <c r="F107" s="462"/>
+      <c r="C107" s="460"/>
+      <c r="D107" s="460"/>
+      <c r="E107" s="460"/>
+      <c r="F107" s="460"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="462" t="s">
+      <c r="B108" s="460" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="462"/>
-      <c r="D108" s="462"/>
-      <c r="E108" s="462"/>
-      <c r="F108" s="462"/>
+      <c r="C108" s="460"/>
+      <c r="D108" s="460"/>
+      <c r="E108" s="460"/>
+      <c r="F108" s="460"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6321,13 +6321,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="462" t="s">
+      <c r="B114" s="460" t="s">
         <v>489</v>
       </c>
-      <c r="C114" s="462"/>
-      <c r="D114" s="462"/>
-      <c r="E114" s="462"/>
-      <c r="F114" s="462"/>
+      <c r="C114" s="460"/>
+      <c r="D114" s="460"/>
+      <c r="E114" s="460"/>
+      <c r="F114" s="460"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6462,13 +6462,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="463" t="s">
+      <c r="B124" s="461" t="s">
         <v>355</v>
       </c>
-      <c r="C124" s="463"/>
-      <c r="D124" s="463"/>
-      <c r="E124" s="463"/>
-      <c r="F124" s="463"/>
+      <c r="C124" s="461"/>
+      <c r="D124" s="461"/>
+      <c r="E124" s="461"/>
+      <c r="F124" s="461"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6503,22 +6503,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="467" t="s">
+      <c r="B131" s="463" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="467"/>
-      <c r="D131" s="467"/>
-      <c r="E131" s="467"/>
-      <c r="F131" s="467"/>
+      <c r="C131" s="463"/>
+      <c r="D131" s="463"/>
+      <c r="E131" s="463"/>
+      <c r="F131" s="463"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="462" t="s">
+      <c r="B132" s="460" t="s">
         <v>357</v>
       </c>
-      <c r="C132" s="462"/>
-      <c r="D132" s="462"/>
-      <c r="E132" s="462"/>
-      <c r="F132" s="462"/>
+      <c r="C132" s="460"/>
+      <c r="D132" s="460"/>
+      <c r="E132" s="460"/>
+      <c r="F132" s="460"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6694,13 +6694,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="461" t="s">
+      <c r="B149" s="467" t="s">
         <v>358</v>
       </c>
-      <c r="C149" s="462"/>
-      <c r="D149" s="462"/>
-      <c r="E149" s="462"/>
-      <c r="F149" s="462"/>
+      <c r="C149" s="460"/>
+      <c r="D149" s="460"/>
+      <c r="E149" s="460"/>
+      <c r="F149" s="460"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6737,13 +6737,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="463" t="s">
+      <c r="B158" s="461" t="s">
         <v>436</v>
       </c>
-      <c r="C158" s="463"/>
-      <c r="D158" s="463"/>
-      <c r="E158" s="463"/>
-      <c r="F158" s="463"/>
+      <c r="C158" s="461"/>
+      <c r="D158" s="461"/>
+      <c r="E158" s="461"/>
+      <c r="F158" s="461"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6751,22 +6751,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="460" t="s">
+      <c r="B161" s="466" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="460"/>
-      <c r="D161" s="460"/>
-      <c r="E161" s="460"/>
-      <c r="F161" s="460"/>
+      <c r="C161" s="466"/>
+      <c r="D161" s="466"/>
+      <c r="E161" s="466"/>
+      <c r="F161" s="466"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="460" t="s">
+      <c r="B162" s="466" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="460"/>
-      <c r="D162" s="460"/>
-      <c r="E162" s="460"/>
-      <c r="F162" s="460"/>
+      <c r="C162" s="466"/>
+      <c r="D162" s="466"/>
+      <c r="E162" s="466"/>
+      <c r="F162" s="466"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6790,6 +6790,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6806,18 +6818,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -14008,16 +14008,16 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>2.7912507339988256E-2</v>
+        <v>2.7703739679456045E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>2.7912507339988256E-2</v>
+        <v>2.7703739679456045E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>4.1133294186729299E-2</v>
+        <v>4.0825643516270035E-2</v>
       </c>
       <c r="I92" s="22" t="str">
         <f t="shared" si="38"/>
@@ -15228,18 +15228,18 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>7.5140177536225108E-2</v>
+        <v>7.4578177179713281E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>6.670956157700976E-2</v>
+        <v>6.6210616823106916E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>6.4227035458961412E-2</v>
+        <v>6.3746658408904103E-2</v>
       </c>
       <c r="I124" s="74" t="str">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
@@ -15285,11 +15285,11 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.3690267819485825E-2</v>
+        <v>8.3064318269014698E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.9472952781609332E-2</v>
+        <v>7.887854604395185E-2</v>
       </c>
       <c r="I125" s="22" t="str">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -19747,7 +19747,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>102.18</v>
+        <v>102.95</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19758,7 +19758,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.12206270179382848</v>
+        <v>0.11918961100802902</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -20254,7 +20254,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>102.18</v>
+        <v>102.95</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20272,14 +20272,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>396622.70595090004</v>
+        <v>399611.54411475</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>526</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.12206270179382848</v>
+        <v>0.11918961100802902</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20287,13 +20287,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="474" t="s">
+      <c r="B12" s="471" t="s">
         <v>495</v>
       </c>
-      <c r="C12" s="474"/>
-      <c r="D12" s="474"/>
-      <c r="E12" s="474"/>
-      <c r="F12" s="474"/>
+      <c r="C12" s="471"/>
+      <c r="D12" s="471"/>
+      <c r="E12" s="471"/>
+      <c r="F12" s="471"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20478,22 +20478,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="474" t="s">
+      <c r="B29" s="471" t="s">
         <v>496</v>
       </c>
-      <c r="C29" s="474"/>
-      <c r="D29" s="474"/>
-      <c r="E29" s="474"/>
-      <c r="F29" s="474"/>
+      <c r="C29" s="471"/>
+      <c r="D29" s="471"/>
+      <c r="E29" s="471"/>
+      <c r="F29" s="471"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="477" t="s">
+      <c r="B30" s="472" t="s">
         <v>497</v>
       </c>
-      <c r="C30" s="477"/>
-      <c r="D30" s="477"/>
-      <c r="E30" s="477"/>
-      <c r="F30" s="477"/>
+      <c r="C30" s="472"/>
+      <c r="D30" s="472"/>
+      <c r="E30" s="472"/>
+      <c r="F30" s="472"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20683,10 +20683,10 @@
       <c r="B54" s="470" t="s">
         <v>504</v>
       </c>
-      <c r="C54" s="476"/>
-      <c r="D54" s="476"/>
-      <c r="E54" s="476"/>
-      <c r="F54" s="476"/>
+      <c r="C54" s="473"/>
+      <c r="D54" s="473"/>
+      <c r="E54" s="473"/>
+      <c r="F54" s="473"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20702,22 +20702,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="474" t="s">
+      <c r="B57" s="471" t="s">
         <v>505</v>
       </c>
-      <c r="C57" s="474"/>
-      <c r="D57" s="474"/>
-      <c r="E57" s="474"/>
-      <c r="F57" s="474"/>
+      <c r="C57" s="471"/>
+      <c r="D57" s="471"/>
+      <c r="E57" s="471"/>
+      <c r="F57" s="471"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="474" t="s">
+      <c r="B58" s="471" t="s">
         <v>506</v>
       </c>
-      <c r="C58" s="474"/>
-      <c r="D58" s="474"/>
-      <c r="E58" s="474"/>
-      <c r="F58" s="474"/>
+      <c r="C58" s="471"/>
+      <c r="D58" s="471"/>
+      <c r="E58" s="471"/>
+      <c r="F58" s="471"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20751,7 +20751,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>7.5140177536225108E-2</v>
+        <v>7.4578177179713281E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20761,7 +20761,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>2.7912507339988256E-2</v>
+        <v>2.7703739679456045E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>371</v>
@@ -20852,22 +20852,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="474" t="s">
+      <c r="B73" s="471" t="s">
         <v>507</v>
       </c>
-      <c r="C73" s="474"/>
-      <c r="D73" s="474"/>
-      <c r="E73" s="474"/>
-      <c r="F73" s="474"/>
+      <c r="C73" s="471"/>
+      <c r="D73" s="471"/>
+      <c r="E73" s="471"/>
+      <c r="F73" s="471"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="477" t="s">
+      <c r="B74" s="472" t="s">
         <v>477</v>
       </c>
-      <c r="C74" s="477"/>
-      <c r="D74" s="477"/>
-      <c r="E74" s="477"/>
-      <c r="F74" s="477"/>
+      <c r="C74" s="472"/>
+      <c r="D74" s="472"/>
+      <c r="E74" s="472"/>
+      <c r="F74" s="472"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -20875,13 +20875,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="474" t="s">
+      <c r="B77" s="471" t="s">
         <v>508</v>
       </c>
-      <c r="C77" s="474"/>
-      <c r="D77" s="474"/>
-      <c r="E77" s="474"/>
-      <c r="F77" s="474"/>
+      <c r="C77" s="471"/>
+      <c r="D77" s="471"/>
+      <c r="E77" s="471"/>
+      <c r="F77" s="471"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21030,33 +21030,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="474" t="s">
+      <c r="B96" s="471" t="s">
         <v>511</v>
       </c>
-      <c r="C96" s="474"/>
-      <c r="D96" s="474"/>
-      <c r="E96" s="474"/>
-      <c r="F96" s="474"/>
+      <c r="C96" s="471"/>
+      <c r="D96" s="471"/>
+      <c r="E96" s="471"/>
+      <c r="F96" s="471"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="477" t="s">
+      <c r="B97" s="472" t="s">
         <v>512</v>
       </c>
-      <c r="C97" s="477"/>
-      <c r="D97" s="477"/>
-      <c r="E97" s="477"/>
-      <c r="F97" s="477"/>
+      <c r="C97" s="472"/>
+      <c r="D97" s="472"/>
+      <c r="E97" s="472"/>
+      <c r="F97" s="472"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="477" t="s">
+      <c r="B98" s="472" t="s">
         <v>513</v>
       </c>
-      <c r="C98" s="477"/>
-      <c r="D98" s="477"/>
-      <c r="E98" s="477"/>
-      <c r="F98" s="477"/>
+      <c r="C98" s="472"/>
+      <c r="D98" s="472"/>
+      <c r="E98" s="472"/>
+      <c r="F98" s="472"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21119,23 +21119,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="474" t="s">
+      <c r="B107" s="471" t="s">
         <v>514</v>
       </c>
-      <c r="C107" s="474"/>
-      <c r="D107" s="474"/>
-      <c r="E107" s="474"/>
-      <c r="F107" s="474"/>
+      <c r="C107" s="471"/>
+      <c r="D107" s="471"/>
+      <c r="E107" s="471"/>
+      <c r="F107" s="471"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="474" t="s">
+      <c r="B108" s="471" t="s">
         <v>533</v>
       </c>
-      <c r="C108" s="474"/>
-      <c r="D108" s="474"/>
-      <c r="E108" s="474"/>
-      <c r="F108" s="474"/>
+      <c r="C108" s="471"/>
+      <c r="D108" s="471"/>
+      <c r="E108" s="471"/>
+      <c r="F108" s="471"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21179,13 +21179,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="474" t="s">
+      <c r="B114" s="471" t="s">
         <v>515</v>
       </c>
-      <c r="C114" s="474"/>
-      <c r="D114" s="474"/>
-      <c r="E114" s="474"/>
-      <c r="F114" s="474"/>
+      <c r="C114" s="471"/>
+      <c r="D114" s="471"/>
+      <c r="E114" s="471"/>
+      <c r="F114" s="471"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21349,13 +21349,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="472" t="s">
+      <c r="B127" s="475" t="s">
         <v>517</v>
       </c>
-      <c r="C127" s="472"/>
-      <c r="D127" s="472"/>
-      <c r="E127" s="472"/>
-      <c r="F127" s="472"/>
+      <c r="C127" s="475"/>
+      <c r="D127" s="475"/>
+      <c r="E127" s="475"/>
+      <c r="F127" s="475"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21368,22 +21368,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="473" t="s">
+      <c r="B131" s="476" t="s">
         <v>518</v>
       </c>
-      <c r="C131" s="473"/>
-      <c r="D131" s="473"/>
-      <c r="E131" s="473"/>
-      <c r="F131" s="473"/>
+      <c r="C131" s="476"/>
+      <c r="D131" s="476"/>
+      <c r="E131" s="476"/>
+      <c r="F131" s="476"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="474" t="s">
+      <c r="B132" s="471" t="s">
         <v>519</v>
       </c>
-      <c r="C132" s="474"/>
-      <c r="D132" s="474"/>
-      <c r="E132" s="474"/>
-      <c r="F132" s="474"/>
+      <c r="C132" s="471"/>
+      <c r="D132" s="471"/>
+      <c r="E132" s="471"/>
+      <c r="F132" s="471"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21552,13 +21552,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="475" t="s">
+      <c r="B149" s="477" t="s">
         <v>520</v>
       </c>
-      <c r="C149" s="474"/>
-      <c r="D149" s="474"/>
-      <c r="E149" s="474"/>
-      <c r="F149" s="474"/>
+      <c r="C149" s="471"/>
+      <c r="D149" s="471"/>
+      <c r="E149" s="471"/>
+      <c r="F149" s="471"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21566,13 +21566,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="476" t="s">
+      <c r="B152" s="473" t="s">
         <v>521</v>
       </c>
-      <c r="C152" s="476"/>
-      <c r="D152" s="476"/>
-      <c r="E152" s="476"/>
-      <c r="F152" s="476"/>
+      <c r="C152" s="473"/>
+      <c r="D152" s="473"/>
+      <c r="E152" s="473"/>
+      <c r="F152" s="473"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21609,22 +21609,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="471" t="s">
+      <c r="B161" s="474" t="s">
         <v>386</v>
       </c>
-      <c r="C161" s="471"/>
-      <c r="D161" s="471"/>
-      <c r="E161" s="471"/>
-      <c r="F161" s="471"/>
+      <c r="C161" s="474"/>
+      <c r="D161" s="474"/>
+      <c r="E161" s="474"/>
+      <c r="F161" s="474"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="471" t="s">
+      <c r="B162" s="474" t="s">
         <v>387</v>
       </c>
-      <c r="C162" s="471"/>
-      <c r="D162" s="471"/>
-      <c r="E162" s="471"/>
-      <c r="F162" s="471"/>
+      <c r="C162" s="474"/>
+      <c r="D162" s="474"/>
+      <c r="E162" s="474"/>
+      <c r="F162" s="474"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21648,12 +21648,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21668,15 +21671,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/000858.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/000858.SZ_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4FA0417-B5F0-4188-81E0-66E06FC8D0BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D1CE32B-8334-46FC-91B4-D42C44D1C119}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1470" yWindow="1470" windowWidth="12690" windowHeight="7643" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4986,30 +4986,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5019,25 +5019,25 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5407,7 +5407,7 @@
         <v>348</v>
       </c>
       <c r="C8" s="47">
-        <v>102.95</v>
+        <v>105.66</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5425,14 +5425,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>399611.54411475</v>
+        <v>410130.70180829999</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>525</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.11918961100802902</v>
+        <v>0.10930488673979756</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5440,13 +5440,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="460" t="s">
+      <c r="B12" s="462" t="s">
         <v>353</v>
       </c>
-      <c r="C12" s="460"/>
-      <c r="D12" s="460"/>
-      <c r="E12" s="460"/>
-      <c r="F12" s="460"/>
+      <c r="C12" s="462"/>
+      <c r="D12" s="462"/>
+      <c r="E12" s="462"/>
+      <c r="F12" s="462"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5624,22 +5624,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="460" t="s">
+      <c r="B29" s="462" t="s">
         <v>354</v>
       </c>
-      <c r="C29" s="460"/>
-      <c r="D29" s="460"/>
-      <c r="E29" s="460"/>
-      <c r="F29" s="460"/>
+      <c r="C29" s="462"/>
+      <c r="D29" s="462"/>
+      <c r="E29" s="462"/>
+      <c r="F29" s="462"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="462" t="s">
+      <c r="B30" s="466" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="462"/>
-      <c r="D30" s="462"/>
-      <c r="E30" s="462"/>
-      <c r="F30" s="462"/>
+      <c r="C30" s="466"/>
+      <c r="D30" s="466"/>
+      <c r="E30" s="466"/>
+      <c r="F30" s="466"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5651,13 +5651,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="461" t="s">
+      <c r="B33" s="463" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="461"/>
-      <c r="D33" s="461"/>
-      <c r="E33" s="461"/>
-      <c r="F33" s="461"/>
+      <c r="C33" s="463"/>
+      <c r="D33" s="463"/>
+      <c r="E33" s="463"/>
+      <c r="F33" s="463"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5677,13 +5677,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="461" t="s">
+      <c r="B36" s="463" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="461"/>
-      <c r="D36" s="461"/>
-      <c r="E36" s="461"/>
-      <c r="F36" s="461"/>
+      <c r="C36" s="463"/>
+      <c r="D36" s="463"/>
+      <c r="E36" s="463"/>
+      <c r="F36" s="463"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5712,13 +5712,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="461" t="s">
+      <c r="B40" s="463" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="461"/>
-      <c r="D40" s="461"/>
-      <c r="E40" s="461"/>
-      <c r="F40" s="461"/>
+      <c r="C40" s="463"/>
+      <c r="D40" s="463"/>
+      <c r="E40" s="463"/>
+      <c r="F40" s="463"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5734,13 +5734,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="461" t="s">
+      <c r="B43" s="463" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="461"/>
-      <c r="D43" s="461"/>
-      <c r="E43" s="461"/>
-      <c r="F43" s="461"/>
+      <c r="C43" s="463"/>
+      <c r="D43" s="463"/>
+      <c r="E43" s="463"/>
+      <c r="F43" s="463"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5804,13 +5804,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="461" t="s">
+      <c r="B51" s="463" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="461"/>
-      <c r="D51" s="461"/>
-      <c r="E51" s="461"/>
-      <c r="F51" s="461"/>
+      <c r="C51" s="463"/>
+      <c r="D51" s="463"/>
+      <c r="E51" s="463"/>
+      <c r="F51" s="463"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5826,7 +5826,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="461" t="s">
+      <c r="B54" s="463" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="464"/>
@@ -5848,22 +5848,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="460" t="s">
+      <c r="B57" s="462" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="460"/>
-      <c r="D57" s="460"/>
-      <c r="E57" s="460"/>
-      <c r="F57" s="460"/>
+      <c r="C57" s="462"/>
+      <c r="D57" s="462"/>
+      <c r="E57" s="462"/>
+      <c r="F57" s="462"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="460" t="s">
+      <c r="B58" s="462" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="460"/>
-      <c r="D58" s="460"/>
-      <c r="E58" s="460"/>
-      <c r="F58" s="460"/>
+      <c r="C58" s="462"/>
+      <c r="D58" s="462"/>
+      <c r="E58" s="462"/>
+      <c r="F58" s="462"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>7.4578177179713281E-2</v>
+        <v>7.2665373278927525E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5907,7 +5907,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>2.7703739679456045E-2</v>
+        <v>2.6993185689948896E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>321</v>
@@ -5998,13 +5998,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="460" t="s">
+      <c r="B73" s="462" t="s">
         <v>476</v>
       </c>
-      <c r="C73" s="460"/>
-      <c r="D73" s="460"/>
-      <c r="E73" s="460"/>
-      <c r="F73" s="460"/>
+      <c r="C73" s="462"/>
+      <c r="D73" s="462"/>
+      <c r="E73" s="462"/>
+      <c r="F73" s="462"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6023,13 +6023,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="460" t="s">
+      <c r="B77" s="462" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="460"/>
-      <c r="D77" s="460"/>
-      <c r="E77" s="460"/>
-      <c r="F77" s="460"/>
+      <c r="C77" s="462"/>
+      <c r="D77" s="462"/>
+      <c r="E77" s="462"/>
+      <c r="F77" s="462"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6198,31 +6198,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="460" t="s">
+      <c r="B96" s="462" t="s">
         <v>483</v>
       </c>
-      <c r="C96" s="460"/>
-      <c r="D96" s="460"/>
-      <c r="E96" s="460"/>
-      <c r="F96" s="460"/>
+      <c r="C96" s="462"/>
+      <c r="D96" s="462"/>
+      <c r="E96" s="462"/>
+      <c r="F96" s="462"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="462" t="s">
+      <c r="B97" s="466" t="s">
         <v>482</v>
       </c>
-      <c r="C97" s="462"/>
-      <c r="D97" s="462"/>
-      <c r="E97" s="462"/>
-      <c r="F97" s="462"/>
+      <c r="C97" s="466"/>
+      <c r="D97" s="466"/>
+      <c r="E97" s="466"/>
+      <c r="F97" s="466"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="462" t="s">
+      <c r="B98" s="466" t="s">
         <v>481</v>
       </c>
-      <c r="C98" s="462"/>
-      <c r="D98" s="462"/>
-      <c r="E98" s="462"/>
-      <c r="F98" s="462"/>
+      <c r="C98" s="466"/>
+      <c r="D98" s="466"/>
+      <c r="E98" s="466"/>
+      <c r="F98" s="466"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6272,22 +6272,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="460" t="s">
+      <c r="B107" s="462" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="460"/>
-      <c r="D107" s="460"/>
-      <c r="E107" s="460"/>
-      <c r="F107" s="460"/>
+      <c r="C107" s="462"/>
+      <c r="D107" s="462"/>
+      <c r="E107" s="462"/>
+      <c r="F107" s="462"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="460" t="s">
+      <c r="B108" s="462" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="460"/>
-      <c r="D108" s="460"/>
-      <c r="E108" s="460"/>
-      <c r="F108" s="460"/>
+      <c r="C108" s="462"/>
+      <c r="D108" s="462"/>
+      <c r="E108" s="462"/>
+      <c r="F108" s="462"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6321,13 +6321,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="460" t="s">
+      <c r="B114" s="462" t="s">
         <v>489</v>
       </c>
-      <c r="C114" s="460"/>
-      <c r="D114" s="460"/>
-      <c r="E114" s="460"/>
-      <c r="F114" s="460"/>
+      <c r="C114" s="462"/>
+      <c r="D114" s="462"/>
+      <c r="E114" s="462"/>
+      <c r="F114" s="462"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6462,13 +6462,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="461" t="s">
+      <c r="B124" s="463" t="s">
         <v>355</v>
       </c>
-      <c r="C124" s="461"/>
-      <c r="D124" s="461"/>
-      <c r="E124" s="461"/>
-      <c r="F124" s="461"/>
+      <c r="C124" s="463"/>
+      <c r="D124" s="463"/>
+      <c r="E124" s="463"/>
+      <c r="F124" s="463"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6503,22 +6503,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="463" t="s">
+      <c r="B131" s="467" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="463"/>
-      <c r="D131" s="463"/>
-      <c r="E131" s="463"/>
-      <c r="F131" s="463"/>
+      <c r="C131" s="467"/>
+      <c r="D131" s="467"/>
+      <c r="E131" s="467"/>
+      <c r="F131" s="467"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="460" t="s">
+      <c r="B132" s="462" t="s">
         <v>357</v>
       </c>
-      <c r="C132" s="460"/>
-      <c r="D132" s="460"/>
-      <c r="E132" s="460"/>
-      <c r="F132" s="460"/>
+      <c r="C132" s="462"/>
+      <c r="D132" s="462"/>
+      <c r="E132" s="462"/>
+      <c r="F132" s="462"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6694,13 +6694,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="467" t="s">
+      <c r="B149" s="461" t="s">
         <v>358</v>
       </c>
-      <c r="C149" s="460"/>
-      <c r="D149" s="460"/>
-      <c r="E149" s="460"/>
-      <c r="F149" s="460"/>
+      <c r="C149" s="462"/>
+      <c r="D149" s="462"/>
+      <c r="E149" s="462"/>
+      <c r="F149" s="462"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6737,13 +6737,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="461" t="s">
+      <c r="B158" s="463" t="s">
         <v>436</v>
       </c>
-      <c r="C158" s="461"/>
-      <c r="D158" s="461"/>
-      <c r="E158" s="461"/>
-      <c r="F158" s="461"/>
+      <c r="C158" s="463"/>
+      <c r="D158" s="463"/>
+      <c r="E158" s="463"/>
+      <c r="F158" s="463"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6751,22 +6751,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="466" t="s">
+      <c r="B161" s="460" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="466"/>
-      <c r="D161" s="466"/>
-      <c r="E161" s="466"/>
-      <c r="F161" s="466"/>
+      <c r="C161" s="460"/>
+      <c r="D161" s="460"/>
+      <c r="E161" s="460"/>
+      <c r="F161" s="460"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="466" t="s">
+      <c r="B162" s="460" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="466"/>
-      <c r="D162" s="466"/>
-      <c r="E162" s="466"/>
-      <c r="F162" s="466"/>
+      <c r="C162" s="460"/>
+      <c r="D162" s="460"/>
+      <c r="E162" s="460"/>
+      <c r="F162" s="460"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6790,18 +6790,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6818,6 +6806,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -14008,16 +14008,16 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>2.7703739679456045E-2</v>
+        <v>2.6993185689948896E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>2.7703739679456045E-2</v>
+        <v>2.6993185689948896E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>4.0825643516270035E-2</v>
+        <v>3.9778534923339014E-2</v>
       </c>
       <c r="I92" s="22" t="str">
         <f t="shared" si="38"/>
@@ -15228,18 +15228,18 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>7.4578177179713281E-2</v>
+        <v>7.2665373278927525E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>6.6210616823106916E-2</v>
+        <v>6.4512426669873724E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>6.3746658408904103E-2</v>
+        <v>6.2111664614770752E-2</v>
       </c>
       <c r="I124" s="74" t="str">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
@@ -15285,11 +15285,11 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.3064318269014698E-2</v>
+        <v>8.093385922577194E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.887854604395185E-2</v>
+        <v>7.6855444967109998E-2</v>
       </c>
       <c r="I125" s="22" t="str">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -19747,7 +19747,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>102.95</v>
+        <v>105.66</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19758,7 +19758,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.11918961100802902</v>
+        <v>0.10930488673979756</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -20254,7 +20254,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>102.95</v>
+        <v>105.66</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20272,14 +20272,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>399611.54411475</v>
+        <v>410130.70180829999</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>526</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.11918961100802902</v>
+        <v>0.10930488673979756</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20287,13 +20287,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="471" t="s">
+      <c r="B12" s="474" t="s">
         <v>495</v>
       </c>
-      <c r="C12" s="471"/>
-      <c r="D12" s="471"/>
-      <c r="E12" s="471"/>
-      <c r="F12" s="471"/>
+      <c r="C12" s="474"/>
+      <c r="D12" s="474"/>
+      <c r="E12" s="474"/>
+      <c r="F12" s="474"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20478,22 +20478,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="471" t="s">
+      <c r="B29" s="474" t="s">
         <v>496</v>
       </c>
-      <c r="C29" s="471"/>
-      <c r="D29" s="471"/>
-      <c r="E29" s="471"/>
-      <c r="F29" s="471"/>
+      <c r="C29" s="474"/>
+      <c r="D29" s="474"/>
+      <c r="E29" s="474"/>
+      <c r="F29" s="474"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="472" t="s">
+      <c r="B30" s="477" t="s">
         <v>497</v>
       </c>
-      <c r="C30" s="472"/>
-      <c r="D30" s="472"/>
-      <c r="E30" s="472"/>
-      <c r="F30" s="472"/>
+      <c r="C30" s="477"/>
+      <c r="D30" s="477"/>
+      <c r="E30" s="477"/>
+      <c r="F30" s="477"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20683,10 +20683,10 @@
       <c r="B54" s="470" t="s">
         <v>504</v>
       </c>
-      <c r="C54" s="473"/>
-      <c r="D54" s="473"/>
-      <c r="E54" s="473"/>
-      <c r="F54" s="473"/>
+      <c r="C54" s="476"/>
+      <c r="D54" s="476"/>
+      <c r="E54" s="476"/>
+      <c r="F54" s="476"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20702,22 +20702,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="471" t="s">
+      <c r="B57" s="474" t="s">
         <v>505</v>
       </c>
-      <c r="C57" s="471"/>
-      <c r="D57" s="471"/>
-      <c r="E57" s="471"/>
-      <c r="F57" s="471"/>
+      <c r="C57" s="474"/>
+      <c r="D57" s="474"/>
+      <c r="E57" s="474"/>
+      <c r="F57" s="474"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="471" t="s">
+      <c r="B58" s="474" t="s">
         <v>506</v>
       </c>
-      <c r="C58" s="471"/>
-      <c r="D58" s="471"/>
-      <c r="E58" s="471"/>
-      <c r="F58" s="471"/>
+      <c r="C58" s="474"/>
+      <c r="D58" s="474"/>
+      <c r="E58" s="474"/>
+      <c r="F58" s="474"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20751,7 +20751,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>7.4578177179713281E-2</v>
+        <v>7.2665373278927525E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20761,7 +20761,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>2.7703739679456045E-2</v>
+        <v>2.6993185689948896E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>371</v>
@@ -20852,22 +20852,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="471" t="s">
+      <c r="B73" s="474" t="s">
         <v>507</v>
       </c>
-      <c r="C73" s="471"/>
-      <c r="D73" s="471"/>
-      <c r="E73" s="471"/>
-      <c r="F73" s="471"/>
+      <c r="C73" s="474"/>
+      <c r="D73" s="474"/>
+      <c r="E73" s="474"/>
+      <c r="F73" s="474"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="472" t="s">
+      <c r="B74" s="477" t="s">
         <v>477</v>
       </c>
-      <c r="C74" s="472"/>
-      <c r="D74" s="472"/>
-      <c r="E74" s="472"/>
-      <c r="F74" s="472"/>
+      <c r="C74" s="477"/>
+      <c r="D74" s="477"/>
+      <c r="E74" s="477"/>
+      <c r="F74" s="477"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -20875,13 +20875,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="471" t="s">
+      <c r="B77" s="474" t="s">
         <v>508</v>
       </c>
-      <c r="C77" s="471"/>
-      <c r="D77" s="471"/>
-      <c r="E77" s="471"/>
-      <c r="F77" s="471"/>
+      <c r="C77" s="474"/>
+      <c r="D77" s="474"/>
+      <c r="E77" s="474"/>
+      <c r="F77" s="474"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21030,33 +21030,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="471" t="s">
+      <c r="B96" s="474" t="s">
         <v>511</v>
       </c>
-      <c r="C96" s="471"/>
-      <c r="D96" s="471"/>
-      <c r="E96" s="471"/>
-      <c r="F96" s="471"/>
+      <c r="C96" s="474"/>
+      <c r="D96" s="474"/>
+      <c r="E96" s="474"/>
+      <c r="F96" s="474"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="472" t="s">
+      <c r="B97" s="477" t="s">
         <v>512</v>
       </c>
-      <c r="C97" s="472"/>
-      <c r="D97" s="472"/>
-      <c r="E97" s="472"/>
-      <c r="F97" s="472"/>
+      <c r="C97" s="477"/>
+      <c r="D97" s="477"/>
+      <c r="E97" s="477"/>
+      <c r="F97" s="477"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="472" t="s">
+      <c r="B98" s="477" t="s">
         <v>513</v>
       </c>
-      <c r="C98" s="472"/>
-      <c r="D98" s="472"/>
-      <c r="E98" s="472"/>
-      <c r="F98" s="472"/>
+      <c r="C98" s="477"/>
+      <c r="D98" s="477"/>
+      <c r="E98" s="477"/>
+      <c r="F98" s="477"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21119,23 +21119,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="471" t="s">
+      <c r="B107" s="474" t="s">
         <v>514</v>
       </c>
-      <c r="C107" s="471"/>
-      <c r="D107" s="471"/>
-      <c r="E107" s="471"/>
-      <c r="F107" s="471"/>
+      <c r="C107" s="474"/>
+      <c r="D107" s="474"/>
+      <c r="E107" s="474"/>
+      <c r="F107" s="474"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="471" t="s">
+      <c r="B108" s="474" t="s">
         <v>533</v>
       </c>
-      <c r="C108" s="471"/>
-      <c r="D108" s="471"/>
-      <c r="E108" s="471"/>
-      <c r="F108" s="471"/>
+      <c r="C108" s="474"/>
+      <c r="D108" s="474"/>
+      <c r="E108" s="474"/>
+      <c r="F108" s="474"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21179,13 +21179,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="471" t="s">
+      <c r="B114" s="474" t="s">
         <v>515</v>
       </c>
-      <c r="C114" s="471"/>
-      <c r="D114" s="471"/>
-      <c r="E114" s="471"/>
-      <c r="F114" s="471"/>
+      <c r="C114" s="474"/>
+      <c r="D114" s="474"/>
+      <c r="E114" s="474"/>
+      <c r="F114" s="474"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21349,13 +21349,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="475" t="s">
+      <c r="B127" s="472" t="s">
         <v>517</v>
       </c>
-      <c r="C127" s="475"/>
-      <c r="D127" s="475"/>
-      <c r="E127" s="475"/>
-      <c r="F127" s="475"/>
+      <c r="C127" s="472"/>
+      <c r="D127" s="472"/>
+      <c r="E127" s="472"/>
+      <c r="F127" s="472"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21368,22 +21368,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="476" t="s">
+      <c r="B131" s="473" t="s">
         <v>518</v>
       </c>
-      <c r="C131" s="476"/>
-      <c r="D131" s="476"/>
-      <c r="E131" s="476"/>
-      <c r="F131" s="476"/>
+      <c r="C131" s="473"/>
+      <c r="D131" s="473"/>
+      <c r="E131" s="473"/>
+      <c r="F131" s="473"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="471" t="s">
+      <c r="B132" s="474" t="s">
         <v>519</v>
       </c>
-      <c r="C132" s="471"/>
-      <c r="D132" s="471"/>
-      <c r="E132" s="471"/>
-      <c r="F132" s="471"/>
+      <c r="C132" s="474"/>
+      <c r="D132" s="474"/>
+      <c r="E132" s="474"/>
+      <c r="F132" s="474"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21552,13 +21552,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="477" t="s">
+      <c r="B149" s="475" t="s">
         <v>520</v>
       </c>
-      <c r="C149" s="471"/>
-      <c r="D149" s="471"/>
-      <c r="E149" s="471"/>
-      <c r="F149" s="471"/>
+      <c r="C149" s="474"/>
+      <c r="D149" s="474"/>
+      <c r="E149" s="474"/>
+      <c r="F149" s="474"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21566,13 +21566,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="473" t="s">
+      <c r="B152" s="476" t="s">
         <v>521</v>
       </c>
-      <c r="C152" s="473"/>
-      <c r="D152" s="473"/>
-      <c r="E152" s="473"/>
-      <c r="F152" s="473"/>
+      <c r="C152" s="476"/>
+      <c r="D152" s="476"/>
+      <c r="E152" s="476"/>
+      <c r="F152" s="476"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21609,22 +21609,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="474" t="s">
+      <c r="B161" s="471" t="s">
         <v>386</v>
       </c>
-      <c r="C161" s="474"/>
-      <c r="D161" s="474"/>
-      <c r="E161" s="474"/>
-      <c r="F161" s="474"/>
+      <c r="C161" s="471"/>
+      <c r="D161" s="471"/>
+      <c r="E161" s="471"/>
+      <c r="F161" s="471"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="474" t="s">
+      <c r="B162" s="471" t="s">
         <v>387</v>
       </c>
-      <c r="C162" s="474"/>
-      <c r="D162" s="474"/>
-      <c r="E162" s="474"/>
-      <c r="F162" s="474"/>
+      <c r="C162" s="471"/>
+      <c r="D162" s="471"/>
+      <c r="E162" s="471"/>
+      <c r="F162" s="471"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21648,15 +21648,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21671,12 +21668,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/000858.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/000858.SZ_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D1CE32B-8334-46FC-91B4-D42C44D1C119}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{438BD202-866B-4FC8-81DE-CB46C5ABC449}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1470" yWindow="1470" windowWidth="12690" windowHeight="7643" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4986,30 +4986,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5019,6 +5019,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5028,16 +5037,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5407,7 +5407,7 @@
         <v>348</v>
       </c>
       <c r="C8" s="47">
-        <v>105.66</v>
+        <v>104.79</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5425,14 +5425,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>410130.70180829999</v>
+        <v>406753.70284395001</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>525</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.10930488673979756</v>
+        <v>0.11244042740653257</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5440,13 +5440,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="462" t="s">
+      <c r="B12" s="460" t="s">
         <v>353</v>
       </c>
-      <c r="C12" s="462"/>
-      <c r="D12" s="462"/>
-      <c r="E12" s="462"/>
-      <c r="F12" s="462"/>
+      <c r="C12" s="460"/>
+      <c r="D12" s="460"/>
+      <c r="E12" s="460"/>
+      <c r="F12" s="460"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5555,13 +5555,13 @@
       </c>
       <c r="C22" s="255">
         <f>E140</f>
-        <v>62.294573384207148</v>
+        <v>66.49378342223514</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>404</v>
       </c>
       <c r="E22" s="79">
-        <v>0.32950289523458665</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -5570,13 +5570,13 @@
       </c>
       <c r="C23" s="256">
         <f>E141</f>
-        <v>78.83107675053482</v>
+        <v>83.96331433949689</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>405</v>
       </c>
       <c r="E23" s="443">
-        <v>0.22621703288100403</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -5624,22 +5624,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="462" t="s">
+      <c r="B29" s="460" t="s">
         <v>354</v>
       </c>
-      <c r="C29" s="462"/>
-      <c r="D29" s="462"/>
-      <c r="E29" s="462"/>
-      <c r="F29" s="462"/>
+      <c r="C29" s="460"/>
+      <c r="D29" s="460"/>
+      <c r="E29" s="460"/>
+      <c r="F29" s="460"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="466" t="s">
+      <c r="B30" s="462" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="466"/>
-      <c r="D30" s="466"/>
-      <c r="E30" s="466"/>
-      <c r="F30" s="466"/>
+      <c r="C30" s="462"/>
+      <c r="D30" s="462"/>
+      <c r="E30" s="462"/>
+      <c r="F30" s="462"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5651,13 +5651,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="463" t="s">
+      <c r="B33" s="461" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="463"/>
-      <c r="D33" s="463"/>
-      <c r="E33" s="463"/>
-      <c r="F33" s="463"/>
+      <c r="C33" s="461"/>
+      <c r="D33" s="461"/>
+      <c r="E33" s="461"/>
+      <c r="F33" s="461"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5677,13 +5677,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="463" t="s">
+      <c r="B36" s="461" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="463"/>
-      <c r="D36" s="463"/>
-      <c r="E36" s="463"/>
-      <c r="F36" s="463"/>
+      <c r="C36" s="461"/>
+      <c r="D36" s="461"/>
+      <c r="E36" s="461"/>
+      <c r="F36" s="461"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5712,13 +5712,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="463" t="s">
+      <c r="B40" s="461" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="463"/>
-      <c r="D40" s="463"/>
-      <c r="E40" s="463"/>
-      <c r="F40" s="463"/>
+      <c r="C40" s="461"/>
+      <c r="D40" s="461"/>
+      <c r="E40" s="461"/>
+      <c r="F40" s="461"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5734,13 +5734,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="463" t="s">
+      <c r="B43" s="461" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="463"/>
-      <c r="D43" s="463"/>
-      <c r="E43" s="463"/>
-      <c r="F43" s="463"/>
+      <c r="C43" s="461"/>
+      <c r="D43" s="461"/>
+      <c r="E43" s="461"/>
+      <c r="F43" s="461"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5804,13 +5804,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="463" t="s">
+      <c r="B51" s="461" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="463"/>
-      <c r="D51" s="463"/>
-      <c r="E51" s="463"/>
-      <c r="F51" s="463"/>
+      <c r="C51" s="461"/>
+      <c r="D51" s="461"/>
+      <c r="E51" s="461"/>
+      <c r="F51" s="461"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5826,7 +5826,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="463" t="s">
+      <c r="B54" s="461" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="464"/>
@@ -5848,22 +5848,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="462" t="s">
+      <c r="B57" s="460" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="462"/>
-      <c r="D57" s="462"/>
-      <c r="E57" s="462"/>
-      <c r="F57" s="462"/>
+      <c r="C57" s="460"/>
+      <c r="D57" s="460"/>
+      <c r="E57" s="460"/>
+      <c r="F57" s="460"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="462" t="s">
+      <c r="B58" s="460" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="462"/>
-      <c r="D58" s="462"/>
-      <c r="E58" s="462"/>
-      <c r="F58" s="462"/>
+      <c r="C58" s="460"/>
+      <c r="D58" s="460"/>
+      <c r="E58" s="460"/>
+      <c r="F58" s="460"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>7.2665373278927525E-2</v>
+        <v>7.3268664382588819E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5907,7 +5907,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>2.6993185689948896E-2</v>
+        <v>2.721729172630976E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>321</v>
@@ -5998,13 +5998,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="462" t="s">
+      <c r="B73" s="460" t="s">
         <v>476</v>
       </c>
-      <c r="C73" s="462"/>
-      <c r="D73" s="462"/>
-      <c r="E73" s="462"/>
-      <c r="F73" s="462"/>
+      <c r="C73" s="460"/>
+      <c r="D73" s="460"/>
+      <c r="E73" s="460"/>
+      <c r="F73" s="460"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6023,13 +6023,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="462" t="s">
+      <c r="B77" s="460" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="462"/>
-      <c r="D77" s="462"/>
-      <c r="E77" s="462"/>
-      <c r="F77" s="462"/>
+      <c r="C77" s="460"/>
+      <c r="D77" s="460"/>
+      <c r="E77" s="460"/>
+      <c r="F77" s="460"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6198,31 +6198,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="462" t="s">
+      <c r="B96" s="460" t="s">
         <v>483</v>
       </c>
-      <c r="C96" s="462"/>
-      <c r="D96" s="462"/>
-      <c r="E96" s="462"/>
-      <c r="F96" s="462"/>
+      <c r="C96" s="460"/>
+      <c r="D96" s="460"/>
+      <c r="E96" s="460"/>
+      <c r="F96" s="460"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="466" t="s">
+      <c r="B97" s="462" t="s">
         <v>482</v>
       </c>
-      <c r="C97" s="466"/>
-      <c r="D97" s="466"/>
-      <c r="E97" s="466"/>
-      <c r="F97" s="466"/>
+      <c r="C97" s="462"/>
+      <c r="D97" s="462"/>
+      <c r="E97" s="462"/>
+      <c r="F97" s="462"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="466" t="s">
+      <c r="B98" s="462" t="s">
         <v>481</v>
       </c>
-      <c r="C98" s="466"/>
-      <c r="D98" s="466"/>
-      <c r="E98" s="466"/>
-      <c r="F98" s="466"/>
+      <c r="C98" s="462"/>
+      <c r="D98" s="462"/>
+      <c r="E98" s="462"/>
+      <c r="F98" s="462"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6272,22 +6272,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="462" t="s">
+      <c r="B107" s="460" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="462"/>
-      <c r="D107" s="462"/>
-      <c r="E107" s="462"/>
-      <c r="F107" s="462"/>
+      <c r="C107" s="460"/>
+      <c r="D107" s="460"/>
+      <c r="E107" s="460"/>
+      <c r="F107" s="460"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="462" t="s">
+      <c r="B108" s="460" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="462"/>
-      <c r="D108" s="462"/>
-      <c r="E108" s="462"/>
-      <c r="F108" s="462"/>
+      <c r="C108" s="460"/>
+      <c r="D108" s="460"/>
+      <c r="E108" s="460"/>
+      <c r="F108" s="460"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6321,13 +6321,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="462" t="s">
+      <c r="B114" s="460" t="s">
         <v>489</v>
       </c>
-      <c r="C114" s="462"/>
-      <c r="D114" s="462"/>
-      <c r="E114" s="462"/>
-      <c r="F114" s="462"/>
+      <c r="C114" s="460"/>
+      <c r="D114" s="460"/>
+      <c r="E114" s="460"/>
+      <c r="F114" s="460"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6462,13 +6462,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="463" t="s">
+      <c r="B124" s="461" t="s">
         <v>355</v>
       </c>
-      <c r="C124" s="463"/>
-      <c r="D124" s="463"/>
-      <c r="E124" s="463"/>
-      <c r="F124" s="463"/>
+      <c r="C124" s="461"/>
+      <c r="D124" s="461"/>
+      <c r="E124" s="461"/>
+      <c r="F124" s="461"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6503,22 +6503,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="467" t="s">
+      <c r="B131" s="463" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="467"/>
-      <c r="D131" s="467"/>
-      <c r="E131" s="467"/>
-      <c r="F131" s="467"/>
+      <c r="C131" s="463"/>
+      <c r="D131" s="463"/>
+      <c r="E131" s="463"/>
+      <c r="F131" s="463"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="462" t="s">
+      <c r="B132" s="460" t="s">
         <v>357</v>
       </c>
-      <c r="C132" s="462"/>
-      <c r="D132" s="462"/>
-      <c r="E132" s="462"/>
-      <c r="F132" s="462"/>
+      <c r="C132" s="460"/>
+      <c r="D132" s="460"/>
+      <c r="E132" s="460"/>
+      <c r="F132" s="460"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6579,19 +6579,19 @@
       </c>
       <c r="C140" s="333">
         <f>Scenarios!C62</f>
-        <v>4.9724613932919821</v>
+        <v>5.179735548475195</v>
       </c>
       <c r="D140" s="333">
         <f>Scenarios!D62</f>
-        <v>57.322111990915168</v>
+        <v>61.314047873759939</v>
       </c>
       <c r="E140" s="334">
         <f>Scenarios!E62</f>
-        <v>62.294573384207148</v>
+        <v>66.49378342223514</v>
       </c>
       <c r="F140" s="335">
         <f>E22</f>
-        <v>0.32950289523458665</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="141" spans="1:6">
@@ -6600,19 +6600,19 @@
       </c>
       <c r="C141" s="333">
         <f>Scenarios!C63</f>
-        <v>5.7696729926225894</v>
+        <v>6.0078958333333334</v>
       </c>
       <c r="D141" s="333">
         <f>Scenarios!D63</f>
-        <v>73.061403757912231</v>
+        <v>77.955418506163554</v>
       </c>
       <c r="E141" s="334">
         <f>Scenarios!E63</f>
-        <v>78.83107675053482</v>
+        <v>83.96331433949689</v>
       </c>
       <c r="F141" s="335">
         <f>Scenarios!F63</f>
-        <v>0.22621703288100403</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="142" spans="1:6">
@@ -6694,13 +6694,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="461" t="s">
+      <c r="B149" s="467" t="s">
         <v>358</v>
       </c>
-      <c r="C149" s="462"/>
-      <c r="D149" s="462"/>
-      <c r="E149" s="462"/>
-      <c r="F149" s="462"/>
+      <c r="C149" s="460"/>
+      <c r="D149" s="460"/>
+      <c r="E149" s="460"/>
+      <c r="F149" s="460"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6737,13 +6737,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="463" t="s">
+      <c r="B158" s="461" t="s">
         <v>436</v>
       </c>
-      <c r="C158" s="463"/>
-      <c r="D158" s="463"/>
-      <c r="E158" s="463"/>
-      <c r="F158" s="463"/>
+      <c r="C158" s="461"/>
+      <c r="D158" s="461"/>
+      <c r="E158" s="461"/>
+      <c r="F158" s="461"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6751,22 +6751,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="460" t="s">
+      <c r="B161" s="466" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="460"/>
-      <c r="D161" s="460"/>
-      <c r="E161" s="460"/>
-      <c r="F161" s="460"/>
+      <c r="C161" s="466"/>
+      <c r="D161" s="466"/>
+      <c r="E161" s="466"/>
+      <c r="F161" s="466"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="460" t="s">
+      <c r="B162" s="466" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="460"/>
-      <c r="D162" s="460"/>
-      <c r="E162" s="460"/>
-      <c r="F162" s="460"/>
+      <c r="C162" s="466"/>
+      <c r="D162" s="466"/>
+      <c r="E162" s="466"/>
+      <c r="F162" s="466"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6790,6 +6790,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6806,18 +6818,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -14008,16 +14008,16 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>2.6993185689948896E-2</v>
+        <v>2.721729172630976E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>2.6993185689948896E-2</v>
+        <v>2.721729172630976E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>3.9778534923339014E-2</v>
+        <v>4.01087890065846E-2</v>
       </c>
       <c r="I92" s="22" t="str">
         <f t="shared" si="38"/>
@@ -15228,18 +15228,18 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>7.2665373278927525E-2</v>
+        <v>7.3268664382588819E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>6.4512426669873724E-2</v>
+        <v>6.5048029410619879E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>6.2111664614770752E-2</v>
+        <v>6.2627335463275854E-2</v>
       </c>
       <c r="I124" s="74" t="str">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
@@ -15285,11 +15285,11 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.093385922577194E-2</v>
+        <v>8.1605797936778912E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.6855444967109998E-2</v>
+        <v>7.7493523382239166E-2</v>
       </c>
       <c r="I125" s="22" t="str">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -19747,7 +19747,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>105.66</v>
+        <v>104.79</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19758,7 +19758,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.10930488673979756</v>
+        <v>0.11244042740653257</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -20031,23 +20031,23 @@
       </c>
       <c r="C62" s="119">
         <f>PV(F62, Holding_Period, -C58, 0)</f>
-        <v>4.9724613932919821</v>
+        <v>5.179735548475195</v>
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>57.322111990915168</v>
+        <v>61.314047873759939</v>
       </c>
       <c r="E62" s="332">
         <f>C62+D62</f>
-        <v>62.294573384207148</v>
+        <v>66.49378342223514</v>
       </c>
       <c r="F62" s="301">
         <f>Thesis!E22</f>
-        <v>0.32950289523458665</v>
+        <v>0.3</v>
       </c>
       <c r="G62" s="440">
         <f>(1-E62/C36)</f>
-        <v>0.53755491242430398</v>
+        <v>0.50638198758849629</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20056,23 +20056,23 @@
       </c>
       <c r="C63" s="119">
         <f>PV(F63, Holding_Period, -C58, 0)</f>
-        <v>5.7696729926225894</v>
+        <v>6.0078958333333334</v>
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>73.061403757912231</v>
+        <v>77.955418506163554</v>
       </c>
       <c r="E63" s="332">
         <f>C63+D63</f>
-        <v>78.83107675053482</v>
+        <v>83.96331433949689</v>
       </c>
       <c r="F63" s="301">
         <f>Thesis!E23</f>
-        <v>0.22621703288100403</v>
+        <v>0.2</v>
       </c>
       <c r="G63" s="440">
         <f>(1-E63/C36)</f>
-        <v>0.41479582873538823</v>
+        <v>0.37669655407387259</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20254,7 +20254,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>105.66</v>
+        <v>104.79</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20272,14 +20272,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>410130.70180829999</v>
+        <v>406753.70284395001</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>526</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.10930488673979756</v>
+        <v>0.11244042740653257</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20287,13 +20287,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="474" t="s">
+      <c r="B12" s="471" t="s">
         <v>495</v>
       </c>
-      <c r="C12" s="474"/>
-      <c r="D12" s="474"/>
-      <c r="E12" s="474"/>
-      <c r="F12" s="474"/>
+      <c r="C12" s="471"/>
+      <c r="D12" s="471"/>
+      <c r="E12" s="471"/>
+      <c r="F12" s="471"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20409,14 +20409,14 @@
       </c>
       <c r="C22" s="364">
         <f>E140</f>
-        <v>62.294573384207148</v>
+        <v>66.49378342223514</v>
       </c>
       <c r="D22" s="365" t="s">
         <v>438</v>
       </c>
       <c r="E22" s="366">
         <f>Thesis!E22</f>
-        <v>0.32950289523458665</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -20425,14 +20425,14 @@
       </c>
       <c r="C23" s="367">
         <f>E141</f>
-        <v>78.83107675053482</v>
+        <v>83.96331433949689</v>
       </c>
       <c r="D23" s="365" t="s">
         <v>439</v>
       </c>
       <c r="E23" s="368">
         <f>Thesis!E23</f>
-        <v>0.22621703288100403</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -20478,22 +20478,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="474" t="s">
+      <c r="B29" s="471" t="s">
         <v>496</v>
       </c>
-      <c r="C29" s="474"/>
-      <c r="D29" s="474"/>
-      <c r="E29" s="474"/>
-      <c r="F29" s="474"/>
+      <c r="C29" s="471"/>
+      <c r="D29" s="471"/>
+      <c r="E29" s="471"/>
+      <c r="F29" s="471"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="477" t="s">
+      <c r="B30" s="472" t="s">
         <v>497</v>
       </c>
-      <c r="C30" s="477"/>
-      <c r="D30" s="477"/>
-      <c r="E30" s="477"/>
-      <c r="F30" s="477"/>
+      <c r="C30" s="472"/>
+      <c r="D30" s="472"/>
+      <c r="E30" s="472"/>
+      <c r="F30" s="472"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20683,10 +20683,10 @@
       <c r="B54" s="470" t="s">
         <v>504</v>
       </c>
-      <c r="C54" s="476"/>
-      <c r="D54" s="476"/>
-      <c r="E54" s="476"/>
-      <c r="F54" s="476"/>
+      <c r="C54" s="473"/>
+      <c r="D54" s="473"/>
+      <c r="E54" s="473"/>
+      <c r="F54" s="473"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20702,22 +20702,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="474" t="s">
+      <c r="B57" s="471" t="s">
         <v>505</v>
       </c>
-      <c r="C57" s="474"/>
-      <c r="D57" s="474"/>
-      <c r="E57" s="474"/>
-      <c r="F57" s="474"/>
+      <c r="C57" s="471"/>
+      <c r="D57" s="471"/>
+      <c r="E57" s="471"/>
+      <c r="F57" s="471"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="474" t="s">
+      <c r="B58" s="471" t="s">
         <v>506</v>
       </c>
-      <c r="C58" s="474"/>
-      <c r="D58" s="474"/>
-      <c r="E58" s="474"/>
-      <c r="F58" s="474"/>
+      <c r="C58" s="471"/>
+      <c r="D58" s="471"/>
+      <c r="E58" s="471"/>
+      <c r="F58" s="471"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20751,7 +20751,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>7.2665373278927525E-2</v>
+        <v>7.3268664382588819E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20761,7 +20761,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>2.6993185689948896E-2</v>
+        <v>2.721729172630976E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>371</v>
@@ -20852,22 +20852,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="474" t="s">
+      <c r="B73" s="471" t="s">
         <v>507</v>
       </c>
-      <c r="C73" s="474"/>
-      <c r="D73" s="474"/>
-      <c r="E73" s="474"/>
-      <c r="F73" s="474"/>
+      <c r="C73" s="471"/>
+      <c r="D73" s="471"/>
+      <c r="E73" s="471"/>
+      <c r="F73" s="471"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="477" t="s">
+      <c r="B74" s="472" t="s">
         <v>477</v>
       </c>
-      <c r="C74" s="477"/>
-      <c r="D74" s="477"/>
-      <c r="E74" s="477"/>
-      <c r="F74" s="477"/>
+      <c r="C74" s="472"/>
+      <c r="D74" s="472"/>
+      <c r="E74" s="472"/>
+      <c r="F74" s="472"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -20875,13 +20875,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="474" t="s">
+      <c r="B77" s="471" t="s">
         <v>508</v>
       </c>
-      <c r="C77" s="474"/>
-      <c r="D77" s="474"/>
-      <c r="E77" s="474"/>
-      <c r="F77" s="474"/>
+      <c r="C77" s="471"/>
+      <c r="D77" s="471"/>
+      <c r="E77" s="471"/>
+      <c r="F77" s="471"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21030,33 +21030,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="474" t="s">
+      <c r="B96" s="471" t="s">
         <v>511</v>
       </c>
-      <c r="C96" s="474"/>
-      <c r="D96" s="474"/>
-      <c r="E96" s="474"/>
-      <c r="F96" s="474"/>
+      <c r="C96" s="471"/>
+      <c r="D96" s="471"/>
+      <c r="E96" s="471"/>
+      <c r="F96" s="471"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="477" t="s">
+      <c r="B97" s="472" t="s">
         <v>512</v>
       </c>
-      <c r="C97" s="477"/>
-      <c r="D97" s="477"/>
-      <c r="E97" s="477"/>
-      <c r="F97" s="477"/>
+      <c r="C97" s="472"/>
+      <c r="D97" s="472"/>
+      <c r="E97" s="472"/>
+      <c r="F97" s="472"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="477" t="s">
+      <c r="B98" s="472" t="s">
         <v>513</v>
       </c>
-      <c r="C98" s="477"/>
-      <c r="D98" s="477"/>
-      <c r="E98" s="477"/>
-      <c r="F98" s="477"/>
+      <c r="C98" s="472"/>
+      <c r="D98" s="472"/>
+      <c r="E98" s="472"/>
+      <c r="F98" s="472"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21119,23 +21119,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="474" t="s">
+      <c r="B107" s="471" t="s">
         <v>514</v>
       </c>
-      <c r="C107" s="474"/>
-      <c r="D107" s="474"/>
-      <c r="E107" s="474"/>
-      <c r="F107" s="474"/>
+      <c r="C107" s="471"/>
+      <c r="D107" s="471"/>
+      <c r="E107" s="471"/>
+      <c r="F107" s="471"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="474" t="s">
+      <c r="B108" s="471" t="s">
         <v>533</v>
       </c>
-      <c r="C108" s="474"/>
-      <c r="D108" s="474"/>
-      <c r="E108" s="474"/>
-      <c r="F108" s="474"/>
+      <c r="C108" s="471"/>
+      <c r="D108" s="471"/>
+      <c r="E108" s="471"/>
+      <c r="F108" s="471"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21179,13 +21179,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="474" t="s">
+      <c r="B114" s="471" t="s">
         <v>515</v>
       </c>
-      <c r="C114" s="474"/>
-      <c r="D114" s="474"/>
-      <c r="E114" s="474"/>
-      <c r="F114" s="474"/>
+      <c r="C114" s="471"/>
+      <c r="D114" s="471"/>
+      <c r="E114" s="471"/>
+      <c r="F114" s="471"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21349,13 +21349,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="472" t="s">
+      <c r="B127" s="475" t="s">
         <v>517</v>
       </c>
-      <c r="C127" s="472"/>
-      <c r="D127" s="472"/>
-      <c r="E127" s="472"/>
-      <c r="F127" s="472"/>
+      <c r="C127" s="475"/>
+      <c r="D127" s="475"/>
+      <c r="E127" s="475"/>
+      <c r="F127" s="475"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21368,22 +21368,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="473" t="s">
+      <c r="B131" s="476" t="s">
         <v>518</v>
       </c>
-      <c r="C131" s="473"/>
-      <c r="D131" s="473"/>
-      <c r="E131" s="473"/>
-      <c r="F131" s="473"/>
+      <c r="C131" s="476"/>
+      <c r="D131" s="476"/>
+      <c r="E131" s="476"/>
+      <c r="F131" s="476"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="474" t="s">
+      <c r="B132" s="471" t="s">
         <v>519</v>
       </c>
-      <c r="C132" s="474"/>
-      <c r="D132" s="474"/>
-      <c r="E132" s="474"/>
-      <c r="F132" s="474"/>
+      <c r="C132" s="471"/>
+      <c r="D132" s="471"/>
+      <c r="E132" s="471"/>
+      <c r="F132" s="471"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21444,19 +21444,19 @@
       </c>
       <c r="C140" s="409">
         <f>Scenarios!C62</f>
-        <v>4.9724613932919821</v>
+        <v>5.179735548475195</v>
       </c>
       <c r="D140" s="409">
         <f>Scenarios!D62</f>
-        <v>57.322111990915168</v>
+        <v>61.314047873759939</v>
       </c>
       <c r="E140" s="410">
         <f>Scenarios!E62</f>
-        <v>62.294573384207148</v>
+        <v>66.49378342223514</v>
       </c>
       <c r="F140" s="411">
         <f>E22</f>
-        <v>0.32950289523458665</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="141" spans="1:6">
@@ -21465,19 +21465,19 @@
       </c>
       <c r="C141" s="409">
         <f>Scenarios!C63</f>
-        <v>5.7696729926225894</v>
+        <v>6.0078958333333334</v>
       </c>
       <c r="D141" s="409">
         <f>Scenarios!D63</f>
-        <v>73.061403757912231</v>
+        <v>77.955418506163554</v>
       </c>
       <c r="E141" s="410">
         <f>Scenarios!E63</f>
-        <v>78.83107675053482</v>
+        <v>83.96331433949689</v>
       </c>
       <c r="F141" s="411">
         <f>Scenarios!F63</f>
-        <v>0.22621703288100403</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -21552,13 +21552,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="475" t="s">
+      <c r="B149" s="477" t="s">
         <v>520</v>
       </c>
-      <c r="C149" s="474"/>
-      <c r="D149" s="474"/>
-      <c r="E149" s="474"/>
-      <c r="F149" s="474"/>
+      <c r="C149" s="471"/>
+      <c r="D149" s="471"/>
+      <c r="E149" s="471"/>
+      <c r="F149" s="471"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21566,13 +21566,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="476" t="s">
+      <c r="B152" s="473" t="s">
         <v>521</v>
       </c>
-      <c r="C152" s="476"/>
-      <c r="D152" s="476"/>
-      <c r="E152" s="476"/>
-      <c r="F152" s="476"/>
+      <c r="C152" s="473"/>
+      <c r="D152" s="473"/>
+      <c r="E152" s="473"/>
+      <c r="F152" s="473"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21609,22 +21609,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="471" t="s">
+      <c r="B161" s="474" t="s">
         <v>386</v>
       </c>
-      <c r="C161" s="471"/>
-      <c r="D161" s="471"/>
-      <c r="E161" s="471"/>
-      <c r="F161" s="471"/>
+      <c r="C161" s="474"/>
+      <c r="D161" s="474"/>
+      <c r="E161" s="474"/>
+      <c r="F161" s="474"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="471" t="s">
+      <c r="B162" s="474" t="s">
         <v>387</v>
       </c>
-      <c r="C162" s="471"/>
-      <c r="D162" s="471"/>
-      <c r="E162" s="471"/>
-      <c r="F162" s="471"/>
+      <c r="C162" s="474"/>
+      <c r="D162" s="474"/>
+      <c r="E162" s="474"/>
+      <c r="F162" s="474"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21648,12 +21648,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21668,15 +21671,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/000858.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/000858.SZ_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{438BD202-866B-4FC8-81DE-CB46C5ABC449}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6CB9290-38CD-4225-A2AA-601618379F9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4986,30 +4986,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5019,25 +5019,25 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5440,13 +5440,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="460" t="s">
+      <c r="B12" s="462" t="s">
         <v>353</v>
       </c>
-      <c r="C12" s="460"/>
-      <c r="D12" s="460"/>
-      <c r="E12" s="460"/>
-      <c r="F12" s="460"/>
+      <c r="C12" s="462"/>
+      <c r="D12" s="462"/>
+      <c r="E12" s="462"/>
+      <c r="F12" s="462"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5624,22 +5624,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="460" t="s">
+      <c r="B29" s="462" t="s">
         <v>354</v>
       </c>
-      <c r="C29" s="460"/>
-      <c r="D29" s="460"/>
-      <c r="E29" s="460"/>
-      <c r="F29" s="460"/>
+      <c r="C29" s="462"/>
+      <c r="D29" s="462"/>
+      <c r="E29" s="462"/>
+      <c r="F29" s="462"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="462" t="s">
+      <c r="B30" s="466" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="462"/>
-      <c r="D30" s="462"/>
-      <c r="E30" s="462"/>
-      <c r="F30" s="462"/>
+      <c r="C30" s="466"/>
+      <c r="D30" s="466"/>
+      <c r="E30" s="466"/>
+      <c r="F30" s="466"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5651,13 +5651,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="461" t="s">
+      <c r="B33" s="463" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="461"/>
-      <c r="D33" s="461"/>
-      <c r="E33" s="461"/>
-      <c r="F33" s="461"/>
+      <c r="C33" s="463"/>
+      <c r="D33" s="463"/>
+      <c r="E33" s="463"/>
+      <c r="F33" s="463"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5677,13 +5677,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="461" t="s">
+      <c r="B36" s="463" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="461"/>
-      <c r="D36" s="461"/>
-      <c r="E36" s="461"/>
-      <c r="F36" s="461"/>
+      <c r="C36" s="463"/>
+      <c r="D36" s="463"/>
+      <c r="E36" s="463"/>
+      <c r="F36" s="463"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5712,13 +5712,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="461" t="s">
+      <c r="B40" s="463" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="461"/>
-      <c r="D40" s="461"/>
-      <c r="E40" s="461"/>
-      <c r="F40" s="461"/>
+      <c r="C40" s="463"/>
+      <c r="D40" s="463"/>
+      <c r="E40" s="463"/>
+      <c r="F40" s="463"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5734,13 +5734,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="461" t="s">
+      <c r="B43" s="463" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="461"/>
-      <c r="D43" s="461"/>
-      <c r="E43" s="461"/>
-      <c r="F43" s="461"/>
+      <c r="C43" s="463"/>
+      <c r="D43" s="463"/>
+      <c r="E43" s="463"/>
+      <c r="F43" s="463"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5804,13 +5804,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="461" t="s">
+      <c r="B51" s="463" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="461"/>
-      <c r="D51" s="461"/>
-      <c r="E51" s="461"/>
-      <c r="F51" s="461"/>
+      <c r="C51" s="463"/>
+      <c r="D51" s="463"/>
+      <c r="E51" s="463"/>
+      <c r="F51" s="463"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5826,7 +5826,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="461" t="s">
+      <c r="B54" s="463" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="464"/>
@@ -5848,22 +5848,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="460" t="s">
+      <c r="B57" s="462" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="460"/>
-      <c r="D57" s="460"/>
-      <c r="E57" s="460"/>
-      <c r="F57" s="460"/>
+      <c r="C57" s="462"/>
+      <c r="D57" s="462"/>
+      <c r="E57" s="462"/>
+      <c r="F57" s="462"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="460" t="s">
+      <c r="B58" s="462" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="460"/>
-      <c r="D58" s="460"/>
-      <c r="E58" s="460"/>
-      <c r="F58" s="460"/>
+      <c r="C58" s="462"/>
+      <c r="D58" s="462"/>
+      <c r="E58" s="462"/>
+      <c r="F58" s="462"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5998,13 +5998,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="460" t="s">
+      <c r="B73" s="462" t="s">
         <v>476</v>
       </c>
-      <c r="C73" s="460"/>
-      <c r="D73" s="460"/>
-      <c r="E73" s="460"/>
-      <c r="F73" s="460"/>
+      <c r="C73" s="462"/>
+      <c r="D73" s="462"/>
+      <c r="E73" s="462"/>
+      <c r="F73" s="462"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6023,13 +6023,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="460" t="s">
+      <c r="B77" s="462" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="460"/>
-      <c r="D77" s="460"/>
-      <c r="E77" s="460"/>
-      <c r="F77" s="460"/>
+      <c r="C77" s="462"/>
+      <c r="D77" s="462"/>
+      <c r="E77" s="462"/>
+      <c r="F77" s="462"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6198,31 +6198,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="460" t="s">
+      <c r="B96" s="462" t="s">
         <v>483</v>
       </c>
-      <c r="C96" s="460"/>
-      <c r="D96" s="460"/>
-      <c r="E96" s="460"/>
-      <c r="F96" s="460"/>
+      <c r="C96" s="462"/>
+      <c r="D96" s="462"/>
+      <c r="E96" s="462"/>
+      <c r="F96" s="462"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="462" t="s">
+      <c r="B97" s="466" t="s">
         <v>482</v>
       </c>
-      <c r="C97" s="462"/>
-      <c r="D97" s="462"/>
-      <c r="E97" s="462"/>
-      <c r="F97" s="462"/>
+      <c r="C97" s="466"/>
+      <c r="D97" s="466"/>
+      <c r="E97" s="466"/>
+      <c r="F97" s="466"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="462" t="s">
+      <c r="B98" s="466" t="s">
         <v>481</v>
       </c>
-      <c r="C98" s="462"/>
-      <c r="D98" s="462"/>
-      <c r="E98" s="462"/>
-      <c r="F98" s="462"/>
+      <c r="C98" s="466"/>
+      <c r="D98" s="466"/>
+      <c r="E98" s="466"/>
+      <c r="F98" s="466"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6272,22 +6272,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="460" t="s">
+      <c r="B107" s="462" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="460"/>
-      <c r="D107" s="460"/>
-      <c r="E107" s="460"/>
-      <c r="F107" s="460"/>
+      <c r="C107" s="462"/>
+      <c r="D107" s="462"/>
+      <c r="E107" s="462"/>
+      <c r="F107" s="462"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="460" t="s">
+      <c r="B108" s="462" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="460"/>
-      <c r="D108" s="460"/>
-      <c r="E108" s="460"/>
-      <c r="F108" s="460"/>
+      <c r="C108" s="462"/>
+      <c r="D108" s="462"/>
+      <c r="E108" s="462"/>
+      <c r="F108" s="462"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6321,13 +6321,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="460" t="s">
+      <c r="B114" s="462" t="s">
         <v>489</v>
       </c>
-      <c r="C114" s="460"/>
-      <c r="D114" s="460"/>
-      <c r="E114" s="460"/>
-      <c r="F114" s="460"/>
+      <c r="C114" s="462"/>
+      <c r="D114" s="462"/>
+      <c r="E114" s="462"/>
+      <c r="F114" s="462"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6462,13 +6462,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="461" t="s">
+      <c r="B124" s="463" t="s">
         <v>355</v>
       </c>
-      <c r="C124" s="461"/>
-      <c r="D124" s="461"/>
-      <c r="E124" s="461"/>
-      <c r="F124" s="461"/>
+      <c r="C124" s="463"/>
+      <c r="D124" s="463"/>
+      <c r="E124" s="463"/>
+      <c r="F124" s="463"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6503,22 +6503,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="463" t="s">
+      <c r="B131" s="467" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="463"/>
-      <c r="D131" s="463"/>
-      <c r="E131" s="463"/>
-      <c r="F131" s="463"/>
+      <c r="C131" s="467"/>
+      <c r="D131" s="467"/>
+      <c r="E131" s="467"/>
+      <c r="F131" s="467"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="460" t="s">
+      <c r="B132" s="462" t="s">
         <v>357</v>
       </c>
-      <c r="C132" s="460"/>
-      <c r="D132" s="460"/>
-      <c r="E132" s="460"/>
-      <c r="F132" s="460"/>
+      <c r="C132" s="462"/>
+      <c r="D132" s="462"/>
+      <c r="E132" s="462"/>
+      <c r="F132" s="462"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6694,13 +6694,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="467" t="s">
+      <c r="B149" s="461" t="s">
         <v>358</v>
       </c>
-      <c r="C149" s="460"/>
-      <c r="D149" s="460"/>
-      <c r="E149" s="460"/>
-      <c r="F149" s="460"/>
+      <c r="C149" s="462"/>
+      <c r="D149" s="462"/>
+      <c r="E149" s="462"/>
+      <c r="F149" s="462"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6737,13 +6737,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="461" t="s">
+      <c r="B158" s="463" t="s">
         <v>436</v>
       </c>
-      <c r="C158" s="461"/>
-      <c r="D158" s="461"/>
-      <c r="E158" s="461"/>
-      <c r="F158" s="461"/>
+      <c r="C158" s="463"/>
+      <c r="D158" s="463"/>
+      <c r="E158" s="463"/>
+      <c r="F158" s="463"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6751,22 +6751,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="466" t="s">
+      <c r="B161" s="460" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="466"/>
-      <c r="D161" s="466"/>
-      <c r="E161" s="466"/>
-      <c r="F161" s="466"/>
+      <c r="C161" s="460"/>
+      <c r="D161" s="460"/>
+      <c r="E161" s="460"/>
+      <c r="F161" s="460"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="466" t="s">
+      <c r="B162" s="460" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="466"/>
-      <c r="D162" s="466"/>
-      <c r="E162" s="466"/>
-      <c r="F162" s="466"/>
+      <c r="C162" s="460"/>
+      <c r="D162" s="460"/>
+      <c r="E162" s="460"/>
+      <c r="F162" s="460"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6790,18 +6790,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6818,6 +6806,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -20287,13 +20287,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="471" t="s">
+      <c r="B12" s="474" t="s">
         <v>495</v>
       </c>
-      <c r="C12" s="471"/>
-      <c r="D12" s="471"/>
-      <c r="E12" s="471"/>
-      <c r="F12" s="471"/>
+      <c r="C12" s="474"/>
+      <c r="D12" s="474"/>
+      <c r="E12" s="474"/>
+      <c r="F12" s="474"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20478,22 +20478,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="471" t="s">
+      <c r="B29" s="474" t="s">
         <v>496</v>
       </c>
-      <c r="C29" s="471"/>
-      <c r="D29" s="471"/>
-      <c r="E29" s="471"/>
-      <c r="F29" s="471"/>
+      <c r="C29" s="474"/>
+      <c r="D29" s="474"/>
+      <c r="E29" s="474"/>
+      <c r="F29" s="474"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="472" t="s">
+      <c r="B30" s="477" t="s">
         <v>497</v>
       </c>
-      <c r="C30" s="472"/>
-      <c r="D30" s="472"/>
-      <c r="E30" s="472"/>
-      <c r="F30" s="472"/>
+      <c r="C30" s="477"/>
+      <c r="D30" s="477"/>
+      <c r="E30" s="477"/>
+      <c r="F30" s="477"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20683,10 +20683,10 @@
       <c r="B54" s="470" t="s">
         <v>504</v>
       </c>
-      <c r="C54" s="473"/>
-      <c r="D54" s="473"/>
-      <c r="E54" s="473"/>
-      <c r="F54" s="473"/>
+      <c r="C54" s="476"/>
+      <c r="D54" s="476"/>
+      <c r="E54" s="476"/>
+      <c r="F54" s="476"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20702,22 +20702,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="471" t="s">
+      <c r="B57" s="474" t="s">
         <v>505</v>
       </c>
-      <c r="C57" s="471"/>
-      <c r="D57" s="471"/>
-      <c r="E57" s="471"/>
-      <c r="F57" s="471"/>
+      <c r="C57" s="474"/>
+      <c r="D57" s="474"/>
+      <c r="E57" s="474"/>
+      <c r="F57" s="474"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="471" t="s">
+      <c r="B58" s="474" t="s">
         <v>506</v>
       </c>
-      <c r="C58" s="471"/>
-      <c r="D58" s="471"/>
-      <c r="E58" s="471"/>
-      <c r="F58" s="471"/>
+      <c r="C58" s="474"/>
+      <c r="D58" s="474"/>
+      <c r="E58" s="474"/>
+      <c r="F58" s="474"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20852,22 +20852,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="471" t="s">
+      <c r="B73" s="474" t="s">
         <v>507</v>
       </c>
-      <c r="C73" s="471"/>
-      <c r="D73" s="471"/>
-      <c r="E73" s="471"/>
-      <c r="F73" s="471"/>
+      <c r="C73" s="474"/>
+      <c r="D73" s="474"/>
+      <c r="E73" s="474"/>
+      <c r="F73" s="474"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="472" t="s">
+      <c r="B74" s="477" t="s">
         <v>477</v>
       </c>
-      <c r="C74" s="472"/>
-      <c r="D74" s="472"/>
-      <c r="E74" s="472"/>
-      <c r="F74" s="472"/>
+      <c r="C74" s="477"/>
+      <c r="D74" s="477"/>
+      <c r="E74" s="477"/>
+      <c r="F74" s="477"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -20875,13 +20875,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="471" t="s">
+      <c r="B77" s="474" t="s">
         <v>508</v>
       </c>
-      <c r="C77" s="471"/>
-      <c r="D77" s="471"/>
-      <c r="E77" s="471"/>
-      <c r="F77" s="471"/>
+      <c r="C77" s="474"/>
+      <c r="D77" s="474"/>
+      <c r="E77" s="474"/>
+      <c r="F77" s="474"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21030,33 +21030,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="471" t="s">
+      <c r="B96" s="474" t="s">
         <v>511</v>
       </c>
-      <c r="C96" s="471"/>
-      <c r="D96" s="471"/>
-      <c r="E96" s="471"/>
-      <c r="F96" s="471"/>
+      <c r="C96" s="474"/>
+      <c r="D96" s="474"/>
+      <c r="E96" s="474"/>
+      <c r="F96" s="474"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="472" t="s">
+      <c r="B97" s="477" t="s">
         <v>512</v>
       </c>
-      <c r="C97" s="472"/>
-      <c r="D97" s="472"/>
-      <c r="E97" s="472"/>
-      <c r="F97" s="472"/>
+      <c r="C97" s="477"/>
+      <c r="D97" s="477"/>
+      <c r="E97" s="477"/>
+      <c r="F97" s="477"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="472" t="s">
+      <c r="B98" s="477" t="s">
         <v>513</v>
       </c>
-      <c r="C98" s="472"/>
-      <c r="D98" s="472"/>
-      <c r="E98" s="472"/>
-      <c r="F98" s="472"/>
+      <c r="C98" s="477"/>
+      <c r="D98" s="477"/>
+      <c r="E98" s="477"/>
+      <c r="F98" s="477"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21119,23 +21119,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="471" t="s">
+      <c r="B107" s="474" t="s">
         <v>514</v>
       </c>
-      <c r="C107" s="471"/>
-      <c r="D107" s="471"/>
-      <c r="E107" s="471"/>
-      <c r="F107" s="471"/>
+      <c r="C107" s="474"/>
+      <c r="D107" s="474"/>
+      <c r="E107" s="474"/>
+      <c r="F107" s="474"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="471" t="s">
+      <c r="B108" s="474" t="s">
         <v>533</v>
       </c>
-      <c r="C108" s="471"/>
-      <c r="D108" s="471"/>
-      <c r="E108" s="471"/>
-      <c r="F108" s="471"/>
+      <c r="C108" s="474"/>
+      <c r="D108" s="474"/>
+      <c r="E108" s="474"/>
+      <c r="F108" s="474"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21179,13 +21179,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="471" t="s">
+      <c r="B114" s="474" t="s">
         <v>515</v>
       </c>
-      <c r="C114" s="471"/>
-      <c r="D114" s="471"/>
-      <c r="E114" s="471"/>
-      <c r="F114" s="471"/>
+      <c r="C114" s="474"/>
+      <c r="D114" s="474"/>
+      <c r="E114" s="474"/>
+      <c r="F114" s="474"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21349,13 +21349,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="475" t="s">
+      <c r="B127" s="472" t="s">
         <v>517</v>
       </c>
-      <c r="C127" s="475"/>
-      <c r="D127" s="475"/>
-      <c r="E127" s="475"/>
-      <c r="F127" s="475"/>
+      <c r="C127" s="472"/>
+      <c r="D127" s="472"/>
+      <c r="E127" s="472"/>
+      <c r="F127" s="472"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21368,22 +21368,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="476" t="s">
+      <c r="B131" s="473" t="s">
         <v>518</v>
       </c>
-      <c r="C131" s="476"/>
-      <c r="D131" s="476"/>
-      <c r="E131" s="476"/>
-      <c r="F131" s="476"/>
+      <c r="C131" s="473"/>
+      <c r="D131" s="473"/>
+      <c r="E131" s="473"/>
+      <c r="F131" s="473"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="471" t="s">
+      <c r="B132" s="474" t="s">
         <v>519</v>
       </c>
-      <c r="C132" s="471"/>
-      <c r="D132" s="471"/>
-      <c r="E132" s="471"/>
-      <c r="F132" s="471"/>
+      <c r="C132" s="474"/>
+      <c r="D132" s="474"/>
+      <c r="E132" s="474"/>
+      <c r="F132" s="474"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21552,13 +21552,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="477" t="s">
+      <c r="B149" s="475" t="s">
         <v>520</v>
       </c>
-      <c r="C149" s="471"/>
-      <c r="D149" s="471"/>
-      <c r="E149" s="471"/>
-      <c r="F149" s="471"/>
+      <c r="C149" s="474"/>
+      <c r="D149" s="474"/>
+      <c r="E149" s="474"/>
+      <c r="F149" s="474"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21566,13 +21566,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="473" t="s">
+      <c r="B152" s="476" t="s">
         <v>521</v>
       </c>
-      <c r="C152" s="473"/>
-      <c r="D152" s="473"/>
-      <c r="E152" s="473"/>
-      <c r="F152" s="473"/>
+      <c r="C152" s="476"/>
+      <c r="D152" s="476"/>
+      <c r="E152" s="476"/>
+      <c r="F152" s="476"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21609,22 +21609,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="474" t="s">
+      <c r="B161" s="471" t="s">
         <v>386</v>
       </c>
-      <c r="C161" s="474"/>
-      <c r="D161" s="474"/>
-      <c r="E161" s="474"/>
-      <c r="F161" s="474"/>
+      <c r="C161" s="471"/>
+      <c r="D161" s="471"/>
+      <c r="E161" s="471"/>
+      <c r="F161" s="471"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="474" t="s">
+      <c r="B162" s="471" t="s">
         <v>387</v>
       </c>
-      <c r="C162" s="474"/>
-      <c r="D162" s="474"/>
-      <c r="E162" s="474"/>
-      <c r="F162" s="474"/>
+      <c r="C162" s="471"/>
+      <c r="D162" s="471"/>
+      <c r="E162" s="471"/>
+      <c r="F162" s="471"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21648,15 +21648,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21671,12 +21668,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/000858.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/000858.SZ_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6CB9290-38CD-4225-A2AA-601618379F9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F805AA2-80BB-47CB-AD9B-D57813CCB183}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4986,30 +4986,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5019,6 +5019,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5028,16 +5037,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5407,7 +5407,7 @@
         <v>348</v>
       </c>
       <c r="C8" s="47">
-        <v>104.79</v>
+        <v>102.4</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5425,14 +5425,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>406753.70284395001</v>
+        <v>397476.65971199999</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>525</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.11244042740653257</v>
+        <v>0.12123883246616156</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5440,13 +5440,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="462" t="s">
+      <c r="B12" s="460" t="s">
         <v>353</v>
       </c>
-      <c r="C12" s="462"/>
-      <c r="D12" s="462"/>
-      <c r="E12" s="462"/>
-      <c r="F12" s="462"/>
+      <c r="C12" s="460"/>
+      <c r="D12" s="460"/>
+      <c r="E12" s="460"/>
+      <c r="F12" s="460"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5624,22 +5624,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="462" t="s">
+      <c r="B29" s="460" t="s">
         <v>354</v>
       </c>
-      <c r="C29" s="462"/>
-      <c r="D29" s="462"/>
-      <c r="E29" s="462"/>
-      <c r="F29" s="462"/>
+      <c r="C29" s="460"/>
+      <c r="D29" s="460"/>
+      <c r="E29" s="460"/>
+      <c r="F29" s="460"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="466" t="s">
+      <c r="B30" s="462" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="466"/>
-      <c r="D30" s="466"/>
-      <c r="E30" s="466"/>
-      <c r="F30" s="466"/>
+      <c r="C30" s="462"/>
+      <c r="D30" s="462"/>
+      <c r="E30" s="462"/>
+      <c r="F30" s="462"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5651,13 +5651,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="463" t="s">
+      <c r="B33" s="461" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="463"/>
-      <c r="D33" s="463"/>
-      <c r="E33" s="463"/>
-      <c r="F33" s="463"/>
+      <c r="C33" s="461"/>
+      <c r="D33" s="461"/>
+      <c r="E33" s="461"/>
+      <c r="F33" s="461"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5677,13 +5677,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="463" t="s">
+      <c r="B36" s="461" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="463"/>
-      <c r="D36" s="463"/>
-      <c r="E36" s="463"/>
-      <c r="F36" s="463"/>
+      <c r="C36" s="461"/>
+      <c r="D36" s="461"/>
+      <c r="E36" s="461"/>
+      <c r="F36" s="461"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5712,13 +5712,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="463" t="s">
+      <c r="B40" s="461" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="463"/>
-      <c r="D40" s="463"/>
-      <c r="E40" s="463"/>
-      <c r="F40" s="463"/>
+      <c r="C40" s="461"/>
+      <c r="D40" s="461"/>
+      <c r="E40" s="461"/>
+      <c r="F40" s="461"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5734,13 +5734,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="463" t="s">
+      <c r="B43" s="461" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="463"/>
-      <c r="D43" s="463"/>
-      <c r="E43" s="463"/>
-      <c r="F43" s="463"/>
+      <c r="C43" s="461"/>
+      <c r="D43" s="461"/>
+      <c r="E43" s="461"/>
+      <c r="F43" s="461"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5804,13 +5804,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="463" t="s">
+      <c r="B51" s="461" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="463"/>
-      <c r="D51" s="463"/>
-      <c r="E51" s="463"/>
-      <c r="F51" s="463"/>
+      <c r="C51" s="461"/>
+      <c r="D51" s="461"/>
+      <c r="E51" s="461"/>
+      <c r="F51" s="461"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5826,7 +5826,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="463" t="s">
+      <c r="B54" s="461" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="464"/>
@@ -5848,22 +5848,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="462" t="s">
+      <c r="B57" s="460" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="462"/>
-      <c r="D57" s="462"/>
-      <c r="E57" s="462"/>
-      <c r="F57" s="462"/>
+      <c r="C57" s="460"/>
+      <c r="D57" s="460"/>
+      <c r="E57" s="460"/>
+      <c r="F57" s="460"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="462" t="s">
+      <c r="B58" s="460" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="462"/>
-      <c r="D58" s="462"/>
-      <c r="E58" s="462"/>
-      <c r="F58" s="462"/>
+      <c r="C58" s="460"/>
+      <c r="D58" s="460"/>
+      <c r="E58" s="460"/>
+      <c r="F58" s="460"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>7.3268664382588819E-2</v>
+        <v>7.4978743561049638E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5907,7 +5907,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>2.721729172630976E-2</v>
+        <v>2.7852539062500001E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>321</v>
@@ -5998,13 +5998,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="462" t="s">
+      <c r="B73" s="460" t="s">
         <v>476</v>
       </c>
-      <c r="C73" s="462"/>
-      <c r="D73" s="462"/>
-      <c r="E73" s="462"/>
-      <c r="F73" s="462"/>
+      <c r="C73" s="460"/>
+      <c r="D73" s="460"/>
+      <c r="E73" s="460"/>
+      <c r="F73" s="460"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6023,13 +6023,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="462" t="s">
+      <c r="B77" s="460" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="462"/>
-      <c r="D77" s="462"/>
-      <c r="E77" s="462"/>
-      <c r="F77" s="462"/>
+      <c r="C77" s="460"/>
+      <c r="D77" s="460"/>
+      <c r="E77" s="460"/>
+      <c r="F77" s="460"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6198,31 +6198,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="462" t="s">
+      <c r="B96" s="460" t="s">
         <v>483</v>
       </c>
-      <c r="C96" s="462"/>
-      <c r="D96" s="462"/>
-      <c r="E96" s="462"/>
-      <c r="F96" s="462"/>
+      <c r="C96" s="460"/>
+      <c r="D96" s="460"/>
+      <c r="E96" s="460"/>
+      <c r="F96" s="460"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="466" t="s">
+      <c r="B97" s="462" t="s">
         <v>482</v>
       </c>
-      <c r="C97" s="466"/>
-      <c r="D97" s="466"/>
-      <c r="E97" s="466"/>
-      <c r="F97" s="466"/>
+      <c r="C97" s="462"/>
+      <c r="D97" s="462"/>
+      <c r="E97" s="462"/>
+      <c r="F97" s="462"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="466" t="s">
+      <c r="B98" s="462" t="s">
         <v>481</v>
       </c>
-      <c r="C98" s="466"/>
-      <c r="D98" s="466"/>
-      <c r="E98" s="466"/>
-      <c r="F98" s="466"/>
+      <c r="C98" s="462"/>
+      <c r="D98" s="462"/>
+      <c r="E98" s="462"/>
+      <c r="F98" s="462"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6272,22 +6272,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="462" t="s">
+      <c r="B107" s="460" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="462"/>
-      <c r="D107" s="462"/>
-      <c r="E107" s="462"/>
-      <c r="F107" s="462"/>
+      <c r="C107" s="460"/>
+      <c r="D107" s="460"/>
+      <c r="E107" s="460"/>
+      <c r="F107" s="460"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="462" t="s">
+      <c r="B108" s="460" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="462"/>
-      <c r="D108" s="462"/>
-      <c r="E108" s="462"/>
-      <c r="F108" s="462"/>
+      <c r="C108" s="460"/>
+      <c r="D108" s="460"/>
+      <c r="E108" s="460"/>
+      <c r="F108" s="460"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6321,13 +6321,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="462" t="s">
+      <c r="B114" s="460" t="s">
         <v>489</v>
       </c>
-      <c r="C114" s="462"/>
-      <c r="D114" s="462"/>
-      <c r="E114" s="462"/>
-      <c r="F114" s="462"/>
+      <c r="C114" s="460"/>
+      <c r="D114" s="460"/>
+      <c r="E114" s="460"/>
+      <c r="F114" s="460"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6462,13 +6462,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="463" t="s">
+      <c r="B124" s="461" t="s">
         <v>355</v>
       </c>
-      <c r="C124" s="463"/>
-      <c r="D124" s="463"/>
-      <c r="E124" s="463"/>
-      <c r="F124" s="463"/>
+      <c r="C124" s="461"/>
+      <c r="D124" s="461"/>
+      <c r="E124" s="461"/>
+      <c r="F124" s="461"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6503,22 +6503,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="467" t="s">
+      <c r="B131" s="463" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="467"/>
-      <c r="D131" s="467"/>
-      <c r="E131" s="467"/>
-      <c r="F131" s="467"/>
+      <c r="C131" s="463"/>
+      <c r="D131" s="463"/>
+      <c r="E131" s="463"/>
+      <c r="F131" s="463"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="462" t="s">
+      <c r="B132" s="460" t="s">
         <v>357</v>
       </c>
-      <c r="C132" s="462"/>
-      <c r="D132" s="462"/>
-      <c r="E132" s="462"/>
-      <c r="F132" s="462"/>
+      <c r="C132" s="460"/>
+      <c r="D132" s="460"/>
+      <c r="E132" s="460"/>
+      <c r="F132" s="460"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6694,13 +6694,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="461" t="s">
+      <c r="B149" s="467" t="s">
         <v>358</v>
       </c>
-      <c r="C149" s="462"/>
-      <c r="D149" s="462"/>
-      <c r="E149" s="462"/>
-      <c r="F149" s="462"/>
+      <c r="C149" s="460"/>
+      <c r="D149" s="460"/>
+      <c r="E149" s="460"/>
+      <c r="F149" s="460"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6737,13 +6737,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="463" t="s">
+      <c r="B158" s="461" t="s">
         <v>436</v>
       </c>
-      <c r="C158" s="463"/>
-      <c r="D158" s="463"/>
-      <c r="E158" s="463"/>
-      <c r="F158" s="463"/>
+      <c r="C158" s="461"/>
+      <c r="D158" s="461"/>
+      <c r="E158" s="461"/>
+      <c r="F158" s="461"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6751,22 +6751,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="460" t="s">
+      <c r="B161" s="466" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="460"/>
-      <c r="D161" s="460"/>
-      <c r="E161" s="460"/>
-      <c r="F161" s="460"/>
+      <c r="C161" s="466"/>
+      <c r="D161" s="466"/>
+      <c r="E161" s="466"/>
+      <c r="F161" s="466"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="460" t="s">
+      <c r="B162" s="466" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="460"/>
-      <c r="D162" s="460"/>
-      <c r="E162" s="460"/>
-      <c r="F162" s="460"/>
+      <c r="C162" s="466"/>
+      <c r="D162" s="466"/>
+      <c r="E162" s="466"/>
+      <c r="F162" s="466"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6790,6 +6790,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6806,18 +6818,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -14008,16 +14008,16 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>2.721729172630976E-2</v>
+        <v>2.7852539062500001E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>2.721729172630976E-2</v>
+        <v>2.7852539062500001E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>4.01087890065846E-2</v>
+        <v>4.1044921875000001E-2</v>
       </c>
       <c r="I92" s="22" t="str">
         <f t="shared" si="38"/>
@@ -15228,18 +15228,18 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>7.3268664382588819E-2</v>
+        <v>7.4978743561049638E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>6.5048029410619879E-2</v>
+        <v>6.656624025330915E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>6.2627335463275854E-2</v>
+        <v>6.4089047687467551E-2</v>
       </c>
       <c r="I124" s="74" t="str">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
@@ -15285,11 +15285,11 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.1605797936778912E-2</v>
+        <v>8.3510464509717414E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.7493523382239166E-2</v>
+        <v>7.9302210109617605E-2</v>
       </c>
       <c r="I125" s="22" t="str">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -19747,7 +19747,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>104.79</v>
+        <v>102.4</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19758,7 +19758,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.11244042740653257</v>
+        <v>0.12123883246616156</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -20254,7 +20254,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>104.79</v>
+        <v>102.4</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20272,14 +20272,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>406753.70284395001</v>
+        <v>397476.65971199999</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>526</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.11244042740653257</v>
+        <v>0.12123883246616156</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20287,13 +20287,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="474" t="s">
+      <c r="B12" s="471" t="s">
         <v>495</v>
       </c>
-      <c r="C12" s="474"/>
-      <c r="D12" s="474"/>
-      <c r="E12" s="474"/>
-      <c r="F12" s="474"/>
+      <c r="C12" s="471"/>
+      <c r="D12" s="471"/>
+      <c r="E12" s="471"/>
+      <c r="F12" s="471"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20478,22 +20478,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="474" t="s">
+      <c r="B29" s="471" t="s">
         <v>496</v>
       </c>
-      <c r="C29" s="474"/>
-      <c r="D29" s="474"/>
-      <c r="E29" s="474"/>
-      <c r="F29" s="474"/>
+      <c r="C29" s="471"/>
+      <c r="D29" s="471"/>
+      <c r="E29" s="471"/>
+      <c r="F29" s="471"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="477" t="s">
+      <c r="B30" s="472" t="s">
         <v>497</v>
       </c>
-      <c r="C30" s="477"/>
-      <c r="D30" s="477"/>
-      <c r="E30" s="477"/>
-      <c r="F30" s="477"/>
+      <c r="C30" s="472"/>
+      <c r="D30" s="472"/>
+      <c r="E30" s="472"/>
+      <c r="F30" s="472"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20683,10 +20683,10 @@
       <c r="B54" s="470" t="s">
         <v>504</v>
       </c>
-      <c r="C54" s="476"/>
-      <c r="D54" s="476"/>
-      <c r="E54" s="476"/>
-      <c r="F54" s="476"/>
+      <c r="C54" s="473"/>
+      <c r="D54" s="473"/>
+      <c r="E54" s="473"/>
+      <c r="F54" s="473"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20702,22 +20702,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="474" t="s">
+      <c r="B57" s="471" t="s">
         <v>505</v>
       </c>
-      <c r="C57" s="474"/>
-      <c r="D57" s="474"/>
-      <c r="E57" s="474"/>
-      <c r="F57" s="474"/>
+      <c r="C57" s="471"/>
+      <c r="D57" s="471"/>
+      <c r="E57" s="471"/>
+      <c r="F57" s="471"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="474" t="s">
+      <c r="B58" s="471" t="s">
         <v>506</v>
       </c>
-      <c r="C58" s="474"/>
-      <c r="D58" s="474"/>
-      <c r="E58" s="474"/>
-      <c r="F58" s="474"/>
+      <c r="C58" s="471"/>
+      <c r="D58" s="471"/>
+      <c r="E58" s="471"/>
+      <c r="F58" s="471"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20751,7 +20751,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>7.3268664382588819E-2</v>
+        <v>7.4978743561049638E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20761,7 +20761,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>2.721729172630976E-2</v>
+        <v>2.7852539062500001E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>371</v>
@@ -20852,22 +20852,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="474" t="s">
+      <c r="B73" s="471" t="s">
         <v>507</v>
       </c>
-      <c r="C73" s="474"/>
-      <c r="D73" s="474"/>
-      <c r="E73" s="474"/>
-      <c r="F73" s="474"/>
+      <c r="C73" s="471"/>
+      <c r="D73" s="471"/>
+      <c r="E73" s="471"/>
+      <c r="F73" s="471"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="477" t="s">
+      <c r="B74" s="472" t="s">
         <v>477</v>
       </c>
-      <c r="C74" s="477"/>
-      <c r="D74" s="477"/>
-      <c r="E74" s="477"/>
-      <c r="F74" s="477"/>
+      <c r="C74" s="472"/>
+      <c r="D74" s="472"/>
+      <c r="E74" s="472"/>
+      <c r="F74" s="472"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -20875,13 +20875,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="474" t="s">
+      <c r="B77" s="471" t="s">
         <v>508</v>
       </c>
-      <c r="C77" s="474"/>
-      <c r="D77" s="474"/>
-      <c r="E77" s="474"/>
-      <c r="F77" s="474"/>
+      <c r="C77" s="471"/>
+      <c r="D77" s="471"/>
+      <c r="E77" s="471"/>
+      <c r="F77" s="471"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21030,33 +21030,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="474" t="s">
+      <c r="B96" s="471" t="s">
         <v>511</v>
       </c>
-      <c r="C96" s="474"/>
-      <c r="D96" s="474"/>
-      <c r="E96" s="474"/>
-      <c r="F96" s="474"/>
+      <c r="C96" s="471"/>
+      <c r="D96" s="471"/>
+      <c r="E96" s="471"/>
+      <c r="F96" s="471"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="477" t="s">
+      <c r="B97" s="472" t="s">
         <v>512</v>
       </c>
-      <c r="C97" s="477"/>
-      <c r="D97" s="477"/>
-      <c r="E97" s="477"/>
-      <c r="F97" s="477"/>
+      <c r="C97" s="472"/>
+      <c r="D97" s="472"/>
+      <c r="E97" s="472"/>
+      <c r="F97" s="472"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="477" t="s">
+      <c r="B98" s="472" t="s">
         <v>513</v>
       </c>
-      <c r="C98" s="477"/>
-      <c r="D98" s="477"/>
-      <c r="E98" s="477"/>
-      <c r="F98" s="477"/>
+      <c r="C98" s="472"/>
+      <c r="D98" s="472"/>
+      <c r="E98" s="472"/>
+      <c r="F98" s="472"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21119,23 +21119,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="474" t="s">
+      <c r="B107" s="471" t="s">
         <v>514</v>
       </c>
-      <c r="C107" s="474"/>
-      <c r="D107" s="474"/>
-      <c r="E107" s="474"/>
-      <c r="F107" s="474"/>
+      <c r="C107" s="471"/>
+      <c r="D107" s="471"/>
+      <c r="E107" s="471"/>
+      <c r="F107" s="471"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="474" t="s">
+      <c r="B108" s="471" t="s">
         <v>533</v>
       </c>
-      <c r="C108" s="474"/>
-      <c r="D108" s="474"/>
-      <c r="E108" s="474"/>
-      <c r="F108" s="474"/>
+      <c r="C108" s="471"/>
+      <c r="D108" s="471"/>
+      <c r="E108" s="471"/>
+      <c r="F108" s="471"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21179,13 +21179,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="474" t="s">
+      <c r="B114" s="471" t="s">
         <v>515</v>
       </c>
-      <c r="C114" s="474"/>
-      <c r="D114" s="474"/>
-      <c r="E114" s="474"/>
-      <c r="F114" s="474"/>
+      <c r="C114" s="471"/>
+      <c r="D114" s="471"/>
+      <c r="E114" s="471"/>
+      <c r="F114" s="471"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21349,13 +21349,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="472" t="s">
+      <c r="B127" s="475" t="s">
         <v>517</v>
       </c>
-      <c r="C127" s="472"/>
-      <c r="D127" s="472"/>
-      <c r="E127" s="472"/>
-      <c r="F127" s="472"/>
+      <c r="C127" s="475"/>
+      <c r="D127" s="475"/>
+      <c r="E127" s="475"/>
+      <c r="F127" s="475"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21368,22 +21368,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="473" t="s">
+      <c r="B131" s="476" t="s">
         <v>518</v>
       </c>
-      <c r="C131" s="473"/>
-      <c r="D131" s="473"/>
-      <c r="E131" s="473"/>
-      <c r="F131" s="473"/>
+      <c r="C131" s="476"/>
+      <c r="D131" s="476"/>
+      <c r="E131" s="476"/>
+      <c r="F131" s="476"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="474" t="s">
+      <c r="B132" s="471" t="s">
         <v>519</v>
       </c>
-      <c r="C132" s="474"/>
-      <c r="D132" s="474"/>
-      <c r="E132" s="474"/>
-      <c r="F132" s="474"/>
+      <c r="C132" s="471"/>
+      <c r="D132" s="471"/>
+      <c r="E132" s="471"/>
+      <c r="F132" s="471"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21552,13 +21552,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="475" t="s">
+      <c r="B149" s="477" t="s">
         <v>520</v>
       </c>
-      <c r="C149" s="474"/>
-      <c r="D149" s="474"/>
-      <c r="E149" s="474"/>
-      <c r="F149" s="474"/>
+      <c r="C149" s="471"/>
+      <c r="D149" s="471"/>
+      <c r="E149" s="471"/>
+      <c r="F149" s="471"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21566,13 +21566,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="476" t="s">
+      <c r="B152" s="473" t="s">
         <v>521</v>
       </c>
-      <c r="C152" s="476"/>
-      <c r="D152" s="476"/>
-      <c r="E152" s="476"/>
-      <c r="F152" s="476"/>
+      <c r="C152" s="473"/>
+      <c r="D152" s="473"/>
+      <c r="E152" s="473"/>
+      <c r="F152" s="473"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21609,22 +21609,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="471" t="s">
+      <c r="B161" s="474" t="s">
         <v>386</v>
       </c>
-      <c r="C161" s="471"/>
-      <c r="D161" s="471"/>
-      <c r="E161" s="471"/>
-      <c r="F161" s="471"/>
+      <c r="C161" s="474"/>
+      <c r="D161" s="474"/>
+      <c r="E161" s="474"/>
+      <c r="F161" s="474"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="471" t="s">
+      <c r="B162" s="474" t="s">
         <v>387</v>
       </c>
-      <c r="C162" s="471"/>
-      <c r="D162" s="471"/>
-      <c r="E162" s="471"/>
-      <c r="F162" s="471"/>
+      <c r="C162" s="474"/>
+      <c r="D162" s="474"/>
+      <c r="E162" s="474"/>
+      <c r="F162" s="474"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21648,12 +21648,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21668,15 +21671,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/000858.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/000858.SZ_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F805AA2-80BB-47CB-AD9B-D57813CCB183}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6539FA3-30D2-49FE-A0A3-CA883164FC89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4986,30 +4986,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5019,25 +5019,25 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5407,7 +5407,7 @@
         <v>348</v>
       </c>
       <c r="C8" s="47">
-        <v>102.4</v>
+        <v>101.34</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5425,14 +5425,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>397476.65971199999</v>
+        <v>393362.15522670001</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>525</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.12123883246616156</v>
+        <v>0.1662777039253833</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5440,18 +5440,18 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="460" t="s">
+      <c r="B12" s="462" t="s">
         <v>353</v>
       </c>
-      <c r="C12" s="460"/>
-      <c r="D12" s="460"/>
-      <c r="E12" s="460"/>
-      <c r="F12" s="460"/>
+      <c r="C12" s="462"/>
+      <c r="D12" s="462"/>
+      <c r="E12" s="462"/>
+      <c r="F12" s="462"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
         <f>Scenarios!B39&amp;" Valuation Conclusion"</f>
-        <v>2-stage DCF Valuation Conclusion</v>
+        <v>1-stage DCF Valuation Conclusion</v>
       </c>
       <c r="C14" s="43"/>
     </row>
@@ -5489,7 +5489,7 @@
         <v>529</v>
       </c>
       <c r="C17" s="456">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>274</v>
@@ -5505,7 +5505,7 @@
       </c>
       <c r="C18" s="252">
         <f>C125</f>
-        <v>134.70696317865062</v>
+        <v>150.70538803259237</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>345</v>
@@ -5520,7 +5520,7 @@
       </c>
       <c r="C19" s="31" t="str">
         <f>IF(Terminal_Growth&lt;2%, "Lower than Inflation rate", IF(Terminal_Growth&lt;5%, "Low growth", IF(Terminal_Growth&lt;8%, "Medium growth", "High growth")))</f>
-        <v>Low growth</v>
+        <v>Lower than Inflation rate</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>346</v>
@@ -5555,7 +5555,7 @@
       </c>
       <c r="C22" s="255">
         <f>E140</f>
-        <v>66.49378342223514</v>
+        <v>73.77572463932286</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>404</v>
@@ -5570,7 +5570,7 @@
       </c>
       <c r="C23" s="256">
         <f>E141</f>
-        <v>83.96331433949689</v>
+        <v>93.221662055898364</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>405</v>
@@ -5585,7 +5585,7 @@
       </c>
       <c r="C24" s="256">
         <f>E144</f>
-        <v>112.14039032279322</v>
+        <v>124.59667696127181</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>406</v>
@@ -5600,7 +5600,7 @@
       </c>
       <c r="C25" s="256">
         <f>E145</f>
-        <v>116.64459638273874</v>
+        <v>129.61296430141905</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>407</v>
@@ -5624,22 +5624,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="460" t="s">
+      <c r="B29" s="462" t="s">
         <v>354</v>
       </c>
-      <c r="C29" s="460"/>
-      <c r="D29" s="460"/>
-      <c r="E29" s="460"/>
-      <c r="F29" s="460"/>
+      <c r="C29" s="462"/>
+      <c r="D29" s="462"/>
+      <c r="E29" s="462"/>
+      <c r="F29" s="462"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="462" t="s">
+      <c r="B30" s="466" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="462"/>
-      <c r="D30" s="462"/>
-      <c r="E30" s="462"/>
-      <c r="F30" s="462"/>
+      <c r="C30" s="466"/>
+      <c r="D30" s="466"/>
+      <c r="E30" s="466"/>
+      <c r="F30" s="466"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5651,13 +5651,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="461" t="s">
+      <c r="B33" s="463" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="461"/>
-      <c r="D33" s="461"/>
-      <c r="E33" s="461"/>
-      <c r="F33" s="461"/>
+      <c r="C33" s="463"/>
+      <c r="D33" s="463"/>
+      <c r="E33" s="463"/>
+      <c r="F33" s="463"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5677,13 +5677,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="461" t="s">
+      <c r="B36" s="463" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="461"/>
-      <c r="D36" s="461"/>
-      <c r="E36" s="461"/>
-      <c r="F36" s="461"/>
+      <c r="C36" s="463"/>
+      <c r="D36" s="463"/>
+      <c r="E36" s="463"/>
+      <c r="F36" s="463"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5712,13 +5712,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="461" t="s">
+      <c r="B40" s="463" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="461"/>
-      <c r="D40" s="461"/>
-      <c r="E40" s="461"/>
-      <c r="F40" s="461"/>
+      <c r="C40" s="463"/>
+      <c r="D40" s="463"/>
+      <c r="E40" s="463"/>
+      <c r="F40" s="463"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5734,13 +5734,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="461" t="s">
+      <c r="B43" s="463" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="461"/>
-      <c r="D43" s="461"/>
-      <c r="E43" s="461"/>
-      <c r="F43" s="461"/>
+      <c r="C43" s="463"/>
+      <c r="D43" s="463"/>
+      <c r="E43" s="463"/>
+      <c r="F43" s="463"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5804,13 +5804,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="461" t="s">
+      <c r="B51" s="463" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="461"/>
-      <c r="D51" s="461"/>
-      <c r="E51" s="461"/>
-      <c r="F51" s="461"/>
+      <c r="C51" s="463"/>
+      <c r="D51" s="463"/>
+      <c r="E51" s="463"/>
+      <c r="F51" s="463"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5826,7 +5826,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="461" t="s">
+      <c r="B54" s="463" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="464"/>
@@ -5848,22 +5848,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="460" t="s">
+      <c r="B57" s="462" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="460"/>
-      <c r="D57" s="460"/>
-      <c r="E57" s="460"/>
-      <c r="F57" s="460"/>
+      <c r="C57" s="462"/>
+      <c r="D57" s="462"/>
+      <c r="E57" s="462"/>
+      <c r="F57" s="462"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="460" t="s">
+      <c r="B58" s="462" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="460"/>
-      <c r="D58" s="460"/>
-      <c r="E58" s="460"/>
-      <c r="F58" s="460"/>
+      <c r="C58" s="462"/>
+      <c r="D58" s="462"/>
+      <c r="E58" s="462"/>
+      <c r="F58" s="462"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>7.4978743561049638E-2</v>
+        <v>7.5763009084778787E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5907,7 +5907,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>2.7852539062500001E-2</v>
+        <v>2.8143872113676732E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>321</v>
@@ -5934,7 +5934,7 @@
       </c>
       <c r="C66" s="89">
         <f>Normalized_FCF!E119</f>
-        <v>0.25</v>
+        <v>0.28867573532952973</v>
       </c>
       <c r="D66" s="89">
         <f>Normalized_FCF!G119</f>
@@ -5948,7 +5948,7 @@
       </c>
       <c r="C67" s="263">
         <f>Normalized_FCF!E116</f>
-        <v>0.40406742273746776</v>
+        <v>0.4665778415257858</v>
       </c>
       <c r="D67" s="263">
         <f>Normalized_FCF!G116</f>
@@ -5998,13 +5998,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="460" t="s">
+      <c r="B73" s="462" t="s">
         <v>476</v>
       </c>
-      <c r="C73" s="460"/>
-      <c r="D73" s="460"/>
-      <c r="E73" s="460"/>
-      <c r="F73" s="460"/>
+      <c r="C73" s="462"/>
+      <c r="D73" s="462"/>
+      <c r="E73" s="462"/>
+      <c r="F73" s="462"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6023,13 +6023,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="460" t="s">
+      <c r="B77" s="462" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="460"/>
-      <c r="D77" s="460"/>
-      <c r="E77" s="460"/>
-      <c r="F77" s="460"/>
+      <c r="C77" s="462"/>
+      <c r="D77" s="462"/>
+      <c r="E77" s="462"/>
+      <c r="F77" s="462"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6198,31 +6198,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="460" t="s">
+      <c r="B96" s="462" t="s">
         <v>483</v>
       </c>
-      <c r="C96" s="460"/>
-      <c r="D96" s="460"/>
-      <c r="E96" s="460"/>
-      <c r="F96" s="460"/>
+      <c r="C96" s="462"/>
+      <c r="D96" s="462"/>
+      <c r="E96" s="462"/>
+      <c r="F96" s="462"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="462" t="s">
+      <c r="B97" s="466" t="s">
         <v>482</v>
       </c>
-      <c r="C97" s="462"/>
-      <c r="D97" s="462"/>
-      <c r="E97" s="462"/>
-      <c r="F97" s="462"/>
+      <c r="C97" s="466"/>
+      <c r="D97" s="466"/>
+      <c r="E97" s="466"/>
+      <c r="F97" s="466"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="462" t="s">
+      <c r="B98" s="466" t="s">
         <v>481</v>
       </c>
-      <c r="C98" s="462"/>
-      <c r="D98" s="462"/>
-      <c r="E98" s="462"/>
-      <c r="F98" s="462"/>
+      <c r="C98" s="466"/>
+      <c r="D98" s="466"/>
+      <c r="E98" s="466"/>
+      <c r="F98" s="466"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6262,7 +6262,7 @@
       </c>
       <c r="C104" s="211">
         <f>Terminal_Growth</f>
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="106" spans="2:6">
@@ -6272,22 +6272,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="460" t="s">
+      <c r="B107" s="462" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="460"/>
-      <c r="D107" s="460"/>
-      <c r="E107" s="460"/>
-      <c r="F107" s="460"/>
+      <c r="C107" s="462"/>
+      <c r="D107" s="462"/>
+      <c r="E107" s="462"/>
+      <c r="F107" s="462"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="460" t="s">
+      <c r="B108" s="462" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="460"/>
-      <c r="D108" s="460"/>
-      <c r="E108" s="460"/>
-      <c r="F108" s="460"/>
+      <c r="C108" s="462"/>
+      <c r="D108" s="462"/>
+      <c r="E108" s="462"/>
+      <c r="F108" s="462"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6313,7 +6313,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>179.64719550176477</v>
+        <v>154.55168149689248</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6321,13 +6321,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="460" t="s">
+      <c r="B114" s="462" t="s">
         <v>489</v>
       </c>
-      <c r="C114" s="460"/>
-      <c r="D114" s="460"/>
-      <c r="E114" s="460"/>
-      <c r="F114" s="460"/>
+      <c r="C114" s="462"/>
+      <c r="D114" s="462"/>
+      <c r="E114" s="462"/>
+      <c r="F114" s="462"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6354,15 +6354,15 @@
     <row r="118" spans="2:6">
       <c r="B118" s="205" t="str">
         <f>DCF!B90&amp;" ("&amp;DCF!D90&amp;"yrs)"</f>
-        <v>Snowball Scenario (5yrs)</v>
+        <v>Snowball Scenario (15yrs)</v>
       </c>
       <c r="C118" s="206">
         <f>DCF!C90</f>
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>147.07 CNY</v>
+        <v>173.41 CNY</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6370,21 +6370,21 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>-8.8861014087690589E-3</v>
+        <v>-2.847183453609721E-2</v>
       </c>
     </row>
     <row r="119" spans="2:6">
       <c r="B119" s="205" t="str">
         <f>DCF!B91&amp;" ("&amp;DCF!D91&amp;"yrs)"</f>
-        <v>Optimistic (5yrs)</v>
+        <v>Optimistic (15yrs)</v>
       </c>
       <c r="C119" s="198">
         <f>DCF!C91</f>
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>137.65 CNY</v>
+        <v>159.77 CNY</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6392,21 +6392,21 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>1.3678062151602804E-2</v>
+        <v>-1.0718128589896074E-3</v>
       </c>
     </row>
     <row r="120" spans="2:6">
       <c r="B120" s="205" t="str">
         <f>DCF!B92&amp;" ("&amp;DCF!D92&amp;"yrs)"</f>
-        <v>Base (5yrs)</v>
+        <v>Base (15yrs)</v>
       </c>
       <c r="C120" s="198">
         <f>DCF!C92</f>
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="D120" s="207" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>133.19 CNY</v>
+        <v>147.6 CNY</v>
       </c>
       <c r="E120" s="199">
         <f>DCF!F92</f>
@@ -6414,21 +6414,21 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>2.5106272015644755E-2</v>
+        <v>2.6160226066460235E-2</v>
       </c>
     </row>
     <row r="121" spans="2:6">
       <c r="B121" s="205" t="str">
         <f>DCF!B93&amp;" ("&amp;DCF!D93&amp;"yrs)"</f>
-        <v>Pessimistic (5yrs)</v>
+        <v>Pessimistic (15yrs)</v>
       </c>
       <c r="C121" s="198">
         <f>DCF!C93</f>
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>128.89 CNY</v>
+        <v>136.75 CNY</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6436,13 +6436,13 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>3.6626507210125503E-2</v>
+        <v>5.3128977754099187E-2</v>
       </c>
     </row>
     <row r="122" spans="2:6">
       <c r="B122" s="205" t="str">
         <f>DCF!B94&amp;" ("&amp;DCF!D94&amp;"yrs)"</f>
-        <v>Devil's advocate (5yrs)</v>
+        <v>Devil's advocate (15yrs)</v>
       </c>
       <c r="C122" s="198">
         <f>DCF!C94</f>
@@ -6450,7 +6450,7 @@
       </c>
       <c r="D122" s="207" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>124.75 CNY</v>
+        <v>136.75 CNY</v>
       </c>
       <c r="E122" s="199">
         <f>DCF!F94</f>
@@ -6458,17 +6458,17 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>4.823427764461069E-2</v>
+        <v>5.3128977754099187E-2</v>
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="461" t="s">
+      <c r="B124" s="463" t="s">
         <v>355</v>
       </c>
-      <c r="C124" s="461"/>
-      <c r="D124" s="461"/>
-      <c r="E124" s="461"/>
-      <c r="F124" s="461"/>
+      <c r="C124" s="463"/>
+      <c r="D124" s="463"/>
+      <c r="E124" s="463"/>
+      <c r="F124" s="463"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6476,7 +6476,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>134.70696317865062</v>
+        <v>150.70538803259237</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6503,22 +6503,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="463" t="s">
+      <c r="B131" s="467" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="463"/>
-      <c r="D131" s="463"/>
-      <c r="E131" s="463"/>
-      <c r="F131" s="463"/>
+      <c r="C131" s="467"/>
+      <c r="D131" s="467"/>
+      <c r="E131" s="467"/>
+      <c r="F131" s="467"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="460" t="s">
+      <c r="B132" s="462" t="s">
         <v>357</v>
       </c>
-      <c r="C132" s="460"/>
-      <c r="D132" s="460"/>
-      <c r="E132" s="460"/>
-      <c r="F132" s="460"/>
+      <c r="C132" s="462"/>
+      <c r="D132" s="462"/>
+      <c r="E132" s="462"/>
+      <c r="F132" s="462"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6583,11 +6583,11 @@
       </c>
       <c r="D140" s="333">
         <f>Scenarios!D62</f>
-        <v>61.314047873759939</v>
+        <v>68.595989090847667</v>
       </c>
       <c r="E140" s="334">
         <f>Scenarios!E62</f>
-        <v>66.49378342223514</v>
+        <v>73.77572463932286</v>
       </c>
       <c r="F140" s="335">
         <f>E22</f>
@@ -6604,11 +6604,11 @@
       </c>
       <c r="D141" s="333">
         <f>Scenarios!D63</f>
-        <v>77.955418506163554</v>
+        <v>87.213766222565027</v>
       </c>
       <c r="E141" s="334">
         <f>Scenarios!E63</f>
-        <v>83.96331433949689</v>
+        <v>93.221662055898364</v>
       </c>
       <c r="F141" s="335">
         <f>Scenarios!F63</f>
@@ -6651,11 +6651,11 @@
       </c>
       <c r="D144" s="333">
         <f>Scenarios!D66</f>
-        <v>104.88210938708983</v>
+        <v>117.33839602556841</v>
       </c>
       <c r="E144" s="334">
         <f>Scenarios!E66</f>
-        <v>112.14039032279322</v>
+        <v>124.59667696127181</v>
       </c>
       <c r="F144" s="335">
         <f>E24</f>
@@ -6672,11 +6672,11 @@
       </c>
       <c r="D145" s="333">
         <f>Scenarios!D67</f>
-        <v>109.19384099731857</v>
+        <v>122.16220891599889</v>
       </c>
       <c r="E145" s="334">
         <f>Scenarios!E67</f>
-        <v>116.64459638273874</v>
+        <v>129.61296430141905</v>
       </c>
       <c r="F145" s="335">
         <f>Scenarios!F67</f>
@@ -6694,13 +6694,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="467" t="s">
+      <c r="B149" s="461" t="s">
         <v>358</v>
       </c>
-      <c r="C149" s="460"/>
-      <c r="D149" s="460"/>
-      <c r="E149" s="460"/>
-      <c r="F149" s="460"/>
+      <c r="C149" s="462"/>
+      <c r="D149" s="462"/>
+      <c r="E149" s="462"/>
+      <c r="F149" s="462"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6737,13 +6737,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="461" t="s">
+      <c r="B158" s="463" t="s">
         <v>436</v>
       </c>
-      <c r="C158" s="461"/>
-      <c r="D158" s="461"/>
-      <c r="E158" s="461"/>
-      <c r="F158" s="461"/>
+      <c r="C158" s="463"/>
+      <c r="D158" s="463"/>
+      <c r="E158" s="463"/>
+      <c r="F158" s="463"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6751,22 +6751,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="466" t="s">
+      <c r="B161" s="460" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="466"/>
-      <c r="D161" s="466"/>
-      <c r="E161" s="466"/>
-      <c r="F161" s="466"/>
+      <c r="C161" s="460"/>
+      <c r="D161" s="460"/>
+      <c r="E161" s="460"/>
+      <c r="F161" s="460"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="466" t="s">
+      <c r="B162" s="460" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="466"/>
-      <c r="D162" s="466"/>
-      <c r="E162" s="466"/>
-      <c r="F162" s="466"/>
+      <c r="C162" s="460"/>
+      <c r="D162" s="460"/>
+      <c r="E162" s="460"/>
+      <c r="F162" s="460"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6790,18 +6790,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6818,6 +6806,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -14008,16 +14008,16 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>2.7852539062500001E-2</v>
+        <v>2.8143872113676732E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>2.7852539062500001E-2</v>
+        <v>2.8143872113676732E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>4.1044921875000001E-2</v>
+        <v>4.1474245115452932E-2</v>
       </c>
       <c r="I92" s="22" t="str">
         <f t="shared" si="38"/>
@@ -14819,7 +14819,7 @@
       <c r="D115" s="52"/>
       <c r="E115" s="451" t="str">
         <f>DCF!F15&amp;"yrs Projection"</f>
-        <v>3yrs Projection</v>
+        <v>16yrs Projection</v>
       </c>
       <c r="F115" s="52"/>
       <c r="G115" s="22" t="str">
@@ -14878,7 +14878,7 @@
       </c>
       <c r="E116" s="22">
         <f>E119/E117/E118</f>
-        <v>0.40406742273746776</v>
+        <v>0.4665778415257858</v>
       </c>
       <c r="G116" s="22">
         <f t="shared" ref="G116:Q116" si="44">IF(G4="","",G77)</f>
@@ -15052,7 +15052,8 @@
       </c>
       <c r="D119" s="100"/>
       <c r="E119" s="453">
-        <v>0.25</v>
+        <f>C119</f>
+        <v>0.28867573532952973</v>
       </c>
       <c r="F119" s="100"/>
       <c r="G119" s="99">
@@ -15228,18 +15229,18 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>7.4978743561049638E-2</v>
+        <v>7.5763009084778787E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>6.656624025330915E-2</v>
+        <v>6.7262512353847018E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>6.4089047687467551E-2</v>
+        <v>6.4759408754654399E-2</v>
       </c>
       <c r="I124" s="74" t="str">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
@@ -15285,11 +15286,11 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.3510464509717414E-2</v>
+        <v>8.4383970453868778E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.9302210109617605E-2</v>
+        <v>8.0131698393771877E-2</v>
       </c>
       <c r="I125" s="22" t="str">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16136,7 +16137,7 @@
       </c>
       <c r="C6" s="283">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>579016124778.08789</v>
+        <v>481605176727.18604</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -16199,7 +16200,7 @@
       </c>
       <c r="C8" s="283">
         <f>C6+C7</f>
-        <v>697319992135.45007</v>
+        <v>599909044084.54822</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -16260,7 +16261,7 @@
       </c>
       <c r="C10" s="283">
         <f>C8*Exchange_Rate</f>
-        <v>697319992135.45007</v>
+        <v>599909044084.54822</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16282,7 +16283,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>179.64719550176477</v>
+        <v>154.55168149689248</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16319,7 +16320,7 @@
       </c>
       <c r="F14" s="309" t="str">
         <f>IF(ROUND(F17,4)=ROUND(C17,4),"I","II")</f>
-        <v>II</v>
+        <v>I</v>
       </c>
       <c r="H14" s="106" t="s">
         <v>411</v>
@@ -16331,22 +16332,22 @@
       </c>
       <c r="C15" s="148">
         <f>Scenarios!C45</f>
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E15" s="308" t="str">
         <f>IF(F14="II","Change year","Terminal Year")</f>
-        <v>Change year</v>
+        <v>Terminal Year</v>
       </c>
       <c r="F15" s="310">
         <f>IF(F14="II",_xlfn.CEILING.MATH(C15/2),C15+1)</f>
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="H15" s="97" t="s">
         <v>427</v>
       </c>
       <c r="I15" s="126">
         <f>Terminal_Growth</f>
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="J15" s="126"/>
     </row>
@@ -16379,7 +16380,7 @@
       </c>
       <c r="F17" s="311">
         <f>Scenarios!C40</f>
-        <v>0.40406742273746776</v>
+        <v>0.4665778415257858</v>
       </c>
       <c r="H17" s="106" t="s">
         <v>410</v>
@@ -16405,7 +16406,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>134.89477814489302</v>
+        <v>164.84370370396726</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -16555,7 +16556,7 @@
     <row r="23" spans="1:21">
       <c r="A23" s="302" t="str">
         <f t="shared" si="0"/>
-        <v>II</v>
+        <v>I</v>
       </c>
       <c r="B23" s="117">
         <v>3</v>
@@ -16570,11 +16571,11 @@
       </c>
       <c r="E23" s="299">
         <f t="shared" si="6"/>
-        <v>0.40406742273746776</v>
+        <v>0.4665778415257858</v>
       </c>
       <c r="F23" s="277">
         <f t="shared" si="7"/>
-        <v>38673578329.929779</v>
+        <v>44656494648.866585</v>
       </c>
       <c r="G23" s="299">
         <f t="shared" si="2"/>
@@ -16582,15 +16583,15 @@
       </c>
       <c r="H23" s="277">
         <f t="shared" si="8"/>
-        <v>27499283445.102375</v>
+        <v>31986470684.304981</v>
       </c>
       <c r="I23" s="299">
         <f t="shared" si="9"/>
-        <v>-0.11977459625120046</v>
+        <v>2.3855917147759476E-2</v>
       </c>
       <c r="J23" s="299">
         <f t="shared" ref="J23:J50" si="10">IF(A23="", 0,H23/C23)</f>
-        <v>0.28731669187669412</v>
+        <v>0.33419950596793269</v>
       </c>
       <c r="K23" s="119">
         <f t="shared" si="3"/>
@@ -16598,7 +16599,7 @@
       </c>
       <c r="L23" s="277">
         <f t="shared" si="4"/>
-        <v>22290996049.420277</v>
+        <v>25928322571.827847</v>
       </c>
       <c r="N23" s="275"/>
       <c r="O23" s="275"/>
@@ -16612,7 +16613,7 @@
     <row r="24" spans="1:21">
       <c r="A24" s="302" t="str">
         <f t="shared" si="0"/>
-        <v>II</v>
+        <v>I</v>
       </c>
       <c r="B24" s="117">
         <v>4</v>
@@ -16627,11 +16628,11 @@
       </c>
       <c r="E24" s="299">
         <f t="shared" si="6"/>
-        <v>0.40406742273746776</v>
+        <v>0.4665778415257858</v>
       </c>
       <c r="F24" s="277">
         <f t="shared" si="7"/>
-        <v>39596172010.375977</v>
+        <v>45721816285.319313</v>
       </c>
       <c r="G24" s="299">
         <f t="shared" si="2"/>
@@ -16639,15 +16640,15 @@
       </c>
       <c r="H24" s="277">
         <f t="shared" si="8"/>
-        <v>28155304072.591496</v>
+        <v>32749537278.799</v>
       </c>
       <c r="I24" s="299">
         <f t="shared" si="9"/>
-        <v>2.3855917147759698E-2</v>
+        <v>2.3855917147759476E-2</v>
       </c>
       <c r="J24" s="299">
         <f t="shared" si="10"/>
-        <v>0.28731669187669417</v>
+        <v>0.33419950596793269</v>
       </c>
       <c r="K24" s="119">
         <f t="shared" si="3"/>
@@ -16655,7 +16656,7 @@
       </c>
       <c r="L24" s="277">
         <f t="shared" si="4"/>
-        <v>21279970353.674854</v>
+        <v>24752323064.691612</v>
       </c>
       <c r="N24" s="275"/>
       <c r="O24" s="275"/>
@@ -16669,7 +16670,7 @@
     <row r="25" spans="1:21">
       <c r="A25" s="302" t="str">
         <f t="shared" si="0"/>
-        <v>II</v>
+        <v>I</v>
       </c>
       <c r="B25" s="117">
         <v>5</v>
@@ -16684,11 +16685,11 @@
       </c>
       <c r="E25" s="299">
         <f t="shared" si="6"/>
-        <v>0.40406742273746776</v>
+        <v>0.4665778415257858</v>
       </c>
       <c r="F25" s="277">
         <f t="shared" si="7"/>
-        <v>40540775009.223938</v>
+        <v>46812552146.466972</v>
       </c>
       <c r="G25" s="299">
         <f t="shared" si="2"/>
@@ -16696,7 +16697,7 @@
       </c>
       <c r="H25" s="277">
         <f t="shared" si="8"/>
-        <v>28826974673.817215</v>
+        <v>33530807526.749489</v>
       </c>
       <c r="I25" s="299">
         <f t="shared" si="9"/>
@@ -16704,7 +16705,7 @@
       </c>
       <c r="J25" s="299">
         <f t="shared" si="10"/>
-        <v>0.28731669187669417</v>
+        <v>0.33419950596793269</v>
       </c>
       <c r="K25" s="119">
         <f t="shared" si="3"/>
@@ -16712,7 +16713,7 @@
       </c>
       <c r="L25" s="277">
         <f t="shared" si="4"/>
-        <v>20314800525.257717</v>
+        <v>23629661942.132843</v>
       </c>
       <c r="N25" s="275"/>
       <c r="O25" s="275"/>
@@ -16726,26 +16727,26 @@
     <row r="26" spans="1:21">
       <c r="A26" s="302" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>I</v>
       </c>
       <c r="B26" s="117">
         <v>6</v>
       </c>
       <c r="C26" s="277">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>102725213771.85764</v>
       </c>
       <c r="D26" s="299">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2.38559171477595E-2</v>
       </c>
       <c r="E26" s="299">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>0.4665778415257858</v>
       </c>
       <c r="F26" s="277">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>47929308511.948257</v>
       </c>
       <c r="G26" s="299">
         <f t="shared" si="2"/>
@@ -16753,48 +16754,48 @@
       </c>
       <c r="H26" s="277">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>34330715693.0051</v>
       </c>
       <c r="I26" s="299">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>2.3855917147759698E-2</v>
       </c>
       <c r="J26" s="299">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>0.33419950596793274</v>
       </c>
       <c r="K26" s="119">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.65707689293158289</v>
       </c>
       <c r="L26" s="277">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>22557919999.677326</v>
       </c>
     </row>
     <row r="27" spans="1:21">
       <c r="A27" s="302" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>I</v>
       </c>
       <c r="B27" s="117">
         <v>7</v>
       </c>
       <c r="C27" s="277">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>105175817960.58495</v>
       </c>
       <c r="D27" s="299">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2.38559171477595E-2</v>
       </c>
       <c r="E27" s="299">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>0.4665778415257858</v>
       </c>
       <c r="F27" s="277">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>49072706124.758698</v>
       </c>
       <c r="G27" s="299">
         <f t="shared" si="2"/>
@@ -16802,48 +16803,48 @@
       </c>
       <c r="H27" s="277">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>35149706402.200706</v>
       </c>
       <c r="I27" s="299">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>2.3855917147759254E-2</v>
       </c>
       <c r="J27" s="299">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>0.33419950596793263</v>
       </c>
       <c r="K27" s="119">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.61265910762851561</v>
       </c>
       <c r="L27" s="277">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>21534787757.776608</v>
       </c>
     </row>
     <row r="28" spans="1:21">
       <c r="A28" s="302" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>I</v>
       </c>
       <c r="B28" s="117">
         <v>8</v>
       </c>
       <c r="C28" s="277">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>107684883559.80049</v>
       </c>
       <c r="D28" s="299">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2.38559171477595E-2</v>
       </c>
       <c r="E28" s="299">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>0.4665778415257858</v>
       </c>
       <c r="F28" s="277">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>50243380536.287292</v>
       </c>
       <c r="G28" s="299">
         <f t="shared" si="2"/>
@@ -16851,48 +16852,48 @@
       </c>
       <c r="H28" s="277">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>35988234885.899681</v>
       </c>
       <c r="I28" s="299">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>2.3855917147759476E-2</v>
       </c>
       <c r="J28" s="299">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>0.33419950596793269</v>
       </c>
       <c r="K28" s="119">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.5712439231967511</v>
       </c>
       <c r="L28" s="277">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>20558060485.147514</v>
       </c>
     </row>
     <row r="29" spans="1:21">
       <c r="A29" s="302" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>I</v>
       </c>
       <c r="B29" s="117">
         <v>9</v>
       </c>
       <c r="C29" s="277">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>110253805220.06921</v>
       </c>
       <c r="D29" s="299">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2.38559171477595E-2</v>
       </c>
       <c r="E29" s="299">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>0.4665778415257858</v>
       </c>
       <c r="F29" s="277">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>51441982459.584305</v>
       </c>
       <c r="G29" s="299">
         <f t="shared" si="2"/>
@@ -16900,48 +16901,48 @@
       </c>
       <c r="H29" s="277">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>36846767235.631813</v>
       </c>
       <c r="I29" s="299">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>2.3855917147759476E-2</v>
       </c>
       <c r="J29" s="299">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>0.33419950596793274</v>
       </c>
       <c r="K29" s="119">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.53262836661701729</v>
       </c>
       <c r="L29" s="277">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>19625633447.832001</v>
       </c>
     </row>
     <row r="30" spans="1:21">
       <c r="A30" s="302" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>I</v>
       </c>
       <c r="B30" s="117">
         <v>10</v>
       </c>
       <c r="C30" s="277">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>112884010862.62439</v>
       </c>
       <c r="D30" s="299">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2.38559171477595E-2</v>
       </c>
       <c r="E30" s="299">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>0.4665778415257858</v>
       </c>
       <c r="F30" s="277">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>52669178131.056648</v>
       </c>
       <c r="G30" s="299">
         <f t="shared" si="2"/>
@@ -16949,48 +16950,48 @@
       </c>
       <c r="H30" s="277">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>37725780661.967819</v>
       </c>
       <c r="I30" s="299">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>2.3855917147759254E-2</v>
       </c>
       <c r="J30" s="299">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>0.33419950596793269</v>
       </c>
       <c r="K30" s="119">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.49662318565689262</v>
       </c>
       <c r="L30" s="277">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>18735497373.739655</v>
       </c>
     </row>
     <row r="31" spans="1:21">
       <c r="A31" s="302" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>I</v>
       </c>
       <c r="B31" s="117">
         <v>11</v>
       </c>
       <c r="C31" s="277">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>115576962473.06993</v>
       </c>
       <c r="D31" s="299">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2.38559171477595E-2</v>
       </c>
       <c r="E31" s="299">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>0.4665778415257858</v>
       </c>
       <c r="F31" s="277">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>53925649680.791718</v>
       </c>
       <c r="G31" s="299">
         <f t="shared" si="2"/>
@@ -16998,48 +16999,48 @@
       </c>
       <c r="H31" s="277">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>38625763759.774269</v>
       </c>
       <c r="I31" s="299">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>2.3855917147759476E-2</v>
       </c>
       <c r="J31" s="299">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>0.33419950596793269</v>
       </c>
       <c r="K31" s="119">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.46305192135840806</v>
       </c>
       <c r="L31" s="277">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>17885734122.899445</v>
       </c>
     </row>
     <row r="32" spans="1:21">
       <c r="A32" s="302" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>I</v>
       </c>
       <c r="B32" s="117">
         <v>12</v>
       </c>
       <c r="C32" s="277">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>118334156914.0172</v>
       </c>
       <c r="D32" s="299">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2.38559171477595E-2</v>
       </c>
       <c r="E32" s="299">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>0.4665778415257858</v>
       </c>
       <c r="F32" s="277">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>55212095511.715782</v>
       </c>
       <c r="G32" s="299">
         <f t="shared" si="2"/>
@@ -17047,48 +17048,48 @@
       </c>
       <c r="H32" s="277">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>39547216779.796371</v>
       </c>
       <c r="I32" s="299">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>2.3855917147759476E-2</v>
       </c>
       <c r="J32" s="299">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>0.33419950596793269</v>
       </c>
       <c r="K32" s="119">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.43175004322462285</v>
       </c>
       <c r="L32" s="277">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>17074512554.090614</v>
       </c>
     </row>
     <row r="33" spans="1:21">
       <c r="A33" s="302" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>I</v>
       </c>
       <c r="B33" s="117">
         <v>13</v>
       </c>
       <c r="C33" s="277">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>121157126757.10796</v>
       </c>
       <c r="D33" s="299">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2.38559171477595E-2</v>
       </c>
       <c r="E33" s="299">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>0.4665778415257858</v>
       </c>
       <c r="F33" s="277">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>56529230687.797455</v>
       </c>
       <c r="G33" s="299">
         <f t="shared" si="2"/>
@@ -17096,23 +17097,23 @@
       </c>
       <c r="H33" s="277">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>40490651906.719673</v>
       </c>
       <c r="I33" s="299">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>2.3855917147759476E-2</v>
       </c>
       <c r="J33" s="299">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>0.33419950596793263</v>
       </c>
       <c r="K33" s="119">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.40256414286678116</v>
       </c>
       <c r="L33" s="277">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>16300084578.945803</v>
       </c>
       <c r="N33" s="275"/>
       <c r="O33" s="275"/>
@@ -17126,26 +17127,26 @@
     <row r="34" spans="1:21">
       <c r="A34" s="302" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>I</v>
       </c>
       <c r="B34" s="117">
         <v>14</v>
       </c>
       <c r="C34" s="277">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>124047441134.88611</v>
       </c>
       <c r="D34" s="299">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2.38559171477595E-2</v>
       </c>
       <c r="E34" s="299">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>0.4665778415257858</v>
       </c>
       <c r="F34" s="277">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>57877787331.512131</v>
       </c>
       <c r="G34" s="299">
         <f t="shared" si="2"/>
@@ -17153,23 +17154,23 @@
       </c>
       <c r="H34" s="277">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>41456593543.865143</v>
       </c>
       <c r="I34" s="299">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>2.3855917147759476E-2</v>
       </c>
       <c r="J34" s="299">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>0.33419950596793263</v>
       </c>
       <c r="K34" s="119">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.37535118216016894</v>
       </c>
       <c r="L34" s="277">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>15560781395.023409</v>
       </c>
       <c r="N34" s="275"/>
       <c r="O34" s="275"/>
@@ -17183,26 +17184,26 @@
     <row r="35" spans="1:21">
       <c r="A35" s="302" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>I</v>
       </c>
       <c r="B35" s="117">
         <v>15</v>
       </c>
       <c r="C35" s="277">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>127006706612.99152</v>
       </c>
       <c r="D35" s="299">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2.38559171477595E-2</v>
       </c>
       <c r="E35" s="299">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>0.4665778415257858</v>
       </c>
       <c r="F35" s="277">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>59258515030.78833</v>
       </c>
       <c r="G35" s="299">
         <f t="shared" si="2"/>
@@ -17210,23 +17211,23 @@
       </c>
       <c r="H35" s="277">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>42445578604.675934</v>
       </c>
       <c r="I35" s="299">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>2.3855917147759476E-2</v>
       </c>
       <c r="J35" s="299">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>0.33419950596793269</v>
       </c>
       <c r="K35" s="119">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.34997779222393377</v>
       </c>
       <c r="L35" s="277">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>14855009889.731922</v>
       </c>
       <c r="N35" s="275"/>
       <c r="O35" s="275"/>
@@ -18010,23 +18011,23 @@
       </c>
       <c r="B51" s="316">
         <f>C15+1</f>
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C51" s="277">
         <f>VLOOKUP(C15,B21:C50,2,FALSE)*(1+Terminal_Growth)</f>
-        <v>102338343015.2832</v>
+        <v>128276773679.12143</v>
       </c>
       <c r="D51" s="301">
         <f>Terminal_Growth</f>
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="E51" s="301">
         <f>F17</f>
-        <v>0.40406742273746776</v>
+        <v>0.4665778415257858</v>
       </c>
       <c r="F51" s="277">
         <f>C51*E51</f>
-        <v>41351590509.408417</v>
+        <v>59851100181.096207</v>
       </c>
       <c r="G51" s="299">
         <f>F18</f>
@@ -18034,20 +18035,20 @@
       </c>
       <c r="H51" s="277">
         <f>(F51*(1-$I$10)+C51*(G51-$I$9))/Equity_Cost</f>
-        <v>405565712652.32501</v>
+        <v>591310819182.38208</v>
       </c>
       <c r="I51" s="415">
         <f>(F51*(1-$I$10)+C51*(G51-$I$9))/VLOOKUP(C15,B21:H50,COLUMN(H20)-1,FALSE)-1</f>
-        <v>2.0000000000000018E-2</v>
+        <v>1.0000000000000009E-2</v>
       </c>
       <c r="J51" s="454"/>
       <c r="K51" s="119">
         <f>1/(1+Equity_Cost)^C15</f>
-        <v>0.70471496766912267</v>
+        <v>0.34997779222393377</v>
       </c>
       <c r="L51" s="277">
         <f t="shared" si="4"/>
-        <v>285808228079.48792</v>
+        <v>206945655015.57578</v>
       </c>
     </row>
     <row r="52" spans="1:21" ht="13.15">
@@ -18060,7 +18061,7 @@
       <c r="K52" s="468"/>
       <c r="L52" s="317">
         <f>SUM(L21:L51)</f>
-        <v>405304783322.55359</v>
+        <v>521554772513.8053</v>
       </c>
     </row>
     <row r="53" spans="1:21">
@@ -18084,7 +18085,7 @@
     <row r="55" spans="1:21" ht="13.15">
       <c r="A55" s="125">
         <f>L52</f>
-        <v>405304783322.55359</v>
+        <v>521554772513.8053</v>
       </c>
       <c r="B55" s="123">
         <f>C94</f>
@@ -18092,19 +18093,19 @@
       </c>
       <c r="C55" s="123">
         <f>C93</f>
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="D55" s="123">
         <f>C92</f>
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="E55" s="123">
         <f>C91</f>
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="F55" s="123">
         <f>C90</f>
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="G55" s="123"/>
       <c r="H55" s="123"/>
@@ -18119,19 +18120,19 @@
       </c>
       <c r="B56" s="118">
         <f t="dataTable" ref="B56:F69" dt2D="1" dtr="1" r1="C16" r2="C15"/>
-        <v>363888618175.51416</v>
+        <v>414898999560.84106</v>
       </c>
       <c r="C56" s="118">
-        <v>367527504357.26935</v>
+        <v>414898999560.84106</v>
       </c>
       <c r="D56" s="118">
-        <v>371166390539.02448</v>
+        <v>419047989556.44952</v>
       </c>
       <c r="E56" s="118">
-        <v>374805276720.77954</v>
+        <v>423196979552.05792</v>
       </c>
       <c r="F56" s="118">
-        <v>382083049084.29004</v>
+        <v>427345969547.66632</v>
       </c>
       <c r="G56" s="295"/>
       <c r="H56" s="295"/>
@@ -18145,19 +18146,19 @@
         <v>2</v>
       </c>
       <c r="B57" s="118">
-        <v>363443125838.77289</v>
+        <v>414639906853.97644</v>
       </c>
       <c r="C57" s="118">
-        <v>370467676970.73877</v>
+        <v>414639906853.97644</v>
       </c>
       <c r="D57" s="118">
-        <v>377559359189.31018</v>
+        <v>422693513284.34796</v>
       </c>
       <c r="E57" s="118">
-        <v>384718172494.48706</v>
+        <v>430824490157.52802</v>
       </c>
       <c r="F57" s="118">
-        <v>399237192364.65747</v>
+        <v>439032837473.5166</v>
       </c>
       <c r="G57" s="295"/>
       <c r="H57" s="295"/>
@@ -18171,19 +18172,19 @@
         <v>3</v>
       </c>
       <c r="B58" s="118">
-        <v>363027748368.6178</v>
+        <v>414398328572.51758</v>
       </c>
       <c r="C58" s="118">
-        <v>373236510853.81952</v>
+        <v>414398328572.51758</v>
       </c>
       <c r="D58" s="118">
-        <v>383639385318.25305</v>
+        <v>426126593904.55994</v>
       </c>
       <c r="E58" s="118">
-        <v>394238249554.55103</v>
+        <v>438078626117.97498</v>
       </c>
       <c r="F58" s="118">
-        <v>416031458513.26886</v>
+        <v>450256589420.95306</v>
       </c>
       <c r="G58" s="295"/>
       <c r="H58" s="295"/>
@@ -18197,19 +18198,19 @@
         <v>4</v>
       </c>
       <c r="B59" s="118">
-        <v>362640450028.14679</v>
+        <v>414173080757.63745</v>
       </c>
       <c r="C59" s="118">
-        <v>375843990781.0097</v>
+        <v>414173080757.63745</v>
       </c>
       <c r="D59" s="118">
-        <v>389421787790.53448</v>
+        <v>429359611551.56616</v>
       </c>
       <c r="E59" s="118">
-        <v>403381074143.70337</v>
+        <v>444977664513.92444</v>
       </c>
       <c r="F59" s="118">
-        <v>432473397400.02124</v>
+        <v>461035577305.20441</v>
       </c>
       <c r="G59" s="295"/>
       <c r="H59" s="295"/>
@@ -18223,19 +18224,19 @@
         <v>5</v>
       </c>
       <c r="B60" s="118">
-        <v>365913986543.77197</v>
+        <v>413963059485.02197</v>
       </c>
       <c r="C60" s="118">
-        <v>382007230055.26251</v>
+        <v>413963059485.02197</v>
       </c>
       <c r="D60" s="118">
-        <v>398702629461.25385</v>
+        <v>432404224906.78882</v>
       </c>
       <c r="E60" s="118">
-        <v>416017599929.38422</v>
+        <v>451538987743.63879</v>
       </c>
       <c r="F60" s="118">
-        <v>452577606374.89362</v>
+        <v>471387425809.42725</v>
       </c>
       <c r="G60" s="295"/>
       <c r="H60" s="295"/>
@@ -18249,19 +18250,19 @@
         <v>6</v>
       </c>
       <c r="B61" s="118">
-        <v>365577280405.0564</v>
+        <v>413767235454.61133</v>
       </c>
       <c r="C61" s="118">
-        <v>384319662849.02185</v>
+        <v>413767235454.61133</v>
       </c>
       <c r="D61" s="118">
-        <v>403932778423.41907</v>
+        <v>435271413241.31073</v>
       </c>
       <c r="E61" s="118">
-        <v>424450175372.14453</v>
+        <v>457779127318.75165</v>
       </c>
       <c r="F61" s="118">
-        <v>468336910114.9469</v>
+        <v>481329061202.76001</v>
       </c>
       <c r="G61" s="295"/>
       <c r="H61" s="295"/>
@@ -18275,19 +18276,19 @@
         <v>7</v>
       </c>
       <c r="B62" s="118">
-        <v>368652289925.50586</v>
+        <v>413584648946.06995</v>
       </c>
       <c r="C62" s="118">
-        <v>389988981839.59094</v>
+        <v>413584648946.06995</v>
       </c>
       <c r="D62" s="118">
-        <v>412503291881.33997</v>
+        <v>437971516008.55304</v>
       </c>
       <c r="E62" s="118">
-        <v>436251795048.53979</v>
+        <v>463713805516.06189</v>
       </c>
       <c r="F62" s="118">
-        <v>487688737704.19141</v>
+        <v>490876739016.40375</v>
       </c>
       <c r="G62" s="295"/>
       <c r="H62" s="295"/>
@@ -18301,19 +18302,19 @@
         <v>8</v>
       </c>
       <c r="B63" s="118">
-        <v>368359567205.05505</v>
+        <v>413414405115.26208</v>
       </c>
       <c r="C63" s="118">
-        <v>392039753302.83142</v>
+        <v>413414405115.26208</v>
       </c>
       <c r="D63" s="118">
-        <v>417233930797.87415</v>
+        <v>440514270129.68542</v>
       </c>
       <c r="E63" s="118">
-        <v>444029296181.20013</v>
+        <v>469357974990.42676</v>
       </c>
       <c r="F63" s="118">
-        <v>502793747890.75513</v>
+        <v>500046070622.97992</v>
       </c>
       <c r="G63" s="295"/>
       <c r="H63" s="295"/>
@@ -18327,19 +18328,19 @@
         <v>9</v>
       </c>
       <c r="B64" s="118">
-        <v>371246496732.03137</v>
+        <v>413255669608.68127</v>
       </c>
       <c r="C64" s="118">
-        <v>397259183572.31592</v>
+        <v>413255669608.68127</v>
       </c>
       <c r="D64" s="118">
-        <v>425153338894.80774</v>
+        <v>442908845106.22974</v>
       </c>
       <c r="E64" s="118">
-        <v>455055053261.43237</v>
+        <v>474725856448.56396</v>
       </c>
       <c r="F64" s="118">
-        <v>521422704757.4303</v>
+        <v>508852048762.62878</v>
       </c>
       <c r="G64" s="295"/>
       <c r="H64" s="295"/>
@@ -18353,19 +18354,19 @@
         <v>10</v>
       </c>
       <c r="B65" s="118">
-        <v>370992011941.83716</v>
+        <v>413107664474.34033</v>
       </c>
       <c r="C65" s="118">
-        <v>399077901766.32843</v>
+        <v>413107664474.34033</v>
       </c>
       <c r="D65" s="118">
-        <v>429432173918.53589</v>
+        <v>445163876086.47198</v>
       </c>
       <c r="E65" s="118">
-        <v>462228368730.60657</v>
+        <v>479830974478.68054</v>
       </c>
       <c r="F65" s="118">
-        <v>535900586299.64014</v>
+        <v>517309072057.58295</v>
       </c>
       <c r="G65" s="295"/>
       <c r="H65" s="295"/>
@@ -18379,19 +18380,19 @@
         <v>15</v>
       </c>
       <c r="B66" s="118">
-        <v>378210273252.08185</v>
+        <v>412504854807.04333</v>
       </c>
       <c r="C66" s="277">
-        <v>415458765979.00354</v>
+        <v>412504854807.04333</v>
       </c>
       <c r="D66" s="118">
-        <v>457171048062.15704</v>
+        <v>454614471400.29492</v>
       </c>
       <c r="E66" s="118">
-        <v>503895675228.34998</v>
+        <v>501843901830.70947</v>
       </c>
       <c r="F66" s="118">
-        <v>614905238311.41565</v>
+        <v>554825118771.83691</v>
       </c>
       <c r="G66" s="295"/>
       <c r="H66" s="295"/>
@@ -18414,19 +18415,19 @@
         <v>20</v>
       </c>
       <c r="B67" s="118">
-        <v>382094893839.24988</v>
+        <v>412080045811.84357</v>
       </c>
       <c r="C67" s="277">
-        <v>426125688068.81348</v>
+        <v>412080045811.84357</v>
       </c>
       <c r="D67" s="118">
-        <v>476985784771.55322</v>
+        <v>461614173079.27698</v>
       </c>
       <c r="E67" s="118">
-        <v>535823261004.99988</v>
+        <v>518971330001.22839</v>
       </c>
       <c r="F67" s="118">
-        <v>683011489752.96399</v>
+        <v>585474145452.20325</v>
       </c>
       <c r="G67" s="295"/>
       <c r="H67" s="295"/>
@@ -18449,19 +18450,19 @@
         <v>25</v>
       </c>
       <c r="B68" s="118">
-        <v>387397395746.58539</v>
+        <v>411780676554.52576</v>
       </c>
       <c r="C68" s="277">
-        <v>436794323999.78656</v>
+        <v>411780676554.52576</v>
       </c>
       <c r="D68" s="118">
-        <v>495382376022.05774</v>
+        <v>466798589718.41498</v>
       </c>
       <c r="E68" s="118">
-        <v>565105188820.07056</v>
+        <v>532297535600.55981</v>
       </c>
       <c r="F68" s="118">
-        <v>747921340602.3208</v>
+        <v>610513106609.50757</v>
       </c>
       <c r="G68" s="295"/>
       <c r="H68" s="295"/>
@@ -18484,19 +18485,19 @@
         <v>30</v>
       </c>
       <c r="B69" s="118">
-        <v>390286942551.47412</v>
+        <v>411569706558.034</v>
       </c>
       <c r="C69" s="277">
-        <v>443610541832.98694</v>
+        <v>411569706558.034</v>
       </c>
       <c r="D69" s="118">
-        <v>508320584123.45398</v>
+        <v>470638492777.26648</v>
       </c>
       <c r="E69" s="118">
-        <v>587301182779.15784</v>
+        <v>542666153346.76239</v>
       </c>
       <c r="F69" s="118">
-        <v>803647417523.41626</v>
+        <v>630968881025.2937</v>
       </c>
       <c r="G69" s="295"/>
       <c r="H69" s="295"/>
@@ -18566,19 +18567,19 @@
       </c>
       <c r="C72" s="124">
         <f>C55</f>
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="D72" s="124">
         <f>D55</f>
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="E72" s="124">
         <f>E55</f>
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="F72" s="124">
         <f>F55</f>
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="G72" s="124"/>
       <c r="H72" s="124"/>
@@ -18593,23 +18594,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>179.64719550176477</v>
+        <v>154.55168149689248</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>179.64719550176477</v>
+        <v>154.55168149689248</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>179.64719550176477</v>
+        <v>154.55168149689248</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>179.64719550176477</v>
+        <v>154.55168149689248</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>179.64719550176477</v>
+        <v>154.55168149689248</v>
       </c>
       <c r="G73" s="296"/>
       <c r="H73" s="296"/>
@@ -18624,23 +18625,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>124.22493072761385</v>
+        <v>137.36648992669296</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>125.16239947177036</v>
+        <v>137.36648992669296</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>126.09986821592685</v>
+        <v>138.43537426284027</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>127.03733696008332</v>
+        <v>139.50425859898755</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>128.91227444839637</v>
+        <v>140.57314293513483</v>
       </c>
       <c r="G74" s="296"/>
       <c r="H74" s="296"/>
@@ -18655,23 +18656,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>124.11016067969365</v>
+        <v>137.29974111884559</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>125.91986200010452</v>
+        <v>137.29974111884559</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>127.74685797946061</v>
+        <v>139.3745530060834</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>129.59114861776192</v>
+        <v>141.46929746835428</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>133.3316138712002</v>
+        <v>143.5839745056582</v>
       </c>
       <c r="G75" s="296"/>
       <c r="H75" s="296"/>
@@ -18686,23 +18687,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>124.00314898000114</v>
+        <v>137.23750446817203</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>126.63318335545883</v>
+        <v>137.23750446817203</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>129.31322586645771</v>
+        <v>140.25900105333335</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>132.04376027968163</v>
+        <v>143.33814562383591</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>137.65823987953959</v>
+        <v>146.47549573422609</v>
       </c>
       <c r="G76" s="296"/>
       <c r="H76" s="296"/>
@@ -18717,23 +18718,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>123.90337117143002</v>
+        <v>137.17947495705448</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>127.30493586726101</v>
+        <v>137.17947495705448</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>130.8029184023431</v>
+        <v>141.09190783908855</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>134.39918220208472</v>
+        <v>145.11551170177646</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>141.89409751008162</v>
+        <v>149.25243453648707</v>
       </c>
       <c r="G77" s="296"/>
       <c r="H77" s="296"/>
@@ -18748,23 +18749,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>124.74671663841393</v>
+        <v>137.12536818678171</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>128.8927415566335</v>
+        <v>137.12536818678171</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>133.19389700161545</v>
+        <v>141.87627693336617</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>137.65466955923245</v>
+        <v>146.80587384583183</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>147.07344816810163</v>
+        <v>151.919331474789</v>
       </c>
       <c r="G78" s="296"/>
       <c r="H78" s="296"/>
@@ -18779,23 +18780,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>124.65997265543527</v>
+        <v>137.07491898373019</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>129.48848249461091</v>
+        <v>137.07491898373019</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>134.54131512199962</v>
+        <v>142.61493687296561</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>139.8271134103112</v>
+        <v>148.41349098982855</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>151.13344178923833</v>
+        <v>154.4805471824356</v>
       </c>
       <c r="G79" s="296"/>
       <c r="H79" s="296"/>
@@ -18811,23 +18812,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>125.45217256755635</v>
+        <v>137.02788009976607</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>130.94904187702826</v>
+        <v>137.02788009976607</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>136.74929528044967</v>
+        <v>143.31055136153947</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>142.86750792237765</v>
+        <v>149.94241358831493</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>156.11896004979349</v>
+        <v>156.94026949374194</v>
       </c>
       <c r="G80" s="296"/>
       <c r="H80" s="296"/>
@@ -18842,23 +18843,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>125.37675982106732</v>
+        <v>136.98402100049881</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>131.47737226500121</v>
+        <v>136.98402100049881</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>137.96802703039469</v>
+        <v>143.96562887525465</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>144.87118812981797</v>
+        <v>151.39649382184047</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>160.01039116986192</v>
+        <v>159.30252029154659</v>
       </c>
       <c r="G81" s="296"/>
       <c r="H81" s="296"/>
@@ -18874,23 +18875,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>126.12050558912469</v>
+        <v>136.94312673544775</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>132.82202898014637</v>
+        <v>136.94312673544775</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>140.00826604647574</v>
+        <v>144.58253170868343</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>147.71170089309277</v>
+        <v>152.77939530267588</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>164.80967972313127</v>
+        <v>161.5711620833776</v>
       </c>
       <c r="G82" s="296"/>
       <c r="H82" s="296"/>
@@ -18906,23 +18907,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>126.05494389668526</v>
+        <v>136.90499688458434</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>133.29057660053201</v>
+        <v>136.90499688458434</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>141.11060173266983</v>
+        <v>145.16348449354413</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>149.55972765415007</v>
+        <v>154.09460230542851</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>168.53954670701023</v>
+        <v>163.7499043170242</v>
       </c>
       <c r="G83" s="296"/>
       <c r="H83" s="296"/>
@@ -18938,23 +18939,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>127.91454983859043</v>
+        <v>136.74969792948104</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>137.51069985655747</v>
+        <v>136.74969792948104</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>148.25683445578099</v>
+        <v>147.59819590738326</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>160.29427540963457</v>
+        <v>159.7656868981214</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>188.89313519662784</v>
+        <v>173.41498298182717</v>
       </c>
       <c r="G84" s="296"/>
       <c r="H84" s="296"/>
@@ -18970,23 +18971,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>128.91532595564402</v>
+        <v>136.64025643135642</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>140.25876768722702</v>
+        <v>136.64025643135642</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>153.36160976639252</v>
+        <v>149.40149538274645</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>168.51962576328262</v>
+        <v>164.17814383567321</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>206.43902116806515</v>
+        <v>181.31094430530098</v>
       </c>
       <c r="G85" s="296"/>
       <c r="H85" s="296"/>
@@ -19002,23 +19003,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>130.28138401727858</v>
+        <v>136.56313136954384</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>143.00727704655196</v>
+        <v>136.56313136954384</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>158.10103508363409</v>
+        <v>150.73713170471916</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>176.06338798176319</v>
+        <v>167.61131008588848</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>223.1614338294531</v>
+        <v>187.76161143218525</v>
       </c>
       <c r="G86" s="296"/>
       <c r="H86" s="296"/>
@@ -19034,23 +19035,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>131.02580406205556</v>
+        <v>136.50878018410214</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>144.76330646127394</v>
+        <v>136.50878018410214</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>161.43424340470366</v>
+        <v>151.72638746004148</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>181.78163514389186</v>
+        <v>170.28252720334254</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>237.51787498716746</v>
+        <v>193.03153420373675</v>
       </c>
       <c r="G87" s="296"/>
       <c r="H87" s="296"/>
@@ -19089,15 +19090,15 @@
       </c>
       <c r="C90" s="130">
         <f>Scenarios!C29</f>
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="D90" s="133">
         <f>Scenarios!D29</f>
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>147.07344816810163</v>
+        <v>173.41498298182717</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19117,15 +19118,15 @@
       </c>
       <c r="C91" s="130">
         <f>Scenarios!C22</f>
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="D91" s="133">
         <f>Scenarios!D22</f>
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>137.65466955923245</v>
+        <v>159.7656868981214</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19145,15 +19146,15 @@
       </c>
       <c r="C92" s="130">
         <f>Scenarios!C23</f>
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="D92" s="133">
         <f>Scenarios!D23</f>
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>133.19389700161545</v>
+        <v>147.59819590738326</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19173,15 +19174,15 @@
       </c>
       <c r="C93" s="130">
         <f>Scenarios!C24</f>
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="D93" s="133">
         <f>Scenarios!D24</f>
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>128.8927415566335</v>
+        <v>136.74969792948104</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19205,11 +19206,11 @@
       </c>
       <c r="D94" s="133">
         <f>Scenarios!D30</f>
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>124.74671663841393</v>
+        <v>136.74969792948104</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19517,7 +19518,7 @@
         <v>111</v>
       </c>
       <c r="C18" s="137">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E18" s="450" t="s">
         <v>541</v>
@@ -19561,15 +19562,15 @@
         <v>443</v>
       </c>
       <c r="C22" s="324">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="D22" s="325">
         <f>C18</f>
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E22" s="326">
         <f>DCF!E91</f>
-        <v>137.65466955923245</v>
+        <v>159.7656868981214</v>
       </c>
       <c r="F22" s="328">
         <f>1-F23-F24</f>
@@ -19585,15 +19586,15 @@
         <v>435</v>
       </c>
       <c r="C23" s="324">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="D23" s="325">
         <f>C18</f>
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E23" s="326">
         <f>DCF!E92</f>
-        <v>133.19389700161545</v>
+        <v>147.59819590738326</v>
       </c>
       <c r="F23" s="327">
         <v>0.55000000000000004</v>
@@ -19608,15 +19609,15 @@
         <v>444</v>
       </c>
       <c r="C24" s="324">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="D24" s="325">
         <f>C18</f>
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E24" s="326">
         <f>DCF!E93</f>
-        <v>128.8927415566335</v>
+        <v>136.74969792948104</v>
       </c>
       <c r="F24" s="327">
         <v>0.25</v>
@@ -19632,7 +19633,7 @@
       </c>
       <c r="C25" s="441">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>133.01076265189337</v>
+        <v>147.31956961105533</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19671,15 +19672,15 @@
         <v>442</v>
       </c>
       <c r="C29" s="324">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="D29" s="325">
         <f>C18</f>
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E29" s="326">
         <f>DCF!E90</f>
-        <v>147.07344816810163</v>
+        <v>173.41498298182717</v>
       </c>
       <c r="F29" s="327">
         <v>0.15</v>
@@ -19698,11 +19699,11 @@
       </c>
       <c r="D30" s="325">
         <f>C18</f>
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E30" s="326">
         <f>DCF!E94</f>
-        <v>124.74671663841393</v>
+        <v>136.74969792948104</v>
       </c>
       <c r="F30" s="327">
         <v>0.05</v>
@@ -19747,7 +19748,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>102.4</v>
+        <v>101.34</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19758,7 +19759,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.12123883246616156</v>
+        <v>0.1662777039253833</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19767,7 +19768,7 @@
       </c>
       <c r="C35" s="320">
         <f>DCF!C11</f>
-        <v>179.64719550176477</v>
+        <v>154.55168149689248</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19778,7 +19779,7 @@
       </c>
       <c r="F35" s="330">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>-7.3996144898412761E-2</v>
+        <v>1.0242821335361347E-2</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19787,7 +19788,7 @@
       </c>
       <c r="C36" s="321">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>134.70696317865062</v>
+        <v>150.70538803259237</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -19813,7 +19814,7 @@
     <row r="39" spans="2:7" ht="13.15">
       <c r="B39" s="414" t="str">
         <f>IF(DCF!F14="II","2","1")&amp;"-stage DCF"</f>
-        <v>2-stage DCF</v>
+        <v>1-stage DCF</v>
       </c>
       <c r="E39" s="222" t="s">
         <v>251</v>
@@ -19825,7 +19826,7 @@
       </c>
       <c r="C40" s="126">
         <f>Normalized_FCF!E116</f>
-        <v>0.40406742273746776</v>
+        <v>0.4665778415257858</v>
       </c>
       <c r="E40" s="97" t="s">
         <v>399</v>
@@ -19865,7 +19866,7 @@
       </c>
       <c r="C45" s="150">
         <f>C18</f>
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D45" s="137"/>
       <c r="E45" s="221" t="s">
@@ -19890,7 +19891,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>134.89477814489302</v>
+        <v>164.84370370396726</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -19957,7 +19958,7 @@
       </c>
       <c r="F53" s="249">
         <f>BS!D89/C36</f>
-        <v>0.2262544978580209</v>
+        <v>0.20223600967321193</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -20035,11 +20036,11 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>61.314047873759939</v>
+        <v>68.595989090847667</v>
       </c>
       <c r="E62" s="332">
         <f>C62+D62</f>
-        <v>66.49378342223514</v>
+        <v>73.77572463932286</v>
       </c>
       <c r="F62" s="301">
         <f>Thesis!E22</f>
@@ -20047,7 +20048,7 @@
       </c>
       <c r="G62" s="440">
         <f>(1-E62/C36)</f>
-        <v>0.50638198758849629</v>
+        <v>0.51046392167897991</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20060,11 +20061,11 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>77.955418506163554</v>
+        <v>87.213766222565027</v>
       </c>
       <c r="E63" s="332">
         <f>C63+D63</f>
-        <v>83.96331433949689</v>
+        <v>93.221662055898364</v>
       </c>
       <c r="F63" s="301">
         <f>Thesis!E23</f>
@@ -20072,7 +20073,7 @@
       </c>
       <c r="G63" s="440">
         <f>(1-E63/C36)</f>
-        <v>0.37669655407387259</v>
+        <v>0.38143112683046387</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20106,11 +20107,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>104.88210938708983</v>
+        <v>117.33839602556841</v>
       </c>
       <c r="E66" s="332">
         <f>C66+D66</f>
-        <v>112.14039032279322</v>
+        <v>124.59667696127181</v>
       </c>
       <c r="F66" s="301">
         <f>Thesis!E24</f>
@@ -20118,7 +20119,7 @@
       </c>
       <c r="G66" s="440">
         <f>(1-E66/C36)</f>
-        <v>0.16752343251869795</v>
+        <v>0.1732433817540362</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20131,11 +20132,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>109.19384099731857</v>
+        <v>122.16220891599889</v>
       </c>
       <c r="E67" s="332">
         <f>C67+D67</f>
-        <v>116.64459638273874</v>
+        <v>129.61296430141905</v>
       </c>
       <c r="F67" s="301">
         <f>Thesis!E25</f>
@@ -20143,7 +20144,7 @@
       </c>
       <c r="G67" s="440">
         <f>(1-E67/C36)</f>
-        <v>0.13408636324135137</v>
+        <v>0.13995799358289529</v>
       </c>
     </row>
   </sheetData>
@@ -20254,7 +20255,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>102.4</v>
+        <v>101.34</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20272,14 +20273,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>397476.65971199999</v>
+        <v>393362.15522670001</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>526</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.12123883246616156</v>
+        <v>0.1662777039253833</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20287,13 +20288,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="471" t="s">
+      <c r="B12" s="474" t="s">
         <v>495</v>
       </c>
-      <c r="C12" s="471"/>
-      <c r="D12" s="471"/>
-      <c r="E12" s="471"/>
-      <c r="F12" s="471"/>
+      <c r="C12" s="474"/>
+      <c r="D12" s="474"/>
+      <c r="E12" s="474"/>
+      <c r="F12" s="474"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20340,7 +20341,7 @@
       </c>
       <c r="C17" s="424">
         <f>Terminal_Growth</f>
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="D17" s="351" t="s">
         <v>337</v>
@@ -20357,7 +20358,7 @@
       </c>
       <c r="C18" s="359">
         <f>C125</f>
-        <v>134.70696317865062</v>
+        <v>150.70538803259237</v>
       </c>
       <c r="D18" s="350" t="s">
         <v>360</v>
@@ -20409,7 +20410,7 @@
       </c>
       <c r="C22" s="364">
         <f>E140</f>
-        <v>66.49378342223514</v>
+        <v>73.77572463932286</v>
       </c>
       <c r="D22" s="365" t="s">
         <v>438</v>
@@ -20425,7 +20426,7 @@
       </c>
       <c r="C23" s="367">
         <f>E141</f>
-        <v>83.96331433949689</v>
+        <v>93.221662055898364</v>
       </c>
       <c r="D23" s="365" t="s">
         <v>439</v>
@@ -20441,7 +20442,7 @@
       </c>
       <c r="C24" s="367">
         <f>E144</f>
-        <v>112.14039032279322</v>
+        <v>124.59667696127181</v>
       </c>
       <c r="D24" s="365" t="s">
         <v>441</v>
@@ -20457,7 +20458,7 @@
       </c>
       <c r="C25" s="367">
         <f>E145</f>
-        <v>116.64459638273874</v>
+        <v>129.61296430141905</v>
       </c>
       <c r="D25" s="365" t="s">
         <v>440</v>
@@ -20478,22 +20479,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="471" t="s">
+      <c r="B29" s="474" t="s">
         <v>496</v>
       </c>
-      <c r="C29" s="471"/>
-      <c r="D29" s="471"/>
-      <c r="E29" s="471"/>
-      <c r="F29" s="471"/>
+      <c r="C29" s="474"/>
+      <c r="D29" s="474"/>
+      <c r="E29" s="474"/>
+      <c r="F29" s="474"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="472" t="s">
+      <c r="B30" s="477" t="s">
         <v>497</v>
       </c>
-      <c r="C30" s="472"/>
-      <c r="D30" s="472"/>
-      <c r="E30" s="472"/>
-      <c r="F30" s="472"/>
+      <c r="C30" s="477"/>
+      <c r="D30" s="477"/>
+      <c r="E30" s="477"/>
+      <c r="F30" s="477"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20683,10 +20684,10 @@
       <c r="B54" s="470" t="s">
         <v>504</v>
       </c>
-      <c r="C54" s="473"/>
-      <c r="D54" s="473"/>
-      <c r="E54" s="473"/>
-      <c r="F54" s="473"/>
+      <c r="C54" s="476"/>
+      <c r="D54" s="476"/>
+      <c r="E54" s="476"/>
+      <c r="F54" s="476"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20702,22 +20703,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="471" t="s">
+      <c r="B57" s="474" t="s">
         <v>505</v>
       </c>
-      <c r="C57" s="471"/>
-      <c r="D57" s="471"/>
-      <c r="E57" s="471"/>
-      <c r="F57" s="471"/>
+      <c r="C57" s="474"/>
+      <c r="D57" s="474"/>
+      <c r="E57" s="474"/>
+      <c r="F57" s="474"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="471" t="s">
+      <c r="B58" s="474" t="s">
         <v>506</v>
       </c>
-      <c r="C58" s="471"/>
-      <c r="D58" s="471"/>
-      <c r="E58" s="471"/>
-      <c r="F58" s="471"/>
+      <c r="C58" s="474"/>
+      <c r="D58" s="474"/>
+      <c r="E58" s="474"/>
+      <c r="F58" s="474"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20751,7 +20752,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>7.4978743561049638E-2</v>
+        <v>7.5763009084778787E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20761,7 +20762,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>2.7852539062500001E-2</v>
+        <v>2.8143872113676732E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>371</v>
@@ -20788,7 +20789,7 @@
       </c>
       <c r="C66" s="378">
         <f>Normalized_FCF!E119</f>
-        <v>0.25</v>
+        <v>0.28867573532952973</v>
       </c>
       <c r="D66" s="378">
         <f>Normalized_FCF!G119</f>
@@ -20802,7 +20803,7 @@
       </c>
       <c r="C67" s="383">
         <f>Normalized_FCF!E116</f>
-        <v>0.40406742273746776</v>
+        <v>0.4665778415257858</v>
       </c>
       <c r="D67" s="383">
         <f>Normalized_FCF!G116</f>
@@ -20852,22 +20853,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="471" t="s">
+      <c r="B73" s="474" t="s">
         <v>507</v>
       </c>
-      <c r="C73" s="471"/>
-      <c r="D73" s="471"/>
-      <c r="E73" s="471"/>
-      <c r="F73" s="471"/>
+      <c r="C73" s="474"/>
+      <c r="D73" s="474"/>
+      <c r="E73" s="474"/>
+      <c r="F73" s="474"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="472" t="s">
+      <c r="B74" s="477" t="s">
         <v>477</v>
       </c>
-      <c r="C74" s="472"/>
-      <c r="D74" s="472"/>
-      <c r="E74" s="472"/>
-      <c r="F74" s="472"/>
+      <c r="C74" s="477"/>
+      <c r="D74" s="477"/>
+      <c r="E74" s="477"/>
+      <c r="F74" s="477"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -20875,13 +20876,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="471" t="s">
+      <c r="B77" s="474" t="s">
         <v>508</v>
       </c>
-      <c r="C77" s="471"/>
-      <c r="D77" s="471"/>
-      <c r="E77" s="471"/>
-      <c r="F77" s="471"/>
+      <c r="C77" s="474"/>
+      <c r="D77" s="474"/>
+      <c r="E77" s="474"/>
+      <c r="F77" s="474"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21030,33 +21031,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="471" t="s">
+      <c r="B96" s="474" t="s">
         <v>511</v>
       </c>
-      <c r="C96" s="471"/>
-      <c r="D96" s="471"/>
-      <c r="E96" s="471"/>
-      <c r="F96" s="471"/>
+      <c r="C96" s="474"/>
+      <c r="D96" s="474"/>
+      <c r="E96" s="474"/>
+      <c r="F96" s="474"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="472" t="s">
+      <c r="B97" s="477" t="s">
         <v>512</v>
       </c>
-      <c r="C97" s="472"/>
-      <c r="D97" s="472"/>
-      <c r="E97" s="472"/>
-      <c r="F97" s="472"/>
+      <c r="C97" s="477"/>
+      <c r="D97" s="477"/>
+      <c r="E97" s="477"/>
+      <c r="F97" s="477"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="472" t="s">
+      <c r="B98" s="477" t="s">
         <v>513</v>
       </c>
-      <c r="C98" s="472"/>
-      <c r="D98" s="472"/>
-      <c r="E98" s="472"/>
-      <c r="F98" s="472"/>
+      <c r="C98" s="477"/>
+      <c r="D98" s="477"/>
+      <c r="E98" s="477"/>
+      <c r="F98" s="477"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21119,23 +21120,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="471" t="s">
+      <c r="B107" s="474" t="s">
         <v>514</v>
       </c>
-      <c r="C107" s="471"/>
-      <c r="D107" s="471"/>
-      <c r="E107" s="471"/>
-      <c r="F107" s="471"/>
+      <c r="C107" s="474"/>
+      <c r="D107" s="474"/>
+      <c r="E107" s="474"/>
+      <c r="F107" s="474"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="471" t="s">
+      <c r="B108" s="474" t="s">
         <v>533</v>
       </c>
-      <c r="C108" s="471"/>
-      <c r="D108" s="471"/>
-      <c r="E108" s="471"/>
-      <c r="F108" s="471"/>
+      <c r="C108" s="474"/>
+      <c r="D108" s="474"/>
+      <c r="E108" s="474"/>
+      <c r="F108" s="474"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21167,7 +21168,7 @@
       </c>
       <c r="C112" s="394">
         <f>DCF!C11</f>
-        <v>179.64719550176477</v>
+        <v>154.55168149689248</v>
       </c>
       <c r="D112" s="343" t="str">
         <f>Market_currency</f>
@@ -21179,13 +21180,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="471" t="s">
+      <c r="B114" s="474" t="s">
         <v>515</v>
       </c>
-      <c r="C114" s="471"/>
-      <c r="D114" s="471"/>
-      <c r="E114" s="471"/>
-      <c r="F114" s="471"/>
+      <c r="C114" s="474"/>
+      <c r="D114" s="474"/>
+      <c r="E114" s="474"/>
+      <c r="F114" s="474"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21222,15 +21223,15 @@
       </c>
       <c r="C118" s="396">
         <f>DCF!C90</f>
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="D118" s="397">
         <f>DCF!D90</f>
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E118" s="398" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>147.07 CNY</v>
+        <v>173.41 CNY</v>
       </c>
       <c r="F118" s="399">
         <f>DCF!F90</f>
@@ -21245,15 +21246,15 @@
       </c>
       <c r="C119" s="401">
         <f>DCF!C91</f>
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="D119" s="402">
         <f>DCF!D91</f>
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E119" s="398" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>137.65 CNY</v>
+        <v>159.77 CNY</v>
       </c>
       <c r="F119" s="403">
         <f>DCF!F91</f>
@@ -21267,15 +21268,15 @@
       </c>
       <c r="C120" s="401">
         <f>DCF!C92</f>
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="D120" s="402">
         <f>DCF!D92</f>
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E120" s="398" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>133.19 CNY</v>
+        <v>147.6 CNY</v>
       </c>
       <c r="F120" s="403">
         <f>DCF!F92</f>
@@ -21289,15 +21290,15 @@
       </c>
       <c r="C121" s="401">
         <f>DCF!C93</f>
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="D121" s="402">
         <f>DCF!D93</f>
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E121" s="398" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>128.89 CNY</v>
+        <v>136.75 CNY</v>
       </c>
       <c r="F121" s="403">
         <f>DCF!F93</f>
@@ -21315,11 +21316,11 @@
       </c>
       <c r="D122" s="402">
         <f>DCF!D94</f>
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E122" s="398" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>124.75 CNY</v>
+        <v>136.75 CNY</v>
       </c>
       <c r="F122" s="403">
         <f>DCF!F94</f>
@@ -21341,7 +21342,7 @@
       </c>
       <c r="C125" s="404">
         <f>Scenarios!C36</f>
-        <v>134.70696317865062</v>
+        <v>150.70538803259237</v>
       </c>
       <c r="D125" s="343" t="str">
         <f>Market_currency</f>
@@ -21349,13 +21350,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="475" t="s">
+      <c r="B127" s="472" t="s">
         <v>517</v>
       </c>
-      <c r="C127" s="475"/>
-      <c r="D127" s="475"/>
-      <c r="E127" s="475"/>
-      <c r="F127" s="475"/>
+      <c r="C127" s="472"/>
+      <c r="D127" s="472"/>
+      <c r="E127" s="472"/>
+      <c r="F127" s="472"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21368,22 +21369,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="476" t="s">
+      <c r="B131" s="473" t="s">
         <v>518</v>
       </c>
-      <c r="C131" s="476"/>
-      <c r="D131" s="476"/>
-      <c r="E131" s="476"/>
-      <c r="F131" s="476"/>
+      <c r="C131" s="473"/>
+      <c r="D131" s="473"/>
+      <c r="E131" s="473"/>
+      <c r="F131" s="473"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="471" t="s">
+      <c r="B132" s="474" t="s">
         <v>519</v>
       </c>
-      <c r="C132" s="471"/>
-      <c r="D132" s="471"/>
-      <c r="E132" s="471"/>
-      <c r="F132" s="471"/>
+      <c r="C132" s="474"/>
+      <c r="D132" s="474"/>
+      <c r="E132" s="474"/>
+      <c r="F132" s="474"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21448,11 +21449,11 @@
       </c>
       <c r="D140" s="409">
         <f>Scenarios!D62</f>
-        <v>61.314047873759939</v>
+        <v>68.595989090847667</v>
       </c>
       <c r="E140" s="410">
         <f>Scenarios!E62</f>
-        <v>66.49378342223514</v>
+        <v>73.77572463932286</v>
       </c>
       <c r="F140" s="411">
         <f>E22</f>
@@ -21469,11 +21470,11 @@
       </c>
       <c r="D141" s="409">
         <f>Scenarios!D63</f>
-        <v>77.955418506163554</v>
+        <v>87.213766222565027</v>
       </c>
       <c r="E141" s="410">
         <f>Scenarios!E63</f>
-        <v>83.96331433949689</v>
+        <v>93.221662055898364</v>
       </c>
       <c r="F141" s="411">
         <f>Scenarios!F63</f>
@@ -21509,11 +21510,11 @@
       </c>
       <c r="D144" s="409">
         <f>Scenarios!D66</f>
-        <v>104.88210938708983</v>
+        <v>117.33839602556841</v>
       </c>
       <c r="E144" s="410">
         <f>Scenarios!E66</f>
-        <v>112.14039032279322</v>
+        <v>124.59667696127181</v>
       </c>
       <c r="F144" s="411">
         <f>E24</f>
@@ -21530,11 +21531,11 @@
       </c>
       <c r="D145" s="409">
         <f>Scenarios!D67</f>
-        <v>109.19384099731857</v>
+        <v>122.16220891599889</v>
       </c>
       <c r="E145" s="410">
         <f>Scenarios!E67</f>
-        <v>116.64459638273874</v>
+        <v>129.61296430141905</v>
       </c>
       <c r="F145" s="411">
         <f>Scenarios!F67</f>
@@ -21552,13 +21553,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="477" t="s">
+      <c r="B149" s="475" t="s">
         <v>520</v>
       </c>
-      <c r="C149" s="471"/>
-      <c r="D149" s="471"/>
-      <c r="E149" s="471"/>
-      <c r="F149" s="471"/>
+      <c r="C149" s="474"/>
+      <c r="D149" s="474"/>
+      <c r="E149" s="474"/>
+      <c r="F149" s="474"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21566,13 +21567,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="473" t="s">
+      <c r="B152" s="476" t="s">
         <v>521</v>
       </c>
-      <c r="C152" s="473"/>
-      <c r="D152" s="473"/>
-      <c r="E152" s="473"/>
-      <c r="F152" s="473"/>
+      <c r="C152" s="476"/>
+      <c r="D152" s="476"/>
+      <c r="E152" s="476"/>
+      <c r="F152" s="476"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21609,22 +21610,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="474" t="s">
+      <c r="B161" s="471" t="s">
         <v>386</v>
       </c>
-      <c r="C161" s="474"/>
-      <c r="D161" s="474"/>
-      <c r="E161" s="474"/>
-      <c r="F161" s="474"/>
+      <c r="C161" s="471"/>
+      <c r="D161" s="471"/>
+      <c r="E161" s="471"/>
+      <c r="F161" s="471"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="474" t="s">
+      <c r="B162" s="471" t="s">
         <v>387</v>
       </c>
-      <c r="C162" s="474"/>
-      <c r="D162" s="474"/>
-      <c r="E162" s="474"/>
-      <c r="F162" s="474"/>
+      <c r="C162" s="471"/>
+      <c r="D162" s="471"/>
+      <c r="E162" s="471"/>
+      <c r="F162" s="471"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21648,15 +21649,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21671,12 +21669,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/000858.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/000858.SZ_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6539FA3-30D2-49FE-A0A3-CA883164FC89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EA97C9C-E348-4E40-8D1D-45E1FBC34033}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/financial_models/opportunities/000858.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/000858.SZ_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EA97C9C-E348-4E40-8D1D-45E1FBC34033}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6BE1F9F-16D4-4CBC-882B-FC7C27FC78F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4986,30 +4986,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5019,6 +5019,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5028,16 +5037,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5407,7 +5407,7 @@
         <v>348</v>
       </c>
       <c r="C8" s="47">
-        <v>101.34</v>
+        <v>102.45</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5425,14 +5425,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>393362.15522670001</v>
+        <v>397670.74011224997</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>525</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.1662777039253833</v>
+        <v>0.16195140985561304</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5440,13 +5440,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="462" t="s">
+      <c r="B12" s="460" t="s">
         <v>353</v>
       </c>
-      <c r="C12" s="462"/>
-      <c r="D12" s="462"/>
-      <c r="E12" s="462"/>
-      <c r="F12" s="462"/>
+      <c r="C12" s="460"/>
+      <c r="D12" s="460"/>
+      <c r="E12" s="460"/>
+      <c r="F12" s="460"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5624,22 +5624,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="462" t="s">
+      <c r="B29" s="460" t="s">
         <v>354</v>
       </c>
-      <c r="C29" s="462"/>
-      <c r="D29" s="462"/>
-      <c r="E29" s="462"/>
-      <c r="F29" s="462"/>
+      <c r="C29" s="460"/>
+      <c r="D29" s="460"/>
+      <c r="E29" s="460"/>
+      <c r="F29" s="460"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="466" t="s">
+      <c r="B30" s="462" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="466"/>
-      <c r="D30" s="466"/>
-      <c r="E30" s="466"/>
-      <c r="F30" s="466"/>
+      <c r="C30" s="462"/>
+      <c r="D30" s="462"/>
+      <c r="E30" s="462"/>
+      <c r="F30" s="462"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5651,13 +5651,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="463" t="s">
+      <c r="B33" s="461" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="463"/>
-      <c r="D33" s="463"/>
-      <c r="E33" s="463"/>
-      <c r="F33" s="463"/>
+      <c r="C33" s="461"/>
+      <c r="D33" s="461"/>
+      <c r="E33" s="461"/>
+      <c r="F33" s="461"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5677,13 +5677,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="463" t="s">
+      <c r="B36" s="461" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="463"/>
-      <c r="D36" s="463"/>
-      <c r="E36" s="463"/>
-      <c r="F36" s="463"/>
+      <c r="C36" s="461"/>
+      <c r="D36" s="461"/>
+      <c r="E36" s="461"/>
+      <c r="F36" s="461"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5712,13 +5712,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="463" t="s">
+      <c r="B40" s="461" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="463"/>
-      <c r="D40" s="463"/>
-      <c r="E40" s="463"/>
-      <c r="F40" s="463"/>
+      <c r="C40" s="461"/>
+      <c r="D40" s="461"/>
+      <c r="E40" s="461"/>
+      <c r="F40" s="461"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5734,13 +5734,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="463" t="s">
+      <c r="B43" s="461" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="463"/>
-      <c r="D43" s="463"/>
-      <c r="E43" s="463"/>
-      <c r="F43" s="463"/>
+      <c r="C43" s="461"/>
+      <c r="D43" s="461"/>
+      <c r="E43" s="461"/>
+      <c r="F43" s="461"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5804,13 +5804,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="463" t="s">
+      <c r="B51" s="461" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="463"/>
-      <c r="D51" s="463"/>
-      <c r="E51" s="463"/>
-      <c r="F51" s="463"/>
+      <c r="C51" s="461"/>
+      <c r="D51" s="461"/>
+      <c r="E51" s="461"/>
+      <c r="F51" s="461"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5826,7 +5826,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="463" t="s">
+      <c r="B54" s="461" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="464"/>
@@ -5848,22 +5848,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="462" t="s">
+      <c r="B57" s="460" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="462"/>
-      <c r="D57" s="462"/>
-      <c r="E57" s="462"/>
-      <c r="F57" s="462"/>
+      <c r="C57" s="460"/>
+      <c r="D57" s="460"/>
+      <c r="E57" s="460"/>
+      <c r="F57" s="460"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="462" t="s">
+      <c r="B58" s="460" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="462"/>
-      <c r="D58" s="462"/>
-      <c r="E58" s="462"/>
-      <c r="F58" s="462"/>
+      <c r="C58" s="460"/>
+      <c r="D58" s="460"/>
+      <c r="E58" s="460"/>
+      <c r="F58" s="460"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>7.5763009084778787E-2</v>
+        <v>7.4942150714021299E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5907,7 +5907,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>2.8143872113676732E-2</v>
+        <v>2.7838945827232797E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>321</v>
@@ -5998,13 +5998,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="462" t="s">
+      <c r="B73" s="460" t="s">
         <v>476</v>
       </c>
-      <c r="C73" s="462"/>
-      <c r="D73" s="462"/>
-      <c r="E73" s="462"/>
-      <c r="F73" s="462"/>
+      <c r="C73" s="460"/>
+      <c r="D73" s="460"/>
+      <c r="E73" s="460"/>
+      <c r="F73" s="460"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6023,13 +6023,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="462" t="s">
+      <c r="B77" s="460" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="462"/>
-      <c r="D77" s="462"/>
-      <c r="E77" s="462"/>
-      <c r="F77" s="462"/>
+      <c r="C77" s="460"/>
+      <c r="D77" s="460"/>
+      <c r="E77" s="460"/>
+      <c r="F77" s="460"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6198,31 +6198,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="462" t="s">
+      <c r="B96" s="460" t="s">
         <v>483</v>
       </c>
-      <c r="C96" s="462"/>
-      <c r="D96" s="462"/>
-      <c r="E96" s="462"/>
-      <c r="F96" s="462"/>
+      <c r="C96" s="460"/>
+      <c r="D96" s="460"/>
+      <c r="E96" s="460"/>
+      <c r="F96" s="460"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="466" t="s">
+      <c r="B97" s="462" t="s">
         <v>482</v>
       </c>
-      <c r="C97" s="466"/>
-      <c r="D97" s="466"/>
-      <c r="E97" s="466"/>
-      <c r="F97" s="466"/>
+      <c r="C97" s="462"/>
+      <c r="D97" s="462"/>
+      <c r="E97" s="462"/>
+      <c r="F97" s="462"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="466" t="s">
+      <c r="B98" s="462" t="s">
         <v>481</v>
       </c>
-      <c r="C98" s="466"/>
-      <c r="D98" s="466"/>
-      <c r="E98" s="466"/>
-      <c r="F98" s="466"/>
+      <c r="C98" s="462"/>
+      <c r="D98" s="462"/>
+      <c r="E98" s="462"/>
+      <c r="F98" s="462"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6272,22 +6272,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="462" t="s">
+      <c r="B107" s="460" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="462"/>
-      <c r="D107" s="462"/>
-      <c r="E107" s="462"/>
-      <c r="F107" s="462"/>
+      <c r="C107" s="460"/>
+      <c r="D107" s="460"/>
+      <c r="E107" s="460"/>
+      <c r="F107" s="460"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="462" t="s">
+      <c r="B108" s="460" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="462"/>
-      <c r="D108" s="462"/>
-      <c r="E108" s="462"/>
-      <c r="F108" s="462"/>
+      <c r="C108" s="460"/>
+      <c r="D108" s="460"/>
+      <c r="E108" s="460"/>
+      <c r="F108" s="460"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6321,13 +6321,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="462" t="s">
+      <c r="B114" s="460" t="s">
         <v>489</v>
       </c>
-      <c r="C114" s="462"/>
-      <c r="D114" s="462"/>
-      <c r="E114" s="462"/>
-      <c r="F114" s="462"/>
+      <c r="C114" s="460"/>
+      <c r="D114" s="460"/>
+      <c r="E114" s="460"/>
+      <c r="F114" s="460"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6462,13 +6462,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="463" t="s">
+      <c r="B124" s="461" t="s">
         <v>355</v>
       </c>
-      <c r="C124" s="463"/>
-      <c r="D124" s="463"/>
-      <c r="E124" s="463"/>
-      <c r="F124" s="463"/>
+      <c r="C124" s="461"/>
+      <c r="D124" s="461"/>
+      <c r="E124" s="461"/>
+      <c r="F124" s="461"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6503,22 +6503,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="467" t="s">
+      <c r="B131" s="463" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="467"/>
-      <c r="D131" s="467"/>
-      <c r="E131" s="467"/>
-      <c r="F131" s="467"/>
+      <c r="C131" s="463"/>
+      <c r="D131" s="463"/>
+      <c r="E131" s="463"/>
+      <c r="F131" s="463"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="462" t="s">
+      <c r="B132" s="460" t="s">
         <v>357</v>
       </c>
-      <c r="C132" s="462"/>
-      <c r="D132" s="462"/>
-      <c r="E132" s="462"/>
-      <c r="F132" s="462"/>
+      <c r="C132" s="460"/>
+      <c r="D132" s="460"/>
+      <c r="E132" s="460"/>
+      <c r="F132" s="460"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6694,13 +6694,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="461" t="s">
+      <c r="B149" s="467" t="s">
         <v>358</v>
       </c>
-      <c r="C149" s="462"/>
-      <c r="D149" s="462"/>
-      <c r="E149" s="462"/>
-      <c r="F149" s="462"/>
+      <c r="C149" s="460"/>
+      <c r="D149" s="460"/>
+      <c r="E149" s="460"/>
+      <c r="F149" s="460"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6737,13 +6737,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="463" t="s">
+      <c r="B158" s="461" t="s">
         <v>436</v>
       </c>
-      <c r="C158" s="463"/>
-      <c r="D158" s="463"/>
-      <c r="E158" s="463"/>
-      <c r="F158" s="463"/>
+      <c r="C158" s="461"/>
+      <c r="D158" s="461"/>
+      <c r="E158" s="461"/>
+      <c r="F158" s="461"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6751,22 +6751,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="460" t="s">
+      <c r="B161" s="466" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="460"/>
-      <c r="D161" s="460"/>
-      <c r="E161" s="460"/>
-      <c r="F161" s="460"/>
+      <c r="C161" s="466"/>
+      <c r="D161" s="466"/>
+      <c r="E161" s="466"/>
+      <c r="F161" s="466"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="460" t="s">
+      <c r="B162" s="466" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="460"/>
-      <c r="D162" s="460"/>
-      <c r="E162" s="460"/>
-      <c r="F162" s="460"/>
+      <c r="C162" s="466"/>
+      <c r="D162" s="466"/>
+      <c r="E162" s="466"/>
+      <c r="F162" s="466"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6790,6 +6790,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6806,18 +6818,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -14008,16 +14008,16 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>2.8143872113676732E-2</v>
+        <v>2.7838945827232797E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>2.8143872113676732E-2</v>
+        <v>2.7838945827232797E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>4.1474245115452932E-2</v>
+        <v>4.1024890190336755E-2</v>
       </c>
       <c r="I92" s="22" t="str">
         <f t="shared" si="38"/>
@@ -15229,18 +15229,18 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>7.5763009084778787E-2</v>
+        <v>7.4942150714021299E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>6.7262512353847018E-2</v>
+        <v>6.6533753069193333E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>6.4759408754654399E-2</v>
+        <v>6.4057769479713783E-2</v>
       </c>
       <c r="I124" s="74" t="str">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
@@ -15286,11 +15286,11 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.4383970453868778E-2</v>
+        <v>8.3469707816447664E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.0131698393771877E-2</v>
+        <v>7.9263507225230276E-2</v>
       </c>
       <c r="I125" s="22" t="str">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -19748,7 +19748,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>101.34</v>
+        <v>102.45</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19759,7 +19759,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.1662777039253833</v>
+        <v>0.16195140985561304</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -20255,7 +20255,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>101.34</v>
+        <v>102.45</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20273,14 +20273,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>393362.15522670001</v>
+        <v>397670.74011224997</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>526</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.1662777039253833</v>
+        <v>0.16195140985561304</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20288,13 +20288,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="474" t="s">
+      <c r="B12" s="471" t="s">
         <v>495</v>
       </c>
-      <c r="C12" s="474"/>
-      <c r="D12" s="474"/>
-      <c r="E12" s="474"/>
-      <c r="F12" s="474"/>
+      <c r="C12" s="471"/>
+      <c r="D12" s="471"/>
+      <c r="E12" s="471"/>
+      <c r="F12" s="471"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20479,22 +20479,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="474" t="s">
+      <c r="B29" s="471" t="s">
         <v>496</v>
       </c>
-      <c r="C29" s="474"/>
-      <c r="D29" s="474"/>
-      <c r="E29" s="474"/>
-      <c r="F29" s="474"/>
+      <c r="C29" s="471"/>
+      <c r="D29" s="471"/>
+      <c r="E29" s="471"/>
+      <c r="F29" s="471"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="477" t="s">
+      <c r="B30" s="472" t="s">
         <v>497</v>
       </c>
-      <c r="C30" s="477"/>
-      <c r="D30" s="477"/>
-      <c r="E30" s="477"/>
-      <c r="F30" s="477"/>
+      <c r="C30" s="472"/>
+      <c r="D30" s="472"/>
+      <c r="E30" s="472"/>
+      <c r="F30" s="472"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20684,10 +20684,10 @@
       <c r="B54" s="470" t="s">
         <v>504</v>
       </c>
-      <c r="C54" s="476"/>
-      <c r="D54" s="476"/>
-      <c r="E54" s="476"/>
-      <c r="F54" s="476"/>
+      <c r="C54" s="473"/>
+      <c r="D54" s="473"/>
+      <c r="E54" s="473"/>
+      <c r="F54" s="473"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20703,22 +20703,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="474" t="s">
+      <c r="B57" s="471" t="s">
         <v>505</v>
       </c>
-      <c r="C57" s="474"/>
-      <c r="D57" s="474"/>
-      <c r="E57" s="474"/>
-      <c r="F57" s="474"/>
+      <c r="C57" s="471"/>
+      <c r="D57" s="471"/>
+      <c r="E57" s="471"/>
+      <c r="F57" s="471"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="474" t="s">
+      <c r="B58" s="471" t="s">
         <v>506</v>
       </c>
-      <c r="C58" s="474"/>
-      <c r="D58" s="474"/>
-      <c r="E58" s="474"/>
-      <c r="F58" s="474"/>
+      <c r="C58" s="471"/>
+      <c r="D58" s="471"/>
+      <c r="E58" s="471"/>
+      <c r="F58" s="471"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20752,7 +20752,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>7.5763009084778787E-2</v>
+        <v>7.4942150714021299E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20762,7 +20762,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>2.8143872113676732E-2</v>
+        <v>2.7838945827232797E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>371</v>
@@ -20853,22 +20853,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="474" t="s">
+      <c r="B73" s="471" t="s">
         <v>507</v>
       </c>
-      <c r="C73" s="474"/>
-      <c r="D73" s="474"/>
-      <c r="E73" s="474"/>
-      <c r="F73" s="474"/>
+      <c r="C73" s="471"/>
+      <c r="D73" s="471"/>
+      <c r="E73" s="471"/>
+      <c r="F73" s="471"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="477" t="s">
+      <c r="B74" s="472" t="s">
         <v>477</v>
       </c>
-      <c r="C74" s="477"/>
-      <c r="D74" s="477"/>
-      <c r="E74" s="477"/>
-      <c r="F74" s="477"/>
+      <c r="C74" s="472"/>
+      <c r="D74" s="472"/>
+      <c r="E74" s="472"/>
+      <c r="F74" s="472"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -20876,13 +20876,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="474" t="s">
+      <c r="B77" s="471" t="s">
         <v>508</v>
       </c>
-      <c r="C77" s="474"/>
-      <c r="D77" s="474"/>
-      <c r="E77" s="474"/>
-      <c r="F77" s="474"/>
+      <c r="C77" s="471"/>
+      <c r="D77" s="471"/>
+      <c r="E77" s="471"/>
+      <c r="F77" s="471"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21031,33 +21031,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="474" t="s">
+      <c r="B96" s="471" t="s">
         <v>511</v>
       </c>
-      <c r="C96" s="474"/>
-      <c r="D96" s="474"/>
-      <c r="E96" s="474"/>
-      <c r="F96" s="474"/>
+      <c r="C96" s="471"/>
+      <c r="D96" s="471"/>
+      <c r="E96" s="471"/>
+      <c r="F96" s="471"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="477" t="s">
+      <c r="B97" s="472" t="s">
         <v>512</v>
       </c>
-      <c r="C97" s="477"/>
-      <c r="D97" s="477"/>
-      <c r="E97" s="477"/>
-      <c r="F97" s="477"/>
+      <c r="C97" s="472"/>
+      <c r="D97" s="472"/>
+      <c r="E97" s="472"/>
+      <c r="F97" s="472"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="477" t="s">
+      <c r="B98" s="472" t="s">
         <v>513</v>
       </c>
-      <c r="C98" s="477"/>
-      <c r="D98" s="477"/>
-      <c r="E98" s="477"/>
-      <c r="F98" s="477"/>
+      <c r="C98" s="472"/>
+      <c r="D98" s="472"/>
+      <c r="E98" s="472"/>
+      <c r="F98" s="472"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21120,23 +21120,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="474" t="s">
+      <c r="B107" s="471" t="s">
         <v>514</v>
       </c>
-      <c r="C107" s="474"/>
-      <c r="D107" s="474"/>
-      <c r="E107" s="474"/>
-      <c r="F107" s="474"/>
+      <c r="C107" s="471"/>
+      <c r="D107" s="471"/>
+      <c r="E107" s="471"/>
+      <c r="F107" s="471"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="474" t="s">
+      <c r="B108" s="471" t="s">
         <v>533</v>
       </c>
-      <c r="C108" s="474"/>
-      <c r="D108" s="474"/>
-      <c r="E108" s="474"/>
-      <c r="F108" s="474"/>
+      <c r="C108" s="471"/>
+      <c r="D108" s="471"/>
+      <c r="E108" s="471"/>
+      <c r="F108" s="471"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21180,13 +21180,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="474" t="s">
+      <c r="B114" s="471" t="s">
         <v>515</v>
       </c>
-      <c r="C114" s="474"/>
-      <c r="D114" s="474"/>
-      <c r="E114" s="474"/>
-      <c r="F114" s="474"/>
+      <c r="C114" s="471"/>
+      <c r="D114" s="471"/>
+      <c r="E114" s="471"/>
+      <c r="F114" s="471"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21350,13 +21350,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="472" t="s">
+      <c r="B127" s="475" t="s">
         <v>517</v>
       </c>
-      <c r="C127" s="472"/>
-      <c r="D127" s="472"/>
-      <c r="E127" s="472"/>
-      <c r="F127" s="472"/>
+      <c r="C127" s="475"/>
+      <c r="D127" s="475"/>
+      <c r="E127" s="475"/>
+      <c r="F127" s="475"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21369,22 +21369,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="473" t="s">
+      <c r="B131" s="476" t="s">
         <v>518</v>
       </c>
-      <c r="C131" s="473"/>
-      <c r="D131" s="473"/>
-      <c r="E131" s="473"/>
-      <c r="F131" s="473"/>
+      <c r="C131" s="476"/>
+      <c r="D131" s="476"/>
+      <c r="E131" s="476"/>
+      <c r="F131" s="476"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="474" t="s">
+      <c r="B132" s="471" t="s">
         <v>519</v>
       </c>
-      <c r="C132" s="474"/>
-      <c r="D132" s="474"/>
-      <c r="E132" s="474"/>
-      <c r="F132" s="474"/>
+      <c r="C132" s="471"/>
+      <c r="D132" s="471"/>
+      <c r="E132" s="471"/>
+      <c r="F132" s="471"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21553,13 +21553,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="475" t="s">
+      <c r="B149" s="477" t="s">
         <v>520</v>
       </c>
-      <c r="C149" s="474"/>
-      <c r="D149" s="474"/>
-      <c r="E149" s="474"/>
-      <c r="F149" s="474"/>
+      <c r="C149" s="471"/>
+      <c r="D149" s="471"/>
+      <c r="E149" s="471"/>
+      <c r="F149" s="471"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21567,13 +21567,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="476" t="s">
+      <c r="B152" s="473" t="s">
         <v>521</v>
       </c>
-      <c r="C152" s="476"/>
-      <c r="D152" s="476"/>
-      <c r="E152" s="476"/>
-      <c r="F152" s="476"/>
+      <c r="C152" s="473"/>
+      <c r="D152" s="473"/>
+      <c r="E152" s="473"/>
+      <c r="F152" s="473"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21610,22 +21610,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="471" t="s">
+      <c r="B161" s="474" t="s">
         <v>386</v>
       </c>
-      <c r="C161" s="471"/>
-      <c r="D161" s="471"/>
-      <c r="E161" s="471"/>
-      <c r="F161" s="471"/>
+      <c r="C161" s="474"/>
+      <c r="D161" s="474"/>
+      <c r="E161" s="474"/>
+      <c r="F161" s="474"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="471" t="s">
+      <c r="B162" s="474" t="s">
         <v>387</v>
       </c>
-      <c r="C162" s="471"/>
-      <c r="D162" s="471"/>
-      <c r="E162" s="471"/>
-      <c r="F162" s="471"/>
+      <c r="C162" s="474"/>
+      <c r="D162" s="474"/>
+      <c r="E162" s="474"/>
+      <c r="F162" s="474"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21649,12 +21649,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21669,15 +21672,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/000858.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/000858.SZ_Valuation.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6BE1F9F-16D4-4CBC-882B-FC7C27FC78F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1ED6913-E76F-4556-A12D-D53FDF725DB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4986,30 +4986,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5019,25 +5019,25 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5407,7 +5407,7 @@
         <v>348</v>
       </c>
       <c r="C8" s="47">
-        <v>102.45</v>
+        <v>103.46</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5425,14 +5425,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>397670.74011224997</v>
+        <v>401591.16419729998</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>525</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.16195140985561304</v>
+        <v>0.15806966595742114</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5440,13 +5440,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="460" t="s">
+      <c r="B12" s="462" t="s">
         <v>353</v>
       </c>
-      <c r="C12" s="460"/>
-      <c r="D12" s="460"/>
-      <c r="E12" s="460"/>
-      <c r="F12" s="460"/>
+      <c r="C12" s="462"/>
+      <c r="D12" s="462"/>
+      <c r="E12" s="462"/>
+      <c r="F12" s="462"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5624,22 +5624,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="460" t="s">
+      <c r="B29" s="462" t="s">
         <v>354</v>
       </c>
-      <c r="C29" s="460"/>
-      <c r="D29" s="460"/>
-      <c r="E29" s="460"/>
-      <c r="F29" s="460"/>
+      <c r="C29" s="462"/>
+      <c r="D29" s="462"/>
+      <c r="E29" s="462"/>
+      <c r="F29" s="462"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="462" t="s">
+      <c r="B30" s="466" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="462"/>
-      <c r="D30" s="462"/>
-      <c r="E30" s="462"/>
-      <c r="F30" s="462"/>
+      <c r="C30" s="466"/>
+      <c r="D30" s="466"/>
+      <c r="E30" s="466"/>
+      <c r="F30" s="466"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5651,13 +5651,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="461" t="s">
+      <c r="B33" s="463" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="461"/>
-      <c r="D33" s="461"/>
-      <c r="E33" s="461"/>
-      <c r="F33" s="461"/>
+      <c r="C33" s="463"/>
+      <c r="D33" s="463"/>
+      <c r="E33" s="463"/>
+      <c r="F33" s="463"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5677,13 +5677,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="461" t="s">
+      <c r="B36" s="463" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="461"/>
-      <c r="D36" s="461"/>
-      <c r="E36" s="461"/>
-      <c r="F36" s="461"/>
+      <c r="C36" s="463"/>
+      <c r="D36" s="463"/>
+      <c r="E36" s="463"/>
+      <c r="F36" s="463"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5712,13 +5712,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="461" t="s">
+      <c r="B40" s="463" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="461"/>
-      <c r="D40" s="461"/>
-      <c r="E40" s="461"/>
-      <c r="F40" s="461"/>
+      <c r="C40" s="463"/>
+      <c r="D40" s="463"/>
+      <c r="E40" s="463"/>
+      <c r="F40" s="463"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5734,13 +5734,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="461" t="s">
+      <c r="B43" s="463" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="461"/>
-      <c r="D43" s="461"/>
-      <c r="E43" s="461"/>
-      <c r="F43" s="461"/>
+      <c r="C43" s="463"/>
+      <c r="D43" s="463"/>
+      <c r="E43" s="463"/>
+      <c r="F43" s="463"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5804,13 +5804,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="461" t="s">
+      <c r="B51" s="463" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="461"/>
-      <c r="D51" s="461"/>
-      <c r="E51" s="461"/>
-      <c r="F51" s="461"/>
+      <c r="C51" s="463"/>
+      <c r="D51" s="463"/>
+      <c r="E51" s="463"/>
+      <c r="F51" s="463"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5826,7 +5826,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="461" t="s">
+      <c r="B54" s="463" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="464"/>
@@ -5848,22 +5848,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="460" t="s">
+      <c r="B57" s="462" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="460"/>
-      <c r="D57" s="460"/>
-      <c r="E57" s="460"/>
-      <c r="F57" s="460"/>
+      <c r="C57" s="462"/>
+      <c r="D57" s="462"/>
+      <c r="E57" s="462"/>
+      <c r="F57" s="462"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="460" t="s">
+      <c r="B58" s="462" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="460"/>
-      <c r="D58" s="460"/>
-      <c r="E58" s="460"/>
-      <c r="F58" s="460"/>
+      <c r="C58" s="462"/>
+      <c r="D58" s="462"/>
+      <c r="E58" s="462"/>
+      <c r="F58" s="462"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>7.4942150714021299E-2</v>
+        <v>7.4210548430808848E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5907,7 +5907,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>2.7838945827232797E-2</v>
+        <v>2.756717572008506E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>321</v>
@@ -5998,13 +5998,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="460" t="s">
+      <c r="B73" s="462" t="s">
         <v>476</v>
       </c>
-      <c r="C73" s="460"/>
-      <c r="D73" s="460"/>
-      <c r="E73" s="460"/>
-      <c r="F73" s="460"/>
+      <c r="C73" s="462"/>
+      <c r="D73" s="462"/>
+      <c r="E73" s="462"/>
+      <c r="F73" s="462"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6023,13 +6023,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="460" t="s">
+      <c r="B77" s="462" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="460"/>
-      <c r="D77" s="460"/>
-      <c r="E77" s="460"/>
-      <c r="F77" s="460"/>
+      <c r="C77" s="462"/>
+      <c r="D77" s="462"/>
+      <c r="E77" s="462"/>
+      <c r="F77" s="462"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6198,31 +6198,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="460" t="s">
+      <c r="B96" s="462" t="s">
         <v>483</v>
       </c>
-      <c r="C96" s="460"/>
-      <c r="D96" s="460"/>
-      <c r="E96" s="460"/>
-      <c r="F96" s="460"/>
+      <c r="C96" s="462"/>
+      <c r="D96" s="462"/>
+      <c r="E96" s="462"/>
+      <c r="F96" s="462"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="462" t="s">
+      <c r="B97" s="466" t="s">
         <v>482</v>
       </c>
-      <c r="C97" s="462"/>
-      <c r="D97" s="462"/>
-      <c r="E97" s="462"/>
-      <c r="F97" s="462"/>
+      <c r="C97" s="466"/>
+      <c r="D97" s="466"/>
+      <c r="E97" s="466"/>
+      <c r="F97" s="466"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="462" t="s">
+      <c r="B98" s="466" t="s">
         <v>481</v>
       </c>
-      <c r="C98" s="462"/>
-      <c r="D98" s="462"/>
-      <c r="E98" s="462"/>
-      <c r="F98" s="462"/>
+      <c r="C98" s="466"/>
+      <c r="D98" s="466"/>
+      <c r="E98" s="466"/>
+      <c r="F98" s="466"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6272,22 +6272,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="460" t="s">
+      <c r="B107" s="462" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="460"/>
-      <c r="D107" s="460"/>
-      <c r="E107" s="460"/>
-      <c r="F107" s="460"/>
+      <c r="C107" s="462"/>
+      <c r="D107" s="462"/>
+      <c r="E107" s="462"/>
+      <c r="F107" s="462"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="460" t="s">
+      <c r="B108" s="462" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="460"/>
-      <c r="D108" s="460"/>
-      <c r="E108" s="460"/>
-      <c r="F108" s="460"/>
+      <c r="C108" s="462"/>
+      <c r="D108" s="462"/>
+      <c r="E108" s="462"/>
+      <c r="F108" s="462"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6321,13 +6321,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="460" t="s">
+      <c r="B114" s="462" t="s">
         <v>489</v>
       </c>
-      <c r="C114" s="460"/>
-      <c r="D114" s="460"/>
-      <c r="E114" s="460"/>
-      <c r="F114" s="460"/>
+      <c r="C114" s="462"/>
+      <c r="D114" s="462"/>
+      <c r="E114" s="462"/>
+      <c r="F114" s="462"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6462,13 +6462,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="461" t="s">
+      <c r="B124" s="463" t="s">
         <v>355</v>
       </c>
-      <c r="C124" s="461"/>
-      <c r="D124" s="461"/>
-      <c r="E124" s="461"/>
-      <c r="F124" s="461"/>
+      <c r="C124" s="463"/>
+      <c r="D124" s="463"/>
+      <c r="E124" s="463"/>
+      <c r="F124" s="463"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6503,22 +6503,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="463" t="s">
+      <c r="B131" s="467" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="463"/>
-      <c r="D131" s="463"/>
-      <c r="E131" s="463"/>
-      <c r="F131" s="463"/>
+      <c r="C131" s="467"/>
+      <c r="D131" s="467"/>
+      <c r="E131" s="467"/>
+      <c r="F131" s="467"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="460" t="s">
+      <c r="B132" s="462" t="s">
         <v>357</v>
       </c>
-      <c r="C132" s="460"/>
-      <c r="D132" s="460"/>
-      <c r="E132" s="460"/>
-      <c r="F132" s="460"/>
+      <c r="C132" s="462"/>
+      <c r="D132" s="462"/>
+      <c r="E132" s="462"/>
+      <c r="F132" s="462"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6694,13 +6694,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="467" t="s">
+      <c r="B149" s="461" t="s">
         <v>358</v>
       </c>
-      <c r="C149" s="460"/>
-      <c r="D149" s="460"/>
-      <c r="E149" s="460"/>
-      <c r="F149" s="460"/>
+      <c r="C149" s="462"/>
+      <c r="D149" s="462"/>
+      <c r="E149" s="462"/>
+      <c r="F149" s="462"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6737,13 +6737,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="461" t="s">
+      <c r="B158" s="463" t="s">
         <v>436</v>
       </c>
-      <c r="C158" s="461"/>
-      <c r="D158" s="461"/>
-      <c r="E158" s="461"/>
-      <c r="F158" s="461"/>
+      <c r="C158" s="463"/>
+      <c r="D158" s="463"/>
+      <c r="E158" s="463"/>
+      <c r="F158" s="463"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6751,22 +6751,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="466" t="s">
+      <c r="B161" s="460" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="466"/>
-      <c r="D161" s="466"/>
-      <c r="E161" s="466"/>
-      <c r="F161" s="466"/>
+      <c r="C161" s="460"/>
+      <c r="D161" s="460"/>
+      <c r="E161" s="460"/>
+      <c r="F161" s="460"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="466" t="s">
+      <c r="B162" s="460" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="466"/>
-      <c r="D162" s="466"/>
-      <c r="E162" s="466"/>
-      <c r="F162" s="466"/>
+      <c r="C162" s="460"/>
+      <c r="D162" s="460"/>
+      <c r="E162" s="460"/>
+      <c r="F162" s="460"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6790,18 +6790,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6818,6 +6806,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -14008,16 +14008,16 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>2.7838945827232797E-2</v>
+        <v>2.756717572008506E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>2.7838945827232797E-2</v>
+        <v>2.756717572008506E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>4.1024890190336755E-2</v>
+        <v>4.0624395901797804E-2</v>
       </c>
       <c r="I92" s="22" t="str">
         <f t="shared" si="38"/>
@@ -15229,18 +15229,18 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>7.4942150714021299E-2</v>
+        <v>7.4210548430808848E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>6.6533753069193333E-2</v>
+        <v>6.5884235472055463E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>6.4057769479713783E-2</v>
+        <v>6.3432422996294979E-2</v>
       </c>
       <c r="I124" s="74" t="str">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
@@ -15286,11 +15286,11 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.3469707816447664E-2</v>
+        <v>8.2654857585492583E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.9263507225230276E-2</v>
+        <v>7.848971887903386E-2</v>
       </c>
       <c r="I125" s="22" t="str">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -19748,7 +19748,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>102.45</v>
+        <v>103.46</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19759,7 +19759,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.16195140985561304</v>
+        <v>0.15806966595742114</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -20255,7 +20255,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>102.45</v>
+        <v>103.46</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20273,14 +20273,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>397670.74011224997</v>
+        <v>401591.16419729998</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>526</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.16195140985561304</v>
+        <v>0.15806966595742114</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20288,13 +20288,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="471" t="s">
+      <c r="B12" s="474" t="s">
         <v>495</v>
       </c>
-      <c r="C12" s="471"/>
-      <c r="D12" s="471"/>
-      <c r="E12" s="471"/>
-      <c r="F12" s="471"/>
+      <c r="C12" s="474"/>
+      <c r="D12" s="474"/>
+      <c r="E12" s="474"/>
+      <c r="F12" s="474"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20479,22 +20479,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="471" t="s">
+      <c r="B29" s="474" t="s">
         <v>496</v>
       </c>
-      <c r="C29" s="471"/>
-      <c r="D29" s="471"/>
-      <c r="E29" s="471"/>
-      <c r="F29" s="471"/>
+      <c r="C29" s="474"/>
+      <c r="D29" s="474"/>
+      <c r="E29" s="474"/>
+      <c r="F29" s="474"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="472" t="s">
+      <c r="B30" s="477" t="s">
         <v>497</v>
       </c>
-      <c r="C30" s="472"/>
-      <c r="D30" s="472"/>
-      <c r="E30" s="472"/>
-      <c r="F30" s="472"/>
+      <c r="C30" s="477"/>
+      <c r="D30" s="477"/>
+      <c r="E30" s="477"/>
+      <c r="F30" s="477"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20684,10 +20684,10 @@
       <c r="B54" s="470" t="s">
         <v>504</v>
       </c>
-      <c r="C54" s="473"/>
-      <c r="D54" s="473"/>
-      <c r="E54" s="473"/>
-      <c r="F54" s="473"/>
+      <c r="C54" s="476"/>
+      <c r="D54" s="476"/>
+      <c r="E54" s="476"/>
+      <c r="F54" s="476"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20703,22 +20703,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="471" t="s">
+      <c r="B57" s="474" t="s">
         <v>505</v>
       </c>
-      <c r="C57" s="471"/>
-      <c r="D57" s="471"/>
-      <c r="E57" s="471"/>
-      <c r="F57" s="471"/>
+      <c r="C57" s="474"/>
+      <c r="D57" s="474"/>
+      <c r="E57" s="474"/>
+      <c r="F57" s="474"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="471" t="s">
+      <c r="B58" s="474" t="s">
         <v>506</v>
       </c>
-      <c r="C58" s="471"/>
-      <c r="D58" s="471"/>
-      <c r="E58" s="471"/>
-      <c r="F58" s="471"/>
+      <c r="C58" s="474"/>
+      <c r="D58" s="474"/>
+      <c r="E58" s="474"/>
+      <c r="F58" s="474"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20752,7 +20752,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>7.4942150714021299E-2</v>
+        <v>7.4210548430808848E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20762,7 +20762,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>2.7838945827232797E-2</v>
+        <v>2.756717572008506E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>371</v>
@@ -20853,22 +20853,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="471" t="s">
+      <c r="B73" s="474" t="s">
         <v>507</v>
       </c>
-      <c r="C73" s="471"/>
-      <c r="D73" s="471"/>
-      <c r="E73" s="471"/>
-      <c r="F73" s="471"/>
+      <c r="C73" s="474"/>
+      <c r="D73" s="474"/>
+      <c r="E73" s="474"/>
+      <c r="F73" s="474"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="472" t="s">
+      <c r="B74" s="477" t="s">
         <v>477</v>
       </c>
-      <c r="C74" s="472"/>
-      <c r="D74" s="472"/>
-      <c r="E74" s="472"/>
-      <c r="F74" s="472"/>
+      <c r="C74" s="477"/>
+      <c r="D74" s="477"/>
+      <c r="E74" s="477"/>
+      <c r="F74" s="477"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -20876,13 +20876,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="471" t="s">
+      <c r="B77" s="474" t="s">
         <v>508</v>
       </c>
-      <c r="C77" s="471"/>
-      <c r="D77" s="471"/>
-      <c r="E77" s="471"/>
-      <c r="F77" s="471"/>
+      <c r="C77" s="474"/>
+      <c r="D77" s="474"/>
+      <c r="E77" s="474"/>
+      <c r="F77" s="474"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21031,33 +21031,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="471" t="s">
+      <c r="B96" s="474" t="s">
         <v>511</v>
       </c>
-      <c r="C96" s="471"/>
-      <c r="D96" s="471"/>
-      <c r="E96" s="471"/>
-      <c r="F96" s="471"/>
+      <c r="C96" s="474"/>
+      <c r="D96" s="474"/>
+      <c r="E96" s="474"/>
+      <c r="F96" s="474"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="472" t="s">
+      <c r="B97" s="477" t="s">
         <v>512</v>
       </c>
-      <c r="C97" s="472"/>
-      <c r="D97" s="472"/>
-      <c r="E97" s="472"/>
-      <c r="F97" s="472"/>
+      <c r="C97" s="477"/>
+      <c r="D97" s="477"/>
+      <c r="E97" s="477"/>
+      <c r="F97" s="477"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="472" t="s">
+      <c r="B98" s="477" t="s">
         <v>513</v>
       </c>
-      <c r="C98" s="472"/>
-      <c r="D98" s="472"/>
-      <c r="E98" s="472"/>
-      <c r="F98" s="472"/>
+      <c r="C98" s="477"/>
+      <c r="D98" s="477"/>
+      <c r="E98" s="477"/>
+      <c r="F98" s="477"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21120,23 +21120,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="471" t="s">
+      <c r="B107" s="474" t="s">
         <v>514</v>
       </c>
-      <c r="C107" s="471"/>
-      <c r="D107" s="471"/>
-      <c r="E107" s="471"/>
-      <c r="F107" s="471"/>
+      <c r="C107" s="474"/>
+      <c r="D107" s="474"/>
+      <c r="E107" s="474"/>
+      <c r="F107" s="474"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="471" t="s">
+      <c r="B108" s="474" t="s">
         <v>533</v>
       </c>
-      <c r="C108" s="471"/>
-      <c r="D108" s="471"/>
-      <c r="E108" s="471"/>
-      <c r="F108" s="471"/>
+      <c r="C108" s="474"/>
+      <c r="D108" s="474"/>
+      <c r="E108" s="474"/>
+      <c r="F108" s="474"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21180,13 +21180,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="471" t="s">
+      <c r="B114" s="474" t="s">
         <v>515</v>
       </c>
-      <c r="C114" s="471"/>
-      <c r="D114" s="471"/>
-      <c r="E114" s="471"/>
-      <c r="F114" s="471"/>
+      <c r="C114" s="474"/>
+      <c r="D114" s="474"/>
+      <c r="E114" s="474"/>
+      <c r="F114" s="474"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21350,13 +21350,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="475" t="s">
+      <c r="B127" s="472" t="s">
         <v>517</v>
       </c>
-      <c r="C127" s="475"/>
-      <c r="D127" s="475"/>
-      <c r="E127" s="475"/>
-      <c r="F127" s="475"/>
+      <c r="C127" s="472"/>
+      <c r="D127" s="472"/>
+      <c r="E127" s="472"/>
+      <c r="F127" s="472"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21369,22 +21369,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="476" t="s">
+      <c r="B131" s="473" t="s">
         <v>518</v>
       </c>
-      <c r="C131" s="476"/>
-      <c r="D131" s="476"/>
-      <c r="E131" s="476"/>
-      <c r="F131" s="476"/>
+      <c r="C131" s="473"/>
+      <c r="D131" s="473"/>
+      <c r="E131" s="473"/>
+      <c r="F131" s="473"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="471" t="s">
+      <c r="B132" s="474" t="s">
         <v>519</v>
       </c>
-      <c r="C132" s="471"/>
-      <c r="D132" s="471"/>
-      <c r="E132" s="471"/>
-      <c r="F132" s="471"/>
+      <c r="C132" s="474"/>
+      <c r="D132" s="474"/>
+      <c r="E132" s="474"/>
+      <c r="F132" s="474"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21553,13 +21553,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="477" t="s">
+      <c r="B149" s="475" t="s">
         <v>520</v>
       </c>
-      <c r="C149" s="471"/>
-      <c r="D149" s="471"/>
-      <c r="E149" s="471"/>
-      <c r="F149" s="471"/>
+      <c r="C149" s="474"/>
+      <c r="D149" s="474"/>
+      <c r="E149" s="474"/>
+      <c r="F149" s="474"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21567,13 +21567,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="473" t="s">
+      <c r="B152" s="476" t="s">
         <v>521</v>
       </c>
-      <c r="C152" s="473"/>
-      <c r="D152" s="473"/>
-      <c r="E152" s="473"/>
-      <c r="F152" s="473"/>
+      <c r="C152" s="476"/>
+      <c r="D152" s="476"/>
+      <c r="E152" s="476"/>
+      <c r="F152" s="476"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21610,22 +21610,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="474" t="s">
+      <c r="B161" s="471" t="s">
         <v>386</v>
       </c>
-      <c r="C161" s="474"/>
-      <c r="D161" s="474"/>
-      <c r="E161" s="474"/>
-      <c r="F161" s="474"/>
+      <c r="C161" s="471"/>
+      <c r="D161" s="471"/>
+      <c r="E161" s="471"/>
+      <c r="F161" s="471"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="474" t="s">
+      <c r="B162" s="471" t="s">
         <v>387</v>
       </c>
-      <c r="C162" s="474"/>
-      <c r="D162" s="474"/>
-      <c r="E162" s="474"/>
-      <c r="F162" s="474"/>
+      <c r="C162" s="471"/>
+      <c r="D162" s="471"/>
+      <c r="E162" s="471"/>
+      <c r="F162" s="471"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21649,15 +21649,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21672,12 +21669,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/000858.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/000858.SZ_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1ED6913-E76F-4556-A12D-D53FDF725DB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B68AD4DF-0114-4768-B7AB-F8AF4C669978}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -96,9 +96,6 @@
   </si>
   <si>
     <t>Other LT liabilities</t>
-  </si>
-  <si>
-    <t>Biological assets</t>
   </si>
   <si>
     <t>Intangible assets</t>
@@ -3252,16 +3249,19 @@
     <t>Sales/Total Assets g Projection</t>
   </si>
   <si>
+    <t>Biological/Mineral assets</t>
+  </si>
+  <si>
+    <t>CN</t>
+  </si>
+  <si>
+    <t>五粮液</t>
+  </si>
+  <si>
     <t>000858.SZ</t>
   </si>
   <si>
     <t>CNY</t>
-  </si>
-  <si>
-    <t>五粮液</t>
-  </si>
-  <si>
-    <t>CN</t>
   </si>
 </sst>
 </file>
@@ -5335,7 +5335,7 @@
   <sheetData>
     <row r="2" spans="1:9" ht="13.9">
       <c r="A2" s="200" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B2" s="34"/>
       <c r="C2" s="34"/>
@@ -5348,7 +5348,7 @@
     </row>
     <row r="3" spans="1:9">
       <c r="E3" s="428" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="F3" s="429">
         <v>46066</v>
@@ -5356,64 +5356,64 @@
     </row>
     <row r="4" spans="1:9" ht="12.4">
       <c r="B4" s="421" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C4" s="420" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="E4" s="430" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="F4" s="431" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="B5" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C5" s="46" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="E5" s="433" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="F5" s="432" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="B6" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C6" s="45" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="D6" s="45"/>
       <c r="E6" s="45"/>
     </row>
     <row r="7" spans="1:9">
       <c r="B7" s="1" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C7" s="45" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="D7" s="45"/>
       <c r="E7" s="45"/>
     </row>
     <row r="8" spans="1:9">
       <c r="B8" s="4" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C8" s="47">
-        <v>103.46</v>
+        <v>104.39</v>
       </c>
       <c r="E8" s="32"/>
     </row>
     <row r="9" spans="1:9">
       <c r="B9" s="4" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C9" s="48">
         <v>3881608005</v>
@@ -5421,18 +5421,18 @@
     </row>
     <row r="10" spans="1:9">
       <c r="B10" s="4" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>401591.16419729998</v>
+        <v>405201.05964195001</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.15806966595742114</v>
+        <v>0.15454049112527285</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5441,7 +5441,7 @@
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
       <c r="B12" s="462" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C12" s="462"/>
       <c r="D12" s="462"/>
@@ -5457,13 +5457,13 @@
     </row>
     <row r="15" spans="1:9">
       <c r="B15" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C15" s="417" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E15" s="253" t="str">
         <f>IF(E17=C7,C7,E17&amp;"/"&amp;C7)</f>
@@ -5472,13 +5472,13 @@
     </row>
     <row r="16" spans="1:9">
       <c r="B16" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C16" s="417" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="E16" s="416">
         <v>1</v>
@@ -5486,16 +5486,16 @@
     </row>
     <row r="17" spans="1:6">
       <c r="B17" s="1" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C17" s="456">
         <v>0.01</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E17" s="224" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -5508,7 +5508,7 @@
         <v>150.70538803259237</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E18" s="418">
         <v>6</v>
@@ -5516,14 +5516,14 @@
     </row>
     <row r="19" spans="1:6">
       <c r="B19" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C19" s="31" t="str">
         <f>IF(Terminal_Growth&lt;2%, "Lower than Inflation rate", IF(Terminal_Growth&lt;5%, "Low growth", IF(Terminal_Growth&lt;8%, "Medium growth", "High growth")))</f>
         <v>Lower than Inflation rate</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E19" s="419">
         <f>EOMONTH(EDATE(BS!C1,E18+2),0)</f>
@@ -5536,14 +5536,14 @@
     </row>
     <row r="21" spans="1:6">
       <c r="B21" s="42" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C21" s="254" t="str">
         <f>C138&amp;" ("&amp;Market_currency&amp;")"</f>
         <v xml:space="preserve"> (CNY)</v>
       </c>
       <c r="D21" s="31" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E21" s="442">
         <v>3</v>
@@ -5551,14 +5551,14 @@
     </row>
     <row r="22" spans="1:6">
       <c r="B22" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C22" s="255">
         <f>E140</f>
         <v>73.77572463932286</v>
       </c>
       <c r="D22" s="38" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E22" s="79">
         <v>0.3</v>
@@ -5566,14 +5566,14 @@
     </row>
     <row r="23" spans="1:6">
       <c r="B23" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C23" s="256">
         <f>E141</f>
         <v>93.221662055898364</v>
       </c>
       <c r="D23" s="38" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E23" s="443">
         <v>0.2</v>
@@ -5581,14 +5581,14 @@
     </row>
     <row r="24" spans="1:6">
       <c r="B24" s="1" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C24" s="256">
         <f>E144</f>
         <v>124.59667696127181</v>
       </c>
       <c r="D24" s="38" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="E24" s="443">
         <v>8.6999999999999994E-2</v>
@@ -5596,14 +5596,14 @@
     </row>
     <row r="25" spans="1:6">
       <c r="B25" s="1" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C25" s="256">
         <f>E145</f>
         <v>129.61296430141905</v>
       </c>
       <c r="D25" s="38" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="E25" s="444">
         <v>7.2499999999999995E-2</v>
@@ -5615,7 +5615,7 @@
     </row>
     <row r="27" spans="1:6" ht="13.9">
       <c r="A27" s="200" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B27" s="34"/>
       <c r="C27" s="34"/>
@@ -5625,7 +5625,7 @@
     </row>
     <row r="29" spans="1:6">
       <c r="B29" s="462" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C29" s="462"/>
       <c r="D29" s="462"/>
@@ -5634,7 +5634,7 @@
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
       <c r="B30" s="466" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C30" s="466"/>
       <c r="D30" s="466"/>
@@ -5643,7 +5643,7 @@
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C32" s="105">
         <f>scaling_factor</f>
@@ -5652,7 +5652,7 @@
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
       <c r="B33" s="463" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C33" s="463"/>
       <c r="D33" s="463"/>
@@ -5661,7 +5661,7 @@
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C34" s="285">
         <f>Normalized_FCF!C8</f>
@@ -5678,7 +5678,7 @@
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
       <c r="B36" s="463" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C36" s="463"/>
       <c r="D36" s="463"/>
@@ -5687,7 +5687,7 @@
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C37" s="285">
         <f>Normalized_FCF!C15</f>
@@ -5700,7 +5700,7 @@
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="49" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C38" s="285">
         <f>Normalized_FCF!C16</f>
@@ -5713,7 +5713,7 @@
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="463" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C40" s="463"/>
       <c r="D40" s="463"/>
@@ -5722,7 +5722,7 @@
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C41" s="285">
         <f>Normalized_FCF!C9</f>
@@ -5735,7 +5735,7 @@
     </row>
     <row r="43" spans="2:6">
       <c r="B43" s="463" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C43" s="463"/>
       <c r="D43" s="463"/>
@@ -5744,7 +5744,7 @@
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C44" s="286">
         <f>Normalized_FCF!C46</f>
@@ -5759,7 +5759,7 @@
     </row>
     <row r="45" spans="2:6">
       <c r="B45" s="44" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C45" s="286">
         <f>Normalized_FCF!C45</f>
@@ -5774,7 +5774,7 @@
     </row>
     <row r="46" spans="2:6">
       <c r="B46" s="44" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C46" s="285">
         <f>Normalized_FCF!C10</f>
@@ -5787,12 +5787,12 @@
     </row>
     <row r="48" spans="2:6">
       <c r="B48" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="49" spans="2:6">
       <c r="B49" s="44" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C49" s="285">
         <f>Normalized_FCF!C13</f>
@@ -5805,7 +5805,7 @@
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="463" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C51" s="463"/>
       <c r="D51" s="463"/>
@@ -5814,7 +5814,7 @@
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C52" s="285">
         <f>Normalized_FCF!C12</f>
@@ -5827,7 +5827,7 @@
     </row>
     <row r="54" spans="2:6">
       <c r="B54" s="463" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C54" s="464"/>
       <c r="D54" s="464"/>
@@ -5836,7 +5836,7 @@
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="44" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C55" s="285">
         <f>Normalized_FCF!C17</f>
@@ -5849,7 +5849,7 @@
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
       <c r="B57" s="462" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C57" s="462"/>
       <c r="D57" s="462"/>
@@ -5858,7 +5858,7 @@
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
       <c r="B58" s="462" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C58" s="462"/>
       <c r="D58" s="462"/>
@@ -5867,7 +5867,7 @@
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C60" s="285">
         <f>Normalized_FCF!G19</f>
@@ -5880,7 +5880,7 @@
     </row>
     <row r="61" spans="2:6">
       <c r="B61" s="44" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C61" s="285">
         <f>Normalized_FCF!C19</f>
@@ -5893,24 +5893,24 @@
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="204" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>7.4210548430808848E-2</v>
+        <v>7.3549414126367299E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
     <row r="63" spans="2:6">
       <c r="B63" s="204" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>2.756717572008506E-2</v>
+        <v>2.7321582527061981E-2</v>
       </c>
       <c r="E63" s="44" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F63" s="258">
         <f>Normalized_FCF!C90</f>
@@ -5919,18 +5919,18 @@
     </row>
     <row r="65" spans="1:6">
       <c r="B65" s="192" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C65" s="264" t="s">
+        <v>324</v>
+      </c>
+      <c r="D65" s="264" t="s">
         <v>325</v>
-      </c>
-      <c r="D65" s="264" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="66" spans="1:6">
       <c r="B66" s="44" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C66" s="89">
         <f>Normalized_FCF!E119</f>
@@ -5985,7 +5985,7 @@
     </row>
     <row r="71" spans="1:6" ht="13.9">
       <c r="A71" s="200" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B71" s="34"/>
       <c r="C71" s="34"/>
@@ -5999,7 +5999,7 @@
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
       <c r="B73" s="462" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C73" s="462"/>
       <c r="D73" s="462"/>
@@ -6009,7 +6009,7 @@
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
       <c r="B74" s="1" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="75" spans="1:6">
@@ -6018,13 +6018,13 @@
     <row r="76" spans="1:6">
       <c r="A76" s="191"/>
       <c r="B76" s="192" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
       <c r="B77" s="462" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C77" s="462"/>
       <c r="D77" s="462"/>
@@ -6034,7 +6034,7 @@
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
       <c r="B78" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C78" s="285">
         <f>DCF!F4</f>
@@ -6048,7 +6048,7 @@
     <row r="79" spans="1:6">
       <c r="A79" s="191"/>
       <c r="B79" s="44" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
@@ -6062,7 +6062,7 @@
     <row r="80" spans="1:6">
       <c r="A80" s="191"/>
       <c r="B80" s="229" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C80" s="337">
         <f>IF(BS!G31/BS!G27&gt;300%,"nm",BS!G31/BS!G27)</f>
@@ -6072,7 +6072,7 @@
     <row r="81" spans="1:6">
       <c r="A81" s="191"/>
       <c r="B81" s="229" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C81" s="338">
         <f>IF(BS!C50&gt;30,"nm",BS!C50)</f>
@@ -6085,13 +6085,13 @@
     <row r="83" spans="1:6">
       <c r="A83" s="191"/>
       <c r="B83" s="1" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="84" spans="1:6">
       <c r="A84" s="191"/>
       <c r="B84" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C84" s="285">
         <f>DCF!F5</f>
@@ -6105,7 +6105,7 @@
     <row r="85" spans="1:6">
       <c r="A85" s="191"/>
       <c r="B85" s="229" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C85" s="291">
         <f>BS!C66</f>
@@ -6119,7 +6119,7 @@
     <row r="86" spans="1:6">
       <c r="A86" s="191"/>
       <c r="B86" s="44" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
@@ -6136,13 +6136,13 @@
     <row r="88" spans="1:6">
       <c r="A88" s="191"/>
       <c r="B88" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="89" spans="1:6">
       <c r="A89" s="191"/>
       <c r="B89" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C89" s="285">
         <f>DCF!F6</f>
@@ -6156,7 +6156,7 @@
     <row r="90" spans="1:6">
       <c r="A90" s="191"/>
       <c r="B90" s="44" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
@@ -6173,7 +6173,7 @@
     <row r="92" spans="1:6">
       <c r="A92" s="191"/>
       <c r="B92" s="44" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
@@ -6186,7 +6186,7 @@
     </row>
     <row r="94" spans="1:6" ht="13.9">
       <c r="A94" s="200" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B94" s="34"/>
       <c r="C94" s="34"/>
@@ -6199,7 +6199,7 @@
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
       <c r="B96" s="462" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C96" s="462"/>
       <c r="D96" s="462"/>
@@ -6208,7 +6208,7 @@
     </row>
     <row r="97" spans="2:6">
       <c r="B97" s="466" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C97" s="466"/>
       <c r="D97" s="466"/>
@@ -6217,7 +6217,7 @@
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="466" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C98" s="466"/>
       <c r="D98" s="466"/>
@@ -6226,12 +6226,12 @@
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="101" spans="2:6">
       <c r="B101" s="49" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C101" s="211">
         <f>E25+C103</f>
@@ -6240,7 +6240,7 @@
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="229" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C102" s="263">
         <f>E25</f>
@@ -6249,7 +6249,7 @@
     </row>
     <row r="103" spans="2:6">
       <c r="B103" s="229" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C103" s="263">
         <f>IF(C15="Y",1%,0)+IF(C16="Y",1%,0)</f>
@@ -6258,7 +6258,7 @@
     </row>
     <row r="104" spans="2:6">
       <c r="B104" s="44" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C104" s="211">
         <f>Terminal_Growth</f>
@@ -6267,13 +6267,13 @@
     </row>
     <row r="106" spans="2:6">
       <c r="B106" s="250" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
       <c r="B107" s="462" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C107" s="462"/>
       <c r="D107" s="462"/>
@@ -6282,7 +6282,7 @@
     </row>
     <row r="108" spans="2:6">
       <c r="B108" s="462" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C108" s="462"/>
       <c r="D108" s="462"/>
@@ -6291,12 +6291,12 @@
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="111" spans="2:6">
       <c r="B111" s="49" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
@@ -6309,7 +6309,7 @@
     </row>
     <row r="112" spans="2:6">
       <c r="B112" s="44" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
@@ -6322,7 +6322,7 @@
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
       <c r="B114" s="462" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C114" s="462"/>
       <c r="D114" s="462"/>
@@ -6331,24 +6331,24 @@
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="117" spans="2:6" ht="12.4">
       <c r="B117" s="342" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C117" s="342" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D117" s="342" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E117" s="342" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F117" s="342" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="118" spans="2:6">
@@ -6463,7 +6463,7 @@
     </row>
     <row r="124" spans="2:6">
       <c r="B124" s="463" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C124" s="463"/>
       <c r="D124" s="463"/>
@@ -6472,7 +6472,7 @@
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
@@ -6485,7 +6485,7 @@
     </row>
     <row r="127" spans="2:6" ht="24.5" customHeight="1">
       <c r="B127" s="465" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C127" s="465"/>
       <c r="D127" s="465"/>
@@ -6494,7 +6494,7 @@
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="200" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B129" s="34"/>
       <c r="C129" s="34"/>
@@ -6504,7 +6504,7 @@
     </row>
     <row r="131" spans="1:6">
       <c r="B131" s="467" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C131" s="467"/>
       <c r="D131" s="467"/>
@@ -6513,7 +6513,7 @@
     </row>
     <row r="132" spans="1:6">
       <c r="B132" s="462" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C132" s="462"/>
       <c r="D132" s="462"/>
@@ -6522,12 +6522,12 @@
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="135" spans="1:6">
       <c r="B135" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C135" s="202">
         <f>E21</f>
@@ -6536,7 +6536,7 @@
     </row>
     <row r="136" spans="1:6">
       <c r="B136" s="194" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C136" s="195">
         <f>Scenarios!C58</f>
@@ -6549,33 +6549,33 @@
     </row>
     <row r="138" spans="1:6">
       <c r="B138" s="192" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C138" s="214"/>
       <c r="D138" s="215"/>
     </row>
     <row r="139" spans="1:6" ht="12.4">
       <c r="B139" s="340" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C139" s="340" t="str">
         <f>"PV("&amp;Holding_Period&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
       <c r="D139" s="340" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="E139" s="341" t="str">
         <f>"Buy below ("&amp;Market_currency&amp;")"</f>
         <v>Buy below (CNY)</v>
       </c>
       <c r="F139" s="341" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="336" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C140" s="333">
         <f>Scenarios!C62</f>
@@ -6596,7 +6596,7 @@
     </row>
     <row r="141" spans="1:6">
       <c r="B141" s="336" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C141" s="333">
         <f>Scenarios!C63</f>
@@ -6624,26 +6624,26 @@
     </row>
     <row r="143" spans="1:6" ht="12.4">
       <c r="B143" s="340" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C143" s="340" t="str">
         <f>"PV("&amp;Holding_Period&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
       <c r="D143" s="340" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="E143" s="341" t="str">
         <f>"Sell above ("&amp;Market_currency&amp;")"</f>
         <v>Sell above (CNY)</v>
       </c>
       <c r="F143" s="341" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="144" spans="1:6">
       <c r="B144" s="336" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C144" s="333">
         <f>Scenarios!C66</f>
@@ -6664,7 +6664,7 @@
     </row>
     <row r="145" spans="1:6">
       <c r="B145" s="336" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C145" s="333">
         <f>Scenarios!C67</f>
@@ -6685,7 +6685,7 @@
     </row>
     <row r="147" spans="1:6" ht="13.9">
       <c r="A147" s="200" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B147" s="34"/>
       <c r="C147" s="34"/>
@@ -6695,7 +6695,7 @@
     </row>
     <row r="149" spans="1:6">
       <c r="B149" s="461" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C149" s="462"/>
       <c r="D149" s="462"/>
@@ -6704,12 +6704,12 @@
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="152" spans="1:6">
       <c r="B152" s="464" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C152" s="464"/>
       <c r="D152" s="464"/>
@@ -6718,27 +6718,27 @@
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="196" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="154" spans="1:6">
       <c r="B154" s="196" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="155" spans="1:6">
       <c r="B155" s="196" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="157" spans="1:6">
       <c r="B157" s="1" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
       <c r="B158" s="463" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C158" s="463"/>
       <c r="D158" s="463"/>
@@ -6747,12 +6747,12 @@
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
       <c r="B161" s="460" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C161" s="460"/>
       <c r="D161" s="460"/>
@@ -6761,7 +6761,7 @@
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
       <c r="B162" s="460" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C162" s="460"/>
       <c r="D162" s="460"/>
@@ -6770,22 +6770,22 @@
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="165" spans="2:6">
       <c r="B165" s="196" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="166" spans="2:6">
       <c r="B166" s="196" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="167" spans="2:6">
       <c r="B167" s="196" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
   </sheetData>
@@ -6904,7 +6904,7 @@
     </row>
     <row r="2" spans="2:13" ht="13.9">
       <c r="B2" s="34" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C2" s="35"/>
       <c r="D2" s="35"/>
@@ -6920,7 +6920,7 @@
     </row>
     <row r="3" spans="2:13">
       <c r="B3" s="16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C3" s="103">
         <v>1</v>
@@ -6948,7 +6948,7 @@
     </row>
     <row r="5" spans="2:13">
       <c r="B5" s="38" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C5" s="287">
         <f>20461423083.74+13040913970.28</f>
@@ -6970,7 +6970,7 @@
     </row>
     <row r="6" spans="2:13">
       <c r="B6" s="38" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C6" s="287">
         <f>3555238122.5+C7</f>
@@ -6992,7 +6992,7 @@
     </row>
     <row r="7" spans="2:13">
       <c r="B7" s="66" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C7" s="288">
         <v>10692376117.41</v>
@@ -7012,7 +7012,7 @@
     </row>
     <row r="8" spans="2:13">
       <c r="B8" s="38" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C8" s="287">
         <v>405053632.26999998</v>
@@ -7032,7 +7032,7 @@
     </row>
     <row r="9" spans="2:13">
       <c r="B9" s="38" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C9" s="287"/>
       <c r="D9" s="287"/>
@@ -7048,7 +7048,7 @@
     </row>
     <row r="10" spans="2:13">
       <c r="B10" s="38" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C10" s="287"/>
       <c r="D10" s="287"/>
@@ -7064,7 +7064,7 @@
     </row>
     <row r="11" spans="2:13">
       <c r="B11" s="38" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C11" s="287"/>
       <c r="D11" s="287"/>
@@ -7080,7 +7080,7 @@
     </row>
     <row r="12" spans="2:13">
       <c r="B12" s="38" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C12" s="287">
         <f>2833530840.46</f>
@@ -7101,7 +7101,7 @@
     </row>
     <row r="13" spans="2:13">
       <c r="B13" s="38" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C13" s="287">
         <v>2875863410.1100001</v>
@@ -7121,7 +7121,7 @@
     </row>
     <row r="14" spans="2:13">
       <c r="B14" s="38" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C14" s="287">
         <v>10969864757.690001</v>
@@ -7141,7 +7141,7 @@
     </row>
     <row r="15" spans="2:13">
       <c r="B15" s="41" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C15" s="289">
         <v>33193460484.32</v>
@@ -7161,7 +7161,7 @@
     </row>
     <row r="16" spans="2:13">
       <c r="B16" s="27" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C16" s="287">
         <v>1340287950.3399999</v>
@@ -7181,13 +7181,13 @@
     </row>
     <row r="18" spans="2:13">
       <c r="B18" s="16" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C18" s="9"/>
     </row>
     <row r="19" spans="2:13">
       <c r="B19" s="26" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C19" s="287"/>
       <c r="D19" s="287"/>
@@ -7203,7 +7203,7 @@
     </row>
     <row r="20" spans="2:13">
       <c r="B20" s="26" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C20" s="287"/>
       <c r="D20" s="287"/>
@@ -7219,7 +7219,7 @@
     </row>
     <row r="21" spans="2:13">
       <c r="B21" s="26" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C21" s="287"/>
       <c r="D21" s="287"/>
@@ -7235,7 +7235,7 @@
     </row>
     <row r="22" spans="2:13">
       <c r="B22" s="26" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C22" s="287">
         <v>33939755192.779999</v>
@@ -7255,7 +7255,7 @@
     </row>
     <row r="23" spans="2:13">
       <c r="B23" s="26" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C23" s="287">
         <v>-2642221739.0500002</v>
@@ -7275,7 +7275,7 @@
     </row>
     <row r="24" spans="2:13">
       <c r="B24" s="26" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C24" s="287">
         <v>-19622477387.77</v>
@@ -7318,15 +7318,15 @@
     </row>
     <row r="27" spans="2:13">
       <c r="B27" s="16" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C27" s="94" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
     </row>
     <row r="28" spans="2:13">
       <c r="B28" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C28" s="270">
         <f>BS!C4</f>
@@ -7348,7 +7348,7 @@
     </row>
     <row r="29" spans="2:13">
       <c r="B29" s="25" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C29" s="270">
         <f>BS!C6</f>
@@ -7369,7 +7369,7 @@
     </row>
     <row r="30" spans="2:13">
       <c r="B30" s="28" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C30" s="271">
         <f>BS!C33+BS!C42</f>
@@ -7390,7 +7390,7 @@
     </row>
     <row r="31" spans="2:13">
       <c r="B31" s="28" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C31" s="271">
         <f>BS!G27</f>
@@ -7411,7 +7411,7 @@
     </row>
     <row r="32" spans="2:13">
       <c r="B32" s="25" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C32" s="270">
         <f>BS!G28</f>
@@ -7432,7 +7432,7 @@
     </row>
     <row r="34" spans="2:13" ht="13.9">
       <c r="B34" s="34" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C34" s="35"/>
       <c r="D34" s="35"/>
@@ -7448,7 +7448,7 @@
     </row>
     <row r="35" spans="2:13">
       <c r="B35" s="16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="36" spans="2:13">
@@ -7502,7 +7502,7 @@
     </row>
     <row r="37" spans="2:13">
       <c r="B37" s="38" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C37" s="270">
         <f t="shared" ref="C37:M37" si="2">IF(C$4="","",-C5)</f>
@@ -7551,7 +7551,7 @@
     </row>
     <row r="38" spans="2:13">
       <c r="B38" s="30" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C38" s="267">
         <f>IF(C36="","",C36+C37)</f>
@@ -7600,7 +7600,7 @@
     </row>
     <row r="39" spans="2:13">
       <c r="B39" s="38" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C39" s="270">
         <f t="shared" ref="C39:M39" si="13">IF(C$4="","",-C6)</f>
@@ -7649,7 +7649,7 @@
     </row>
     <row r="40" spans="2:13">
       <c r="B40" s="66" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C40" s="282">
         <f t="shared" ref="C40:M40" si="14">IF(C$4="","",-C7)</f>
@@ -7698,7 +7698,7 @@
     </row>
     <row r="41" spans="2:13">
       <c r="B41" s="66" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C41" s="282">
         <f>IF(C$4="","",C39-C40)</f>
@@ -7747,7 +7747,7 @@
     </row>
     <row r="42" spans="2:13">
       <c r="B42" s="38" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C42" s="270">
         <f t="shared" ref="C42:M42" si="16">IF(C$4="","",-C8)</f>
@@ -7796,7 +7796,7 @@
     </row>
     <row r="43" spans="2:13">
       <c r="B43" s="41" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C43" s="271">
         <f>IF(C$4="","",C38+C39+C42)</f>
@@ -7845,7 +7845,7 @@
     </row>
     <row r="44" spans="2:13">
       <c r="B44" s="41" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C44" s="290">
         <f t="shared" ref="C44:M44" si="18">IF(C$4="","",C47-C46-C45-C43)</f>
@@ -7894,7 +7894,7 @@
     </row>
     <row r="45" spans="2:13">
       <c r="B45" s="38" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C45" s="285">
         <f t="shared" ref="C45:M45" si="19">IF(C$4="","",C51+C52)</f>
@@ -7943,7 +7943,7 @@
     </row>
     <row r="46" spans="2:13">
       <c r="B46" s="38" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C46" s="270">
         <f>IF(C$4="","",-C14)</f>
@@ -7992,7 +7992,7 @@
     </row>
     <row r="47" spans="2:13">
       <c r="B47" s="41" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C47" s="271">
         <f t="shared" ref="C47:M47" si="21">IF(C$4="","",C15)</f>
@@ -8041,7 +8041,7 @@
     </row>
     <row r="48" spans="2:13">
       <c r="B48" s="27" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C48" s="270">
         <f t="shared" ref="C48:M48" si="22">IF(C$4="","",MIN(-C16,0))</f>
@@ -8090,12 +8090,12 @@
     </row>
     <row r="50" spans="2:13">
       <c r="B50" s="16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="51" spans="2:13">
       <c r="B51" s="38" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C51" s="270">
         <f t="shared" ref="C51:M51" si="23">IF(C$4="","",-C12)</f>
@@ -8144,7 +8144,7 @@
     </row>
     <row r="52" spans="2:13">
       <c r="B52" s="38" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C52" s="270">
         <f>IF(C$4="","",C13)</f>
@@ -8193,12 +8193,12 @@
     </row>
     <row r="54" spans="2:13">
       <c r="B54" s="156" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="55" spans="2:13">
       <c r="B55" s="38" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C55" s="285">
         <f t="shared" ref="C55:M55" si="25">IF(C$4="","",C9)</f>
@@ -8247,7 +8247,7 @@
     </row>
     <row r="56" spans="2:13">
       <c r="B56" s="38" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C56" s="285">
         <f t="shared" ref="C56:M56" si="26">IF(C$4="","",C10)</f>
@@ -8296,7 +8296,7 @@
     </row>
     <row r="57" spans="2:13">
       <c r="B57" s="38" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C57" s="285">
         <f t="shared" ref="C57:M57" si="27">IF(C$4="","",C11)</f>
@@ -8345,7 +8345,7 @@
     </row>
     <row r="58" spans="2:13">
       <c r="B58" s="38" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C58" s="285">
         <f>IF(C$4="","",C44-C55-C56-C57)</f>
@@ -8394,13 +8394,13 @@
     </row>
     <row r="60" spans="2:13">
       <c r="B60" s="16" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C60" s="9"/>
     </row>
     <row r="61" spans="2:13">
       <c r="B61" s="26" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C61" s="270">
         <f>IF(C$4="","",-C19)</f>
@@ -8449,7 +8449,7 @@
     </row>
     <row r="62" spans="2:13">
       <c r="B62" s="26" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C62" s="270">
         <f>IF(C$4="","",IF(C20=0,C61,-C20))</f>
@@ -8498,7 +8498,7 @@
     </row>
     <row r="63" spans="2:13">
       <c r="B63" s="26" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C63" s="270">
         <f>IF(C$4="","",-C21)</f>
@@ -8547,7 +8547,7 @@
     </row>
     <row r="64" spans="2:13">
       <c r="B64" s="26" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C64" s="270">
         <f>IF(C$4="","",C22+C23+C24)</f>
@@ -8596,7 +8596,7 @@
     </row>
     <row r="65" spans="2:13">
       <c r="B65" s="23" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C65" s="70">
         <f>IF(C$4="","",C25)</f>
@@ -8645,7 +8645,7 @@
     </row>
     <row r="67" spans="2:13">
       <c r="B67" s="88" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="68" spans="2:13">
@@ -8700,7 +8700,7 @@
     </row>
     <row r="69" spans="2:13">
       <c r="B69" s="30" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C69" s="89">
         <f>IF(D$36="","",C38/D38-1)</f>
@@ -8799,7 +8799,7 @@
     </row>
     <row r="71" spans="2:13">
       <c r="B71" s="41" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C71" s="98">
         <f>IF(D$36="","",C44/D44-1)</f>
@@ -8898,7 +8898,7 @@
     </row>
     <row r="74" spans="2:13" ht="13.9">
       <c r="B74" s="34" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C74" s="35"/>
       <c r="D74" s="35"/>
@@ -8914,7 +8914,7 @@
     </row>
     <row r="75" spans="2:13">
       <c r="B75" s="16" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C75" s="9"/>
     </row>
@@ -8969,7 +8969,7 @@
     </row>
     <row r="77" spans="2:13">
       <c r="B77" s="90" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C77" s="260">
         <f t="shared" ref="C77:H78" si="40">IF(C$4="","",C28)</f>
@@ -9003,7 +9003,7 @@
     </row>
     <row r="78" spans="2:13">
       <c r="B78" s="90" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C78" s="260">
         <f t="shared" si="40"/>
@@ -9037,7 +9037,7 @@
     </row>
     <row r="79" spans="2:13">
       <c r="B79" s="25" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C79" s="259">
         <f t="shared" ref="C79:M79" si="41">IF(C$4="","",C30)</f>
@@ -9086,7 +9086,7 @@
     </row>
     <row r="80" spans="2:13">
       <c r="B80" s="25" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C80" s="259">
         <f t="shared" ref="C80:M80" si="42">IF(C$4="","",C31)</f>
@@ -9150,7 +9150,7 @@
       <formula>ISBLANK(C36)</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="1">
+  <dataValidations disablePrompts="1" count="1">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C1" xr:uid="{87139493-416E-4F03-A3A9-B1C3E5C019E4}"/>
   </dataValidations>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9178,7 +9178,7 @@
   <sheetData>
     <row r="1" spans="2:8" ht="15" customHeight="1">
       <c r="B1" s="17" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C1" s="96">
         <v>45838</v>
@@ -9194,7 +9194,7 @@
     </row>
     <row r="2" spans="2:8" ht="15" customHeight="1">
       <c r="B2" s="76" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C2" s="35"/>
       <c r="D2" s="35"/>
@@ -9205,27 +9205,27 @@
     </row>
     <row r="3" spans="2:8" ht="15" customHeight="1">
       <c r="B3" s="16" t="s">
+        <v>153</v>
+      </c>
+      <c r="C3" s="164" t="s">
+        <v>112</v>
+      </c>
+      <c r="D3" s="165" t="s">
+        <v>32</v>
+      </c>
+      <c r="F3" s="16" t="s">
         <v>154</v>
       </c>
-      <c r="C3" s="164" t="s">
-        <v>113</v>
-      </c>
-      <c r="D3" s="165" t="s">
-        <v>33</v>
-      </c>
-      <c r="F3" s="16" t="s">
-        <v>155</v>
-      </c>
       <c r="G3" s="164" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H3" s="165" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" spans="2:8" ht="15" customHeight="1">
       <c r="B4" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C4" s="18">
         <f>3368850.3+64351041.9+3888593774.07+60621424.66</f>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="E4" s="24"/>
       <c r="F4" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G4" s="18">
         <v>148319946342.06</v>
@@ -9247,7 +9247,7 @@
     </row>
     <row r="5" spans="2:8" ht="15" customHeight="1">
       <c r="B5" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C5" s="18">
         <v>0</v>
@@ -9257,7 +9257,7 @@
       </c>
       <c r="E5" s="24"/>
       <c r="F5" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G5" s="18">
         <v>0</v>
@@ -9278,7 +9278,7 @@
       </c>
       <c r="E6" s="24"/>
       <c r="F6" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G6" s="18">
         <v>0</v>
@@ -9289,7 +9289,7 @@
     </row>
     <row r="7" spans="2:8" ht="15" customHeight="1">
       <c r="B7" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C7" s="18">
         <v>0</v>
@@ -9299,7 +9299,7 @@
       </c>
       <c r="E7" s="24"/>
       <c r="F7" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G7" s="18">
         <v>0</v>
@@ -9310,7 +9310,7 @@
     </row>
     <row r="8" spans="2:8" ht="15" customHeight="1">
       <c r="B8" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C8" s="18">
         <v>0</v>
@@ -9320,7 +9320,7 @@
       </c>
       <c r="E8" s="24"/>
       <c r="F8" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G8" s="18">
         <v>0</v>
@@ -9331,7 +9331,7 @@
     </row>
     <row r="9" spans="2:8" ht="15" customHeight="1">
       <c r="B9" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C9" s="18">
         <v>230243788.88</v>
@@ -9341,7 +9341,7 @@
       </c>
       <c r="E9" s="24"/>
       <c r="F9" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G9" s="18">
         <v>0</v>
@@ -9361,7 +9361,7 @@
         <v>0.9</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="G10" s="18">
         <v>0</v>
@@ -9384,7 +9384,7 @@
     </row>
     <row r="12" spans="2:8" ht="15" customHeight="1">
       <c r="B12" s="77" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C12" s="78">
         <f>SUM(C4:C11)</f>
@@ -9395,7 +9395,7 @@
         <v>11315641130.995998</v>
       </c>
       <c r="F12" s="77" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G12" s="78">
         <f>SUM(G4:G10)</f>
@@ -9413,27 +9413,27 @@
     </row>
     <row r="14" spans="2:8" ht="15" customHeight="1">
       <c r="B14" s="16" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C14" s="164" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D14" s="165" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F14" s="16" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G14" s="164" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H14" s="165" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="15" spans="2:8" ht="15" customHeight="1">
       <c r="B15" s="4" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C15" s="18">
         <v>0</v>
@@ -9442,7 +9442,7 @@
         <v>0.4</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G15" s="18">
         <v>0</v>
@@ -9453,7 +9453,7 @@
     </row>
     <row r="16" spans="2:8" ht="15" customHeight="1">
       <c r="B16" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C16" s="18">
         <v>0</v>
@@ -9462,7 +9462,7 @@
         <v>0.5</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G16" s="18">
         <v>0</v>
@@ -9473,7 +9473,7 @@
     </row>
     <row r="17" spans="2:8" ht="15" customHeight="1">
       <c r="B17" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C17" s="18">
         <v>0</v>
@@ -9482,7 +9482,7 @@
         <v>0.6</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G17" s="18">
         <v>0</v>
@@ -9493,7 +9493,7 @@
     </row>
     <row r="18" spans="2:8" ht="15" customHeight="1">
       <c r="B18" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C18" s="18">
         <v>0</v>
@@ -9502,7 +9502,7 @@
         <v>0.6</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="G18" s="18">
         <v>0</v>
@@ -9513,7 +9513,7 @@
     </row>
     <row r="19" spans="2:8" ht="15" customHeight="1">
       <c r="B19" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C19" s="18">
         <f>7745514521.75+5932852216.53+581324329.56</f>
@@ -9523,7 +9523,7 @@
         <v>0.1</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G19" s="18">
         <v>2173006025.0500002</v>
@@ -9534,7 +9534,7 @@
     </row>
     <row r="20" spans="2:8" ht="15" customHeight="1">
       <c r="B20" s="4" t="s">
-        <v>16</v>
+        <v>552</v>
       </c>
       <c r="C20" s="18">
         <v>0</v>
@@ -9543,7 +9543,7 @@
         <v>0.05</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G20" s="18">
         <v>0</v>
@@ -9554,7 +9554,7 @@
     </row>
     <row r="21" spans="2:8" ht="15" customHeight="1">
       <c r="B21" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C21" s="18">
         <v>2720969313.54</v>
@@ -9563,7 +9563,7 @@
         <v>0.05</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G21" s="18">
         <v>0</v>
@@ -9574,7 +9574,7 @@
     </row>
     <row r="22" spans="2:8" ht="15" customHeight="1">
       <c r="B22" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C22" s="18">
         <v>3149965433.77</v>
@@ -9586,7 +9586,7 @@
     </row>
     <row r="23" spans="2:8" ht="15" customHeight="1">
       <c r="B23" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C23" s="18">
         <f>1200000+1621619.53+136367275.12+468258650.52</f>
@@ -9599,7 +9599,7 @@
     </row>
     <row r="24" spans="2:8" ht="15" customHeight="1">
       <c r="B24" s="77" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C24" s="78">
         <f>SUM(C15:C23)</f>
@@ -9610,7 +9610,7 @@
         <v>4396986462.8540001</v>
       </c>
       <c r="F24" s="77" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G24" s="78">
         <f>SUM(G15:G21)</f>
@@ -9623,19 +9623,19 @@
     </row>
     <row r="26" spans="2:8" ht="15" customHeight="1">
       <c r="B26" s="16" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C26" s="164" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F26" s="166" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G26" s="167" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H26" s="168" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="27" spans="2:8" ht="15" customHeight="1">
@@ -9646,7 +9646,7 @@
         <v>0</v>
       </c>
       <c r="F27" s="169" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G27" s="82">
         <f>G32-G30</f>
@@ -9665,7 +9665,7 @@
         <v>0</v>
       </c>
       <c r="F28" s="171" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="G28" s="287">
         <v>3654729261.3800001</v>
@@ -9680,7 +9680,7 @@
         <v>0</v>
       </c>
       <c r="F29" s="172" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G29" s="14">
         <f>G27-G28</f>
@@ -9699,7 +9699,7 @@
         <v>0</v>
       </c>
       <c r="F30" s="169" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G30" s="82">
         <f>C33+C42</f>
@@ -9709,14 +9709,14 @@
     </row>
     <row r="31" spans="2:8" ht="15" customHeight="1">
       <c r="B31" s="77" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C31" s="78">
         <f>SUM(C27:C30)</f>
         <v>0</v>
       </c>
       <c r="F31" s="172" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G31" s="173">
         <f>C31+C40</f>
@@ -9733,7 +9733,7 @@
         <v>48677259367.199997</v>
       </c>
       <c r="F32" s="174" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G32" s="175">
         <f>G35+G40</f>
@@ -9759,24 +9759,24 @@
       <c r="B34" s="80"/>
       <c r="C34" s="81"/>
       <c r="F34" s="178" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G34" s="179" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H34" s="180" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="35" spans="2:8" ht="15" customHeight="1">
       <c r="B35" s="16" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C35" s="164" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F35" s="181" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G35" s="175">
         <f>C12+C24</f>
@@ -9795,7 +9795,7 @@
         <v>0</v>
       </c>
       <c r="F36" s="172" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G36" s="173">
         <f>C4+C15</f>
@@ -9811,7 +9811,7 @@
         <v>215370747.58000001</v>
       </c>
       <c r="F37" s="172" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G37" s="173">
         <f>C6</f>
@@ -9827,7 +9827,7 @@
         <v>0</v>
       </c>
       <c r="F38" s="172" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G38" s="173">
         <f>C7+C17</f>
@@ -9843,7 +9843,7 @@
         <v>0</v>
       </c>
       <c r="F39" s="172" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G39" s="173">
         <f>C7+C17+C19+C20</f>
@@ -9856,14 +9856,14 @@
     </row>
     <row r="40" spans="2:8" ht="15" customHeight="1">
       <c r="B40" s="77" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C40" s="78">
         <f>SUM(C36:C39)</f>
         <v>215370747.58000001</v>
       </c>
       <c r="F40" s="181" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G40" s="175">
         <f>G12+G24</f>
@@ -9883,7 +9883,7 @@
         <v>391614539.89999998</v>
       </c>
       <c r="F41" s="172" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G41" s="173">
         <f>C70</f>
@@ -9896,13 +9896,13 @@
     </row>
     <row r="42" spans="2:8" ht="15" customHeight="1">
       <c r="B42" s="80" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C42" s="81">
         <v>606985287.48000002</v>
       </c>
       <c r="F42" s="183" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G42" s="184">
         <f>C82</f>
@@ -9915,7 +9915,7 @@
     </row>
     <row r="44" spans="2:8" ht="15" customHeight="1">
       <c r="B44" s="76" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C44" s="35"/>
       <c r="D44" s="35"/>
@@ -9926,21 +9926,21 @@
     </row>
     <row r="45" spans="2:8" ht="15" customHeight="1">
       <c r="B45" s="16" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C45" s="209" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D45" s="164" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F45" s="226" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="46" spans="2:8" ht="15" customHeight="1">
       <c r="B46" s="1" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C46" s="73">
         <f>G29</f>
@@ -9972,20 +9972,20 @@
     </row>
     <row r="49" spans="2:8" ht="15" customHeight="1">
       <c r="B49" s="143" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C49" s="210" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D49" s="179" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" s="223"/>
     </row>
     <row r="50" spans="2:8" ht="15" customHeight="1">
       <c r="B50" s="8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C50" s="92">
         <f>G31/Normalized_FCF!C8</f>
@@ -9999,7 +9999,7 @@
     </row>
     <row r="51" spans="2:8" ht="15" customHeight="1">
       <c r="B51" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C51" s="163"/>
       <c r="D51" s="89">
@@ -10013,19 +10013,19 @@
     </row>
     <row r="53" spans="2:8" ht="15" customHeight="1">
       <c r="B53" s="143" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C53" s="210" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D53" s="179" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F53" s="223"/>
     </row>
     <row r="54" spans="2:8" ht="15" customHeight="1">
       <c r="B54" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C54" s="89">
         <f>Normalized_FCF!C8/G35</f>
@@ -10039,7 +10039,7 @@
     </row>
     <row r="55" spans="2:8" ht="15" customHeight="1">
       <c r="B55" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C55" s="89">
         <f>Normalized_FCF!C9/G40</f>
@@ -10056,19 +10056,19 @@
     </row>
     <row r="57" spans="2:8" ht="15" customHeight="1">
       <c r="B57" s="143" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C57" s="210" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D57" s="179" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F57" s="223"/>
     </row>
     <row r="58" spans="2:8" ht="15" customHeight="1">
       <c r="B58" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C58" s="95"/>
       <c r="D58" s="22">
@@ -10079,7 +10079,7 @@
     </row>
     <row r="59" spans="2:8" ht="15" customHeight="1">
       <c r="B59" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C59" s="95"/>
       <c r="D59" s="89">
@@ -10093,19 +10093,19 @@
     </row>
     <row r="61" spans="2:8" ht="15" customHeight="1">
       <c r="B61" s="143" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C61" s="210" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D61" s="179" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F61" s="223"/>
     </row>
     <row r="62" spans="2:8" ht="15" customHeight="1">
       <c r="B62" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C62" s="89">
         <f>IF(G28&lt;=0,0,G28/G29)</f>
@@ -10116,12 +10116,12 @@
         <v>2.6016676370001695E-2</v>
       </c>
       <c r="F62" s="223" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="64" spans="2:8" ht="15" customHeight="1">
       <c r="B64" s="76" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C64" s="35"/>
       <c r="D64" s="35"/>
@@ -10132,21 +10132,21 @@
     </row>
     <row r="65" spans="2:6" ht="15" customHeight="1">
       <c r="B65" s="16" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C65" s="209" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D65" s="165" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F65" s="226" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="66" spans="2:6" ht="15" customHeight="1">
       <c r="B66" s="102" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C66" s="19">
         <f>G4+G5+G15</f>
@@ -10157,12 +10157,12 @@
         <v>118301937502.43723</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="67" spans="2:6" ht="15" customHeight="1">
       <c r="B67" s="102" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C67" s="19">
         <f>G6+G16</f>
@@ -10172,7 +10172,7 @@
     </row>
     <row r="68" spans="2:6" ht="15" customHeight="1">
       <c r="B68" s="102" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C68" s="19">
         <f>G18</f>
@@ -10182,7 +10182,7 @@
     </row>
     <row r="69" spans="2:6" ht="15" customHeight="1">
       <c r="B69" s="102" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C69" s="19">
         <f>G8+G20</f>
@@ -10192,7 +10192,7 @@
     </row>
     <row r="70" spans="2:6" ht="15" customHeight="1">
       <c r="B70" s="77" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C70" s="78">
         <f>SUM(C66:C69)</f>
@@ -10205,19 +10205,19 @@
     </row>
     <row r="72" spans="2:6" ht="15" customHeight="1">
       <c r="B72" s="225" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C72" s="209" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D72" s="164" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F72" s="223"/>
     </row>
     <row r="73" spans="2:6" ht="15" customHeight="1">
       <c r="B73" s="102" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C73" s="285">
         <f>(Normalized_FCF!G26+Normalized_FCF!G35-Normalized_FCF!G89)/12</f>
@@ -10228,12 +10228,12 @@
         <v>-5003001473.2704611</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="15" customHeight="1">
       <c r="B74" s="227" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C74" s="228">
         <f>-$C$66/C73</f>
@@ -10244,12 +10244,12 @@
         <v>29.646192817349558</v>
       </c>
       <c r="F74" s="223" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="75" spans="2:6" ht="15" customHeight="1">
       <c r="B75" s="77" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C75" s="261"/>
       <c r="D75" s="262">
@@ -10257,12 +10257,12 @@
         <v>30018008839.622765</v>
       </c>
       <c r="F75" s="223" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="76" spans="2:6" ht="15" customHeight="1">
       <c r="B76" s="229" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C76" s="230"/>
       <c r="D76" s="248">
@@ -10270,7 +10270,7 @@
         <v>6</v>
       </c>
       <c r="F76" s="223" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="77" spans="2:6" ht="15" customHeight="1">
@@ -10278,19 +10278,19 @@
     </row>
     <row r="78" spans="2:6" ht="15" customHeight="1">
       <c r="B78" s="16" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C78" s="209" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D78" s="165" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F78" s="223"/>
     </row>
     <row r="79" spans="2:6" ht="15" customHeight="1">
       <c r="B79" s="102" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C79" s="19">
         <f>G7+G17</f>
@@ -10304,7 +10304,7 @@
     </row>
     <row r="80" spans="2:6" ht="15" customHeight="1">
       <c r="B80" s="102" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C80" s="19">
         <f>G19</f>
@@ -10318,7 +10318,7 @@
     </row>
     <row r="81" spans="2:8" ht="15" customHeight="1">
       <c r="B81" s="102" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C81" s="19">
         <f>G9+G21</f>
@@ -10332,7 +10332,7 @@
     </row>
     <row r="82" spans="2:8" ht="15" customHeight="1">
       <c r="B82" s="77" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C82" s="78">
         <f>SUM(C79:C81)</f>
@@ -10346,7 +10346,7 @@
     </row>
     <row r="84" spans="2:8" ht="15" customHeight="1">
       <c r="B84" s="76" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C84" s="35"/>
       <c r="D84" s="35"/>
@@ -10357,15 +10357,15 @@
     </row>
     <row r="85" spans="2:8" ht="15" customHeight="1">
       <c r="B85" s="16" t="s">
+        <v>241</v>
+      </c>
+      <c r="D85" s="215" t="s">
         <v>242</v>
-      </c>
-      <c r="D85" s="215" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="86" spans="2:8" ht="15" customHeight="1">
       <c r="B86" s="212" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C86" s="73">
         <f>DCF!F4*Exchange_Rate</f>
@@ -10382,7 +10382,7 @@
     </row>
     <row r="87" spans="2:8" ht="15" customHeight="1">
       <c r="B87" s="212" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
@@ -10399,7 +10399,7 @@
     </row>
     <row r="88" spans="2:8" ht="15" customHeight="1">
       <c r="B88" s="213" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
@@ -10416,7 +10416,7 @@
     </row>
     <row r="89" spans="2:8" ht="15" customHeight="1">
       <c r="B89" s="77" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
@@ -10469,7 +10469,7 @@
         <v>CNY</v>
       </c>
       <c r="C1" s="50" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D1" s="50"/>
       <c r="E1" s="50"/>
@@ -10522,12 +10522,12 @@
     <row r="2" spans="1:17" ht="15.75" customHeight="1">
       <c r="A2" s="3"/>
       <c r="B2" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C2" s="51"/>
       <c r="D2" s="53"/>
       <c r="E2" s="63" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F2" s="53"/>
       <c r="G2" s="35"/>
@@ -10545,7 +10545,7 @@
     <row r="3" spans="1:17" ht="15.75" customHeight="1">
       <c r="A3" s="10"/>
       <c r="B3" s="16" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C3" s="104">
         <f>scaling_factor</f>
@@ -10555,7 +10555,7 @@
       <c r="E3" s="237"/>
       <c r="F3" s="9"/>
       <c r="G3" s="16" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H3" s="104">
         <f>scaling_factor</f>
@@ -10622,7 +10622,7 @@
     <row r="5" spans="1:17" ht="15.75" customHeight="1">
       <c r="A5" s="10"/>
       <c r="B5" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C5" s="266">
         <f>C26</f>
@@ -10677,7 +10677,7 @@
     <row r="6" spans="1:17" ht="15.75" customHeight="1">
       <c r="A6" s="10"/>
       <c r="B6" s="30" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C6" s="267">
         <f>C4+C5</f>
@@ -10732,7 +10732,7 @@
     <row r="7" spans="1:17" ht="15.75" customHeight="1">
       <c r="A7" s="10"/>
       <c r="B7" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C7" s="266">
         <f>C35</f>
@@ -10787,7 +10787,7 @@
     <row r="8" spans="1:17" ht="15.75" customHeight="1">
       <c r="A8" s="10"/>
       <c r="B8" s="28" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C8" s="268">
         <f>C6+C7</f>
@@ -10844,7 +10844,7 @@
     <row r="9" spans="1:17" ht="15.75" customHeight="1">
       <c r="A9" s="10"/>
       <c r="B9" s="26" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C9" s="300">
         <f>C61</f>
@@ -10901,7 +10901,7 @@
     <row r="10" spans="1:17" ht="15.75" customHeight="1">
       <c r="A10" s="10"/>
       <c r="B10" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C10" s="266">
         <f>C48</f>
@@ -10956,7 +10956,7 @@
     <row r="11" spans="1:17" ht="15.75" customHeight="1">
       <c r="A11" s="10"/>
       <c r="B11" s="67" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C11" s="267">
         <f>SUM(C8:C10)</f>
@@ -11011,7 +11011,7 @@
     <row r="12" spans="1:17" ht="15.75" customHeight="1">
       <c r="A12" s="10"/>
       <c r="B12" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C12" s="266">
         <f>-C11*C41</f>
@@ -11066,7 +11066,7 @@
     <row r="13" spans="1:17" ht="15.75" customHeight="1">
       <c r="A13" s="10"/>
       <c r="B13" s="38" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C13" s="266">
         <f>-C4*C79</f>
@@ -11123,7 +11123,7 @@
     <row r="14" spans="1:17" ht="15.75" customHeight="1">
       <c r="A14" s="10"/>
       <c r="B14" s="39" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C14" s="269">
         <f>SUM(C11:C13)</f>
@@ -11180,7 +11180,7 @@
     <row r="15" spans="1:17" ht="15.75" customHeight="1">
       <c r="A15" s="10"/>
       <c r="B15" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C15" s="266">
         <f>BS!$G$39*BS!D58</f>
@@ -11235,7 +11235,7 @@
     <row r="16" spans="1:17" ht="15.75" customHeight="1">
       <c r="A16" s="10"/>
       <c r="B16" s="2" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C16" s="266">
         <f>-C4*C82</f>
@@ -11290,7 +11290,7 @@
     <row r="17" spans="1:17" ht="15.75" customHeight="1">
       <c r="A17" s="10"/>
       <c r="B17" s="26" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C17" s="266">
         <f>-C4*C83</f>
@@ -11298,7 +11298,7 @@
       </c>
       <c r="D17" s="55"/>
       <c r="E17" s="236" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="F17" s="55"/>
       <c r="G17" s="272"/>
@@ -11316,14 +11316,14 @@
     <row r="18" spans="1:17" ht="15.75" customHeight="1">
       <c r="A18" s="10"/>
       <c r="B18" s="26" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C18" s="266">
         <v>0</v>
       </c>
       <c r="D18" s="55"/>
       <c r="E18" s="236" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="F18" s="55"/>
       <c r="G18" s="273"/>
@@ -11341,7 +11341,7 @@
     <row r="19" spans="1:17" ht="15.75" customHeight="1">
       <c r="A19" s="10"/>
       <c r="B19" s="30" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C19" s="267">
         <f>C14+C17</f>
@@ -11417,12 +11417,12 @@
     <row r="21" spans="1:17" ht="15.75" customHeight="1">
       <c r="A21" s="10"/>
       <c r="B21" s="51" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C21" s="51"/>
       <c r="D21" s="53"/>
       <c r="E21" s="63" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F21" s="53"/>
       <c r="G21" s="35"/>
@@ -11440,7 +11440,7 @@
     <row r="22" spans="1:17" ht="15.75" customHeight="1">
       <c r="A22" s="10"/>
       <c r="B22" s="61" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C22" s="59"/>
       <c r="D22" s="26"/>
@@ -11461,7 +11461,7 @@
     <row r="23" spans="1:17" ht="15.75" customHeight="1">
       <c r="A23" s="10"/>
       <c r="B23" s="26" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C23" s="274">
         <f>-C4*C29</f>
@@ -11518,7 +11518,7 @@
     <row r="24" spans="1:17" ht="15.75" customHeight="1">
       <c r="A24" s="10"/>
       <c r="B24" s="65" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C24" s="266">
         <f>-C4*C30</f>
@@ -11575,7 +11575,7 @@
     <row r="25" spans="1:17" ht="15.75" customHeight="1">
       <c r="A25" s="10"/>
       <c r="B25" s="26" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C25" s="266">
         <f>-C4*C31</f>
@@ -11632,7 +11632,7 @@
     <row r="26" spans="1:17" ht="15.75" customHeight="1">
       <c r="A26" s="10"/>
       <c r="B26" s="67" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C26" s="267">
         <f>SUM(C23:C25)</f>
@@ -11693,14 +11693,14 @@
     <row r="28" spans="1:17" ht="15.75" customHeight="1">
       <c r="A28" s="10"/>
       <c r="B28" s="61" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E28" s="237"/>
     </row>
     <row r="29" spans="1:17" ht="15.75" customHeight="1">
       <c r="A29" s="10"/>
       <c r="B29" s="25" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C29" s="60">
         <f>AVERAGE(G29:H29)</f>
@@ -11873,7 +11873,7 @@
     <row r="32" spans="1:17" ht="15.75" customHeight="1">
       <c r="A32" s="10"/>
       <c r="B32" s="67" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C32" s="68">
         <f>ABS(C26/$C$4)</f>
@@ -11932,14 +11932,14 @@
     <row r="34" spans="1:17" ht="15.75" customHeight="1">
       <c r="A34" s="10"/>
       <c r="B34" s="61" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E34" s="237"/>
     </row>
     <row r="35" spans="1:17" ht="15.75" customHeight="1">
       <c r="A35" s="10"/>
       <c r="B35" s="298" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C35" s="276">
         <f>G35</f>
@@ -12000,14 +12000,14 @@
     <row r="37" spans="1:17" ht="15.75" customHeight="1">
       <c r="A37" s="10"/>
       <c r="B37" s="61" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E37" s="237"/>
     </row>
     <row r="38" spans="1:17" ht="15.75" customHeight="1">
       <c r="A38" s="10"/>
       <c r="B38" s="298" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C38" s="68">
         <f>ABS(C35/$C$4)</f>
@@ -12066,21 +12066,21 @@
     <row r="40" spans="1:17" ht="15.75" customHeight="1">
       <c r="A40" s="10"/>
       <c r="B40" s="61" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E40" s="237"/>
     </row>
     <row r="41" spans="1:17" ht="15.75" customHeight="1">
       <c r="A41" s="10"/>
       <c r="B41" s="26" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C41" s="457">
         <v>0.25</v>
       </c>
       <c r="D41" s="26"/>
       <c r="E41" s="234" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="F41" s="26"/>
       <c r="G41" s="6">
@@ -12134,12 +12134,12 @@
     <row r="43" spans="1:17" ht="15.75" customHeight="1">
       <c r="A43" s="10"/>
       <c r="B43" s="51" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C43" s="51"/>
       <c r="D43" s="53"/>
       <c r="E43" s="63" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F43" s="53"/>
       <c r="G43" s="35"/>
@@ -12157,14 +12157,14 @@
     <row r="44" spans="1:17" ht="15.75" customHeight="1">
       <c r="A44" s="10"/>
       <c r="B44" s="61" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E44" s="237"/>
     </row>
     <row r="45" spans="1:17" ht="15.75" customHeight="1">
       <c r="A45" s="10"/>
       <c r="B45" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C45" s="266">
         <f>-BS!G31*Normalized_FCF!C52</f>
@@ -12219,7 +12219,7 @@
     <row r="46" spans="1:17" ht="15.75" customHeight="1">
       <c r="A46" s="10"/>
       <c r="B46" s="2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C46" s="266">
         <f>BS!D75*C51</f>
@@ -12274,7 +12274,7 @@
     <row r="47" spans="1:17" ht="15.75" customHeight="1">
       <c r="A47" s="10"/>
       <c r="B47" s="245" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C47" s="278">
         <f>BS!$C$66*C51</f>
@@ -12331,7 +12331,7 @@
     <row r="48" spans="1:17" ht="15.75" customHeight="1">
       <c r="A48" s="10"/>
       <c r="B48" s="67" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C48" s="267">
         <f>C45+C46</f>
@@ -12390,17 +12390,17 @@
     <row r="50" spans="1:17" ht="15.75" customHeight="1">
       <c r="A50" s="10"/>
       <c r="B50" s="69" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E50" s="237"/>
       <c r="G50" s="94" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="51" spans="1:17" ht="15.75" customHeight="1">
       <c r="A51" s="10"/>
       <c r="B51" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C51" s="84">
         <v>6.0000000000000001E-3</v>
@@ -12424,7 +12424,7 @@
     <row r="52" spans="1:17" ht="15.75" customHeight="1">
       <c r="A52" s="10"/>
       <c r="B52" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C52" s="79">
         <v>0.06</v>
@@ -12448,7 +12448,7 @@
     <row r="53" spans="1:17" ht="15.75" customHeight="1">
       <c r="A53" s="10"/>
       <c r="B53" s="25" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C53" s="40">
         <f>-C8/C45</f>
@@ -12507,17 +12507,17 @@
     <row r="55" spans="1:17" ht="15.75" customHeight="1">
       <c r="A55" s="10"/>
       <c r="B55" s="61" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E55" s="237"/>
       <c r="G55" s="94" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="56" spans="1:17" ht="15.75" customHeight="1">
       <c r="A56" s="10"/>
       <c r="B56" s="38" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C56" s="266">
         <f>BS!$C67*C64</f>
@@ -12572,7 +12572,7 @@
     <row r="57" spans="1:17" ht="15.75" customHeight="1">
       <c r="A57" s="10"/>
       <c r="B57" s="38" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C57" s="266">
         <f>BS!$C68*C65</f>
@@ -12627,7 +12627,7 @@
     <row r="58" spans="1:17" ht="15.75" customHeight="1">
       <c r="A58" s="10"/>
       <c r="B58" s="38" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C58" s="266">
         <f>BS!$C69*C66</f>
@@ -12682,7 +12682,7 @@
     <row r="59" spans="1:17" ht="15.75" customHeight="1">
       <c r="A59" s="10"/>
       <c r="B59" s="30" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C59" s="267">
         <f>SUM(C56:C58)</f>
@@ -12737,13 +12737,13 @@
     <row r="60" spans="1:17" ht="15.75" customHeight="1">
       <c r="A60" s="10"/>
       <c r="B60" s="38" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C60" s="279">
         <v>0</v>
       </c>
       <c r="E60" s="235" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="G60" s="266">
         <f>Data!C58</f>
@@ -12793,7 +12793,7 @@
     <row r="61" spans="1:17" ht="15.75" customHeight="1">
       <c r="A61" s="10"/>
       <c r="B61" s="30" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C61" s="267">
         <f>C59+C60</f>
@@ -12852,17 +12852,17 @@
     <row r="63" spans="1:17" ht="15.75" customHeight="1">
       <c r="A63" s="10"/>
       <c r="B63" s="93" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E63" s="237"/>
       <c r="G63" s="94" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="64" spans="1:17" ht="15.75" customHeight="1">
       <c r="A64" s="10"/>
       <c r="B64" s="38" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C64" s="158">
         <f>G64</f>
@@ -12887,7 +12887,7 @@
     <row r="65" spans="1:17" ht="15.75" customHeight="1">
       <c r="A65" s="10"/>
       <c r="B65" s="102" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C65" s="158">
         <f>G65</f>
@@ -12912,7 +12912,7 @@
     <row r="66" spans="1:17" ht="15.75" customHeight="1">
       <c r="A66" s="10"/>
       <c r="B66" s="102" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C66" s="158">
         <f>G66</f>
@@ -12937,7 +12937,7 @@
     <row r="67" spans="1:17" ht="15.75" customHeight="1">
       <c r="A67" s="10"/>
       <c r="B67" s="30" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C67" s="68">
         <f>C59/BS!C70</f>
@@ -12967,12 +12967,12 @@
     <row r="69" spans="1:17" ht="15.75" customHeight="1">
       <c r="A69" s="10"/>
       <c r="B69" s="51" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C69" s="51"/>
       <c r="D69" s="53"/>
       <c r="E69" s="63" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F69" s="53"/>
       <c r="G69" s="35"/>
@@ -12990,7 +12990,7 @@
     <row r="70" spans="1:17" ht="15.75" customHeight="1">
       <c r="A70" s="10"/>
       <c r="B70" s="69" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C70" s="59"/>
       <c r="D70" s="26"/>
@@ -13011,7 +13011,7 @@
     <row r="71" spans="1:17" ht="15.75" customHeight="1">
       <c r="A71" s="10"/>
       <c r="B71" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C71" s="74">
         <f t="shared" ref="C71:C76" si="22">ABS(C5/C$4)</f>
@@ -13068,7 +13068,7 @@
     <row r="72" spans="1:17" ht="15.75" customHeight="1">
       <c r="A72" s="10"/>
       <c r="B72" s="30" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C72" s="75">
         <f t="shared" si="22"/>
@@ -13125,7 +13125,7 @@
     <row r="73" spans="1:17" ht="15.75" customHeight="1">
       <c r="A73" s="10"/>
       <c r="B73" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C73" s="74">
         <f t="shared" si="22"/>
@@ -13182,7 +13182,7 @@
     <row r="74" spans="1:17" ht="15.75" customHeight="1">
       <c r="A74" s="10"/>
       <c r="B74" s="28" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C74" s="75">
         <f t="shared" si="22"/>
@@ -13239,7 +13239,7 @@
     <row r="75" spans="1:17" ht="15.75" customHeight="1">
       <c r="A75" s="10"/>
       <c r="B75" s="26" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C75" s="74">
         <f t="shared" si="22"/>
@@ -13296,7 +13296,7 @@
     <row r="76" spans="1:17" ht="15.75" customHeight="1">
       <c r="A76" s="10"/>
       <c r="B76" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C76" s="74">
         <f t="shared" si="22"/>
@@ -13353,7 +13353,7 @@
     <row r="77" spans="1:17" ht="15.75" customHeight="1">
       <c r="A77" s="10"/>
       <c r="B77" s="67" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C77" s="75">
         <f>C11/C4</f>
@@ -13410,7 +13410,7 @@
     <row r="78" spans="1:17" ht="15.75" customHeight="1">
       <c r="A78" s="10"/>
       <c r="B78" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C78" s="74">
         <f>ABS(C12/C$4)</f>
@@ -13525,7 +13525,7 @@
     <row r="80" spans="1:17" ht="15.75" customHeight="1">
       <c r="A80" s="10"/>
       <c r="B80" s="39" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C80" s="75">
         <f>ABS(C14/C$4)</f>
@@ -13582,7 +13582,7 @@
     <row r="81" spans="1:17" ht="15.75" customHeight="1">
       <c r="A81" s="10"/>
       <c r="B81" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C81" s="74">
         <f>ABS(C15/C$4)</f>
@@ -13639,7 +13639,7 @@
     <row r="82" spans="1:17" ht="15.75" customHeight="1">
       <c r="A82" s="10"/>
       <c r="B82" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C82" s="85">
         <f>MAX(AVERAGE(G82:J82),C81)</f>
@@ -13647,7 +13647,7 @@
       </c>
       <c r="D82" s="26"/>
       <c r="E82" s="235" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="F82" s="26"/>
       <c r="G82" s="6">
@@ -13698,7 +13698,7 @@
     <row r="83" spans="1:17" ht="15.75" customHeight="1">
       <c r="A83" s="10"/>
       <c r="B83" s="26" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C83" s="233">
         <v>0</v>
@@ -13724,7 +13724,7 @@
     <row r="84" spans="1:17" ht="15.75" customHeight="1">
       <c r="A84" s="10"/>
       <c r="B84" s="8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C84" s="74">
         <v>0</v>
@@ -13748,7 +13748,7 @@
     <row r="85" spans="1:17" ht="15.75" customHeight="1">
       <c r="A85" s="10"/>
       <c r="B85" s="30" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C85" s="75">
         <f>ABS(C19/C$4)</f>
@@ -13809,7 +13809,7 @@
     <row r="87" spans="1:17" ht="15.75" customHeight="1">
       <c r="A87" s="10"/>
       <c r="B87" s="61" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E87" s="237"/>
     </row>
@@ -13928,7 +13928,7 @@
     <row r="90" spans="1:17" ht="15.75" customHeight="1">
       <c r="A90" s="10"/>
       <c r="B90" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C90" s="22">
         <f>C88/(C19*scaling_factor/Common_Shares)</f>
@@ -13983,7 +13983,7 @@
     <row r="91" spans="1:17" ht="15.75" customHeight="1">
       <c r="A91" s="10"/>
       <c r="B91" s="2" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C91" s="292">
         <v>0.1</v>
@@ -14004,20 +14004,20 @@
     <row r="92" spans="1:17" ht="15.75" customHeight="1">
       <c r="A92" s="10"/>
       <c r="B92" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>2.756717572008506E-2</v>
+        <v>2.7321582527061981E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>2.756717572008506E-2</v>
+        <v>2.7321582527061981E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>4.0624395901797804E-2</v>
+        <v>4.0262477248778621E-2</v>
       </c>
       <c r="I92" s="22" t="str">
         <f t="shared" si="38"/>
@@ -14063,7 +14063,7 @@
     <row r="94" spans="1:17" ht="15.75" customHeight="1">
       <c r="A94" s="10"/>
       <c r="B94" s="143" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C94" s="59"/>
       <c r="D94" s="26"/>
@@ -14084,7 +14084,7 @@
     <row r="95" spans="1:17" ht="15.75" customHeight="1">
       <c r="A95" s="10"/>
       <c r="B95" s="26" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C95" s="74">
         <f>C4/G4-1</f>
@@ -14141,7 +14141,7 @@
     <row r="96" spans="1:17" ht="15.75" customHeight="1">
       <c r="A96" s="10"/>
       <c r="B96" s="67" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C96" s="74">
         <f>C11/G11-1</f>
@@ -14201,12 +14201,12 @@
     <row r="98" spans="1:17" ht="15.75" customHeight="1">
       <c r="A98" s="3"/>
       <c r="B98" s="51" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C98" s="51"/>
       <c r="D98" s="53"/>
       <c r="E98" s="63" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F98" s="53"/>
       <c r="G98" s="35"/>
@@ -14224,11 +14224,11 @@
     <row r="99" spans="1:17" ht="15.75" customHeight="1">
       <c r="A99" s="10"/>
       <c r="B99" s="61" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E99" s="237"/>
       <c r="G99" s="94" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="100" spans="1:17" ht="15.75" customHeight="1">
@@ -14291,7 +14291,7 @@
     <row r="101" spans="1:17" ht="15.75" customHeight="1">
       <c r="A101" s="10"/>
       <c r="B101" s="90" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C101" s="281">
         <f>BS!C4</f>
@@ -14348,7 +14348,7 @@
     <row r="102" spans="1:17" ht="15.75" customHeight="1">
       <c r="A102" s="10"/>
       <c r="B102" s="90" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C102" s="281">
         <f>BS!C6+BS!C7</f>
@@ -14405,7 +14405,7 @@
     <row r="103" spans="1:17" ht="15.75" customHeight="1">
       <c r="A103" s="10"/>
       <c r="B103" s="25" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C103" s="280">
         <f>BS!G30</f>
@@ -14462,7 +14462,7 @@
     <row r="104" spans="1:17" ht="15.75" customHeight="1">
       <c r="A104" s="10"/>
       <c r="B104" s="25" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C104" s="280">
         <f>BS!G27</f>
@@ -14523,14 +14523,14 @@
     <row r="106" spans="1:17" ht="15.75" customHeight="1">
       <c r="A106" s="10"/>
       <c r="B106" s="88" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C106" s="25"/>
       <c r="D106" s="25"/>
       <c r="E106" s="238"/>
       <c r="F106" s="25"/>
       <c r="G106" s="94" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H106" s="12"/>
       <c r="I106" s="12"/>
@@ -14546,7 +14546,7 @@
     <row r="107" spans="1:17" ht="15.75" customHeight="1">
       <c r="A107" s="10"/>
       <c r="B107" s="25" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C107" s="91">
         <f>C101/C$4</f>
@@ -14603,7 +14603,7 @@
     <row r="108" spans="1:17" ht="15.75" customHeight="1">
       <c r="A108" s="10"/>
       <c r="B108" s="25" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C108" s="91">
         <f>C102/C$4</f>
@@ -14660,7 +14660,7 @@
     <row r="109" spans="1:17" ht="15.75" customHeight="1">
       <c r="A109" s="10"/>
       <c r="B109" s="25" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C109" s="91">
         <f>BS!$G$38/C$4</f>
@@ -14691,18 +14691,18 @@
     <row r="111" spans="1:17" ht="15.75" customHeight="1">
       <c r="A111" s="10"/>
       <c r="B111" s="61" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E111" s="237"/>
     </row>
     <row r="112" spans="1:17" ht="15.75" customHeight="1">
       <c r="A112" s="10"/>
       <c r="B112" s="2" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C112" s="151"/>
       <c r="E112" s="451" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="G112" s="251">
         <f>IF(G$4="","",Data!C$22/Data!C15)</f>
@@ -14752,7 +14752,7 @@
     <row r="113" spans="1:17" ht="15.75" customHeight="1">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C113" s="151"/>
       <c r="E113" s="459">
@@ -14811,10 +14811,10 @@
     <row r="115" spans="1:17" ht="15.75" customHeight="1">
       <c r="A115" s="10"/>
       <c r="B115" s="88" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C115" s="451" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D115" s="52"/>
       <c r="E115" s="451" t="str">
@@ -14870,7 +14870,7 @@
     <row r="116" spans="1:17" ht="15.75" customHeight="1">
       <c r="A116" s="10"/>
       <c r="B116" s="7" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C116" s="22">
         <f>C77</f>
@@ -14927,7 +14927,7 @@
     </row>
     <row r="117" spans="1:17" ht="15.75" customHeight="1">
       <c r="B117" s="7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C117" s="452">
         <f>G117</f>
@@ -14984,7 +14984,7 @@
     </row>
     <row r="118" spans="1:17" ht="15.75" customHeight="1">
       <c r="B118" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C118" s="15">
         <f>C100/C104</f>
@@ -15044,7 +15044,7 @@
     <row r="119" spans="1:17" ht="15.75" customHeight="1">
       <c r="A119" s="10"/>
       <c r="B119" s="67" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C119" s="62">
         <f>C11/C104</f>
@@ -15123,12 +15123,12 @@
     <row r="121" spans="1:17" ht="15.75" customHeight="1">
       <c r="A121" s="10"/>
       <c r="B121" s="51" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C121" s="51"/>
       <c r="D121" s="53"/>
       <c r="E121" s="63" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F121" s="53"/>
       <c r="G121" s="35"/>
@@ -15146,7 +15146,7 @@
     <row r="122" spans="1:17" ht="15.75" customHeight="1">
       <c r="A122" s="10"/>
       <c r="B122" s="160" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C122" s="161"/>
       <c r="D122" s="26"/>
@@ -15225,22 +15225,22 @@
     <row r="124" spans="1:17" ht="15.75" customHeight="1">
       <c r="A124" s="10"/>
       <c r="B124" s="26" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>7.4210548430808848E-2</v>
+        <v>7.3549414126367299E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>6.5884235472055463E-2</v>
+        <v>6.5297279451469084E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>6.3432422996294979E-2</v>
+        <v>6.2867309926206316E-2</v>
       </c>
       <c r="I124" s="74" t="str">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
@@ -15281,16 +15281,16 @@
     </row>
     <row r="125" spans="1:17" ht="15.75" customHeight="1">
       <c r="B125" s="2" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.2654857585492583E-2</v>
+        <v>8.1918493780966203E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.848971887903386E-2</v>
+        <v>7.7790461875896569E-2</v>
       </c>
       <c r="I125" s="22" t="str">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16043,7 +16043,7 @@
   <sheetData>
     <row r="2" spans="2:15" ht="13.9">
       <c r="B2" s="34" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C2" s="35"/>
       <c r="D2" s="35"/>
@@ -16058,22 +16058,22 @@
     </row>
     <row r="3" spans="2:15" ht="13.15">
       <c r="B3" s="106" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C3" s="104">
         <f>scaling_factor</f>
         <v>1</v>
       </c>
       <c r="E3" s="106" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H3" s="106" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="4" spans="2:15">
       <c r="B4" s="97" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C4" s="275">
         <f>Normalized_FCF!C19</f>
@@ -16084,7 +16084,7 @@
         <v>CNY</v>
       </c>
       <c r="E4" s="135" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="F4" s="275">
         <f>-BS!G31</f>
@@ -16095,7 +16095,7 @@
         <v>CNY</v>
       </c>
       <c r="H4" s="308" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="I4" s="305">
         <f>Normalized_FCF!C4</f>
@@ -16105,14 +16105,14 @@
     </row>
     <row r="5" spans="2:15">
       <c r="B5" s="187" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C5" s="188">
         <f>Equity_Cost</f>
         <v>7.2499999999999995E-2</v>
       </c>
       <c r="E5" s="135" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="F5" s="275">
         <f>BS!D66</f>
@@ -16123,7 +16123,7 @@
         <v>CNY</v>
       </c>
       <c r="H5" s="308" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="I5" s="305">
         <f>Normalized_FCF!C7</f>
@@ -16133,7 +16133,7 @@
     </row>
     <row r="6" spans="2:15" ht="13.25" customHeight="1">
       <c r="B6" s="136" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C6" s="283">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
@@ -16144,7 +16144,7 @@
         <v>CNY</v>
       </c>
       <c r="E6" s="187" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="F6" s="284">
         <f>BS!H42</f>
@@ -16155,7 +16155,7 @@
         <v>CNY</v>
       </c>
       <c r="H6" s="308" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="I6" s="305">
         <f>I7+I8</f>
@@ -16166,14 +16166,14 @@
     </row>
     <row r="7" spans="2:15" ht="12.75" customHeight="1">
       <c r="B7" s="318" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C7" s="275">
         <f>F7</f>
         <v>118303867357.36223</v>
       </c>
       <c r="E7" s="140" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="F7" s="283">
         <f>SUM(F4:F6)</f>
@@ -16184,7 +16184,7 @@
         <v>CNY</v>
       </c>
       <c r="H7" s="312" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="I7" s="313">
         <f>Normalized_FCF!C9</f>
@@ -16196,7 +16196,7 @@
     </row>
     <row r="8" spans="2:15" ht="13.15">
       <c r="B8" s="136" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C8" s="283">
         <f>C6+C7</f>
@@ -16207,7 +16207,7 @@
         <v>CNY</v>
       </c>
       <c r="E8" s="140" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
@@ -16257,7 +16257,7 @@
     </row>
     <row r="10" spans="2:15" ht="13.5" thickTop="1">
       <c r="B10" s="107" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C10" s="283">
         <f>C8*Exchange_Rate</f>
@@ -16268,7 +16268,7 @@
         <v>CNY</v>
       </c>
       <c r="H10" s="308" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="I10" s="306">
         <f>Normalized_FCF!C41</f>
@@ -16279,7 +16279,7 @@
     </row>
     <row r="11" spans="2:15" ht="13.15">
       <c r="B11" s="136" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
@@ -16295,7 +16295,7 @@
     </row>
     <row r="13" spans="2:15" ht="13.9">
       <c r="B13" s="34" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C13" s="35"/>
       <c r="D13" s="35"/>
@@ -16310,25 +16310,25 @@
     </row>
     <row r="14" spans="2:15" ht="13.15">
       <c r="B14" s="106" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C14" s="309" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E14" s="106" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="F14" s="309" t="str">
         <f>IF(ROUND(F17,4)=ROUND(C17,4),"I","II")</f>
         <v>I</v>
       </c>
       <c r="H14" s="106" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="15" spans="2:15">
       <c r="B15" s="139" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C15" s="148">
         <f>Scenarios!C45</f>
@@ -16343,7 +16343,7 @@
         <v>16</v>
       </c>
       <c r="H15" s="97" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="I15" s="126">
         <f>Terminal_Growth</f>
@@ -16353,14 +16353,14 @@
     </row>
     <row r="16" spans="2:15" ht="13.25" customHeight="1">
       <c r="B16" s="114" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C16" s="147">
         <f>Scenarios!C46</f>
         <v>2.38559171477595E-2</v>
       </c>
       <c r="E16" s="308" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="F16" s="311">
         <f>Scenarios!C41</f>
@@ -16369,40 +16369,40 @@
     </row>
     <row r="17" spans="1:21" ht="13.25" customHeight="1">
       <c r="B17" s="308" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="C17" s="306">
         <f>Normalized_FCF!C77</f>
         <v>0.4665778415257858</v>
       </c>
       <c r="E17" s="308" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="F17" s="311">
         <f>Scenarios!C40</f>
         <v>0.4665778415257858</v>
       </c>
       <c r="H17" s="106" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="18" spans="1:21" ht="13.25" customHeight="1">
       <c r="B18" s="308" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C18" s="306">
         <f>Normalized_FCF!C81-Normalized_FCF!C82</f>
         <v>0</v>
       </c>
       <c r="E18" s="308" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F18" s="144">
         <f>IF(F14="II",C18/2,C18)</f>
         <v>0</v>
       </c>
       <c r="H18" s="140" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
@@ -16418,41 +16418,41 @@
     </row>
     <row r="20" spans="1:21" ht="13.15">
       <c r="A20" s="121" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B20" s="121" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C20" s="121" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D20" s="121" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E20" s="121" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="F20" s="121" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="G20" s="121" t="str">
         <f>B18</f>
         <v>D&amp;A - maint. Capx</v>
       </c>
       <c r="H20" s="121" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="I20" s="121" t="s">
+        <v>526</v>
+      </c>
+      <c r="J20" s="121" t="s">
+        <v>549</v>
+      </c>
+      <c r="K20" s="121" t="s">
         <v>527</v>
       </c>
-      <c r="J20" s="121" t="s">
-        <v>550</v>
-      </c>
-      <c r="K20" s="121" t="s">
-        <v>528</v>
-      </c>
       <c r="L20" s="122" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="21" spans="1:21">
@@ -18007,7 +18007,7 @@
     </row>
     <row r="51" spans="1:21">
       <c r="A51" s="315" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B51" s="316">
         <f>C15+1</f>
@@ -18056,7 +18056,7 @@
       <c r="H52" s="111"/>
       <c r="I52" s="111"/>
       <c r="J52" s="468" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="K52" s="468"/>
       <c r="L52" s="317">
@@ -18069,7 +18069,7 @@
     </row>
     <row r="54" spans="1:21" ht="13.15">
       <c r="B54" s="115" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C54" s="128"/>
       <c r="D54" s="128"/>
@@ -18538,7 +18538,7 @@
     </row>
     <row r="71" spans="1:21" ht="13.15">
       <c r="B71" s="115" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C71" s="275"/>
       <c r="D71" s="111"/>
@@ -19062,19 +19062,19 @@
     </row>
     <row r="89" spans="1:12" ht="13.15">
       <c r="B89" s="153" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C89" s="153" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D89" s="153" t="s">
+        <v>98</v>
+      </c>
+      <c r="E89" s="154" t="s">
         <v>99</v>
       </c>
-      <c r="E89" s="154" t="s">
-        <v>100</v>
-      </c>
       <c r="F89" s="154" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="G89" s="323"/>
       <c r="H89" s="323"/>
@@ -19342,7 +19342,7 @@
   <sheetData>
     <row r="2" spans="2:7" ht="13.9">
       <c r="B2" s="34" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C2" s="35"/>
       <c r="D2" s="35"/>
@@ -19352,16 +19352,16 @@
     </row>
     <row r="3" spans="2:7" ht="13.15">
       <c r="B3" s="145" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D3" s="97" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="E3" s="97"/>
     </row>
     <row r="4" spans="2:7" ht="12.75" customHeight="1">
       <c r="B4" s="139" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C4" s="449">
         <v>2</v>
@@ -19389,7 +19389,7 @@
     </row>
     <row r="6" spans="2:7" ht="13.15">
       <c r="B6" s="145" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C6" s="446" t="str">
         <f>DCF!C3&amp;" "&amp;Reporting_currency</f>
@@ -19402,7 +19402,7 @@
     </row>
     <row r="7" spans="2:7" ht="12.75" customHeight="1">
       <c r="B7" s="97" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C7" s="447">
         <f>Normalized_FCF!G8</f>
@@ -19415,7 +19415,7 @@
     </row>
     <row r="8" spans="2:7">
       <c r="B8" s="97" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C8" s="447">
         <f>Normalized_FCF!G19</f>
@@ -19428,7 +19428,7 @@
     </row>
     <row r="9" spans="2:7">
       <c r="B9" s="97" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C9" s="447">
         <f>Normalized_FCF!C19</f>
@@ -19448,7 +19448,7 @@
     </row>
     <row r="11" spans="2:7" ht="13.15">
       <c r="B11" s="145" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C11" s="448"/>
       <c r="D11" s="469"/>
@@ -19458,7 +19458,7 @@
     </row>
     <row r="12" spans="2:7">
       <c r="B12" s="114" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C12" s="249" t="e">
         <f ca="1">(Normalized_FCF!G4/OFFSET(Normalized_FCF!G4, 0, $C$4))^(1/$C$4) - 1</f>
@@ -19471,7 +19471,7 @@
     </row>
     <row r="13" spans="2:7">
       <c r="B13" s="135" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C13" s="249" t="e">
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
@@ -19484,7 +19484,7 @@
     </row>
     <row r="14" spans="2:7">
       <c r="B14" s="97" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C14" s="249" t="e">
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
@@ -19497,7 +19497,7 @@
     </row>
     <row r="16" spans="2:7" ht="13.9">
       <c r="B16" s="34" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C16" s="35"/>
       <c r="D16" s="35"/>
@@ -19507,21 +19507,21 @@
     </row>
     <row r="17" spans="2:7" ht="13.15">
       <c r="B17" s="106" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E17" s="222" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="18" spans="2:7" ht="12.75" customHeight="1">
       <c r="B18" s="139" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C18" s="137">
         <v>15</v>
       </c>
       <c r="E18" s="450" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="F18" s="319"/>
     </row>
@@ -19531,35 +19531,35 @@
     </row>
     <row r="20" spans="2:7" ht="13.15">
       <c r="B20" s="106" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="E20" s="319"/>
       <c r="F20" s="319"/>
     </row>
     <row r="21" spans="2:7" ht="13.15">
       <c r="B21" s="153" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C21" s="153" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="D21" s="153" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="E21" s="154" t="str">
         <f>"Value per share ("&amp;Market_currency&amp;")"</f>
         <v>Value per share (CNY)</v>
       </c>
       <c r="F21" s="154" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="G21" s="154" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="22" spans="2:7">
       <c r="B22" s="302" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C22" s="324">
         <v>0.02</v>
@@ -19583,7 +19583,7 @@
     </row>
     <row r="23" spans="2:7">
       <c r="B23" s="302" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C23" s="324">
         <v>0.01</v>
@@ -19606,7 +19606,7 @@
     </row>
     <row r="24" spans="2:7">
       <c r="B24" s="302" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C24" s="324">
         <v>0</v>
@@ -19629,7 +19629,7 @@
     </row>
     <row r="25" spans="2:7">
       <c r="B25" s="141" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C25" s="441">
         <f>E23*F23+E24*F24+E22*F22</f>
@@ -19643,33 +19643,33 @@
     </row>
     <row r="27" spans="2:7" ht="13.15">
       <c r="B27" s="106" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="28" spans="2:7" ht="13.15">
       <c r="B28" s="153" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C28" s="153" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="D28" s="153" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="E28" s="154" t="str">
         <f>"Value per share ("&amp;Market_currency&amp;")"</f>
         <v>Value per share (CNY)</v>
       </c>
       <c r="F28" s="154" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="G28" s="154" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="29" spans="2:7">
       <c r="B29" s="302" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C29" s="324">
         <v>0.03</v>
@@ -19692,7 +19692,7 @@
     </row>
     <row r="30" spans="2:7">
       <c r="B30" s="315" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C30" s="324">
         <v>0</v>
@@ -19719,12 +19719,12 @@
     </row>
     <row r="32" spans="2:7" ht="13.15">
       <c r="B32" s="145" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="33" spans="2:7">
       <c r="B33" s="97" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C33" s="155">
         <f>Normalized_FCF!C88*(1-dividend_tax_rate)</f>
@@ -19735,7 +19735,7 @@
         <v>CNY</v>
       </c>
       <c r="E33" s="97" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F33" s="219">
         <f>Holding_Period</f>
@@ -19744,27 +19744,27 @@
     </row>
     <row r="34" spans="2:7">
       <c r="B34" s="97" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>103.46</v>
+        <v>104.39</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
       <c r="E34" s="97" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.15806966595742114</v>
+        <v>0.15454049112527285</v>
       </c>
     </row>
     <row r="35" spans="2:7">
       <c r="B35" s="97" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C35" s="320">
         <f>DCF!C11</f>
@@ -19775,7 +19775,7 @@
         <v>CNY</v>
       </c>
       <c r="E35" s="97" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="F35" s="330">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
@@ -19784,7 +19784,7 @@
     </row>
     <row r="36" spans="2:7">
       <c r="B36" s="97" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C36" s="321">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
@@ -19795,15 +19795,15 @@
         <v>CNY</v>
       </c>
       <c r="E36" s="97" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="F36" s="331" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="38" spans="2:7" ht="13.9">
       <c r="B38" s="34" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C38" s="35"/>
       <c r="D38" s="35"/>
@@ -19817,24 +19817,24 @@
         <v>1-stage DCF</v>
       </c>
       <c r="E39" s="222" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="40" spans="2:7">
       <c r="B40" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C40" s="126">
         <f>Normalized_FCF!E116</f>
         <v>0.4665778415257858</v>
       </c>
       <c r="E40" s="97" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="41" spans="2:7">
       <c r="B41" s="97" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C41" s="455">
         <f>DCF!C16</f>
@@ -19844,7 +19844,7 @@
     </row>
     <row r="43" spans="2:7" ht="13.9">
       <c r="B43" s="34" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C43" s="35"/>
       <c r="D43" s="35"/>
@@ -19854,15 +19854,15 @@
     </row>
     <row r="44" spans="2:7" ht="13.15">
       <c r="B44" s="106" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E44" s="222" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="45" spans="2:7">
       <c r="B45" s="139" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C45" s="150">
         <f>C18</f>
@@ -19870,24 +19870,24 @@
       </c>
       <c r="D45" s="137"/>
       <c r="E45" s="221" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="46" spans="2:7">
       <c r="B46" s="114" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C46" s="138">
         <v>2.38559171477595E-2</v>
       </c>
       <c r="D46" s="138"/>
       <c r="E46" s="221" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="47" spans="2:7">
       <c r="B47" s="97" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
@@ -19898,24 +19898,24 @@
         <v>CNY</v>
       </c>
       <c r="E47" s="221" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="49" spans="2:7" ht="13.15">
       <c r="B49" s="106" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C49" s="218" t="str">
         <f>IF(Scenarios!C50="Y",Scenarios!B50,"")&amp;IF(Scenarios!C51="Y",Scenarios!B51,"")&amp;IF(Scenarios!C52="Y",Scenarios!B52,"")&amp;" "&amp;IF(Scenarios!C53="Y",Scenarios!B53,"")</f>
         <v xml:space="preserve">Negative Growth </v>
       </c>
       <c r="E49" s="222" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="50" spans="2:7">
       <c r="B50" s="97" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C50" s="218" t="str">
         <f>IF(C36&lt;C35,"Y","N")</f>
@@ -19925,19 +19925,19 @@
     </row>
     <row r="51" spans="2:7">
       <c r="B51" s="97" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C51" s="218" t="str">
         <f>IF(C50="Y","N",IF(C46&gt;8%,"N","Y"))</f>
         <v>N</v>
       </c>
       <c r="E51" s="221" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="52" spans="2:7">
       <c r="B52" s="97" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C52" s="218" t="str">
         <f>IF(C46&gt;8%,"Y","N")</f>
@@ -19947,14 +19947,14 @@
     </row>
     <row r="53" spans="2:7">
       <c r="B53" s="97" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C53" s="217" t="str">
         <f>IF(F53&gt;50%,"Y","N")</f>
         <v>N</v>
       </c>
       <c r="E53" s="126" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="F53" s="249">
         <f>BS!D89/C36</f>
@@ -19963,7 +19963,7 @@
     </row>
     <row r="55" spans="2:7" ht="13.9">
       <c r="B55" s="34" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C55" s="35"/>
       <c r="D55" s="35"/>
@@ -19973,12 +19973,12 @@
     </row>
     <row r="56" spans="2:7" ht="13.15">
       <c r="B56" s="106" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="57" spans="2:7">
       <c r="B57" s="220" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C57" s="219">
         <f>Holding_Period</f>
@@ -19988,7 +19988,7 @@
     </row>
     <row r="58" spans="2:7">
       <c r="B58" s="97" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C58" s="155">
         <f>C33</f>
@@ -20001,34 +20001,34 @@
     </row>
     <row r="60" spans="2:7" ht="13.15">
       <c r="B60" s="106" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E60" s="413"/>
     </row>
     <row r="61" spans="2:7" ht="13.15">
       <c r="B61" s="153" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C61" s="153" t="s">
+        <v>102</v>
+      </c>
+      <c r="D61" s="153" t="s">
         <v>103</v>
-      </c>
-      <c r="D61" s="153" t="s">
-        <v>104</v>
       </c>
       <c r="E61" s="154" t="str">
         <f>"Buy below ("&amp;Market_currency&amp;")"</f>
         <v>Buy below (CNY)</v>
       </c>
       <c r="F61" s="154" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="G61" s="154" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="62" spans="2:7" ht="13.15">
       <c r="B62" s="302" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C62" s="119">
         <f>PV(F62, Holding_Period, -C58, 0)</f>
@@ -20053,7 +20053,7 @@
     </row>
     <row r="63" spans="2:7" ht="13.15">
       <c r="B63" s="302" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C63" s="119">
         <f>PV(F63, Holding_Period, -C58, 0)</f>
@@ -20078,28 +20078,28 @@
     </row>
     <row r="65" spans="2:7" ht="13.15">
       <c r="B65" s="153" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C65" s="153" t="s">
+        <v>102</v>
+      </c>
+      <c r="D65" s="153" t="s">
         <v>103</v>
-      </c>
-      <c r="D65" s="153" t="s">
-        <v>104</v>
       </c>
       <c r="E65" s="154" t="str">
         <f>"Sell above ("&amp;Market_currency&amp;")"</f>
         <v>Sell above (CNY)</v>
       </c>
       <c r="F65" s="154" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="G65" s="154" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="66" spans="2:7" ht="13.15">
       <c r="B66" s="302" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C66" s="119">
         <f>PV(F66, Holding_Period, -C58, 0)</f>
@@ -20124,7 +20124,7 @@
     </row>
     <row r="67" spans="2:7" ht="13.15">
       <c r="B67" s="302" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C67" s="119">
         <f>PV(F67, Holding_Period, -C58, 0)</f>
@@ -20174,7 +20174,7 @@
   <sheetData>
     <row r="2" spans="1:10" ht="13.9">
       <c r="A2" s="345" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B2" s="345"/>
       <c r="C2" s="345"/>
@@ -20188,7 +20188,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="E3" s="435" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="F3" s="436">
         <f>Thesis!F3</f>
@@ -20197,7 +20197,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="B4" s="422" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C4" s="423" t="str">
         <f>Thesis!C4</f>
@@ -20205,7 +20205,7 @@
       </c>
       <c r="D4" s="349"/>
       <c r="E4" s="434" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="F4" s="437" t="str">
         <f>Thesis!F4</f>
@@ -20214,14 +20214,14 @@
     </row>
     <row r="5" spans="1:10">
       <c r="B5" s="343" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C5" s="355" t="str">
         <f>Thesis!C5</f>
         <v>000858.SZ</v>
       </c>
       <c r="E5" s="438" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="F5" s="439" t="str">
         <f>Thesis!F5</f>
@@ -20230,7 +20230,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="B6" s="350" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C6" s="352" t="str">
         <f>Thesis!C6</f>
@@ -20240,7 +20240,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="B7" s="343" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C7" s="352" t="str">
         <f>Market_currency</f>
@@ -20251,16 +20251,16 @@
     </row>
     <row r="8" spans="1:10">
       <c r="B8" s="351" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>103.46</v>
+        <v>104.39</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="B9" s="351" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C9" s="353">
         <f>Common_Shares</f>
@@ -20269,18 +20269,18 @@
     </row>
     <row r="10" spans="1:10">
       <c r="B10" s="351" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>401591.16419729998</v>
+        <v>405201.05964195001</v>
       </c>
       <c r="D10" s="343" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.15806966595742114</v>
+        <v>0.15454049112527285</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20289,7 +20289,7 @@
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
       <c r="B12" s="474" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C12" s="474"/>
       <c r="D12" s="474"/>
@@ -20298,21 +20298,21 @@
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C14" s="348"/>
       <c r="D14" s="349"/>
     </row>
     <row r="15" spans="1:10">
       <c r="B15" s="343" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C15" s="358" t="str">
         <f>Thesis!C15</f>
         <v>N</v>
       </c>
       <c r="D15" s="351" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="E15" s="344" t="str">
         <f>IF(E17=C7,C7,E17&amp;"/"&amp;C7)</f>
@@ -20321,14 +20321,14 @@
     </row>
     <row r="16" spans="1:10">
       <c r="B16" s="343" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C16" s="358" t="str">
         <f>Thesis!C16</f>
         <v>N</v>
       </c>
       <c r="D16" s="351" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="E16" s="425">
         <f>Exchange_Rate</f>
@@ -20337,14 +20337,14 @@
     </row>
     <row r="17" spans="1:6">
       <c r="B17" s="343" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C17" s="424">
         <f>Terminal_Growth</f>
         <v>0.01</v>
       </c>
       <c r="D17" s="351" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E17" s="344" t="str">
         <f>Reporting_currency</f>
@@ -20361,7 +20361,7 @@
         <v>150.70538803259237</v>
       </c>
       <c r="D18" s="350" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="E18" s="426">
         <f>Thesis!E18</f>
@@ -20370,14 +20370,14 @@
     </row>
     <row r="19" spans="1:6">
       <c r="B19" s="350" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C19" s="352" t="str">
         <f>IF(Scenarios!C50="Y",Scenarios!B50,"")&amp;IF(Scenarios!C51="Y",Scenarios!B51,"")&amp;IF(Scenarios!C52="Y",Scenarios!B52,"")&amp;" "&amp;IF(Scenarios!C53="Y",Scenarios!B53,"")</f>
         <v xml:space="preserve">Negative Growth </v>
       </c>
       <c r="D19" s="343" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="E19" s="427">
         <f>EOMONTH(EDATE(BS!C1,E18+2),0)</f>
@@ -20390,14 +20390,14 @@
     </row>
     <row r="21" spans="1:6">
       <c r="B21" s="347" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C21" s="361" t="str">
         <f>C138&amp;" ("&amp;Market_currency&amp;")"</f>
         <v xml:space="preserve"> (CNY)</v>
       </c>
       <c r="D21" s="362" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E21" s="363">
         <f>Holding_Period</f>
@@ -20406,14 +20406,14 @@
     </row>
     <row r="22" spans="1:6">
       <c r="B22" s="343" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C22" s="364">
         <f>E140</f>
         <v>73.77572463932286</v>
       </c>
       <c r="D22" s="365" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="E22" s="366">
         <f>Thesis!E22</f>
@@ -20422,14 +20422,14 @@
     </row>
     <row r="23" spans="1:6">
       <c r="B23" s="343" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C23" s="367">
         <f>E141</f>
         <v>93.221662055898364</v>
       </c>
       <c r="D23" s="365" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="E23" s="368">
         <f>Thesis!E23</f>
@@ -20438,14 +20438,14 @@
     </row>
     <row r="24" spans="1:6">
       <c r="B24" s="343" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C24" s="367">
         <f>E144</f>
         <v>124.59667696127181</v>
       </c>
       <c r="D24" s="365" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E24" s="368">
         <f>Thesis!E24</f>
@@ -20454,14 +20454,14 @@
     </row>
     <row r="25" spans="1:6">
       <c r="B25" s="343" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C25" s="367">
         <f>E145</f>
         <v>129.61296430141905</v>
       </c>
       <c r="D25" s="365" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E25" s="368">
         <f>Thesis!E25</f>
@@ -20470,7 +20470,7 @@
     </row>
     <row r="27" spans="1:6" ht="13.9">
       <c r="A27" s="345" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B27" s="345"/>
       <c r="C27" s="345"/>
@@ -20480,7 +20480,7 @@
     </row>
     <row r="29" spans="1:6">
       <c r="B29" s="474" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C29" s="474"/>
       <c r="D29" s="474"/>
@@ -20489,7 +20489,7 @@
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
       <c r="B30" s="477" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C30" s="477"/>
       <c r="D30" s="477"/>
@@ -20498,7 +20498,7 @@
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C32" s="370">
         <f>scaling_factor</f>
@@ -20507,7 +20507,7 @@
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="470" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C33" s="470"/>
       <c r="D33" s="470"/>
@@ -20516,7 +20516,7 @@
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="372" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C34" s="373">
         <f>Normalized_FCF!C8</f>
@@ -20533,7 +20533,7 @@
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
       <c r="B36" s="470" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C36" s="470"/>
       <c r="D36" s="470"/>
@@ -20542,7 +20542,7 @@
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="372" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C37" s="373">
         <f>Normalized_FCF!C15</f>
@@ -20555,7 +20555,7 @@
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="375" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C38" s="373">
         <f>Normalized_FCF!C16</f>
@@ -20568,7 +20568,7 @@
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="470" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="C40" s="470"/>
       <c r="D40" s="470"/>
@@ -20577,7 +20577,7 @@
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="372" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C41" s="373">
         <f>Normalized_FCF!C9</f>
@@ -20590,7 +20590,7 @@
     </row>
     <row r="43" spans="2:6">
       <c r="B43" s="470" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C43" s="470"/>
       <c r="D43" s="470"/>
@@ -20599,7 +20599,7 @@
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="372" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C44" s="376">
         <f>Normalized_FCF!C46</f>
@@ -20614,7 +20614,7 @@
     </row>
     <row r="45" spans="2:6">
       <c r="B45" s="372" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C45" s="376">
         <f>Normalized_FCF!C45</f>
@@ -20629,7 +20629,7 @@
     </row>
     <row r="46" spans="2:6">
       <c r="B46" s="372" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C46" s="373">
         <f>Normalized_FCF!C10</f>
@@ -20642,12 +20642,12 @@
     </row>
     <row r="48" spans="2:6">
       <c r="B48" s="343" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="49" spans="2:6">
       <c r="B49" s="372" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C49" s="373">
         <f>Normalized_FCF!C13</f>
@@ -20660,7 +20660,7 @@
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="470" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C51" s="470"/>
       <c r="D51" s="470"/>
@@ -20669,7 +20669,7 @@
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="372" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C52" s="373">
         <f>Normalized_FCF!C12</f>
@@ -20682,7 +20682,7 @@
     </row>
     <row r="54" spans="2:6">
       <c r="B54" s="470" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C54" s="476"/>
       <c r="D54" s="476"/>
@@ -20691,7 +20691,7 @@
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C55" s="373">
         <f>Normalized_FCF!C17</f>
@@ -20704,7 +20704,7 @@
     </row>
     <row r="57" spans="2:6">
       <c r="B57" s="474" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C57" s="474"/>
       <c r="D57" s="474"/>
@@ -20713,7 +20713,7 @@
     </row>
     <row r="58" spans="2:6">
       <c r="B58" s="474" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C58" s="474"/>
       <c r="D58" s="474"/>
@@ -20722,7 +20722,7 @@
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C60" s="373">
         <f>Normalized_FCF!G19</f>
@@ -20735,7 +20735,7 @@
     </row>
     <row r="61" spans="2:6">
       <c r="B61" s="372" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C61" s="373">
         <f>Normalized_FCF!C19</f>
@@ -20748,24 +20748,24 @@
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="377" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>7.4210548430808848E-2</v>
+        <v>7.3549414126367299E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
     <row r="63" spans="2:6">
       <c r="B63" s="377" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>2.756717572008506E-2</v>
+        <v>2.7321582527061981E-2</v>
       </c>
       <c r="E63" s="372" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="F63" s="380">
         <f>Normalized_FCF!C90</f>
@@ -20774,18 +20774,18 @@
     </row>
     <row r="65" spans="1:6">
       <c r="B65" s="369" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C65" s="381" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D65" s="381" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="66" spans="1:6">
       <c r="B66" s="372" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C66" s="378">
         <f>Normalized_FCF!E119</f>
@@ -20840,7 +20840,7 @@
     </row>
     <row r="71" spans="1:6" ht="13.9">
       <c r="A71" s="345" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B71" s="345"/>
       <c r="C71" s="345"/>
@@ -20854,7 +20854,7 @@
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
       <c r="B73" s="474" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="C73" s="474"/>
       <c r="D73" s="474"/>
@@ -20863,7 +20863,7 @@
     </row>
     <row r="74" spans="1:6">
       <c r="B74" s="477" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C74" s="477"/>
       <c r="D74" s="477"/>
@@ -20872,12 +20872,12 @@
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="77" spans="1:6">
       <c r="B77" s="474" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C77" s="474"/>
       <c r="D77" s="474"/>
@@ -20886,7 +20886,7 @@
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C78" s="373">
         <f>DCF!F4</f>
@@ -20899,7 +20899,7 @@
     </row>
     <row r="79" spans="1:6">
       <c r="B79" s="372" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C79" s="387">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
@@ -20912,7 +20912,7 @@
     </row>
     <row r="80" spans="1:6">
       <c r="B80" s="382" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C80" s="388">
         <f>IF(BS!G31/BS!G27&gt;300%,"nm",BS!G31/BS!G27)</f>
@@ -20921,7 +20921,7 @@
     </row>
     <row r="81" spans="1:6">
       <c r="B81" s="382" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C81" s="389">
         <f>IF(BS!C50&gt;30,"nm",BS!C50)</f>
@@ -20930,12 +20930,12 @@
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="343" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="84" spans="1:6">
       <c r="B84" s="343" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C84" s="373">
         <f>DCF!F5</f>
@@ -20948,7 +20948,7 @@
     </row>
     <row r="85" spans="1:6">
       <c r="B85" s="382" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C85" s="390">
         <f>BS!C66</f>
@@ -20961,7 +20961,7 @@
     </row>
     <row r="86" spans="1:6">
       <c r="B86" s="372" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C86" s="387">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
@@ -20974,12 +20974,12 @@
     </row>
     <row r="88" spans="1:6">
       <c r="B88" s="343" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="89" spans="1:6">
       <c r="B89" s="343" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C89" s="373">
         <f>DCF!F6</f>
@@ -20992,7 +20992,7 @@
     </row>
     <row r="90" spans="1:6">
       <c r="B90" s="372" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C90" s="387">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
@@ -21005,7 +21005,7 @@
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="372" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="C92" s="387">
         <f>DCF!F8</f>
@@ -21018,7 +21018,7 @@
     </row>
     <row r="94" spans="1:6" ht="13.9">
       <c r="A94" s="345" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B94" s="345"/>
       <c r="C94" s="345"/>
@@ -21032,7 +21032,7 @@
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
       <c r="B96" s="474" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C96" s="474"/>
       <c r="D96" s="474"/>
@@ -21042,7 +21042,7 @@
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
       <c r="B97" s="477" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C97" s="477"/>
       <c r="D97" s="477"/>
@@ -21052,7 +21052,7 @@
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
       <c r="B98" s="477" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C98" s="477"/>
       <c r="D98" s="477"/>
@@ -21065,13 +21065,13 @@
     <row r="100" spans="1:6">
       <c r="A100" s="385"/>
       <c r="B100" s="369" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="101" spans="1:6">
       <c r="A101" s="385"/>
       <c r="B101" s="372" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C101" s="368">
         <f>E25+C103</f>
@@ -21081,7 +21081,7 @@
     <row r="102" spans="1:6">
       <c r="A102" s="385"/>
       <c r="B102" s="382" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C102" s="383">
         <f>E25</f>
@@ -21091,7 +21091,7 @@
     <row r="103" spans="1:6">
       <c r="A103" s="385"/>
       <c r="B103" s="382" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C103" s="383">
         <f>IF(C15="Y",1%,0)+IF(C16="Y",1%,0)</f>
@@ -21101,7 +21101,7 @@
     <row r="104" spans="1:6">
       <c r="A104" s="385"/>
       <c r="B104" s="372" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C104" s="368">
         <v>0</v>
@@ -21114,14 +21114,14 @@
     <row r="106" spans="1:6">
       <c r="A106" s="385"/>
       <c r="B106" s="393" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C106" s="392"/>
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
       <c r="B107" s="474" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C107" s="474"/>
       <c r="D107" s="474"/>
@@ -21131,7 +21131,7 @@
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
       <c r="B108" s="474" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="C108" s="474"/>
       <c r="D108" s="474"/>
@@ -21144,13 +21144,13 @@
     <row r="110" spans="1:6">
       <c r="A110" s="385"/>
       <c r="B110" s="369" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="111" spans="1:6">
       <c r="A111" s="385"/>
       <c r="B111" s="375" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C111" s="394">
         <f>BS!D47</f>
@@ -21164,7 +21164,7 @@
     <row r="112" spans="1:6">
       <c r="A112" s="385"/>
       <c r="B112" s="372" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C112" s="394">
         <f>DCF!C11</f>
@@ -21181,7 +21181,7 @@
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
       <c r="B114" s="474" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="C114" s="474"/>
       <c r="D114" s="474"/>
@@ -21194,25 +21194,25 @@
     <row r="116" spans="1:6">
       <c r="A116" s="385"/>
       <c r="B116" s="369" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="117" spans="1:6">
       <c r="A117" s="385"/>
       <c r="B117" s="342" t="s">
+        <v>375</v>
+      </c>
+      <c r="C117" s="342" t="s">
         <v>376</v>
       </c>
-      <c r="C117" s="342" t="s">
+      <c r="D117" s="342" t="s">
+        <v>98</v>
+      </c>
+      <c r="E117" s="342" t="s">
         <v>377</v>
       </c>
-      <c r="D117" s="342" t="s">
-        <v>99</v>
-      </c>
-      <c r="E117" s="342" t="s">
+      <c r="F117" s="342" t="s">
         <v>378</v>
-      </c>
-      <c r="F117" s="342" t="s">
-        <v>379</v>
       </c>
     </row>
     <row r="118" spans="1:6">
@@ -21329,7 +21329,7 @@
     </row>
     <row r="124" spans="1:6">
       <c r="B124" s="470" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="C124" s="470"/>
       <c r="D124" s="470"/>
@@ -21338,7 +21338,7 @@
     </row>
     <row r="125" spans="1:6">
       <c r="B125" s="372" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C125" s="404">
         <f>Scenarios!C36</f>
@@ -21351,7 +21351,7 @@
     </row>
     <row r="127" spans="1:6">
       <c r="B127" s="472" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="C127" s="472"/>
       <c r="D127" s="472"/>
@@ -21360,7 +21360,7 @@
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B129" s="345"/>
       <c r="C129" s="345"/>
@@ -21370,7 +21370,7 @@
     </row>
     <row r="131" spans="1:6">
       <c r="B131" s="473" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C131" s="473"/>
       <c r="D131" s="473"/>
@@ -21379,7 +21379,7 @@
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
       <c r="B132" s="474" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C132" s="474"/>
       <c r="D132" s="474"/>
@@ -21388,12 +21388,12 @@
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="135" spans="1:6">
       <c r="B135" s="343" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C135" s="405">
         <f>E21</f>
@@ -21402,7 +21402,7 @@
     </row>
     <row r="136" spans="1:6">
       <c r="B136" s="343" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C136" s="406">
         <f>Scenarios!C58</f>
@@ -21415,33 +21415,33 @@
     </row>
     <row r="138" spans="1:6">
       <c r="B138" s="369" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C138" s="407"/>
       <c r="D138" s="407"/>
     </row>
     <row r="139" spans="1:6">
       <c r="B139" s="340" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C139" s="340" t="str">
         <f>"PV("&amp;Holding_Period&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
       <c r="D139" s="340" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="E139" s="341" t="str">
         <f>"Buy below ("&amp;Market_currency&amp;")"</f>
         <v>Buy below (CNY)</v>
       </c>
       <c r="F139" s="341" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="408" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C140" s="409">
         <f>Scenarios!C62</f>
@@ -21462,7 +21462,7 @@
     </row>
     <row r="141" spans="1:6">
       <c r="B141" s="408" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C141" s="409">
         <f>Scenarios!C63</f>
@@ -21483,26 +21483,26 @@
     </row>
     <row r="143" spans="1:6">
       <c r="B143" s="340" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C143" s="340" t="str">
         <f>"PV("&amp;Holding_Period&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
       <c r="D143" s="340" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="E143" s="341" t="str">
         <f>"Sell above ("&amp;Market_currency&amp;")"</f>
         <v>Sell above (CNY)</v>
       </c>
       <c r="F143" s="341" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="144" spans="1:6">
       <c r="B144" s="408" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C144" s="409">
         <f>Scenarios!C66</f>
@@ -21523,7 +21523,7 @@
     </row>
     <row r="145" spans="1:6">
       <c r="B145" s="408" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C145" s="409">
         <f>Scenarios!C67</f>
@@ -21544,7 +21544,7 @@
     </row>
     <row r="147" spans="1:6" ht="13.9">
       <c r="A147" s="345" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B147" s="345"/>
       <c r="C147" s="345"/>
@@ -21554,7 +21554,7 @@
     </row>
     <row r="149" spans="1:6">
       <c r="B149" s="475" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C149" s="474"/>
       <c r="D149" s="474"/>
@@ -21563,12 +21563,12 @@
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="152" spans="1:6">
       <c r="B152" s="476" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="C152" s="476"/>
       <c r="D152" s="476"/>
@@ -21577,27 +21577,27 @@
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="154" spans="1:6">
       <c r="B154" s="412" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="155" spans="1:6">
       <c r="B155" s="412" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="157" spans="1:6">
       <c r="B157" s="343" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="158" spans="1:6" ht="24.5" customHeight="1">
       <c r="B158" s="470" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C158" s="470"/>
       <c r="D158" s="470"/>
@@ -21606,12 +21606,12 @@
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="343" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="161" spans="2:6">
       <c r="B161" s="471" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C161" s="471"/>
       <c r="D161" s="471"/>
@@ -21620,7 +21620,7 @@
     </row>
     <row r="162" spans="2:6">
       <c r="B162" s="471" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C162" s="471"/>
       <c r="D162" s="471"/>
@@ -21629,22 +21629,22 @@
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="165" spans="2:6">
       <c r="B165" s="412" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="166" spans="2:6">
       <c r="B166" s="412" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="167" spans="2:6">
       <c r="B167" s="412" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
   </sheetData>

--- a/financial_models/opportunities/000858.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/000858.SZ_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B68AD4DF-0114-4768-B7AB-F8AF4C669978}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B978E315-0E5B-4790-84E3-191A86FA288A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4986,30 +4986,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5019,6 +5019,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5028,16 +5037,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5407,7 +5407,7 @@
         <v>347</v>
       </c>
       <c r="C8" s="47">
-        <v>104.39</v>
+        <v>102.07</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5425,14 +5425,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>405201.05964195001</v>
+        <v>396195.72907035</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>524</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.15454049112527285</v>
+        <v>0.1634253086406206</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5440,13 +5440,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="462" t="s">
+      <c r="B12" s="460" t="s">
         <v>352</v>
       </c>
-      <c r="C12" s="462"/>
-      <c r="D12" s="462"/>
-      <c r="E12" s="462"/>
-      <c r="F12" s="462"/>
+      <c r="C12" s="460"/>
+      <c r="D12" s="460"/>
+      <c r="E12" s="460"/>
+      <c r="F12" s="460"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5624,22 +5624,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="462" t="s">
+      <c r="B29" s="460" t="s">
         <v>353</v>
       </c>
-      <c r="C29" s="462"/>
-      <c r="D29" s="462"/>
-      <c r="E29" s="462"/>
-      <c r="F29" s="462"/>
+      <c r="C29" s="460"/>
+      <c r="D29" s="460"/>
+      <c r="E29" s="460"/>
+      <c r="F29" s="460"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="466" t="s">
+      <c r="B30" s="462" t="s">
         <v>265</v>
       </c>
-      <c r="C30" s="466"/>
-      <c r="D30" s="466"/>
-      <c r="E30" s="466"/>
-      <c r="F30" s="466"/>
+      <c r="C30" s="462"/>
+      <c r="D30" s="462"/>
+      <c r="E30" s="462"/>
+      <c r="F30" s="462"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5651,13 +5651,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="463" t="s">
+      <c r="B33" s="461" t="s">
         <v>195</v>
       </c>
-      <c r="C33" s="463"/>
-      <c r="D33" s="463"/>
-      <c r="E33" s="463"/>
-      <c r="F33" s="463"/>
+      <c r="C33" s="461"/>
+      <c r="D33" s="461"/>
+      <c r="E33" s="461"/>
+      <c r="F33" s="461"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5677,13 +5677,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="463" t="s">
+      <c r="B36" s="461" t="s">
         <v>197</v>
       </c>
-      <c r="C36" s="463"/>
-      <c r="D36" s="463"/>
-      <c r="E36" s="463"/>
-      <c r="F36" s="463"/>
+      <c r="C36" s="461"/>
+      <c r="D36" s="461"/>
+      <c r="E36" s="461"/>
+      <c r="F36" s="461"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5712,13 +5712,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="463" t="s">
+      <c r="B40" s="461" t="s">
         <v>200</v>
       </c>
-      <c r="C40" s="463"/>
-      <c r="D40" s="463"/>
-      <c r="E40" s="463"/>
-      <c r="F40" s="463"/>
+      <c r="C40" s="461"/>
+      <c r="D40" s="461"/>
+      <c r="E40" s="461"/>
+      <c r="F40" s="461"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5734,13 +5734,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="463" t="s">
+      <c r="B43" s="461" t="s">
         <v>204</v>
       </c>
-      <c r="C43" s="463"/>
-      <c r="D43" s="463"/>
-      <c r="E43" s="463"/>
-      <c r="F43" s="463"/>
+      <c r="C43" s="461"/>
+      <c r="D43" s="461"/>
+      <c r="E43" s="461"/>
+      <c r="F43" s="461"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5804,13 +5804,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="463" t="s">
+      <c r="B51" s="461" t="s">
         <v>205</v>
       </c>
-      <c r="C51" s="463"/>
-      <c r="D51" s="463"/>
-      <c r="E51" s="463"/>
-      <c r="F51" s="463"/>
+      <c r="C51" s="461"/>
+      <c r="D51" s="461"/>
+      <c r="E51" s="461"/>
+      <c r="F51" s="461"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5826,7 +5826,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="463" t="s">
+      <c r="B54" s="461" t="s">
         <v>264</v>
       </c>
       <c r="C54" s="464"/>
@@ -5848,22 +5848,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="462" t="s">
+      <c r="B57" s="460" t="s">
         <v>269</v>
       </c>
-      <c r="C57" s="462"/>
-      <c r="D57" s="462"/>
-      <c r="E57" s="462"/>
-      <c r="F57" s="462"/>
+      <c r="C57" s="460"/>
+      <c r="D57" s="460"/>
+      <c r="E57" s="460"/>
+      <c r="F57" s="460"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="462" t="s">
+      <c r="B58" s="460" t="s">
         <v>281</v>
       </c>
-      <c r="C58" s="462"/>
-      <c r="D58" s="462"/>
-      <c r="E58" s="462"/>
-      <c r="F58" s="462"/>
+      <c r="C58" s="460"/>
+      <c r="D58" s="460"/>
+      <c r="E58" s="460"/>
+      <c r="F58" s="460"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>7.3549414126367299E-2</v>
+        <v>7.5221155487914998E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5907,7 +5907,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>2.7321582527061981E-2</v>
+        <v>2.7942588419711964E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>320</v>
@@ -5998,13 +5998,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="462" t="s">
+      <c r="B73" s="460" t="s">
         <v>475</v>
       </c>
-      <c r="C73" s="462"/>
-      <c r="D73" s="462"/>
-      <c r="E73" s="462"/>
-      <c r="F73" s="462"/>
+      <c r="C73" s="460"/>
+      <c r="D73" s="460"/>
+      <c r="E73" s="460"/>
+      <c r="F73" s="460"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6023,13 +6023,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="462" t="s">
+      <c r="B77" s="460" t="s">
         <v>270</v>
       </c>
-      <c r="C77" s="462"/>
-      <c r="D77" s="462"/>
-      <c r="E77" s="462"/>
-      <c r="F77" s="462"/>
+      <c r="C77" s="460"/>
+      <c r="D77" s="460"/>
+      <c r="E77" s="460"/>
+      <c r="F77" s="460"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6198,31 +6198,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="462" t="s">
+      <c r="B96" s="460" t="s">
         <v>482</v>
       </c>
-      <c r="C96" s="462"/>
-      <c r="D96" s="462"/>
-      <c r="E96" s="462"/>
-      <c r="F96" s="462"/>
+      <c r="C96" s="460"/>
+      <c r="D96" s="460"/>
+      <c r="E96" s="460"/>
+      <c r="F96" s="460"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="466" t="s">
+      <c r="B97" s="462" t="s">
         <v>481</v>
       </c>
-      <c r="C97" s="466"/>
-      <c r="D97" s="466"/>
-      <c r="E97" s="466"/>
-      <c r="F97" s="466"/>
+      <c r="C97" s="462"/>
+      <c r="D97" s="462"/>
+      <c r="E97" s="462"/>
+      <c r="F97" s="462"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="466" t="s">
+      <c r="B98" s="462" t="s">
         <v>480</v>
       </c>
-      <c r="C98" s="466"/>
-      <c r="D98" s="466"/>
-      <c r="E98" s="466"/>
-      <c r="F98" s="466"/>
+      <c r="C98" s="462"/>
+      <c r="D98" s="462"/>
+      <c r="E98" s="462"/>
+      <c r="F98" s="462"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6272,22 +6272,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="462" t="s">
+      <c r="B107" s="460" t="s">
         <v>282</v>
       </c>
-      <c r="C107" s="462"/>
-      <c r="D107" s="462"/>
-      <c r="E107" s="462"/>
-      <c r="F107" s="462"/>
+      <c r="C107" s="460"/>
+      <c r="D107" s="460"/>
+      <c r="E107" s="460"/>
+      <c r="F107" s="460"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="462" t="s">
+      <c r="B108" s="460" t="s">
         <v>283</v>
       </c>
-      <c r="C108" s="462"/>
-      <c r="D108" s="462"/>
-      <c r="E108" s="462"/>
-      <c r="F108" s="462"/>
+      <c r="C108" s="460"/>
+      <c r="D108" s="460"/>
+      <c r="E108" s="460"/>
+      <c r="F108" s="460"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6321,13 +6321,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="462" t="s">
+      <c r="B114" s="460" t="s">
         <v>488</v>
       </c>
-      <c r="C114" s="462"/>
-      <c r="D114" s="462"/>
-      <c r="E114" s="462"/>
-      <c r="F114" s="462"/>
+      <c r="C114" s="460"/>
+      <c r="D114" s="460"/>
+      <c r="E114" s="460"/>
+      <c r="F114" s="460"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6462,13 +6462,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="463" t="s">
+      <c r="B124" s="461" t="s">
         <v>354</v>
       </c>
-      <c r="C124" s="463"/>
-      <c r="D124" s="463"/>
-      <c r="E124" s="463"/>
-      <c r="F124" s="463"/>
+      <c r="C124" s="461"/>
+      <c r="D124" s="461"/>
+      <c r="E124" s="461"/>
+      <c r="F124" s="461"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6503,22 +6503,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="467" t="s">
+      <c r="B131" s="463" t="s">
         <v>284</v>
       </c>
-      <c r="C131" s="467"/>
-      <c r="D131" s="467"/>
-      <c r="E131" s="467"/>
-      <c r="F131" s="467"/>
+      <c r="C131" s="463"/>
+      <c r="D131" s="463"/>
+      <c r="E131" s="463"/>
+      <c r="F131" s="463"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="462" t="s">
+      <c r="B132" s="460" t="s">
         <v>356</v>
       </c>
-      <c r="C132" s="462"/>
-      <c r="D132" s="462"/>
-      <c r="E132" s="462"/>
-      <c r="F132" s="462"/>
+      <c r="C132" s="460"/>
+      <c r="D132" s="460"/>
+      <c r="E132" s="460"/>
+      <c r="F132" s="460"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6694,13 +6694,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="461" t="s">
+      <c r="B149" s="467" t="s">
         <v>357</v>
       </c>
-      <c r="C149" s="462"/>
-      <c r="D149" s="462"/>
-      <c r="E149" s="462"/>
-      <c r="F149" s="462"/>
+      <c r="C149" s="460"/>
+      <c r="D149" s="460"/>
+      <c r="E149" s="460"/>
+      <c r="F149" s="460"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6737,13 +6737,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="463" t="s">
+      <c r="B158" s="461" t="s">
         <v>435</v>
       </c>
-      <c r="C158" s="463"/>
-      <c r="D158" s="463"/>
-      <c r="E158" s="463"/>
-      <c r="F158" s="463"/>
+      <c r="C158" s="461"/>
+      <c r="D158" s="461"/>
+      <c r="E158" s="461"/>
+      <c r="F158" s="461"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6751,22 +6751,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="460" t="s">
+      <c r="B161" s="466" t="s">
         <v>293</v>
       </c>
-      <c r="C161" s="460"/>
-      <c r="D161" s="460"/>
-      <c r="E161" s="460"/>
-      <c r="F161" s="460"/>
+      <c r="C161" s="466"/>
+      <c r="D161" s="466"/>
+      <c r="E161" s="466"/>
+      <c r="F161" s="466"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="460" t="s">
+      <c r="B162" s="466" t="s">
         <v>294</v>
       </c>
-      <c r="C162" s="460"/>
-      <c r="D162" s="460"/>
-      <c r="E162" s="460"/>
-      <c r="F162" s="460"/>
+      <c r="C162" s="466"/>
+      <c r="D162" s="466"/>
+      <c r="E162" s="466"/>
+      <c r="F162" s="466"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6790,6 +6790,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6806,18 +6818,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -14008,16 +14008,16 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>2.7321582527061981E-2</v>
+        <v>2.7942588419711964E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>2.7321582527061981E-2</v>
+        <v>2.7942588419711964E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>4.0262477248778621E-2</v>
+        <v>4.1177623199764875E-2</v>
       </c>
       <c r="I92" s="22" t="str">
         <f t="shared" si="38"/>
@@ -15229,18 +15229,18 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>7.3549414126367299E-2</v>
+        <v>7.5221155487914998E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>6.5297279451469084E-2</v>
+        <v>6.6781453923178774E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>6.2867309926206316E-2</v>
+        <v>6.4296252407139001E-2</v>
       </c>
       <c r="I124" s="74" t="str">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
@@ -15286,11 +15286,11 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.1918493780966203E-2</v>
+        <v>8.3780460133193527E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.7790461875896569E-2</v>
+        <v>7.9558600129566406E-2</v>
       </c>
       <c r="I125" s="22" t="str">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -19748,7 +19748,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>104.39</v>
+        <v>102.07</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19759,7 +19759,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.15454049112527285</v>
+        <v>0.1634253086406206</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -20255,7 +20255,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>104.39</v>
+        <v>102.07</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20273,14 +20273,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>405201.05964195001</v>
+        <v>396195.72907035</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>525</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.15454049112527285</v>
+        <v>0.1634253086406206</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20288,13 +20288,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="474" t="s">
+      <c r="B12" s="471" t="s">
         <v>494</v>
       </c>
-      <c r="C12" s="474"/>
-      <c r="D12" s="474"/>
-      <c r="E12" s="474"/>
-      <c r="F12" s="474"/>
+      <c r="C12" s="471"/>
+      <c r="D12" s="471"/>
+      <c r="E12" s="471"/>
+      <c r="F12" s="471"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20479,22 +20479,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="474" t="s">
+      <c r="B29" s="471" t="s">
         <v>495</v>
       </c>
-      <c r="C29" s="474"/>
-      <c r="D29" s="474"/>
-      <c r="E29" s="474"/>
-      <c r="F29" s="474"/>
+      <c r="C29" s="471"/>
+      <c r="D29" s="471"/>
+      <c r="E29" s="471"/>
+      <c r="F29" s="471"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="477" t="s">
+      <c r="B30" s="472" t="s">
         <v>496</v>
       </c>
-      <c r="C30" s="477"/>
-      <c r="D30" s="477"/>
-      <c r="E30" s="477"/>
-      <c r="F30" s="477"/>
+      <c r="C30" s="472"/>
+      <c r="D30" s="472"/>
+      <c r="E30" s="472"/>
+      <c r="F30" s="472"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20684,10 +20684,10 @@
       <c r="B54" s="470" t="s">
         <v>503</v>
       </c>
-      <c r="C54" s="476"/>
-      <c r="D54" s="476"/>
-      <c r="E54" s="476"/>
-      <c r="F54" s="476"/>
+      <c r="C54" s="473"/>
+      <c r="D54" s="473"/>
+      <c r="E54" s="473"/>
+      <c r="F54" s="473"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20703,22 +20703,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="474" t="s">
+      <c r="B57" s="471" t="s">
         <v>504</v>
       </c>
-      <c r="C57" s="474"/>
-      <c r="D57" s="474"/>
-      <c r="E57" s="474"/>
-      <c r="F57" s="474"/>
+      <c r="C57" s="471"/>
+      <c r="D57" s="471"/>
+      <c r="E57" s="471"/>
+      <c r="F57" s="471"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="474" t="s">
+      <c r="B58" s="471" t="s">
         <v>505</v>
       </c>
-      <c r="C58" s="474"/>
-      <c r="D58" s="474"/>
-      <c r="E58" s="474"/>
-      <c r="F58" s="474"/>
+      <c r="C58" s="471"/>
+      <c r="D58" s="471"/>
+      <c r="E58" s="471"/>
+      <c r="F58" s="471"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20752,7 +20752,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>7.3549414126367299E-2</v>
+        <v>7.5221155487914998E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20762,7 +20762,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>2.7321582527061981E-2</v>
+        <v>2.7942588419711964E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>370</v>
@@ -20853,22 +20853,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="474" t="s">
+      <c r="B73" s="471" t="s">
         <v>506</v>
       </c>
-      <c r="C73" s="474"/>
-      <c r="D73" s="474"/>
-      <c r="E73" s="474"/>
-      <c r="F73" s="474"/>
+      <c r="C73" s="471"/>
+      <c r="D73" s="471"/>
+      <c r="E73" s="471"/>
+      <c r="F73" s="471"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="477" t="s">
+      <c r="B74" s="472" t="s">
         <v>476</v>
       </c>
-      <c r="C74" s="477"/>
-      <c r="D74" s="477"/>
-      <c r="E74" s="477"/>
-      <c r="F74" s="477"/>
+      <c r="C74" s="472"/>
+      <c r="D74" s="472"/>
+      <c r="E74" s="472"/>
+      <c r="F74" s="472"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -20876,13 +20876,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="474" t="s">
+      <c r="B77" s="471" t="s">
         <v>507</v>
       </c>
-      <c r="C77" s="474"/>
-      <c r="D77" s="474"/>
-      <c r="E77" s="474"/>
-      <c r="F77" s="474"/>
+      <c r="C77" s="471"/>
+      <c r="D77" s="471"/>
+      <c r="E77" s="471"/>
+      <c r="F77" s="471"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21031,33 +21031,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="474" t="s">
+      <c r="B96" s="471" t="s">
         <v>510</v>
       </c>
-      <c r="C96" s="474"/>
-      <c r="D96" s="474"/>
-      <c r="E96" s="474"/>
-      <c r="F96" s="474"/>
+      <c r="C96" s="471"/>
+      <c r="D96" s="471"/>
+      <c r="E96" s="471"/>
+      <c r="F96" s="471"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="477" t="s">
+      <c r="B97" s="472" t="s">
         <v>511</v>
       </c>
-      <c r="C97" s="477"/>
-      <c r="D97" s="477"/>
-      <c r="E97" s="477"/>
-      <c r="F97" s="477"/>
+      <c r="C97" s="472"/>
+      <c r="D97" s="472"/>
+      <c r="E97" s="472"/>
+      <c r="F97" s="472"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="477" t="s">
+      <c r="B98" s="472" t="s">
         <v>512</v>
       </c>
-      <c r="C98" s="477"/>
-      <c r="D98" s="477"/>
-      <c r="E98" s="477"/>
-      <c r="F98" s="477"/>
+      <c r="C98" s="472"/>
+      <c r="D98" s="472"/>
+      <c r="E98" s="472"/>
+      <c r="F98" s="472"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21120,23 +21120,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="474" t="s">
+      <c r="B107" s="471" t="s">
         <v>513</v>
       </c>
-      <c r="C107" s="474"/>
-      <c r="D107" s="474"/>
-      <c r="E107" s="474"/>
-      <c r="F107" s="474"/>
+      <c r="C107" s="471"/>
+      <c r="D107" s="471"/>
+      <c r="E107" s="471"/>
+      <c r="F107" s="471"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="474" t="s">
+      <c r="B108" s="471" t="s">
         <v>532</v>
       </c>
-      <c r="C108" s="474"/>
-      <c r="D108" s="474"/>
-      <c r="E108" s="474"/>
-      <c r="F108" s="474"/>
+      <c r="C108" s="471"/>
+      <c r="D108" s="471"/>
+      <c r="E108" s="471"/>
+      <c r="F108" s="471"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21180,13 +21180,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="474" t="s">
+      <c r="B114" s="471" t="s">
         <v>514</v>
       </c>
-      <c r="C114" s="474"/>
-      <c r="D114" s="474"/>
-      <c r="E114" s="474"/>
-      <c r="F114" s="474"/>
+      <c r="C114" s="471"/>
+      <c r="D114" s="471"/>
+      <c r="E114" s="471"/>
+      <c r="F114" s="471"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21350,13 +21350,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="472" t="s">
+      <c r="B127" s="475" t="s">
         <v>516</v>
       </c>
-      <c r="C127" s="472"/>
-      <c r="D127" s="472"/>
-      <c r="E127" s="472"/>
-      <c r="F127" s="472"/>
+      <c r="C127" s="475"/>
+      <c r="D127" s="475"/>
+      <c r="E127" s="475"/>
+      <c r="F127" s="475"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21369,22 +21369,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="473" t="s">
+      <c r="B131" s="476" t="s">
         <v>517</v>
       </c>
-      <c r="C131" s="473"/>
-      <c r="D131" s="473"/>
-      <c r="E131" s="473"/>
-      <c r="F131" s="473"/>
+      <c r="C131" s="476"/>
+      <c r="D131" s="476"/>
+      <c r="E131" s="476"/>
+      <c r="F131" s="476"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="474" t="s">
+      <c r="B132" s="471" t="s">
         <v>518</v>
       </c>
-      <c r="C132" s="474"/>
-      <c r="D132" s="474"/>
-      <c r="E132" s="474"/>
-      <c r="F132" s="474"/>
+      <c r="C132" s="471"/>
+      <c r="D132" s="471"/>
+      <c r="E132" s="471"/>
+      <c r="F132" s="471"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21553,13 +21553,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="475" t="s">
+      <c r="B149" s="477" t="s">
         <v>519</v>
       </c>
-      <c r="C149" s="474"/>
-      <c r="D149" s="474"/>
-      <c r="E149" s="474"/>
-      <c r="F149" s="474"/>
+      <c r="C149" s="471"/>
+      <c r="D149" s="471"/>
+      <c r="E149" s="471"/>
+      <c r="F149" s="471"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21567,13 +21567,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="476" t="s">
+      <c r="B152" s="473" t="s">
         <v>520</v>
       </c>
-      <c r="C152" s="476"/>
-      <c r="D152" s="476"/>
-      <c r="E152" s="476"/>
-      <c r="F152" s="476"/>
+      <c r="C152" s="473"/>
+      <c r="D152" s="473"/>
+      <c r="E152" s="473"/>
+      <c r="F152" s="473"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21610,22 +21610,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="471" t="s">
+      <c r="B161" s="474" t="s">
         <v>385</v>
       </c>
-      <c r="C161" s="471"/>
-      <c r="D161" s="471"/>
-      <c r="E161" s="471"/>
-      <c r="F161" s="471"/>
+      <c r="C161" s="474"/>
+      <c r="D161" s="474"/>
+      <c r="E161" s="474"/>
+      <c r="F161" s="474"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="471" t="s">
+      <c r="B162" s="474" t="s">
         <v>386</v>
       </c>
-      <c r="C162" s="471"/>
-      <c r="D162" s="471"/>
-      <c r="E162" s="471"/>
-      <c r="F162" s="471"/>
+      <c r="C162" s="474"/>
+      <c r="D162" s="474"/>
+      <c r="E162" s="474"/>
+      <c r="F162" s="474"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21649,12 +21649,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21669,15 +21672,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/000858.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/000858.SZ_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B978E315-0E5B-4790-84E3-191A86FA288A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E18BE62D-498B-4537-BB2E-8F71BC3B4E19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1103" yWindow="1103" windowWidth="12690" windowHeight="7642" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4986,30 +4986,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5019,25 +5019,25 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5407,7 +5407,7 @@
         <v>347</v>
       </c>
       <c r="C8" s="47">
-        <v>102.07</v>
+        <v>103.44</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5425,14 +5425,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>396195.72907035</v>
+        <v>401513.5320372</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>524</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.1634253086406206</v>
+        <v>0.1581460336011149</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5440,13 +5440,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="460" t="s">
+      <c r="B12" s="462" t="s">
         <v>352</v>
       </c>
-      <c r="C12" s="460"/>
-      <c r="D12" s="460"/>
-      <c r="E12" s="460"/>
-      <c r="F12" s="460"/>
+      <c r="C12" s="462"/>
+      <c r="D12" s="462"/>
+      <c r="E12" s="462"/>
+      <c r="F12" s="462"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5624,22 +5624,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="460" t="s">
+      <c r="B29" s="462" t="s">
         <v>353</v>
       </c>
-      <c r="C29" s="460"/>
-      <c r="D29" s="460"/>
-      <c r="E29" s="460"/>
-      <c r="F29" s="460"/>
+      <c r="C29" s="462"/>
+      <c r="D29" s="462"/>
+      <c r="E29" s="462"/>
+      <c r="F29" s="462"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="462" t="s">
+      <c r="B30" s="466" t="s">
         <v>265</v>
       </c>
-      <c r="C30" s="462"/>
-      <c r="D30" s="462"/>
-      <c r="E30" s="462"/>
-      <c r="F30" s="462"/>
+      <c r="C30" s="466"/>
+      <c r="D30" s="466"/>
+      <c r="E30" s="466"/>
+      <c r="F30" s="466"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5651,13 +5651,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="461" t="s">
+      <c r="B33" s="463" t="s">
         <v>195</v>
       </c>
-      <c r="C33" s="461"/>
-      <c r="D33" s="461"/>
-      <c r="E33" s="461"/>
-      <c r="F33" s="461"/>
+      <c r="C33" s="463"/>
+      <c r="D33" s="463"/>
+      <c r="E33" s="463"/>
+      <c r="F33" s="463"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5677,13 +5677,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="461" t="s">
+      <c r="B36" s="463" t="s">
         <v>197</v>
       </c>
-      <c r="C36" s="461"/>
-      <c r="D36" s="461"/>
-      <c r="E36" s="461"/>
-      <c r="F36" s="461"/>
+      <c r="C36" s="463"/>
+      <c r="D36" s="463"/>
+      <c r="E36" s="463"/>
+      <c r="F36" s="463"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5712,13 +5712,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="461" t="s">
+      <c r="B40" s="463" t="s">
         <v>200</v>
       </c>
-      <c r="C40" s="461"/>
-      <c r="D40" s="461"/>
-      <c r="E40" s="461"/>
-      <c r="F40" s="461"/>
+      <c r="C40" s="463"/>
+      <c r="D40" s="463"/>
+      <c r="E40" s="463"/>
+      <c r="F40" s="463"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5734,13 +5734,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="461" t="s">
+      <c r="B43" s="463" t="s">
         <v>204</v>
       </c>
-      <c r="C43" s="461"/>
-      <c r="D43" s="461"/>
-      <c r="E43" s="461"/>
-      <c r="F43" s="461"/>
+      <c r="C43" s="463"/>
+      <c r="D43" s="463"/>
+      <c r="E43" s="463"/>
+      <c r="F43" s="463"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5804,13 +5804,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="461" t="s">
+      <c r="B51" s="463" t="s">
         <v>205</v>
       </c>
-      <c r="C51" s="461"/>
-      <c r="D51" s="461"/>
-      <c r="E51" s="461"/>
-      <c r="F51" s="461"/>
+      <c r="C51" s="463"/>
+      <c r="D51" s="463"/>
+      <c r="E51" s="463"/>
+      <c r="F51" s="463"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5826,7 +5826,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="461" t="s">
+      <c r="B54" s="463" t="s">
         <v>264</v>
       </c>
       <c r="C54" s="464"/>
@@ -5848,22 +5848,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="460" t="s">
+      <c r="B57" s="462" t="s">
         <v>269</v>
       </c>
-      <c r="C57" s="460"/>
-      <c r="D57" s="460"/>
-      <c r="E57" s="460"/>
-      <c r="F57" s="460"/>
+      <c r="C57" s="462"/>
+      <c r="D57" s="462"/>
+      <c r="E57" s="462"/>
+      <c r="F57" s="462"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="460" t="s">
+      <c r="B58" s="462" t="s">
         <v>281</v>
       </c>
-      <c r="C58" s="460"/>
-      <c r="D58" s="460"/>
-      <c r="E58" s="460"/>
-      <c r="F58" s="460"/>
+      <c r="C58" s="462"/>
+      <c r="D58" s="462"/>
+      <c r="E58" s="462"/>
+      <c r="F58" s="462"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>7.5221155487914998E-2</v>
+        <v>7.4224896951387107E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5907,7 +5907,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>2.7942588419711964E-2</v>
+        <v>2.7572505800464039E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>320</v>
@@ -5998,13 +5998,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="460" t="s">
+      <c r="B73" s="462" t="s">
         <v>475</v>
       </c>
-      <c r="C73" s="460"/>
-      <c r="D73" s="460"/>
-      <c r="E73" s="460"/>
-      <c r="F73" s="460"/>
+      <c r="C73" s="462"/>
+      <c r="D73" s="462"/>
+      <c r="E73" s="462"/>
+      <c r="F73" s="462"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6023,13 +6023,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="460" t="s">
+      <c r="B77" s="462" t="s">
         <v>270</v>
       </c>
-      <c r="C77" s="460"/>
-      <c r="D77" s="460"/>
-      <c r="E77" s="460"/>
-      <c r="F77" s="460"/>
+      <c r="C77" s="462"/>
+      <c r="D77" s="462"/>
+      <c r="E77" s="462"/>
+      <c r="F77" s="462"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6198,31 +6198,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="460" t="s">
+      <c r="B96" s="462" t="s">
         <v>482</v>
       </c>
-      <c r="C96" s="460"/>
-      <c r="D96" s="460"/>
-      <c r="E96" s="460"/>
-      <c r="F96" s="460"/>
+      <c r="C96" s="462"/>
+      <c r="D96" s="462"/>
+      <c r="E96" s="462"/>
+      <c r="F96" s="462"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="462" t="s">
+      <c r="B97" s="466" t="s">
         <v>481</v>
       </c>
-      <c r="C97" s="462"/>
-      <c r="D97" s="462"/>
-      <c r="E97" s="462"/>
-      <c r="F97" s="462"/>
+      <c r="C97" s="466"/>
+      <c r="D97" s="466"/>
+      <c r="E97" s="466"/>
+      <c r="F97" s="466"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="462" t="s">
+      <c r="B98" s="466" t="s">
         <v>480</v>
       </c>
-      <c r="C98" s="462"/>
-      <c r="D98" s="462"/>
-      <c r="E98" s="462"/>
-      <c r="F98" s="462"/>
+      <c r="C98" s="466"/>
+      <c r="D98" s="466"/>
+      <c r="E98" s="466"/>
+      <c r="F98" s="466"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6272,22 +6272,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="460" t="s">
+      <c r="B107" s="462" t="s">
         <v>282</v>
       </c>
-      <c r="C107" s="460"/>
-      <c r="D107" s="460"/>
-      <c r="E107" s="460"/>
-      <c r="F107" s="460"/>
+      <c r="C107" s="462"/>
+      <c r="D107" s="462"/>
+      <c r="E107" s="462"/>
+      <c r="F107" s="462"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="460" t="s">
+      <c r="B108" s="462" t="s">
         <v>283</v>
       </c>
-      <c r="C108" s="460"/>
-      <c r="D108" s="460"/>
-      <c r="E108" s="460"/>
-      <c r="F108" s="460"/>
+      <c r="C108" s="462"/>
+      <c r="D108" s="462"/>
+      <c r="E108" s="462"/>
+      <c r="F108" s="462"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6321,13 +6321,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="460" t="s">
+      <c r="B114" s="462" t="s">
         <v>488</v>
       </c>
-      <c r="C114" s="460"/>
-      <c r="D114" s="460"/>
-      <c r="E114" s="460"/>
-      <c r="F114" s="460"/>
+      <c r="C114" s="462"/>
+      <c r="D114" s="462"/>
+      <c r="E114" s="462"/>
+      <c r="F114" s="462"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6462,13 +6462,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="461" t="s">
+      <c r="B124" s="463" t="s">
         <v>354</v>
       </c>
-      <c r="C124" s="461"/>
-      <c r="D124" s="461"/>
-      <c r="E124" s="461"/>
-      <c r="F124" s="461"/>
+      <c r="C124" s="463"/>
+      <c r="D124" s="463"/>
+      <c r="E124" s="463"/>
+      <c r="F124" s="463"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6503,22 +6503,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="463" t="s">
+      <c r="B131" s="467" t="s">
         <v>284</v>
       </c>
-      <c r="C131" s="463"/>
-      <c r="D131" s="463"/>
-      <c r="E131" s="463"/>
-      <c r="F131" s="463"/>
+      <c r="C131" s="467"/>
+      <c r="D131" s="467"/>
+      <c r="E131" s="467"/>
+      <c r="F131" s="467"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="460" t="s">
+      <c r="B132" s="462" t="s">
         <v>356</v>
       </c>
-      <c r="C132" s="460"/>
-      <c r="D132" s="460"/>
-      <c r="E132" s="460"/>
-      <c r="F132" s="460"/>
+      <c r="C132" s="462"/>
+      <c r="D132" s="462"/>
+      <c r="E132" s="462"/>
+      <c r="F132" s="462"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6694,13 +6694,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="467" t="s">
+      <c r="B149" s="461" t="s">
         <v>357</v>
       </c>
-      <c r="C149" s="460"/>
-      <c r="D149" s="460"/>
-      <c r="E149" s="460"/>
-      <c r="F149" s="460"/>
+      <c r="C149" s="462"/>
+      <c r="D149" s="462"/>
+      <c r="E149" s="462"/>
+      <c r="F149" s="462"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6737,13 +6737,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="461" t="s">
+      <c r="B158" s="463" t="s">
         <v>435</v>
       </c>
-      <c r="C158" s="461"/>
-      <c r="D158" s="461"/>
-      <c r="E158" s="461"/>
-      <c r="F158" s="461"/>
+      <c r="C158" s="463"/>
+      <c r="D158" s="463"/>
+      <c r="E158" s="463"/>
+      <c r="F158" s="463"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6751,22 +6751,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="466" t="s">
+      <c r="B161" s="460" t="s">
         <v>293</v>
       </c>
-      <c r="C161" s="466"/>
-      <c r="D161" s="466"/>
-      <c r="E161" s="466"/>
-      <c r="F161" s="466"/>
+      <c r="C161" s="460"/>
+      <c r="D161" s="460"/>
+      <c r="E161" s="460"/>
+      <c r="F161" s="460"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="466" t="s">
+      <c r="B162" s="460" t="s">
         <v>294</v>
       </c>
-      <c r="C162" s="466"/>
-      <c r="D162" s="466"/>
-      <c r="E162" s="466"/>
-      <c r="F162" s="466"/>
+      <c r="C162" s="460"/>
+      <c r="D162" s="460"/>
+      <c r="E162" s="460"/>
+      <c r="F162" s="460"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6790,18 +6790,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6818,6 +6806,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -14008,16 +14008,16 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>2.7942588419711964E-2</v>
+        <v>2.7572505800464039E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>2.7942588419711964E-2</v>
+        <v>2.7572505800464039E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>4.1177623199764875E-2</v>
+        <v>4.0632250580046408E-2</v>
       </c>
       <c r="I92" s="22" t="str">
         <f t="shared" si="38"/>
@@ -15229,18 +15229,18 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>7.5221155487914998E-2</v>
+        <v>7.4224896951387107E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>6.6781453923178774E-2</v>
+        <v>6.5896974110004419E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>6.4296252407139001E-2</v>
+        <v>6.3444687579240891E-2</v>
       </c>
       <c r="I124" s="74" t="str">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
@@ -15286,11 +15286,11 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.3780460133193527E-2</v>
+        <v>8.2670838803123189E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.9558600129566406E-2</v>
+        <v>7.8504894772088579E-2</v>
       </c>
       <c r="I125" s="22" t="str">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -19748,7 +19748,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>102.07</v>
+        <v>103.44</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19759,7 +19759,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.1634253086406206</v>
+        <v>0.1581460336011149</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -20255,7 +20255,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>102.07</v>
+        <v>103.44</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20273,14 +20273,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>396195.72907035</v>
+        <v>401513.5320372</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>525</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.1634253086406206</v>
+        <v>0.1581460336011149</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20288,13 +20288,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="471" t="s">
+      <c r="B12" s="474" t="s">
         <v>494</v>
       </c>
-      <c r="C12" s="471"/>
-      <c r="D12" s="471"/>
-      <c r="E12" s="471"/>
-      <c r="F12" s="471"/>
+      <c r="C12" s="474"/>
+      <c r="D12" s="474"/>
+      <c r="E12" s="474"/>
+      <c r="F12" s="474"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20479,22 +20479,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="471" t="s">
+      <c r="B29" s="474" t="s">
         <v>495</v>
       </c>
-      <c r="C29" s="471"/>
-      <c r="D29" s="471"/>
-      <c r="E29" s="471"/>
-      <c r="F29" s="471"/>
+      <c r="C29" s="474"/>
+      <c r="D29" s="474"/>
+      <c r="E29" s="474"/>
+      <c r="F29" s="474"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="472" t="s">
+      <c r="B30" s="477" t="s">
         <v>496</v>
       </c>
-      <c r="C30" s="472"/>
-      <c r="D30" s="472"/>
-      <c r="E30" s="472"/>
-      <c r="F30" s="472"/>
+      <c r="C30" s="477"/>
+      <c r="D30" s="477"/>
+      <c r="E30" s="477"/>
+      <c r="F30" s="477"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20684,10 +20684,10 @@
       <c r="B54" s="470" t="s">
         <v>503</v>
       </c>
-      <c r="C54" s="473"/>
-      <c r="D54" s="473"/>
-      <c r="E54" s="473"/>
-      <c r="F54" s="473"/>
+      <c r="C54" s="476"/>
+      <c r="D54" s="476"/>
+      <c r="E54" s="476"/>
+      <c r="F54" s="476"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20703,22 +20703,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="471" t="s">
+      <c r="B57" s="474" t="s">
         <v>504</v>
       </c>
-      <c r="C57" s="471"/>
-      <c r="D57" s="471"/>
-      <c r="E57" s="471"/>
-      <c r="F57" s="471"/>
+      <c r="C57" s="474"/>
+      <c r="D57" s="474"/>
+      <c r="E57" s="474"/>
+      <c r="F57" s="474"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="471" t="s">
+      <c r="B58" s="474" t="s">
         <v>505</v>
       </c>
-      <c r="C58" s="471"/>
-      <c r="D58" s="471"/>
-      <c r="E58" s="471"/>
-      <c r="F58" s="471"/>
+      <c r="C58" s="474"/>
+      <c r="D58" s="474"/>
+      <c r="E58" s="474"/>
+      <c r="F58" s="474"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20752,7 +20752,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>7.5221155487914998E-2</v>
+        <v>7.4224896951387107E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20762,7 +20762,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>2.7942588419711964E-2</v>
+        <v>2.7572505800464039E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>370</v>
@@ -20853,22 +20853,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="471" t="s">
+      <c r="B73" s="474" t="s">
         <v>506</v>
       </c>
-      <c r="C73" s="471"/>
-      <c r="D73" s="471"/>
-      <c r="E73" s="471"/>
-      <c r="F73" s="471"/>
+      <c r="C73" s="474"/>
+      <c r="D73" s="474"/>
+      <c r="E73" s="474"/>
+      <c r="F73" s="474"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="472" t="s">
+      <c r="B74" s="477" t="s">
         <v>476</v>
       </c>
-      <c r="C74" s="472"/>
-      <c r="D74" s="472"/>
-      <c r="E74" s="472"/>
-      <c r="F74" s="472"/>
+      <c r="C74" s="477"/>
+      <c r="D74" s="477"/>
+      <c r="E74" s="477"/>
+      <c r="F74" s="477"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -20876,13 +20876,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="471" t="s">
+      <c r="B77" s="474" t="s">
         <v>507</v>
       </c>
-      <c r="C77" s="471"/>
-      <c r="D77" s="471"/>
-      <c r="E77" s="471"/>
-      <c r="F77" s="471"/>
+      <c r="C77" s="474"/>
+      <c r="D77" s="474"/>
+      <c r="E77" s="474"/>
+      <c r="F77" s="474"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21031,33 +21031,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="471" t="s">
+      <c r="B96" s="474" t="s">
         <v>510</v>
       </c>
-      <c r="C96" s="471"/>
-      <c r="D96" s="471"/>
-      <c r="E96" s="471"/>
-      <c r="F96" s="471"/>
+      <c r="C96" s="474"/>
+      <c r="D96" s="474"/>
+      <c r="E96" s="474"/>
+      <c r="F96" s="474"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="472" t="s">
+      <c r="B97" s="477" t="s">
         <v>511</v>
       </c>
-      <c r="C97" s="472"/>
-      <c r="D97" s="472"/>
-      <c r="E97" s="472"/>
-      <c r="F97" s="472"/>
+      <c r="C97" s="477"/>
+      <c r="D97" s="477"/>
+      <c r="E97" s="477"/>
+      <c r="F97" s="477"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="472" t="s">
+      <c r="B98" s="477" t="s">
         <v>512</v>
       </c>
-      <c r="C98" s="472"/>
-      <c r="D98" s="472"/>
-      <c r="E98" s="472"/>
-      <c r="F98" s="472"/>
+      <c r="C98" s="477"/>
+      <c r="D98" s="477"/>
+      <c r="E98" s="477"/>
+      <c r="F98" s="477"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21120,23 +21120,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="471" t="s">
+      <c r="B107" s="474" t="s">
         <v>513</v>
       </c>
-      <c r="C107" s="471"/>
-      <c r="D107" s="471"/>
-      <c r="E107" s="471"/>
-      <c r="F107" s="471"/>
+      <c r="C107" s="474"/>
+      <c r="D107" s="474"/>
+      <c r="E107" s="474"/>
+      <c r="F107" s="474"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="471" t="s">
+      <c r="B108" s="474" t="s">
         <v>532</v>
       </c>
-      <c r="C108" s="471"/>
-      <c r="D108" s="471"/>
-      <c r="E108" s="471"/>
-      <c r="F108" s="471"/>
+      <c r="C108" s="474"/>
+      <c r="D108" s="474"/>
+      <c r="E108" s="474"/>
+      <c r="F108" s="474"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21180,13 +21180,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="471" t="s">
+      <c r="B114" s="474" t="s">
         <v>514</v>
       </c>
-      <c r="C114" s="471"/>
-      <c r="D114" s="471"/>
-      <c r="E114" s="471"/>
-      <c r="F114" s="471"/>
+      <c r="C114" s="474"/>
+      <c r="D114" s="474"/>
+      <c r="E114" s="474"/>
+      <c r="F114" s="474"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21350,13 +21350,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="475" t="s">
+      <c r="B127" s="472" t="s">
         <v>516</v>
       </c>
-      <c r="C127" s="475"/>
-      <c r="D127" s="475"/>
-      <c r="E127" s="475"/>
-      <c r="F127" s="475"/>
+      <c r="C127" s="472"/>
+      <c r="D127" s="472"/>
+      <c r="E127" s="472"/>
+      <c r="F127" s="472"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21369,22 +21369,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="476" t="s">
+      <c r="B131" s="473" t="s">
         <v>517</v>
       </c>
-      <c r="C131" s="476"/>
-      <c r="D131" s="476"/>
-      <c r="E131" s="476"/>
-      <c r="F131" s="476"/>
+      <c r="C131" s="473"/>
+      <c r="D131" s="473"/>
+      <c r="E131" s="473"/>
+      <c r="F131" s="473"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="471" t="s">
+      <c r="B132" s="474" t="s">
         <v>518</v>
       </c>
-      <c r="C132" s="471"/>
-      <c r="D132" s="471"/>
-      <c r="E132" s="471"/>
-      <c r="F132" s="471"/>
+      <c r="C132" s="474"/>
+      <c r="D132" s="474"/>
+      <c r="E132" s="474"/>
+      <c r="F132" s="474"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21553,13 +21553,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="477" t="s">
+      <c r="B149" s="475" t="s">
         <v>519</v>
       </c>
-      <c r="C149" s="471"/>
-      <c r="D149" s="471"/>
-      <c r="E149" s="471"/>
-      <c r="F149" s="471"/>
+      <c r="C149" s="474"/>
+      <c r="D149" s="474"/>
+      <c r="E149" s="474"/>
+      <c r="F149" s="474"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21567,13 +21567,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="473" t="s">
+      <c r="B152" s="476" t="s">
         <v>520</v>
       </c>
-      <c r="C152" s="473"/>
-      <c r="D152" s="473"/>
-      <c r="E152" s="473"/>
-      <c r="F152" s="473"/>
+      <c r="C152" s="476"/>
+      <c r="D152" s="476"/>
+      <c r="E152" s="476"/>
+      <c r="F152" s="476"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21610,22 +21610,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="474" t="s">
+      <c r="B161" s="471" t="s">
         <v>385</v>
       </c>
-      <c r="C161" s="474"/>
-      <c r="D161" s="474"/>
-      <c r="E161" s="474"/>
-      <c r="F161" s="474"/>
+      <c r="C161" s="471"/>
+      <c r="D161" s="471"/>
+      <c r="E161" s="471"/>
+      <c r="F161" s="471"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="474" t="s">
+      <c r="B162" s="471" t="s">
         <v>386</v>
       </c>
-      <c r="C162" s="474"/>
-      <c r="D162" s="474"/>
-      <c r="E162" s="474"/>
-      <c r="F162" s="474"/>
+      <c r="C162" s="471"/>
+      <c r="D162" s="471"/>
+      <c r="E162" s="471"/>
+      <c r="F162" s="471"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21649,15 +21649,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21672,12 +21669,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/000858.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/000858.SZ_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E18BE62D-498B-4537-BB2E-8F71BC3B4E19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09C0DF11-D3AE-4B9D-99CE-BAC30D3C5B59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1103" yWindow="1103" windowWidth="12690" windowHeight="7642" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="735" yWindow="735" windowWidth="12690" windowHeight="7643" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4986,30 +4986,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5019,6 +5019,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5028,16 +5037,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5407,7 +5407,7 @@
         <v>347</v>
       </c>
       <c r="C8" s="47">
-        <v>103.44</v>
+        <v>101.86</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5425,14 +5425,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>401513.5320372</v>
+        <v>395380.59138930001</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>524</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.1581460336011149</v>
+        <v>0.16424302340067351</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5440,13 +5440,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="462" t="s">
+      <c r="B12" s="460" t="s">
         <v>352</v>
       </c>
-      <c r="C12" s="462"/>
-      <c r="D12" s="462"/>
-      <c r="E12" s="462"/>
-      <c r="F12" s="462"/>
+      <c r="C12" s="460"/>
+      <c r="D12" s="460"/>
+      <c r="E12" s="460"/>
+      <c r="F12" s="460"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5624,22 +5624,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="462" t="s">
+      <c r="B29" s="460" t="s">
         <v>353</v>
       </c>
-      <c r="C29" s="462"/>
-      <c r="D29" s="462"/>
-      <c r="E29" s="462"/>
-      <c r="F29" s="462"/>
+      <c r="C29" s="460"/>
+      <c r="D29" s="460"/>
+      <c r="E29" s="460"/>
+      <c r="F29" s="460"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="466" t="s">
+      <c r="B30" s="462" t="s">
         <v>265</v>
       </c>
-      <c r="C30" s="466"/>
-      <c r="D30" s="466"/>
-      <c r="E30" s="466"/>
-      <c r="F30" s="466"/>
+      <c r="C30" s="462"/>
+      <c r="D30" s="462"/>
+      <c r="E30" s="462"/>
+      <c r="F30" s="462"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5651,13 +5651,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="463" t="s">
+      <c r="B33" s="461" t="s">
         <v>195</v>
       </c>
-      <c r="C33" s="463"/>
-      <c r="D33" s="463"/>
-      <c r="E33" s="463"/>
-      <c r="F33" s="463"/>
+      <c r="C33" s="461"/>
+      <c r="D33" s="461"/>
+      <c r="E33" s="461"/>
+      <c r="F33" s="461"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5677,13 +5677,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="463" t="s">
+      <c r="B36" s="461" t="s">
         <v>197</v>
       </c>
-      <c r="C36" s="463"/>
-      <c r="D36" s="463"/>
-      <c r="E36" s="463"/>
-      <c r="F36" s="463"/>
+      <c r="C36" s="461"/>
+      <c r="D36" s="461"/>
+      <c r="E36" s="461"/>
+      <c r="F36" s="461"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5712,13 +5712,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="463" t="s">
+      <c r="B40" s="461" t="s">
         <v>200</v>
       </c>
-      <c r="C40" s="463"/>
-      <c r="D40" s="463"/>
-      <c r="E40" s="463"/>
-      <c r="F40" s="463"/>
+      <c r="C40" s="461"/>
+      <c r="D40" s="461"/>
+      <c r="E40" s="461"/>
+      <c r="F40" s="461"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5734,13 +5734,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="463" t="s">
+      <c r="B43" s="461" t="s">
         <v>204</v>
       </c>
-      <c r="C43" s="463"/>
-      <c r="D43" s="463"/>
-      <c r="E43" s="463"/>
-      <c r="F43" s="463"/>
+      <c r="C43" s="461"/>
+      <c r="D43" s="461"/>
+      <c r="E43" s="461"/>
+      <c r="F43" s="461"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5804,13 +5804,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="463" t="s">
+      <c r="B51" s="461" t="s">
         <v>205</v>
       </c>
-      <c r="C51" s="463"/>
-      <c r="D51" s="463"/>
-      <c r="E51" s="463"/>
-      <c r="F51" s="463"/>
+      <c r="C51" s="461"/>
+      <c r="D51" s="461"/>
+      <c r="E51" s="461"/>
+      <c r="F51" s="461"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5826,7 +5826,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="463" t="s">
+      <c r="B54" s="461" t="s">
         <v>264</v>
       </c>
       <c r="C54" s="464"/>
@@ -5848,22 +5848,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="462" t="s">
+      <c r="B57" s="460" t="s">
         <v>269</v>
       </c>
-      <c r="C57" s="462"/>
-      <c r="D57" s="462"/>
-      <c r="E57" s="462"/>
-      <c r="F57" s="462"/>
+      <c r="C57" s="460"/>
+      <c r="D57" s="460"/>
+      <c r="E57" s="460"/>
+      <c r="F57" s="460"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="462" t="s">
+      <c r="B58" s="460" t="s">
         <v>281</v>
       </c>
-      <c r="C58" s="462"/>
-      <c r="D58" s="462"/>
-      <c r="E58" s="462"/>
-      <c r="F58" s="462"/>
+      <c r="C58" s="460"/>
+      <c r="D58" s="460"/>
+      <c r="E58" s="460"/>
+      <c r="F58" s="460"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>7.4224896951387107E-2</v>
+        <v>7.537623542756218E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5907,7 +5907,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>2.7572505800464039E-2</v>
+        <v>2.8000196347928531E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>320</v>
@@ -5998,13 +5998,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="462" t="s">
+      <c r="B73" s="460" t="s">
         <v>475</v>
       </c>
-      <c r="C73" s="462"/>
-      <c r="D73" s="462"/>
-      <c r="E73" s="462"/>
-      <c r="F73" s="462"/>
+      <c r="C73" s="460"/>
+      <c r="D73" s="460"/>
+      <c r="E73" s="460"/>
+      <c r="F73" s="460"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6023,13 +6023,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="462" t="s">
+      <c r="B77" s="460" t="s">
         <v>270</v>
       </c>
-      <c r="C77" s="462"/>
-      <c r="D77" s="462"/>
-      <c r="E77" s="462"/>
-      <c r="F77" s="462"/>
+      <c r="C77" s="460"/>
+      <c r="D77" s="460"/>
+      <c r="E77" s="460"/>
+      <c r="F77" s="460"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6198,31 +6198,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="462" t="s">
+      <c r="B96" s="460" t="s">
         <v>482</v>
       </c>
-      <c r="C96" s="462"/>
-      <c r="D96" s="462"/>
-      <c r="E96" s="462"/>
-      <c r="F96" s="462"/>
+      <c r="C96" s="460"/>
+      <c r="D96" s="460"/>
+      <c r="E96" s="460"/>
+      <c r="F96" s="460"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="466" t="s">
+      <c r="B97" s="462" t="s">
         <v>481</v>
       </c>
-      <c r="C97" s="466"/>
-      <c r="D97" s="466"/>
-      <c r="E97" s="466"/>
-      <c r="F97" s="466"/>
+      <c r="C97" s="462"/>
+      <c r="D97" s="462"/>
+      <c r="E97" s="462"/>
+      <c r="F97" s="462"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="466" t="s">
+      <c r="B98" s="462" t="s">
         <v>480</v>
       </c>
-      <c r="C98" s="466"/>
-      <c r="D98" s="466"/>
-      <c r="E98" s="466"/>
-      <c r="F98" s="466"/>
+      <c r="C98" s="462"/>
+      <c r="D98" s="462"/>
+      <c r="E98" s="462"/>
+      <c r="F98" s="462"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6272,22 +6272,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="462" t="s">
+      <c r="B107" s="460" t="s">
         <v>282</v>
       </c>
-      <c r="C107" s="462"/>
-      <c r="D107" s="462"/>
-      <c r="E107" s="462"/>
-      <c r="F107" s="462"/>
+      <c r="C107" s="460"/>
+      <c r="D107" s="460"/>
+      <c r="E107" s="460"/>
+      <c r="F107" s="460"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="462" t="s">
+      <c r="B108" s="460" t="s">
         <v>283</v>
       </c>
-      <c r="C108" s="462"/>
-      <c r="D108" s="462"/>
-      <c r="E108" s="462"/>
-      <c r="F108" s="462"/>
+      <c r="C108" s="460"/>
+      <c r="D108" s="460"/>
+      <c r="E108" s="460"/>
+      <c r="F108" s="460"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6321,13 +6321,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="462" t="s">
+      <c r="B114" s="460" t="s">
         <v>488</v>
       </c>
-      <c r="C114" s="462"/>
-      <c r="D114" s="462"/>
-      <c r="E114" s="462"/>
-      <c r="F114" s="462"/>
+      <c r="C114" s="460"/>
+      <c r="D114" s="460"/>
+      <c r="E114" s="460"/>
+      <c r="F114" s="460"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6462,13 +6462,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="463" t="s">
+      <c r="B124" s="461" t="s">
         <v>354</v>
       </c>
-      <c r="C124" s="463"/>
-      <c r="D124" s="463"/>
-      <c r="E124" s="463"/>
-      <c r="F124" s="463"/>
+      <c r="C124" s="461"/>
+      <c r="D124" s="461"/>
+      <c r="E124" s="461"/>
+      <c r="F124" s="461"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6503,22 +6503,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="467" t="s">
+      <c r="B131" s="463" t="s">
         <v>284</v>
       </c>
-      <c r="C131" s="467"/>
-      <c r="D131" s="467"/>
-      <c r="E131" s="467"/>
-      <c r="F131" s="467"/>
+      <c r="C131" s="463"/>
+      <c r="D131" s="463"/>
+      <c r="E131" s="463"/>
+      <c r="F131" s="463"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="462" t="s">
+      <c r="B132" s="460" t="s">
         <v>356</v>
       </c>
-      <c r="C132" s="462"/>
-      <c r="D132" s="462"/>
-      <c r="E132" s="462"/>
-      <c r="F132" s="462"/>
+      <c r="C132" s="460"/>
+      <c r="D132" s="460"/>
+      <c r="E132" s="460"/>
+      <c r="F132" s="460"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6694,13 +6694,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="461" t="s">
+      <c r="B149" s="467" t="s">
         <v>357</v>
       </c>
-      <c r="C149" s="462"/>
-      <c r="D149" s="462"/>
-      <c r="E149" s="462"/>
-      <c r="F149" s="462"/>
+      <c r="C149" s="460"/>
+      <c r="D149" s="460"/>
+      <c r="E149" s="460"/>
+      <c r="F149" s="460"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6737,13 +6737,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="463" t="s">
+      <c r="B158" s="461" t="s">
         <v>435</v>
       </c>
-      <c r="C158" s="463"/>
-      <c r="D158" s="463"/>
-      <c r="E158" s="463"/>
-      <c r="F158" s="463"/>
+      <c r="C158" s="461"/>
+      <c r="D158" s="461"/>
+      <c r="E158" s="461"/>
+      <c r="F158" s="461"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6751,22 +6751,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="460" t="s">
+      <c r="B161" s="466" t="s">
         <v>293</v>
       </c>
-      <c r="C161" s="460"/>
-      <c r="D161" s="460"/>
-      <c r="E161" s="460"/>
-      <c r="F161" s="460"/>
+      <c r="C161" s="466"/>
+      <c r="D161" s="466"/>
+      <c r="E161" s="466"/>
+      <c r="F161" s="466"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="460" t="s">
+      <c r="B162" s="466" t="s">
         <v>294</v>
       </c>
-      <c r="C162" s="460"/>
-      <c r="D162" s="460"/>
-      <c r="E162" s="460"/>
-      <c r="F162" s="460"/>
+      <c r="C162" s="466"/>
+      <c r="D162" s="466"/>
+      <c r="E162" s="466"/>
+      <c r="F162" s="466"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6790,6 +6790,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6806,18 +6818,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -14008,16 +14008,16 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>2.7572505800464039E-2</v>
+        <v>2.8000196347928531E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>2.7572505800464039E-2</v>
+        <v>2.8000196347928531E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>4.0632250580046408E-2</v>
+        <v>4.1262517180443749E-2</v>
       </c>
       <c r="I92" s="22" t="str">
         <f t="shared" si="38"/>
@@ -15229,18 +15229,18 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>7.4224896951387107E-2</v>
+        <v>7.537623542756218E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>6.5896974110004419E-2</v>
+        <v>6.691913412466971E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>6.3444687579240891E-2</v>
+        <v>6.4428808984848596E-2</v>
       </c>
       <c r="I124" s="74" t="str">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
@@ -15286,11 +15286,11 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.2670838803123189E-2</v>
+        <v>8.3953186391076601E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.8504894772088579E-2</v>
+        <v>7.972262237605382E-2</v>
       </c>
       <c r="I125" s="22" t="str">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -19748,7 +19748,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>103.44</v>
+        <v>101.86</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19759,7 +19759,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.1581460336011149</v>
+        <v>0.16424302340067351</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -20255,7 +20255,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>103.44</v>
+        <v>101.86</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20273,14 +20273,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>401513.5320372</v>
+        <v>395380.59138930001</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>525</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.1581460336011149</v>
+        <v>0.16424302340067351</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20288,13 +20288,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="474" t="s">
+      <c r="B12" s="471" t="s">
         <v>494</v>
       </c>
-      <c r="C12" s="474"/>
-      <c r="D12" s="474"/>
-      <c r="E12" s="474"/>
-      <c r="F12" s="474"/>
+      <c r="C12" s="471"/>
+      <c r="D12" s="471"/>
+      <c r="E12" s="471"/>
+      <c r="F12" s="471"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20479,22 +20479,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="474" t="s">
+      <c r="B29" s="471" t="s">
         <v>495</v>
       </c>
-      <c r="C29" s="474"/>
-      <c r="D29" s="474"/>
-      <c r="E29" s="474"/>
-      <c r="F29" s="474"/>
+      <c r="C29" s="471"/>
+      <c r="D29" s="471"/>
+      <c r="E29" s="471"/>
+      <c r="F29" s="471"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="477" t="s">
+      <c r="B30" s="472" t="s">
         <v>496</v>
       </c>
-      <c r="C30" s="477"/>
-      <c r="D30" s="477"/>
-      <c r="E30" s="477"/>
-      <c r="F30" s="477"/>
+      <c r="C30" s="472"/>
+      <c r="D30" s="472"/>
+      <c r="E30" s="472"/>
+      <c r="F30" s="472"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20684,10 +20684,10 @@
       <c r="B54" s="470" t="s">
         <v>503</v>
       </c>
-      <c r="C54" s="476"/>
-      <c r="D54" s="476"/>
-      <c r="E54" s="476"/>
-      <c r="F54" s="476"/>
+      <c r="C54" s="473"/>
+      <c r="D54" s="473"/>
+      <c r="E54" s="473"/>
+      <c r="F54" s="473"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20703,22 +20703,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="474" t="s">
+      <c r="B57" s="471" t="s">
         <v>504</v>
       </c>
-      <c r="C57" s="474"/>
-      <c r="D57" s="474"/>
-      <c r="E57" s="474"/>
-      <c r="F57" s="474"/>
+      <c r="C57" s="471"/>
+      <c r="D57" s="471"/>
+      <c r="E57" s="471"/>
+      <c r="F57" s="471"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="474" t="s">
+      <c r="B58" s="471" t="s">
         <v>505</v>
       </c>
-      <c r="C58" s="474"/>
-      <c r="D58" s="474"/>
-      <c r="E58" s="474"/>
-      <c r="F58" s="474"/>
+      <c r="C58" s="471"/>
+      <c r="D58" s="471"/>
+      <c r="E58" s="471"/>
+      <c r="F58" s="471"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20752,7 +20752,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>7.4224896951387107E-2</v>
+        <v>7.537623542756218E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20762,7 +20762,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>2.7572505800464039E-2</v>
+        <v>2.8000196347928531E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>370</v>
@@ -20853,22 +20853,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="474" t="s">
+      <c r="B73" s="471" t="s">
         <v>506</v>
       </c>
-      <c r="C73" s="474"/>
-      <c r="D73" s="474"/>
-      <c r="E73" s="474"/>
-      <c r="F73" s="474"/>
+      <c r="C73" s="471"/>
+      <c r="D73" s="471"/>
+      <c r="E73" s="471"/>
+      <c r="F73" s="471"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="477" t="s">
+      <c r="B74" s="472" t="s">
         <v>476</v>
       </c>
-      <c r="C74" s="477"/>
-      <c r="D74" s="477"/>
-      <c r="E74" s="477"/>
-      <c r="F74" s="477"/>
+      <c r="C74" s="472"/>
+      <c r="D74" s="472"/>
+      <c r="E74" s="472"/>
+      <c r="F74" s="472"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -20876,13 +20876,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="474" t="s">
+      <c r="B77" s="471" t="s">
         <v>507</v>
       </c>
-      <c r="C77" s="474"/>
-      <c r="D77" s="474"/>
-      <c r="E77" s="474"/>
-      <c r="F77" s="474"/>
+      <c r="C77" s="471"/>
+      <c r="D77" s="471"/>
+      <c r="E77" s="471"/>
+      <c r="F77" s="471"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21031,33 +21031,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="474" t="s">
+      <c r="B96" s="471" t="s">
         <v>510</v>
       </c>
-      <c r="C96" s="474"/>
-      <c r="D96" s="474"/>
-      <c r="E96" s="474"/>
-      <c r="F96" s="474"/>
+      <c r="C96" s="471"/>
+      <c r="D96" s="471"/>
+      <c r="E96" s="471"/>
+      <c r="F96" s="471"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="477" t="s">
+      <c r="B97" s="472" t="s">
         <v>511</v>
       </c>
-      <c r="C97" s="477"/>
-      <c r="D97" s="477"/>
-      <c r="E97" s="477"/>
-      <c r="F97" s="477"/>
+      <c r="C97" s="472"/>
+      <c r="D97" s="472"/>
+      <c r="E97" s="472"/>
+      <c r="F97" s="472"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="477" t="s">
+      <c r="B98" s="472" t="s">
         <v>512</v>
       </c>
-      <c r="C98" s="477"/>
-      <c r="D98" s="477"/>
-      <c r="E98" s="477"/>
-      <c r="F98" s="477"/>
+      <c r="C98" s="472"/>
+      <c r="D98" s="472"/>
+      <c r="E98" s="472"/>
+      <c r="F98" s="472"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21120,23 +21120,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="474" t="s">
+      <c r="B107" s="471" t="s">
         <v>513</v>
       </c>
-      <c r="C107" s="474"/>
-      <c r="D107" s="474"/>
-      <c r="E107" s="474"/>
-      <c r="F107" s="474"/>
+      <c r="C107" s="471"/>
+      <c r="D107" s="471"/>
+      <c r="E107" s="471"/>
+      <c r="F107" s="471"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="474" t="s">
+      <c r="B108" s="471" t="s">
         <v>532</v>
       </c>
-      <c r="C108" s="474"/>
-      <c r="D108" s="474"/>
-      <c r="E108" s="474"/>
-      <c r="F108" s="474"/>
+      <c r="C108" s="471"/>
+      <c r="D108" s="471"/>
+      <c r="E108" s="471"/>
+      <c r="F108" s="471"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21180,13 +21180,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="474" t="s">
+      <c r="B114" s="471" t="s">
         <v>514</v>
       </c>
-      <c r="C114" s="474"/>
-      <c r="D114" s="474"/>
-      <c r="E114" s="474"/>
-      <c r="F114" s="474"/>
+      <c r="C114" s="471"/>
+      <c r="D114" s="471"/>
+      <c r="E114" s="471"/>
+      <c r="F114" s="471"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21350,13 +21350,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="472" t="s">
+      <c r="B127" s="475" t="s">
         <v>516</v>
       </c>
-      <c r="C127" s="472"/>
-      <c r="D127" s="472"/>
-      <c r="E127" s="472"/>
-      <c r="F127" s="472"/>
+      <c r="C127" s="475"/>
+      <c r="D127" s="475"/>
+      <c r="E127" s="475"/>
+      <c r="F127" s="475"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21369,22 +21369,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="473" t="s">
+      <c r="B131" s="476" t="s">
         <v>517</v>
       </c>
-      <c r="C131" s="473"/>
-      <c r="D131" s="473"/>
-      <c r="E131" s="473"/>
-      <c r="F131" s="473"/>
+      <c r="C131" s="476"/>
+      <c r="D131" s="476"/>
+      <c r="E131" s="476"/>
+      <c r="F131" s="476"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="474" t="s">
+      <c r="B132" s="471" t="s">
         <v>518</v>
       </c>
-      <c r="C132" s="474"/>
-      <c r="D132" s="474"/>
-      <c r="E132" s="474"/>
-      <c r="F132" s="474"/>
+      <c r="C132" s="471"/>
+      <c r="D132" s="471"/>
+      <c r="E132" s="471"/>
+      <c r="F132" s="471"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21553,13 +21553,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="475" t="s">
+      <c r="B149" s="477" t="s">
         <v>519</v>
       </c>
-      <c r="C149" s="474"/>
-      <c r="D149" s="474"/>
-      <c r="E149" s="474"/>
-      <c r="F149" s="474"/>
+      <c r="C149" s="471"/>
+      <c r="D149" s="471"/>
+      <c r="E149" s="471"/>
+      <c r="F149" s="471"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21567,13 +21567,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="476" t="s">
+      <c r="B152" s="473" t="s">
         <v>520</v>
       </c>
-      <c r="C152" s="476"/>
-      <c r="D152" s="476"/>
-      <c r="E152" s="476"/>
-      <c r="F152" s="476"/>
+      <c r="C152" s="473"/>
+      <c r="D152" s="473"/>
+      <c r="E152" s="473"/>
+      <c r="F152" s="473"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21610,22 +21610,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="471" t="s">
+      <c r="B161" s="474" t="s">
         <v>385</v>
       </c>
-      <c r="C161" s="471"/>
-      <c r="D161" s="471"/>
-      <c r="E161" s="471"/>
-      <c r="F161" s="471"/>
+      <c r="C161" s="474"/>
+      <c r="D161" s="474"/>
+      <c r="E161" s="474"/>
+      <c r="F161" s="474"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="471" t="s">
+      <c r="B162" s="474" t="s">
         <v>386</v>
       </c>
-      <c r="C162" s="471"/>
-      <c r="D162" s="471"/>
-      <c r="E162" s="471"/>
-      <c r="F162" s="471"/>
+      <c r="C162" s="474"/>
+      <c r="D162" s="474"/>
+      <c r="E162" s="474"/>
+      <c r="F162" s="474"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21649,12 +21649,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21669,15 +21672,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/000858.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/000858.SZ_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09C0DF11-D3AE-4B9D-99CE-BAC30D3C5B59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{947E05A2-6F49-4153-8EB5-696A01D98ED5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="735" yWindow="735" windowWidth="12690" windowHeight="7643" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4986,30 +4986,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5019,25 +5019,25 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5407,7 +5407,7 @@
         <v>347</v>
       </c>
       <c r="C8" s="47">
-        <v>101.86</v>
+        <v>101.18</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5425,14 +5425,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>395380.59138930001</v>
+        <v>392741.09794590005</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>524</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.16424302340067351</v>
+        <v>0.16690660595789986</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5440,13 +5440,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="460" t="s">
+      <c r="B12" s="462" t="s">
         <v>352</v>
       </c>
-      <c r="C12" s="460"/>
-      <c r="D12" s="460"/>
-      <c r="E12" s="460"/>
-      <c r="F12" s="460"/>
+      <c r="C12" s="462"/>
+      <c r="D12" s="462"/>
+      <c r="E12" s="462"/>
+      <c r="F12" s="462"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5624,22 +5624,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="460" t="s">
+      <c r="B29" s="462" t="s">
         <v>353</v>
       </c>
-      <c r="C29" s="460"/>
-      <c r="D29" s="460"/>
-      <c r="E29" s="460"/>
-      <c r="F29" s="460"/>
+      <c r="C29" s="462"/>
+      <c r="D29" s="462"/>
+      <c r="E29" s="462"/>
+      <c r="F29" s="462"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="462" t="s">
+      <c r="B30" s="466" t="s">
         <v>265</v>
       </c>
-      <c r="C30" s="462"/>
-      <c r="D30" s="462"/>
-      <c r="E30" s="462"/>
-      <c r="F30" s="462"/>
+      <c r="C30" s="466"/>
+      <c r="D30" s="466"/>
+      <c r="E30" s="466"/>
+      <c r="F30" s="466"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5651,13 +5651,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="461" t="s">
+      <c r="B33" s="463" t="s">
         <v>195</v>
       </c>
-      <c r="C33" s="461"/>
-      <c r="D33" s="461"/>
-      <c r="E33" s="461"/>
-      <c r="F33" s="461"/>
+      <c r="C33" s="463"/>
+      <c r="D33" s="463"/>
+      <c r="E33" s="463"/>
+      <c r="F33" s="463"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5677,13 +5677,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="461" t="s">
+      <c r="B36" s="463" t="s">
         <v>197</v>
       </c>
-      <c r="C36" s="461"/>
-      <c r="D36" s="461"/>
-      <c r="E36" s="461"/>
-      <c r="F36" s="461"/>
+      <c r="C36" s="463"/>
+      <c r="D36" s="463"/>
+      <c r="E36" s="463"/>
+      <c r="F36" s="463"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5712,13 +5712,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="461" t="s">
+      <c r="B40" s="463" t="s">
         <v>200</v>
       </c>
-      <c r="C40" s="461"/>
-      <c r="D40" s="461"/>
-      <c r="E40" s="461"/>
-      <c r="F40" s="461"/>
+      <c r="C40" s="463"/>
+      <c r="D40" s="463"/>
+      <c r="E40" s="463"/>
+      <c r="F40" s="463"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5734,13 +5734,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="461" t="s">
+      <c r="B43" s="463" t="s">
         <v>204</v>
       </c>
-      <c r="C43" s="461"/>
-      <c r="D43" s="461"/>
-      <c r="E43" s="461"/>
-      <c r="F43" s="461"/>
+      <c r="C43" s="463"/>
+      <c r="D43" s="463"/>
+      <c r="E43" s="463"/>
+      <c r="F43" s="463"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5804,13 +5804,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="461" t="s">
+      <c r="B51" s="463" t="s">
         <v>205</v>
       </c>
-      <c r="C51" s="461"/>
-      <c r="D51" s="461"/>
-      <c r="E51" s="461"/>
-      <c r="F51" s="461"/>
+      <c r="C51" s="463"/>
+      <c r="D51" s="463"/>
+      <c r="E51" s="463"/>
+      <c r="F51" s="463"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5826,7 +5826,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="461" t="s">
+      <c r="B54" s="463" t="s">
         <v>264</v>
       </c>
       <c r="C54" s="464"/>
@@ -5848,22 +5848,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="460" t="s">
+      <c r="B57" s="462" t="s">
         <v>269</v>
       </c>
-      <c r="C57" s="460"/>
-      <c r="D57" s="460"/>
-      <c r="E57" s="460"/>
-      <c r="F57" s="460"/>
+      <c r="C57" s="462"/>
+      <c r="D57" s="462"/>
+      <c r="E57" s="462"/>
+      <c r="F57" s="462"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="460" t="s">
+      <c r="B58" s="462" t="s">
         <v>281</v>
       </c>
-      <c r="C58" s="460"/>
-      <c r="D58" s="460"/>
-      <c r="E58" s="460"/>
-      <c r="F58" s="460"/>
+      <c r="C58" s="462"/>
+      <c r="D58" s="462"/>
+      <c r="E58" s="462"/>
+      <c r="F58" s="462"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>7.537623542756218E-2</v>
+        <v>7.5882816175642243E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5907,7 +5907,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>2.8000196347928531E-2</v>
+        <v>2.8188377149634312E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>320</v>
@@ -5998,13 +5998,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="460" t="s">
+      <c r="B73" s="462" t="s">
         <v>475</v>
       </c>
-      <c r="C73" s="460"/>
-      <c r="D73" s="460"/>
-      <c r="E73" s="460"/>
-      <c r="F73" s="460"/>
+      <c r="C73" s="462"/>
+      <c r="D73" s="462"/>
+      <c r="E73" s="462"/>
+      <c r="F73" s="462"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6023,13 +6023,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="460" t="s">
+      <c r="B77" s="462" t="s">
         <v>270</v>
       </c>
-      <c r="C77" s="460"/>
-      <c r="D77" s="460"/>
-      <c r="E77" s="460"/>
-      <c r="F77" s="460"/>
+      <c r="C77" s="462"/>
+      <c r="D77" s="462"/>
+      <c r="E77" s="462"/>
+      <c r="F77" s="462"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6198,31 +6198,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="460" t="s">
+      <c r="B96" s="462" t="s">
         <v>482</v>
       </c>
-      <c r="C96" s="460"/>
-      <c r="D96" s="460"/>
-      <c r="E96" s="460"/>
-      <c r="F96" s="460"/>
+      <c r="C96" s="462"/>
+      <c r="D96" s="462"/>
+      <c r="E96" s="462"/>
+      <c r="F96" s="462"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="462" t="s">
+      <c r="B97" s="466" t="s">
         <v>481</v>
       </c>
-      <c r="C97" s="462"/>
-      <c r="D97" s="462"/>
-      <c r="E97" s="462"/>
-      <c r="F97" s="462"/>
+      <c r="C97" s="466"/>
+      <c r="D97" s="466"/>
+      <c r="E97" s="466"/>
+      <c r="F97" s="466"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="462" t="s">
+      <c r="B98" s="466" t="s">
         <v>480</v>
       </c>
-      <c r="C98" s="462"/>
-      <c r="D98" s="462"/>
-      <c r="E98" s="462"/>
-      <c r="F98" s="462"/>
+      <c r="C98" s="466"/>
+      <c r="D98" s="466"/>
+      <c r="E98" s="466"/>
+      <c r="F98" s="466"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6272,22 +6272,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="460" t="s">
+      <c r="B107" s="462" t="s">
         <v>282</v>
       </c>
-      <c r="C107" s="460"/>
-      <c r="D107" s="460"/>
-      <c r="E107" s="460"/>
-      <c r="F107" s="460"/>
+      <c r="C107" s="462"/>
+      <c r="D107" s="462"/>
+      <c r="E107" s="462"/>
+      <c r="F107" s="462"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="460" t="s">
+      <c r="B108" s="462" t="s">
         <v>283</v>
       </c>
-      <c r="C108" s="460"/>
-      <c r="D108" s="460"/>
-      <c r="E108" s="460"/>
-      <c r="F108" s="460"/>
+      <c r="C108" s="462"/>
+      <c r="D108" s="462"/>
+      <c r="E108" s="462"/>
+      <c r="F108" s="462"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6321,13 +6321,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="460" t="s">
+      <c r="B114" s="462" t="s">
         <v>488</v>
       </c>
-      <c r="C114" s="460"/>
-      <c r="D114" s="460"/>
-      <c r="E114" s="460"/>
-      <c r="F114" s="460"/>
+      <c r="C114" s="462"/>
+      <c r="D114" s="462"/>
+      <c r="E114" s="462"/>
+      <c r="F114" s="462"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6462,13 +6462,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="461" t="s">
+      <c r="B124" s="463" t="s">
         <v>354</v>
       </c>
-      <c r="C124" s="461"/>
-      <c r="D124" s="461"/>
-      <c r="E124" s="461"/>
-      <c r="F124" s="461"/>
+      <c r="C124" s="463"/>
+      <c r="D124" s="463"/>
+      <c r="E124" s="463"/>
+      <c r="F124" s="463"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6503,22 +6503,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="463" t="s">
+      <c r="B131" s="467" t="s">
         <v>284</v>
       </c>
-      <c r="C131" s="463"/>
-      <c r="D131" s="463"/>
-      <c r="E131" s="463"/>
-      <c r="F131" s="463"/>
+      <c r="C131" s="467"/>
+      <c r="D131" s="467"/>
+      <c r="E131" s="467"/>
+      <c r="F131" s="467"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="460" t="s">
+      <c r="B132" s="462" t="s">
         <v>356</v>
       </c>
-      <c r="C132" s="460"/>
-      <c r="D132" s="460"/>
-      <c r="E132" s="460"/>
-      <c r="F132" s="460"/>
+      <c r="C132" s="462"/>
+      <c r="D132" s="462"/>
+      <c r="E132" s="462"/>
+      <c r="F132" s="462"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6694,13 +6694,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="467" t="s">
+      <c r="B149" s="461" t="s">
         <v>357</v>
       </c>
-      <c r="C149" s="460"/>
-      <c r="D149" s="460"/>
-      <c r="E149" s="460"/>
-      <c r="F149" s="460"/>
+      <c r="C149" s="462"/>
+      <c r="D149" s="462"/>
+      <c r="E149" s="462"/>
+      <c r="F149" s="462"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6737,13 +6737,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="461" t="s">
+      <c r="B158" s="463" t="s">
         <v>435</v>
       </c>
-      <c r="C158" s="461"/>
-      <c r="D158" s="461"/>
-      <c r="E158" s="461"/>
-      <c r="F158" s="461"/>
+      <c r="C158" s="463"/>
+      <c r="D158" s="463"/>
+      <c r="E158" s="463"/>
+      <c r="F158" s="463"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6751,22 +6751,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="466" t="s">
+      <c r="B161" s="460" t="s">
         <v>293</v>
       </c>
-      <c r="C161" s="466"/>
-      <c r="D161" s="466"/>
-      <c r="E161" s="466"/>
-      <c r="F161" s="466"/>
+      <c r="C161" s="460"/>
+      <c r="D161" s="460"/>
+      <c r="E161" s="460"/>
+      <c r="F161" s="460"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="466" t="s">
+      <c r="B162" s="460" t="s">
         <v>294</v>
       </c>
-      <c r="C162" s="466"/>
-      <c r="D162" s="466"/>
-      <c r="E162" s="466"/>
-      <c r="F162" s="466"/>
+      <c r="C162" s="460"/>
+      <c r="D162" s="460"/>
+      <c r="E162" s="460"/>
+      <c r="F162" s="460"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6790,18 +6790,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6818,6 +6806,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -14008,16 +14008,16 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>2.8000196347928531E-2</v>
+        <v>2.8188377149634312E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>2.8000196347928531E-2</v>
+        <v>2.8188377149634312E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>4.1262517180443749E-2</v>
+        <v>4.1539830005930027E-2</v>
       </c>
       <c r="I92" s="22" t="str">
         <f t="shared" si="38"/>
@@ -15229,18 +15229,18 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>7.537623542756218E-2</v>
+        <v>7.5882816175642243E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>6.691913412466971E-2</v>
+        <v>6.7368877267630523E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>6.4428808984848596E-2</v>
+        <v>6.4861815410127269E-2</v>
       </c>
       <c r="I124" s="74" t="str">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
@@ -15286,11 +15286,11 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.3953186391076601E-2</v>
+        <v>8.4517410217385472E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.972262237605382E-2</v>
+        <v>8.0258413868598957E-2</v>
       </c>
       <c r="I125" s="22" t="str">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -19748,7 +19748,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>101.86</v>
+        <v>101.18</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19759,7 +19759,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.16424302340067351</v>
+        <v>0.16690660595789986</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -20255,7 +20255,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>101.86</v>
+        <v>101.18</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20273,14 +20273,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>395380.59138930001</v>
+        <v>392741.09794590005</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>525</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.16424302340067351</v>
+        <v>0.16690660595789986</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20288,13 +20288,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="471" t="s">
+      <c r="B12" s="474" t="s">
         <v>494</v>
       </c>
-      <c r="C12" s="471"/>
-      <c r="D12" s="471"/>
-      <c r="E12" s="471"/>
-      <c r="F12" s="471"/>
+      <c r="C12" s="474"/>
+      <c r="D12" s="474"/>
+      <c r="E12" s="474"/>
+      <c r="F12" s="474"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20479,22 +20479,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="471" t="s">
+      <c r="B29" s="474" t="s">
         <v>495</v>
       </c>
-      <c r="C29" s="471"/>
-      <c r="D29" s="471"/>
-      <c r="E29" s="471"/>
-      <c r="F29" s="471"/>
+      <c r="C29" s="474"/>
+      <c r="D29" s="474"/>
+      <c r="E29" s="474"/>
+      <c r="F29" s="474"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="472" t="s">
+      <c r="B30" s="477" t="s">
         <v>496</v>
       </c>
-      <c r="C30" s="472"/>
-      <c r="D30" s="472"/>
-      <c r="E30" s="472"/>
-      <c r="F30" s="472"/>
+      <c r="C30" s="477"/>
+      <c r="D30" s="477"/>
+      <c r="E30" s="477"/>
+      <c r="F30" s="477"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20684,10 +20684,10 @@
       <c r="B54" s="470" t="s">
         <v>503</v>
       </c>
-      <c r="C54" s="473"/>
-      <c r="D54" s="473"/>
-      <c r="E54" s="473"/>
-      <c r="F54" s="473"/>
+      <c r="C54" s="476"/>
+      <c r="D54" s="476"/>
+      <c r="E54" s="476"/>
+      <c r="F54" s="476"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20703,22 +20703,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="471" t="s">
+      <c r="B57" s="474" t="s">
         <v>504</v>
       </c>
-      <c r="C57" s="471"/>
-      <c r="D57" s="471"/>
-      <c r="E57" s="471"/>
-      <c r="F57" s="471"/>
+      <c r="C57" s="474"/>
+      <c r="D57" s="474"/>
+      <c r="E57" s="474"/>
+      <c r="F57" s="474"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="471" t="s">
+      <c r="B58" s="474" t="s">
         <v>505</v>
       </c>
-      <c r="C58" s="471"/>
-      <c r="D58" s="471"/>
-      <c r="E58" s="471"/>
-      <c r="F58" s="471"/>
+      <c r="C58" s="474"/>
+      <c r="D58" s="474"/>
+      <c r="E58" s="474"/>
+      <c r="F58" s="474"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20752,7 +20752,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>7.537623542756218E-2</v>
+        <v>7.5882816175642243E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20762,7 +20762,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>2.8000196347928531E-2</v>
+        <v>2.8188377149634312E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>370</v>
@@ -20853,22 +20853,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="471" t="s">
+      <c r="B73" s="474" t="s">
         <v>506</v>
       </c>
-      <c r="C73" s="471"/>
-      <c r="D73" s="471"/>
-      <c r="E73" s="471"/>
-      <c r="F73" s="471"/>
+      <c r="C73" s="474"/>
+      <c r="D73" s="474"/>
+      <c r="E73" s="474"/>
+      <c r="F73" s="474"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="472" t="s">
+      <c r="B74" s="477" t="s">
         <v>476</v>
       </c>
-      <c r="C74" s="472"/>
-      <c r="D74" s="472"/>
-      <c r="E74" s="472"/>
-      <c r="F74" s="472"/>
+      <c r="C74" s="477"/>
+      <c r="D74" s="477"/>
+      <c r="E74" s="477"/>
+      <c r="F74" s="477"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -20876,13 +20876,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="471" t="s">
+      <c r="B77" s="474" t="s">
         <v>507</v>
       </c>
-      <c r="C77" s="471"/>
-      <c r="D77" s="471"/>
-      <c r="E77" s="471"/>
-      <c r="F77" s="471"/>
+      <c r="C77" s="474"/>
+      <c r="D77" s="474"/>
+      <c r="E77" s="474"/>
+      <c r="F77" s="474"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21031,33 +21031,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="471" t="s">
+      <c r="B96" s="474" t="s">
         <v>510</v>
       </c>
-      <c r="C96" s="471"/>
-      <c r="D96" s="471"/>
-      <c r="E96" s="471"/>
-      <c r="F96" s="471"/>
+      <c r="C96" s="474"/>
+      <c r="D96" s="474"/>
+      <c r="E96" s="474"/>
+      <c r="F96" s="474"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="472" t="s">
+      <c r="B97" s="477" t="s">
         <v>511</v>
       </c>
-      <c r="C97" s="472"/>
-      <c r="D97" s="472"/>
-      <c r="E97" s="472"/>
-      <c r="F97" s="472"/>
+      <c r="C97" s="477"/>
+      <c r="D97" s="477"/>
+      <c r="E97" s="477"/>
+      <c r="F97" s="477"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="472" t="s">
+      <c r="B98" s="477" t="s">
         <v>512</v>
       </c>
-      <c r="C98" s="472"/>
-      <c r="D98" s="472"/>
-      <c r="E98" s="472"/>
-      <c r="F98" s="472"/>
+      <c r="C98" s="477"/>
+      <c r="D98" s="477"/>
+      <c r="E98" s="477"/>
+      <c r="F98" s="477"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21120,23 +21120,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="471" t="s">
+      <c r="B107" s="474" t="s">
         <v>513</v>
       </c>
-      <c r="C107" s="471"/>
-      <c r="D107" s="471"/>
-      <c r="E107" s="471"/>
-      <c r="F107" s="471"/>
+      <c r="C107" s="474"/>
+      <c r="D107" s="474"/>
+      <c r="E107" s="474"/>
+      <c r="F107" s="474"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="471" t="s">
+      <c r="B108" s="474" t="s">
         <v>532</v>
       </c>
-      <c r="C108" s="471"/>
-      <c r="D108" s="471"/>
-      <c r="E108" s="471"/>
-      <c r="F108" s="471"/>
+      <c r="C108" s="474"/>
+      <c r="D108" s="474"/>
+      <c r="E108" s="474"/>
+      <c r="F108" s="474"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21180,13 +21180,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="471" t="s">
+      <c r="B114" s="474" t="s">
         <v>514</v>
       </c>
-      <c r="C114" s="471"/>
-      <c r="D114" s="471"/>
-      <c r="E114" s="471"/>
-      <c r="F114" s="471"/>
+      <c r="C114" s="474"/>
+      <c r="D114" s="474"/>
+      <c r="E114" s="474"/>
+      <c r="F114" s="474"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21350,13 +21350,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="475" t="s">
+      <c r="B127" s="472" t="s">
         <v>516</v>
       </c>
-      <c r="C127" s="475"/>
-      <c r="D127" s="475"/>
-      <c r="E127" s="475"/>
-      <c r="F127" s="475"/>
+      <c r="C127" s="472"/>
+      <c r="D127" s="472"/>
+      <c r="E127" s="472"/>
+      <c r="F127" s="472"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21369,22 +21369,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="476" t="s">
+      <c r="B131" s="473" t="s">
         <v>517</v>
       </c>
-      <c r="C131" s="476"/>
-      <c r="D131" s="476"/>
-      <c r="E131" s="476"/>
-      <c r="F131" s="476"/>
+      <c r="C131" s="473"/>
+      <c r="D131" s="473"/>
+      <c r="E131" s="473"/>
+      <c r="F131" s="473"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="471" t="s">
+      <c r="B132" s="474" t="s">
         <v>518</v>
       </c>
-      <c r="C132" s="471"/>
-      <c r="D132" s="471"/>
-      <c r="E132" s="471"/>
-      <c r="F132" s="471"/>
+      <c r="C132" s="474"/>
+      <c r="D132" s="474"/>
+      <c r="E132" s="474"/>
+      <c r="F132" s="474"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21553,13 +21553,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="477" t="s">
+      <c r="B149" s="475" t="s">
         <v>519</v>
       </c>
-      <c r="C149" s="471"/>
-      <c r="D149" s="471"/>
-      <c r="E149" s="471"/>
-      <c r="F149" s="471"/>
+      <c r="C149" s="474"/>
+      <c r="D149" s="474"/>
+      <c r="E149" s="474"/>
+      <c r="F149" s="474"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21567,13 +21567,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="473" t="s">
+      <c r="B152" s="476" t="s">
         <v>520</v>
       </c>
-      <c r="C152" s="473"/>
-      <c r="D152" s="473"/>
-      <c r="E152" s="473"/>
-      <c r="F152" s="473"/>
+      <c r="C152" s="476"/>
+      <c r="D152" s="476"/>
+      <c r="E152" s="476"/>
+      <c r="F152" s="476"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21610,22 +21610,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="474" t="s">
+      <c r="B161" s="471" t="s">
         <v>385</v>
       </c>
-      <c r="C161" s="474"/>
-      <c r="D161" s="474"/>
-      <c r="E161" s="474"/>
-      <c r="F161" s="474"/>
+      <c r="C161" s="471"/>
+      <c r="D161" s="471"/>
+      <c r="E161" s="471"/>
+      <c r="F161" s="471"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="474" t="s">
+      <c r="B162" s="471" t="s">
         <v>386</v>
       </c>
-      <c r="C162" s="474"/>
-      <c r="D162" s="474"/>
-      <c r="E162" s="474"/>
-      <c r="F162" s="474"/>
+      <c r="C162" s="471"/>
+      <c r="D162" s="471"/>
+      <c r="E162" s="471"/>
+      <c r="F162" s="471"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21649,15 +21649,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21672,12 +21669,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/000858.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/000858.SZ_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{947E05A2-6F49-4153-8EB5-696A01D98ED5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C0ACCCB-FCD9-4C0E-9794-92A68C8DD655}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4986,30 +4986,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5019,6 +5019,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5028,16 +5037,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5407,7 +5407,7 @@
         <v>347</v>
       </c>
       <c r="C8" s="47">
-        <v>101.18</v>
+        <v>100.64</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5425,14 +5425,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>392741.09794590005</v>
+        <v>390645.02962320001</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>524</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.16690660595789986</v>
+        <v>0.16903913408793184</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5440,13 +5440,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="462" t="s">
+      <c r="B12" s="460" t="s">
         <v>352</v>
       </c>
-      <c r="C12" s="462"/>
-      <c r="D12" s="462"/>
-      <c r="E12" s="462"/>
-      <c r="F12" s="462"/>
+      <c r="C12" s="460"/>
+      <c r="D12" s="460"/>
+      <c r="E12" s="460"/>
+      <c r="F12" s="460"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5624,22 +5624,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="462" t="s">
+      <c r="B29" s="460" t="s">
         <v>353</v>
       </c>
-      <c r="C29" s="462"/>
-      <c r="D29" s="462"/>
-      <c r="E29" s="462"/>
-      <c r="F29" s="462"/>
+      <c r="C29" s="460"/>
+      <c r="D29" s="460"/>
+      <c r="E29" s="460"/>
+      <c r="F29" s="460"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="466" t="s">
+      <c r="B30" s="462" t="s">
         <v>265</v>
       </c>
-      <c r="C30" s="466"/>
-      <c r="D30" s="466"/>
-      <c r="E30" s="466"/>
-      <c r="F30" s="466"/>
+      <c r="C30" s="462"/>
+      <c r="D30" s="462"/>
+      <c r="E30" s="462"/>
+      <c r="F30" s="462"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5651,13 +5651,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="463" t="s">
+      <c r="B33" s="461" t="s">
         <v>195</v>
       </c>
-      <c r="C33" s="463"/>
-      <c r="D33" s="463"/>
-      <c r="E33" s="463"/>
-      <c r="F33" s="463"/>
+      <c r="C33" s="461"/>
+      <c r="D33" s="461"/>
+      <c r="E33" s="461"/>
+      <c r="F33" s="461"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5677,13 +5677,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="463" t="s">
+      <c r="B36" s="461" t="s">
         <v>197</v>
       </c>
-      <c r="C36" s="463"/>
-      <c r="D36" s="463"/>
-      <c r="E36" s="463"/>
-      <c r="F36" s="463"/>
+      <c r="C36" s="461"/>
+      <c r="D36" s="461"/>
+      <c r="E36" s="461"/>
+      <c r="F36" s="461"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5712,13 +5712,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="463" t="s">
+      <c r="B40" s="461" t="s">
         <v>200</v>
       </c>
-      <c r="C40" s="463"/>
-      <c r="D40" s="463"/>
-      <c r="E40" s="463"/>
-      <c r="F40" s="463"/>
+      <c r="C40" s="461"/>
+      <c r="D40" s="461"/>
+      <c r="E40" s="461"/>
+      <c r="F40" s="461"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5734,13 +5734,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="463" t="s">
+      <c r="B43" s="461" t="s">
         <v>204</v>
       </c>
-      <c r="C43" s="463"/>
-      <c r="D43" s="463"/>
-      <c r="E43" s="463"/>
-      <c r="F43" s="463"/>
+      <c r="C43" s="461"/>
+      <c r="D43" s="461"/>
+      <c r="E43" s="461"/>
+      <c r="F43" s="461"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5804,13 +5804,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="463" t="s">
+      <c r="B51" s="461" t="s">
         <v>205</v>
       </c>
-      <c r="C51" s="463"/>
-      <c r="D51" s="463"/>
-      <c r="E51" s="463"/>
-      <c r="F51" s="463"/>
+      <c r="C51" s="461"/>
+      <c r="D51" s="461"/>
+      <c r="E51" s="461"/>
+      <c r="F51" s="461"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5826,7 +5826,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="463" t="s">
+      <c r="B54" s="461" t="s">
         <v>264</v>
       </c>
       <c r="C54" s="464"/>
@@ -5848,22 +5848,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="462" t="s">
+      <c r="B57" s="460" t="s">
         <v>269</v>
       </c>
-      <c r="C57" s="462"/>
-      <c r="D57" s="462"/>
-      <c r="E57" s="462"/>
-      <c r="F57" s="462"/>
+      <c r="C57" s="460"/>
+      <c r="D57" s="460"/>
+      <c r="E57" s="460"/>
+      <c r="F57" s="460"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="462" t="s">
+      <c r="B58" s="460" t="s">
         <v>281</v>
       </c>
-      <c r="C58" s="462"/>
-      <c r="D58" s="462"/>
-      <c r="E58" s="462"/>
-      <c r="F58" s="462"/>
+      <c r="C58" s="460"/>
+      <c r="D58" s="460"/>
+      <c r="E58" s="460"/>
+      <c r="F58" s="460"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>7.5882816175642243E-2</v>
+        <v>7.628997755019358E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5907,7 +5907,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>2.8188377149634312E-2</v>
+        <v>2.8339626391096981E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>320</v>
@@ -5998,13 +5998,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="462" t="s">
+      <c r="B73" s="460" t="s">
         <v>475</v>
       </c>
-      <c r="C73" s="462"/>
-      <c r="D73" s="462"/>
-      <c r="E73" s="462"/>
-      <c r="F73" s="462"/>
+      <c r="C73" s="460"/>
+      <c r="D73" s="460"/>
+      <c r="E73" s="460"/>
+      <c r="F73" s="460"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6023,13 +6023,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="462" t="s">
+      <c r="B77" s="460" t="s">
         <v>270</v>
       </c>
-      <c r="C77" s="462"/>
-      <c r="D77" s="462"/>
-      <c r="E77" s="462"/>
-      <c r="F77" s="462"/>
+      <c r="C77" s="460"/>
+      <c r="D77" s="460"/>
+      <c r="E77" s="460"/>
+      <c r="F77" s="460"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6198,31 +6198,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="462" t="s">
+      <c r="B96" s="460" t="s">
         <v>482</v>
       </c>
-      <c r="C96" s="462"/>
-      <c r="D96" s="462"/>
-      <c r="E96" s="462"/>
-      <c r="F96" s="462"/>
+      <c r="C96" s="460"/>
+      <c r="D96" s="460"/>
+      <c r="E96" s="460"/>
+      <c r="F96" s="460"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="466" t="s">
+      <c r="B97" s="462" t="s">
         <v>481</v>
       </c>
-      <c r="C97" s="466"/>
-      <c r="D97" s="466"/>
-      <c r="E97" s="466"/>
-      <c r="F97" s="466"/>
+      <c r="C97" s="462"/>
+      <c r="D97" s="462"/>
+      <c r="E97" s="462"/>
+      <c r="F97" s="462"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="466" t="s">
+      <c r="B98" s="462" t="s">
         <v>480</v>
       </c>
-      <c r="C98" s="466"/>
-      <c r="D98" s="466"/>
-      <c r="E98" s="466"/>
-      <c r="F98" s="466"/>
+      <c r="C98" s="462"/>
+      <c r="D98" s="462"/>
+      <c r="E98" s="462"/>
+      <c r="F98" s="462"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6272,22 +6272,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="462" t="s">
+      <c r="B107" s="460" t="s">
         <v>282</v>
       </c>
-      <c r="C107" s="462"/>
-      <c r="D107" s="462"/>
-      <c r="E107" s="462"/>
-      <c r="F107" s="462"/>
+      <c r="C107" s="460"/>
+      <c r="D107" s="460"/>
+      <c r="E107" s="460"/>
+      <c r="F107" s="460"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="462" t="s">
+      <c r="B108" s="460" t="s">
         <v>283</v>
       </c>
-      <c r="C108" s="462"/>
-      <c r="D108" s="462"/>
-      <c r="E108" s="462"/>
-      <c r="F108" s="462"/>
+      <c r="C108" s="460"/>
+      <c r="D108" s="460"/>
+      <c r="E108" s="460"/>
+      <c r="F108" s="460"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6321,13 +6321,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="462" t="s">
+      <c r="B114" s="460" t="s">
         <v>488</v>
       </c>
-      <c r="C114" s="462"/>
-      <c r="D114" s="462"/>
-      <c r="E114" s="462"/>
-      <c r="F114" s="462"/>
+      <c r="C114" s="460"/>
+      <c r="D114" s="460"/>
+      <c r="E114" s="460"/>
+      <c r="F114" s="460"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6462,13 +6462,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="463" t="s">
+      <c r="B124" s="461" t="s">
         <v>354</v>
       </c>
-      <c r="C124" s="463"/>
-      <c r="D124" s="463"/>
-      <c r="E124" s="463"/>
-      <c r="F124" s="463"/>
+      <c r="C124" s="461"/>
+      <c r="D124" s="461"/>
+      <c r="E124" s="461"/>
+      <c r="F124" s="461"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6503,22 +6503,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="467" t="s">
+      <c r="B131" s="463" t="s">
         <v>284</v>
       </c>
-      <c r="C131" s="467"/>
-      <c r="D131" s="467"/>
-      <c r="E131" s="467"/>
-      <c r="F131" s="467"/>
+      <c r="C131" s="463"/>
+      <c r="D131" s="463"/>
+      <c r="E131" s="463"/>
+      <c r="F131" s="463"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="462" t="s">
+      <c r="B132" s="460" t="s">
         <v>356</v>
       </c>
-      <c r="C132" s="462"/>
-      <c r="D132" s="462"/>
-      <c r="E132" s="462"/>
-      <c r="F132" s="462"/>
+      <c r="C132" s="460"/>
+      <c r="D132" s="460"/>
+      <c r="E132" s="460"/>
+      <c r="F132" s="460"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6694,13 +6694,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="461" t="s">
+      <c r="B149" s="467" t="s">
         <v>357</v>
       </c>
-      <c r="C149" s="462"/>
-      <c r="D149" s="462"/>
-      <c r="E149" s="462"/>
-      <c r="F149" s="462"/>
+      <c r="C149" s="460"/>
+      <c r="D149" s="460"/>
+      <c r="E149" s="460"/>
+      <c r="F149" s="460"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6737,13 +6737,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="463" t="s">
+      <c r="B158" s="461" t="s">
         <v>435</v>
       </c>
-      <c r="C158" s="463"/>
-      <c r="D158" s="463"/>
-      <c r="E158" s="463"/>
-      <c r="F158" s="463"/>
+      <c r="C158" s="461"/>
+      <c r="D158" s="461"/>
+      <c r="E158" s="461"/>
+      <c r="F158" s="461"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6751,22 +6751,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="460" t="s">
+      <c r="B161" s="466" t="s">
         <v>293</v>
       </c>
-      <c r="C161" s="460"/>
-      <c r="D161" s="460"/>
-      <c r="E161" s="460"/>
-      <c r="F161" s="460"/>
+      <c r="C161" s="466"/>
+      <c r="D161" s="466"/>
+      <c r="E161" s="466"/>
+      <c r="F161" s="466"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="460" t="s">
+      <c r="B162" s="466" t="s">
         <v>294</v>
       </c>
-      <c r="C162" s="460"/>
-      <c r="D162" s="460"/>
-      <c r="E162" s="460"/>
-      <c r="F162" s="460"/>
+      <c r="C162" s="466"/>
+      <c r="D162" s="466"/>
+      <c r="E162" s="466"/>
+      <c r="F162" s="466"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6790,6 +6790,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6806,18 +6818,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -14008,16 +14008,16 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>2.8188377149634312E-2</v>
+        <v>2.8339626391096981E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>2.8188377149634312E-2</v>
+        <v>2.8339626391096981E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>4.1539830005930027E-2</v>
+        <v>4.1762718600953895E-2</v>
       </c>
       <c r="I92" s="22" t="str">
         <f t="shared" si="38"/>
@@ -15229,18 +15229,18 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>7.5882816175642243E-2</v>
+        <v>7.628997755019358E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>6.7368877267630523E-2</v>
+        <v>6.7730355742635709E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>6.4861815410127269E-2</v>
+        <v>6.5209841844164132E-2</v>
       </c>
       <c r="I124" s="74" t="str">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
@@ -15286,11 +15286,11 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.4517410217385472E-2</v>
+        <v>8.4970901885880981E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.0258413868598957E-2</v>
+        <v>8.0689053211693576E-2</v>
       </c>
       <c r="I125" s="22" t="str">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -19748,7 +19748,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>101.18</v>
+        <v>100.64</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19759,7 +19759,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.16690660595789986</v>
+        <v>0.16903913408793184</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -20255,7 +20255,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>101.18</v>
+        <v>100.64</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20273,14 +20273,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>392741.09794590005</v>
+        <v>390645.02962320001</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>525</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.16690660595789986</v>
+        <v>0.16903913408793184</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20288,13 +20288,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="474" t="s">
+      <c r="B12" s="471" t="s">
         <v>494</v>
       </c>
-      <c r="C12" s="474"/>
-      <c r="D12" s="474"/>
-      <c r="E12" s="474"/>
-      <c r="F12" s="474"/>
+      <c r="C12" s="471"/>
+      <c r="D12" s="471"/>
+      <c r="E12" s="471"/>
+      <c r="F12" s="471"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20479,22 +20479,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="474" t="s">
+      <c r="B29" s="471" t="s">
         <v>495</v>
       </c>
-      <c r="C29" s="474"/>
-      <c r="D29" s="474"/>
-      <c r="E29" s="474"/>
-      <c r="F29" s="474"/>
+      <c r="C29" s="471"/>
+      <c r="D29" s="471"/>
+      <c r="E29" s="471"/>
+      <c r="F29" s="471"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="477" t="s">
+      <c r="B30" s="472" t="s">
         <v>496</v>
       </c>
-      <c r="C30" s="477"/>
-      <c r="D30" s="477"/>
-      <c r="E30" s="477"/>
-      <c r="F30" s="477"/>
+      <c r="C30" s="472"/>
+      <c r="D30" s="472"/>
+      <c r="E30" s="472"/>
+      <c r="F30" s="472"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20684,10 +20684,10 @@
       <c r="B54" s="470" t="s">
         <v>503</v>
       </c>
-      <c r="C54" s="476"/>
-      <c r="D54" s="476"/>
-      <c r="E54" s="476"/>
-      <c r="F54" s="476"/>
+      <c r="C54" s="473"/>
+      <c r="D54" s="473"/>
+      <c r="E54" s="473"/>
+      <c r="F54" s="473"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20703,22 +20703,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="474" t="s">
+      <c r="B57" s="471" t="s">
         <v>504</v>
       </c>
-      <c r="C57" s="474"/>
-      <c r="D57" s="474"/>
-      <c r="E57" s="474"/>
-      <c r="F57" s="474"/>
+      <c r="C57" s="471"/>
+      <c r="D57" s="471"/>
+      <c r="E57" s="471"/>
+      <c r="F57" s="471"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="474" t="s">
+      <c r="B58" s="471" t="s">
         <v>505</v>
       </c>
-      <c r="C58" s="474"/>
-      <c r="D58" s="474"/>
-      <c r="E58" s="474"/>
-      <c r="F58" s="474"/>
+      <c r="C58" s="471"/>
+      <c r="D58" s="471"/>
+      <c r="E58" s="471"/>
+      <c r="F58" s="471"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20752,7 +20752,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>7.5882816175642243E-2</v>
+        <v>7.628997755019358E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20762,7 +20762,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>2.8188377149634312E-2</v>
+        <v>2.8339626391096981E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>370</v>
@@ -20853,22 +20853,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="474" t="s">
+      <c r="B73" s="471" t="s">
         <v>506</v>
       </c>
-      <c r="C73" s="474"/>
-      <c r="D73" s="474"/>
-      <c r="E73" s="474"/>
-      <c r="F73" s="474"/>
+      <c r="C73" s="471"/>
+      <c r="D73" s="471"/>
+      <c r="E73" s="471"/>
+      <c r="F73" s="471"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="477" t="s">
+      <c r="B74" s="472" t="s">
         <v>476</v>
       </c>
-      <c r="C74" s="477"/>
-      <c r="D74" s="477"/>
-      <c r="E74" s="477"/>
-      <c r="F74" s="477"/>
+      <c r="C74" s="472"/>
+      <c r="D74" s="472"/>
+      <c r="E74" s="472"/>
+      <c r="F74" s="472"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -20876,13 +20876,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="474" t="s">
+      <c r="B77" s="471" t="s">
         <v>507</v>
       </c>
-      <c r="C77" s="474"/>
-      <c r="D77" s="474"/>
-      <c r="E77" s="474"/>
-      <c r="F77" s="474"/>
+      <c r="C77" s="471"/>
+      <c r="D77" s="471"/>
+      <c r="E77" s="471"/>
+      <c r="F77" s="471"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21031,33 +21031,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="474" t="s">
+      <c r="B96" s="471" t="s">
         <v>510</v>
       </c>
-      <c r="C96" s="474"/>
-      <c r="D96" s="474"/>
-      <c r="E96" s="474"/>
-      <c r="F96" s="474"/>
+      <c r="C96" s="471"/>
+      <c r="D96" s="471"/>
+      <c r="E96" s="471"/>
+      <c r="F96" s="471"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="477" t="s">
+      <c r="B97" s="472" t="s">
         <v>511</v>
       </c>
-      <c r="C97" s="477"/>
-      <c r="D97" s="477"/>
-      <c r="E97" s="477"/>
-      <c r="F97" s="477"/>
+      <c r="C97" s="472"/>
+      <c r="D97" s="472"/>
+      <c r="E97" s="472"/>
+      <c r="F97" s="472"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="477" t="s">
+      <c r="B98" s="472" t="s">
         <v>512</v>
       </c>
-      <c r="C98" s="477"/>
-      <c r="D98" s="477"/>
-      <c r="E98" s="477"/>
-      <c r="F98" s="477"/>
+      <c r="C98" s="472"/>
+      <c r="D98" s="472"/>
+      <c r="E98" s="472"/>
+      <c r="F98" s="472"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21120,23 +21120,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="474" t="s">
+      <c r="B107" s="471" t="s">
         <v>513</v>
       </c>
-      <c r="C107" s="474"/>
-      <c r="D107" s="474"/>
-      <c r="E107" s="474"/>
-      <c r="F107" s="474"/>
+      <c r="C107" s="471"/>
+      <c r="D107" s="471"/>
+      <c r="E107" s="471"/>
+      <c r="F107" s="471"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="474" t="s">
+      <c r="B108" s="471" t="s">
         <v>532</v>
       </c>
-      <c r="C108" s="474"/>
-      <c r="D108" s="474"/>
-      <c r="E108" s="474"/>
-      <c r="F108" s="474"/>
+      <c r="C108" s="471"/>
+      <c r="D108" s="471"/>
+      <c r="E108" s="471"/>
+      <c r="F108" s="471"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21180,13 +21180,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="474" t="s">
+      <c r="B114" s="471" t="s">
         <v>514</v>
       </c>
-      <c r="C114" s="474"/>
-      <c r="D114" s="474"/>
-      <c r="E114" s="474"/>
-      <c r="F114" s="474"/>
+      <c r="C114" s="471"/>
+      <c r="D114" s="471"/>
+      <c r="E114" s="471"/>
+      <c r="F114" s="471"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21350,13 +21350,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="472" t="s">
+      <c r="B127" s="475" t="s">
         <v>516</v>
       </c>
-      <c r="C127" s="472"/>
-      <c r="D127" s="472"/>
-      <c r="E127" s="472"/>
-      <c r="F127" s="472"/>
+      <c r="C127" s="475"/>
+      <c r="D127" s="475"/>
+      <c r="E127" s="475"/>
+      <c r="F127" s="475"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21369,22 +21369,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="473" t="s">
+      <c r="B131" s="476" t="s">
         <v>517</v>
       </c>
-      <c r="C131" s="473"/>
-      <c r="D131" s="473"/>
-      <c r="E131" s="473"/>
-      <c r="F131" s="473"/>
+      <c r="C131" s="476"/>
+      <c r="D131" s="476"/>
+      <c r="E131" s="476"/>
+      <c r="F131" s="476"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="474" t="s">
+      <c r="B132" s="471" t="s">
         <v>518</v>
       </c>
-      <c r="C132" s="474"/>
-      <c r="D132" s="474"/>
-      <c r="E132" s="474"/>
-      <c r="F132" s="474"/>
+      <c r="C132" s="471"/>
+      <c r="D132" s="471"/>
+      <c r="E132" s="471"/>
+      <c r="F132" s="471"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21553,13 +21553,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="475" t="s">
+      <c r="B149" s="477" t="s">
         <v>519</v>
       </c>
-      <c r="C149" s="474"/>
-      <c r="D149" s="474"/>
-      <c r="E149" s="474"/>
-      <c r="F149" s="474"/>
+      <c r="C149" s="471"/>
+      <c r="D149" s="471"/>
+      <c r="E149" s="471"/>
+      <c r="F149" s="471"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21567,13 +21567,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="476" t="s">
+      <c r="B152" s="473" t="s">
         <v>520</v>
       </c>
-      <c r="C152" s="476"/>
-      <c r="D152" s="476"/>
-      <c r="E152" s="476"/>
-      <c r="F152" s="476"/>
+      <c r="C152" s="473"/>
+      <c r="D152" s="473"/>
+      <c r="E152" s="473"/>
+      <c r="F152" s="473"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21610,22 +21610,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="471" t="s">
+      <c r="B161" s="474" t="s">
         <v>385</v>
       </c>
-      <c r="C161" s="471"/>
-      <c r="D161" s="471"/>
-      <c r="E161" s="471"/>
-      <c r="F161" s="471"/>
+      <c r="C161" s="474"/>
+      <c r="D161" s="474"/>
+      <c r="E161" s="474"/>
+      <c r="F161" s="474"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="471" t="s">
+      <c r="B162" s="474" t="s">
         <v>386</v>
       </c>
-      <c r="C162" s="471"/>
-      <c r="D162" s="471"/>
-      <c r="E162" s="471"/>
-      <c r="F162" s="471"/>
+      <c r="C162" s="474"/>
+      <c r="D162" s="474"/>
+      <c r="E162" s="474"/>
+      <c r="F162" s="474"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21649,12 +21649,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21669,15 +21672,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/000858.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/000858.SZ_Valuation.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C0ACCCB-FCD9-4C0E-9794-92A68C8DD655}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB971561-342C-43C4-AA0D-F29292F865E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4986,30 +4986,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5019,25 +5019,25 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5407,7 +5407,7 @@
         <v>347</v>
       </c>
       <c r="C8" s="47">
-        <v>100.64</v>
+        <v>101.27</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5425,14 +5425,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>390645.02962320001</v>
+        <v>393090.44266634999</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>524</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.16903913408793184</v>
+        <v>0.16655268298421899</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5440,13 +5440,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="460" t="s">
+      <c r="B12" s="462" t="s">
         <v>352</v>
       </c>
-      <c r="C12" s="460"/>
-      <c r="D12" s="460"/>
-      <c r="E12" s="460"/>
-      <c r="F12" s="460"/>
+      <c r="C12" s="462"/>
+      <c r="D12" s="462"/>
+      <c r="E12" s="462"/>
+      <c r="F12" s="462"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5624,22 +5624,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="460" t="s">
+      <c r="B29" s="462" t="s">
         <v>353</v>
       </c>
-      <c r="C29" s="460"/>
-      <c r="D29" s="460"/>
-      <c r="E29" s="460"/>
-      <c r="F29" s="460"/>
+      <c r="C29" s="462"/>
+      <c r="D29" s="462"/>
+      <c r="E29" s="462"/>
+      <c r="F29" s="462"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="462" t="s">
+      <c r="B30" s="466" t="s">
         <v>265</v>
       </c>
-      <c r="C30" s="462"/>
-      <c r="D30" s="462"/>
-      <c r="E30" s="462"/>
-      <c r="F30" s="462"/>
+      <c r="C30" s="466"/>
+      <c r="D30" s="466"/>
+      <c r="E30" s="466"/>
+      <c r="F30" s="466"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5651,13 +5651,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="461" t="s">
+      <c r="B33" s="463" t="s">
         <v>195</v>
       </c>
-      <c r="C33" s="461"/>
-      <c r="D33" s="461"/>
-      <c r="E33" s="461"/>
-      <c r="F33" s="461"/>
+      <c r="C33" s="463"/>
+      <c r="D33" s="463"/>
+      <c r="E33" s="463"/>
+      <c r="F33" s="463"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5677,13 +5677,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="461" t="s">
+      <c r="B36" s="463" t="s">
         <v>197</v>
       </c>
-      <c r="C36" s="461"/>
-      <c r="D36" s="461"/>
-      <c r="E36" s="461"/>
-      <c r="F36" s="461"/>
+      <c r="C36" s="463"/>
+      <c r="D36" s="463"/>
+      <c r="E36" s="463"/>
+      <c r="F36" s="463"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5712,13 +5712,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="461" t="s">
+      <c r="B40" s="463" t="s">
         <v>200</v>
       </c>
-      <c r="C40" s="461"/>
-      <c r="D40" s="461"/>
-      <c r="E40" s="461"/>
-      <c r="F40" s="461"/>
+      <c r="C40" s="463"/>
+      <c r="D40" s="463"/>
+      <c r="E40" s="463"/>
+      <c r="F40" s="463"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5734,13 +5734,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="461" t="s">
+      <c r="B43" s="463" t="s">
         <v>204</v>
       </c>
-      <c r="C43" s="461"/>
-      <c r="D43" s="461"/>
-      <c r="E43" s="461"/>
-      <c r="F43" s="461"/>
+      <c r="C43" s="463"/>
+      <c r="D43" s="463"/>
+      <c r="E43" s="463"/>
+      <c r="F43" s="463"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5804,13 +5804,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="461" t="s">
+      <c r="B51" s="463" t="s">
         <v>205</v>
       </c>
-      <c r="C51" s="461"/>
-      <c r="D51" s="461"/>
-      <c r="E51" s="461"/>
-      <c r="F51" s="461"/>
+      <c r="C51" s="463"/>
+      <c r="D51" s="463"/>
+      <c r="E51" s="463"/>
+      <c r="F51" s="463"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5826,7 +5826,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="461" t="s">
+      <c r="B54" s="463" t="s">
         <v>264</v>
       </c>
       <c r="C54" s="464"/>
@@ -5848,22 +5848,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="460" t="s">
+      <c r="B57" s="462" t="s">
         <v>269</v>
       </c>
-      <c r="C57" s="460"/>
-      <c r="D57" s="460"/>
-      <c r="E57" s="460"/>
-      <c r="F57" s="460"/>
+      <c r="C57" s="462"/>
+      <c r="D57" s="462"/>
+      <c r="E57" s="462"/>
+      <c r="F57" s="462"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="460" t="s">
+      <c r="B58" s="462" t="s">
         <v>281</v>
       </c>
-      <c r="C58" s="460"/>
-      <c r="D58" s="460"/>
-      <c r="E58" s="460"/>
-      <c r="F58" s="460"/>
+      <c r="C58" s="462"/>
+      <c r="D58" s="462"/>
+      <c r="E58" s="462"/>
+      <c r="F58" s="462"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>7.628997755019358E-2</v>
+        <v>7.5815378104586578E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5907,7 +5907,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>2.8339626391096981E-2</v>
+        <v>2.8163325762812285E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>320</v>
@@ -5998,13 +5998,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="460" t="s">
+      <c r="B73" s="462" t="s">
         <v>475</v>
       </c>
-      <c r="C73" s="460"/>
-      <c r="D73" s="460"/>
-      <c r="E73" s="460"/>
-      <c r="F73" s="460"/>
+      <c r="C73" s="462"/>
+      <c r="D73" s="462"/>
+      <c r="E73" s="462"/>
+      <c r="F73" s="462"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6023,13 +6023,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="460" t="s">
+      <c r="B77" s="462" t="s">
         <v>270</v>
       </c>
-      <c r="C77" s="460"/>
-      <c r="D77" s="460"/>
-      <c r="E77" s="460"/>
-      <c r="F77" s="460"/>
+      <c r="C77" s="462"/>
+      <c r="D77" s="462"/>
+      <c r="E77" s="462"/>
+      <c r="F77" s="462"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6198,31 +6198,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="460" t="s">
+      <c r="B96" s="462" t="s">
         <v>482</v>
       </c>
-      <c r="C96" s="460"/>
-      <c r="D96" s="460"/>
-      <c r="E96" s="460"/>
-      <c r="F96" s="460"/>
+      <c r="C96" s="462"/>
+      <c r="D96" s="462"/>
+      <c r="E96" s="462"/>
+      <c r="F96" s="462"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="462" t="s">
+      <c r="B97" s="466" t="s">
         <v>481</v>
       </c>
-      <c r="C97" s="462"/>
-      <c r="D97" s="462"/>
-      <c r="E97" s="462"/>
-      <c r="F97" s="462"/>
+      <c r="C97" s="466"/>
+      <c r="D97" s="466"/>
+      <c r="E97" s="466"/>
+      <c r="F97" s="466"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="462" t="s">
+      <c r="B98" s="466" t="s">
         <v>480</v>
       </c>
-      <c r="C98" s="462"/>
-      <c r="D98" s="462"/>
-      <c r="E98" s="462"/>
-      <c r="F98" s="462"/>
+      <c r="C98" s="466"/>
+      <c r="D98" s="466"/>
+      <c r="E98" s="466"/>
+      <c r="F98" s="466"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6272,22 +6272,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="460" t="s">
+      <c r="B107" s="462" t="s">
         <v>282</v>
       </c>
-      <c r="C107" s="460"/>
-      <c r="D107" s="460"/>
-      <c r="E107" s="460"/>
-      <c r="F107" s="460"/>
+      <c r="C107" s="462"/>
+      <c r="D107" s="462"/>
+      <c r="E107" s="462"/>
+      <c r="F107" s="462"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="460" t="s">
+      <c r="B108" s="462" t="s">
         <v>283</v>
       </c>
-      <c r="C108" s="460"/>
-      <c r="D108" s="460"/>
-      <c r="E108" s="460"/>
-      <c r="F108" s="460"/>
+      <c r="C108" s="462"/>
+      <c r="D108" s="462"/>
+      <c r="E108" s="462"/>
+      <c r="F108" s="462"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6321,13 +6321,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="460" t="s">
+      <c r="B114" s="462" t="s">
         <v>488</v>
       </c>
-      <c r="C114" s="460"/>
-      <c r="D114" s="460"/>
-      <c r="E114" s="460"/>
-      <c r="F114" s="460"/>
+      <c r="C114" s="462"/>
+      <c r="D114" s="462"/>
+      <c r="E114" s="462"/>
+      <c r="F114" s="462"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6462,13 +6462,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="461" t="s">
+      <c r="B124" s="463" t="s">
         <v>354</v>
       </c>
-      <c r="C124" s="461"/>
-      <c r="D124" s="461"/>
-      <c r="E124" s="461"/>
-      <c r="F124" s="461"/>
+      <c r="C124" s="463"/>
+      <c r="D124" s="463"/>
+      <c r="E124" s="463"/>
+      <c r="F124" s="463"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6503,22 +6503,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="463" t="s">
+      <c r="B131" s="467" t="s">
         <v>284</v>
       </c>
-      <c r="C131" s="463"/>
-      <c r="D131" s="463"/>
-      <c r="E131" s="463"/>
-      <c r="F131" s="463"/>
+      <c r="C131" s="467"/>
+      <c r="D131" s="467"/>
+      <c r="E131" s="467"/>
+      <c r="F131" s="467"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="460" t="s">
+      <c r="B132" s="462" t="s">
         <v>356</v>
       </c>
-      <c r="C132" s="460"/>
-      <c r="D132" s="460"/>
-      <c r="E132" s="460"/>
-      <c r="F132" s="460"/>
+      <c r="C132" s="462"/>
+      <c r="D132" s="462"/>
+      <c r="E132" s="462"/>
+      <c r="F132" s="462"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6694,13 +6694,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="467" t="s">
+      <c r="B149" s="461" t="s">
         <v>357</v>
       </c>
-      <c r="C149" s="460"/>
-      <c r="D149" s="460"/>
-      <c r="E149" s="460"/>
-      <c r="F149" s="460"/>
+      <c r="C149" s="462"/>
+      <c r="D149" s="462"/>
+      <c r="E149" s="462"/>
+      <c r="F149" s="462"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6737,13 +6737,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="461" t="s">
+      <c r="B158" s="463" t="s">
         <v>435</v>
       </c>
-      <c r="C158" s="461"/>
-      <c r="D158" s="461"/>
-      <c r="E158" s="461"/>
-      <c r="F158" s="461"/>
+      <c r="C158" s="463"/>
+      <c r="D158" s="463"/>
+      <c r="E158" s="463"/>
+      <c r="F158" s="463"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6751,22 +6751,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="466" t="s">
+      <c r="B161" s="460" t="s">
         <v>293</v>
       </c>
-      <c r="C161" s="466"/>
-      <c r="D161" s="466"/>
-      <c r="E161" s="466"/>
-      <c r="F161" s="466"/>
+      <c r="C161" s="460"/>
+      <c r="D161" s="460"/>
+      <c r="E161" s="460"/>
+      <c r="F161" s="460"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="466" t="s">
+      <c r="B162" s="460" t="s">
         <v>294</v>
       </c>
-      <c r="C162" s="466"/>
-      <c r="D162" s="466"/>
-      <c r="E162" s="466"/>
-      <c r="F162" s="466"/>
+      <c r="C162" s="460"/>
+      <c r="D162" s="460"/>
+      <c r="E162" s="460"/>
+      <c r="F162" s="460"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6790,18 +6790,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6818,6 +6806,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -14008,16 +14008,16 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>2.8339626391096981E-2</v>
+        <v>2.8163325762812285E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>2.8339626391096981E-2</v>
+        <v>2.8163325762812285E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>4.1762718600953895E-2</v>
+        <v>4.1502913004838556E-2</v>
       </c>
       <c r="I92" s="22" t="str">
         <f t="shared" si="38"/>
@@ -15229,18 +15229,18 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>7.628997755019358E-2</v>
+        <v>7.5815378104586578E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>6.7730355742635709E-2</v>
+        <v>6.7309005647663248E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>6.5209841844164132E-2</v>
+        <v>6.4804171849478398E-2</v>
       </c>
       <c r="I124" s="74" t="str">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
@@ -15286,11 +15286,11 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.4970901885880981E-2</v>
+        <v>8.4442298467414467E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.0689053211693576E-2</v>
+        <v>8.0187087145500574E-2</v>
       </c>
       <c r="I125" s="22" t="str">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -19748,7 +19748,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>100.64</v>
+        <v>101.27</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19759,7 +19759,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.16903913408793184</v>
+        <v>0.16655268298421899</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -20255,7 +20255,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>100.64</v>
+        <v>101.27</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20273,14 +20273,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>390645.02962320001</v>
+        <v>393090.44266634999</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>525</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.16903913408793184</v>
+        <v>0.16655268298421899</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20288,13 +20288,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="471" t="s">
+      <c r="B12" s="474" t="s">
         <v>494</v>
       </c>
-      <c r="C12" s="471"/>
-      <c r="D12" s="471"/>
-      <c r="E12" s="471"/>
-      <c r="F12" s="471"/>
+      <c r="C12" s="474"/>
+      <c r="D12" s="474"/>
+      <c r="E12" s="474"/>
+      <c r="F12" s="474"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20479,22 +20479,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="471" t="s">
+      <c r="B29" s="474" t="s">
         <v>495</v>
       </c>
-      <c r="C29" s="471"/>
-      <c r="D29" s="471"/>
-      <c r="E29" s="471"/>
-      <c r="F29" s="471"/>
+      <c r="C29" s="474"/>
+      <c r="D29" s="474"/>
+      <c r="E29" s="474"/>
+      <c r="F29" s="474"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="472" t="s">
+      <c r="B30" s="477" t="s">
         <v>496</v>
       </c>
-      <c r="C30" s="472"/>
-      <c r="D30" s="472"/>
-      <c r="E30" s="472"/>
-      <c r="F30" s="472"/>
+      <c r="C30" s="477"/>
+      <c r="D30" s="477"/>
+      <c r="E30" s="477"/>
+      <c r="F30" s="477"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20684,10 +20684,10 @@
       <c r="B54" s="470" t="s">
         <v>503</v>
       </c>
-      <c r="C54" s="473"/>
-      <c r="D54" s="473"/>
-      <c r="E54" s="473"/>
-      <c r="F54" s="473"/>
+      <c r="C54" s="476"/>
+      <c r="D54" s="476"/>
+      <c r="E54" s="476"/>
+      <c r="F54" s="476"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20703,22 +20703,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="471" t="s">
+      <c r="B57" s="474" t="s">
         <v>504</v>
       </c>
-      <c r="C57" s="471"/>
-      <c r="D57" s="471"/>
-      <c r="E57" s="471"/>
-      <c r="F57" s="471"/>
+      <c r="C57" s="474"/>
+      <c r="D57" s="474"/>
+      <c r="E57" s="474"/>
+      <c r="F57" s="474"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="471" t="s">
+      <c r="B58" s="474" t="s">
         <v>505</v>
       </c>
-      <c r="C58" s="471"/>
-      <c r="D58" s="471"/>
-      <c r="E58" s="471"/>
-      <c r="F58" s="471"/>
+      <c r="C58" s="474"/>
+      <c r="D58" s="474"/>
+      <c r="E58" s="474"/>
+      <c r="F58" s="474"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20752,7 +20752,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>7.628997755019358E-2</v>
+        <v>7.5815378104586578E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20762,7 +20762,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>2.8339626391096981E-2</v>
+        <v>2.8163325762812285E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>370</v>
@@ -20853,22 +20853,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="471" t="s">
+      <c r="B73" s="474" t="s">
         <v>506</v>
       </c>
-      <c r="C73" s="471"/>
-      <c r="D73" s="471"/>
-      <c r="E73" s="471"/>
-      <c r="F73" s="471"/>
+      <c r="C73" s="474"/>
+      <c r="D73" s="474"/>
+      <c r="E73" s="474"/>
+      <c r="F73" s="474"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="472" t="s">
+      <c r="B74" s="477" t="s">
         <v>476</v>
       </c>
-      <c r="C74" s="472"/>
-      <c r="D74" s="472"/>
-      <c r="E74" s="472"/>
-      <c r="F74" s="472"/>
+      <c r="C74" s="477"/>
+      <c r="D74" s="477"/>
+      <c r="E74" s="477"/>
+      <c r="F74" s="477"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -20876,13 +20876,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="471" t="s">
+      <c r="B77" s="474" t="s">
         <v>507</v>
       </c>
-      <c r="C77" s="471"/>
-      <c r="D77" s="471"/>
-      <c r="E77" s="471"/>
-      <c r="F77" s="471"/>
+      <c r="C77" s="474"/>
+      <c r="D77" s="474"/>
+      <c r="E77" s="474"/>
+      <c r="F77" s="474"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21031,33 +21031,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="471" t="s">
+      <c r="B96" s="474" t="s">
         <v>510</v>
       </c>
-      <c r="C96" s="471"/>
-      <c r="D96" s="471"/>
-      <c r="E96" s="471"/>
-      <c r="F96" s="471"/>
+      <c r="C96" s="474"/>
+      <c r="D96" s="474"/>
+      <c r="E96" s="474"/>
+      <c r="F96" s="474"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="472" t="s">
+      <c r="B97" s="477" t="s">
         <v>511</v>
       </c>
-      <c r="C97" s="472"/>
-      <c r="D97" s="472"/>
-      <c r="E97" s="472"/>
-      <c r="F97" s="472"/>
+      <c r="C97" s="477"/>
+      <c r="D97" s="477"/>
+      <c r="E97" s="477"/>
+      <c r="F97" s="477"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="472" t="s">
+      <c r="B98" s="477" t="s">
         <v>512</v>
       </c>
-      <c r="C98" s="472"/>
-      <c r="D98" s="472"/>
-      <c r="E98" s="472"/>
-      <c r="F98" s="472"/>
+      <c r="C98" s="477"/>
+      <c r="D98" s="477"/>
+      <c r="E98" s="477"/>
+      <c r="F98" s="477"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21120,23 +21120,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="471" t="s">
+      <c r="B107" s="474" t="s">
         <v>513</v>
       </c>
-      <c r="C107" s="471"/>
-      <c r="D107" s="471"/>
-      <c r="E107" s="471"/>
-      <c r="F107" s="471"/>
+      <c r="C107" s="474"/>
+      <c r="D107" s="474"/>
+      <c r="E107" s="474"/>
+      <c r="F107" s="474"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="471" t="s">
+      <c r="B108" s="474" t="s">
         <v>532</v>
       </c>
-      <c r="C108" s="471"/>
-      <c r="D108" s="471"/>
-      <c r="E108" s="471"/>
-      <c r="F108" s="471"/>
+      <c r="C108" s="474"/>
+      <c r="D108" s="474"/>
+      <c r="E108" s="474"/>
+      <c r="F108" s="474"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21180,13 +21180,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="471" t="s">
+      <c r="B114" s="474" t="s">
         <v>514</v>
       </c>
-      <c r="C114" s="471"/>
-      <c r="D114" s="471"/>
-      <c r="E114" s="471"/>
-      <c r="F114" s="471"/>
+      <c r="C114" s="474"/>
+      <c r="D114" s="474"/>
+      <c r="E114" s="474"/>
+      <c r="F114" s="474"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21350,13 +21350,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="475" t="s">
+      <c r="B127" s="472" t="s">
         <v>516</v>
       </c>
-      <c r="C127" s="475"/>
-      <c r="D127" s="475"/>
-      <c r="E127" s="475"/>
-      <c r="F127" s="475"/>
+      <c r="C127" s="472"/>
+      <c r="D127" s="472"/>
+      <c r="E127" s="472"/>
+      <c r="F127" s="472"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21369,22 +21369,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="476" t="s">
+      <c r="B131" s="473" t="s">
         <v>517</v>
       </c>
-      <c r="C131" s="476"/>
-      <c r="D131" s="476"/>
-      <c r="E131" s="476"/>
-      <c r="F131" s="476"/>
+      <c r="C131" s="473"/>
+      <c r="D131" s="473"/>
+      <c r="E131" s="473"/>
+      <c r="F131" s="473"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="471" t="s">
+      <c r="B132" s="474" t="s">
         <v>518</v>
       </c>
-      <c r="C132" s="471"/>
-      <c r="D132" s="471"/>
-      <c r="E132" s="471"/>
-      <c r="F132" s="471"/>
+      <c r="C132" s="474"/>
+      <c r="D132" s="474"/>
+      <c r="E132" s="474"/>
+      <c r="F132" s="474"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21553,13 +21553,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="477" t="s">
+      <c r="B149" s="475" t="s">
         <v>519</v>
       </c>
-      <c r="C149" s="471"/>
-      <c r="D149" s="471"/>
-      <c r="E149" s="471"/>
-      <c r="F149" s="471"/>
+      <c r="C149" s="474"/>
+      <c r="D149" s="474"/>
+      <c r="E149" s="474"/>
+      <c r="F149" s="474"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21567,13 +21567,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="473" t="s">
+      <c r="B152" s="476" t="s">
         <v>520</v>
       </c>
-      <c r="C152" s="473"/>
-      <c r="D152" s="473"/>
-      <c r="E152" s="473"/>
-      <c r="F152" s="473"/>
+      <c r="C152" s="476"/>
+      <c r="D152" s="476"/>
+      <c r="E152" s="476"/>
+      <c r="F152" s="476"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21610,22 +21610,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="474" t="s">
+      <c r="B161" s="471" t="s">
         <v>385</v>
       </c>
-      <c r="C161" s="474"/>
-      <c r="D161" s="474"/>
-      <c r="E161" s="474"/>
-      <c r="F161" s="474"/>
+      <c r="C161" s="471"/>
+      <c r="D161" s="471"/>
+      <c r="E161" s="471"/>
+      <c r="F161" s="471"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="474" t="s">
+      <c r="B162" s="471" t="s">
         <v>386</v>
       </c>
-      <c r="C162" s="474"/>
-      <c r="D162" s="474"/>
-      <c r="E162" s="474"/>
-      <c r="F162" s="474"/>
+      <c r="C162" s="471"/>
+      <c r="D162" s="471"/>
+      <c r="E162" s="471"/>
+      <c r="F162" s="471"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21649,15 +21649,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21672,12 +21669,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/000858.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/000858.SZ_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB971561-342C-43C4-AA0D-F29292F865E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19C9D076-B930-4A70-AF8A-1BA5CFDE174B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4986,30 +4986,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5019,6 +5019,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5028,16 +5037,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5440,13 +5440,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="462" t="s">
+      <c r="B12" s="460" t="s">
         <v>352</v>
       </c>
-      <c r="C12" s="462"/>
-      <c r="D12" s="462"/>
-      <c r="E12" s="462"/>
-      <c r="F12" s="462"/>
+      <c r="C12" s="460"/>
+      <c r="D12" s="460"/>
+      <c r="E12" s="460"/>
+      <c r="F12" s="460"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5624,22 +5624,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="462" t="s">
+      <c r="B29" s="460" t="s">
         <v>353</v>
       </c>
-      <c r="C29" s="462"/>
-      <c r="D29" s="462"/>
-      <c r="E29" s="462"/>
-      <c r="F29" s="462"/>
+      <c r="C29" s="460"/>
+      <c r="D29" s="460"/>
+      <c r="E29" s="460"/>
+      <c r="F29" s="460"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="466" t="s">
+      <c r="B30" s="462" t="s">
         <v>265</v>
       </c>
-      <c r="C30" s="466"/>
-      <c r="D30" s="466"/>
-      <c r="E30" s="466"/>
-      <c r="F30" s="466"/>
+      <c r="C30" s="462"/>
+      <c r="D30" s="462"/>
+      <c r="E30" s="462"/>
+      <c r="F30" s="462"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5651,13 +5651,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="463" t="s">
+      <c r="B33" s="461" t="s">
         <v>195</v>
       </c>
-      <c r="C33" s="463"/>
-      <c r="D33" s="463"/>
-      <c r="E33" s="463"/>
-      <c r="F33" s="463"/>
+      <c r="C33" s="461"/>
+      <c r="D33" s="461"/>
+      <c r="E33" s="461"/>
+      <c r="F33" s="461"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5677,13 +5677,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="463" t="s">
+      <c r="B36" s="461" t="s">
         <v>197</v>
       </c>
-      <c r="C36" s="463"/>
-      <c r="D36" s="463"/>
-      <c r="E36" s="463"/>
-      <c r="F36" s="463"/>
+      <c r="C36" s="461"/>
+      <c r="D36" s="461"/>
+      <c r="E36" s="461"/>
+      <c r="F36" s="461"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5712,13 +5712,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="463" t="s">
+      <c r="B40" s="461" t="s">
         <v>200</v>
       </c>
-      <c r="C40" s="463"/>
-      <c r="D40" s="463"/>
-      <c r="E40" s="463"/>
-      <c r="F40" s="463"/>
+      <c r="C40" s="461"/>
+      <c r="D40" s="461"/>
+      <c r="E40" s="461"/>
+      <c r="F40" s="461"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5734,13 +5734,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="463" t="s">
+      <c r="B43" s="461" t="s">
         <v>204</v>
       </c>
-      <c r="C43" s="463"/>
-      <c r="D43" s="463"/>
-      <c r="E43" s="463"/>
-      <c r="F43" s="463"/>
+      <c r="C43" s="461"/>
+      <c r="D43" s="461"/>
+      <c r="E43" s="461"/>
+      <c r="F43" s="461"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5804,13 +5804,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="463" t="s">
+      <c r="B51" s="461" t="s">
         <v>205</v>
       </c>
-      <c r="C51" s="463"/>
-      <c r="D51" s="463"/>
-      <c r="E51" s="463"/>
-      <c r="F51" s="463"/>
+      <c r="C51" s="461"/>
+      <c r="D51" s="461"/>
+      <c r="E51" s="461"/>
+      <c r="F51" s="461"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5826,7 +5826,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="463" t="s">
+      <c r="B54" s="461" t="s">
         <v>264</v>
       </c>
       <c r="C54" s="464"/>
@@ -5848,22 +5848,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="462" t="s">
+      <c r="B57" s="460" t="s">
         <v>269</v>
       </c>
-      <c r="C57" s="462"/>
-      <c r="D57" s="462"/>
-      <c r="E57" s="462"/>
-      <c r="F57" s="462"/>
+      <c r="C57" s="460"/>
+      <c r="D57" s="460"/>
+      <c r="E57" s="460"/>
+      <c r="F57" s="460"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="462" t="s">
+      <c r="B58" s="460" t="s">
         <v>281</v>
       </c>
-      <c r="C58" s="462"/>
-      <c r="D58" s="462"/>
-      <c r="E58" s="462"/>
-      <c r="F58" s="462"/>
+      <c r="C58" s="460"/>
+      <c r="D58" s="460"/>
+      <c r="E58" s="460"/>
+      <c r="F58" s="460"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5998,13 +5998,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="462" t="s">
+      <c r="B73" s="460" t="s">
         <v>475</v>
       </c>
-      <c r="C73" s="462"/>
-      <c r="D73" s="462"/>
-      <c r="E73" s="462"/>
-      <c r="F73" s="462"/>
+      <c r="C73" s="460"/>
+      <c r="D73" s="460"/>
+      <c r="E73" s="460"/>
+      <c r="F73" s="460"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6023,13 +6023,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="462" t="s">
+      <c r="B77" s="460" t="s">
         <v>270</v>
       </c>
-      <c r="C77" s="462"/>
-      <c r="D77" s="462"/>
-      <c r="E77" s="462"/>
-      <c r="F77" s="462"/>
+      <c r="C77" s="460"/>
+      <c r="D77" s="460"/>
+      <c r="E77" s="460"/>
+      <c r="F77" s="460"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6198,31 +6198,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="462" t="s">
+      <c r="B96" s="460" t="s">
         <v>482</v>
       </c>
-      <c r="C96" s="462"/>
-      <c r="D96" s="462"/>
-      <c r="E96" s="462"/>
-      <c r="F96" s="462"/>
+      <c r="C96" s="460"/>
+      <c r="D96" s="460"/>
+      <c r="E96" s="460"/>
+      <c r="F96" s="460"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="466" t="s">
+      <c r="B97" s="462" t="s">
         <v>481</v>
       </c>
-      <c r="C97" s="466"/>
-      <c r="D97" s="466"/>
-      <c r="E97" s="466"/>
-      <c r="F97" s="466"/>
+      <c r="C97" s="462"/>
+      <c r="D97" s="462"/>
+      <c r="E97" s="462"/>
+      <c r="F97" s="462"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="466" t="s">
+      <c r="B98" s="462" t="s">
         <v>480</v>
       </c>
-      <c r="C98" s="466"/>
-      <c r="D98" s="466"/>
-      <c r="E98" s="466"/>
-      <c r="F98" s="466"/>
+      <c r="C98" s="462"/>
+      <c r="D98" s="462"/>
+      <c r="E98" s="462"/>
+      <c r="F98" s="462"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6272,22 +6272,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="462" t="s">
+      <c r="B107" s="460" t="s">
         <v>282</v>
       </c>
-      <c r="C107" s="462"/>
-      <c r="D107" s="462"/>
-      <c r="E107" s="462"/>
-      <c r="F107" s="462"/>
+      <c r="C107" s="460"/>
+      <c r="D107" s="460"/>
+      <c r="E107" s="460"/>
+      <c r="F107" s="460"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="462" t="s">
+      <c r="B108" s="460" t="s">
         <v>283</v>
       </c>
-      <c r="C108" s="462"/>
-      <c r="D108" s="462"/>
-      <c r="E108" s="462"/>
-      <c r="F108" s="462"/>
+      <c r="C108" s="460"/>
+      <c r="D108" s="460"/>
+      <c r="E108" s="460"/>
+      <c r="F108" s="460"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6321,13 +6321,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="462" t="s">
+      <c r="B114" s="460" t="s">
         <v>488</v>
       </c>
-      <c r="C114" s="462"/>
-      <c r="D114" s="462"/>
-      <c r="E114" s="462"/>
-      <c r="F114" s="462"/>
+      <c r="C114" s="460"/>
+      <c r="D114" s="460"/>
+      <c r="E114" s="460"/>
+      <c r="F114" s="460"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6462,13 +6462,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="463" t="s">
+      <c r="B124" s="461" t="s">
         <v>354</v>
       </c>
-      <c r="C124" s="463"/>
-      <c r="D124" s="463"/>
-      <c r="E124" s="463"/>
-      <c r="F124" s="463"/>
+      <c r="C124" s="461"/>
+      <c r="D124" s="461"/>
+      <c r="E124" s="461"/>
+      <c r="F124" s="461"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6503,22 +6503,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="467" t="s">
+      <c r="B131" s="463" t="s">
         <v>284</v>
       </c>
-      <c r="C131" s="467"/>
-      <c r="D131" s="467"/>
-      <c r="E131" s="467"/>
-      <c r="F131" s="467"/>
+      <c r="C131" s="463"/>
+      <c r="D131" s="463"/>
+      <c r="E131" s="463"/>
+      <c r="F131" s="463"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="462" t="s">
+      <c r="B132" s="460" t="s">
         <v>356</v>
       </c>
-      <c r="C132" s="462"/>
-      <c r="D132" s="462"/>
-      <c r="E132" s="462"/>
-      <c r="F132" s="462"/>
+      <c r="C132" s="460"/>
+      <c r="D132" s="460"/>
+      <c r="E132" s="460"/>
+      <c r="F132" s="460"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6694,13 +6694,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="461" t="s">
+      <c r="B149" s="467" t="s">
         <v>357</v>
       </c>
-      <c r="C149" s="462"/>
-      <c r="D149" s="462"/>
-      <c r="E149" s="462"/>
-      <c r="F149" s="462"/>
+      <c r="C149" s="460"/>
+      <c r="D149" s="460"/>
+      <c r="E149" s="460"/>
+      <c r="F149" s="460"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6737,13 +6737,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="463" t="s">
+      <c r="B158" s="461" t="s">
         <v>435</v>
       </c>
-      <c r="C158" s="463"/>
-      <c r="D158" s="463"/>
-      <c r="E158" s="463"/>
-      <c r="F158" s="463"/>
+      <c r="C158" s="461"/>
+      <c r="D158" s="461"/>
+      <c r="E158" s="461"/>
+      <c r="F158" s="461"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6751,22 +6751,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="460" t="s">
+      <c r="B161" s="466" t="s">
         <v>293</v>
       </c>
-      <c r="C161" s="460"/>
-      <c r="D161" s="460"/>
-      <c r="E161" s="460"/>
-      <c r="F161" s="460"/>
+      <c r="C161" s="466"/>
+      <c r="D161" s="466"/>
+      <c r="E161" s="466"/>
+      <c r="F161" s="466"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="460" t="s">
+      <c r="B162" s="466" t="s">
         <v>294</v>
       </c>
-      <c r="C162" s="460"/>
-      <c r="D162" s="460"/>
-      <c r="E162" s="460"/>
-      <c r="F162" s="460"/>
+      <c r="C162" s="466"/>
+      <c r="D162" s="466"/>
+      <c r="E162" s="466"/>
+      <c r="F162" s="466"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6790,6 +6790,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6806,18 +6818,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -20288,13 +20288,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="474" t="s">
+      <c r="B12" s="471" t="s">
         <v>494</v>
       </c>
-      <c r="C12" s="474"/>
-      <c r="D12" s="474"/>
-      <c r="E12" s="474"/>
-      <c r="F12" s="474"/>
+      <c r="C12" s="471"/>
+      <c r="D12" s="471"/>
+      <c r="E12" s="471"/>
+      <c r="F12" s="471"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20479,22 +20479,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="474" t="s">
+      <c r="B29" s="471" t="s">
         <v>495</v>
       </c>
-      <c r="C29" s="474"/>
-      <c r="D29" s="474"/>
-      <c r="E29" s="474"/>
-      <c r="F29" s="474"/>
+      <c r="C29" s="471"/>
+      <c r="D29" s="471"/>
+      <c r="E29" s="471"/>
+      <c r="F29" s="471"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="477" t="s">
+      <c r="B30" s="472" t="s">
         <v>496</v>
       </c>
-      <c r="C30" s="477"/>
-      <c r="D30" s="477"/>
-      <c r="E30" s="477"/>
-      <c r="F30" s="477"/>
+      <c r="C30" s="472"/>
+      <c r="D30" s="472"/>
+      <c r="E30" s="472"/>
+      <c r="F30" s="472"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20684,10 +20684,10 @@
       <c r="B54" s="470" t="s">
         <v>503</v>
       </c>
-      <c r="C54" s="476"/>
-      <c r="D54" s="476"/>
-      <c r="E54" s="476"/>
-      <c r="F54" s="476"/>
+      <c r="C54" s="473"/>
+      <c r="D54" s="473"/>
+      <c r="E54" s="473"/>
+      <c r="F54" s="473"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20703,22 +20703,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="474" t="s">
+      <c r="B57" s="471" t="s">
         <v>504</v>
       </c>
-      <c r="C57" s="474"/>
-      <c r="D57" s="474"/>
-      <c r="E57" s="474"/>
-      <c r="F57" s="474"/>
+      <c r="C57" s="471"/>
+      <c r="D57" s="471"/>
+      <c r="E57" s="471"/>
+      <c r="F57" s="471"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="474" t="s">
+      <c r="B58" s="471" t="s">
         <v>505</v>
       </c>
-      <c r="C58" s="474"/>
-      <c r="D58" s="474"/>
-      <c r="E58" s="474"/>
-      <c r="F58" s="474"/>
+      <c r="C58" s="471"/>
+      <c r="D58" s="471"/>
+      <c r="E58" s="471"/>
+      <c r="F58" s="471"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20853,22 +20853,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="474" t="s">
+      <c r="B73" s="471" t="s">
         <v>506</v>
       </c>
-      <c r="C73" s="474"/>
-      <c r="D73" s="474"/>
-      <c r="E73" s="474"/>
-      <c r="F73" s="474"/>
+      <c r="C73" s="471"/>
+      <c r="D73" s="471"/>
+      <c r="E73" s="471"/>
+      <c r="F73" s="471"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="477" t="s">
+      <c r="B74" s="472" t="s">
         <v>476</v>
       </c>
-      <c r="C74" s="477"/>
-      <c r="D74" s="477"/>
-      <c r="E74" s="477"/>
-      <c r="F74" s="477"/>
+      <c r="C74" s="472"/>
+      <c r="D74" s="472"/>
+      <c r="E74" s="472"/>
+      <c r="F74" s="472"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -20876,13 +20876,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="474" t="s">
+      <c r="B77" s="471" t="s">
         <v>507</v>
       </c>
-      <c r="C77" s="474"/>
-      <c r="D77" s="474"/>
-      <c r="E77" s="474"/>
-      <c r="F77" s="474"/>
+      <c r="C77" s="471"/>
+      <c r="D77" s="471"/>
+      <c r="E77" s="471"/>
+      <c r="F77" s="471"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21031,33 +21031,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="474" t="s">
+      <c r="B96" s="471" t="s">
         <v>510</v>
       </c>
-      <c r="C96" s="474"/>
-      <c r="D96" s="474"/>
-      <c r="E96" s="474"/>
-      <c r="F96" s="474"/>
+      <c r="C96" s="471"/>
+      <c r="D96" s="471"/>
+      <c r="E96" s="471"/>
+      <c r="F96" s="471"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="477" t="s">
+      <c r="B97" s="472" t="s">
         <v>511</v>
       </c>
-      <c r="C97" s="477"/>
-      <c r="D97" s="477"/>
-      <c r="E97" s="477"/>
-      <c r="F97" s="477"/>
+      <c r="C97" s="472"/>
+      <c r="D97" s="472"/>
+      <c r="E97" s="472"/>
+      <c r="F97" s="472"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="477" t="s">
+      <c r="B98" s="472" t="s">
         <v>512</v>
       </c>
-      <c r="C98" s="477"/>
-      <c r="D98" s="477"/>
-      <c r="E98" s="477"/>
-      <c r="F98" s="477"/>
+      <c r="C98" s="472"/>
+      <c r="D98" s="472"/>
+      <c r="E98" s="472"/>
+      <c r="F98" s="472"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21120,23 +21120,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="474" t="s">
+      <c r="B107" s="471" t="s">
         <v>513</v>
       </c>
-      <c r="C107" s="474"/>
-      <c r="D107" s="474"/>
-      <c r="E107" s="474"/>
-      <c r="F107" s="474"/>
+      <c r="C107" s="471"/>
+      <c r="D107" s="471"/>
+      <c r="E107" s="471"/>
+      <c r="F107" s="471"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="474" t="s">
+      <c r="B108" s="471" t="s">
         <v>532</v>
       </c>
-      <c r="C108" s="474"/>
-      <c r="D108" s="474"/>
-      <c r="E108" s="474"/>
-      <c r="F108" s="474"/>
+      <c r="C108" s="471"/>
+      <c r="D108" s="471"/>
+      <c r="E108" s="471"/>
+      <c r="F108" s="471"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21180,13 +21180,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="474" t="s">
+      <c r="B114" s="471" t="s">
         <v>514</v>
       </c>
-      <c r="C114" s="474"/>
-      <c r="D114" s="474"/>
-      <c r="E114" s="474"/>
-      <c r="F114" s="474"/>
+      <c r="C114" s="471"/>
+      <c r="D114" s="471"/>
+      <c r="E114" s="471"/>
+      <c r="F114" s="471"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21350,13 +21350,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="472" t="s">
+      <c r="B127" s="475" t="s">
         <v>516</v>
       </c>
-      <c r="C127" s="472"/>
-      <c r="D127" s="472"/>
-      <c r="E127" s="472"/>
-      <c r="F127" s="472"/>
+      <c r="C127" s="475"/>
+      <c r="D127" s="475"/>
+      <c r="E127" s="475"/>
+      <c r="F127" s="475"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21369,22 +21369,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="473" t="s">
+      <c r="B131" s="476" t="s">
         <v>517</v>
       </c>
-      <c r="C131" s="473"/>
-      <c r="D131" s="473"/>
-      <c r="E131" s="473"/>
-      <c r="F131" s="473"/>
+      <c r="C131" s="476"/>
+      <c r="D131" s="476"/>
+      <c r="E131" s="476"/>
+      <c r="F131" s="476"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="474" t="s">
+      <c r="B132" s="471" t="s">
         <v>518</v>
       </c>
-      <c r="C132" s="474"/>
-      <c r="D132" s="474"/>
-      <c r="E132" s="474"/>
-      <c r="F132" s="474"/>
+      <c r="C132" s="471"/>
+      <c r="D132" s="471"/>
+      <c r="E132" s="471"/>
+      <c r="F132" s="471"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21553,13 +21553,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="475" t="s">
+      <c r="B149" s="477" t="s">
         <v>519</v>
       </c>
-      <c r="C149" s="474"/>
-      <c r="D149" s="474"/>
-      <c r="E149" s="474"/>
-      <c r="F149" s="474"/>
+      <c r="C149" s="471"/>
+      <c r="D149" s="471"/>
+      <c r="E149" s="471"/>
+      <c r="F149" s="471"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21567,13 +21567,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="476" t="s">
+      <c r="B152" s="473" t="s">
         <v>520</v>
       </c>
-      <c r="C152" s="476"/>
-      <c r="D152" s="476"/>
-      <c r="E152" s="476"/>
-      <c r="F152" s="476"/>
+      <c r="C152" s="473"/>
+      <c r="D152" s="473"/>
+      <c r="E152" s="473"/>
+      <c r="F152" s="473"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21610,22 +21610,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="471" t="s">
+      <c r="B161" s="474" t="s">
         <v>385</v>
       </c>
-      <c r="C161" s="471"/>
-      <c r="D161" s="471"/>
-      <c r="E161" s="471"/>
-      <c r="F161" s="471"/>
+      <c r="C161" s="474"/>
+      <c r="D161" s="474"/>
+      <c r="E161" s="474"/>
+      <c r="F161" s="474"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="471" t="s">
+      <c r="B162" s="474" t="s">
         <v>386</v>
       </c>
-      <c r="C162" s="471"/>
-      <c r="D162" s="471"/>
-      <c r="E162" s="471"/>
-      <c r="F162" s="471"/>
+      <c r="C162" s="474"/>
+      <c r="D162" s="474"/>
+      <c r="E162" s="474"/>
+      <c r="F162" s="474"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21649,12 +21649,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21669,15 +21672,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/000858.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/000858.SZ_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19C9D076-B930-4A70-AF8A-1BA5CFDE174B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CB5D554-48DC-4BD0-A840-2FD2A7D44467}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4986,30 +4986,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5019,25 +5019,25 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5407,7 +5407,7 @@
         <v>347</v>
       </c>
       <c r="C8" s="47">
-        <v>101.27</v>
+        <v>98.34</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5425,14 +5425,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>393090.44266634999</v>
+        <v>381717.33121169999</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>524</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.16655268298421899</v>
+        <v>0.17829877655836915</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5440,13 +5440,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="460" t="s">
+      <c r="B12" s="462" t="s">
         <v>352</v>
       </c>
-      <c r="C12" s="460"/>
-      <c r="D12" s="460"/>
-      <c r="E12" s="460"/>
-      <c r="F12" s="460"/>
+      <c r="C12" s="462"/>
+      <c r="D12" s="462"/>
+      <c r="E12" s="462"/>
+      <c r="F12" s="462"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5624,22 +5624,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="460" t="s">
+      <c r="B29" s="462" t="s">
         <v>353</v>
       </c>
-      <c r="C29" s="460"/>
-      <c r="D29" s="460"/>
-      <c r="E29" s="460"/>
-      <c r="F29" s="460"/>
+      <c r="C29" s="462"/>
+      <c r="D29" s="462"/>
+      <c r="E29" s="462"/>
+      <c r="F29" s="462"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="462" t="s">
+      <c r="B30" s="466" t="s">
         <v>265</v>
       </c>
-      <c r="C30" s="462"/>
-      <c r="D30" s="462"/>
-      <c r="E30" s="462"/>
-      <c r="F30" s="462"/>
+      <c r="C30" s="466"/>
+      <c r="D30" s="466"/>
+      <c r="E30" s="466"/>
+      <c r="F30" s="466"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5651,13 +5651,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="461" t="s">
+      <c r="B33" s="463" t="s">
         <v>195</v>
       </c>
-      <c r="C33" s="461"/>
-      <c r="D33" s="461"/>
-      <c r="E33" s="461"/>
-      <c r="F33" s="461"/>
+      <c r="C33" s="463"/>
+      <c r="D33" s="463"/>
+      <c r="E33" s="463"/>
+      <c r="F33" s="463"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5677,13 +5677,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="461" t="s">
+      <c r="B36" s="463" t="s">
         <v>197</v>
       </c>
-      <c r="C36" s="461"/>
-      <c r="D36" s="461"/>
-      <c r="E36" s="461"/>
-      <c r="F36" s="461"/>
+      <c r="C36" s="463"/>
+      <c r="D36" s="463"/>
+      <c r="E36" s="463"/>
+      <c r="F36" s="463"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5712,13 +5712,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="461" t="s">
+      <c r="B40" s="463" t="s">
         <v>200</v>
       </c>
-      <c r="C40" s="461"/>
-      <c r="D40" s="461"/>
-      <c r="E40" s="461"/>
-      <c r="F40" s="461"/>
+      <c r="C40" s="463"/>
+      <c r="D40" s="463"/>
+      <c r="E40" s="463"/>
+      <c r="F40" s="463"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5734,13 +5734,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="461" t="s">
+      <c r="B43" s="463" t="s">
         <v>204</v>
       </c>
-      <c r="C43" s="461"/>
-      <c r="D43" s="461"/>
-      <c r="E43" s="461"/>
-      <c r="F43" s="461"/>
+      <c r="C43" s="463"/>
+      <c r="D43" s="463"/>
+      <c r="E43" s="463"/>
+      <c r="F43" s="463"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5804,13 +5804,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="461" t="s">
+      <c r="B51" s="463" t="s">
         <v>205</v>
       </c>
-      <c r="C51" s="461"/>
-      <c r="D51" s="461"/>
-      <c r="E51" s="461"/>
-      <c r="F51" s="461"/>
+      <c r="C51" s="463"/>
+      <c r="D51" s="463"/>
+      <c r="E51" s="463"/>
+      <c r="F51" s="463"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5826,7 +5826,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="461" t="s">
+      <c r="B54" s="463" t="s">
         <v>264</v>
       </c>
       <c r="C54" s="464"/>
@@ -5848,22 +5848,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="460" t="s">
+      <c r="B57" s="462" t="s">
         <v>269</v>
       </c>
-      <c r="C57" s="460"/>
-      <c r="D57" s="460"/>
-      <c r="E57" s="460"/>
-      <c r="F57" s="460"/>
+      <c r="C57" s="462"/>
+      <c r="D57" s="462"/>
+      <c r="E57" s="462"/>
+      <c r="F57" s="462"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="460" t="s">
+      <c r="B58" s="462" t="s">
         <v>281</v>
       </c>
-      <c r="C58" s="460"/>
-      <c r="D58" s="460"/>
-      <c r="E58" s="460"/>
-      <c r="F58" s="460"/>
+      <c r="C58" s="462"/>
+      <c r="D58" s="462"/>
+      <c r="E58" s="462"/>
+      <c r="F58" s="462"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>7.5815378104586578E-2</v>
+        <v>7.8074266225864164E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5907,7 +5907,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>2.8163325762812285E-2</v>
+        <v>2.9002440512507627E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>320</v>
@@ -5998,13 +5998,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="460" t="s">
+      <c r="B73" s="462" t="s">
         <v>475</v>
       </c>
-      <c r="C73" s="460"/>
-      <c r="D73" s="460"/>
-      <c r="E73" s="460"/>
-      <c r="F73" s="460"/>
+      <c r="C73" s="462"/>
+      <c r="D73" s="462"/>
+      <c r="E73" s="462"/>
+      <c r="F73" s="462"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6023,13 +6023,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="460" t="s">
+      <c r="B77" s="462" t="s">
         <v>270</v>
       </c>
-      <c r="C77" s="460"/>
-      <c r="D77" s="460"/>
-      <c r="E77" s="460"/>
-      <c r="F77" s="460"/>
+      <c r="C77" s="462"/>
+      <c r="D77" s="462"/>
+      <c r="E77" s="462"/>
+      <c r="F77" s="462"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6198,31 +6198,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="460" t="s">
+      <c r="B96" s="462" t="s">
         <v>482</v>
       </c>
-      <c r="C96" s="460"/>
-      <c r="D96" s="460"/>
-      <c r="E96" s="460"/>
-      <c r="F96" s="460"/>
+      <c r="C96" s="462"/>
+      <c r="D96" s="462"/>
+      <c r="E96" s="462"/>
+      <c r="F96" s="462"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="462" t="s">
+      <c r="B97" s="466" t="s">
         <v>481</v>
       </c>
-      <c r="C97" s="462"/>
-      <c r="D97" s="462"/>
-      <c r="E97" s="462"/>
-      <c r="F97" s="462"/>
+      <c r="C97" s="466"/>
+      <c r="D97" s="466"/>
+      <c r="E97" s="466"/>
+      <c r="F97" s="466"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="462" t="s">
+      <c r="B98" s="466" t="s">
         <v>480</v>
       </c>
-      <c r="C98" s="462"/>
-      <c r="D98" s="462"/>
-      <c r="E98" s="462"/>
-      <c r="F98" s="462"/>
+      <c r="C98" s="466"/>
+      <c r="D98" s="466"/>
+      <c r="E98" s="466"/>
+      <c r="F98" s="466"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6272,22 +6272,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="460" t="s">
+      <c r="B107" s="462" t="s">
         <v>282</v>
       </c>
-      <c r="C107" s="460"/>
-      <c r="D107" s="460"/>
-      <c r="E107" s="460"/>
-      <c r="F107" s="460"/>
+      <c r="C107" s="462"/>
+      <c r="D107" s="462"/>
+      <c r="E107" s="462"/>
+      <c r="F107" s="462"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="460" t="s">
+      <c r="B108" s="462" t="s">
         <v>283</v>
       </c>
-      <c r="C108" s="460"/>
-      <c r="D108" s="460"/>
-      <c r="E108" s="460"/>
-      <c r="F108" s="460"/>
+      <c r="C108" s="462"/>
+      <c r="D108" s="462"/>
+      <c r="E108" s="462"/>
+      <c r="F108" s="462"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6321,13 +6321,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="460" t="s">
+      <c r="B114" s="462" t="s">
         <v>488</v>
       </c>
-      <c r="C114" s="460"/>
-      <c r="D114" s="460"/>
-      <c r="E114" s="460"/>
-      <c r="F114" s="460"/>
+      <c r="C114" s="462"/>
+      <c r="D114" s="462"/>
+      <c r="E114" s="462"/>
+      <c r="F114" s="462"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6462,13 +6462,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="461" t="s">
+      <c r="B124" s="463" t="s">
         <v>354</v>
       </c>
-      <c r="C124" s="461"/>
-      <c r="D124" s="461"/>
-      <c r="E124" s="461"/>
-      <c r="F124" s="461"/>
+      <c r="C124" s="463"/>
+      <c r="D124" s="463"/>
+      <c r="E124" s="463"/>
+      <c r="F124" s="463"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6503,22 +6503,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="463" t="s">
+      <c r="B131" s="467" t="s">
         <v>284</v>
       </c>
-      <c r="C131" s="463"/>
-      <c r="D131" s="463"/>
-      <c r="E131" s="463"/>
-      <c r="F131" s="463"/>
+      <c r="C131" s="467"/>
+      <c r="D131" s="467"/>
+      <c r="E131" s="467"/>
+      <c r="F131" s="467"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="460" t="s">
+      <c r="B132" s="462" t="s">
         <v>356</v>
       </c>
-      <c r="C132" s="460"/>
-      <c r="D132" s="460"/>
-      <c r="E132" s="460"/>
-      <c r="F132" s="460"/>
+      <c r="C132" s="462"/>
+      <c r="D132" s="462"/>
+      <c r="E132" s="462"/>
+      <c r="F132" s="462"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6694,13 +6694,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="467" t="s">
+      <c r="B149" s="461" t="s">
         <v>357</v>
       </c>
-      <c r="C149" s="460"/>
-      <c r="D149" s="460"/>
-      <c r="E149" s="460"/>
-      <c r="F149" s="460"/>
+      <c r="C149" s="462"/>
+      <c r="D149" s="462"/>
+      <c r="E149" s="462"/>
+      <c r="F149" s="462"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6737,13 +6737,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="461" t="s">
+      <c r="B158" s="463" t="s">
         <v>435</v>
       </c>
-      <c r="C158" s="461"/>
-      <c r="D158" s="461"/>
-      <c r="E158" s="461"/>
-      <c r="F158" s="461"/>
+      <c r="C158" s="463"/>
+      <c r="D158" s="463"/>
+      <c r="E158" s="463"/>
+      <c r="F158" s="463"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6751,22 +6751,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="466" t="s">
+      <c r="B161" s="460" t="s">
         <v>293</v>
       </c>
-      <c r="C161" s="466"/>
-      <c r="D161" s="466"/>
-      <c r="E161" s="466"/>
-      <c r="F161" s="466"/>
+      <c r="C161" s="460"/>
+      <c r="D161" s="460"/>
+      <c r="E161" s="460"/>
+      <c r="F161" s="460"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="466" t="s">
+      <c r="B162" s="460" t="s">
         <v>294</v>
       </c>
-      <c r="C162" s="466"/>
-      <c r="D162" s="466"/>
-      <c r="E162" s="466"/>
-      <c r="F162" s="466"/>
+      <c r="C162" s="460"/>
+      <c r="D162" s="460"/>
+      <c r="E162" s="460"/>
+      <c r="F162" s="460"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6790,18 +6790,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6818,6 +6806,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -14008,16 +14008,16 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>2.8163325762812285E-2</v>
+        <v>2.9002440512507627E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>2.8163325762812285E-2</v>
+        <v>2.9002440512507627E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>4.1502913004838556E-2</v>
+        <v>4.2739475289810862E-2</v>
       </c>
       <c r="I92" s="22" t="str">
         <f t="shared" si="38"/>
@@ -15229,18 +15229,18 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>7.5815378104586578E-2</v>
+        <v>7.8074266225864164E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>6.7309005647663248E-2</v>
+        <v>6.9314449887521432E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>6.4804171849478398E-2</v>
+        <v>6.6734985592807383E-2</v>
       </c>
       <c r="I124" s="74" t="str">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
@@ -15286,11 +15286,11 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.4442298467414467E-2</v>
+        <v>8.6958222145567032E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.0187087145500574E-2</v>
+        <v>8.2576228546113906E-2</v>
       </c>
       <c r="I125" s="22" t="str">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -19748,7 +19748,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>101.27</v>
+        <v>98.34</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19759,7 +19759,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.16655268298421899</v>
+        <v>0.17829877655836915</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -20255,7 +20255,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>101.27</v>
+        <v>98.34</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20273,14 +20273,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>393090.44266634999</v>
+        <v>381717.33121169999</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>525</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.16655268298421899</v>
+        <v>0.17829877655836915</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20288,13 +20288,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="471" t="s">
+      <c r="B12" s="474" t="s">
         <v>494</v>
       </c>
-      <c r="C12" s="471"/>
-      <c r="D12" s="471"/>
-      <c r="E12" s="471"/>
-      <c r="F12" s="471"/>
+      <c r="C12" s="474"/>
+      <c r="D12" s="474"/>
+      <c r="E12" s="474"/>
+      <c r="F12" s="474"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20479,22 +20479,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="471" t="s">
+      <c r="B29" s="474" t="s">
         <v>495</v>
       </c>
-      <c r="C29" s="471"/>
-      <c r="D29" s="471"/>
-      <c r="E29" s="471"/>
-      <c r="F29" s="471"/>
+      <c r="C29" s="474"/>
+      <c r="D29" s="474"/>
+      <c r="E29" s="474"/>
+      <c r="F29" s="474"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="472" t="s">
+      <c r="B30" s="477" t="s">
         <v>496</v>
       </c>
-      <c r="C30" s="472"/>
-      <c r="D30" s="472"/>
-      <c r="E30" s="472"/>
-      <c r="F30" s="472"/>
+      <c r="C30" s="477"/>
+      <c r="D30" s="477"/>
+      <c r="E30" s="477"/>
+      <c r="F30" s="477"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20684,10 +20684,10 @@
       <c r="B54" s="470" t="s">
         <v>503</v>
       </c>
-      <c r="C54" s="473"/>
-      <c r="D54" s="473"/>
-      <c r="E54" s="473"/>
-      <c r="F54" s="473"/>
+      <c r="C54" s="476"/>
+      <c r="D54" s="476"/>
+      <c r="E54" s="476"/>
+      <c r="F54" s="476"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20703,22 +20703,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="471" t="s">
+      <c r="B57" s="474" t="s">
         <v>504</v>
       </c>
-      <c r="C57" s="471"/>
-      <c r="D57" s="471"/>
-      <c r="E57" s="471"/>
-      <c r="F57" s="471"/>
+      <c r="C57" s="474"/>
+      <c r="D57" s="474"/>
+      <c r="E57" s="474"/>
+      <c r="F57" s="474"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="471" t="s">
+      <c r="B58" s="474" t="s">
         <v>505</v>
       </c>
-      <c r="C58" s="471"/>
-      <c r="D58" s="471"/>
-      <c r="E58" s="471"/>
-      <c r="F58" s="471"/>
+      <c r="C58" s="474"/>
+      <c r="D58" s="474"/>
+      <c r="E58" s="474"/>
+      <c r="F58" s="474"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20752,7 +20752,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>7.5815378104586578E-2</v>
+        <v>7.8074266225864164E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20762,7 +20762,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>2.8163325762812285E-2</v>
+        <v>2.9002440512507627E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>370</v>
@@ -20853,22 +20853,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="471" t="s">
+      <c r="B73" s="474" t="s">
         <v>506</v>
       </c>
-      <c r="C73" s="471"/>
-      <c r="D73" s="471"/>
-      <c r="E73" s="471"/>
-      <c r="F73" s="471"/>
+      <c r="C73" s="474"/>
+      <c r="D73" s="474"/>
+      <c r="E73" s="474"/>
+      <c r="F73" s="474"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="472" t="s">
+      <c r="B74" s="477" t="s">
         <v>476</v>
       </c>
-      <c r="C74" s="472"/>
-      <c r="D74" s="472"/>
-      <c r="E74" s="472"/>
-      <c r="F74" s="472"/>
+      <c r="C74" s="477"/>
+      <c r="D74" s="477"/>
+      <c r="E74" s="477"/>
+      <c r="F74" s="477"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -20876,13 +20876,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="471" t="s">
+      <c r="B77" s="474" t="s">
         <v>507</v>
       </c>
-      <c r="C77" s="471"/>
-      <c r="D77" s="471"/>
-      <c r="E77" s="471"/>
-      <c r="F77" s="471"/>
+      <c r="C77" s="474"/>
+      <c r="D77" s="474"/>
+      <c r="E77" s="474"/>
+      <c r="F77" s="474"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21031,33 +21031,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="471" t="s">
+      <c r="B96" s="474" t="s">
         <v>510</v>
       </c>
-      <c r="C96" s="471"/>
-      <c r="D96" s="471"/>
-      <c r="E96" s="471"/>
-      <c r="F96" s="471"/>
+      <c r="C96" s="474"/>
+      <c r="D96" s="474"/>
+      <c r="E96" s="474"/>
+      <c r="F96" s="474"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="472" t="s">
+      <c r="B97" s="477" t="s">
         <v>511</v>
       </c>
-      <c r="C97" s="472"/>
-      <c r="D97" s="472"/>
-      <c r="E97" s="472"/>
-      <c r="F97" s="472"/>
+      <c r="C97" s="477"/>
+      <c r="D97" s="477"/>
+      <c r="E97" s="477"/>
+      <c r="F97" s="477"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="472" t="s">
+      <c r="B98" s="477" t="s">
         <v>512</v>
       </c>
-      <c r="C98" s="472"/>
-      <c r="D98" s="472"/>
-      <c r="E98" s="472"/>
-      <c r="F98" s="472"/>
+      <c r="C98" s="477"/>
+      <c r="D98" s="477"/>
+      <c r="E98" s="477"/>
+      <c r="F98" s="477"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21120,23 +21120,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="471" t="s">
+      <c r="B107" s="474" t="s">
         <v>513</v>
       </c>
-      <c r="C107" s="471"/>
-      <c r="D107" s="471"/>
-      <c r="E107" s="471"/>
-      <c r="F107" s="471"/>
+      <c r="C107" s="474"/>
+      <c r="D107" s="474"/>
+      <c r="E107" s="474"/>
+      <c r="F107" s="474"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="471" t="s">
+      <c r="B108" s="474" t="s">
         <v>532</v>
       </c>
-      <c r="C108" s="471"/>
-      <c r="D108" s="471"/>
-      <c r="E108" s="471"/>
-      <c r="F108" s="471"/>
+      <c r="C108" s="474"/>
+      <c r="D108" s="474"/>
+      <c r="E108" s="474"/>
+      <c r="F108" s="474"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21180,13 +21180,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="471" t="s">
+      <c r="B114" s="474" t="s">
         <v>514</v>
       </c>
-      <c r="C114" s="471"/>
-      <c r="D114" s="471"/>
-      <c r="E114" s="471"/>
-      <c r="F114" s="471"/>
+      <c r="C114" s="474"/>
+      <c r="D114" s="474"/>
+      <c r="E114" s="474"/>
+      <c r="F114" s="474"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21350,13 +21350,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="475" t="s">
+      <c r="B127" s="472" t="s">
         <v>516</v>
       </c>
-      <c r="C127" s="475"/>
-      <c r="D127" s="475"/>
-      <c r="E127" s="475"/>
-      <c r="F127" s="475"/>
+      <c r="C127" s="472"/>
+      <c r="D127" s="472"/>
+      <c r="E127" s="472"/>
+      <c r="F127" s="472"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21369,22 +21369,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="476" t="s">
+      <c r="B131" s="473" t="s">
         <v>517</v>
       </c>
-      <c r="C131" s="476"/>
-      <c r="D131" s="476"/>
-      <c r="E131" s="476"/>
-      <c r="F131" s="476"/>
+      <c r="C131" s="473"/>
+      <c r="D131" s="473"/>
+      <c r="E131" s="473"/>
+      <c r="F131" s="473"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="471" t="s">
+      <c r="B132" s="474" t="s">
         <v>518</v>
       </c>
-      <c r="C132" s="471"/>
-      <c r="D132" s="471"/>
-      <c r="E132" s="471"/>
-      <c r="F132" s="471"/>
+      <c r="C132" s="474"/>
+      <c r="D132" s="474"/>
+      <c r="E132" s="474"/>
+      <c r="F132" s="474"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21553,13 +21553,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="477" t="s">
+      <c r="B149" s="475" t="s">
         <v>519</v>
       </c>
-      <c r="C149" s="471"/>
-      <c r="D149" s="471"/>
-      <c r="E149" s="471"/>
-      <c r="F149" s="471"/>
+      <c r="C149" s="474"/>
+      <c r="D149" s="474"/>
+      <c r="E149" s="474"/>
+      <c r="F149" s="474"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21567,13 +21567,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="473" t="s">
+      <c r="B152" s="476" t="s">
         <v>520</v>
       </c>
-      <c r="C152" s="473"/>
-      <c r="D152" s="473"/>
-      <c r="E152" s="473"/>
-      <c r="F152" s="473"/>
+      <c r="C152" s="476"/>
+      <c r="D152" s="476"/>
+      <c r="E152" s="476"/>
+      <c r="F152" s="476"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21610,22 +21610,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="474" t="s">
+      <c r="B161" s="471" t="s">
         <v>385</v>
       </c>
-      <c r="C161" s="474"/>
-      <c r="D161" s="474"/>
-      <c r="E161" s="474"/>
-      <c r="F161" s="474"/>
+      <c r="C161" s="471"/>
+      <c r="D161" s="471"/>
+      <c r="E161" s="471"/>
+      <c r="F161" s="471"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="474" t="s">
+      <c r="B162" s="471" t="s">
         <v>386</v>
       </c>
-      <c r="C162" s="474"/>
-      <c r="D162" s="474"/>
-      <c r="E162" s="474"/>
-      <c r="F162" s="474"/>
+      <c r="C162" s="471"/>
+      <c r="D162" s="471"/>
+      <c r="E162" s="471"/>
+      <c r="F162" s="471"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21649,15 +21649,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21672,12 +21669,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">
